--- a/Index.xlsx
+++ b/Index.xlsx
@@ -32,10 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="60" formatCode="#,##,##0.##"/>
     <numFmt numFmtId="61" formatCode="#,##,##0.##&quot;%&quot;"/>
+    <numFmt numFmtId="62" formatCode="0.##"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -66,10 +67,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="61" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="62" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:S90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -441,6 +443,24 @@
         <v>SMA50</v>
       </c>
       <c r="M1" t="str">
+        <v>macd_line</v>
+      </c>
+      <c r="N1" t="str">
+        <v>macd_signal</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Weekly MACD_Line</v>
+      </c>
+      <c r="P1" t="str">
+        <v>weekly macd_signal</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>MONTHLY macd_line</v>
+      </c>
+      <c r="R1" t="str">
+        <v>MONTLY macd_signal</v>
+      </c>
+      <c r="S1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -449,39 +469,57 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Nifty IT</v>
+        <v>India VIX</v>
       </c>
       <c r="C2" t="str">
-        <v>CNXIT</v>
+        <v>INDIAVIX</v>
       </c>
       <c r="D2" s="1">
-        <v>31924.1</v>
+        <v>15.68</v>
       </c>
       <c r="E2" s="2">
-        <v>3.92</v>
+        <v>6.16</v>
       </c>
       <c r="F2" s="2">
-        <v>11.72</v>
+        <v>11.52</v>
       </c>
       <c r="G2" s="2">
-        <v>15.23</v>
+        <v>16.23</v>
       </c>
       <c r="H2" s="2">
-        <v>-15.73</v>
+        <v>65.4</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>30938.67</v>
+        <v>14.84</v>
       </c>
       <c r="K2" s="1">
-        <v>29662.75</v>
+        <v>14.53</v>
       </c>
       <c r="L2" s="1">
-        <v>29801.41</v>
-      </c>
-      <c r="M2" t="str">
+        <v>12.43</v>
+      </c>
+      <c r="M2" s="3">
+        <v>-0.29</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="O2" s="3">
+        <v>-0.29</v>
+      </c>
+      <c r="P2" s="3">
+        <v>-0.75</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>-0.02</v>
+      </c>
+      <c r="R2" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="S2" t="str">
         <v/>
       </c>
     </row>
@@ -490,39 +528,57 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>CNXIT</v>
       </c>
       <c r="D3" s="1">
-        <v>8670.15</v>
+        <v>32422.5</v>
       </c>
       <c r="E3" s="2">
-        <v>2.09</v>
+        <v>2.88</v>
       </c>
       <c r="F3" s="2">
-        <v>6.11</v>
+        <v>1.56</v>
       </c>
       <c r="G3" s="2">
-        <v>8.02</v>
+        <v>17.03</v>
       </c>
       <c r="H3" s="2">
-        <v>-7.99</v>
+        <v>-14.42</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>8271.56</v>
+        <v>30874.09</v>
       </c>
       <c r="K3" s="1">
-        <v>8353.02</v>
+        <v>30440.26</v>
       </c>
       <c r="L3" s="1">
-        <v>8542.79</v>
-      </c>
-      <c r="M3" t="str">
+        <v>29827.11</v>
+      </c>
+      <c r="M3" s="3">
+        <v>-122.78</v>
+      </c>
+      <c r="N3" s="3">
+        <v>44.9</v>
+      </c>
+      <c r="O3" s="3">
+        <v>-122.78</v>
+      </c>
+      <c r="P3" s="3">
+        <v>-512.74</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>-1626.95</v>
+      </c>
+      <c r="R3" s="3">
+        <v>44.9</v>
+      </c>
+      <c r="S3" t="str">
         <v/>
       </c>
     </row>
@@ -537,33 +593,51 @@
         <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D4" s="1">
-        <v>11025.45</v>
+        <v>10988.55</v>
       </c>
       <c r="E4" s="2">
-        <v>2.04</v>
+        <v>0.64</v>
       </c>
       <c r="F4" s="2">
-        <v>5.78</v>
+        <v>-0.33</v>
       </c>
       <c r="G4" s="2">
-        <v>4.61</v>
+        <v>4.26</v>
       </c>
       <c r="H4" s="2">
-        <v>-11.68</v>
+        <v>-11.98</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>11247.1</v>
+        <v>11232.15</v>
       </c>
       <c r="K4" s="1">
-        <v>10672.83</v>
+        <v>10766.87</v>
       </c>
       <c r="L4" s="1">
-        <v>11138.62</v>
-      </c>
-      <c r="M4" t="str">
+        <v>11105.59</v>
+      </c>
+      <c r="M4" s="3">
+        <v>-106.66</v>
+      </c>
+      <c r="N4" s="3">
+        <v>-138.92</v>
+      </c>
+      <c r="O4" s="3">
+        <v>-106.66</v>
+      </c>
+      <c r="P4" s="3">
+        <v>-74.45</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>39.38</v>
+      </c>
+      <c r="R4" s="3">
+        <v>-138.92</v>
+      </c>
+      <c r="S4" t="str">
         <v/>
       </c>
     </row>
@@ -572,39 +646,57 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C5" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D5" s="1">
-        <v>1648.25</v>
+        <v>8599.15</v>
       </c>
       <c r="E5" s="2">
-        <v>1.92</v>
+        <v>0.55</v>
       </c>
       <c r="F5" s="2">
-        <v>6.11</v>
+        <v>-0.82</v>
       </c>
       <c r="G5" s="2">
-        <v>4.11</v>
+        <v>7.13</v>
       </c>
       <c r="H5" s="2">
-        <v>14.09</v>
+        <v>-8.74</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>1465.95</v>
+        <v>8261.69</v>
       </c>
       <c r="K5" s="1">
-        <v>1605.18</v>
+        <v>8427.43</v>
       </c>
       <c r="L5" s="1">
-        <v>1570.29</v>
-      </c>
-      <c r="M5" t="str">
+        <v>8539.65</v>
+      </c>
+      <c r="M5" s="3">
+        <v>72.59</v>
+      </c>
+      <c r="N5" s="3">
+        <v>-54.53</v>
+      </c>
+      <c r="O5" s="3">
+        <v>72.59</v>
+      </c>
+      <c r="P5" s="3">
+        <v>60.56</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>379.07</v>
+      </c>
+      <c r="R5" s="3">
+        <v>-54.53</v>
+      </c>
+      <c r="S5" t="str">
         <v/>
       </c>
     </row>
@@ -613,39 +705,57 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="C6" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D6" s="1">
-        <v>30481.85</v>
+        <v>190.05</v>
       </c>
       <c r="E6" s="2">
-        <v>1.62</v>
+        <v>0.37</v>
       </c>
       <c r="F6" s="2">
-        <v>4.78</v>
+        <v>1.52</v>
       </c>
       <c r="G6" s="2">
-        <v>5.06</v>
+        <v>-0.71</v>
       </c>
       <c r="H6" s="2">
-        <v>-9.43</v>
+        <v>16.13</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>31013.26</v>
+        <v>178.41</v>
       </c>
       <c r="K6" s="1">
-        <v>29561.71</v>
+        <v>190.06</v>
       </c>
       <c r="L6" s="1">
-        <v>30184.92</v>
-      </c>
-      <c r="M6" t="str">
+        <v>184.26</v>
+      </c>
+      <c r="M6" s="3">
+        <v>3.4</v>
+      </c>
+      <c r="N6" s="3">
+        <v>2.17</v>
+      </c>
+      <c r="O6" s="3">
+        <v>3.4</v>
+      </c>
+      <c r="P6" s="3">
+        <v>2.46</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>-2.58</v>
+      </c>
+      <c r="R6" s="3">
+        <v>2.17</v>
+      </c>
+      <c r="S6" t="str">
         <v/>
       </c>
     </row>
@@ -654,39 +764,57 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="C7" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D7" s="1">
-        <v>7459.4</v>
+        <v>234.35</v>
       </c>
       <c r="E7" s="2">
-        <v>1.38</v>
+        <v>0.36</v>
       </c>
       <c r="F7" s="2">
-        <v>4.2</v>
+        <v>1.52</v>
       </c>
       <c r="G7" s="2">
-        <v>5.42</v>
+        <v>-0.68</v>
       </c>
       <c r="H7" s="2">
-        <v>-1.36</v>
+        <v>17.18</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>7336.83</v>
+        <v>218.9</v>
       </c>
       <c r="K7" s="1">
-        <v>7256.57</v>
+        <v>234.35</v>
       </c>
       <c r="L7" s="1">
-        <v>7426.25</v>
-      </c>
-      <c r="M7" t="str">
+        <v>227.14</v>
+      </c>
+      <c r="M7" s="3">
+        <v>4.58</v>
+      </c>
+      <c r="N7" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="O7" s="3">
+        <v>4.58</v>
+      </c>
+      <c r="P7" s="3">
+        <v>3.44</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>-0.76</v>
+      </c>
+      <c r="R7" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="S7" t="str">
         <v/>
       </c>
     </row>
@@ -695,39 +823,57 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C8" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D8" s="1">
-        <v>202.16</v>
+        <v>30163.75</v>
       </c>
       <c r="E8" s="2">
-        <v>1.37</v>
+        <v>0.21</v>
       </c>
       <c r="F8" s="2">
-        <v>2.73</v>
+        <v>-1.04</v>
       </c>
       <c r="G8" s="2">
-        <v>2.73</v>
+        <v>3.96</v>
       </c>
       <c r="H8" s="2">
-        <v>-18.86</v>
+        <v>-10.38</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>181.36</v>
+        <v>30978.13</v>
       </c>
       <c r="K8" s="1">
-        <v>198.46</v>
+        <v>29751.22</v>
       </c>
       <c r="L8" s="1">
-        <v>193.8</v>
-      </c>
-      <c r="M8" t="str">
+        <v>30135.4</v>
+      </c>
+      <c r="M8" s="3">
+        <v>-341.3</v>
+      </c>
+      <c r="N8" s="3">
+        <v>-202.88</v>
+      </c>
+      <c r="O8" s="3">
+        <v>-341.3</v>
+      </c>
+      <c r="P8" s="3">
+        <v>-313.76</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>500.38</v>
+      </c>
+      <c r="R8" s="3">
+        <v>-202.88</v>
+      </c>
+      <c r="S8" t="str">
         <v/>
       </c>
     </row>
@@ -736,39 +882,57 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C9" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D9" s="1">
-        <v>16606</v>
+        <v>5609.55</v>
       </c>
       <c r="E9" s="2">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="2">
-        <v>5.51</v>
+        <v>-0.39</v>
       </c>
       <c r="G9" s="2">
-        <v>4.37</v>
+        <v>2.5</v>
       </c>
       <c r="H9" s="2">
-        <v>-24.51</v>
+        <v>-12.15</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>18484.56</v>
+        <v>5956.86</v>
       </c>
       <c r="K9" s="1">
-        <v>16102.19</v>
+        <v>5544.34</v>
       </c>
       <c r="L9" s="1">
-        <v>17312.09</v>
-      </c>
-      <c r="M9" t="str">
+        <v>5697.85</v>
+      </c>
+      <c r="M9" s="3">
+        <v>-114.41</v>
+      </c>
+      <c r="N9" s="3">
+        <v>-62.87</v>
+      </c>
+      <c r="O9" s="3">
+        <v>-114.41</v>
+      </c>
+      <c r="P9" s="3">
+        <v>-94.87</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>29.69</v>
+      </c>
+      <c r="R9" s="3">
+        <v>-62.87</v>
+      </c>
+      <c r="S9" t="str">
         <v/>
       </c>
     </row>
@@ -777,39 +941,57 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C10" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D10" s="1">
-        <v>10886.7</v>
+        <v>11401.45</v>
       </c>
       <c r="E10" s="2">
-        <v>1.28</v>
+        <v>0.08</v>
       </c>
       <c r="F10" s="2">
-        <v>5.46</v>
+        <v>-1.13</v>
       </c>
       <c r="G10" s="2">
-        <v>4.32</v>
+        <v>2.3</v>
       </c>
       <c r="H10" s="2">
-        <v>-25.94</v>
+        <v>-14.12</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>12253.27</v>
+        <v>12190.9</v>
       </c>
       <c r="K10" s="1">
-        <v>10559.8</v>
+        <v>11326.98</v>
       </c>
       <c r="L10" s="1">
-        <v>11357.99</v>
-      </c>
-      <c r="M10" t="str">
+        <v>11569.55</v>
+      </c>
+      <c r="M10" s="3">
+        <v>-258.01</v>
+      </c>
+      <c r="N10" s="3">
+        <v>-102.06</v>
+      </c>
+      <c r="O10" s="3">
+        <v>-258.01</v>
+      </c>
+      <c r="P10" s="3">
+        <v>-234.43</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>-123.99</v>
+      </c>
+      <c r="R10" s="3">
+        <v>-102.06</v>
+      </c>
+      <c r="S10" t="str">
         <v/>
       </c>
     </row>
@@ -818,39 +1000,57 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D11" s="1">
-        <v>13953.65</v>
+        <v>8339</v>
       </c>
       <c r="E11" s="2">
-        <v>1.21</v>
+        <v>0.03</v>
       </c>
       <c r="F11" s="2">
-        <v>4.81</v>
+        <v>-1.29</v>
       </c>
       <c r="G11" s="2">
-        <v>4.5</v>
+        <v>3.24</v>
       </c>
       <c r="H11" s="2">
-        <v>-8.76</v>
+        <v>-16.98</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>14414.52</v>
+        <v>8780.69</v>
       </c>
       <c r="K11" s="1">
-        <v>13602.59</v>
+        <v>8282.19</v>
       </c>
       <c r="L11" s="1">
-        <v>14097.66</v>
-      </c>
-      <c r="M11" t="str">
+        <v>8406.86</v>
+      </c>
+      <c r="M11" s="3">
+        <v>-157</v>
+      </c>
+      <c r="N11" s="3">
+        <v>-53.46</v>
+      </c>
+      <c r="O11" s="3">
+        <v>-157</v>
+      </c>
+      <c r="P11" s="3">
+        <v>-157.92</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>-302.34</v>
+      </c>
+      <c r="R11" s="3">
+        <v>-53.46</v>
+      </c>
+      <c r="S11" t="str">
         <v/>
       </c>
     </row>
@@ -859,39 +1059,57 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C12" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D12" s="1">
-        <v>5472</v>
+        <v>202.16</v>
       </c>
       <c r="E12" s="2">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="H12" s="2">
-        <v>-6.62</v>
+        <v>-18.86</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>5555.32</v>
+        <v>180.89</v>
       </c>
       <c r="K12" s="1">
-        <v>5365.66</v>
+        <v>199.68</v>
       </c>
       <c r="L12" s="1">
-        <v>5544.39</v>
-      </c>
-      <c r="M12" t="str">
+        <v>194.5</v>
+      </c>
+      <c r="M12" s="3">
+        <v>11.77</v>
+      </c>
+      <c r="N12" s="3">
+        <v>2.55</v>
+      </c>
+      <c r="O12" s="3">
+        <v>11.77</v>
+      </c>
+      <c r="P12" s="3">
+        <v>5.66</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>5.31</v>
+      </c>
+      <c r="R12" s="3">
+        <v>2.55</v>
+      </c>
+      <c r="S12" t="str">
         <v/>
       </c>
     </row>
@@ -900,39 +1118,57 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C13" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D13" s="1">
-        <v>5631.45</v>
+        <v>13826.6</v>
       </c>
       <c r="E13" s="2">
-        <v>1.08</v>
+        <v>-0.01</v>
       </c>
       <c r="F13" s="2">
-        <v>3.9</v>
+        <v>-0.91</v>
       </c>
       <c r="G13" s="2">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="H13" s="2">
-        <v>-11.81</v>
+        <v>-9.59</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>5964.29</v>
+        <v>14401.1</v>
       </c>
       <c r="K13" s="1">
-        <v>5514.59</v>
+        <v>13676.81</v>
       </c>
       <c r="L13" s="1">
-        <v>5715.55</v>
-      </c>
-      <c r="M13" t="str">
+        <v>14058.48</v>
+      </c>
+      <c r="M13" s="3">
+        <v>-209.79</v>
+      </c>
+      <c r="N13" s="3">
+        <v>-154.97</v>
+      </c>
+      <c r="O13" s="3">
+        <v>-209.79</v>
+      </c>
+      <c r="P13" s="3">
+        <v>-159.4</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>-529.71</v>
+      </c>
+      <c r="R13" s="3">
+        <v>-154.97</v>
+      </c>
+      <c r="S13" t="str">
         <v/>
       </c>
     </row>
@@ -941,39 +1177,57 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>NIFTY100ESG</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C14" t="str">
-        <v>NIFTY100ESG</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D14" s="1">
-        <v>4789.1</v>
+        <v>1446.87</v>
       </c>
       <c r="E14" s="2">
-        <v>0.96</v>
+        <v>-0.05</v>
       </c>
       <c r="F14" s="2">
-        <v>3.26</v>
+        <v>-0.01</v>
       </c>
       <c r="G14" s="2">
-        <v>2.25</v>
+        <v>-0.48</v>
       </c>
       <c r="H14" s="2">
-        <v>-7.57</v>
+        <v>1.56</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>4921.97</v>
+        <v>1440.68</v>
       </c>
       <c r="K14" s="1">
-        <v>4708.9</v>
+        <v>1449.83</v>
       </c>
       <c r="L14" s="1">
-        <v>4892.88</v>
-      </c>
-      <c r="M14" t="str">
+        <v>1458.76</v>
+      </c>
+      <c r="M14" s="3">
+        <v>4.31</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-2.6</v>
+      </c>
+      <c r="O14" s="3">
+        <v>4.31</v>
+      </c>
+      <c r="P14" s="3">
+        <v>7.35</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>29.24</v>
+      </c>
+      <c r="R14" s="3">
+        <v>-2.6</v>
+      </c>
+      <c r="S14" t="str">
         <v/>
       </c>
     </row>
@@ -982,39 +1236,57 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>NIFTYMETAL</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="C15" t="str">
-        <v>NIFTYMETAL</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="D15" s="1">
-        <v>12133.2</v>
+        <v>1307.62</v>
       </c>
       <c r="E15" s="2">
-        <v>0.95</v>
+        <v>-0.07</v>
       </c>
       <c r="F15" s="2">
-        <v>1.1</v>
+        <v>-0.01</v>
       </c>
       <c r="G15" s="2">
-        <v>-4.92</v>
+        <v>-0.6</v>
       </c>
       <c r="H15" s="2">
-        <v>8.65</v>
+        <v>0.73</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>12466.56</v>
+        <v>1307.95</v>
       </c>
       <c r="K15" s="1">
-        <v>12193.58</v>
+        <v>1311.03</v>
       </c>
       <c r="L15" s="1">
-        <v>12913.53</v>
-      </c>
-      <c r="M15" t="str">
+        <v>1322.5</v>
+      </c>
+      <c r="M15" s="3">
+        <v>2.29</v>
+      </c>
+      <c r="N15" s="3">
+        <v>-3.41</v>
+      </c>
+      <c r="O15" s="3">
+        <v>2.29</v>
+      </c>
+      <c r="P15" s="3">
+        <v>5.72</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>24.09</v>
+      </c>
+      <c r="R15" s="3">
+        <v>-3.41</v>
+      </c>
+      <c r="S15" t="str">
         <v/>
       </c>
     </row>
@@ -1023,39 +1295,57 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D16" s="1">
-        <v>8448.2</v>
+        <v>10536.3</v>
       </c>
       <c r="E16" s="2">
-        <v>0.83</v>
+        <v>-0.08</v>
       </c>
       <c r="F16" s="2">
-        <v>3.03</v>
+        <v>-0.19</v>
       </c>
       <c r="G16" s="2">
-        <v>4.59</v>
+        <v>-0.74</v>
       </c>
       <c r="H16" s="2">
-        <v>-15.89</v>
+        <v>-13.86</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>8797.42</v>
+        <v>11308.09</v>
       </c>
       <c r="K16" s="1">
-        <v>8254.66</v>
+        <v>10523.07</v>
       </c>
       <c r="L16" s="1">
-        <v>8423.81</v>
-      </c>
-      <c r="M16" t="str">
+        <v>10905.06</v>
+      </c>
+      <c r="M16" s="3">
+        <v>-218</v>
+      </c>
+      <c r="N16" s="3">
+        <v>-142.5</v>
+      </c>
+      <c r="O16" s="3">
+        <v>-218</v>
+      </c>
+      <c r="P16" s="3">
+        <v>-158.8</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>80.45</v>
+      </c>
+      <c r="R16" s="3">
+        <v>-142.5</v>
+      </c>
+      <c r="S16" t="str">
         <v/>
       </c>
     </row>
@@ -1064,39 +1354,57 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C17" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D17" s="1">
-        <v>3865.55</v>
+        <v>1600.86</v>
       </c>
       <c r="E17" s="2">
-        <v>0.78</v>
+        <v>-0.11</v>
       </c>
       <c r="F17" s="2">
-        <v>3.06</v>
+        <v>-0.04</v>
       </c>
       <c r="G17" s="2">
-        <v>2.2</v>
+        <v>-0.38</v>
       </c>
       <c r="H17" s="2">
-        <v>-11.2</v>
+        <v>2.17</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>4042.82</v>
+        <v>1586.5</v>
       </c>
       <c r="K17" s="1">
-        <v>3801.94</v>
+        <v>1603.81</v>
       </c>
       <c r="L17" s="1">
-        <v>3945.65</v>
-      </c>
-      <c r="M17" t="str">
+        <v>1609.22</v>
+      </c>
+      <c r="M17" s="3">
+        <v>6.91</v>
+      </c>
+      <c r="N17" s="3">
+        <v>-1.42</v>
+      </c>
+      <c r="O17" s="3">
+        <v>6.91</v>
+      </c>
+      <c r="P17" s="3">
+        <v>9.36</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>34.86</v>
+      </c>
+      <c r="R17" s="3">
+        <v>-1.42</v>
+      </c>
+      <c r="S17" t="str">
         <v/>
       </c>
     </row>
@@ -1105,39 +1413,57 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C18" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D18" s="1">
-        <v>25768.5</v>
+        <v>18714.9</v>
       </c>
       <c r="E18" s="2">
-        <v>0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="F18" s="2">
-        <v>3.65</v>
+        <v>-1.08</v>
       </c>
       <c r="G18" s="2">
-        <v>-2</v>
+        <v>-0.38</v>
       </c>
       <c r="H18" s="2">
-        <v>-8.59</v>
+        <v>-11.43</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>26965.55</v>
+        <v>19879.38</v>
       </c>
       <c r="K18" s="1">
-        <v>25497</v>
+        <v>18763.95</v>
       </c>
       <c r="L18" s="1">
-        <v>27512.17</v>
-      </c>
-      <c r="M18" t="str">
+        <v>19544.08</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-297.59</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-272.22</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-297.59</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-145.05</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>758.22</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-272.22</v>
+      </c>
+      <c r="S18" t="str">
         <v/>
       </c>
     </row>
@@ -1146,39 +1472,57 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C19" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D19" s="1">
-        <v>25735.85</v>
+        <v>3278.79</v>
       </c>
       <c r="E19" s="2">
-        <v>0.71</v>
+        <v>-0.17</v>
       </c>
       <c r="F19" s="2">
-        <v>0.78</v>
+        <v>-0.08</v>
       </c>
       <c r="G19" s="2">
-        <v>-1.96</v>
+        <v>-0.9</v>
       </c>
       <c r="H19" s="2">
-        <v>14.15</v>
+        <v>1.74</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>23581.11</v>
+        <v>3279.88</v>
       </c>
       <c r="K19" s="1">
-        <v>25832.32</v>
+        <v>3287.81</v>
       </c>
       <c r="L19" s="1">
-        <v>26194.26</v>
-      </c>
-      <c r="M19" t="str">
+        <v>3322.72</v>
+      </c>
+      <c r="M19" s="3">
+        <v>7.86</v>
+      </c>
+      <c r="N19" s="3">
+        <v>-10.9</v>
+      </c>
+      <c r="O19" s="3">
+        <v>7.86</v>
+      </c>
+      <c r="P19" s="3">
+        <v>18.02</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>139.63</v>
+      </c>
+      <c r="R19" s="3">
+        <v>-10.9</v>
+      </c>
+      <c r="S19" t="str">
         <v/>
       </c>
     </row>
@@ -1187,39 +1531,57 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D20" s="1">
-        <v>8094.95</v>
+        <v>1262.52</v>
       </c>
       <c r="E20" s="2">
-        <v>0.67</v>
+        <v>-0.17</v>
       </c>
       <c r="F20" s="2">
-        <v>-0.39</v>
+        <v>-0.14</v>
       </c>
       <c r="G20" s="2">
-        <v>0.98</v>
+        <v>-0.84</v>
       </c>
       <c r="H20" s="2">
-        <v>-5.14</v>
+        <v>0.08</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>8575.3</v>
+        <v>1268.34</v>
       </c>
       <c r="K20" s="1">
-        <v>8091.68</v>
+        <v>1267.59</v>
       </c>
       <c r="L20" s="1">
-        <v>8383.49</v>
-      </c>
-      <c r="M20" t="str">
+        <v>1280.91</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-3.99</v>
+      </c>
+      <c r="O20" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="P20" s="3">
+        <v>4.94</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>21.3</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-3.99</v>
+      </c>
+      <c r="S20" t="str">
         <v/>
       </c>
     </row>
@@ -1228,39 +1590,57 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D21" s="1">
-        <v>11532.3</v>
+        <v>7360</v>
       </c>
       <c r="E21" s="2">
-        <v>0.66</v>
+        <v>-0.18</v>
       </c>
       <c r="F21" s="2">
-        <v>3.43</v>
+        <v>-1.33</v>
       </c>
       <c r="G21" s="2">
-        <v>3.47</v>
+        <v>4.01</v>
       </c>
       <c r="H21" s="2">
-        <v>-13.13</v>
+        <v>-2.67</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>12209.27</v>
+        <v>7335.66</v>
       </c>
       <c r="K21" s="1">
-        <v>11292.29</v>
+        <v>7292.77</v>
       </c>
       <c r="L21" s="1">
-        <v>11598.77</v>
-      </c>
-      <c r="M21" t="str">
+        <v>7411.18</v>
+      </c>
+      <c r="M21" s="3">
+        <v>1.91</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-48.28</v>
+      </c>
+      <c r="O21" s="3">
+        <v>1.91</v>
+      </c>
+      <c r="P21" s="3">
+        <v>31.86</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>472.8</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-48.28</v>
+      </c>
+      <c r="S21" t="str">
         <v/>
       </c>
     </row>
@@ -1269,39 +1649,57 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>NIFTY</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C22" t="str">
-        <v>NIFTY</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D22" s="1">
-        <v>23146.15</v>
+        <v>25565.9</v>
       </c>
       <c r="E22" s="2">
-        <v>0.65</v>
+        <v>-0.19</v>
       </c>
       <c r="F22" s="2">
-        <v>2.78</v>
+        <v>-0.84</v>
       </c>
       <c r="G22" s="2">
-        <v>2.32</v>
+        <v>-3.3</v>
       </c>
       <c r="H22" s="2">
-        <v>-11.42</v>
+        <v>12.51</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>24184.17</v>
+        <v>24346.94</v>
       </c>
       <c r="K22" s="1">
-        <v>22777.87</v>
+        <v>25889.9</v>
       </c>
       <c r="L22" s="1">
-        <v>23549.21</v>
-      </c>
-      <c r="M22" t="str">
+        <v>26485.28</v>
+      </c>
+      <c r="M22" s="3">
+        <v>596.89</v>
+      </c>
+      <c r="N22" s="3">
+        <v>-167.21</v>
+      </c>
+      <c r="O22" s="3">
+        <v>596.89</v>
+      </c>
+      <c r="P22" s="3">
+        <v>796.4</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>1772.23</v>
+      </c>
+      <c r="R22" s="3">
+        <v>-167.21</v>
+      </c>
+      <c r="S22" t="str">
         <v/>
       </c>
     </row>
@@ -1310,39 +1708,57 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D23" s="1">
-        <v>24133.1</v>
+        <v>3286.75</v>
       </c>
       <c r="E23" s="2">
-        <v>0.61</v>
+        <v>-0.22</v>
       </c>
       <c r="F23" s="2">
-        <v>2.49</v>
+        <v>-0.5</v>
       </c>
       <c r="G23" s="2">
-        <v>1.68</v>
+        <v>-1.05</v>
       </c>
       <c r="H23" s="2">
-        <v>-9.58</v>
+        <v>1.38</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>25081.04</v>
+        <v>3294.91</v>
       </c>
       <c r="K23" s="1">
-        <v>23822.48</v>
+        <v>3299.5</v>
       </c>
       <c r="L23" s="1">
-        <v>24674.54</v>
-      </c>
-      <c r="M23" t="str">
+        <v>3351.83</v>
+      </c>
+      <c r="M23" s="3">
+        <v>7.67</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-17.07</v>
+      </c>
+      <c r="O23" s="3">
+        <v>7.67</v>
+      </c>
+      <c r="P23" s="3">
+        <v>21.52</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>136.55</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-17.07</v>
+      </c>
+      <c r="S23" t="str">
         <v/>
       </c>
     </row>
@@ -1351,39 +1767,57 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C24" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D24" s="1">
-        <v>19470.45</v>
+        <v>3063.81</v>
       </c>
       <c r="E24" s="2">
-        <v>0.53</v>
+        <v>-0.31</v>
       </c>
       <c r="F24" s="2">
-        <v>3.22</v>
+        <v>-0.4</v>
       </c>
       <c r="G24" s="2">
-        <v>2.78</v>
+        <v>-1.3</v>
       </c>
       <c r="H24" s="2">
-        <v>-9.06</v>
+        <v>0.37</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>20133.44</v>
+        <v>3085.9</v>
       </c>
       <c r="K24" s="1">
-        <v>19192.25</v>
+        <v>3077.27</v>
       </c>
       <c r="L24" s="1">
-        <v>19927.12</v>
-      </c>
-      <c r="M24" t="str">
+        <v>3121.15</v>
+      </c>
+      <c r="M24" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="N24" s="3">
+        <v>-13.78</v>
+      </c>
+      <c r="O24" s="3">
+        <v>2.74</v>
+      </c>
+      <c r="P24" s="3">
+        <v>13.99</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>118.74</v>
+      </c>
+      <c r="R24" s="3">
+        <v>-13.78</v>
+      </c>
+      <c r="S24" t="str">
         <v/>
       </c>
     </row>
@@ -1392,39 +1826,57 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D25" s="1">
-        <v>7564.7</v>
+        <v>15507.15</v>
       </c>
       <c r="E25" s="2">
-        <v>0.51</v>
+        <v>-0.32</v>
       </c>
       <c r="F25" s="2">
-        <v>1.15</v>
+        <v>-1.12</v>
       </c>
       <c r="G25" s="2">
-        <v>-1.81</v>
+        <v>-3.91</v>
       </c>
       <c r="H25" s="2">
-        <v>-12.08</v>
+        <v>5.92</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>7702.97</v>
+        <v>15436.28</v>
       </c>
       <c r="K25" s="1">
-        <v>7539.99</v>
+        <v>15759.68</v>
       </c>
       <c r="L25" s="1">
-        <v>7809.65</v>
-      </c>
-      <c r="M25" t="str">
+        <v>16373.32</v>
+      </c>
+      <c r="M25" s="3">
+        <v>170.72</v>
+      </c>
+      <c r="N25" s="3">
+        <v>-197.67</v>
+      </c>
+      <c r="O25" s="3">
+        <v>170.72</v>
+      </c>
+      <c r="P25" s="3">
+        <v>340.41</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>978.42</v>
+      </c>
+      <c r="R25" s="3">
+        <v>-197.67</v>
+      </c>
+      <c r="S25" t="str">
         <v/>
       </c>
     </row>
@@ -1433,39 +1885,57 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C26" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D26" s="1">
-        <v>31199.8</v>
+        <v>5407.3</v>
       </c>
       <c r="E26" s="2">
-        <v>0.48</v>
+        <v>-0.32</v>
       </c>
       <c r="F26" s="2">
-        <v>2.24</v>
+        <v>-1.18</v>
       </c>
       <c r="G26" s="2">
-        <v>0.96</v>
+        <v>1.63</v>
       </c>
       <c r="H26" s="2">
-        <v>-6.39</v>
+        <v>-7.73</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>32387.39</v>
+        <v>5551.02</v>
       </c>
       <c r="K26" s="1">
-        <v>30892.27</v>
+        <v>5382.02</v>
       </c>
       <c r="L26" s="1">
-        <v>32162.78</v>
-      </c>
-      <c r="M26" t="str">
+        <v>5530.09</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-42.26</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-54.85</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-42.26</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-16.83</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>190.86</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-54.85</v>
+      </c>
+      <c r="S26" t="str">
         <v/>
       </c>
     </row>
@@ -1474,39 +1944,57 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY</v>
       </c>
       <c r="C27" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY</v>
       </c>
       <c r="D27" s="1">
-        <v>13337.4</v>
+        <v>22811.35</v>
       </c>
       <c r="E27" s="2">
-        <v>0.47</v>
+        <v>-0.34</v>
       </c>
       <c r="F27" s="2">
-        <v>2.1</v>
+        <v>-1.45</v>
       </c>
       <c r="G27" s="2">
-        <v>1.27</v>
+        <v>0.84</v>
       </c>
       <c r="H27" s="2">
-        <v>-8.23</v>
+        <v>-12.7</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>13813.16</v>
+        <v>24152.75</v>
       </c>
       <c r="K27" s="1">
-        <v>13207</v>
+        <v>22800.48</v>
       </c>
       <c r="L27" s="1">
-        <v>13702.55</v>
-      </c>
-      <c r="M27" t="str">
+        <v>23479.08</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-384.19</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-253.14</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-384.19</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-274.8</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>194.04</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-253.14</v>
+      </c>
+      <c r="S27" t="str">
         <v/>
       </c>
     </row>
@@ -1515,39 +2003,57 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C28" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D28" s="1">
-        <v>68988.6</v>
+        <v>2599.44</v>
       </c>
       <c r="E28" s="2">
-        <v>0.46</v>
+        <v>-0.34</v>
       </c>
       <c r="F28" s="2">
-        <v>1.21</v>
+        <v>-0.45</v>
       </c>
       <c r="G28" s="2">
-        <v>-1.09</v>
+        <v>-1.47</v>
       </c>
       <c r="H28" s="2">
-        <v>-0.54</v>
+        <v>-0.48</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>70049.24</v>
+        <v>2632.39</v>
       </c>
       <c r="K28" s="1">
-        <v>69030.68</v>
+        <v>2612.27</v>
       </c>
       <c r="L28" s="1">
-        <v>72073.22</v>
-      </c>
-      <c r="M28" t="str">
+        <v>2651.46</v>
+      </c>
+      <c r="M28" s="3">
+        <v>-1.92</v>
+      </c>
+      <c r="N28" s="3">
+        <v>-12.45</v>
+      </c>
+      <c r="O28" s="3">
+        <v>-1.92</v>
+      </c>
+      <c r="P28" s="3">
+        <v>7.47</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>89.89</v>
+      </c>
+      <c r="R28" s="3">
+        <v>-12.45</v>
+      </c>
+      <c r="S28" t="str">
         <v/>
       </c>
     </row>
@@ -1556,39 +2062,57 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C29" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D29" s="1">
-        <v>8725.6</v>
+        <v>2970.32</v>
       </c>
       <c r="E29" s="2">
-        <v>0.46</v>
+        <v>-0.35</v>
       </c>
       <c r="F29" s="2">
-        <v>1.76</v>
+        <v>-0.42</v>
       </c>
       <c r="G29" s="2">
-        <v>-0.1</v>
+        <v>-1.45</v>
       </c>
       <c r="H29" s="2">
-        <v>-9.26</v>
+        <v>0.12</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>9239.97</v>
+        <v>3001.36</v>
       </c>
       <c r="K29" s="1">
-        <v>8664.83</v>
+        <v>2985.03</v>
       </c>
       <c r="L29" s="1">
-        <v>9063.66</v>
-      </c>
-      <c r="M29" t="str">
+        <v>3029.09</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="N29" s="3">
+        <v>-13.9</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P29" s="3">
+        <v>11.42</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>114.75</v>
+      </c>
+      <c r="R29" s="3">
+        <v>-13.9</v>
+      </c>
+      <c r="S29" t="str">
         <v/>
       </c>
     </row>
@@ -1597,39 +2121,57 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D30" s="1">
-        <v>32849.65</v>
+        <v>8634</v>
       </c>
       <c r="E30" s="2">
-        <v>0.45</v>
+        <v>-0.38</v>
       </c>
       <c r="F30" s="2">
-        <v>1.73</v>
+        <v>-1.05</v>
       </c>
       <c r="G30" s="2">
-        <v>-0.03</v>
+        <v>-1.14</v>
       </c>
       <c r="H30" s="2">
-        <v>-3.26</v>
+        <v>-10.22</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>33708.72</v>
+        <v>9231.06</v>
       </c>
       <c r="K30" s="1">
-        <v>32699.86</v>
+        <v>8659.47</v>
       </c>
       <c r="L30" s="1">
-        <v>34128.27</v>
-      </c>
-      <c r="M30" t="str">
+        <v>9030.52</v>
+      </c>
+      <c r="M30" s="3">
+        <v>-160.89</v>
+      </c>
+      <c r="N30" s="3">
+        <v>-133.7</v>
+      </c>
+      <c r="O30" s="3">
+        <v>-160.89</v>
+      </c>
+      <c r="P30" s="3">
+        <v>-79.31</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>270.39</v>
+      </c>
+      <c r="R30" s="3">
+        <v>-133.7</v>
+      </c>
+      <c r="S30" t="str">
         <v/>
       </c>
     </row>
@@ -1638,39 +2180,57 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D31" s="1">
-        <v>11054.65</v>
+        <v>838.77</v>
       </c>
       <c r="E31" s="2">
-        <v>0.45</v>
+        <v>-0.39</v>
       </c>
       <c r="F31" s="2">
-        <v>1.39</v>
+        <v>-0.56</v>
       </c>
       <c r="G31" s="2">
-        <v>-0.16</v>
+        <v>-1.92</v>
       </c>
       <c r="H31" s="2">
-        <v>-10.05</v>
+        <v>-5.91</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>11517.11</v>
+        <v>874.12</v>
       </c>
       <c r="K31" s="1">
-        <v>10992.09</v>
+        <v>844.31</v>
       </c>
       <c r="L31" s="1">
-        <v>11558.39</v>
-      </c>
-      <c r="M31" t="str">
+        <v>862.31</v>
+      </c>
+      <c r="M31" s="3">
+        <v>-8.71</v>
+      </c>
+      <c r="N31" s="3">
+        <v>-5.87</v>
+      </c>
+      <c r="O31" s="3">
+        <v>-8.71</v>
+      </c>
+      <c r="P31" s="3">
+        <v>-5.63</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>-17.16</v>
+      </c>
+      <c r="R31" s="3">
+        <v>-5.87</v>
+      </c>
+      <c r="S31" t="str">
         <v/>
       </c>
     </row>
@@ -1679,39 +2239,57 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>Nifty Total Market</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C32" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D32" s="1">
-        <v>12601.8</v>
+        <v>3796.9</v>
       </c>
       <c r="E32" s="2">
-        <v>0.42</v>
+        <v>-0.42</v>
       </c>
       <c r="F32" s="2">
-        <v>1.8</v>
+        <v>-1.78</v>
       </c>
       <c r="G32" s="2">
-        <v>0.77</v>
+        <v>0.39</v>
       </c>
       <c r="H32" s="2">
-        <v>-5.91</v>
+        <v>-12.78</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>12877.27</v>
+        <v>4037.51</v>
       </c>
       <c r="K32" s="1">
-        <v>12513.79</v>
+        <v>3802.67</v>
       </c>
       <c r="L32" s="1">
-        <v>12952.54</v>
-      </c>
-      <c r="M32" t="str">
+        <v>3932.4</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-65.6</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-47.65</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-65.6</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-42.41</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>126.58</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-47.65</v>
+      </c>
+      <c r="S32" t="str">
         <v/>
       </c>
     </row>
@@ -1720,39 +2298,57 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D33" s="1">
-        <v>22270.05</v>
+        <v>3471.25</v>
       </c>
       <c r="E33" s="2">
-        <v>0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="F33" s="2">
-        <v>1.84</v>
+        <v>-0.47</v>
       </c>
       <c r="G33" s="2">
-        <v>0.9</v>
+        <v>-1.44</v>
       </c>
       <c r="H33" s="2">
-        <v>-6.71</v>
+        <v>-0.62</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>22872.03</v>
+        <v>3495.57</v>
       </c>
       <c r="K33" s="1">
-        <v>22103.83</v>
+        <v>3487.63</v>
       </c>
       <c r="L33" s="1">
-        <v>22902.88</v>
-      </c>
-      <c r="M33" t="str">
+        <v>3537.21</v>
+      </c>
+      <c r="M33" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-14.86</v>
+      </c>
+      <c r="O33" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="P33" s="3">
+        <v>15.47</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>119.04</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-14.86</v>
+      </c>
+      <c r="S33" t="str">
         <v/>
       </c>
     </row>
@@ -1761,39 +2357,57 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C34" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D34" s="1">
-        <v>18918.7</v>
+        <v>19156.1</v>
       </c>
       <c r="E34" s="2">
-        <v>0.4</v>
+        <v>-0.46</v>
       </c>
       <c r="F34" s="2">
-        <v>1.57</v>
+        <v>-1.61</v>
       </c>
       <c r="G34" s="2">
-        <v>0.71</v>
+        <v>1.12</v>
       </c>
       <c r="H34" s="2">
-        <v>-10.47</v>
+        <v>-10.53</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>19902.44</v>
+        <v>20111.69</v>
       </c>
       <c r="K34" s="1">
-        <v>18781.78</v>
+        <v>19193.39</v>
       </c>
       <c r="L34" s="1">
-        <v>19622.98</v>
-      </c>
-      <c r="M34" t="str">
+        <v>19857.23</v>
+      </c>
+      <c r="M34" s="3">
+        <v>-265.24</v>
+      </c>
+      <c r="N34" s="3">
+        <v>-231.83</v>
+      </c>
+      <c r="O34" s="3">
+        <v>-265.24</v>
+      </c>
+      <c r="P34" s="3">
+        <v>-138.8</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>500.78</v>
+      </c>
+      <c r="R34" s="3">
+        <v>-231.83</v>
+      </c>
+      <c r="S34" t="str">
         <v/>
       </c>
     </row>
@@ -1802,39 +2416,57 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D35" s="1">
-        <v>15174.1</v>
+        <v>8251.5</v>
       </c>
       <c r="E35" s="2">
-        <v>0.35</v>
+        <v>-0.51</v>
       </c>
       <c r="F35" s="2">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="G35" s="2">
-        <v>-1.81</v>
+        <v>2.94</v>
       </c>
       <c r="H35" s="2">
-        <v>-1.55</v>
+        <v>-3.3</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>15634.71</v>
+        <v>8575.14</v>
       </c>
       <c r="K35" s="1">
-        <v>15186.09</v>
+        <v>8150.85</v>
       </c>
       <c r="L35" s="1">
-        <v>15994.37</v>
-      </c>
-      <c r="M35" t="str">
+        <v>8364.1</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-75.54</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-78.63</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-75.54</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-29.76</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>575.37</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-78.63</v>
+      </c>
+      <c r="S35" t="str">
         <v/>
       </c>
     </row>
@@ -1843,39 +2475,57 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D36" s="1">
-        <v>47681.2</v>
+        <v>30743.2</v>
       </c>
       <c r="E36" s="2">
-        <v>0.33</v>
+        <v>-0.53</v>
       </c>
       <c r="F36" s="2">
-        <v>0.86</v>
+        <v>-1.46</v>
       </c>
       <c r="G36" s="2">
-        <v>-0.37</v>
+        <v>-0.52</v>
       </c>
       <c r="H36" s="2">
-        <v>8.4</v>
+        <v>-7.76</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>44891.24</v>
+        <v>32364.85</v>
       </c>
       <c r="K36" s="1">
-        <v>47800.66</v>
+        <v>30867.57</v>
       </c>
       <c r="L36" s="1">
-        <v>48474.38</v>
-      </c>
-      <c r="M36" t="str">
+        <v>32046.75</v>
+      </c>
+      <c r="M36" s="3">
+        <v>-376.58</v>
+      </c>
+      <c r="N36" s="3">
+        <v>-419.77</v>
+      </c>
+      <c r="O36" s="3">
+        <v>-376.58</v>
+      </c>
+      <c r="P36" s="3">
+        <v>-112.38</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>1837.58</v>
+      </c>
+      <c r="R36" s="3">
+        <v>-419.77</v>
+      </c>
+      <c r="S36" t="str">
         <v/>
       </c>
     </row>
@@ -1884,39 +2534,57 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C37" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D37" s="1">
-        <v>13630.9</v>
+        <v>4711.05</v>
       </c>
       <c r="E37" s="2">
-        <v>0.33</v>
+        <v>-0.55</v>
       </c>
       <c r="F37" s="2">
-        <v>1.1</v>
+        <v>-1.63</v>
       </c>
       <c r="G37" s="2">
-        <v>-0.87</v>
+        <v>0.58</v>
       </c>
       <c r="H37" s="2">
-        <v>-5.81</v>
+        <v>-9.08</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>14163.5</v>
+        <v>4917.65</v>
       </c>
       <c r="K37" s="1">
-        <v>13614.35</v>
+        <v>4713.48</v>
       </c>
       <c r="L37" s="1">
-        <v>14220.4</v>
-      </c>
-      <c r="M37" t="str">
+        <v>4876.33</v>
+      </c>
+      <c r="M37" s="3">
+        <v>-49.2</v>
+      </c>
+      <c r="N37" s="3">
+        <v>-59</v>
+      </c>
+      <c r="O37" s="3">
+        <v>-49.2</v>
+      </c>
+      <c r="P37" s="3">
+        <v>-16.96</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>221.41</v>
+      </c>
+      <c r="R37" s="3">
+        <v>-59</v>
+      </c>
+      <c r="S37" t="str">
         <v/>
       </c>
     </row>
@@ -1925,39 +2593,57 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D38" s="1">
-        <v>9099.5</v>
+        <v>23762.45</v>
       </c>
       <c r="E38" s="2">
-        <v>0.33</v>
+        <v>-0.56</v>
       </c>
       <c r="F38" s="2">
-        <v>1.97</v>
+        <v>-1.54</v>
       </c>
       <c r="G38" s="2">
-        <v>-2.26</v>
+        <v>0.12</v>
       </c>
       <c r="H38" s="2">
-        <v>-4.37</v>
+        <v>-10.97</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>9766.59</v>
+        <v>25053.96</v>
       </c>
       <c r="K38" s="1">
-        <v>9074.94</v>
+        <v>23822.42</v>
       </c>
       <c r="L38" s="1">
-        <v>9559.98</v>
-      </c>
-      <c r="M38" t="str">
+        <v>24598.3</v>
+      </c>
+      <c r="M38" s="3">
+        <v>-338.56</v>
+      </c>
+      <c r="N38" s="3">
+        <v>-278.91</v>
+      </c>
+      <c r="O38" s="3">
+        <v>-338.56</v>
+      </c>
+      <c r="P38" s="3">
+        <v>-195.17</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>333.97</v>
+      </c>
+      <c r="R38" s="3">
+        <v>-278.91</v>
+      </c>
+      <c r="S38" t="str">
         <v/>
       </c>
     </row>
@@ -1966,39 +2652,57 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C39" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D39" s="1">
-        <v>3487.27</v>
+        <v>43720.7</v>
       </c>
       <c r="E39" s="2">
-        <v>0.31</v>
+        <v>-0.58</v>
       </c>
       <c r="F39" s="2">
-        <v>-0.5</v>
+        <v>-2.01</v>
       </c>
       <c r="G39" s="2">
-        <v>-0.98</v>
+        <v>-1.77</v>
       </c>
       <c r="H39" s="2">
-        <v>-0.16</v>
+        <v>-21.19</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>3495.58</v>
+        <v>49030.47</v>
       </c>
       <c r="K39" s="1">
-        <v>3492.26</v>
+        <v>44453.2</v>
       </c>
       <c r="L39" s="1">
-        <v>3540.78</v>
-      </c>
-      <c r="M39" t="str">
+        <v>46007.7</v>
+      </c>
+      <c r="M39" s="3">
+        <v>-1619.09</v>
+      </c>
+      <c r="N39" s="3">
+        <v>-503.4</v>
+      </c>
+      <c r="O39" s="3">
+        <v>-1619.09</v>
+      </c>
+      <c r="P39" s="3">
+        <v>-1344.9</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>-2136.87</v>
+      </c>
+      <c r="R39" s="3">
+        <v>-503.4</v>
+      </c>
+      <c r="S39" t="str">
         <v/>
       </c>
     </row>
@@ -2007,39 +2711,57 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C40" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D40" s="1">
-        <v>15823.2</v>
+        <v>24581.6</v>
       </c>
       <c r="E40" s="2">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="F40" s="2">
-        <v>1.49</v>
+        <v>-1.33</v>
       </c>
       <c r="G40" s="2">
-        <v>0.46</v>
+        <v>-2.53</v>
       </c>
       <c r="H40" s="2">
-        <v>-4.02</v>
+        <v>-9.22</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>16033.47</v>
+        <v>26266.8</v>
       </c>
       <c r="K40" s="1">
-        <v>15754.48</v>
+        <v>24835.34</v>
       </c>
       <c r="L40" s="1">
-        <v>16300.25</v>
-      </c>
-      <c r="M40" t="str">
+        <v>26187.65</v>
+      </c>
+      <c r="M40" s="3">
+        <v>-344.79</v>
+      </c>
+      <c r="N40" s="3">
+        <v>-457.75</v>
+      </c>
+      <c r="O40" s="3">
+        <v>-344.79</v>
+      </c>
+      <c r="P40" s="3">
+        <v>-67.01</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>1146.92</v>
+      </c>
+      <c r="R40" s="3">
+        <v>-457.75</v>
+      </c>
+      <c r="S40" t="str">
         <v/>
       </c>
     </row>
@@ -2048,39 +2770,57 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D41" s="1">
-        <v>15843.15</v>
+        <v>16114</v>
       </c>
       <c r="E41" s="2">
-        <v>0.26</v>
+        <v>-0.71</v>
       </c>
       <c r="F41" s="2">
-        <v>1.56</v>
+        <v>-2.96</v>
       </c>
       <c r="G41" s="2">
-        <v>0.54</v>
+        <v>1.28</v>
       </c>
       <c r="H41" s="2">
-        <v>-6</v>
+        <v>-26.74</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>16313.29</v>
+        <v>18428.48</v>
       </c>
       <c r="K41" s="1">
-        <v>15761.47</v>
+        <v>16123.21</v>
       </c>
       <c r="L41" s="1">
-        <v>16391.97</v>
-      </c>
-      <c r="M41" t="str">
+        <v>17200.33</v>
+      </c>
+      <c r="M41" s="3">
+        <v>-667.86</v>
+      </c>
+      <c r="N41" s="3">
+        <v>-396.25</v>
+      </c>
+      <c r="O41" s="3">
+        <v>-667.86</v>
+      </c>
+      <c r="P41" s="3">
+        <v>-510.36</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>271.55</v>
+      </c>
+      <c r="R41" s="3">
+        <v>-396.25</v>
+      </c>
+      <c r="S41" t="str">
         <v/>
       </c>
     </row>
@@ -2089,39 +2829,57 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D42" s="1">
-        <v>52311.15</v>
+        <v>10564.15</v>
       </c>
       <c r="E42" s="2">
-        <v>0.24</v>
+        <v>-0.71</v>
       </c>
       <c r="F42" s="2">
-        <v>-0.78</v>
+        <v>-2.96</v>
       </c>
       <c r="G42" s="2">
-        <v>-1.1</v>
+        <v>1.23</v>
       </c>
       <c r="H42" s="2">
-        <v>-0.75</v>
+        <v>-28.14</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>52566.61</v>
+        <v>12213.74</v>
       </c>
       <c r="K42" s="1">
-        <v>52848.15</v>
+        <v>10572.46</v>
       </c>
       <c r="L42" s="1">
-        <v>54310.85</v>
-      </c>
-      <c r="M42" t="str">
+        <v>11284</v>
+      </c>
+      <c r="M42" s="3">
+        <v>-483.58</v>
+      </c>
+      <c r="N42" s="3">
+        <v>-262.43</v>
+      </c>
+      <c r="O42" s="3">
+        <v>-483.58</v>
+      </c>
+      <c r="P42" s="3">
+        <v>-385.07</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>-9.91</v>
+      </c>
+      <c r="R42" s="3">
+        <v>-262.43</v>
+      </c>
+      <c r="S42" t="str">
         <v/>
       </c>
     </row>
@@ -2130,39 +2888,57 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>India VIX</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C43" t="str">
-        <v>INDIAVIX</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D43" s="1">
-        <v>14.06</v>
+        <v>5987.5</v>
       </c>
       <c r="E43" s="2">
-        <v>0.21</v>
+        <v>-0.73</v>
       </c>
       <c r="F43" s="2">
-        <v>-2.23</v>
+        <v>-1.28</v>
       </c>
       <c r="G43" s="2">
-        <v>4.23</v>
+        <v>-3.87</v>
       </c>
       <c r="H43" s="2">
-        <v>48.31</v>
+        <v>-5.93</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>14.78</v>
+        <v>6746.92</v>
       </c>
       <c r="K43" s="1">
-        <v>14.16</v>
+        <v>6064.46</v>
       </c>
       <c r="L43" s="1">
-        <v>12.3</v>
-      </c>
-      <c r="M43" t="str">
+        <v>6314.55</v>
+      </c>
+      <c r="M43" s="3">
+        <v>-200.83</v>
+      </c>
+      <c r="N43" s="3">
+        <v>-91.8</v>
+      </c>
+      <c r="O43" s="3">
+        <v>-200.83</v>
+      </c>
+      <c r="P43" s="3">
+        <v>-146.59</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>231.81</v>
+      </c>
+      <c r="R43" s="3">
+        <v>-91.8</v>
+      </c>
+      <c r="S43" t="str">
         <v/>
       </c>
     </row>
@@ -2171,39 +2947,57 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D44" s="1">
-        <v>15786.75</v>
+        <v>13103.15</v>
       </c>
       <c r="E44" s="2">
-        <v>0.19</v>
+        <v>-0.76</v>
       </c>
       <c r="F44" s="2">
-        <v>1.59</v>
+        <v>-1.76</v>
       </c>
       <c r="G44" s="2">
-        <v>-1.44</v>
+        <v>-0.51</v>
       </c>
       <c r="H44" s="2">
-        <v>-1.18</v>
+        <v>-9.84</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>16013.17</v>
+        <v>13800.18</v>
       </c>
       <c r="K44" s="1">
-        <v>15780.89</v>
+        <v>13187.58</v>
       </c>
       <c r="L44" s="1">
-        <v>16521.13</v>
-      </c>
-      <c r="M44" t="str">
+        <v>13659.16</v>
+      </c>
+      <c r="M44" s="3">
+        <v>-163.63</v>
+      </c>
+      <c r="N44" s="3">
+        <v>-163.99</v>
+      </c>
+      <c r="O44" s="3">
+        <v>-163.63</v>
+      </c>
+      <c r="P44" s="3">
+        <v>-67.86</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>272.21</v>
+      </c>
+      <c r="R44" s="3">
+        <v>-163.99</v>
+      </c>
+      <c r="S44" t="str">
         <v/>
       </c>
     </row>
@@ -2212,39 +3006,57 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C45" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D45" s="1">
-        <v>3303.12</v>
+        <v>54976.9</v>
       </c>
       <c r="E45" s="2">
-        <v>0.19</v>
+        <v>-0.92</v>
       </c>
       <c r="F45" s="2">
-        <v>0</v>
+        <v>-1.55</v>
       </c>
       <c r="G45" s="2">
-        <v>-0.56</v>
+        <v>0.63</v>
       </c>
       <c r="H45" s="2">
-        <v>1.89</v>
+        <v>-7.73</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>3294.39</v>
+        <v>56890.68</v>
       </c>
       <c r="K45" s="1">
-        <v>3304.18</v>
+        <v>55317.69</v>
       </c>
       <c r="L45" s="1">
-        <v>3355.73</v>
-      </c>
-      <c r="M45" t="str">
+        <v>56378.11</v>
+      </c>
+      <c r="M45" s="3">
+        <v>-347.01</v>
+      </c>
+      <c r="N45" s="3">
+        <v>-378.44</v>
+      </c>
+      <c r="O45" s="3">
+        <v>-347.01</v>
+      </c>
+      <c r="P45" s="3">
+        <v>-98.28</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>1665.08</v>
+      </c>
+      <c r="R45" s="3">
+        <v>-378.44</v>
+      </c>
+      <c r="S45" t="str">
         <v/>
       </c>
     </row>
@@ -2253,39 +3065,57 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY500</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY500</v>
       </c>
       <c r="D46" s="1">
-        <v>53846.55</v>
+        <v>21837.9</v>
       </c>
       <c r="E46" s="2">
-        <v>0.18</v>
+        <v>-0.92</v>
       </c>
       <c r="F46" s="2">
-        <v>-2.7</v>
+        <v>-1.94</v>
       </c>
       <c r="G46" s="2">
-        <v>-0.43</v>
+        <v>-1.06</v>
       </c>
       <c r="H46" s="2">
-        <v>7.03</v>
+        <v>-8.52</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>52164.16</v>
+        <v>22854.12</v>
       </c>
       <c r="K46" s="1">
-        <v>54658.51</v>
+        <v>22046.22</v>
       </c>
       <c r="L46" s="1">
-        <v>55806.71</v>
-      </c>
-      <c r="M46" t="str">
+        <v>22831.63</v>
+      </c>
+      <c r="M46" s="3">
+        <v>-208.94</v>
+      </c>
+      <c r="N46" s="3">
+        <v>-266.46</v>
+      </c>
+      <c r="O46" s="3">
+        <v>-208.94</v>
+      </c>
+      <c r="P46" s="3">
+        <v>-38.98</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>517.48</v>
+      </c>
+      <c r="R46" s="3">
+        <v>-266.46</v>
+      </c>
+      <c r="S46" t="str">
         <v/>
       </c>
     </row>
@@ -2294,39 +3124,57 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C47" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D47" s="1">
-        <v>9210.6</v>
+        <v>48403.9</v>
       </c>
       <c r="E47" s="2">
-        <v>0.16</v>
+        <v>-0.95</v>
       </c>
       <c r="F47" s="2">
-        <v>2.26</v>
+        <v>-1.81</v>
       </c>
       <c r="G47" s="2">
-        <v>-0.71</v>
+        <v>-5.06</v>
       </c>
       <c r="H47" s="2">
-        <v>18.89</v>
+        <v>10.34</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>8820.27</v>
+        <v>47314.35</v>
       </c>
       <c r="K47" s="1">
-        <v>9205.16</v>
+        <v>49616.65</v>
       </c>
       <c r="L47" s="1">
-        <v>9521.84</v>
-      </c>
-      <c r="M47" t="str">
+        <v>51627.33</v>
+      </c>
+      <c r="M47" s="3">
+        <v>950.03</v>
+      </c>
+      <c r="N47" s="3">
+        <v>-592.18</v>
+      </c>
+      <c r="O47" s="3">
+        <v>950.03</v>
+      </c>
+      <c r="P47" s="3">
+        <v>1562.99</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>2161.01</v>
+      </c>
+      <c r="R47" s="3">
+        <v>-592.18</v>
+      </c>
+      <c r="S47" t="str">
         <v/>
       </c>
     </row>
@@ -2335,39 +3183,57 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D48" s="1">
-        <v>3076.14</v>
+        <v>26578</v>
       </c>
       <c r="E48" s="2">
-        <v>0.15</v>
+        <v>-0.96</v>
       </c>
       <c r="F48" s="2">
-        <v>-0.31</v>
+        <v>-2.33</v>
       </c>
       <c r="G48" s="2">
-        <v>-0.91</v>
+        <v>0.08</v>
       </c>
       <c r="H48" s="2">
-        <v>0.78</v>
+        <v>-11.93</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>3085.73</v>
+        <v>28564.95</v>
       </c>
       <c r="K48" s="1">
-        <v>3081.83</v>
+        <v>26870.58</v>
       </c>
       <c r="L48" s="1">
-        <v>3124.5</v>
-      </c>
-      <c r="M48" t="str">
+        <v>27656.44</v>
+      </c>
+      <c r="M48" s="3">
+        <v>-477.2</v>
+      </c>
+      <c r="N48" s="3">
+        <v>-273.42</v>
+      </c>
+      <c r="O48" s="3">
+        <v>-477.2</v>
+      </c>
+      <c r="P48" s="3">
+        <v>-295.04</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>1312.45</v>
+      </c>
+      <c r="R48" s="3">
+        <v>-273.42</v>
+      </c>
+      <c r="S48" t="str">
         <v/>
       </c>
     </row>
@@ -2376,39 +3242,57 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D49" s="1">
-        <v>2611.33</v>
+        <v>10833.3</v>
       </c>
       <c r="E49" s="2">
-        <v>0.15</v>
+        <v>-0.96</v>
       </c>
       <c r="F49" s="2">
-        <v>-0.29</v>
+        <v>-2</v>
       </c>
       <c r="G49" s="2">
-        <v>-1.02</v>
+        <v>-2.16</v>
       </c>
       <c r="H49" s="2">
-        <v>-0.02</v>
+        <v>-11.85</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>2632.51</v>
+        <v>11503.9</v>
       </c>
       <c r="K49" s="1">
-        <v>2616.69</v>
+        <v>10955.26</v>
       </c>
       <c r="L49" s="1">
-        <v>2654.63</v>
-      </c>
-      <c r="M49" t="str">
+        <v>11506.44</v>
+      </c>
+      <c r="M49" s="3">
+        <v>-151.16</v>
+      </c>
+      <c r="N49" s="3">
+        <v>-183.63</v>
+      </c>
+      <c r="O49" s="3">
+        <v>-151.16</v>
+      </c>
+      <c r="P49" s="3">
+        <v>-41.47</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>217.16</v>
+      </c>
+      <c r="R49" s="3">
+        <v>-183.63</v>
+      </c>
+      <c r="S49" t="str">
         <v/>
       </c>
     </row>
@@ -2417,39 +3301,57 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C50" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D50" s="1">
-        <v>24914.1</v>
+        <v>15526.95</v>
       </c>
       <c r="E50" s="2">
-        <v>0.13</v>
+        <v>-0.97</v>
       </c>
       <c r="F50" s="2">
-        <v>0.9</v>
+        <v>-2</v>
       </c>
       <c r="G50" s="2">
-        <v>-1.21</v>
+        <v>-1.46</v>
       </c>
       <c r="H50" s="2">
-        <v>-7.99</v>
+        <v>-7.88</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>26289.65</v>
+        <v>16301.75</v>
       </c>
       <c r="K50" s="1">
-        <v>24922.41</v>
+        <v>15706.53</v>
       </c>
       <c r="L50" s="1">
-        <v>26306.55</v>
-      </c>
-      <c r="M50" t="str">
+        <v>16338.06</v>
+      </c>
+      <c r="M50" s="3">
+        <v>-145.51</v>
+      </c>
+      <c r="N50" s="3">
+        <v>-211.59</v>
+      </c>
+      <c r="O50" s="3">
+        <v>-145.51</v>
+      </c>
+      <c r="P50" s="3">
+        <v>-1.81</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>917.21</v>
+      </c>
+      <c r="R50" s="3">
+        <v>-211.59</v>
+      </c>
+      <c r="S50" t="str">
         <v/>
       </c>
     </row>
@@ -2458,39 +3360,57 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D51" s="1">
-        <v>843.57</v>
+        <v>8951.3</v>
       </c>
       <c r="E51" s="2">
-        <v>0.13</v>
+        <v>-0.98</v>
       </c>
       <c r="F51" s="2">
-        <v>-0.43</v>
+        <v>-1.63</v>
       </c>
       <c r="G51" s="2">
-        <v>-1.36</v>
+        <v>-3.85</v>
       </c>
       <c r="H51" s="2">
-        <v>-5.37</v>
+        <v>-5.93</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>874.65</v>
+        <v>9763.29</v>
       </c>
       <c r="K51" s="1">
-        <v>846.34</v>
+        <v>9047.24</v>
       </c>
       <c r="L51" s="1">
-        <v>863.86</v>
-      </c>
-      <c r="M51" t="str">
+        <v>9520.84</v>
+      </c>
+      <c r="M51" s="3">
+        <v>-180.52</v>
+      </c>
+      <c r="N51" s="3">
+        <v>-168.6</v>
+      </c>
+      <c r="O51" s="3">
+        <v>-180.52</v>
+      </c>
+      <c r="P51" s="3">
+        <v>-66.31</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>389.72</v>
+      </c>
+      <c r="R51" s="3">
+        <v>-168.6</v>
+      </c>
+      <c r="S51" t="str">
         <v/>
       </c>
     </row>
@@ -2499,39 +3419,57 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D52" s="1">
-        <v>9583.25</v>
+        <v>12344.8</v>
       </c>
       <c r="E52" s="2">
-        <v>0.12</v>
+        <v>-1</v>
       </c>
       <c r="F52" s="2">
-        <v>0.34</v>
+        <v>-2.04</v>
       </c>
       <c r="G52" s="2">
-        <v>-0.52</v>
+        <v>-1.29</v>
       </c>
       <c r="H52" s="2">
-        <v>11.35</v>
+        <v>-7.83</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>8969.44</v>
+        <v>12868.21</v>
       </c>
       <c r="K52" s="1">
-        <v>9641.25</v>
+        <v>12476.41</v>
       </c>
       <c r="L52" s="1">
-        <v>9845.54</v>
-      </c>
-      <c r="M52" t="str">
+        <v>12913.2</v>
+      </c>
+      <c r="M52" s="3">
+        <v>-96.37</v>
+      </c>
+      <c r="N52" s="3">
+        <v>-146.61</v>
+      </c>
+      <c r="O52" s="3">
+        <v>-96.37</v>
+      </c>
+      <c r="P52" s="3">
+        <v>1.22</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>630.33</v>
+      </c>
+      <c r="R52" s="3">
+        <v>-146.61</v>
+      </c>
+      <c r="S52" t="str">
         <v/>
       </c>
     </row>
@@ -2540,39 +3478,57 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C53" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D53" s="1">
-        <v>25387.1</v>
+        <v>32287.7</v>
       </c>
       <c r="E53" s="2">
-        <v>0.09</v>
+        <v>-1.03</v>
       </c>
       <c r="F53" s="2">
-        <v>1.68</v>
+        <v>-1.71</v>
       </c>
       <c r="G53" s="2">
-        <v>2.99</v>
+        <v>-1.74</v>
       </c>
       <c r="H53" s="2">
-        <v>-8.06</v>
+        <v>-4.91</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>26262.37</v>
+        <v>33696.17</v>
       </c>
       <c r="K53" s="1">
-        <v>25085.96</v>
+        <v>32613.79</v>
       </c>
       <c r="L53" s="1">
-        <v>25635.37</v>
-      </c>
-      <c r="M53" t="str">
+        <v>34002.68</v>
+      </c>
+      <c r="M53" s="3">
+        <v>-241.58</v>
+      </c>
+      <c r="N53" s="3">
+        <v>-466.72</v>
+      </c>
+      <c r="O53" s="3">
+        <v>-241.58</v>
+      </c>
+      <c r="P53" s="3">
+        <v>97.77</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>2002</v>
+      </c>
+      <c r="R53" s="3">
+        <v>-466.72</v>
+      </c>
+      <c r="S53" t="str">
         <v/>
       </c>
     </row>
@@ -2581,39 +3537,57 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C54" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D54" s="1">
-        <v>29515.15</v>
+        <v>13389.95</v>
       </c>
       <c r="E54" s="2">
-        <v>0.08</v>
+        <v>-1.03</v>
       </c>
       <c r="F54" s="2">
-        <v>-0.75</v>
+        <v>-1.77</v>
       </c>
       <c r="G54" s="2">
-        <v>-2.7</v>
+        <v>-2.62</v>
       </c>
       <c r="H54" s="2">
-        <v>-3.44</v>
+        <v>-7.47</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>31424.81</v>
+        <v>14154.34</v>
       </c>
       <c r="K54" s="1">
-        <v>29875.06</v>
+        <v>13560.84</v>
       </c>
       <c r="L54" s="1">
-        <v>31838.74</v>
-      </c>
-      <c r="M54" t="str">
+        <v>14168.32</v>
+      </c>
+      <c r="M54" s="3">
+        <v>-165.45</v>
+      </c>
+      <c r="N54" s="3">
+        <v>-205.59</v>
+      </c>
+      <c r="O54" s="3">
+        <v>-165.45</v>
+      </c>
+      <c r="P54" s="3">
+        <v>-14.23</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>75.86</v>
+      </c>
+      <c r="R54" s="3">
+        <v>-205.59</v>
+      </c>
+      <c r="S54" t="str">
         <v/>
       </c>
     </row>
@@ -2628,33 +3602,51 @@
         <v>NIFTYPVTBANK</v>
       </c>
       <c r="D55" s="1">
-        <v>27700.55</v>
+        <v>26904.35</v>
       </c>
       <c r="E55" s="2">
-        <v>0.08</v>
+        <v>-1.05</v>
       </c>
       <c r="F55" s="2">
-        <v>1.76</v>
+        <v>-2.87</v>
       </c>
       <c r="G55" s="2">
-        <v>3.76</v>
+        <v>0.78</v>
       </c>
       <c r="H55" s="2">
-        <v>-3.55</v>
+        <v>-6.33</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>27393.58</v>
+        <v>27380.27</v>
       </c>
       <c r="K55" s="1">
-        <v>27279.86</v>
+        <v>27198.08</v>
       </c>
       <c r="L55" s="1">
-        <v>27316.34</v>
-      </c>
-      <c r="M55" t="str">
+        <v>27296.76</v>
+      </c>
+      <c r="M55" s="3">
+        <v>-33.88</v>
+      </c>
+      <c r="N55" s="3">
+        <v>-42</v>
+      </c>
+      <c r="O55" s="3">
+        <v>-33.88</v>
+      </c>
+      <c r="P55" s="3">
+        <v>18.71</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>649.74</v>
+      </c>
+      <c r="R55" s="3">
+        <v>-42</v>
+      </c>
+      <c r="S55" t="str">
         <v/>
       </c>
     </row>
@@ -2663,39 +3655,57 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C56" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D56" s="1">
-        <v>2982.85</v>
+        <v>9094.4</v>
       </c>
       <c r="E56" s="2">
-        <v>0.08</v>
+        <v>-1.05</v>
       </c>
       <c r="F56" s="2">
-        <v>-0.32</v>
+        <v>-1.65</v>
       </c>
       <c r="G56" s="2">
-        <v>-1.03</v>
+        <v>-2.84</v>
       </c>
       <c r="H56" s="2">
-        <v>0.54</v>
+        <v>-7.71</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>3001.32</v>
+        <v>9992.38</v>
       </c>
       <c r="K56" s="1">
-        <v>2990.02</v>
+        <v>9207.3</v>
       </c>
       <c r="L56" s="1">
-        <v>3032.55</v>
-      </c>
-      <c r="M56" t="str">
+        <v>9554.65</v>
+      </c>
+      <c r="M56" s="3">
+        <v>-227.69</v>
+      </c>
+      <c r="N56" s="3">
+        <v>-125.88</v>
+      </c>
+      <c r="O56" s="3">
+        <v>-227.69</v>
+      </c>
+      <c r="P56" s="3">
+        <v>-146.81</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>792.71</v>
+      </c>
+      <c r="R56" s="3">
+        <v>-125.88</v>
+      </c>
+      <c r="S56" t="str">
         <v/>
       </c>
     </row>
@@ -2704,39 +3714,57 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C57" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D57" s="1">
-        <v>29091.5</v>
+        <v>22448.8</v>
       </c>
       <c r="E57" s="2">
-        <v>0.07</v>
+        <v>-1.1</v>
       </c>
       <c r="F57" s="2">
-        <v>-0.36</v>
+        <v>-2.25</v>
       </c>
       <c r="G57" s="2">
-        <v>-1.45</v>
+        <v>-1.39</v>
       </c>
       <c r="H57" s="2">
-        <v>-6.6</v>
+        <v>-6.69</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>30425.39</v>
+        <v>23501.27</v>
       </c>
       <c r="K57" s="1">
-        <v>29336.45</v>
+        <v>22822.94</v>
       </c>
       <c r="L57" s="1">
-        <v>30435.26</v>
-      </c>
-      <c r="M57" t="str">
+        <v>23785.35</v>
+      </c>
+      <c r="M57" s="3">
+        <v>-199.03</v>
+      </c>
+      <c r="N57" s="3">
+        <v>-296.21</v>
+      </c>
+      <c r="O57" s="3">
+        <v>-199.03</v>
+      </c>
+      <c r="P57" s="3">
+        <v>32.29</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>1021.08</v>
+      </c>
+      <c r="R57" s="3">
+        <v>-296.21</v>
+      </c>
+      <c r="S57" t="str">
         <v/>
       </c>
     </row>
@@ -2745,39 +3773,57 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C58" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D58" s="1">
-        <v>55844</v>
+        <v>24691.45</v>
       </c>
       <c r="E58" s="2">
-        <v>0.06</v>
+        <v>-1.18</v>
       </c>
       <c r="F58" s="2">
-        <v>1.06</v>
+        <v>-2.74</v>
       </c>
       <c r="G58" s="2">
-        <v>2.22</v>
+        <v>0.17</v>
       </c>
       <c r="H58" s="2">
-        <v>-6.27</v>
+        <v>-10.58</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>56928.07</v>
+        <v>26236.79</v>
       </c>
       <c r="K58" s="1">
-        <v>55372.38</v>
+        <v>24999.53</v>
       </c>
       <c r="L58" s="1">
-        <v>56485.01</v>
-      </c>
-      <c r="M58" t="str">
+        <v>25562.35</v>
+      </c>
+      <c r="M58" s="3">
+        <v>-355.41</v>
+      </c>
+      <c r="N58" s="3">
+        <v>-193.73</v>
+      </c>
+      <c r="O58" s="3">
+        <v>-355.41</v>
+      </c>
+      <c r="P58" s="3">
+        <v>-222.35</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>650.94</v>
+      </c>
+      <c r="R58" s="3">
+        <v>-193.73</v>
+      </c>
+      <c r="S58" t="str">
         <v/>
       </c>
     </row>
@@ -2786,39 +3832,57 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D59" s="1">
-        <v>17637.65</v>
+        <v>15471.55</v>
       </c>
       <c r="E59" s="2">
-        <v>0.06</v>
+        <v>-1.18</v>
       </c>
       <c r="F59" s="2">
-        <v>0.36</v>
+        <v>-2.22</v>
       </c>
       <c r="G59" s="2">
-        <v>-0.91</v>
+        <v>-1.77</v>
       </c>
       <c r="H59" s="2">
-        <v>5.71</v>
+        <v>-6.15</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>16942.07</v>
+        <v>16025.26</v>
       </c>
       <c r="K59" s="1">
-        <v>17743.09</v>
+        <v>15688.51</v>
       </c>
       <c r="L59" s="1">
-        <v>18157.34</v>
-      </c>
-      <c r="M59" t="str">
+        <v>16250.98</v>
+      </c>
+      <c r="M59" s="3">
+        <v>-74.4</v>
+      </c>
+      <c r="N59" s="3">
+        <v>-184.14</v>
+      </c>
+      <c r="O59" s="3">
+        <v>-74.4</v>
+      </c>
+      <c r="P59" s="3">
+        <v>61.76</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>918.79</v>
+      </c>
+      <c r="R59" s="3">
+        <v>-184.14</v>
+      </c>
+      <c r="S59" t="str">
         <v/>
       </c>
     </row>
@@ -2827,39 +3891,57 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D60" s="1">
-        <v>49607.05</v>
+        <v>805.85</v>
       </c>
       <c r="E60" s="2">
-        <v>0.02</v>
+        <v>-1.25</v>
       </c>
       <c r="F60" s="2">
-        <v>0.37</v>
+        <v>-2.43</v>
       </c>
       <c r="G60" s="2">
-        <v>0.06</v>
+        <v>-4.9</v>
       </c>
       <c r="H60" s="2">
-        <v>4.29</v>
+        <v>-8.21</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>49067.25</v>
+        <v>822.56</v>
       </c>
       <c r="K60" s="1">
-        <v>49744.1</v>
+        <v>820.8</v>
       </c>
       <c r="L60" s="1">
-        <v>51076.11</v>
-      </c>
-      <c r="M60" t="str">
+        <v>865.65</v>
+      </c>
+      <c r="M60" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="N60" s="3">
+        <v>-14.47</v>
+      </c>
+      <c r="O60" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="P60" s="3">
+        <v>10.56</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>1.73</v>
+      </c>
+      <c r="R60" s="3">
+        <v>-14.47</v>
+      </c>
+      <c r="S60" t="str">
         <v/>
       </c>
     </row>
@@ -2868,39 +3950,57 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D61" s="1">
-        <v>25204.9</v>
+        <v>1622.65</v>
       </c>
       <c r="E61" s="2">
-        <v>0.02</v>
+        <v>-1.29</v>
       </c>
       <c r="F61" s="2">
-        <v>-0.01</v>
+        <v>-1.55</v>
       </c>
       <c r="G61" s="2">
-        <v>-0.75</v>
+        <v>2.49</v>
       </c>
       <c r="H61" s="2">
-        <v>0.88</v>
+        <v>12.32</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>25476.03</v>
+        <v>1468.1</v>
       </c>
       <c r="K61" s="1">
-        <v>25357.81</v>
+        <v>1614.12</v>
       </c>
       <c r="L61" s="1">
-        <v>26296.33</v>
-      </c>
-      <c r="M61" t="str">
+        <v>1573.42</v>
+      </c>
+      <c r="M61" s="3">
+        <v>35.72</v>
+      </c>
+      <c r="N61" s="3">
+        <v>13.97</v>
+      </c>
+      <c r="O61" s="3">
+        <v>35.72</v>
+      </c>
+      <c r="P61" s="3">
+        <v>32.25</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>-70.23</v>
+      </c>
+      <c r="R61" s="3">
+        <v>13.97</v>
+      </c>
+      <c r="S61" t="str">
         <v/>
       </c>
     </row>
@@ -2909,39 +4009,57 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C62" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D62" s="1">
-        <v>3281.39</v>
+        <v>35474.75</v>
       </c>
       <c r="E62" s="2">
-        <v>0.02</v>
+        <v>-1.39</v>
       </c>
       <c r="F62" s="2">
-        <v>-0.49</v>
+        <v>-1.98</v>
       </c>
       <c r="G62" s="2">
-        <v>-0.82</v>
+        <v>-3.17</v>
       </c>
       <c r="H62" s="2">
-        <v>1.82</v>
+        <v>0.42</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>3279.29</v>
+        <v>37725</v>
       </c>
       <c r="K62" s="1">
-        <v>3291.02</v>
+        <v>36101.72</v>
       </c>
       <c r="L62" s="1">
-        <v>3325.39</v>
-      </c>
-      <c r="M62" t="str">
+        <v>37485.67</v>
+      </c>
+      <c r="M62" s="3">
+        <v>-516.35</v>
+      </c>
+      <c r="N62" s="3">
+        <v>-476.06</v>
+      </c>
+      <c r="O62" s="3">
+        <v>-516.35</v>
+      </c>
+      <c r="P62" s="3">
+        <v>-72.31</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>966.04</v>
+      </c>
+      <c r="R62" s="3">
+        <v>-476.06</v>
+      </c>
+      <c r="S62" t="str">
         <v/>
       </c>
     </row>
@@ -2950,39 +4068,57 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C63" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D63" s="1">
-        <v>19129.8</v>
+        <v>21200.25</v>
       </c>
       <c r="E63" s="2">
-        <v>-0.01</v>
+        <v>-1.39</v>
       </c>
       <c r="F63" s="2">
-        <v>-0.12</v>
+        <v>-2.47</v>
       </c>
       <c r="G63" s="2">
-        <v>-0.6</v>
+        <v>-3.05</v>
       </c>
       <c r="H63" s="2">
-        <v>7.99</v>
+        <v>-4.83</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>18173.62</v>
+        <v>22190.22</v>
       </c>
       <c r="K63" s="1">
-        <v>19287.42</v>
+        <v>21643.94</v>
       </c>
       <c r="L63" s="1">
-        <v>19699.23</v>
-      </c>
-      <c r="M63" t="str">
+        <v>22680.93</v>
+      </c>
+      <c r="M63" s="3">
+        <v>-104.32</v>
+      </c>
+      <c r="N63" s="3">
+        <v>-329.9</v>
+      </c>
+      <c r="O63" s="3">
+        <v>-104.32</v>
+      </c>
+      <c r="P63" s="3">
+        <v>157.95</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>1702.72</v>
+      </c>
+      <c r="R63" s="3">
+        <v>-329.9</v>
+      </c>
+      <c r="S63" t="str">
         <v/>
       </c>
     </row>
@@ -2991,39 +4127,57 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C64" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D64" s="1">
-        <v>20270.65</v>
+        <v>13367.85</v>
       </c>
       <c r="E64" s="2">
-        <v>-0.04</v>
+        <v>-1.45</v>
       </c>
       <c r="F64" s="2">
-        <v>0.53</v>
+        <v>-2.55</v>
       </c>
       <c r="G64" s="2">
-        <v>-0.71</v>
+        <v>-2.65</v>
       </c>
       <c r="H64" s="2">
-        <v>0.26</v>
+        <v>-2.97</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>20269.9</v>
+        <v>14001.99</v>
       </c>
       <c r="K64" s="1">
-        <v>20349.72</v>
+        <v>13643.37</v>
       </c>
       <c r="L64" s="1">
-        <v>21100.65</v>
-      </c>
-      <c r="M64" t="str">
+        <v>14377.8</v>
+      </c>
+      <c r="M64" s="3">
+        <v>-68.88</v>
+      </c>
+      <c r="N64" s="3">
+        <v>-238.81</v>
+      </c>
+      <c r="O64" s="3">
+        <v>-68.88</v>
+      </c>
+      <c r="P64" s="3">
+        <v>127.5</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>871.49</v>
+      </c>
+      <c r="R64" s="3">
+        <v>-238.81</v>
+      </c>
+      <c r="S64" t="str">
         <v/>
       </c>
     </row>
@@ -3032,39 +4186,57 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C65" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D65" s="1">
-        <v>13717.4</v>
+        <v>15431.05</v>
       </c>
       <c r="E65" s="2">
-        <v>-0.04</v>
+        <v>-1.46</v>
       </c>
       <c r="F65" s="2">
-        <v>0.93</v>
+        <v>-2.25</v>
       </c>
       <c r="G65" s="2">
-        <v>-0.1</v>
+        <v>-3.66</v>
       </c>
       <c r="H65" s="2">
-        <v>-0.43</v>
+        <v>-3.41</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>14004.2</v>
+        <v>16011</v>
       </c>
       <c r="K65" s="1">
-        <v>13735.59</v>
+        <v>15699.31</v>
       </c>
       <c r="L65" s="1">
-        <v>14432.89</v>
-      </c>
-      <c r="M65" t="str">
+        <v>16459.18</v>
+      </c>
+      <c r="M65" s="3">
+        <v>-42.17</v>
+      </c>
+      <c r="N65" s="3">
+        <v>-242.51</v>
+      </c>
+      <c r="O65" s="3">
+        <v>-42.17</v>
+      </c>
+      <c r="P65" s="3">
+        <v>137.03</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>361.13</v>
+      </c>
+      <c r="R65" s="3">
+        <v>-242.51</v>
+      </c>
+      <c r="S65" t="str">
         <v/>
       </c>
     </row>
@@ -3073,39 +4245,57 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C66" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D66" s="1">
-        <v>1447.02</v>
+        <v>67655.3</v>
       </c>
       <c r="E66" s="2">
-        <v>-0.04</v>
+        <v>-1.51</v>
       </c>
       <c r="F66" s="2">
-        <v>-0.43</v>
+        <v>-1.93</v>
       </c>
       <c r="G66" s="2">
-        <v>-0.47</v>
+        <v>-3</v>
       </c>
       <c r="H66" s="2">
-        <v>1.57</v>
+        <v>-2.46</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>1440.46</v>
+        <v>70043</v>
       </c>
       <c r="K66" s="1">
-        <v>1451.11</v>
+        <v>68730.8</v>
       </c>
       <c r="L66" s="1">
-        <v>1459.54</v>
-      </c>
-      <c r="M66" t="str">
+        <v>71815.76</v>
+      </c>
+      <c r="M66" s="3">
+        <v>-198.3</v>
+      </c>
+      <c r="N66" s="3">
+        <v>-987.31</v>
+      </c>
+      <c r="O66" s="3">
+        <v>-198.3</v>
+      </c>
+      <c r="P66" s="3">
+        <v>578.75</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>2663.93</v>
+      </c>
+      <c r="R66" s="3">
+        <v>-987.31</v>
+      </c>
+      <c r="S66" t="str">
         <v/>
       </c>
     </row>
@@ -3114,39 +4304,57 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D67" s="1">
-        <v>27211</v>
+        <v>25196.65</v>
       </c>
       <c r="E67" s="2">
-        <v>-0.05</v>
+        <v>-1.54</v>
       </c>
       <c r="F67" s="2">
-        <v>1.45</v>
+        <v>-2.22</v>
       </c>
       <c r="G67" s="2">
-        <v>2.46</v>
+        <v>-4.17</v>
       </c>
       <c r="H67" s="2">
-        <v>-9.83</v>
+        <v>-10.62</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>28597.68</v>
+        <v>26942.83</v>
       </c>
       <c r="K67" s="1">
-        <v>26957.61</v>
+        <v>25456.41</v>
       </c>
       <c r="L67" s="1">
-        <v>27752.62</v>
-      </c>
-      <c r="M67" t="str">
+        <v>27352.71</v>
+      </c>
+      <c r="M67" s="3">
+        <v>-282.28</v>
+      </c>
+      <c r="N67" s="3">
+        <v>-630.31</v>
+      </c>
+      <c r="O67" s="3">
+        <v>-282.28</v>
+      </c>
+      <c r="P67" s="3">
+        <v>96.45</v>
+      </c>
+      <c r="Q67" s="3">
+        <v>1475.87</v>
+      </c>
+      <c r="R67" s="3">
+        <v>-630.31</v>
+      </c>
+      <c r="S67" t="str">
         <v/>
       </c>
     </row>
@@ -3155,39 +4363,57 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C68" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D68" s="1">
-        <v>36190.85</v>
+        <v>14841.8</v>
       </c>
       <c r="E68" s="2">
-        <v>-0.06</v>
+        <v>-1.57</v>
       </c>
       <c r="F68" s="2">
-        <v>1.13</v>
+        <v>-2.19</v>
       </c>
       <c r="G68" s="2">
-        <v>-1.22</v>
+        <v>-3.96</v>
       </c>
       <c r="H68" s="2">
-        <v>2.45</v>
+        <v>-3.7</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>37717.4</v>
+        <v>15632.23</v>
       </c>
       <c r="K68" s="1">
-        <v>36300.3</v>
+        <v>15107.46</v>
       </c>
       <c r="L68" s="1">
-        <v>37605.35</v>
-      </c>
-      <c r="M68" t="str">
+        <v>15927.77</v>
+      </c>
+      <c r="M68" s="3">
+        <v>-93.27</v>
+      </c>
+      <c r="N68" s="3">
+        <v>-263.97</v>
+      </c>
+      <c r="O68" s="3">
+        <v>-93.27</v>
+      </c>
+      <c r="P68" s="3">
+        <v>101.61</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>1246.98</v>
+      </c>
+      <c r="R68" s="3">
+        <v>-263.97</v>
+      </c>
+      <c r="S68" t="str">
         <v/>
       </c>
     </row>
@@ -3196,39 +4422,57 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D69" s="1">
-        <v>16946.3</v>
+        <v>57565.85</v>
       </c>
       <c r="E69" s="2">
-        <v>-0.06</v>
+        <v>-1.58</v>
       </c>
       <c r="F69" s="2">
-        <v>0.95</v>
+        <v>-2.64</v>
       </c>
       <c r="G69" s="2">
-        <v>-0.48</v>
+        <v>-2.98</v>
       </c>
       <c r="H69" s="2">
-        <v>-1.78</v>
+        <v>-4.83</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>17233.43</v>
+        <v>60332.89</v>
       </c>
       <c r="K69" s="1">
-        <v>16974.24</v>
+        <v>58857.49</v>
       </c>
       <c r="L69" s="1">
-        <v>17778.3</v>
-      </c>
-      <c r="M69" t="str">
+        <v>61713.48</v>
+      </c>
+      <c r="M69" s="3">
+        <v>-298.42</v>
+      </c>
+      <c r="N69" s="3">
+        <v>-903.29</v>
+      </c>
+      <c r="O69" s="3">
+        <v>-298.42</v>
+      </c>
+      <c r="P69" s="3">
+        <v>424.39</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>2868.81</v>
+      </c>
+      <c r="R69" s="3">
+        <v>-903.29</v>
+      </c>
+      <c r="S69" t="str">
         <v/>
       </c>
     </row>
@@ -3237,39 +4481,57 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D70" s="1">
-        <v>60265.35</v>
+        <v>16500.2</v>
       </c>
       <c r="E70" s="2">
-        <v>-0.07</v>
+        <v>-1.6</v>
       </c>
       <c r="F70" s="2">
-        <v>-0.54</v>
+        <v>-2.63</v>
       </c>
       <c r="G70" s="2">
-        <v>-0.84</v>
+        <v>-3.1</v>
       </c>
       <c r="H70" s="2">
-        <v>-2.67</v>
+        <v>-4.37</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>61775.44</v>
+        <v>17228.37</v>
       </c>
       <c r="K70" s="1">
-        <v>60756.07</v>
+        <v>16857.35</v>
       </c>
       <c r="L70" s="1">
-        <v>62916.82</v>
-      </c>
-      <c r="M70" t="str">
+        <v>17717.7</v>
+      </c>
+      <c r="M70" s="3">
+        <v>-55.2</v>
+      </c>
+      <c r="N70" s="3">
+        <v>-278.57</v>
+      </c>
+      <c r="O70" s="3">
+        <v>-55.2</v>
+      </c>
+      <c r="P70" s="3">
+        <v>160.54</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>894.59</v>
+      </c>
+      <c r="R70" s="3">
+        <v>-278.57</v>
+      </c>
+      <c r="S70" t="str">
         <v/>
       </c>
     </row>
@@ -3278,39 +4540,57 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C71" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D71" s="1">
-        <v>1601.46</v>
+        <v>7371.15</v>
       </c>
       <c r="E71" s="2">
-        <v>-0.08</v>
+        <v>-1.69</v>
       </c>
       <c r="F71" s="2">
-        <v>-0.31</v>
+        <v>-2.56</v>
       </c>
       <c r="G71" s="2">
-        <v>-0.34</v>
+        <v>-4.33</v>
       </c>
       <c r="H71" s="2">
-        <v>2.21</v>
+        <v>-14.33</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>1586.13</v>
+        <v>7691.3</v>
       </c>
       <c r="K71" s="1">
-        <v>1604.88</v>
+        <v>7503.05</v>
       </c>
       <c r="L71" s="1">
-        <v>1609.66</v>
-      </c>
-      <c r="M71" t="str">
+        <v>7781.41</v>
+      </c>
+      <c r="M71" s="3">
+        <v>-66.71</v>
+      </c>
+      <c r="N71" s="3">
+        <v>-87.71</v>
+      </c>
+      <c r="O71" s="3">
+        <v>-66.71</v>
+      </c>
+      <c r="P71" s="3">
+        <v>-18.62</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>-304.51</v>
+      </c>
+      <c r="R71" s="3">
+        <v>-87.71</v>
+      </c>
+      <c r="S71" t="str">
         <v/>
       </c>
     </row>
@@ -3319,39 +4599,57 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D72" s="1">
-        <v>21736.75</v>
+        <v>19705.05</v>
       </c>
       <c r="E72" s="2">
-        <v>-0.09</v>
+        <v>-1.7</v>
       </c>
       <c r="F72" s="2">
-        <v>0.62</v>
+        <v>-2.79</v>
       </c>
       <c r="G72" s="2">
-        <v>-0.6</v>
+        <v>-3.48</v>
       </c>
       <c r="H72" s="2">
-        <v>-2.42</v>
+        <v>-2.53</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>22198.18</v>
+        <v>20267.74</v>
       </c>
       <c r="K72" s="1">
-        <v>21796.6</v>
+        <v>20187.22</v>
       </c>
       <c r="L72" s="1">
-        <v>22760.41</v>
-      </c>
-      <c r="M72" t="str">
+        <v>21034.43</v>
+      </c>
+      <c r="M72" s="3">
+        <v>19.81</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-259.74</v>
+      </c>
+      <c r="O72" s="3">
+        <v>19.81</v>
+      </c>
+      <c r="P72" s="3">
+        <v>249.83</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>1573.19</v>
+      </c>
+      <c r="R72" s="3">
+        <v>-259.74</v>
+      </c>
+      <c r="S72" t="str">
         <v/>
       </c>
     </row>
@@ -3360,39 +4658,57 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C73" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D73" s="1">
-        <v>1307.76</v>
+        <v>11859.55</v>
       </c>
       <c r="E73" s="2">
-        <v>-0.1</v>
+        <v>-1.71</v>
       </c>
       <c r="F73" s="2">
-        <v>-0.56</v>
+        <v>-2.26</v>
       </c>
       <c r="G73" s="2">
-        <v>-0.59</v>
+        <v>-7.06</v>
       </c>
       <c r="H73" s="2">
-        <v>0.74</v>
+        <v>6.2</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>1307.86</v>
+        <v>12478.21</v>
       </c>
       <c r="K73" s="1">
-        <v>1312.51</v>
+        <v>12113.93</v>
       </c>
       <c r="L73" s="1">
-        <v>1323.51</v>
-      </c>
-      <c r="M73" t="str">
+        <v>12865.76</v>
+      </c>
+      <c r="M73" s="3">
+        <v>15.41</v>
+      </c>
+      <c r="N73" s="3">
+        <v>-246.99</v>
+      </c>
+      <c r="O73" s="3">
+        <v>15.41</v>
+      </c>
+      <c r="P73" s="3">
+        <v>208.97</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>1137.8</v>
+      </c>
+      <c r="R73" s="3">
+        <v>-246.99</v>
+      </c>
+      <c r="S73" t="str">
         <v/>
       </c>
     </row>
@@ -3401,39 +4717,57 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C74" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D74" s="1">
-        <v>1264.3</v>
+        <v>15586</v>
       </c>
       <c r="E74" s="2">
-        <v>-0.1</v>
+        <v>-1.76</v>
       </c>
       <c r="F74" s="2">
-        <v>-0.64</v>
+        <v>-3.01</v>
       </c>
       <c r="G74" s="2">
-        <v>-0.7</v>
+        <v>-4.31</v>
       </c>
       <c r="H74" s="2">
-        <v>0.22</v>
+        <v>-2.61</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
       <c r="J74" s="1">
-        <v>1268.31</v>
+        <v>16132.86</v>
       </c>
       <c r="K74" s="1">
-        <v>1269.6</v>
+        <v>16045.65</v>
       </c>
       <c r="L74" s="1">
-        <v>1282.04</v>
-      </c>
-      <c r="M74" t="str">
+        <v>16859.82</v>
+      </c>
+      <c r="M74" s="3">
+        <v>21.19</v>
+      </c>
+      <c r="N74" s="3">
+        <v>-241.93</v>
+      </c>
+      <c r="O74" s="3">
+        <v>21.19</v>
+      </c>
+      <c r="P74" s="3">
+        <v>230.05</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>1543.57</v>
+      </c>
+      <c r="R74" s="3">
+        <v>-241.93</v>
+      </c>
+      <c r="S74" t="str">
         <v/>
       </c>
     </row>
@@ -3442,39 +4776,57 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C75" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D75" s="1">
-        <v>59129.75</v>
+        <v>35175.15</v>
       </c>
       <c r="E75" s="2">
-        <v>-0.11</v>
+        <v>-1.86</v>
       </c>
       <c r="F75" s="2">
-        <v>0.58</v>
+        <v>-2.96</v>
       </c>
       <c r="G75" s="2">
-        <v>-0.34</v>
+        <v>-3.97</v>
       </c>
       <c r="H75" s="2">
-        <v>-2.24</v>
+        <v>-4.3</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>60354.2</v>
+        <v>37120.37</v>
       </c>
       <c r="K75" s="1">
-        <v>59290.43</v>
+        <v>36133.07</v>
       </c>
       <c r="L75" s="1">
-        <v>61928.21</v>
-      </c>
-      <c r="M75" t="str">
+        <v>38507.54</v>
+      </c>
+      <c r="M75" s="3">
+        <v>-196.08</v>
+      </c>
+      <c r="N75" s="3">
+        <v>-739.59</v>
+      </c>
+      <c r="O75" s="3">
+        <v>-196.08</v>
+      </c>
+      <c r="P75" s="3">
+        <v>315.51</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>632.89</v>
+      </c>
+      <c r="R75" s="3">
+        <v>-739.59</v>
+      </c>
+      <c r="S75" t="str">
         <v/>
       </c>
     </row>
@@ -3483,39 +4835,57 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C76" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D76" s="1">
-        <v>9247.3</v>
+        <v>48284.2</v>
       </c>
       <c r="E76" s="2">
-        <v>-0.11</v>
+        <v>-1.89</v>
       </c>
       <c r="F76" s="2">
-        <v>1.87</v>
+        <v>-2.67</v>
       </c>
       <c r="G76" s="2">
-        <v>-1.21</v>
+        <v>-2.6</v>
       </c>
       <c r="H76" s="2">
-        <v>-6.15</v>
+        <v>1.51</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>9998.28</v>
+        <v>49077.35</v>
       </c>
       <c r="K76" s="1">
-        <v>9241.67</v>
+        <v>49399.75</v>
       </c>
       <c r="L76" s="1">
-        <v>9586.14</v>
-      </c>
-      <c r="M76" t="str">
+        <v>50957</v>
+      </c>
+      <c r="M76" s="3">
+        <v>116.31</v>
+      </c>
+      <c r="N76" s="3">
+        <v>-444.45</v>
+      </c>
+      <c r="O76" s="3">
+        <v>116.31</v>
+      </c>
+      <c r="P76" s="3">
+        <v>560.14</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>61.01</v>
+      </c>
+      <c r="R76" s="3">
+        <v>-444.45</v>
+      </c>
+      <c r="S76" t="str">
         <v/>
       </c>
     </row>
@@ -3524,39 +4894,57 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C77" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D77" s="1">
-        <v>25781.65</v>
+        <v>58544.5</v>
       </c>
       <c r="E77" s="2">
-        <v>-0.14</v>
+        <v>-2.06</v>
       </c>
       <c r="F77" s="2">
-        <v>-0.69</v>
+        <v>-2.86</v>
       </c>
       <c r="G77" s="2">
-        <v>-2.48</v>
+        <v>-3.67</v>
       </c>
       <c r="H77" s="2">
-        <v>13.46</v>
+        <v>-5.44</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>24317.35</v>
+        <v>61745.17</v>
       </c>
       <c r="K77" s="1">
-        <v>26038.98</v>
+        <v>60207.98</v>
       </c>
       <c r="L77" s="1">
-        <v>26523.79</v>
-      </c>
-      <c r="M77" t="str">
+        <v>62735.23</v>
+      </c>
+      <c r="M77" s="3">
+        <v>-370.77</v>
+      </c>
+      <c r="N77" s="3">
+        <v>-740.43</v>
+      </c>
+      <c r="O77" s="3">
+        <v>-370.77</v>
+      </c>
+      <c r="P77" s="3">
+        <v>216.3</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>-110.49</v>
+      </c>
+      <c r="R77" s="3">
+        <v>-740.43</v>
+      </c>
+      <c r="S77" t="str">
         <v/>
       </c>
     </row>
@@ -3565,39 +4953,57 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C78" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D78" s="1">
-        <v>22966.1</v>
+        <v>28626.65</v>
       </c>
       <c r="E78" s="2">
-        <v>-0.19</v>
+        <v>-2.1</v>
       </c>
       <c r="F78" s="2">
-        <v>1.13</v>
+        <v>-3.01</v>
       </c>
       <c r="G78" s="2">
-        <v>0.88</v>
+        <v>-5.63</v>
       </c>
       <c r="H78" s="2">
-        <v>-4.54</v>
+        <v>-6.35</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>23515.47</v>
+        <v>31410.71</v>
       </c>
       <c r="K78" s="1">
-        <v>22952.18</v>
+        <v>29553.58</v>
       </c>
       <c r="L78" s="1">
-        <v>23874.38</v>
-      </c>
-      <c r="M78" t="str">
+        <v>31651.86</v>
+      </c>
+      <c r="M78" s="3">
+        <v>-453.52</v>
+      </c>
+      <c r="N78" s="3">
+        <v>-642.67</v>
+      </c>
+      <c r="O78" s="3">
+        <v>-453.52</v>
+      </c>
+      <c r="P78" s="3">
+        <v>75.08</v>
+      </c>
+      <c r="Q78" s="3">
+        <v>1989.94</v>
+      </c>
+      <c r="R78" s="3">
+        <v>-642.67</v>
+      </c>
+      <c r="S78" t="str">
         <v/>
       </c>
     </row>
@@ -3606,39 +5012,57 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C79" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D79" s="1">
-        <v>28364.25</v>
+        <v>24485.75</v>
       </c>
       <c r="E79" s="2">
-        <v>-0.21</v>
+        <v>-2.24</v>
       </c>
       <c r="F79" s="2">
-        <v>1.41</v>
+        <v>-2.85</v>
       </c>
       <c r="G79" s="2">
-        <v>0</v>
-      </c>
-      <c r="H79" t="str">
-        <v/>
+        <v>-3.58</v>
+      </c>
+      <c r="H79" s="2">
+        <v>-2</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
-      <c r="J79" t="str">
-        <v/>
+      <c r="J79" s="1">
+        <v>25474.99</v>
       </c>
       <c r="K79" s="1">
-        <v>28382.43</v>
+        <v>25152.88</v>
       </c>
       <c r="L79" s="1">
-        <v>29525.85</v>
-      </c>
-      <c r="M79" t="str">
+        <v>26223.82</v>
+      </c>
+      <c r="M79" s="3">
+        <v>-46.46</v>
+      </c>
+      <c r="N79" s="3">
+        <v>-316.69</v>
+      </c>
+      <c r="O79" s="3">
+        <v>-46.46</v>
+      </c>
+      <c r="P79" s="3">
+        <v>217.8</v>
+      </c>
+      <c r="Q79" s="3">
+        <v>67.16</v>
+      </c>
+      <c r="R79" s="3">
+        <v>-316.69</v>
+      </c>
+      <c r="S79" t="str">
         <v/>
       </c>
     </row>
@@ -3647,39 +5071,57 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D80" s="1">
-        <v>15683.55</v>
+        <v>46250.45</v>
       </c>
       <c r="E80" s="2">
-        <v>-0.26</v>
+        <v>-2.26</v>
       </c>
       <c r="F80" s="2">
-        <v>-1.08</v>
+        <v>-3</v>
       </c>
       <c r="G80" s="2">
-        <v>-2.81</v>
+        <v>-3.36</v>
       </c>
       <c r="H80" s="2">
-        <v>7.13</v>
+        <v>5.15</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>15427.49</v>
+        <v>44916.55</v>
       </c>
       <c r="K80" s="1">
-        <v>15873.17</v>
+        <v>47447.54</v>
       </c>
       <c r="L80" s="1">
-        <v>16420.14</v>
-      </c>
-      <c r="M80" t="str">
+        <v>48412.97</v>
+      </c>
+      <c r="M80" s="3">
+        <v>797.36</v>
+      </c>
+      <c r="N80" s="3">
+        <v>-239.01</v>
+      </c>
+      <c r="O80" s="3">
+        <v>797.36</v>
+      </c>
+      <c r="P80" s="3">
+        <v>1130.14</v>
+      </c>
+      <c r="Q80" s="3">
+        <v>-311.48</v>
+      </c>
+      <c r="R80" s="3">
+        <v>-239.01</v>
+      </c>
+      <c r="S80" t="str">
         <v/>
       </c>
     </row>
@@ -3688,39 +5130,57 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C81" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D81" s="1">
-        <v>825.95</v>
+        <v>17041.95</v>
       </c>
       <c r="E81" s="2">
-        <v>-0.33</v>
+        <v>-2.26</v>
       </c>
       <c r="F81" s="2">
-        <v>2.74</v>
+        <v>-3.38</v>
       </c>
       <c r="G81" s="2">
-        <v>-2.53</v>
+        <v>-4.25</v>
       </c>
       <c r="H81" s="2">
-        <v>-5.92</v>
+        <v>2.14</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>823.25</v>
+        <v>16948.75</v>
       </c>
       <c r="K81" s="1">
-        <v>825.91</v>
+        <v>17569.8</v>
       </c>
       <c r="L81" s="1">
-        <v>868.67</v>
-      </c>
-      <c r="M81" t="str">
+        <v>18112.58</v>
+      </c>
+      <c r="M81" s="3">
+        <v>206.68</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-148.54</v>
+      </c>
+      <c r="O81" s="3">
+        <v>206.68</v>
+      </c>
+      <c r="P81" s="3">
+        <v>383.2</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>1307.86</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-148.54</v>
+      </c>
+      <c r="S81" t="str">
         <v/>
       </c>
     </row>
@@ -3729,39 +5189,57 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C82" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D82" s="1">
-        <v>44616.15</v>
+        <v>5072.6</v>
       </c>
       <c r="E82" s="2">
-        <v>-0.39</v>
+        <v>-2.28</v>
       </c>
       <c r="F82" s="2">
-        <v>-0.55</v>
+        <v>-3.23</v>
       </c>
       <c r="G82" s="2">
-        <v>0.24</v>
+        <v>-0.34</v>
       </c>
       <c r="H82" s="2">
-        <v>-19.58</v>
+        <v>8.94</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>49143.61</v>
+        <v>5103.01</v>
       </c>
       <c r="K82" s="1">
-        <v>44758.3</v>
+        <v>5200.83</v>
       </c>
       <c r="L82" s="1">
-        <v>46229.88</v>
-      </c>
-      <c r="M82" t="str">
+        <v>5307.19</v>
+      </c>
+      <c r="M82" s="3">
+        <v>28.71</v>
+      </c>
+      <c r="N82" s="3">
+        <v>-30.41</v>
+      </c>
+      <c r="O82" s="3">
+        <v>28.71</v>
+      </c>
+      <c r="P82" s="3">
+        <v>86.76</v>
+      </c>
+      <c r="Q82" s="3">
+        <v>365.15</v>
+      </c>
+      <c r="R82" s="3">
+        <v>-30.41</v>
+      </c>
+      <c r="S82" t="str">
         <v/>
       </c>
     </row>
@@ -3770,39 +5248,57 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C83" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D83" s="1">
-        <v>6065.4</v>
+        <v>9304.7</v>
       </c>
       <c r="E83" s="2">
-        <v>-0.39</v>
+        <v>-2.32</v>
       </c>
       <c r="F83" s="2">
-        <v>1.03</v>
+        <v>-2.91</v>
       </c>
       <c r="G83" s="2">
-        <v>-2.62</v>
+        <v>-3.41</v>
       </c>
       <c r="H83" s="2">
-        <v>-4.71</v>
+        <v>8.12</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>6749.81</v>
+        <v>8977.76</v>
       </c>
       <c r="K83" s="1">
-        <v>6092.73</v>
+        <v>9562.89</v>
       </c>
       <c r="L83" s="1">
-        <v>6333.52</v>
-      </c>
-      <c r="M83" t="str">
+        <v>9824.13</v>
+      </c>
+      <c r="M83" s="3">
+        <v>202.03</v>
+      </c>
+      <c r="N83" s="3">
+        <v>-68.5</v>
+      </c>
+      <c r="O83" s="3">
+        <v>202.03</v>
+      </c>
+      <c r="P83" s="3">
+        <v>294.93</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>732.62</v>
+      </c>
+      <c r="R83" s="3">
+        <v>-68.5</v>
+      </c>
+      <c r="S83" t="str">
         <v/>
       </c>
     </row>
@@ -3811,39 +5307,57 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C84" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D84" s="1">
-        <v>10556.75</v>
+        <v>18487.3</v>
       </c>
       <c r="E84" s="2">
-        <v>-0.45</v>
+        <v>-2.37</v>
       </c>
       <c r="F84" s="2">
-        <v>2.04</v>
+        <v>-3.36</v>
       </c>
       <c r="G84" s="2">
-        <v>-0.54</v>
+        <v>-3.94</v>
       </c>
       <c r="H84" s="2">
-        <v>-13.69</v>
+        <v>4.37</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>11322.24</v>
+        <v>18184.42</v>
       </c>
       <c r="K84" s="1">
-        <v>10514.73</v>
+        <v>19089.63</v>
       </c>
       <c r="L84" s="1">
-        <v>10935.77</v>
-      </c>
-      <c r="M84" t="str">
+        <v>19652.77</v>
+      </c>
+      <c r="M84" s="3">
+        <v>303.54</v>
+      </c>
+      <c r="N84" s="3">
+        <v>-144.59</v>
+      </c>
+      <c r="O84" s="3">
+        <v>303.54</v>
+      </c>
+      <c r="P84" s="3">
+        <v>488.99</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>857</v>
+      </c>
+      <c r="R84" s="3">
+        <v>-144.59</v>
+      </c>
+      <c r="S84" t="str">
         <v/>
       </c>
     </row>
@@ -3852,39 +5366,57 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C85" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D85" s="1">
-        <v>49296.5</v>
+        <v>52417.75</v>
       </c>
       <c r="E85" s="2">
-        <v>-0.52</v>
+        <v>-2.39</v>
       </c>
       <c r="F85" s="2">
-        <v>-1.82</v>
+        <v>-2.65</v>
       </c>
       <c r="G85" s="2">
-        <v>-3.3</v>
+        <v>-3.07</v>
       </c>
       <c r="H85" s="2">
-        <v>12.38</v>
+        <v>4.19</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>47264.73</v>
+        <v>52190.38</v>
       </c>
       <c r="K85" s="1">
-        <v>50112.71</v>
+        <v>54108.5</v>
       </c>
       <c r="L85" s="1">
-        <v>51777.37</v>
-      </c>
-      <c r="M85" t="str">
+        <v>55691.54</v>
+      </c>
+      <c r="M85" s="3">
+        <v>687.99</v>
+      </c>
+      <c r="N85" s="3">
+        <v>-337.93</v>
+      </c>
+      <c r="O85" s="3">
+        <v>687.99</v>
+      </c>
+      <c r="P85" s="3">
+        <v>1152.5</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>3654.57</v>
+      </c>
+      <c r="R85" s="3">
+        <v>-337.93</v>
+      </c>
+      <c r="S85" t="str">
         <v/>
       </c>
     </row>
@@ -3893,39 +5425,57 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D86" s="1">
-        <v>16070.05</v>
+        <v>50864.95</v>
       </c>
       <c r="E86" s="2">
-        <v>-0.52</v>
+        <v>-2.47</v>
       </c>
       <c r="F86" s="2">
-        <v>0.37</v>
+        <v>-2.76</v>
       </c>
       <c r="G86" s="2">
-        <v>-1.34</v>
+        <v>-3.84</v>
       </c>
       <c r="H86" s="2">
-        <v>0.41</v>
+        <v>-3.5</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
       <c r="J86" s="1">
-        <v>16135.3</v>
+        <v>52551.71</v>
       </c>
       <c r="K86" s="1">
-        <v>16210.41</v>
+        <v>52384.29</v>
       </c>
       <c r="L86" s="1">
-        <v>16910.09</v>
-      </c>
-      <c r="M86" t="str">
+        <v>54191.73</v>
+      </c>
+      <c r="M86" s="3">
+        <v>16.41</v>
+      </c>
+      <c r="N86" s="3">
+        <v>-484.74</v>
+      </c>
+      <c r="O86" s="3">
+        <v>16.41</v>
+      </c>
+      <c r="P86" s="3">
+        <v>441.68</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>-766.73</v>
+      </c>
+      <c r="R86" s="3">
+        <v>-484.74</v>
+      </c>
+      <c r="S86" t="str">
         <v/>
       </c>
     </row>
@@ -3934,39 +5484,57 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D87" s="1">
-        <v>36247.95</v>
+        <v>28210.45</v>
       </c>
       <c r="E87" s="2">
-        <v>-0.61</v>
+        <v>-2.47</v>
       </c>
       <c r="F87" s="2">
-        <v>0.77</v>
+        <v>-3.03</v>
       </c>
       <c r="G87" s="2">
-        <v>-1.04</v>
+        <v>-4.43</v>
       </c>
       <c r="H87" s="2">
-        <v>-1.38</v>
+        <v>-9.43</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>37131.85</v>
+        <v>30400.13</v>
       </c>
       <c r="K87" s="1">
-        <v>36458.26</v>
+        <v>29070.51</v>
       </c>
       <c r="L87" s="1">
-        <v>38696.66</v>
-      </c>
-      <c r="M87" t="str">
+        <v>30338.82</v>
+      </c>
+      <c r="M87" s="3">
+        <v>-358.37</v>
+      </c>
+      <c r="N87" s="3">
+        <v>-371.67</v>
+      </c>
+      <c r="O87" s="3">
+        <v>-358.37</v>
+      </c>
+      <c r="P87" s="3">
+        <v>-90.14</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>1434.04</v>
+      </c>
+      <c r="R87" s="3">
+        <v>-371.67</v>
+      </c>
+      <c r="S87" t="str">
         <v/>
       </c>
     </row>
@@ -3975,39 +5543,57 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D88" s="1">
-        <v>230.85</v>
+        <v>8897.2</v>
       </c>
       <c r="E88" s="2">
-        <v>-0.62</v>
+        <v>-2.49</v>
       </c>
       <c r="F88" s="2">
-        <v>-2.66</v>
+        <v>-3.4</v>
       </c>
       <c r="G88" s="2">
-        <v>-2.16</v>
+        <v>-4.09</v>
       </c>
       <c r="H88" s="2">
-        <v>15.43</v>
+        <v>14.84</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>218.58</v>
+        <v>8832.86</v>
       </c>
       <c r="K88" s="1">
-        <v>234.53</v>
+        <v>9137.14</v>
       </c>
       <c r="L88" s="1">
-        <v>226.4</v>
-      </c>
-      <c r="M88" t="str">
+        <v>9494.3</v>
+      </c>
+      <c r="M88" s="3">
+        <v>108</v>
+      </c>
+      <c r="N88" s="3">
+        <v>-102.94</v>
+      </c>
+      <c r="O88" s="3">
+        <v>108</v>
+      </c>
+      <c r="P88" s="3">
+        <v>236.29</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>609.88</v>
+      </c>
+      <c r="R88" s="3">
+        <v>-102.94</v>
+      </c>
+      <c r="S88" t="str">
         <v/>
       </c>
     </row>
@@ -4016,39 +5602,57 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C89" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D89" s="1">
-        <v>187.2</v>
+        <v>24645.85</v>
       </c>
       <c r="E89" s="2">
-        <v>-0.64</v>
+        <v>-2.61</v>
       </c>
       <c r="F89" s="2">
-        <v>-2.68</v>
+        <v>-4.24</v>
       </c>
       <c r="G89" s="2">
-        <v>-2.19</v>
+        <v>-6.11</v>
       </c>
       <c r="H89" s="2">
-        <v>14.39</v>
+        <v>9.31</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>178.16</v>
+        <v>23607.54</v>
       </c>
       <c r="K89" s="1">
-        <v>190.23</v>
+        <v>25538.32</v>
       </c>
       <c r="L89" s="1">
-        <v>183.67</v>
-      </c>
-      <c r="M89" t="str">
+        <v>26151.21</v>
+      </c>
+      <c r="M89" s="3">
+        <v>631.16</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-135.24</v>
+      </c>
+      <c r="O89" s="3">
+        <v>631.16</v>
+      </c>
+      <c r="P89" s="3">
+        <v>861.21</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>2310.69</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-135.24</v>
+      </c>
+      <c r="S89" t="str">
         <v/>
       </c>
     </row>
@@ -4057,45 +5661,63 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C90" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D90" s="1">
-        <v>5242.05</v>
+        <v>27176.35</v>
       </c>
       <c r="E90" s="2">
-        <v>-1.07</v>
+        <v>-2.64</v>
       </c>
       <c r="F90" s="2">
-        <v>1.18</v>
+        <v>-4.19</v>
       </c>
       <c r="G90" s="2">
-        <v>2.99</v>
-      </c>
-      <c r="H90" s="2">
-        <v>12.58</v>
+        <v>-4.18</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
-      <c r="J90" s="1">
-        <v>5098.22</v>
+      <c r="J90" t="str">
+        <v/>
       </c>
       <c r="K90" s="1">
-        <v>5237.87</v>
+        <v>28093.5</v>
       </c>
       <c r="L90" s="1">
-        <v>5310.32</v>
-      </c>
-      <c r="M90" t="str">
+        <v>29400.12</v>
+      </c>
+      <c r="M90" s="3">
+        <v>-188.9</v>
+      </c>
+      <c r="N90" s="3">
+        <v>-400.05</v>
+      </c>
+      <c r="O90" s="3">
+        <v>-188.9</v>
+      </c>
+      <c r="P90" s="3">
+        <v>171.93</v>
+      </c>
+      <c r="Q90" s="3">
+        <v>223.94</v>
+      </c>
+      <c r="R90" s="3">
+        <v>-400.05</v>
+      </c>
+      <c r="S90" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S90"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Index.xlsx
+++ b/Index.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:T90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -461,6 +461,9 @@
         <v>MONTLY macd_signal</v>
       </c>
       <c r="S1" t="str">
+        <v>rsi</v>
+      </c>
+      <c r="T1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -502,7 +505,7 @@
         <v>12.43</v>
       </c>
       <c r="M2" s="3">
-        <v>-0.29</v>
+        <v>0.73</v>
       </c>
       <c r="N2" s="3">
         <v>0.67</v>
@@ -517,9 +520,12 @@
         <v>-0.02</v>
       </c>
       <c r="R2" s="3">
-        <v>0.67</v>
-      </c>
-      <c r="S2" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="S2" s="3">
+        <v>61.67</v>
+      </c>
+      <c r="T2" t="str">
         <v/>
       </c>
     </row>
@@ -561,7 +567,7 @@
         <v>29827.11</v>
       </c>
       <c r="M3" s="3">
-        <v>-122.78</v>
+        <v>574.23</v>
       </c>
       <c r="N3" s="3">
         <v>44.9</v>
@@ -576,9 +582,12 @@
         <v>-1626.95</v>
       </c>
       <c r="R3" s="3">
-        <v>44.9</v>
-      </c>
-      <c r="S3" t="str">
+        <v>-1140.94</v>
+      </c>
+      <c r="S3" s="3">
+        <v>72.87</v>
+      </c>
+      <c r="T3" t="str">
         <v/>
       </c>
     </row>
@@ -620,7 +629,7 @@
         <v>11105.59</v>
       </c>
       <c r="M4" s="3">
-        <v>-106.66</v>
+        <v>-51.3</v>
       </c>
       <c r="N4" s="3">
         <v>-138.92</v>
@@ -635,9 +644,12 @@
         <v>39.38</v>
       </c>
       <c r="R4" s="3">
-        <v>-138.92</v>
-      </c>
-      <c r="S4" t="str">
+        <v>178.12</v>
+      </c>
+      <c r="S4" s="3">
+        <v>57.19</v>
+      </c>
+      <c r="T4" t="str">
         <v/>
       </c>
     </row>
@@ -679,7 +691,7 @@
         <v>8539.65</v>
       </c>
       <c r="M5" s="3">
-        <v>72.59</v>
+        <v>14.19</v>
       </c>
       <c r="N5" s="3">
         <v>-54.53</v>
@@ -694,9 +706,12 @@
         <v>379.07</v>
       </c>
       <c r="R5" s="3">
-        <v>-54.53</v>
-      </c>
-      <c r="S5" t="str">
+        <v>515.06</v>
+      </c>
+      <c r="S5" s="3">
+        <v>59.85</v>
+      </c>
+      <c r="T5" t="str">
         <v/>
       </c>
     </row>
@@ -738,7 +753,7 @@
         <v>184.26</v>
       </c>
       <c r="M6" s="3">
-        <v>3.4</v>
+        <v>1.49</v>
       </c>
       <c r="N6" s="3">
         <v>2.17</v>
@@ -753,9 +768,12 @@
         <v>-2.58</v>
       </c>
       <c r="R6" s="3">
-        <v>2.17</v>
-      </c>
-      <c r="S6" t="str">
+        <v>-6.05</v>
+      </c>
+      <c r="S6" s="3">
+        <v>54.13</v>
+      </c>
+      <c r="T6" t="str">
         <v/>
       </c>
     </row>
@@ -797,7 +815,7 @@
         <v>227.14</v>
       </c>
       <c r="M7" s="3">
-        <v>4.58</v>
+        <v>1.87</v>
       </c>
       <c r="N7" s="3">
         <v>2.7</v>
@@ -812,9 +830,12 @@
         <v>-0.76</v>
       </c>
       <c r="R7" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="S7" t="str">
+        <v>-4.79</v>
+      </c>
+      <c r="S7" s="3">
+        <v>54.26</v>
+      </c>
+      <c r="T7" t="str">
         <v/>
       </c>
     </row>
@@ -856,7 +877,7 @@
         <v>30135.4</v>
       </c>
       <c r="M8" s="3">
-        <v>-341.3</v>
+        <v>-17.67</v>
       </c>
       <c r="N8" s="3">
         <v>-202.88</v>
@@ -871,9 +892,12 @@
         <v>500.38</v>
       </c>
       <c r="R8" s="3">
-        <v>-202.88</v>
-      </c>
-      <c r="S8" t="str">
+        <v>994.57</v>
+      </c>
+      <c r="S8" s="3">
+        <v>56.72</v>
+      </c>
+      <c r="T8" t="str">
         <v/>
       </c>
     </row>
@@ -915,7 +939,7 @@
         <v>5697.85</v>
       </c>
       <c r="M9" s="3">
-        <v>-114.41</v>
+        <v>-30.22</v>
       </c>
       <c r="N9" s="3">
         <v>-62.87</v>
@@ -930,9 +954,12 @@
         <v>29.69</v>
       </c>
       <c r="R9" s="3">
-        <v>-62.87</v>
-      </c>
-      <c r="S9" t="str">
+        <v>140.42</v>
+      </c>
+      <c r="S9" s="3">
+        <v>53.27</v>
+      </c>
+      <c r="T9" t="str">
         <v/>
       </c>
     </row>
@@ -974,7 +1001,7 @@
         <v>11569.55</v>
       </c>
       <c r="M10" s="3">
-        <v>-258.01</v>
+        <v>-47.78</v>
       </c>
       <c r="N10" s="3">
         <v>-102.06</v>
@@ -989,9 +1016,12 @@
         <v>-123.99</v>
       </c>
       <c r="R10" s="3">
-        <v>-102.06</v>
-      </c>
-      <c r="S10" t="str">
+        <v>115.64</v>
+      </c>
+      <c r="S10" s="3">
+        <v>51.31</v>
+      </c>
+      <c r="T10" t="str">
         <v/>
       </c>
     </row>
@@ -1033,7 +1063,7 @@
         <v>8406.86</v>
       </c>
       <c r="M11" s="3">
-        <v>-157</v>
+        <v>-12.44</v>
       </c>
       <c r="N11" s="3">
         <v>-53.46</v>
@@ -1048,9 +1078,12 @@
         <v>-302.34</v>
       </c>
       <c r="R11" s="3">
-        <v>-53.46</v>
-      </c>
-      <c r="S11" t="str">
+        <v>-191.79</v>
+      </c>
+      <c r="S11" s="3">
+        <v>53.08</v>
+      </c>
+      <c r="T11" t="str">
         <v/>
       </c>
     </row>
@@ -1092,7 +1125,7 @@
         <v>194.5</v>
       </c>
       <c r="M12" s="3">
-        <v>11.77</v>
+        <v>2.59</v>
       </c>
       <c r="N12" s="3">
         <v>2.55</v>
@@ -1107,9 +1140,12 @@
         <v>5.31</v>
       </c>
       <c r="R12" s="3">
-        <v>2.55</v>
-      </c>
-      <c r="S12" t="str">
+        <v>7.65</v>
+      </c>
+      <c r="S12" s="3">
+        <v>100</v>
+      </c>
+      <c r="T12" t="str">
         <v/>
       </c>
     </row>
@@ -1151,7 +1187,7 @@
         <v>14058.48</v>
       </c>
       <c r="M13" s="3">
-        <v>-209.79</v>
+        <v>-65.77</v>
       </c>
       <c r="N13" s="3">
         <v>-154.97</v>
@@ -1166,9 +1202,12 @@
         <v>-529.71</v>
       </c>
       <c r="R13" s="3">
-        <v>-154.97</v>
-      </c>
-      <c r="S13" t="str">
+        <v>-490.48</v>
+      </c>
+      <c r="S13" s="3">
+        <v>52.79</v>
+      </c>
+      <c r="T13" t="str">
         <v/>
       </c>
     </row>
@@ -1210,7 +1249,7 @@
         <v>1458.76</v>
       </c>
       <c r="M14" s="3">
-        <v>4.31</v>
+        <v>-3.19</v>
       </c>
       <c r="N14" s="3">
         <v>-2.6</v>
@@ -1225,9 +1264,12 @@
         <v>29.24</v>
       </c>
       <c r="R14" s="3">
-        <v>-2.6</v>
-      </c>
-      <c r="S14" t="str">
+        <v>28.57</v>
+      </c>
+      <c r="S14" s="3">
+        <v>26.99</v>
+      </c>
+      <c r="T14" t="str">
         <v/>
       </c>
     </row>
@@ -1269,7 +1311,7 @@
         <v>1322.5</v>
       </c>
       <c r="M15" s="3">
-        <v>2.29</v>
+        <v>-3.98</v>
       </c>
       <c r="N15" s="3">
         <v>-3.41</v>
@@ -1284,9 +1326,12 @@
         <v>24.09</v>
       </c>
       <c r="R15" s="3">
-        <v>-3.41</v>
-      </c>
-      <c r="S15" t="str">
+        <v>24.23</v>
+      </c>
+      <c r="S15" s="3">
+        <v>24.56</v>
+      </c>
+      <c r="T15" t="str">
         <v/>
       </c>
     </row>
@@ -1328,7 +1373,7 @@
         <v>10905.06</v>
       </c>
       <c r="M16" s="3">
-        <v>-218</v>
+        <v>-119.89</v>
       </c>
       <c r="N16" s="3">
         <v>-142.5</v>
@@ -1343,9 +1388,12 @@
         <v>80.45</v>
       </c>
       <c r="R16" s="3">
-        <v>-142.5</v>
-      </c>
-      <c r="S16" t="str">
+        <v>280.89</v>
+      </c>
+      <c r="S16" s="3">
+        <v>43.21</v>
+      </c>
+      <c r="T16" t="str">
         <v/>
       </c>
     </row>
@@ -1387,7 +1435,7 @@
         <v>1609.22</v>
       </c>
       <c r="M17" s="3">
-        <v>6.91</v>
+        <v>-2.06</v>
       </c>
       <c r="N17" s="3">
         <v>-1.42</v>
@@ -1402,9 +1450,12 @@
         <v>34.86</v>
       </c>
       <c r="R17" s="3">
-        <v>-1.42</v>
-      </c>
-      <c r="S17" t="str">
+        <v>33.12</v>
+      </c>
+      <c r="S17" s="3">
+        <v>31.14</v>
+      </c>
+      <c r="T17" t="str">
         <v/>
       </c>
     </row>
@@ -1446,7 +1497,7 @@
         <v>19544.08</v>
       </c>
       <c r="M18" s="3">
-        <v>-297.59</v>
+        <v>-221.72</v>
       </c>
       <c r="N18" s="3">
         <v>-272.22</v>
@@ -1461,9 +1512,12 @@
         <v>758.22</v>
       </c>
       <c r="R18" s="3">
-        <v>-272.22</v>
-      </c>
-      <c r="S18" t="str">
+        <v>1111.46</v>
+      </c>
+      <c r="S18" s="3">
+        <v>41.01</v>
+      </c>
+      <c r="T18" t="str">
         <v/>
       </c>
     </row>
@@ -1478,51 +1532,54 @@
         <v>NIFTYGS48YR</v>
       </c>
       <c r="D19" s="1">
-        <v>3278.79</v>
+        <v>3279.32</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="F19" s="2">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="G19" s="2">
-        <v>-0.9</v>
+        <v>-0.88</v>
       </c>
       <c r="H19" s="2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>3279.88</v>
+        <v>3279.89</v>
       </c>
       <c r="K19" s="1">
-        <v>3287.81</v>
+        <v>3287.9</v>
       </c>
       <c r="L19" s="1">
-        <v>3322.72</v>
+        <v>3322.73</v>
       </c>
       <c r="M19" s="3">
-        <v>7.86</v>
+        <v>-11.94</v>
       </c>
       <c r="N19" s="3">
-        <v>-10.9</v>
+        <v>-10.89</v>
       </c>
       <c r="O19" s="3">
-        <v>7.86</v>
+        <v>7.91</v>
       </c>
       <c r="P19" s="3">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="Q19" s="3">
-        <v>139.63</v>
+        <v>139.67</v>
       </c>
       <c r="R19" s="3">
-        <v>-10.9</v>
-      </c>
-      <c r="S19" t="str">
+        <v>155.44</v>
+      </c>
+      <c r="S19" s="3">
+        <v>26.28</v>
+      </c>
+      <c r="T19" t="str">
         <v/>
       </c>
     </row>
@@ -1564,7 +1621,7 @@
         <v>1280.91</v>
       </c>
       <c r="M20" s="3">
-        <v>1.21</v>
+        <v>-4.76</v>
       </c>
       <c r="N20" s="3">
         <v>-3.99</v>
@@ -1579,9 +1636,12 @@
         <v>21.3</v>
       </c>
       <c r="R20" s="3">
-        <v>-3.99</v>
-      </c>
-      <c r="S20" t="str">
+        <v>21.95</v>
+      </c>
+      <c r="S20" s="3">
+        <v>21.73</v>
+      </c>
+      <c r="T20" t="str">
         <v/>
       </c>
     </row>
@@ -1623,7 +1683,7 @@
         <v>7411.18</v>
       </c>
       <c r="M21" s="3">
-        <v>1.91</v>
+        <v>-6.23</v>
       </c>
       <c r="N21" s="3">
         <v>-48.28</v>
@@ -1638,9 +1698,12 @@
         <v>472.8</v>
       </c>
       <c r="R21" s="3">
-        <v>-48.28</v>
-      </c>
-      <c r="S21" t="str">
+        <v>552.77</v>
+      </c>
+      <c r="S21" s="3">
+        <v>54.1</v>
+      </c>
+      <c r="T21" t="str">
         <v/>
       </c>
     </row>
@@ -1682,7 +1745,7 @@
         <v>26485.28</v>
       </c>
       <c r="M22" s="3">
-        <v>596.89</v>
+        <v>-251.44</v>
       </c>
       <c r="N22" s="3">
         <v>-167.21</v>
@@ -1697,9 +1760,12 @@
         <v>1772.23</v>
       </c>
       <c r="R22" s="3">
-        <v>-167.21</v>
-      </c>
-      <c r="S22" t="str">
+        <v>1606.89</v>
+      </c>
+      <c r="S22" s="3">
+        <v>35.97</v>
+      </c>
+      <c r="T22" t="str">
         <v/>
       </c>
     </row>
@@ -1714,51 +1780,54 @@
         <v>NIFTYGS1115YR</v>
       </c>
       <c r="D23" s="1">
-        <v>3286.75</v>
+        <v>3285.69</v>
       </c>
       <c r="E23" s="2">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="F23" s="2">
-        <v>-0.5</v>
+        <v>-0.53</v>
       </c>
       <c r="G23" s="2">
-        <v>-1.05</v>
+        <v>-1.08</v>
       </c>
       <c r="H23" s="2">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>3294.91</v>
+        <v>3294.9</v>
       </c>
       <c r="K23" s="1">
-        <v>3299.5</v>
+        <v>3299.31</v>
       </c>
       <c r="L23" s="1">
-        <v>3351.83</v>
+        <v>3351.81</v>
       </c>
       <c r="M23" s="3">
-        <v>7.67</v>
+        <v>-17.55</v>
       </c>
       <c r="N23" s="3">
-        <v>-17.07</v>
+        <v>-17.08</v>
       </c>
       <c r="O23" s="3">
-        <v>7.67</v>
+        <v>7.59</v>
       </c>
       <c r="P23" s="3">
-        <v>21.52</v>
+        <v>21.5</v>
       </c>
       <c r="Q23" s="3">
-        <v>136.55</v>
+        <v>136.47</v>
       </c>
       <c r="R23" s="3">
-        <v>-17.07</v>
-      </c>
-      <c r="S23" t="str">
+        <v>153.9</v>
+      </c>
+      <c r="S23" s="3">
+        <v>32.58</v>
+      </c>
+      <c r="T23" t="str">
         <v/>
       </c>
     </row>
@@ -1767,57 +1836,60 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C24" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D24" s="1">
-        <v>3063.81</v>
+        <v>15507.15</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="F24" s="2">
-        <v>-0.4</v>
+        <v>-1.12</v>
       </c>
       <c r="G24" s="2">
-        <v>-1.3</v>
+        <v>-3.91</v>
       </c>
       <c r="H24" s="2">
-        <v>0.37</v>
+        <v>5.92</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>3085.9</v>
+        <v>15436.28</v>
       </c>
       <c r="K24" s="1">
-        <v>3077.27</v>
+        <v>15759.68</v>
       </c>
       <c r="L24" s="1">
-        <v>3121.15</v>
+        <v>16373.32</v>
       </c>
       <c r="M24" s="3">
-        <v>2.74</v>
+        <v>-247.94</v>
       </c>
       <c r="N24" s="3">
-        <v>-13.78</v>
+        <v>-197.67</v>
       </c>
       <c r="O24" s="3">
-        <v>2.74</v>
+        <v>170.72</v>
       </c>
       <c r="P24" s="3">
-        <v>13.99</v>
+        <v>340.41</v>
       </c>
       <c r="Q24" s="3">
-        <v>118.74</v>
+        <v>978.42</v>
       </c>
       <c r="R24" s="3">
-        <v>-13.78</v>
-      </c>
-      <c r="S24" t="str">
+        <v>994.15</v>
+      </c>
+      <c r="S24" s="3">
+        <v>30.73</v>
+      </c>
+      <c r="T24" t="str">
         <v/>
       </c>
     </row>
@@ -1826,57 +1898,60 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D25" s="1">
-        <v>15507.15</v>
+        <v>5407.3</v>
       </c>
       <c r="E25" s="2">
         <v>-0.32</v>
       </c>
       <c r="F25" s="2">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="G25" s="2">
-        <v>-3.91</v>
+        <v>1.63</v>
       </c>
       <c r="H25" s="2">
-        <v>5.92</v>
+        <v>-7.73</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>15436.28</v>
+        <v>5551.02</v>
       </c>
       <c r="K25" s="1">
-        <v>15759.68</v>
+        <v>5382.02</v>
       </c>
       <c r="L25" s="1">
-        <v>16373.32</v>
+        <v>5530.09</v>
       </c>
       <c r="M25" s="3">
-        <v>170.72</v>
+        <v>-28.38</v>
       </c>
       <c r="N25" s="3">
-        <v>-197.67</v>
+        <v>-54.85</v>
       </c>
       <c r="O25" s="3">
-        <v>170.72</v>
+        <v>-42.26</v>
       </c>
       <c r="P25" s="3">
-        <v>340.41</v>
+        <v>-16.83</v>
       </c>
       <c r="Q25" s="3">
-        <v>978.42</v>
+        <v>190.86</v>
       </c>
       <c r="R25" s="3">
-        <v>-197.67</v>
-      </c>
-      <c r="S25" t="str">
+        <v>261.84</v>
+      </c>
+      <c r="S25" s="3">
+        <v>49.71</v>
+      </c>
+      <c r="T25" t="str">
         <v/>
       </c>
     </row>
@@ -1885,57 +1960,60 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C26" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D26" s="1">
-        <v>5407.3</v>
+        <v>3063.29</v>
       </c>
       <c r="E26" s="2">
         <v>-0.32</v>
       </c>
       <c r="F26" s="2">
-        <v>-1.18</v>
+        <v>-0.42</v>
       </c>
       <c r="G26" s="2">
-        <v>1.63</v>
+        <v>-1.32</v>
       </c>
       <c r="H26" s="2">
-        <v>-7.73</v>
+        <v>0.36</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>5551.02</v>
+        <v>3085.9</v>
       </c>
       <c r="K26" s="1">
-        <v>5382.02</v>
+        <v>3077.18</v>
       </c>
       <c r="L26" s="1">
-        <v>5530.09</v>
+        <v>3121.14</v>
       </c>
       <c r="M26" s="3">
-        <v>-42.26</v>
+        <v>-15.31</v>
       </c>
       <c r="N26" s="3">
-        <v>-54.85</v>
+        <v>-13.79</v>
       </c>
       <c r="O26" s="3">
-        <v>-42.26</v>
+        <v>2.7</v>
       </c>
       <c r="P26" s="3">
-        <v>-16.83</v>
+        <v>13.98</v>
       </c>
       <c r="Q26" s="3">
-        <v>190.86</v>
+        <v>118.7</v>
       </c>
       <c r="R26" s="3">
-        <v>-54.85</v>
-      </c>
-      <c r="S26" t="str">
+        <v>136.59</v>
+      </c>
+      <c r="S26" s="3">
+        <v>28.74</v>
+      </c>
+      <c r="T26" t="str">
         <v/>
       </c>
     </row>
@@ -1944,57 +2022,60 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C27" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D27" s="1">
-        <v>22811.35</v>
+        <v>2599.63</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="F27" s="2">
-        <v>-1.45</v>
+        <v>-0.44</v>
       </c>
       <c r="G27" s="2">
-        <v>0.84</v>
+        <v>-1.46</v>
       </c>
       <c r="H27" s="2">
-        <v>-12.7</v>
+        <v>-0.47</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>24152.75</v>
+        <v>2632.39</v>
       </c>
       <c r="K27" s="1">
-        <v>22800.48</v>
+        <v>2612.3</v>
       </c>
       <c r="L27" s="1">
-        <v>23479.08</v>
+        <v>2651.46</v>
       </c>
       <c r="M27" s="3">
-        <v>-384.19</v>
+        <v>-13.88</v>
       </c>
       <c r="N27" s="3">
-        <v>-253.14</v>
+        <v>-12.44</v>
       </c>
       <c r="O27" s="3">
-        <v>-384.19</v>
+        <v>-1.91</v>
       </c>
       <c r="P27" s="3">
-        <v>-274.8</v>
+        <v>7.47</v>
       </c>
       <c r="Q27" s="3">
-        <v>194.04</v>
+        <v>89.9</v>
       </c>
       <c r="R27" s="3">
-        <v>-253.14</v>
-      </c>
-      <c r="S27" t="str">
+        <v>106.39</v>
+      </c>
+      <c r="S27" s="3">
+        <v>27.72</v>
+      </c>
+      <c r="T27" t="str">
         <v/>
       </c>
     </row>
@@ -2003,57 +2084,60 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTY</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTY</v>
       </c>
       <c r="D28" s="1">
-        <v>2599.44</v>
+        <v>22811.35</v>
       </c>
       <c r="E28" s="2">
         <v>-0.34</v>
       </c>
       <c r="F28" s="2">
-        <v>-0.45</v>
+        <v>-1.45</v>
       </c>
       <c r="G28" s="2">
-        <v>-1.47</v>
+        <v>0.84</v>
       </c>
       <c r="H28" s="2">
-        <v>-0.48</v>
+        <v>-12.7</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>2632.39</v>
+        <v>24152.75</v>
       </c>
       <c r="K28" s="1">
-        <v>2612.27</v>
+        <v>22800.48</v>
       </c>
       <c r="L28" s="1">
-        <v>2651.46</v>
+        <v>23479.08</v>
       </c>
       <c r="M28" s="3">
-        <v>-1.92</v>
+        <v>-170.52</v>
       </c>
       <c r="N28" s="3">
-        <v>-12.45</v>
+        <v>-253.14</v>
       </c>
       <c r="O28" s="3">
-        <v>-1.92</v>
+        <v>-384.19</v>
       </c>
       <c r="P28" s="3">
-        <v>7.47</v>
+        <v>-274.8</v>
       </c>
       <c r="Q28" s="3">
-        <v>89.89</v>
+        <v>194.04</v>
       </c>
       <c r="R28" s="3">
-        <v>-12.45</v>
-      </c>
-      <c r="S28" t="str">
+        <v>599.66</v>
+      </c>
+      <c r="S28" s="3">
+        <v>46.27</v>
+      </c>
+      <c r="T28" t="str">
         <v/>
       </c>
     </row>
@@ -2068,19 +2152,19 @@
         <v>NIFTYGS813YR</v>
       </c>
       <c r="D29" s="1">
-        <v>2970.32</v>
+        <v>2970.67</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="F29" s="2">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="G29" s="2">
-        <v>-1.45</v>
+        <v>-1.43</v>
       </c>
       <c r="H29" s="2">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -2089,30 +2173,33 @@
         <v>3001.36</v>
       </c>
       <c r="K29" s="1">
-        <v>2985.03</v>
+        <v>2985.1</v>
       </c>
       <c r="L29" s="1">
-        <v>3029.09</v>
+        <v>3029.1</v>
       </c>
       <c r="M29" s="3">
-        <v>0.3</v>
+        <v>-15.54</v>
       </c>
       <c r="N29" s="3">
-        <v>-13.9</v>
+        <v>-13.89</v>
       </c>
       <c r="O29" s="3">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="P29" s="3">
         <v>11.42</v>
       </c>
       <c r="Q29" s="3">
-        <v>114.75</v>
+        <v>114.78</v>
       </c>
       <c r="R29" s="3">
-        <v>-13.9</v>
-      </c>
-      <c r="S29" t="str">
+        <v>132.83</v>
+      </c>
+      <c r="S29" s="3">
+        <v>26.3</v>
+      </c>
+      <c r="T29" t="str">
         <v/>
       </c>
     </row>
@@ -2154,7 +2241,7 @@
         <v>9030.52</v>
       </c>
       <c r="M30" s="3">
-        <v>-160.89</v>
+        <v>-115.69</v>
       </c>
       <c r="N30" s="3">
         <v>-133.7</v>
@@ -2169,9 +2256,12 @@
         <v>270.39</v>
       </c>
       <c r="R30" s="3">
-        <v>-133.7</v>
-      </c>
-      <c r="S30" t="str">
+        <v>433.46</v>
+      </c>
+      <c r="S30" s="3">
+        <v>40.81</v>
+      </c>
+      <c r="T30" t="str">
         <v/>
       </c>
     </row>
@@ -2186,19 +2276,19 @@
         <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D31" s="1">
-        <v>838.77</v>
+        <v>838.84</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="F31" s="2">
-        <v>-0.56</v>
+        <v>-0.55</v>
       </c>
       <c r="G31" s="2">
-        <v>-1.92</v>
+        <v>-1.91</v>
       </c>
       <c r="H31" s="2">
-        <v>-5.91</v>
+        <v>-5.9</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -2207,13 +2297,13 @@
         <v>874.12</v>
       </c>
       <c r="K31" s="1">
-        <v>844.31</v>
+        <v>844.32</v>
       </c>
       <c r="L31" s="1">
-        <v>862.31</v>
+        <v>862.32</v>
       </c>
       <c r="M31" s="3">
-        <v>-8.71</v>
+        <v>-6.36</v>
       </c>
       <c r="N31" s="3">
         <v>-5.87</v>
@@ -2222,15 +2312,18 @@
         <v>-8.71</v>
       </c>
       <c r="P31" s="3">
-        <v>-5.63</v>
+        <v>-5.62</v>
       </c>
       <c r="Q31" s="3">
         <v>-17.16</v>
       </c>
       <c r="R31" s="3">
-        <v>-5.87</v>
-      </c>
-      <c r="S31" t="str">
+        <v>-14.18</v>
+      </c>
+      <c r="S31" s="3">
+        <v>21.96</v>
+      </c>
+      <c r="T31" t="str">
         <v/>
       </c>
     </row>
@@ -2272,7 +2365,7 @@
         <v>3932.4</v>
       </c>
       <c r="M32" s="3">
-        <v>-65.6</v>
+        <v>-34.28</v>
       </c>
       <c r="N32" s="3">
         <v>-47.65</v>
@@ -2287,9 +2380,12 @@
         <v>126.58</v>
       </c>
       <c r="R32" s="3">
-        <v>-47.65</v>
-      </c>
-      <c r="S32" t="str">
+        <v>206.84</v>
+      </c>
+      <c r="S32" s="3">
+        <v>44.56</v>
+      </c>
+      <c r="T32" t="str">
         <v/>
       </c>
     </row>
@@ -2298,57 +2394,60 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D33" s="1">
-        <v>3471.25</v>
+        <v>19156.1</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="F33" s="2">
-        <v>-0.47</v>
+        <v>-1.61</v>
       </c>
       <c r="G33" s="2">
-        <v>-1.44</v>
+        <v>1.12</v>
       </c>
       <c r="H33" s="2">
-        <v>-0.62</v>
+        <v>-10.53</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>3495.57</v>
+        <v>20111.69</v>
       </c>
       <c r="K33" s="1">
-        <v>3487.63</v>
+        <v>19193.39</v>
       </c>
       <c r="L33" s="1">
-        <v>3537.21</v>
+        <v>19857.23</v>
       </c>
       <c r="M33" s="3">
-        <v>2.99</v>
+        <v>-149.24</v>
       </c>
       <c r="N33" s="3">
-        <v>-14.86</v>
+        <v>-231.83</v>
       </c>
       <c r="O33" s="3">
-        <v>2.99</v>
+        <v>-265.24</v>
       </c>
       <c r="P33" s="3">
-        <v>15.47</v>
+        <v>-138.8</v>
       </c>
       <c r="Q33" s="3">
-        <v>119.04</v>
+        <v>500.78</v>
       </c>
       <c r="R33" s="3">
-        <v>-14.86</v>
-      </c>
-      <c r="S33" t="str">
+        <v>798.2</v>
+      </c>
+      <c r="S33" s="3">
+        <v>45.01</v>
+      </c>
+      <c r="T33" t="str">
         <v/>
       </c>
     </row>
@@ -2357,57 +2456,60 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C34" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D34" s="1">
-        <v>19156.1</v>
+        <v>8251.5</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.46</v>
+        <v>-0.51</v>
       </c>
       <c r="F34" s="2">
-        <v>-1.61</v>
+        <v>1.93</v>
       </c>
       <c r="G34" s="2">
-        <v>1.12</v>
+        <v>2.94</v>
       </c>
       <c r="H34" s="2">
-        <v>-10.53</v>
+        <v>-3.3</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>20111.69</v>
+        <v>8575.14</v>
       </c>
       <c r="K34" s="1">
-        <v>19193.39</v>
+        <v>8150.85</v>
       </c>
       <c r="L34" s="1">
-        <v>19857.23</v>
+        <v>8364.1</v>
       </c>
       <c r="M34" s="3">
-        <v>-265.24</v>
+        <v>-42.26</v>
       </c>
       <c r="N34" s="3">
-        <v>-231.83</v>
+        <v>-78.63</v>
       </c>
       <c r="O34" s="3">
-        <v>-265.24</v>
+        <v>-75.54</v>
       </c>
       <c r="P34" s="3">
-        <v>-138.8</v>
+        <v>-29.76</v>
       </c>
       <c r="Q34" s="3">
-        <v>500.78</v>
+        <v>575.37</v>
       </c>
       <c r="R34" s="3">
-        <v>-231.83</v>
-      </c>
-      <c r="S34" t="str">
+        <v>685.4</v>
+      </c>
+      <c r="S34" s="3">
+        <v>52.71</v>
+      </c>
+      <c r="T34" t="str">
         <v/>
       </c>
     </row>
@@ -2416,57 +2518,60 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D35" s="1">
-        <v>8251.5</v>
+        <v>30743.2</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="F35" s="2">
-        <v>1.93</v>
+        <v>-1.46</v>
       </c>
       <c r="G35" s="2">
-        <v>2.94</v>
+        <v>-0.52</v>
       </c>
       <c r="H35" s="2">
-        <v>-3.3</v>
+        <v>-7.76</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>8575.14</v>
+        <v>32364.85</v>
       </c>
       <c r="K35" s="1">
-        <v>8150.85</v>
+        <v>30867.57</v>
       </c>
       <c r="L35" s="1">
-        <v>8364.1</v>
+        <v>32046.75</v>
       </c>
       <c r="M35" s="3">
-        <v>-75.54</v>
+        <v>-338.01</v>
       </c>
       <c r="N35" s="3">
-        <v>-78.63</v>
+        <v>-419.77</v>
       </c>
       <c r="O35" s="3">
-        <v>-75.54</v>
+        <v>-376.58</v>
       </c>
       <c r="P35" s="3">
-        <v>-29.76</v>
+        <v>-112.38</v>
       </c>
       <c r="Q35" s="3">
-        <v>575.37</v>
+        <v>1837.58</v>
       </c>
       <c r="R35" s="3">
-        <v>-78.63</v>
-      </c>
-      <c r="S35" t="str">
+        <v>2375</v>
+      </c>
+      <c r="S35" s="3">
+        <v>41.81</v>
+      </c>
+      <c r="T35" t="str">
         <v/>
       </c>
     </row>
@@ -2475,57 +2580,60 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D36" s="1">
-        <v>30743.2</v>
+        <v>3468.19</v>
       </c>
       <c r="E36" s="2">
         <v>-0.53</v>
       </c>
       <c r="F36" s="2">
-        <v>-1.46</v>
+        <v>-0.56</v>
       </c>
       <c r="G36" s="2">
-        <v>-0.52</v>
+        <v>-1.52</v>
       </c>
       <c r="H36" s="2">
-        <v>-7.76</v>
+        <v>-0.71</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>32364.85</v>
+        <v>3495.56</v>
       </c>
       <c r="K36" s="1">
-        <v>30867.57</v>
+        <v>3487.08</v>
       </c>
       <c r="L36" s="1">
-        <v>32046.75</v>
+        <v>3537.15</v>
       </c>
       <c r="M36" s="3">
-        <v>-376.58</v>
+        <v>-17.33</v>
       </c>
       <c r="N36" s="3">
-        <v>-419.77</v>
+        <v>-14.91</v>
       </c>
       <c r="O36" s="3">
-        <v>-376.58</v>
+        <v>2.75</v>
       </c>
       <c r="P36" s="3">
-        <v>-112.38</v>
+        <v>15.42</v>
       </c>
       <c r="Q36" s="3">
-        <v>1837.58</v>
+        <v>118.79</v>
       </c>
       <c r="R36" s="3">
-        <v>-419.77</v>
-      </c>
-      <c r="S36" t="str">
+        <v>141.9</v>
+      </c>
+      <c r="S36" s="3">
+        <v>34.41</v>
+      </c>
+      <c r="T36" t="str">
         <v/>
       </c>
     </row>
@@ -2567,7 +2675,7 @@
         <v>4876.33</v>
       </c>
       <c r="M37" s="3">
-        <v>-49.2</v>
+        <v>-40.85</v>
       </c>
       <c r="N37" s="3">
         <v>-59</v>
@@ -2582,9 +2690,12 @@
         <v>221.41</v>
       </c>
       <c r="R37" s="3">
-        <v>-59</v>
-      </c>
-      <c r="S37" t="str">
+        <v>299.71</v>
+      </c>
+      <c r="S37" s="3">
+        <v>45.15</v>
+      </c>
+      <c r="T37" t="str">
         <v/>
       </c>
     </row>
@@ -2626,7 +2737,7 @@
         <v>24598.3</v>
       </c>
       <c r="M38" s="3">
-        <v>-338.56</v>
+        <v>-208.23</v>
       </c>
       <c r="N38" s="3">
         <v>-278.91</v>
@@ -2641,9 +2752,12 @@
         <v>333.97</v>
       </c>
       <c r="R38" s="3">
-        <v>-278.91</v>
-      </c>
-      <c r="S38" t="str">
+        <v>708.96</v>
+      </c>
+      <c r="S38" s="3">
+        <v>43.81</v>
+      </c>
+      <c r="T38" t="str">
         <v/>
       </c>
     </row>
@@ -2685,7 +2799,7 @@
         <v>46007.7</v>
       </c>
       <c r="M39" s="3">
-        <v>-1619.09</v>
+        <v>-498.49</v>
       </c>
       <c r="N39" s="3">
         <v>-503.4</v>
@@ -2700,9 +2814,12 @@
         <v>-2136.87</v>
       </c>
       <c r="R39" s="3">
-        <v>-503.4</v>
-      </c>
-      <c r="S39" t="str">
+        <v>-960.19</v>
+      </c>
+      <c r="S39" s="3">
+        <v>39.34</v>
+      </c>
+      <c r="T39" t="str">
         <v/>
       </c>
     </row>
@@ -2744,7 +2861,7 @@
         <v>26187.65</v>
       </c>
       <c r="M40" s="3">
-        <v>-344.79</v>
+        <v>-432.82</v>
       </c>
       <c r="N40" s="3">
         <v>-457.75</v>
@@ -2759,9 +2876,12 @@
         <v>1146.92</v>
       </c>
       <c r="R40" s="3">
-        <v>-457.75</v>
-      </c>
-      <c r="S40" t="str">
+        <v>1596.11</v>
+      </c>
+      <c r="S40" s="3">
+        <v>32.82</v>
+      </c>
+      <c r="T40" t="str">
         <v/>
       </c>
     </row>
@@ -2803,7 +2923,7 @@
         <v>17200.33</v>
       </c>
       <c r="M41" s="3">
-        <v>-667.86</v>
+        <v>-279.07</v>
       </c>
       <c r="N41" s="3">
         <v>-396.25</v>
@@ -2818,9 +2938,12 @@
         <v>271.55</v>
       </c>
       <c r="R41" s="3">
-        <v>-396.25</v>
-      </c>
-      <c r="S41" t="str">
+        <v>928.1</v>
+      </c>
+      <c r="S41" s="3">
+        <v>45.26</v>
+      </c>
+      <c r="T41" t="str">
         <v/>
       </c>
     </row>
@@ -2862,7 +2985,7 @@
         <v>11284</v>
       </c>
       <c r="M42" s="3">
-        <v>-483.58</v>
+        <v>-185.56</v>
       </c>
       <c r="N42" s="3">
         <v>-262.43</v>
@@ -2877,9 +3000,12 @@
         <v>-9.91</v>
       </c>
       <c r="R42" s="3">
-        <v>-262.43</v>
-      </c>
-      <c r="S42" t="str">
+        <v>425.44</v>
+      </c>
+      <c r="S42" s="3">
+        <v>45.14</v>
+      </c>
+      <c r="T42" t="str">
         <v/>
       </c>
     </row>
@@ -2921,7 +3047,7 @@
         <v>6314.55</v>
       </c>
       <c r="M43" s="3">
-        <v>-200.83</v>
+        <v>-94.1</v>
       </c>
       <c r="N43" s="3">
         <v>-91.8</v>
@@ -2936,9 +3062,12 @@
         <v>231.81</v>
       </c>
       <c r="R43" s="3">
-        <v>-91.8</v>
-      </c>
-      <c r="S43" t="str">
+        <v>403.51</v>
+      </c>
+      <c r="S43" s="3">
+        <v>32.1</v>
+      </c>
+      <c r="T43" t="str">
         <v/>
       </c>
     </row>
@@ -2980,7 +3109,7 @@
         <v>13659.16</v>
       </c>
       <c r="M44" s="3">
-        <v>-163.63</v>
+        <v>-133.41</v>
       </c>
       <c r="N44" s="3">
         <v>-163.99</v>
@@ -2995,9 +3124,12 @@
         <v>272.21</v>
       </c>
       <c r="R44" s="3">
-        <v>-163.99</v>
-      </c>
-      <c r="S44" t="str">
+        <v>464.84</v>
+      </c>
+      <c r="S44" s="3">
+        <v>40.82</v>
+      </c>
+      <c r="T44" t="str">
         <v/>
       </c>
     </row>
@@ -3039,7 +3171,7 @@
         <v>56378.11</v>
       </c>
       <c r="M45" s="3">
-        <v>-347.01</v>
+        <v>-258.91</v>
       </c>
       <c r="N45" s="3">
         <v>-378.44</v>
@@ -3054,9 +3186,12 @@
         <v>1665.08</v>
       </c>
       <c r="R45" s="3">
-        <v>-378.44</v>
-      </c>
-      <c r="S45" t="str">
+        <v>2288.6</v>
+      </c>
+      <c r="S45" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="T45" t="str">
         <v/>
       </c>
     </row>
@@ -3098,7 +3233,7 @@
         <v>22831.63</v>
       </c>
       <c r="M46" s="3">
-        <v>-208.94</v>
+        <v>-230.62</v>
       </c>
       <c r="N46" s="3">
         <v>-266.46</v>
@@ -3113,9 +3248,12 @@
         <v>517.48</v>
       </c>
       <c r="R46" s="3">
-        <v>-266.46</v>
-      </c>
-      <c r="S46" t="str">
+        <v>805.44</v>
+      </c>
+      <c r="S46" s="3">
+        <v>38.47</v>
+      </c>
+      <c r="T46" t="str">
         <v/>
       </c>
     </row>
@@ -3157,7 +3295,7 @@
         <v>51627.33</v>
       </c>
       <c r="M47" s="3">
-        <v>950.03</v>
+        <v>-819.15</v>
       </c>
       <c r="N47" s="3">
         <v>-592.18</v>
@@ -3172,9 +3310,12 @@
         <v>2161.01</v>
       </c>
       <c r="R47" s="3">
-        <v>-592.18</v>
-      </c>
-      <c r="S47" t="str">
+        <v>1469.77</v>
+      </c>
+      <c r="S47" s="3">
+        <v>27.7</v>
+      </c>
+      <c r="T47" t="str">
         <v/>
       </c>
     </row>
@@ -3216,7 +3357,7 @@
         <v>27656.44</v>
       </c>
       <c r="M48" s="3">
-        <v>-477.2</v>
+        <v>-212.89</v>
       </c>
       <c r="N48" s="3">
         <v>-273.42</v>
@@ -3231,9 +3372,12 @@
         <v>1312.45</v>
       </c>
       <c r="R48" s="3">
-        <v>-273.42</v>
-      </c>
-      <c r="S48" t="str">
+        <v>1900.4</v>
+      </c>
+      <c r="S48" s="3">
+        <v>40.93</v>
+      </c>
+      <c r="T48" t="str">
         <v/>
       </c>
     </row>
@@ -3275,7 +3419,7 @@
         <v>11506.44</v>
       </c>
       <c r="M49" s="3">
-        <v>-151.16</v>
+        <v>-166.82</v>
       </c>
       <c r="N49" s="3">
         <v>-183.63</v>
@@ -3290,9 +3434,12 @@
         <v>217.16</v>
       </c>
       <c r="R49" s="3">
-        <v>-183.63</v>
-      </c>
-      <c r="S49" t="str">
+        <v>394.1</v>
+      </c>
+      <c r="S49" s="3">
+        <v>37.32</v>
+      </c>
+      <c r="T49" t="str">
         <v/>
       </c>
     </row>
@@ -3334,7 +3481,7 @@
         <v>16338.06</v>
       </c>
       <c r="M50" s="3">
-        <v>-145.51</v>
+        <v>-190.62</v>
       </c>
       <c r="N50" s="3">
         <v>-211.59</v>
@@ -3349,9 +3496,12 @@
         <v>917.21</v>
       </c>
       <c r="R50" s="3">
-        <v>-211.59</v>
-      </c>
-      <c r="S50" t="str">
+        <v>1178.93</v>
+      </c>
+      <c r="S50" s="3">
+        <v>36.36</v>
+      </c>
+      <c r="T50" t="str">
         <v/>
       </c>
     </row>
@@ -3393,7 +3543,7 @@
         <v>9520.84</v>
       </c>
       <c r="M51" s="3">
-        <v>-180.52</v>
+        <v>-161.85</v>
       </c>
       <c r="N51" s="3">
         <v>-168.6</v>
@@ -3408,9 +3558,12 @@
         <v>389.72</v>
       </c>
       <c r="R51" s="3">
-        <v>-168.6</v>
-      </c>
-      <c r="S51" t="str">
+        <v>508.31</v>
+      </c>
+      <c r="S51" s="3">
+        <v>35.12</v>
+      </c>
+      <c r="T51" t="str">
         <v/>
       </c>
     </row>
@@ -3452,7 +3605,7 @@
         <v>12913.2</v>
       </c>
       <c r="M52" s="3">
-        <v>-96.37</v>
+        <v>-129.72</v>
       </c>
       <c r="N52" s="3">
         <v>-146.61</v>
@@ -3467,9 +3620,12 @@
         <v>630.33</v>
       </c>
       <c r="R52" s="3">
-        <v>-146.61</v>
-      </c>
-      <c r="S52" t="str">
+        <v>826.14</v>
+      </c>
+      <c r="S52" s="3">
+        <v>37.77</v>
+      </c>
+      <c r="T52" t="str">
         <v/>
       </c>
     </row>
@@ -3511,7 +3667,7 @@
         <v>34002.68</v>
       </c>
       <c r="M53" s="3">
-        <v>-241.58</v>
+        <v>-418.43</v>
       </c>
       <c r="N53" s="3">
         <v>-466.72</v>
@@ -3526,9 +3682,12 @@
         <v>2002</v>
       </c>
       <c r="R53" s="3">
-        <v>-466.72</v>
-      </c>
-      <c r="S53" t="str">
+        <v>2430.32</v>
+      </c>
+      <c r="S53" s="3">
+        <v>36.59</v>
+      </c>
+      <c r="T53" t="str">
         <v/>
       </c>
     </row>
@@ -3570,7 +3729,7 @@
         <v>14168.32</v>
       </c>
       <c r="M54" s="3">
-        <v>-165.45</v>
+        <v>-198.1</v>
       </c>
       <c r="N54" s="3">
         <v>-205.59</v>
@@ -3585,9 +3744,12 @@
         <v>75.86</v>
       </c>
       <c r="R54" s="3">
-        <v>-205.59</v>
-      </c>
-      <c r="S54" t="str">
+        <v>118.36</v>
+      </c>
+      <c r="S54" s="3">
+        <v>34.12</v>
+      </c>
+      <c r="T54" t="str">
         <v/>
       </c>
     </row>
@@ -3629,7 +3791,7 @@
         <v>27296.76</v>
       </c>
       <c r="M55" s="3">
-        <v>-33.88</v>
+        <v>1.17</v>
       </c>
       <c r="N55" s="3">
         <v>-42</v>
@@ -3644,9 +3806,12 @@
         <v>649.74</v>
       </c>
       <c r="R55" s="3">
-        <v>-42</v>
-      </c>
-      <c r="S55" t="str">
+        <v>875.83</v>
+      </c>
+      <c r="S55" s="3">
+        <v>44.99</v>
+      </c>
+      <c r="T55" t="str">
         <v/>
       </c>
     </row>
@@ -3688,7 +3853,7 @@
         <v>9554.65</v>
       </c>
       <c r="M56" s="3">
-        <v>-227.69</v>
+        <v>-120.21</v>
       </c>
       <c r="N56" s="3">
         <v>-125.88</v>
@@ -3703,9 +3868,12 @@
         <v>792.71</v>
       </c>
       <c r="R56" s="3">
-        <v>-125.88</v>
-      </c>
-      <c r="S56" t="str">
+        <v>1091.97</v>
+      </c>
+      <c r="S56" s="3">
+        <v>34.98</v>
+      </c>
+      <c r="T56" t="str">
         <v/>
       </c>
     </row>
@@ -3747,7 +3915,7 @@
         <v>23785.35</v>
       </c>
       <c r="M57" s="3">
-        <v>-199.03</v>
+        <v>-276.57</v>
       </c>
       <c r="N57" s="3">
         <v>-296.21</v>
@@ -3762,9 +3930,12 @@
         <v>1021.08</v>
       </c>
       <c r="R57" s="3">
-        <v>-296.21</v>
-      </c>
-      <c r="S57" t="str">
+        <v>1359.05</v>
+      </c>
+      <c r="S57" s="3">
+        <v>34.75</v>
+      </c>
+      <c r="T57" t="str">
         <v/>
       </c>
     </row>
@@ -3806,7 +3977,7 @@
         <v>25562.35</v>
       </c>
       <c r="M58" s="3">
-        <v>-355.41</v>
+        <v>-142.27</v>
       </c>
       <c r="N58" s="3">
         <v>-193.73</v>
@@ -3821,9 +3992,12 @@
         <v>650.94</v>
       </c>
       <c r="R58" s="3">
-        <v>-193.73</v>
-      </c>
-      <c r="S58" t="str">
+        <v>1081.75</v>
+      </c>
+      <c r="S58" s="3">
+        <v>41.66</v>
+      </c>
+      <c r="T58" t="str">
         <v/>
       </c>
     </row>
@@ -3865,7 +4039,7 @@
         <v>16250.98</v>
       </c>
       <c r="M59" s="3">
-        <v>-74.4</v>
+        <v>-172.83</v>
       </c>
       <c r="N59" s="3">
         <v>-184.14</v>
@@ -3880,9 +4054,12 @@
         <v>918.79</v>
       </c>
       <c r="R59" s="3">
-        <v>-184.14</v>
-      </c>
-      <c r="S59" t="str">
+        <v>1148.44</v>
+      </c>
+      <c r="S59" s="3">
+        <v>35.1</v>
+      </c>
+      <c r="T59" t="str">
         <v/>
       </c>
     </row>
@@ -3924,7 +4101,7 @@
         <v>865.65</v>
       </c>
       <c r="M60" s="3">
-        <v>0.08</v>
+        <v>-14.16</v>
       </c>
       <c r="N60" s="3">
         <v>-14.47</v>
@@ -3939,9 +4116,12 @@
         <v>1.73</v>
       </c>
       <c r="R60" s="3">
-        <v>-14.47</v>
-      </c>
-      <c r="S60" t="str">
+        <v>9.92</v>
+      </c>
+      <c r="S60" s="3">
+        <v>38.18</v>
+      </c>
+      <c r="T60" t="str">
         <v/>
       </c>
     </row>
@@ -3983,7 +4163,7 @@
         <v>1573.42</v>
       </c>
       <c r="M61" s="3">
-        <v>35.72</v>
+        <v>21.39</v>
       </c>
       <c r="N61" s="3">
         <v>13.97</v>
@@ -3998,9 +4178,12 @@
         <v>-70.23</v>
       </c>
       <c r="R61" s="3">
-        <v>13.97</v>
-      </c>
-      <c r="S61" t="str">
+        <v>-104.94</v>
+      </c>
+      <c r="S61" s="3">
+        <v>56.97</v>
+      </c>
+      <c r="T61" t="str">
         <v/>
       </c>
     </row>
@@ -4042,7 +4225,7 @@
         <v>37485.67</v>
       </c>
       <c r="M62" s="3">
-        <v>-516.35</v>
+        <v>-493.27</v>
       </c>
       <c r="N62" s="3">
         <v>-476.06</v>
@@ -4057,9 +4240,12 @@
         <v>966.04</v>
       </c>
       <c r="R62" s="3">
-        <v>-476.06</v>
-      </c>
-      <c r="S62" t="str">
+        <v>1234.53</v>
+      </c>
+      <c r="S62" s="3">
+        <v>32.16</v>
+      </c>
+      <c r="T62" t="str">
         <v/>
       </c>
     </row>
@@ -4101,7 +4287,7 @@
         <v>22680.93</v>
       </c>
       <c r="M63" s="3">
-        <v>-104.32</v>
+        <v>-336.91</v>
       </c>
       <c r="N63" s="3">
         <v>-329.9</v>
@@ -4116,9 +4302,12 @@
         <v>1702.72</v>
       </c>
       <c r="R63" s="3">
-        <v>-329.9</v>
-      </c>
-      <c r="S63" t="str">
+        <v>2027.16</v>
+      </c>
+      <c r="S63" s="3">
+        <v>30.21</v>
+      </c>
+      <c r="T63" t="str">
         <v/>
       </c>
     </row>
@@ -4160,7 +4349,7 @@
         <v>14377.8</v>
       </c>
       <c r="M64" s="3">
-        <v>-68.88</v>
+        <v>-231.56</v>
       </c>
       <c r="N64" s="3">
         <v>-238.81</v>
@@ -4175,9 +4364,12 @@
         <v>871.49</v>
       </c>
       <c r="R64" s="3">
-        <v>-238.81</v>
-      </c>
-      <c r="S64" t="str">
+        <v>1000.98</v>
+      </c>
+      <c r="S64" s="3">
+        <v>31.65</v>
+      </c>
+      <c r="T64" t="str">
         <v/>
       </c>
     </row>
@@ -4219,7 +4411,7 @@
         <v>16459.18</v>
       </c>
       <c r="M65" s="3">
-        <v>-42.17</v>
+        <v>-244.73</v>
       </c>
       <c r="N65" s="3">
         <v>-242.51</v>
@@ -4234,9 +4426,12 @@
         <v>361.13</v>
       </c>
       <c r="R65" s="3">
-        <v>-242.51</v>
-      </c>
-      <c r="S65" t="str">
+        <v>329.12</v>
+      </c>
+      <c r="S65" s="3">
+        <v>32.7</v>
+      </c>
+      <c r="T65" t="str">
         <v/>
       </c>
     </row>
@@ -4278,7 +4473,7 @@
         <v>71815.76</v>
       </c>
       <c r="M66" s="3">
-        <v>-198.3</v>
+        <v>-981.34</v>
       </c>
       <c r="N66" s="3">
         <v>-987.31</v>
@@ -4293,9 +4488,12 @@
         <v>2663.93</v>
       </c>
       <c r="R66" s="3">
-        <v>-987.31</v>
-      </c>
-      <c r="S66" t="str">
+        <v>3182.41</v>
+      </c>
+      <c r="S66" s="3">
+        <v>34.16</v>
+      </c>
+      <c r="T66" t="str">
         <v/>
       </c>
     </row>
@@ -4337,7 +4535,7 @@
         <v>27352.71</v>
       </c>
       <c r="M67" s="3">
-        <v>-282.28</v>
+        <v>-546.48</v>
       </c>
       <c r="N67" s="3">
         <v>-630.31</v>
@@ -4352,9 +4550,12 @@
         <v>1475.87</v>
       </c>
       <c r="R67" s="3">
-        <v>-630.31</v>
-      </c>
-      <c r="S67" t="str">
+        <v>1810.68</v>
+      </c>
+      <c r="S67" s="3">
+        <v>37.51</v>
+      </c>
+      <c r="T67" t="str">
         <v/>
       </c>
     </row>
@@ -4396,7 +4597,7 @@
         <v>15927.77</v>
       </c>
       <c r="M68" s="3">
-        <v>-93.27</v>
+        <v>-264.42</v>
       </c>
       <c r="N68" s="3">
         <v>-263.97</v>
@@ -4411,9 +4612,12 @@
         <v>1246.98</v>
       </c>
       <c r="R68" s="3">
-        <v>-263.97</v>
-      </c>
-      <c r="S68" t="str">
+        <v>1443.88</v>
+      </c>
+      <c r="S68" s="3">
+        <v>31.77</v>
+      </c>
+      <c r="T68" t="str">
         <v/>
       </c>
     </row>
@@ -4455,7 +4659,7 @@
         <v>61713.48</v>
       </c>
       <c r="M69" s="3">
-        <v>-298.42</v>
+        <v>-919.26</v>
       </c>
       <c r="N69" s="3">
         <v>-903.29</v>
@@ -4470,9 +4674,12 @@
         <v>2868.81</v>
       </c>
       <c r="R69" s="3">
-        <v>-903.29</v>
-      </c>
-      <c r="S69" t="str">
+        <v>3479.68</v>
+      </c>
+      <c r="S69" s="3">
+        <v>30.65</v>
+      </c>
+      <c r="T69" t="str">
         <v/>
       </c>
     </row>
@@ -4514,7 +4721,7 @@
         <v>17717.7</v>
       </c>
       <c r="M70" s="3">
-        <v>-55.2</v>
+        <v>-279.9</v>
       </c>
       <c r="N70" s="3">
         <v>-278.57</v>
@@ -4529,9 +4736,12 @@
         <v>894.59</v>
       </c>
       <c r="R70" s="3">
-        <v>-278.57</v>
-      </c>
-      <c r="S70" t="str">
+        <v>1047.16</v>
+      </c>
+      <c r="S70" s="3">
+        <v>30.35</v>
+      </c>
+      <c r="T70" t="str">
         <v/>
       </c>
     </row>
@@ -4573,7 +4783,7 @@
         <v>7781.41</v>
       </c>
       <c r="M71" s="3">
-        <v>-66.71</v>
+        <v>-92.92</v>
       </c>
       <c r="N71" s="3">
         <v>-87.71</v>
@@ -4588,9 +4798,12 @@
         <v>-304.51</v>
       </c>
       <c r="R71" s="3">
-        <v>-87.71</v>
-      </c>
-      <c r="S71" t="str">
+        <v>-248.08</v>
+      </c>
+      <c r="S71" s="3">
+        <v>37.1</v>
+      </c>
+      <c r="T71" t="str">
         <v/>
       </c>
     </row>
@@ -4632,7 +4845,7 @@
         <v>21034.43</v>
       </c>
       <c r="M72" s="3">
-        <v>19.81</v>
+        <v>-283.44</v>
       </c>
       <c r="N72" s="3">
         <v>-259.74</v>
@@ -4647,9 +4860,12 @@
         <v>1573.19</v>
       </c>
       <c r="R72" s="3">
-        <v>-259.74</v>
-      </c>
-      <c r="S72" t="str">
+        <v>1822.38</v>
+      </c>
+      <c r="S72" s="3">
+        <v>29.74</v>
+      </c>
+      <c r="T72" t="str">
         <v/>
       </c>
     </row>
@@ -4691,7 +4907,7 @@
         <v>12865.76</v>
       </c>
       <c r="M73" s="3">
-        <v>15.41</v>
+        <v>-278.11</v>
       </c>
       <c r="N73" s="3">
         <v>-246.99</v>
@@ -4706,9 +4922,12 @@
         <v>1137.8</v>
       </c>
       <c r="R73" s="3">
-        <v>-246.99</v>
-      </c>
-      <c r="S73" t="str">
+        <v>1130.25</v>
+      </c>
+      <c r="S73" s="3">
+        <v>33.96</v>
+      </c>
+      <c r="T73" t="str">
         <v/>
       </c>
     </row>
@@ -4750,7 +4969,7 @@
         <v>16859.82</v>
       </c>
       <c r="M74" s="3">
-        <v>21.19</v>
+        <v>-268.03</v>
       </c>
       <c r="N74" s="3">
         <v>-241.93</v>
@@ -4765,9 +4984,12 @@
         <v>1543.57</v>
       </c>
       <c r="R74" s="3">
-        <v>-241.93</v>
-      </c>
-      <c r="S74" t="str">
+        <v>1747.05</v>
+      </c>
+      <c r="S74" s="3">
+        <v>31.3</v>
+      </c>
+      <c r="T74" t="str">
         <v/>
       </c>
     </row>
@@ -4809,7 +5031,7 @@
         <v>38507.54</v>
       </c>
       <c r="M75" s="3">
-        <v>-196.08</v>
+        <v>-749.75</v>
       </c>
       <c r="N75" s="3">
         <v>-739.59</v>
@@ -4824,9 +5046,12 @@
         <v>632.89</v>
       </c>
       <c r="R75" s="3">
-        <v>-739.59</v>
-      </c>
-      <c r="S75" t="str">
+        <v>938.74</v>
+      </c>
+      <c r="S75" s="3">
+        <v>29.43</v>
+      </c>
+      <c r="T75" t="str">
         <v/>
       </c>
     </row>
@@ -4868,7 +5093,7 @@
         <v>50957</v>
       </c>
       <c r="M76" s="3">
-        <v>116.31</v>
+        <v>-497.9</v>
       </c>
       <c r="N76" s="3">
         <v>-444.45</v>
@@ -4883,9 +5108,12 @@
         <v>61.01</v>
       </c>
       <c r="R76" s="3">
-        <v>-444.45</v>
-      </c>
-      <c r="S76" t="str">
+        <v>-298.96</v>
+      </c>
+      <c r="S76" s="3">
+        <v>32.6</v>
+      </c>
+      <c r="T76" t="str">
         <v/>
       </c>
     </row>
@@ -4927,7 +5155,7 @@
         <v>62735.23</v>
       </c>
       <c r="M77" s="3">
-        <v>-370.77</v>
+        <v>-867.64</v>
       </c>
       <c r="N77" s="3">
         <v>-740.43</v>
@@ -4942,9 +5170,12 @@
         <v>-110.49</v>
       </c>
       <c r="R77" s="3">
-        <v>-740.43</v>
-      </c>
-      <c r="S77" t="str">
+        <v>-195.03</v>
+      </c>
+      <c r="S77" s="3">
+        <v>29.06</v>
+      </c>
+      <c r="T77" t="str">
         <v/>
       </c>
     </row>
@@ -4986,7 +5217,7 @@
         <v>31651.86</v>
       </c>
       <c r="M78" s="3">
-        <v>-453.52</v>
+        <v>-696.88</v>
       </c>
       <c r="N78" s="3">
         <v>-642.67</v>
@@ -5001,9 +5232,12 @@
         <v>1989.94</v>
       </c>
       <c r="R78" s="3">
-        <v>-642.67</v>
-      </c>
-      <c r="S78" t="str">
+        <v>2397.89</v>
+      </c>
+      <c r="S78" s="3">
+        <v>24.47</v>
+      </c>
+      <c r="T78" t="str">
         <v/>
       </c>
     </row>
@@ -5045,7 +5279,7 @@
         <v>26223.82</v>
       </c>
       <c r="M79" s="3">
-        <v>-46.46</v>
+        <v>-354.45</v>
       </c>
       <c r="N79" s="3">
         <v>-316.69</v>
@@ -5060,9 +5294,12 @@
         <v>67.16</v>
       </c>
       <c r="R79" s="3">
-        <v>-316.69</v>
-      </c>
-      <c r="S79" t="str">
+        <v>-55.02</v>
+      </c>
+      <c r="S79" s="3">
+        <v>32.01</v>
+      </c>
+      <c r="T79" t="str">
         <v/>
       </c>
     </row>
@@ -5104,7 +5341,7 @@
         <v>48412.97</v>
       </c>
       <c r="M80" s="3">
-        <v>797.36</v>
+        <v>-346.62</v>
       </c>
       <c r="N80" s="3">
         <v>-239.01</v>
@@ -5119,9 +5356,12 @@
         <v>-311.48</v>
       </c>
       <c r="R80" s="3">
-        <v>-239.01</v>
-      </c>
-      <c r="S80" t="str">
+        <v>-1014.14</v>
+      </c>
+      <c r="S80" s="3">
+        <v>34.57</v>
+      </c>
+      <c r="T80" t="str">
         <v/>
       </c>
     </row>
@@ -5163,7 +5403,7 @@
         <v>18112.58</v>
       </c>
       <c r="M81" s="3">
-        <v>206.68</v>
+        <v>-196.63</v>
       </c>
       <c r="N81" s="3">
         <v>-148.54</v>
@@ -5178,9 +5418,12 @@
         <v>1307.86</v>
       </c>
       <c r="R81" s="3">
-        <v>-148.54</v>
-      </c>
-      <c r="S81" t="str">
+        <v>1428.81</v>
+      </c>
+      <c r="S81" s="3">
+        <v>29.72</v>
+      </c>
+      <c r="T81" t="str">
         <v/>
       </c>
     </row>
@@ -5222,7 +5465,7 @@
         <v>5307.19</v>
       </c>
       <c r="M82" s="3">
-        <v>28.71</v>
+        <v>-31.37</v>
       </c>
       <c r="N82" s="3">
         <v>-30.41</v>
@@ -5237,9 +5480,12 @@
         <v>365.15</v>
       </c>
       <c r="R82" s="3">
-        <v>-30.41</v>
-      </c>
-      <c r="S82" t="str">
+        <v>325.49</v>
+      </c>
+      <c r="S82" s="3">
+        <v>39.53</v>
+      </c>
+      <c r="T82" t="str">
         <v/>
       </c>
     </row>
@@ -5281,7 +5527,7 @@
         <v>9824.13</v>
       </c>
       <c r="M83" s="3">
-        <v>202.03</v>
+        <v>-91.43</v>
       </c>
       <c r="N83" s="3">
         <v>-68.5</v>
@@ -5296,9 +5542,12 @@
         <v>732.62</v>
       </c>
       <c r="R83" s="3">
-        <v>-68.5</v>
-      </c>
-      <c r="S83" t="str">
+        <v>718.15</v>
+      </c>
+      <c r="S83" s="3">
+        <v>33.4</v>
+      </c>
+      <c r="T83" t="str">
         <v/>
       </c>
     </row>
@@ -5340,7 +5589,7 @@
         <v>19652.77</v>
       </c>
       <c r="M84" s="3">
-        <v>303.54</v>
+        <v>-203.78</v>
       </c>
       <c r="N84" s="3">
         <v>-144.59</v>
@@ -5355,9 +5604,12 @@
         <v>857</v>
       </c>
       <c r="R84" s="3">
-        <v>-144.59</v>
-      </c>
-      <c r="S84" t="str">
+        <v>855.57</v>
+      </c>
+      <c r="S84" s="3">
+        <v>30.69</v>
+      </c>
+      <c r="T84" t="str">
         <v/>
       </c>
     </row>
@@ -5399,7 +5651,7 @@
         <v>55691.54</v>
       </c>
       <c r="M85" s="3">
-        <v>687.99</v>
+        <v>-522.51</v>
       </c>
       <c r="N85" s="3">
         <v>-337.93</v>
@@ -5414,9 +5666,12 @@
         <v>3654.57</v>
       </c>
       <c r="R85" s="3">
-        <v>-337.93</v>
-      </c>
-      <c r="S85" t="str">
+        <v>3879.75</v>
+      </c>
+      <c r="S85" s="3">
+        <v>33.61</v>
+      </c>
+      <c r="T85" t="str">
         <v/>
       </c>
     </row>
@@ -5458,7 +5713,7 @@
         <v>54191.73</v>
       </c>
       <c r="M86" s="3">
-        <v>16.41</v>
+        <v>-631.31</v>
       </c>
       <c r="N86" s="3">
         <v>-484.74</v>
@@ -5473,9 +5728,12 @@
         <v>-766.73</v>
       </c>
       <c r="R86" s="3">
-        <v>-484.74</v>
-      </c>
-      <c r="S86" t="str">
+        <v>-1125.04</v>
+      </c>
+      <c r="S86" s="3">
+        <v>31.55</v>
+      </c>
+      <c r="T86" t="str">
         <v/>
       </c>
     </row>
@@ -5517,7 +5775,7 @@
         <v>30338.82</v>
       </c>
       <c r="M87" s="3">
-        <v>-358.37</v>
+        <v>-436.16</v>
       </c>
       <c r="N87" s="3">
         <v>-371.67</v>
@@ -5532,9 +5790,12 @@
         <v>1434.04</v>
       </c>
       <c r="R87" s="3">
-        <v>-371.67</v>
-      </c>
-      <c r="S87" t="str">
+        <v>1996.53</v>
+      </c>
+      <c r="S87" s="3">
+        <v>29.63</v>
+      </c>
+      <c r="T87" t="str">
         <v/>
       </c>
     </row>
@@ -5576,7 +5837,7 @@
         <v>9494.3</v>
       </c>
       <c r="M88" s="3">
-        <v>108</v>
+        <v>-107.5</v>
       </c>
       <c r="N88" s="3">
         <v>-102.94</v>
@@ -5591,9 +5852,12 @@
         <v>609.88</v>
       </c>
       <c r="R88" s="3">
-        <v>-102.94</v>
-      </c>
-      <c r="S88" t="str">
+        <v>524.08</v>
+      </c>
+      <c r="S88" s="3">
+        <v>36.73</v>
+      </c>
+      <c r="T88" t="str">
         <v/>
       </c>
     </row>
@@ -5635,7 +5899,7 @@
         <v>26151.21</v>
       </c>
       <c r="M89" s="3">
-        <v>631.16</v>
+        <v>-250.27</v>
       </c>
       <c r="N89" s="3">
         <v>-135.24</v>
@@ -5650,9 +5914,12 @@
         <v>2310.69</v>
       </c>
       <c r="R89" s="3">
-        <v>-135.24</v>
-      </c>
-      <c r="S89" t="str">
+        <v>2354.84</v>
+      </c>
+      <c r="S89" s="3">
+        <v>32.27</v>
+      </c>
+      <c r="T89" t="str">
         <v/>
       </c>
     </row>
@@ -5694,7 +5961,7 @@
         <v>29400.12</v>
       </c>
       <c r="M90" s="3">
-        <v>-188.9</v>
+        <v>-420.56</v>
       </c>
       <c r="N90" s="3">
         <v>-400.05</v>
@@ -5709,15 +5976,18 @@
         <v>223.94</v>
       </c>
       <c r="R90" s="3">
-        <v>-400.05</v>
-      </c>
-      <c r="S90" t="str">
+        <v>186.07</v>
+      </c>
+      <c r="S90" s="3">
+        <v>31.05</v>
+      </c>
+      <c r="T90" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T90"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Index.xlsx
+++ b/Index.xlsx
@@ -472,58 +472,58 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>India VIX</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C2" t="str">
-        <v>INDIAVIX</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D2" s="1">
-        <v>15.68</v>
+        <v>7452.2</v>
       </c>
       <c r="E2" s="2">
-        <v>6.16</v>
+        <v>1.1</v>
       </c>
       <c r="F2" s="2">
-        <v>11.52</v>
+        <v>-1.49</v>
       </c>
       <c r="G2" s="2">
-        <v>16.23</v>
+        <v>-3.27</v>
       </c>
       <c r="H2" s="2">
-        <v>65.4</v>
+        <v>-13.39</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>14.84</v>
+        <v>7685.96</v>
       </c>
       <c r="K2" s="1">
-        <v>14.53</v>
+        <v>7493.8</v>
       </c>
       <c r="L2" s="1">
-        <v>12.43</v>
+        <v>7767.83</v>
       </c>
       <c r="M2" s="3">
-        <v>0.73</v>
+        <v>-91.28</v>
       </c>
       <c r="N2" s="3">
-        <v>0.67</v>
+        <v>-88.42</v>
       </c>
       <c r="O2" s="3">
-        <v>-0.29</v>
+        <v>-60.24</v>
       </c>
       <c r="P2" s="3">
-        <v>-0.75</v>
+        <v>-17.33</v>
       </c>
       <c r="Q2" s="3">
-        <v>-0.02</v>
+        <v>-298.05</v>
       </c>
       <c r="R2" s="3">
-        <v>0.03</v>
+        <v>-246.79</v>
       </c>
       <c r="S2" s="3">
-        <v>61.67</v>
+        <v>42.04</v>
       </c>
       <c r="T2" t="str">
         <v/>
@@ -534,58 +534,58 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="C3" t="str">
-        <v>CNXIT</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D3" s="1">
-        <v>32422.5</v>
+        <v>191.15</v>
       </c>
       <c r="E3" s="2">
-        <v>2.88</v>
+        <v>0.58</v>
       </c>
       <c r="F3" s="2">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="G3" s="2">
-        <v>17.03</v>
+        <v>-0.13</v>
       </c>
       <c r="H3" s="2">
-        <v>-14.42</v>
+        <v>16.8</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>30874.09</v>
+        <v>178.54</v>
       </c>
       <c r="K3" s="1">
-        <v>30440.26</v>
+        <v>190.26</v>
       </c>
       <c r="L3" s="1">
-        <v>29827.11</v>
+        <v>184.58</v>
       </c>
       <c r="M3" s="3">
-        <v>574.23</v>
+        <v>1.47</v>
       </c>
       <c r="N3" s="3">
-        <v>44.9</v>
+        <v>2.03</v>
       </c>
       <c r="O3" s="3">
-        <v>-122.78</v>
+        <v>3.49</v>
       </c>
       <c r="P3" s="3">
-        <v>-512.74</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" s="3">
-        <v>-1626.95</v>
+        <v>-2.5</v>
       </c>
       <c r="R3" s="3">
-        <v>-1140.94</v>
+        <v>-6.03</v>
       </c>
       <c r="S3" s="3">
-        <v>72.87</v>
+        <v>56.53</v>
       </c>
       <c r="T3" t="str">
         <v/>
@@ -596,58 +596,58 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="C4" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D4" s="1">
-        <v>10988.55</v>
+        <v>235.65</v>
       </c>
       <c r="E4" s="2">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="F4" s="2">
-        <v>-0.33</v>
+        <v>2.08</v>
       </c>
       <c r="G4" s="2">
-        <v>4.26</v>
+        <v>-0.13</v>
       </c>
       <c r="H4" s="2">
-        <v>-11.98</v>
+        <v>17.83</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>11232.15</v>
+        <v>219.08</v>
       </c>
       <c r="K4" s="1">
-        <v>10766.87</v>
+        <v>234.58</v>
       </c>
       <c r="L4" s="1">
-        <v>11105.59</v>
+        <v>227.53</v>
       </c>
       <c r="M4" s="3">
-        <v>-51.3</v>
+        <v>1.84</v>
       </c>
       <c r="N4" s="3">
-        <v>-138.92</v>
+        <v>2.53</v>
       </c>
       <c r="O4" s="3">
-        <v>-106.66</v>
+        <v>4.68</v>
       </c>
       <c r="P4" s="3">
-        <v>-74.45</v>
+        <v>3.46</v>
       </c>
       <c r="Q4" s="3">
-        <v>39.38</v>
+        <v>-0.65</v>
       </c>
       <c r="R4" s="3">
-        <v>178.12</v>
+        <v>-4.77</v>
       </c>
       <c r="S4" s="3">
-        <v>57.19</v>
+        <v>56.57</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -658,58 +658,58 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>India VIX</v>
       </c>
       <c r="C5" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>INDIAVIX</v>
       </c>
       <c r="D5" s="1">
-        <v>8599.15</v>
+        <v>15.76</v>
       </c>
       <c r="E5" s="2">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="F5" s="2">
-        <v>-0.82</v>
+        <v>12.09</v>
       </c>
       <c r="G5" s="2">
-        <v>7.13</v>
+        <v>16.83</v>
       </c>
       <c r="H5" s="2">
-        <v>-8.74</v>
+        <v>66.24</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>8261.69</v>
+        <v>14.87</v>
       </c>
       <c r="K5" s="1">
-        <v>8427.43</v>
+        <v>14.75</v>
       </c>
       <c r="L5" s="1">
-        <v>8539.65</v>
+        <v>12.5</v>
       </c>
       <c r="M5" s="3">
-        <v>14.19</v>
+        <v>0.78</v>
       </c>
       <c r="N5" s="3">
-        <v>-54.53</v>
+        <v>0.69</v>
       </c>
       <c r="O5" s="3">
-        <v>72.59</v>
+        <v>-0.28</v>
       </c>
       <c r="P5" s="3">
-        <v>60.56</v>
+        <v>-0.75</v>
       </c>
       <c r="Q5" s="3">
-        <v>379.07</v>
+        <v>-0.01</v>
       </c>
       <c r="R5" s="3">
-        <v>515.06</v>
+        <v>0.04</v>
       </c>
       <c r="S5" s="3">
-        <v>59.85</v>
+        <v>62.01</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -720,58 +720,58 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C6" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D6" s="1">
-        <v>190.05</v>
+        <v>25596.65</v>
       </c>
       <c r="E6" s="2">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="F6" s="2">
-        <v>1.52</v>
+        <v>-0.72</v>
       </c>
       <c r="G6" s="2">
-        <v>-0.71</v>
+        <v>-3.18</v>
       </c>
       <c r="H6" s="2">
-        <v>16.13</v>
+        <v>12.64</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>178.41</v>
+        <v>24362.22</v>
       </c>
       <c r="K6" s="1">
-        <v>190.06</v>
+        <v>25836.58</v>
       </c>
       <c r="L6" s="1">
-        <v>184.26</v>
+        <v>26467.62</v>
       </c>
       <c r="M6" s="3">
-        <v>1.49</v>
+        <v>-260.98</v>
       </c>
       <c r="N6" s="3">
-        <v>2.17</v>
+        <v>-185.97</v>
       </c>
       <c r="O6" s="3">
-        <v>3.4</v>
+        <v>599.34</v>
       </c>
       <c r="P6" s="3">
-        <v>2.46</v>
+        <v>796.89</v>
       </c>
       <c r="Q6" s="3">
-        <v>-2.58</v>
+        <v>1774.69</v>
       </c>
       <c r="R6" s="3">
-        <v>-6.05</v>
+        <v>1607.38</v>
       </c>
       <c r="S6" s="3">
-        <v>54.13</v>
+        <v>36.82</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -782,58 +782,58 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C7" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D7" s="1">
-        <v>234.35</v>
+        <v>8257.4</v>
       </c>
       <c r="E7" s="2">
-        <v>0.36</v>
+        <v>0.07</v>
       </c>
       <c r="F7" s="2">
-        <v>1.52</v>
+        <v>2.01</v>
       </c>
       <c r="G7" s="2">
-        <v>-0.68</v>
+        <v>3.01</v>
       </c>
       <c r="H7" s="2">
-        <v>17.18</v>
+        <v>-3.23</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>218.9</v>
+        <v>8574.26</v>
       </c>
       <c r="K7" s="1">
-        <v>234.35</v>
+        <v>8170.22</v>
       </c>
       <c r="L7" s="1">
-        <v>227.14</v>
+        <v>8356.45</v>
       </c>
       <c r="M7" s="3">
-        <v>1.87</v>
+        <v>-30.34</v>
       </c>
       <c r="N7" s="3">
-        <v>2.7</v>
+        <v>-68.98</v>
       </c>
       <c r="O7" s="3">
-        <v>4.58</v>
+        <v>-75.07</v>
       </c>
       <c r="P7" s="3">
-        <v>3.44</v>
+        <v>-29.67</v>
       </c>
       <c r="Q7" s="3">
-        <v>-0.76</v>
+        <v>575.84</v>
       </c>
       <c r="R7" s="3">
-        <v>-4.79</v>
+        <v>685.49</v>
       </c>
       <c r="S7" s="3">
-        <v>54.26</v>
+        <v>52.97</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -844,58 +844,58 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C8" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D8" s="1">
-        <v>30163.75</v>
+        <v>15515.25</v>
       </c>
       <c r="E8" s="2">
-        <v>0.21</v>
+        <v>0.05</v>
       </c>
       <c r="F8" s="2">
-        <v>-1.04</v>
+        <v>-1.07</v>
       </c>
       <c r="G8" s="2">
-        <v>3.96</v>
+        <v>-3.86</v>
       </c>
       <c r="H8" s="2">
-        <v>-10.38</v>
+        <v>5.98</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>30978.13</v>
+        <v>15441.14</v>
       </c>
       <c r="K8" s="1">
-        <v>29751.22</v>
+        <v>15715.24</v>
       </c>
       <c r="L8" s="1">
-        <v>30135.4</v>
+        <v>16350.61</v>
       </c>
       <c r="M8" s="3">
-        <v>-17.67</v>
+        <v>-253.06</v>
       </c>
       <c r="N8" s="3">
-        <v>-202.88</v>
+        <v>-208.74</v>
       </c>
       <c r="O8" s="3">
-        <v>-341.3</v>
+        <v>171.36</v>
       </c>
       <c r="P8" s="3">
-        <v>-313.76</v>
+        <v>340.54</v>
       </c>
       <c r="Q8" s="3">
-        <v>500.38</v>
+        <v>979.06</v>
       </c>
       <c r="R8" s="3">
-        <v>994.57</v>
+        <v>994.28</v>
       </c>
       <c r="S8" s="3">
-        <v>56.72</v>
+        <v>31.11</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -906,58 +906,58 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C9" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D9" s="1">
-        <v>5609.55</v>
+        <v>3285.67</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>-0.39</v>
+        <v>-0.53</v>
       </c>
       <c r="G9" s="2">
-        <v>2.5</v>
+        <v>-1.08</v>
       </c>
       <c r="H9" s="2">
-        <v>-12.15</v>
+        <v>1.35</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>5956.86</v>
+        <v>3295.13</v>
       </c>
       <c r="K9" s="1">
-        <v>5544.34</v>
+        <v>3296.83</v>
       </c>
       <c r="L9" s="1">
-        <v>5697.85</v>
+        <v>3349.65</v>
       </c>
       <c r="M9" s="3">
-        <v>-30.22</v>
+        <v>-17.55</v>
       </c>
       <c r="N9" s="3">
-        <v>-62.87</v>
+        <v>-17.18</v>
       </c>
       <c r="O9" s="3">
-        <v>-114.41</v>
+        <v>7.59</v>
       </c>
       <c r="P9" s="3">
-        <v>-94.87</v>
+        <v>21.5</v>
       </c>
       <c r="Q9" s="3">
-        <v>29.69</v>
+        <v>136.46</v>
       </c>
       <c r="R9" s="3">
-        <v>140.42</v>
+        <v>153.9</v>
       </c>
       <c r="S9" s="3">
-        <v>53.27</v>
+        <v>32.57</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -968,58 +968,58 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C10" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D10" s="1">
-        <v>11401.45</v>
+        <v>202.16</v>
       </c>
       <c r="E10" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="H10" s="2">
-        <v>-14.12</v>
+        <v>-18.86</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>12190.9</v>
+        <v>180.66</v>
       </c>
       <c r="K10" s="1">
-        <v>11326.98</v>
+        <v>200.13</v>
       </c>
       <c r="L10" s="1">
-        <v>11569.55</v>
+        <v>194.79</v>
       </c>
       <c r="M10" s="3">
-        <v>-47.78</v>
+        <v>2.62</v>
       </c>
       <c r="N10" s="3">
-        <v>-102.06</v>
+        <v>2.57</v>
       </c>
       <c r="O10" s="3">
-        <v>-258.01</v>
+        <v>11.77</v>
       </c>
       <c r="P10" s="3">
-        <v>-234.43</v>
+        <v>5.66</v>
       </c>
       <c r="Q10" s="3">
-        <v>-123.99</v>
+        <v>5.31</v>
       </c>
       <c r="R10" s="3">
-        <v>115.64</v>
+        <v>7.65</v>
       </c>
       <c r="S10" s="3">
-        <v>51.31</v>
+        <v>100</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -1030,58 +1030,58 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D11" s="1">
-        <v>8339</v>
+        <v>3277.38</v>
       </c>
       <c r="E11" s="2">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="F11" s="2">
-        <v>-1.29</v>
+        <v>-0.12</v>
       </c>
       <c r="G11" s="2">
-        <v>3.24</v>
+        <v>-0.94</v>
       </c>
       <c r="H11" s="2">
-        <v>-16.98</v>
+        <v>1.7</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>8780.69</v>
+        <v>3280.16</v>
       </c>
       <c r="K11" s="1">
-        <v>8282.19</v>
+        <v>3285.99</v>
       </c>
       <c r="L11" s="1">
-        <v>8406.86</v>
+        <v>3321.29</v>
       </c>
       <c r="M11" s="3">
-        <v>-12.44</v>
+        <v>-12.06</v>
       </c>
       <c r="N11" s="3">
-        <v>-53.46</v>
+        <v>-11.13</v>
       </c>
       <c r="O11" s="3">
-        <v>-157</v>
+        <v>7.75</v>
       </c>
       <c r="P11" s="3">
-        <v>-157.92</v>
+        <v>18</v>
       </c>
       <c r="Q11" s="3">
-        <v>-302.34</v>
+        <v>139.52</v>
       </c>
       <c r="R11" s="3">
-        <v>-191.79</v>
+        <v>155.41</v>
       </c>
       <c r="S11" s="3">
-        <v>53.08</v>
+        <v>25.28</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -1092,58 +1092,58 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C12" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D12" s="1">
-        <v>202.16</v>
+        <v>1599.72</v>
       </c>
       <c r="E12" s="2">
-        <v>0</v>
+        <v>-0.07</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="G12" s="2">
-        <v>2.73</v>
+        <v>-0.45</v>
       </c>
       <c r="H12" s="2">
-        <v>-18.86</v>
+        <v>2.1</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>180.89</v>
+        <v>1586.66</v>
       </c>
       <c r="K12" s="1">
-        <v>199.68</v>
+        <v>1603.06</v>
       </c>
       <c r="L12" s="1">
-        <v>194.5</v>
+        <v>1608.95</v>
       </c>
       <c r="M12" s="3">
-        <v>2.59</v>
+        <v>-2.27</v>
       </c>
       <c r="N12" s="3">
-        <v>2.55</v>
+        <v>-1.59</v>
       </c>
       <c r="O12" s="3">
-        <v>11.77</v>
+        <v>6.82</v>
       </c>
       <c r="P12" s="3">
-        <v>5.66</v>
+        <v>9.34</v>
       </c>
       <c r="Q12" s="3">
-        <v>5.31</v>
+        <v>34.77</v>
       </c>
       <c r="R12" s="3">
-        <v>7.65</v>
+        <v>33.1</v>
       </c>
       <c r="S12" s="3">
-        <v>100</v>
+        <v>28.9</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -1154,58 +1154,58 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C13" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D13" s="1">
-        <v>13826.6</v>
+        <v>1261.46</v>
       </c>
       <c r="E13" s="2">
+        <v>-0.08</v>
+      </c>
+      <c r="F13" s="2">
+        <v>-0.22</v>
+      </c>
+      <c r="G13" s="2">
+        <v>-0.92</v>
+      </c>
+      <c r="H13" s="2">
         <v>-0.01</v>
       </c>
-      <c r="F13" s="2">
-        <v>-0.91</v>
-      </c>
-      <c r="G13" s="2">
-        <v>3.55</v>
-      </c>
-      <c r="H13" s="2">
-        <v>-9.59</v>
-      </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>14401.1</v>
+        <v>1268.34</v>
       </c>
       <c r="K13" s="1">
-        <v>13676.81</v>
+        <v>1266.47</v>
       </c>
       <c r="L13" s="1">
-        <v>14058.48</v>
+        <v>1280.28</v>
       </c>
       <c r="M13" s="3">
-        <v>-65.77</v>
+        <v>-4.96</v>
       </c>
       <c r="N13" s="3">
-        <v>-154.97</v>
+        <v>-4.18</v>
       </c>
       <c r="O13" s="3">
-        <v>-209.79</v>
+        <v>1.13</v>
       </c>
       <c r="P13" s="3">
-        <v>-159.4</v>
+        <v>4.93</v>
       </c>
       <c r="Q13" s="3">
-        <v>-529.71</v>
+        <v>21.22</v>
       </c>
       <c r="R13" s="3">
-        <v>-490.48</v>
+        <v>21.94</v>
       </c>
       <c r="S13" s="3">
-        <v>52.79</v>
+        <v>20.6</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1216,58 +1216,58 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C14" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D14" s="1">
-        <v>1446.87</v>
+        <v>54925.7</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="F14" s="2">
-        <v>-0.01</v>
+        <v>-1.64</v>
       </c>
       <c r="G14" s="2">
-        <v>-0.48</v>
+        <v>0.54</v>
       </c>
       <c r="H14" s="2">
-        <v>1.56</v>
+        <v>-7.81</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>1440.68</v>
+        <v>56869.45</v>
       </c>
       <c r="K14" s="1">
-        <v>1449.83</v>
+        <v>55246.42</v>
       </c>
       <c r="L14" s="1">
-        <v>1458.76</v>
+        <v>56322.88</v>
       </c>
       <c r="M14" s="3">
-        <v>-3.19</v>
+        <v>-271.33</v>
       </c>
       <c r="N14" s="3">
-        <v>-2.6</v>
+        <v>-357.02</v>
       </c>
       <c r="O14" s="3">
-        <v>4.31</v>
+        <v>-351.09</v>
       </c>
       <c r="P14" s="3">
-        <v>7.35</v>
+        <v>-99.1</v>
       </c>
       <c r="Q14" s="3">
-        <v>29.24</v>
+        <v>1661</v>
       </c>
       <c r="R14" s="3">
-        <v>28.57</v>
+        <v>2287.78</v>
       </c>
       <c r="S14" s="3">
-        <v>26.99</v>
+        <v>43.05</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1278,58 +1278,58 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C15" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D15" s="1">
-        <v>1307.62</v>
+        <v>2597.53</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.07</v>
+        <v>-0.09</v>
       </c>
       <c r="F15" s="2">
-        <v>-0.01</v>
+        <v>-0.52</v>
       </c>
       <c r="G15" s="2">
-        <v>-0.6</v>
+        <v>-1.54</v>
       </c>
       <c r="H15" s="2">
-        <v>0.73</v>
+        <v>-0.55</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>1307.95</v>
+        <v>2632.29</v>
       </c>
       <c r="K15" s="1">
-        <v>1311.03</v>
+        <v>2609.67</v>
       </c>
       <c r="L15" s="1">
-        <v>1322.5</v>
+        <v>2649.71</v>
       </c>
       <c r="M15" s="3">
-        <v>-3.98</v>
+        <v>-14.2</v>
       </c>
       <c r="N15" s="3">
-        <v>-3.41</v>
+        <v>-12.79</v>
       </c>
       <c r="O15" s="3">
-        <v>2.29</v>
+        <v>-2.08</v>
       </c>
       <c r="P15" s="3">
-        <v>5.72</v>
+        <v>7.44</v>
       </c>
       <c r="Q15" s="3">
-        <v>24.09</v>
+        <v>89.73</v>
       </c>
       <c r="R15" s="3">
-        <v>24.23</v>
+        <v>106.36</v>
       </c>
       <c r="S15" s="3">
-        <v>24.56</v>
+        <v>26.87</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1340,58 +1340,58 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D16" s="1">
-        <v>10536.3</v>
+        <v>1445.49</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="F16" s="2">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="G16" s="2">
-        <v>-0.74</v>
+        <v>-0.58</v>
       </c>
       <c r="H16" s="2">
-        <v>-13.86</v>
+        <v>1.46</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>11308.09</v>
+        <v>1440.78</v>
       </c>
       <c r="K16" s="1">
-        <v>10523.07</v>
+        <v>1449.04</v>
       </c>
       <c r="L16" s="1">
-        <v>10905.06</v>
+        <v>1458.33</v>
       </c>
       <c r="M16" s="3">
-        <v>-119.89</v>
+        <v>-3.35</v>
       </c>
       <c r="N16" s="3">
-        <v>-142.5</v>
+        <v>-2.75</v>
       </c>
       <c r="O16" s="3">
-        <v>-218</v>
+        <v>4.2</v>
       </c>
       <c r="P16" s="3">
-        <v>-158.8</v>
+        <v>7.32</v>
       </c>
       <c r="Q16" s="3">
-        <v>80.45</v>
+        <v>29.13</v>
       </c>
       <c r="R16" s="3">
-        <v>280.89</v>
+        <v>28.55</v>
       </c>
       <c r="S16" s="3">
-        <v>43.21</v>
+        <v>24.73</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1402,58 +1402,58 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C17" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D17" s="1">
-        <v>1600.86</v>
+        <v>3060.34</v>
       </c>
       <c r="E17" s="2">
         <v>-0.11</v>
       </c>
       <c r="F17" s="2">
-        <v>-0.04</v>
+        <v>-0.51</v>
       </c>
       <c r="G17" s="2">
-        <v>-0.38</v>
+        <v>-1.42</v>
       </c>
       <c r="H17" s="2">
-        <v>2.17</v>
+        <v>0.26</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>1586.5</v>
+        <v>3085.94</v>
       </c>
       <c r="K17" s="1">
-        <v>1603.81</v>
+        <v>3074.16</v>
       </c>
       <c r="L17" s="1">
-        <v>1609.22</v>
+        <v>3119.19</v>
       </c>
       <c r="M17" s="3">
-        <v>-2.06</v>
+        <v>-15.71</v>
       </c>
       <c r="N17" s="3">
-        <v>-1.42</v>
+        <v>-14.17</v>
       </c>
       <c r="O17" s="3">
-        <v>6.91</v>
+        <v>2.47</v>
       </c>
       <c r="P17" s="3">
-        <v>9.36</v>
+        <v>13.94</v>
       </c>
       <c r="Q17" s="3">
-        <v>34.86</v>
+        <v>118.47</v>
       </c>
       <c r="R17" s="3">
-        <v>33.12</v>
+        <v>136.54</v>
       </c>
       <c r="S17" s="3">
-        <v>31.14</v>
+        <v>27.67</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1464,58 +1464,58 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C18" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D18" s="1">
-        <v>18714.9</v>
+        <v>837.97</v>
       </c>
       <c r="E18" s="2">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="F18" s="2">
-        <v>-1.08</v>
+        <v>-0.66</v>
       </c>
       <c r="G18" s="2">
-        <v>-0.38</v>
+        <v>-2.02</v>
       </c>
       <c r="H18" s="2">
-        <v>-11.43</v>
+        <v>-6</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>19879.38</v>
+        <v>873.84</v>
       </c>
       <c r="K18" s="1">
-        <v>18763.95</v>
+        <v>843.19</v>
       </c>
       <c r="L18" s="1">
-        <v>19544.08</v>
+        <v>861.49</v>
       </c>
       <c r="M18" s="3">
-        <v>-221.72</v>
+        <v>-6.48</v>
       </c>
       <c r="N18" s="3">
-        <v>-272.22</v>
+        <v>-5.99</v>
       </c>
       <c r="O18" s="3">
-        <v>-297.59</v>
+        <v>-8.78</v>
       </c>
       <c r="P18" s="3">
-        <v>-145.05</v>
+        <v>-5.64</v>
       </c>
       <c r="Q18" s="3">
-        <v>758.22</v>
+        <v>-17.23</v>
       </c>
       <c r="R18" s="3">
-        <v>1111.46</v>
+        <v>-14.2</v>
       </c>
       <c r="S18" s="3">
-        <v>41.01</v>
+        <v>21.18</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1526,58 +1526,58 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C19" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D19" s="1">
-        <v>3279.32</v>
+        <v>2967.49</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="F19" s="2">
-        <v>-0.06</v>
+        <v>-0.51</v>
       </c>
       <c r="G19" s="2">
-        <v>-0.88</v>
+        <v>-1.54</v>
       </c>
       <c r="H19" s="2">
-        <v>1.76</v>
+        <v>0.02</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>3279.89</v>
+        <v>3001.36</v>
       </c>
       <c r="K19" s="1">
-        <v>3287.9</v>
+        <v>2981.99</v>
       </c>
       <c r="L19" s="1">
-        <v>3322.73</v>
+        <v>3027.17</v>
       </c>
       <c r="M19" s="3">
-        <v>-11.94</v>
+        <v>-15.97</v>
       </c>
       <c r="N19" s="3">
-        <v>-10.89</v>
+        <v>-14.3</v>
       </c>
       <c r="O19" s="3">
-        <v>7.91</v>
+        <v>0.08</v>
       </c>
       <c r="P19" s="3">
-        <v>18.03</v>
+        <v>11.37</v>
       </c>
       <c r="Q19" s="3">
-        <v>139.67</v>
+        <v>114.53</v>
       </c>
       <c r="R19" s="3">
-        <v>155.44</v>
+        <v>132.78</v>
       </c>
       <c r="S19" s="3">
-        <v>26.28</v>
+        <v>25.15</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1588,58 +1588,58 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C20" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D20" s="1">
-        <v>1262.52</v>
+        <v>26866.05</v>
       </c>
       <c r="E20" s="2">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="F20" s="2">
-        <v>-0.14</v>
+        <v>-3.01</v>
       </c>
       <c r="G20" s="2">
-        <v>-0.84</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="2">
-        <v>0.08</v>
+        <v>-6.46</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>1268.34</v>
+        <v>27372.43</v>
       </c>
       <c r="K20" s="1">
-        <v>1267.59</v>
+        <v>27137.71</v>
       </c>
       <c r="L20" s="1">
-        <v>1280.91</v>
+        <v>27283.4</v>
       </c>
       <c r="M20" s="3">
-        <v>-4.76</v>
+        <v>-24.38</v>
       </c>
       <c r="N20" s="3">
-        <v>-3.99</v>
+        <v>-38.48</v>
       </c>
       <c r="O20" s="3">
-        <v>1.21</v>
+        <v>-36.94</v>
       </c>
       <c r="P20" s="3">
-        <v>4.94</v>
+        <v>18.1</v>
       </c>
       <c r="Q20" s="3">
-        <v>21.3</v>
+        <v>646.68</v>
       </c>
       <c r="R20" s="3">
-        <v>21.95</v>
+        <v>875.22</v>
       </c>
       <c r="S20" s="3">
-        <v>21.73</v>
+        <v>44.39</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1650,58 +1650,58 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D21" s="1">
-        <v>7360</v>
+        <v>24657.7</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="F21" s="2">
-        <v>-1.33</v>
+        <v>-2.87</v>
       </c>
       <c r="G21" s="2">
-        <v>4.01</v>
+        <v>0.03</v>
       </c>
       <c r="H21" s="2">
-        <v>-2.67</v>
+        <v>-10.7</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>7335.66</v>
+        <v>26223.16</v>
       </c>
       <c r="K21" s="1">
-        <v>7292.77</v>
+        <v>24937.38</v>
       </c>
       <c r="L21" s="1">
-        <v>7411.18</v>
+        <v>25524.6</v>
       </c>
       <c r="M21" s="3">
-        <v>-6.23</v>
+        <v>-159.46</v>
       </c>
       <c r="N21" s="3">
-        <v>-48.28</v>
+        <v>-186.87</v>
       </c>
       <c r="O21" s="3">
-        <v>1.91</v>
+        <v>-358.1</v>
       </c>
       <c r="P21" s="3">
-        <v>31.86</v>
+        <v>-222.89</v>
       </c>
       <c r="Q21" s="3">
-        <v>472.8</v>
+        <v>648.25</v>
       </c>
       <c r="R21" s="3">
-        <v>552.77</v>
+        <v>1081.21</v>
       </c>
       <c r="S21" s="3">
-        <v>54.1</v>
+        <v>41.17</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1712,58 +1712,58 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>CNXPHARMA</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="C22" t="str">
-        <v>CNXPHARMA</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="D22" s="1">
-        <v>25565.9</v>
+        <v>1305.6</v>
       </c>
       <c r="E22" s="2">
-        <v>-0.19</v>
+        <v>-0.15</v>
       </c>
       <c r="F22" s="2">
-        <v>-0.84</v>
+        <v>-0.17</v>
       </c>
       <c r="G22" s="2">
-        <v>-3.3</v>
+        <v>-0.75</v>
       </c>
       <c r="H22" s="2">
-        <v>12.51</v>
+        <v>0.57</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>24346.94</v>
+        <v>1307.99</v>
       </c>
       <c r="K22" s="1">
-        <v>25889.9</v>
+        <v>1310.04</v>
       </c>
       <c r="L22" s="1">
-        <v>26485.28</v>
+        <v>1321.92</v>
       </c>
       <c r="M22" s="3">
-        <v>-251.44</v>
+        <v>-4.18</v>
       </c>
       <c r="N22" s="3">
-        <v>-167.21</v>
+        <v>-3.57</v>
       </c>
       <c r="O22" s="3">
-        <v>596.89</v>
+        <v>2.13</v>
       </c>
       <c r="P22" s="3">
-        <v>796.4</v>
+        <v>5.69</v>
       </c>
       <c r="Q22" s="3">
-        <v>1772.23</v>
+        <v>23.93</v>
       </c>
       <c r="R22" s="3">
-        <v>1606.89</v>
+        <v>24.2</v>
       </c>
       <c r="S22" s="3">
-        <v>35.97</v>
+        <v>21.86</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1774,58 +1774,58 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D23" s="1">
-        <v>3285.69</v>
+        <v>3461.91</v>
       </c>
       <c r="E23" s="2">
-        <v>-0.25</v>
+        <v>-0.18</v>
       </c>
       <c r="F23" s="2">
-        <v>-0.53</v>
+        <v>-0.74</v>
       </c>
       <c r="G23" s="2">
-        <v>-1.08</v>
+        <v>-1.7</v>
       </c>
       <c r="H23" s="2">
-        <v>1.35</v>
+        <v>-0.89</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>3294.9</v>
+        <v>3495.45</v>
       </c>
       <c r="K23" s="1">
-        <v>3299.31</v>
+        <v>3482.5</v>
       </c>
       <c r="L23" s="1">
-        <v>3351.81</v>
+        <v>3534.62</v>
       </c>
       <c r="M23" s="3">
-        <v>-17.55</v>
+        <v>-18.31</v>
       </c>
       <c r="N23" s="3">
-        <v>-17.08</v>
+        <v>-15.59</v>
       </c>
       <c r="O23" s="3">
-        <v>7.59</v>
+        <v>2.25</v>
       </c>
       <c r="P23" s="3">
-        <v>21.5</v>
+        <v>15.32</v>
       </c>
       <c r="Q23" s="3">
-        <v>136.47</v>
+        <v>118.29</v>
       </c>
       <c r="R23" s="3">
-        <v>153.9</v>
+        <v>141.8</v>
       </c>
       <c r="S23" s="3">
-        <v>32.58</v>
+        <v>32.82</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1836,58 +1836,58 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C24" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D24" s="1">
-        <v>15507.15</v>
+        <v>26507.55</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="F24" s="2">
-        <v>-1.12</v>
+        <v>-2.59</v>
       </c>
       <c r="G24" s="2">
-        <v>-3.91</v>
+        <v>-0.18</v>
       </c>
       <c r="H24" s="2">
-        <v>5.92</v>
+        <v>-12.16</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>15436.28</v>
+        <v>28547.73</v>
       </c>
       <c r="K24" s="1">
-        <v>15759.68</v>
+        <v>26804.57</v>
       </c>
       <c r="L24" s="1">
-        <v>16373.32</v>
+        <v>27607.95</v>
       </c>
       <c r="M24" s="3">
-        <v>-247.94</v>
+        <v>-227.16</v>
       </c>
       <c r="N24" s="3">
-        <v>-197.67</v>
+        <v>-264.17</v>
       </c>
       <c r="O24" s="3">
-        <v>170.72</v>
+        <v>-482.82</v>
       </c>
       <c r="P24" s="3">
-        <v>340.41</v>
+        <v>-296.17</v>
       </c>
       <c r="Q24" s="3">
-        <v>978.42</v>
+        <v>1306.83</v>
       </c>
       <c r="R24" s="3">
-        <v>994.15</v>
+        <v>1899.28</v>
       </c>
       <c r="S24" s="3">
-        <v>30.73</v>
+        <v>39.98</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1898,58 +1898,58 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D25" s="1">
-        <v>5407.3</v>
+        <v>24515.7</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="F25" s="2">
-        <v>-1.18</v>
+        <v>-1.6</v>
       </c>
       <c r="G25" s="2">
-        <v>1.63</v>
+        <v>-2.79</v>
       </c>
       <c r="H25" s="2">
-        <v>-7.73</v>
+        <v>-9.46</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>5551.02</v>
+        <v>26255.24</v>
       </c>
       <c r="K25" s="1">
-        <v>5382.02</v>
+        <v>24777.22</v>
       </c>
       <c r="L25" s="1">
-        <v>5530.09</v>
+        <v>26124.11</v>
       </c>
       <c r="M25" s="3">
-        <v>-28.38</v>
+        <v>-430.74</v>
       </c>
       <c r="N25" s="3">
-        <v>-54.85</v>
+        <v>-452.35</v>
       </c>
       <c r="O25" s="3">
-        <v>-42.26</v>
+        <v>-350.04</v>
       </c>
       <c r="P25" s="3">
-        <v>-16.83</v>
+        <v>-68.07</v>
       </c>
       <c r="Q25" s="3">
-        <v>190.86</v>
+        <v>1141.66</v>
       </c>
       <c r="R25" s="3">
-        <v>261.84</v>
+        <v>1595.06</v>
       </c>
       <c r="S25" s="3">
-        <v>49.71</v>
+        <v>31.89</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1960,58 +1960,58 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C26" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D26" s="1">
-        <v>3063.29</v>
+        <v>803.45</v>
       </c>
       <c r="E26" s="2">
-        <v>-0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="F26" s="2">
-        <v>-0.42</v>
+        <v>-2.72</v>
       </c>
       <c r="G26" s="2">
-        <v>-1.32</v>
+        <v>-5.18</v>
       </c>
       <c r="H26" s="2">
-        <v>0.36</v>
+        <v>-8.49</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>3085.9</v>
+        <v>822.22</v>
       </c>
       <c r="K26" s="1">
-        <v>3077.18</v>
+        <v>817.64</v>
       </c>
       <c r="L26" s="1">
-        <v>3121.14</v>
+        <v>863.76</v>
       </c>
       <c r="M26" s="3">
-        <v>-15.31</v>
+        <v>-14.65</v>
       </c>
       <c r="N26" s="3">
-        <v>-13.79</v>
+        <v>-14.5</v>
       </c>
       <c r="O26" s="3">
-        <v>2.7</v>
+        <v>-0.11</v>
       </c>
       <c r="P26" s="3">
-        <v>13.98</v>
+        <v>10.52</v>
       </c>
       <c r="Q26" s="3">
-        <v>118.7</v>
+        <v>1.54</v>
       </c>
       <c r="R26" s="3">
-        <v>136.59</v>
+        <v>9.88</v>
       </c>
       <c r="S26" s="3">
-        <v>28.74</v>
+        <v>37.52</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -2022,58 +2022,58 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C27" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D27" s="1">
-        <v>2599.63</v>
+        <v>5056.35</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="F27" s="2">
-        <v>-0.44</v>
+        <v>-3.54</v>
       </c>
       <c r="G27" s="2">
-        <v>-1.46</v>
+        <v>-0.65</v>
       </c>
       <c r="H27" s="2">
-        <v>-0.47</v>
+        <v>8.59</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>2632.39</v>
+        <v>5105.31</v>
       </c>
       <c r="K27" s="1">
-        <v>2612.3</v>
+        <v>5174.56</v>
       </c>
       <c r="L27" s="1">
-        <v>2651.46</v>
+        <v>5302.4</v>
       </c>
       <c r="M27" s="3">
-        <v>-13.88</v>
+        <v>-40.94</v>
       </c>
       <c r="N27" s="3">
-        <v>-12.44</v>
+        <v>-32.52</v>
       </c>
       <c r="O27" s="3">
-        <v>-1.91</v>
+        <v>27.41</v>
       </c>
       <c r="P27" s="3">
-        <v>7.47</v>
+        <v>86.51</v>
       </c>
       <c r="Q27" s="3">
-        <v>89.9</v>
+        <v>363.85</v>
       </c>
       <c r="R27" s="3">
-        <v>106.39</v>
+        <v>325.23</v>
       </c>
       <c r="S27" s="3">
-        <v>27.72</v>
+        <v>38.74</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -2084,58 +2084,58 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D28" s="1">
-        <v>22811.35</v>
+        <v>48224.25</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.34</v>
+        <v>-0.37</v>
       </c>
       <c r="F28" s="2">
-        <v>-1.45</v>
+        <v>-2.18</v>
       </c>
       <c r="G28" s="2">
-        <v>0.84</v>
+        <v>-5.41</v>
       </c>
       <c r="H28" s="2">
-        <v>-12.7</v>
+        <v>9.94</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>24152.75</v>
+        <v>47339.06</v>
       </c>
       <c r="K28" s="1">
-        <v>22800.48</v>
+        <v>49363.48</v>
       </c>
       <c r="L28" s="1">
-        <v>23479.08</v>
+        <v>51543.84</v>
       </c>
       <c r="M28" s="3">
-        <v>-170.52</v>
+        <v>-884</v>
       </c>
       <c r="N28" s="3">
-        <v>-253.14</v>
+        <v>-650.54</v>
       </c>
       <c r="O28" s="3">
-        <v>-384.19</v>
+        <v>935.69</v>
       </c>
       <c r="P28" s="3">
-        <v>-274.8</v>
+        <v>1560.12</v>
       </c>
       <c r="Q28" s="3">
-        <v>194.04</v>
+        <v>2146.68</v>
       </c>
       <c r="R28" s="3">
-        <v>599.66</v>
+        <v>1466.91</v>
       </c>
       <c r="S28" s="3">
-        <v>46.27</v>
+        <v>26.75</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -2146,58 +2146,58 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C29" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D29" s="1">
-        <v>2970.67</v>
+        <v>8917.6</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.34</v>
+        <v>-0.38</v>
       </c>
       <c r="F29" s="2">
-        <v>-0.4</v>
+        <v>-2</v>
       </c>
       <c r="G29" s="2">
-        <v>-1.43</v>
+        <v>-4.21</v>
       </c>
       <c r="H29" s="2">
-        <v>0.13</v>
+        <v>-6.28</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>3001.36</v>
+        <v>9761.05</v>
       </c>
       <c r="K29" s="1">
-        <v>2985.1</v>
+        <v>9023.67</v>
       </c>
       <c r="L29" s="1">
-        <v>3029.1</v>
+        <v>9498.97</v>
       </c>
       <c r="M29" s="3">
-        <v>-15.54</v>
+        <v>-161.95</v>
       </c>
       <c r="N29" s="3">
-        <v>-13.89</v>
+        <v>-167.27</v>
       </c>
       <c r="O29" s="3">
-        <v>0.33</v>
+        <v>-183.21</v>
       </c>
       <c r="P29" s="3">
-        <v>11.42</v>
+        <v>-66.85</v>
       </c>
       <c r="Q29" s="3">
-        <v>114.78</v>
+        <v>387.03</v>
       </c>
       <c r="R29" s="3">
-        <v>132.83</v>
+        <v>507.77</v>
       </c>
       <c r="S29" s="3">
-        <v>26.3</v>
+        <v>33.95</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2208,58 +2208,58 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C30" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D30" s="1">
-        <v>8634</v>
+        <v>18642.35</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="F30" s="2">
-        <v>-1.05</v>
+        <v>-1.46</v>
       </c>
       <c r="G30" s="2">
-        <v>-1.14</v>
+        <v>-0.76</v>
       </c>
       <c r="H30" s="2">
-        <v>-10.22</v>
+        <v>-11.77</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>9231.06</v>
+        <v>19867.71</v>
       </c>
       <c r="K30" s="1">
-        <v>8659.47</v>
+        <v>18741.84</v>
       </c>
       <c r="L30" s="1">
-        <v>9030.52</v>
+        <v>19503.04</v>
       </c>
       <c r="M30" s="3">
-        <v>-115.69</v>
+        <v>-216.46</v>
       </c>
       <c r="N30" s="3">
-        <v>-133.7</v>
+        <v>-261.07</v>
       </c>
       <c r="O30" s="3">
-        <v>-160.89</v>
+        <v>-303.38</v>
       </c>
       <c r="P30" s="3">
-        <v>-79.31</v>
+        <v>-146.21</v>
       </c>
       <c r="Q30" s="3">
-        <v>270.39</v>
+        <v>752.43</v>
       </c>
       <c r="R30" s="3">
-        <v>433.46</v>
+        <v>1110.31</v>
       </c>
       <c r="S30" s="3">
-        <v>40.81</v>
+        <v>39.34</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2270,58 +2270,58 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D31" s="1">
-        <v>838.84</v>
+        <v>13315.2</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="F31" s="2">
-        <v>-0.55</v>
+        <v>-2.93</v>
       </c>
       <c r="G31" s="2">
-        <v>-1.91</v>
+        <v>-3.03</v>
       </c>
       <c r="H31" s="2">
-        <v>-5.9</v>
+        <v>-3.35</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>874.12</v>
+        <v>14000.56</v>
       </c>
       <c r="K31" s="1">
-        <v>844.32</v>
+        <v>13583.71</v>
       </c>
       <c r="L31" s="1">
-        <v>862.32</v>
+        <v>14344.89</v>
       </c>
       <c r="M31" s="3">
-        <v>-6.36</v>
+        <v>-243.09</v>
       </c>
       <c r="N31" s="3">
-        <v>-5.87</v>
+        <v>-239.67</v>
       </c>
       <c r="O31" s="3">
-        <v>-8.71</v>
+        <v>-73.08</v>
       </c>
       <c r="P31" s="3">
-        <v>-5.62</v>
+        <v>126.66</v>
       </c>
       <c r="Q31" s="3">
-        <v>-17.16</v>
+        <v>867.29</v>
       </c>
       <c r="R31" s="3">
-        <v>-14.18</v>
+        <v>1000.14</v>
       </c>
       <c r="S31" s="3">
-        <v>21.96</v>
+        <v>30.58</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2332,58 +2332,58 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C32" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D32" s="1">
-        <v>3796.9</v>
+        <v>8302.75</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="F32" s="2">
-        <v>-1.78</v>
+        <v>-1.72</v>
       </c>
       <c r="G32" s="2">
-        <v>0.39</v>
+        <v>2.79</v>
       </c>
       <c r="H32" s="2">
-        <v>-12.78</v>
+        <v>-17.34</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>4037.51</v>
+        <v>8772.29</v>
       </c>
       <c r="K32" s="1">
-        <v>3802.67</v>
+        <v>8285.93</v>
       </c>
       <c r="L32" s="1">
-        <v>3932.4</v>
+        <v>8397.69</v>
       </c>
       <c r="M32" s="3">
-        <v>-34.28</v>
+        <v>-9.12</v>
       </c>
       <c r="N32" s="3">
-        <v>-47.65</v>
+        <v>-44.59</v>
       </c>
       <c r="O32" s="3">
-        <v>-65.6</v>
+        <v>-159.89</v>
       </c>
       <c r="P32" s="3">
-        <v>-42.41</v>
+        <v>-158.5</v>
       </c>
       <c r="Q32" s="3">
-        <v>126.58</v>
+        <v>-305.23</v>
       </c>
       <c r="R32" s="3">
-        <v>206.84</v>
+        <v>-192.37</v>
       </c>
       <c r="S32" s="3">
-        <v>44.56</v>
+        <v>50.84</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2394,58 +2394,58 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D33" s="1">
-        <v>19156.1</v>
+        <v>67354.15</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="F33" s="2">
-        <v>-1.61</v>
+        <v>-2.37</v>
       </c>
       <c r="G33" s="2">
-        <v>1.12</v>
+        <v>-3.43</v>
       </c>
       <c r="H33" s="2">
-        <v>-10.53</v>
+        <v>-2.9</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>20111.69</v>
+        <v>70036.43</v>
       </c>
       <c r="K33" s="1">
-        <v>19193.39</v>
+        <v>68480.5</v>
       </c>
       <c r="L33" s="1">
-        <v>19857.23</v>
+        <v>71667.51</v>
       </c>
       <c r="M33" s="3">
-        <v>-149.24</v>
+        <v>-1029.68</v>
       </c>
       <c r="N33" s="3">
-        <v>-231.83</v>
+        <v>-995.78</v>
       </c>
       <c r="O33" s="3">
-        <v>-265.24</v>
+        <v>-222.32</v>
       </c>
       <c r="P33" s="3">
-        <v>-138.8</v>
+        <v>573.95</v>
       </c>
       <c r="Q33" s="3">
-        <v>500.78</v>
+        <v>2639.9</v>
       </c>
       <c r="R33" s="3">
-        <v>798.2</v>
+        <v>3177.6</v>
       </c>
       <c r="S33" s="3">
-        <v>45.01</v>
+        <v>32.78</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2456,58 +2456,58 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C34" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D34" s="1">
-        <v>8251.5</v>
+        <v>8592.1</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.51</v>
+        <v>-0.49</v>
       </c>
       <c r="F34" s="2">
-        <v>1.93</v>
+        <v>-1.53</v>
       </c>
       <c r="G34" s="2">
-        <v>2.94</v>
+        <v>-1.62</v>
       </c>
       <c r="H34" s="2">
-        <v>-3.3</v>
+        <v>-10.65</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>8575.14</v>
+        <v>9226.49</v>
       </c>
       <c r="K34" s="1">
-        <v>8150.85</v>
+        <v>8647.22</v>
       </c>
       <c r="L34" s="1">
-        <v>8364.1</v>
+        <v>9013.05</v>
       </c>
       <c r="M34" s="3">
-        <v>-42.26</v>
+        <v>-113.45</v>
       </c>
       <c r="N34" s="3">
-        <v>-78.63</v>
+        <v>-129.65</v>
       </c>
       <c r="O34" s="3">
-        <v>-75.54</v>
+        <v>-164.24</v>
       </c>
       <c r="P34" s="3">
-        <v>-29.76</v>
+        <v>-79.98</v>
       </c>
       <c r="Q34" s="3">
-        <v>575.37</v>
+        <v>267.04</v>
       </c>
       <c r="R34" s="3">
-        <v>685.4</v>
+        <v>432.8</v>
       </c>
       <c r="S34" s="3">
-        <v>52.71</v>
+        <v>38.96</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2518,58 +2518,58 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D35" s="1">
-        <v>30743.2</v>
+        <v>4688.15</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.53</v>
+        <v>-0.49</v>
       </c>
       <c r="F35" s="2">
-        <v>-1.46</v>
+        <v>-2.11</v>
       </c>
       <c r="G35" s="2">
-        <v>-0.52</v>
+        <v>0.09</v>
       </c>
       <c r="H35" s="2">
-        <v>-7.76</v>
+        <v>-9.52</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>32364.85</v>
+        <v>4915.37</v>
       </c>
       <c r="K35" s="1">
-        <v>30867.57</v>
+        <v>4708.88</v>
       </c>
       <c r="L35" s="1">
-        <v>32046.75</v>
+        <v>4867.4</v>
       </c>
       <c r="M35" s="3">
-        <v>-338.01</v>
+        <v>-39.92</v>
       </c>
       <c r="N35" s="3">
-        <v>-419.77</v>
+        <v>-55.19</v>
       </c>
       <c r="O35" s="3">
-        <v>-376.58</v>
+        <v>-51.03</v>
       </c>
       <c r="P35" s="3">
-        <v>-112.38</v>
+        <v>-17.32</v>
       </c>
       <c r="Q35" s="3">
-        <v>1837.58</v>
+        <v>219.58</v>
       </c>
       <c r="R35" s="3">
-        <v>2375</v>
+        <v>299.35</v>
       </c>
       <c r="S35" s="3">
-        <v>41.81</v>
+        <v>43.14</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2580,58 +2580,58 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D36" s="1">
-        <v>3468.19</v>
+        <v>13757.8</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.53</v>
+        <v>-0.5</v>
       </c>
       <c r="F36" s="2">
-        <v>-0.56</v>
+        <v>-1.4</v>
       </c>
       <c r="G36" s="2">
-        <v>-1.52</v>
+        <v>3.03</v>
       </c>
       <c r="H36" s="2">
-        <v>-0.71</v>
+        <v>-10.04</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>3495.56</v>
+        <v>14394.16</v>
       </c>
       <c r="K36" s="1">
-        <v>3487.08</v>
+        <v>13691.54</v>
       </c>
       <c r="L36" s="1">
-        <v>3537.15</v>
+        <v>14035.63</v>
       </c>
       <c r="M36" s="3">
-        <v>-17.33</v>
+        <v>-53.28</v>
       </c>
       <c r="N36" s="3">
-        <v>-14.91</v>
+        <v>-134.63</v>
       </c>
       <c r="O36" s="3">
-        <v>2.75</v>
+        <v>-215.28</v>
       </c>
       <c r="P36" s="3">
-        <v>15.42</v>
+        <v>-160.49</v>
       </c>
       <c r="Q36" s="3">
-        <v>118.79</v>
+        <v>-535.2</v>
       </c>
       <c r="R36" s="3">
-        <v>141.9</v>
+        <v>-491.58</v>
       </c>
       <c r="S36" s="3">
-        <v>34.41</v>
+        <v>50.63</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2642,58 +2642,58 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C37" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D37" s="1">
-        <v>4711.05</v>
+        <v>23637.8</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="F37" s="2">
-        <v>-1.63</v>
+        <v>-2.05</v>
       </c>
       <c r="G37" s="2">
-        <v>0.58</v>
+        <v>-0.41</v>
       </c>
       <c r="H37" s="2">
-        <v>-9.08</v>
+        <v>-11.43</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>4917.65</v>
+        <v>25039.74</v>
       </c>
       <c r="K37" s="1">
-        <v>4713.48</v>
+        <v>23788.85</v>
       </c>
       <c r="L37" s="1">
-        <v>4876.33</v>
+        <v>24556.49</v>
       </c>
       <c r="M37" s="3">
-        <v>-40.85</v>
+        <v>-208.41</v>
       </c>
       <c r="N37" s="3">
-        <v>-59</v>
+        <v>-264.81</v>
       </c>
       <c r="O37" s="3">
-        <v>-49.2</v>
+        <v>-348.51</v>
       </c>
       <c r="P37" s="3">
-        <v>-16.96</v>
+        <v>-197.16</v>
       </c>
       <c r="Q37" s="3">
-        <v>221.41</v>
+        <v>324.02</v>
       </c>
       <c r="R37" s="3">
-        <v>299.71</v>
+        <v>706.97</v>
       </c>
       <c r="S37" s="3">
-        <v>45.15</v>
+        <v>41.65</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2704,58 +2704,58 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D38" s="1">
-        <v>23762.45</v>
+        <v>11798.35</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.56</v>
+        <v>-0.52</v>
       </c>
       <c r="F38" s="2">
-        <v>-1.54</v>
+        <v>-2.76</v>
       </c>
       <c r="G38" s="2">
-        <v>0.12</v>
+        <v>-7.54</v>
       </c>
       <c r="H38" s="2">
-        <v>-10.97</v>
+        <v>5.65</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>25053.96</v>
+        <v>12482.16</v>
       </c>
       <c r="K38" s="1">
-        <v>23822.42</v>
+        <v>12056.55</v>
       </c>
       <c r="L38" s="1">
-        <v>24598.3</v>
+        <v>12837.2</v>
       </c>
       <c r="M38" s="3">
-        <v>-208.23</v>
+        <v>-286.63</v>
       </c>
       <c r="N38" s="3">
-        <v>-278.91</v>
+        <v>-254.92</v>
       </c>
       <c r="O38" s="3">
-        <v>-338.56</v>
+        <v>10.53</v>
       </c>
       <c r="P38" s="3">
-        <v>-195.17</v>
+        <v>208</v>
       </c>
       <c r="Q38" s="3">
-        <v>333.97</v>
+        <v>1132.92</v>
       </c>
       <c r="R38" s="3">
-        <v>708.96</v>
+        <v>1129.27</v>
       </c>
       <c r="S38" s="3">
-        <v>43.81</v>
+        <v>32.88</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2766,58 +2766,58 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C39" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D39" s="1">
-        <v>43720.7</v>
+        <v>5580.35</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.58</v>
+        <v>-0.52</v>
       </c>
       <c r="F39" s="2">
-        <v>-2.01</v>
+        <v>-0.91</v>
       </c>
       <c r="G39" s="2">
-        <v>-1.77</v>
+        <v>1.97</v>
       </c>
       <c r="H39" s="2">
-        <v>-21.19</v>
+        <v>-12.61</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>49030.47</v>
+        <v>5953.06</v>
       </c>
       <c r="K39" s="1">
-        <v>44453.2</v>
+        <v>5550.89</v>
       </c>
       <c r="L39" s="1">
-        <v>46007.7</v>
+        <v>5688.8</v>
       </c>
       <c r="M39" s="3">
-        <v>-498.49</v>
+        <v>-24.75</v>
       </c>
       <c r="N39" s="3">
-        <v>-503.4</v>
+        <v>-55.24</v>
       </c>
       <c r="O39" s="3">
-        <v>-1619.09</v>
+        <v>-116.74</v>
       </c>
       <c r="P39" s="3">
-        <v>-1344.9</v>
+        <v>-95.33</v>
       </c>
       <c r="Q39" s="3">
-        <v>-2136.87</v>
+        <v>27.36</v>
       </c>
       <c r="R39" s="3">
-        <v>-960.19</v>
+        <v>139.95</v>
       </c>
       <c r="S39" s="3">
-        <v>39.34</v>
+        <v>50.58</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2828,58 +2828,58 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTY</v>
       </c>
       <c r="C40" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTY</v>
       </c>
       <c r="D40" s="1">
-        <v>24581.6</v>
+        <v>22687.65</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.7</v>
+        <v>-0.54</v>
       </c>
       <c r="F40" s="2">
-        <v>-1.33</v>
+        <v>-1.98</v>
       </c>
       <c r="G40" s="2">
-        <v>-2.53</v>
+        <v>0.3</v>
       </c>
       <c r="H40" s="2">
-        <v>-9.22</v>
+        <v>-13.17</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>26266.8</v>
+        <v>24136.49</v>
       </c>
       <c r="K40" s="1">
-        <v>24835.34</v>
+        <v>22779.97</v>
       </c>
       <c r="L40" s="1">
-        <v>26187.65</v>
+        <v>23441.16</v>
       </c>
       <c r="M40" s="3">
-        <v>-432.82</v>
+        <v>-167.07</v>
       </c>
       <c r="N40" s="3">
-        <v>-457.75</v>
+        <v>-235.92</v>
       </c>
       <c r="O40" s="3">
-        <v>-344.79</v>
+        <v>-394.06</v>
       </c>
       <c r="P40" s="3">
-        <v>-67.01</v>
+        <v>-276.78</v>
       </c>
       <c r="Q40" s="3">
-        <v>1146.92</v>
+        <v>184.18</v>
       </c>
       <c r="R40" s="3">
-        <v>1596.11</v>
+        <v>597.68</v>
       </c>
       <c r="S40" s="3">
-        <v>32.82</v>
+        <v>43.98</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2890,58 +2890,58 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D41" s="1">
-        <v>16114</v>
+        <v>16410.8</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.71</v>
+        <v>-0.54</v>
       </c>
       <c r="F41" s="2">
-        <v>-2.96</v>
+        <v>-3.16</v>
       </c>
       <c r="G41" s="2">
-        <v>1.28</v>
+        <v>-3.63</v>
       </c>
       <c r="H41" s="2">
-        <v>-26.74</v>
+        <v>-4.89</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>18428.48</v>
+        <v>17225.13</v>
       </c>
       <c r="K41" s="1">
-        <v>16123.21</v>
+        <v>16776.16</v>
       </c>
       <c r="L41" s="1">
-        <v>17200.33</v>
+        <v>17679.94</v>
       </c>
       <c r="M41" s="3">
-        <v>-279.07</v>
+        <v>-298.05</v>
       </c>
       <c r="N41" s="3">
-        <v>-396.25</v>
+        <v>-282.47</v>
       </c>
       <c r="O41" s="3">
-        <v>-667.86</v>
+        <v>-62.33</v>
       </c>
       <c r="P41" s="3">
-        <v>-510.36</v>
+        <v>159.12</v>
       </c>
       <c r="Q41" s="3">
-        <v>271.55</v>
+        <v>887.46</v>
       </c>
       <c r="R41" s="3">
-        <v>928.1</v>
+        <v>1045.73</v>
       </c>
       <c r="S41" s="3">
-        <v>45.26</v>
+        <v>28.89</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2952,58 +2952,58 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D42" s="1">
-        <v>10564.15</v>
+        <v>29997.95</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.71</v>
+        <v>-0.55</v>
       </c>
       <c r="F42" s="2">
-        <v>-2.96</v>
+        <v>-1.59</v>
       </c>
       <c r="G42" s="2">
-        <v>1.23</v>
+        <v>3.39</v>
       </c>
       <c r="H42" s="2">
-        <v>-28.14</v>
+        <v>-10.87</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>12213.74</v>
+        <v>30960.55</v>
       </c>
       <c r="K42" s="1">
-        <v>10572.46</v>
+        <v>29796.08</v>
       </c>
       <c r="L42" s="1">
-        <v>11284</v>
+        <v>30109.16</v>
       </c>
       <c r="M42" s="3">
-        <v>-185.56</v>
+        <v>7.1</v>
       </c>
       <c r="N42" s="3">
-        <v>-262.43</v>
+        <v>-160.88</v>
       </c>
       <c r="O42" s="3">
-        <v>-483.58</v>
+        <v>-354.53</v>
       </c>
       <c r="P42" s="3">
-        <v>-385.07</v>
+        <v>-316.41</v>
       </c>
       <c r="Q42" s="3">
-        <v>-9.91</v>
+        <v>487.16</v>
       </c>
       <c r="R42" s="3">
-        <v>425.44</v>
+        <v>991.93</v>
       </c>
       <c r="S42" s="3">
-        <v>45.14</v>
+        <v>53.94</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -3014,58 +3014,58 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C43" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D43" s="1">
-        <v>5987.5</v>
+        <v>13316.5</v>
       </c>
       <c r="E43" s="2">
-        <v>-0.73</v>
+        <v>-0.55</v>
       </c>
       <c r="F43" s="2">
-        <v>-1.28</v>
+        <v>-2.31</v>
       </c>
       <c r="G43" s="2">
-        <v>-3.87</v>
+        <v>-3.15</v>
       </c>
       <c r="H43" s="2">
-        <v>-5.93</v>
+        <v>-7.98</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>6746.92</v>
+        <v>14149.36</v>
       </c>
       <c r="K43" s="1">
-        <v>6064.46</v>
+        <v>13516.42</v>
       </c>
       <c r="L43" s="1">
-        <v>6314.55</v>
+        <v>14139.31</v>
       </c>
       <c r="M43" s="3">
-        <v>-94.1</v>
+        <v>-205.04</v>
       </c>
       <c r="N43" s="3">
-        <v>-91.8</v>
+        <v>-205.48</v>
       </c>
       <c r="O43" s="3">
-        <v>-200.83</v>
+        <v>-171.3</v>
       </c>
       <c r="P43" s="3">
-        <v>-146.59</v>
+        <v>-15.4</v>
       </c>
       <c r="Q43" s="3">
-        <v>231.81</v>
+        <v>70</v>
       </c>
       <c r="R43" s="3">
-        <v>403.51</v>
+        <v>117.18</v>
       </c>
       <c r="S43" s="3">
-        <v>32.1</v>
+        <v>32.28</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -3076,58 +3076,58 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D44" s="1">
-        <v>13103.15</v>
+        <v>32107.2</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.76</v>
+        <v>-0.56</v>
       </c>
       <c r="F44" s="2">
-        <v>-1.76</v>
+        <v>-2.26</v>
       </c>
       <c r="G44" s="2">
-        <v>-0.51</v>
+        <v>-2.29</v>
       </c>
       <c r="H44" s="2">
-        <v>-9.84</v>
+        <v>-5.44</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>13800.18</v>
+        <v>33688.52</v>
       </c>
       <c r="K44" s="1">
-        <v>13187.58</v>
+        <v>32521.69</v>
       </c>
       <c r="L44" s="1">
-        <v>13659.16</v>
+        <v>33932.23</v>
       </c>
       <c r="M44" s="3">
-        <v>-133.41</v>
+        <v>-431.64</v>
       </c>
       <c r="N44" s="3">
-        <v>-163.99</v>
+        <v>-459.71</v>
       </c>
       <c r="O44" s="3">
-        <v>-163.63</v>
+        <v>-255.98</v>
       </c>
       <c r="P44" s="3">
-        <v>-67.86</v>
+        <v>94.89</v>
       </c>
       <c r="Q44" s="3">
-        <v>272.21</v>
+        <v>1987.6</v>
       </c>
       <c r="R44" s="3">
-        <v>464.84</v>
+        <v>2427.44</v>
       </c>
       <c r="S44" s="3">
-        <v>40.82</v>
+        <v>34.56</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -3138,58 +3138,58 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C45" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D45" s="1">
-        <v>54976.9</v>
+        <v>30563.6</v>
       </c>
       <c r="E45" s="2">
-        <v>-0.92</v>
+        <v>-0.58</v>
       </c>
       <c r="F45" s="2">
-        <v>-1.55</v>
+        <v>-2.04</v>
       </c>
       <c r="G45" s="2">
-        <v>0.63</v>
+        <v>-1.1</v>
       </c>
       <c r="H45" s="2">
-        <v>-7.73</v>
+        <v>-8.3</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>56890.68</v>
+        <v>32352.54</v>
       </c>
       <c r="K45" s="1">
-        <v>55317.69</v>
+        <v>30812.3</v>
       </c>
       <c r="L45" s="1">
-        <v>56378.11</v>
+        <v>31983.53</v>
       </c>
       <c r="M45" s="3">
-        <v>-258.91</v>
+        <v>-339.37</v>
       </c>
       <c r="N45" s="3">
-        <v>-378.44</v>
+        <v>-403.69</v>
       </c>
       <c r="O45" s="3">
-        <v>-347.01</v>
+        <v>-390.9</v>
       </c>
       <c r="P45" s="3">
-        <v>-98.28</v>
+        <v>-115.25</v>
       </c>
       <c r="Q45" s="3">
-        <v>1665.08</v>
+        <v>1823.26</v>
       </c>
       <c r="R45" s="3">
-        <v>2288.6</v>
+        <v>2372.14</v>
       </c>
       <c r="S45" s="3">
-        <v>43.5</v>
+        <v>39.56</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3200,58 +3200,58 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D46" s="1">
-        <v>21837.9</v>
+        <v>13025.5</v>
       </c>
       <c r="E46" s="2">
-        <v>-0.92</v>
+        <v>-0.59</v>
       </c>
       <c r="F46" s="2">
-        <v>-1.94</v>
+        <v>-2.34</v>
       </c>
       <c r="G46" s="2">
-        <v>-1.06</v>
+        <v>-1.1</v>
       </c>
       <c r="H46" s="2">
-        <v>-8.52</v>
+        <v>-10.38</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>22854.12</v>
+        <v>13793.23</v>
       </c>
       <c r="K46" s="1">
-        <v>22046.22</v>
+        <v>13158.11</v>
       </c>
       <c r="L46" s="1">
-        <v>22831.63</v>
+        <v>13634.56</v>
       </c>
       <c r="M46" s="3">
-        <v>-230.62</v>
+        <v>-137.33</v>
       </c>
       <c r="N46" s="3">
-        <v>-266.46</v>
+        <v>-158.66</v>
       </c>
       <c r="O46" s="3">
-        <v>-208.94</v>
+        <v>-169.83</v>
       </c>
       <c r="P46" s="3">
-        <v>-38.98</v>
+        <v>-69.09</v>
       </c>
       <c r="Q46" s="3">
-        <v>517.48</v>
+        <v>266.02</v>
       </c>
       <c r="R46" s="3">
-        <v>805.44</v>
+        <v>463.6</v>
       </c>
       <c r="S46" s="3">
-        <v>38.47</v>
+        <v>38.52</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3262,58 +3262,58 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C47" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D47" s="1">
-        <v>48403.9</v>
+        <v>7315.1</v>
       </c>
       <c r="E47" s="2">
-        <v>-0.95</v>
+        <v>-0.61</v>
       </c>
       <c r="F47" s="2">
-        <v>-1.81</v>
+        <v>-1.93</v>
       </c>
       <c r="G47" s="2">
-        <v>-5.06</v>
+        <v>3.38</v>
       </c>
       <c r="H47" s="2">
-        <v>10.34</v>
+        <v>-3.27</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>47314.35</v>
+        <v>7334.84</v>
       </c>
       <c r="K47" s="1">
-        <v>49616.65</v>
+        <v>7296.83</v>
       </c>
       <c r="L47" s="1">
-        <v>51627.33</v>
+        <v>7403.27</v>
       </c>
       <c r="M47" s="3">
-        <v>-819.15</v>
+        <v>-3.14</v>
       </c>
       <c r="N47" s="3">
-        <v>-592.18</v>
+        <v>-39.25</v>
       </c>
       <c r="O47" s="3">
-        <v>950.03</v>
+        <v>-1.67</v>
       </c>
       <c r="P47" s="3">
-        <v>1562.99</v>
+        <v>31.14</v>
       </c>
       <c r="Q47" s="3">
-        <v>2161.01</v>
+        <v>469.21</v>
       </c>
       <c r="R47" s="3">
-        <v>1469.77</v>
+        <v>552.05</v>
       </c>
       <c r="S47" s="3">
-        <v>27.7</v>
+        <v>51.36</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3324,58 +3324,58 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D48" s="1">
-        <v>26578</v>
+        <v>3773.9</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.96</v>
+        <v>-0.61</v>
       </c>
       <c r="F48" s="2">
-        <v>-2.33</v>
+        <v>-2.37</v>
       </c>
       <c r="G48" s="2">
-        <v>0.08</v>
+        <v>-0.22</v>
       </c>
       <c r="H48" s="2">
-        <v>-11.93</v>
+        <v>-13.31</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>28564.95</v>
+        <v>4034.76</v>
       </c>
       <c r="K48" s="1">
-        <v>26870.58</v>
+        <v>3797.44</v>
       </c>
       <c r="L48" s="1">
-        <v>27656.44</v>
+        <v>3925.14</v>
       </c>
       <c r="M48" s="3">
-        <v>-212.89</v>
+        <v>-34.14</v>
       </c>
       <c r="N48" s="3">
-        <v>-273.42</v>
+        <v>-44.95</v>
       </c>
       <c r="O48" s="3">
-        <v>-477.2</v>
+        <v>-67.44</v>
       </c>
       <c r="P48" s="3">
-        <v>-295.04</v>
+        <v>-42.77</v>
       </c>
       <c r="Q48" s="3">
-        <v>1312.45</v>
+        <v>124.74</v>
       </c>
       <c r="R48" s="3">
-        <v>1900.4</v>
+        <v>206.47</v>
       </c>
       <c r="S48" s="3">
-        <v>40.93</v>
+        <v>42.18</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3386,58 +3386,58 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D49" s="1">
-        <v>10833.3</v>
+        <v>14747.95</v>
       </c>
       <c r="E49" s="2">
-        <v>-0.96</v>
+        <v>-0.63</v>
       </c>
       <c r="F49" s="2">
-        <v>-2</v>
+        <v>-2.81</v>
       </c>
       <c r="G49" s="2">
-        <v>-2.16</v>
+        <v>-4.57</v>
       </c>
       <c r="H49" s="2">
-        <v>-11.85</v>
+        <v>-4.31</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>11503.9</v>
+        <v>15629.87</v>
       </c>
       <c r="K49" s="1">
-        <v>10955.26</v>
+        <v>15042.09</v>
       </c>
       <c r="L49" s="1">
-        <v>11506.44</v>
+        <v>15889.62</v>
       </c>
       <c r="M49" s="3">
-        <v>-166.82</v>
+        <v>-276.58</v>
       </c>
       <c r="N49" s="3">
-        <v>-183.63</v>
+        <v>-266.49</v>
       </c>
       <c r="O49" s="3">
-        <v>-151.16</v>
+        <v>-100.76</v>
       </c>
       <c r="P49" s="3">
-        <v>-41.47</v>
+        <v>100.11</v>
       </c>
       <c r="Q49" s="3">
-        <v>217.16</v>
+        <v>1239.5</v>
       </c>
       <c r="R49" s="3">
-        <v>394.1</v>
+        <v>1442.38</v>
       </c>
       <c r="S49" s="3">
-        <v>37.32</v>
+        <v>30.01</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3448,58 +3448,58 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY500</v>
       </c>
       <c r="C50" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY500</v>
       </c>
       <c r="D50" s="1">
-        <v>15526.95</v>
+        <v>21696.55</v>
       </c>
       <c r="E50" s="2">
-        <v>-0.97</v>
+        <v>-0.65</v>
       </c>
       <c r="F50" s="2">
-        <v>-2</v>
+        <v>-2.58</v>
       </c>
       <c r="G50" s="2">
-        <v>-1.46</v>
+        <v>-1.7</v>
       </c>
       <c r="H50" s="2">
-        <v>-7.88</v>
+        <v>-9.11</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>16301.75</v>
+        <v>22844.26</v>
       </c>
       <c r="K50" s="1">
-        <v>15706.53</v>
+        <v>21982.64</v>
       </c>
       <c r="L50" s="1">
-        <v>16338.06</v>
+        <v>22790.7</v>
       </c>
       <c r="M50" s="3">
-        <v>-190.62</v>
+        <v>-243.31</v>
       </c>
       <c r="N50" s="3">
-        <v>-211.59</v>
+        <v>-261.83</v>
       </c>
       <c r="O50" s="3">
-        <v>-145.51</v>
+        <v>-220.21</v>
       </c>
       <c r="P50" s="3">
-        <v>-1.81</v>
+        <v>-41.24</v>
       </c>
       <c r="Q50" s="3">
-        <v>917.21</v>
+        <v>506.21</v>
       </c>
       <c r="R50" s="3">
-        <v>1178.93</v>
+        <v>803.19</v>
       </c>
       <c r="S50" s="3">
-        <v>36.36</v>
+        <v>36.02</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3510,58 +3510,58 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D51" s="1">
-        <v>8951.3</v>
+        <v>15423.75</v>
       </c>
       <c r="E51" s="2">
-        <v>-0.98</v>
+        <v>-0.66</v>
       </c>
       <c r="F51" s="2">
-        <v>-1.63</v>
+        <v>-2.65</v>
       </c>
       <c r="G51" s="2">
-        <v>-3.85</v>
+        <v>-2.12</v>
       </c>
       <c r="H51" s="2">
-        <v>-5.93</v>
+        <v>-8.49</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>9763.29</v>
+        <v>16295.33</v>
       </c>
       <c r="K51" s="1">
-        <v>9047.24</v>
+        <v>15655.11</v>
       </c>
       <c r="L51" s="1">
-        <v>9520.84</v>
+        <v>16306.59</v>
       </c>
       <c r="M51" s="3">
-        <v>-161.85</v>
+        <v>-200.8</v>
       </c>
       <c r="N51" s="3">
-        <v>-168.6</v>
+        <v>-209.43</v>
       </c>
       <c r="O51" s="3">
-        <v>-180.52</v>
+        <v>-153.74</v>
       </c>
       <c r="P51" s="3">
-        <v>-66.31</v>
+        <v>-3.46</v>
       </c>
       <c r="Q51" s="3">
-        <v>389.72</v>
+        <v>908.97</v>
       </c>
       <c r="R51" s="3">
-        <v>508.31</v>
+        <v>1177.28</v>
       </c>
       <c r="S51" s="3">
-        <v>35.12</v>
+        <v>34.01</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3578,52 +3578,52 @@
         <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D52" s="1">
-        <v>12344.8</v>
+        <v>12262.9</v>
       </c>
       <c r="E52" s="2">
-        <v>-1</v>
+        <v>-0.66</v>
       </c>
       <c r="F52" s="2">
-        <v>-2.04</v>
+        <v>-2.69</v>
       </c>
       <c r="G52" s="2">
-        <v>-1.29</v>
+        <v>-1.94</v>
       </c>
       <c r="H52" s="2">
-        <v>-7.83</v>
+        <v>-8.44</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>12868.21</v>
+        <v>12863.13</v>
       </c>
       <c r="K52" s="1">
-        <v>12476.41</v>
+        <v>12437.59</v>
       </c>
       <c r="L52" s="1">
-        <v>12913.2</v>
+        <v>12890.41</v>
       </c>
       <c r="M52" s="3">
-        <v>-129.72</v>
+        <v>-138.27</v>
       </c>
       <c r="N52" s="3">
-        <v>-146.61</v>
+        <v>-144.94</v>
       </c>
       <c r="O52" s="3">
-        <v>-96.37</v>
+        <v>-102.9</v>
       </c>
       <c r="P52" s="3">
-        <v>1.22</v>
+        <v>-0.09</v>
       </c>
       <c r="Q52" s="3">
-        <v>630.33</v>
+        <v>623.8</v>
       </c>
       <c r="R52" s="3">
-        <v>826.14</v>
+        <v>824.84</v>
       </c>
       <c r="S52" s="3">
-        <v>37.77</v>
+        <v>35.29</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3634,58 +3634,58 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C53" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D53" s="1">
-        <v>32287.7</v>
+        <v>10916.2</v>
       </c>
       <c r="E53" s="2">
-        <v>-1.03</v>
+        <v>-0.66</v>
       </c>
       <c r="F53" s="2">
-        <v>-1.71</v>
+        <v>-0.99</v>
       </c>
       <c r="G53" s="2">
-        <v>-1.74</v>
+        <v>3.57</v>
       </c>
       <c r="H53" s="2">
-        <v>-4.91</v>
+        <v>-12.56</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>33696.17</v>
+        <v>11224.6</v>
       </c>
       <c r="K53" s="1">
-        <v>32613.79</v>
+        <v>10794.02</v>
       </c>
       <c r="L53" s="1">
-        <v>34002.68</v>
+        <v>11086.78</v>
       </c>
       <c r="M53" s="3">
-        <v>-418.43</v>
+        <v>-34.31</v>
       </c>
       <c r="N53" s="3">
-        <v>-466.72</v>
+        <v>-118</v>
       </c>
       <c r="O53" s="3">
-        <v>-241.58</v>
+        <v>-112.43</v>
       </c>
       <c r="P53" s="3">
-        <v>97.77</v>
+        <v>-75.61</v>
       </c>
       <c r="Q53" s="3">
-        <v>2002</v>
+        <v>33.61</v>
       </c>
       <c r="R53" s="3">
-        <v>2430.32</v>
+        <v>176.96</v>
       </c>
       <c r="S53" s="3">
-        <v>36.59</v>
+        <v>54.05</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3696,58 +3696,58 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C54" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D54" s="1">
-        <v>13389.95</v>
+        <v>9034.35</v>
       </c>
       <c r="E54" s="2">
-        <v>-1.03</v>
+        <v>-0.66</v>
       </c>
       <c r="F54" s="2">
-        <v>-1.77</v>
+        <v>-2.3</v>
       </c>
       <c r="G54" s="2">
-        <v>-2.62</v>
+        <v>-3.48</v>
       </c>
       <c r="H54" s="2">
-        <v>-7.47</v>
+        <v>-8.31</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>14154.34</v>
+        <v>9989.14</v>
       </c>
       <c r="K54" s="1">
-        <v>13560.84</v>
+        <v>9175.85</v>
       </c>
       <c r="L54" s="1">
-        <v>14168.32</v>
+        <v>9538.32</v>
       </c>
       <c r="M54" s="3">
-        <v>-198.1</v>
+        <v>-126.37</v>
       </c>
       <c r="N54" s="3">
-        <v>-205.59</v>
+        <v>-125.98</v>
       </c>
       <c r="O54" s="3">
-        <v>-165.45</v>
+        <v>-232.48</v>
       </c>
       <c r="P54" s="3">
-        <v>-14.23</v>
+        <v>-147.76</v>
       </c>
       <c r="Q54" s="3">
-        <v>75.86</v>
+        <v>787.92</v>
       </c>
       <c r="R54" s="3">
-        <v>118.36</v>
+        <v>1091.01</v>
       </c>
       <c r="S54" s="3">
-        <v>34.12</v>
+        <v>32.69</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3758,58 +3758,58 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D55" s="1">
-        <v>26904.35</v>
+        <v>11320.85</v>
       </c>
       <c r="E55" s="2">
-        <v>-1.05</v>
+        <v>-0.71</v>
       </c>
       <c r="F55" s="2">
-        <v>-2.87</v>
+        <v>-1.83</v>
       </c>
       <c r="G55" s="2">
-        <v>0.78</v>
+        <v>1.58</v>
       </c>
       <c r="H55" s="2">
-        <v>-6.33</v>
+        <v>-14.72</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>27380.27</v>
+        <v>12181.48</v>
       </c>
       <c r="K55" s="1">
-        <v>27198.08</v>
+        <v>11325.87</v>
       </c>
       <c r="L55" s="1">
-        <v>27296.76</v>
+        <v>11553.89</v>
       </c>
       <c r="M55" s="3">
-        <v>1.17</v>
+        <v>-44.11</v>
       </c>
       <c r="N55" s="3">
-        <v>-42</v>
+        <v>-90.47</v>
       </c>
       <c r="O55" s="3">
-        <v>-33.88</v>
+        <v>-264.44</v>
       </c>
       <c r="P55" s="3">
-        <v>18.71</v>
+        <v>-235.71</v>
       </c>
       <c r="Q55" s="3">
-        <v>649.74</v>
+        <v>-130.42</v>
       </c>
       <c r="R55" s="3">
-        <v>875.83</v>
+        <v>114.35</v>
       </c>
       <c r="S55" s="3">
-        <v>44.99</v>
+        <v>47.77</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3820,58 +3820,58 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C56" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D56" s="1">
-        <v>9094.4</v>
+        <v>25011.5</v>
       </c>
       <c r="E56" s="2">
-        <v>-1.05</v>
+        <v>-0.73</v>
       </c>
       <c r="F56" s="2">
-        <v>-1.65</v>
+        <v>-2.94</v>
       </c>
       <c r="G56" s="2">
-        <v>-2.84</v>
+        <v>-4.88</v>
       </c>
       <c r="H56" s="2">
-        <v>-7.71</v>
+        <v>-11.27</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>9992.38</v>
+        <v>26928.44</v>
       </c>
       <c r="K56" s="1">
-        <v>9207.3</v>
+        <v>25375.52</v>
       </c>
       <c r="L56" s="1">
-        <v>9554.65</v>
+        <v>27260.53</v>
       </c>
       <c r="M56" s="3">
-        <v>-120.21</v>
+        <v>-546.04</v>
       </c>
       <c r="N56" s="3">
-        <v>-125.88</v>
+        <v>-613.46</v>
       </c>
       <c r="O56" s="3">
-        <v>-227.69</v>
+        <v>-297.05</v>
       </c>
       <c r="P56" s="3">
-        <v>-146.81</v>
+        <v>93.49</v>
       </c>
       <c r="Q56" s="3">
-        <v>792.71</v>
+        <v>1461.1</v>
       </c>
       <c r="R56" s="3">
-        <v>1091.97</v>
+        <v>1807.72</v>
       </c>
       <c r="S56" s="3">
-        <v>34.98</v>
+        <v>35.68</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3882,58 +3882,58 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C57" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D57" s="1">
-        <v>22448.8</v>
+        <v>15358.1</v>
       </c>
       <c r="E57" s="2">
-        <v>-1.1</v>
+        <v>-0.73</v>
       </c>
       <c r="F57" s="2">
-        <v>-2.25</v>
+        <v>-2.94</v>
       </c>
       <c r="G57" s="2">
-        <v>-1.39</v>
+        <v>-2.49</v>
       </c>
       <c r="H57" s="2">
-        <v>-6.69</v>
+        <v>-6.84</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>23501.27</v>
+        <v>16020.38</v>
       </c>
       <c r="K57" s="1">
-        <v>22822.94</v>
+        <v>15628.43</v>
       </c>
       <c r="L57" s="1">
-        <v>23785.35</v>
+        <v>16221.84</v>
       </c>
       <c r="M57" s="3">
-        <v>-276.57</v>
+        <v>-188.13</v>
       </c>
       <c r="N57" s="3">
-        <v>-296.21</v>
+        <v>-184.94</v>
       </c>
       <c r="O57" s="3">
-        <v>-199.03</v>
+        <v>-83.45</v>
       </c>
       <c r="P57" s="3">
-        <v>32.29</v>
+        <v>59.95</v>
       </c>
       <c r="Q57" s="3">
-        <v>1021.08</v>
+        <v>909.74</v>
       </c>
       <c r="R57" s="3">
-        <v>1359.05</v>
+        <v>1146.63</v>
       </c>
       <c r="S57" s="3">
-        <v>34.75</v>
+        <v>32.51</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3944,58 +3944,58 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D58" s="1">
-        <v>24691.45</v>
+        <v>10753.25</v>
       </c>
       <c r="E58" s="2">
-        <v>-1.18</v>
+        <v>-0.74</v>
       </c>
       <c r="F58" s="2">
-        <v>-2.74</v>
+        <v>-2.73</v>
       </c>
       <c r="G58" s="2">
-        <v>0.17</v>
+        <v>-2.88</v>
       </c>
       <c r="H58" s="2">
-        <v>-10.58</v>
+        <v>-12.5</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>26236.79</v>
+        <v>11496.75</v>
       </c>
       <c r="K58" s="1">
-        <v>24999.53</v>
+        <v>10918.53</v>
       </c>
       <c r="L58" s="1">
-        <v>25562.35</v>
+        <v>11476.92</v>
       </c>
       <c r="M58" s="3">
-        <v>-142.27</v>
+        <v>-172.14</v>
       </c>
       <c r="N58" s="3">
-        <v>-193.73</v>
+        <v>-181.33</v>
       </c>
       <c r="O58" s="3">
-        <v>-355.41</v>
+        <v>-157.54</v>
       </c>
       <c r="P58" s="3">
-        <v>-222.35</v>
+        <v>-42.75</v>
       </c>
       <c r="Q58" s="3">
-        <v>650.94</v>
+        <v>210.77</v>
       </c>
       <c r="R58" s="3">
-        <v>1081.75</v>
+        <v>392.82</v>
       </c>
       <c r="S58" s="3">
-        <v>41.66</v>
+        <v>35.09</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -4006,58 +4006,58 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D59" s="1">
-        <v>15471.55</v>
+        <v>27994.55</v>
       </c>
       <c r="E59" s="2">
-        <v>-1.18</v>
+        <v>-0.77</v>
       </c>
       <c r="F59" s="2">
-        <v>-2.22</v>
+        <v>-3.77</v>
       </c>
       <c r="G59" s="2">
-        <v>-1.77</v>
+        <v>-5.16</v>
       </c>
       <c r="H59" s="2">
-        <v>-6.15</v>
+        <v>-10.12</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>16025.26</v>
+        <v>30385.86</v>
       </c>
       <c r="K59" s="1">
-        <v>15688.51</v>
+        <v>28874.88</v>
       </c>
       <c r="L59" s="1">
-        <v>16250.98</v>
+        <v>30272.63</v>
       </c>
       <c r="M59" s="3">
-        <v>-172.83</v>
+        <v>-496.07</v>
       </c>
       <c r="N59" s="3">
-        <v>-184.14</v>
+        <v>-396.55</v>
       </c>
       <c r="O59" s="3">
-        <v>-74.4</v>
+        <v>-375.6</v>
       </c>
       <c r="P59" s="3">
-        <v>61.76</v>
+        <v>-93.58</v>
       </c>
       <c r="Q59" s="3">
-        <v>918.79</v>
+        <v>1416.82</v>
       </c>
       <c r="R59" s="3">
-        <v>1148.44</v>
+        <v>1993.08</v>
       </c>
       <c r="S59" s="3">
-        <v>35.1</v>
+        <v>27.89</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -4068,58 +4068,58 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C60" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D60" s="1">
-        <v>805.85</v>
+        <v>24289.25</v>
       </c>
       <c r="E60" s="2">
-        <v>-1.25</v>
+        <v>-0.8</v>
       </c>
       <c r="F60" s="2">
-        <v>-2.43</v>
+        <v>-3.63</v>
       </c>
       <c r="G60" s="2">
-        <v>-4.9</v>
+        <v>-4.35</v>
       </c>
       <c r="H60" s="2">
-        <v>-8.21</v>
+        <v>-2.79</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>822.56</v>
+        <v>25473.04</v>
       </c>
       <c r="K60" s="1">
-        <v>820.8</v>
+        <v>24995.85</v>
       </c>
       <c r="L60" s="1">
-        <v>865.65</v>
+        <v>26172.53</v>
       </c>
       <c r="M60" s="3">
-        <v>-14.16</v>
+        <v>-401.97</v>
       </c>
       <c r="N60" s="3">
-        <v>-14.47</v>
+        <v>-333.75</v>
       </c>
       <c r="O60" s="3">
-        <v>0.08</v>
+        <v>-62.14</v>
       </c>
       <c r="P60" s="3">
-        <v>10.56</v>
+        <v>214.66</v>
       </c>
       <c r="Q60" s="3">
-        <v>1.73</v>
+        <v>51.49</v>
       </c>
       <c r="R60" s="3">
-        <v>9.92</v>
+        <v>-58.15</v>
       </c>
       <c r="S60" s="3">
-        <v>38.18</v>
+        <v>30.08</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -4130,58 +4130,58 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D61" s="1">
-        <v>1622.65</v>
+        <v>21028.65</v>
       </c>
       <c r="E61" s="2">
-        <v>-1.29</v>
+        <v>-0.81</v>
       </c>
       <c r="F61" s="2">
-        <v>-1.55</v>
+        <v>-3.26</v>
       </c>
       <c r="G61" s="2">
-        <v>2.49</v>
+        <v>-3.84</v>
       </c>
       <c r="H61" s="2">
-        <v>12.32</v>
+        <v>-5.6</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>1468.1</v>
+        <v>22185.05</v>
       </c>
       <c r="K61" s="1">
-        <v>1614.12</v>
+        <v>21532.07</v>
       </c>
       <c r="L61" s="1">
-        <v>1573.42</v>
+        <v>22632.09</v>
       </c>
       <c r="M61" s="3">
-        <v>21.39</v>
+        <v>-365.06</v>
       </c>
       <c r="N61" s="3">
-        <v>13.97</v>
+        <v>-336.93</v>
       </c>
       <c r="O61" s="3">
-        <v>35.72</v>
+        <v>-118</v>
       </c>
       <c r="P61" s="3">
-        <v>32.25</v>
+        <v>155.21</v>
       </c>
       <c r="Q61" s="3">
-        <v>-70.23</v>
+        <v>1689.03</v>
       </c>
       <c r="R61" s="3">
-        <v>-104.94</v>
+        <v>2024.42</v>
       </c>
       <c r="S61" s="3">
-        <v>56.97</v>
+        <v>27.99</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4192,58 +4192,58 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C62" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D62" s="1">
-        <v>35474.75</v>
+        <v>26950.65</v>
       </c>
       <c r="E62" s="2">
-        <v>-1.39</v>
+        <v>-0.83</v>
       </c>
       <c r="F62" s="2">
-        <v>-1.98</v>
+        <v>-4.98</v>
       </c>
       <c r="G62" s="2">
-        <v>-3.17</v>
-      </c>
-      <c r="H62" s="2">
-        <v>0.42</v>
+        <v>-4.98</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
-      <c r="J62" s="1">
-        <v>37725</v>
+      <c r="J62" t="str">
+        <v/>
       </c>
       <c r="K62" s="1">
-        <v>36101.72</v>
+        <v>27885.71</v>
       </c>
       <c r="L62" s="1">
-        <v>37485.67</v>
+        <v>29325.74</v>
       </c>
       <c r="M62" s="3">
-        <v>-493.27</v>
+        <v>-485.79</v>
       </c>
       <c r="N62" s="3">
-        <v>-476.06</v>
+        <v>-417.2</v>
       </c>
       <c r="O62" s="3">
-        <v>-516.35</v>
+        <v>-206.91</v>
       </c>
       <c r="P62" s="3">
-        <v>-72.31</v>
+        <v>168.33</v>
       </c>
       <c r="Q62" s="3">
-        <v>966.04</v>
+        <v>205.94</v>
       </c>
       <c r="R62" s="3">
-        <v>1234.53</v>
+        <v>182.47</v>
       </c>
       <c r="S62" s="3">
-        <v>32.16</v>
+        <v>29.3</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4254,58 +4254,58 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C63" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D63" s="1">
-        <v>21200.25</v>
+        <v>15302.2</v>
       </c>
       <c r="E63" s="2">
-        <v>-1.39</v>
+        <v>-0.84</v>
       </c>
       <c r="F63" s="2">
-        <v>-2.47</v>
+        <v>-3.07</v>
       </c>
       <c r="G63" s="2">
-        <v>-3.05</v>
+        <v>-4.46</v>
       </c>
       <c r="H63" s="2">
-        <v>-4.83</v>
+        <v>-4.21</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>22190.22</v>
+        <v>16008.69</v>
       </c>
       <c r="K63" s="1">
-        <v>21643.94</v>
+        <v>15627.1</v>
       </c>
       <c r="L63" s="1">
-        <v>22680.93</v>
+        <v>16423.41</v>
       </c>
       <c r="M63" s="3">
-        <v>-336.91</v>
+        <v>-261.16</v>
       </c>
       <c r="N63" s="3">
-        <v>-329.9</v>
+        <v>-246.24</v>
       </c>
       <c r="O63" s="3">
-        <v>-104.32</v>
+        <v>-52.45</v>
       </c>
       <c r="P63" s="3">
-        <v>157.95</v>
+        <v>134.97</v>
       </c>
       <c r="Q63" s="3">
-        <v>1702.72</v>
+        <v>350.85</v>
       </c>
       <c r="R63" s="3">
-        <v>2027.16</v>
+        <v>327.06</v>
       </c>
       <c r="S63" s="3">
-        <v>30.21</v>
+        <v>30.31</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4316,58 +4316,58 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C64" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D64" s="1">
-        <v>13367.85</v>
+        <v>10445.65</v>
       </c>
       <c r="E64" s="2">
-        <v>-1.45</v>
+        <v>-0.86</v>
       </c>
       <c r="F64" s="2">
-        <v>-2.55</v>
+        <v>-1.05</v>
       </c>
       <c r="G64" s="2">
-        <v>-2.65</v>
+        <v>-1.59</v>
       </c>
       <c r="H64" s="2">
-        <v>-2.97</v>
+        <v>-14.6</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>14001.99</v>
+        <v>11300.75</v>
       </c>
       <c r="K64" s="1">
-        <v>13643.37</v>
+        <v>10508.99</v>
       </c>
       <c r="L64" s="1">
-        <v>14377.8</v>
+        <v>10888.56</v>
       </c>
       <c r="M64" s="3">
-        <v>-231.56</v>
+        <v>-118.1</v>
       </c>
       <c r="N64" s="3">
-        <v>-238.81</v>
+        <v>-137.62</v>
       </c>
       <c r="O64" s="3">
-        <v>-68.88</v>
+        <v>-225.23</v>
       </c>
       <c r="P64" s="3">
-        <v>127.5</v>
+        <v>-160.25</v>
       </c>
       <c r="Q64" s="3">
-        <v>871.49</v>
+        <v>73.22</v>
       </c>
       <c r="R64" s="3">
-        <v>1000.98</v>
+        <v>279.44</v>
       </c>
       <c r="S64" s="3">
-        <v>31.65</v>
+        <v>39.39</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4378,58 +4378,58 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C65" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D65" s="1">
-        <v>15431.05</v>
+        <v>57063.95</v>
       </c>
       <c r="E65" s="2">
-        <v>-1.46</v>
+        <v>-0.87</v>
       </c>
       <c r="F65" s="2">
-        <v>-2.25</v>
+        <v>-3.49</v>
       </c>
       <c r="G65" s="2">
-        <v>-3.66</v>
+        <v>-3.82</v>
       </c>
       <c r="H65" s="2">
-        <v>-3.41</v>
+        <v>-5.66</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>16011</v>
+        <v>60318.63</v>
       </c>
       <c r="K65" s="1">
-        <v>15699.31</v>
+        <v>58531.39</v>
       </c>
       <c r="L65" s="1">
-        <v>16459.18</v>
+        <v>61577.64</v>
       </c>
       <c r="M65" s="3">
-        <v>-244.73</v>
+        <v>-1005.14</v>
       </c>
       <c r="N65" s="3">
-        <v>-242.51</v>
+        <v>-923.66</v>
       </c>
       <c r="O65" s="3">
-        <v>-42.17</v>
+        <v>-338.45</v>
       </c>
       <c r="P65" s="3">
-        <v>137.03</v>
+        <v>416.39</v>
       </c>
       <c r="Q65" s="3">
-        <v>361.13</v>
+        <v>2828.77</v>
       </c>
       <c r="R65" s="3">
-        <v>329.12</v>
+        <v>3471.67</v>
       </c>
       <c r="S65" s="3">
-        <v>32.7</v>
+        <v>28.36</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4440,58 +4440,58 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C66" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D66" s="1">
-        <v>67655.3</v>
+        <v>5359.5</v>
       </c>
       <c r="E66" s="2">
-        <v>-1.51</v>
+        <v>-0.88</v>
       </c>
       <c r="F66" s="2">
-        <v>-1.93</v>
+        <v>-2.06</v>
       </c>
       <c r="G66" s="2">
-        <v>-3</v>
+        <v>0.74</v>
       </c>
       <c r="H66" s="2">
-        <v>-2.46</v>
+        <v>-8.54</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>70043</v>
+        <v>5548.68</v>
       </c>
       <c r="K66" s="1">
-        <v>68730.8</v>
+        <v>5377.93</v>
       </c>
       <c r="L66" s="1">
-        <v>71815.76</v>
+        <v>5521.35</v>
       </c>
       <c r="M66" s="3">
-        <v>-981.34</v>
+        <v>-27.83</v>
       </c>
       <c r="N66" s="3">
-        <v>-987.31</v>
+        <v>-49.45</v>
       </c>
       <c r="O66" s="3">
-        <v>-198.3</v>
+        <v>-46.07</v>
       </c>
       <c r="P66" s="3">
-        <v>578.75</v>
+        <v>-17.59</v>
       </c>
       <c r="Q66" s="3">
-        <v>2663.93</v>
+        <v>187.05</v>
       </c>
       <c r="R66" s="3">
-        <v>3182.41</v>
+        <v>261.07</v>
       </c>
       <c r="S66" s="3">
-        <v>34.16</v>
+        <v>45.73</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4502,58 +4502,58 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D67" s="1">
-        <v>25196.65</v>
+        <v>19526.1</v>
       </c>
       <c r="E67" s="2">
-        <v>-1.54</v>
+        <v>-0.91</v>
       </c>
       <c r="F67" s="2">
-        <v>-2.22</v>
+        <v>-3.67</v>
       </c>
       <c r="G67" s="2">
-        <v>-4.17</v>
+        <v>-4.35</v>
       </c>
       <c r="H67" s="2">
-        <v>-10.62</v>
+        <v>-3.42</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>26942.83</v>
+        <v>20265.32</v>
       </c>
       <c r="K67" s="1">
-        <v>25456.41</v>
+        <v>20067.01</v>
       </c>
       <c r="L67" s="1">
-        <v>27352.71</v>
+        <v>20992.81</v>
       </c>
       <c r="M67" s="3">
-        <v>-546.48</v>
+        <v>-318.95</v>
       </c>
       <c r="N67" s="3">
-        <v>-630.31</v>
+        <v>-271.58</v>
       </c>
       <c r="O67" s="3">
-        <v>-282.28</v>
+        <v>5.54</v>
       </c>
       <c r="P67" s="3">
-        <v>96.45</v>
+        <v>246.97</v>
       </c>
       <c r="Q67" s="3">
-        <v>1475.87</v>
+        <v>1558.91</v>
       </c>
       <c r="R67" s="3">
-        <v>1810.68</v>
+        <v>1819.52</v>
       </c>
       <c r="S67" s="3">
-        <v>37.51</v>
+        <v>27.36</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4564,58 +4564,58 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D68" s="1">
-        <v>14841.8</v>
+        <v>58001.55</v>
       </c>
       <c r="E68" s="2">
-        <v>-1.57</v>
+        <v>-0.93</v>
       </c>
       <c r="F68" s="2">
-        <v>-2.19</v>
+        <v>-3.76</v>
       </c>
       <c r="G68" s="2">
-        <v>-3.96</v>
+        <v>-4.56</v>
       </c>
       <c r="H68" s="2">
-        <v>-3.7</v>
+        <v>-6.32</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>15632.23</v>
+        <v>61728.51</v>
       </c>
       <c r="K68" s="1">
-        <v>15107.46</v>
+        <v>59806.81</v>
       </c>
       <c r="L68" s="1">
-        <v>15927.77</v>
+        <v>62611.84</v>
       </c>
       <c r="M68" s="3">
-        <v>-264.42</v>
+        <v>-992.06</v>
       </c>
       <c r="N68" s="3">
-        <v>-263.97</v>
+        <v>-790.76</v>
       </c>
       <c r="O68" s="3">
-        <v>-93.27</v>
+        <v>-414.08</v>
       </c>
       <c r="P68" s="3">
-        <v>101.61</v>
+        <v>207.64</v>
       </c>
       <c r="Q68" s="3">
-        <v>1246.98</v>
+        <v>-153.8</v>
       </c>
       <c r="R68" s="3">
-        <v>1443.88</v>
+        <v>-203.69</v>
       </c>
       <c r="S68" s="3">
-        <v>31.77</v>
+        <v>26.84</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4626,58 +4626,58 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C69" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D69" s="1">
-        <v>57565.85</v>
+        <v>5931.85</v>
       </c>
       <c r="E69" s="2">
-        <v>-1.58</v>
+        <v>-0.93</v>
       </c>
       <c r="F69" s="2">
-        <v>-2.64</v>
+        <v>-2.2</v>
       </c>
       <c r="G69" s="2">
-        <v>-2.98</v>
+        <v>-4.77</v>
       </c>
       <c r="H69" s="2">
-        <v>-4.83</v>
+        <v>-6.81</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>60332.89</v>
+        <v>6745.2</v>
       </c>
       <c r="K69" s="1">
-        <v>58857.49</v>
+        <v>6040.35</v>
       </c>
       <c r="L69" s="1">
-        <v>61713.48</v>
+        <v>6303.72</v>
       </c>
       <c r="M69" s="3">
-        <v>-919.26</v>
+        <v>-98.85</v>
       </c>
       <c r="N69" s="3">
-        <v>-903.29</v>
+        <v>-93.21</v>
       </c>
       <c r="O69" s="3">
-        <v>-298.42</v>
+        <v>-205.27</v>
       </c>
       <c r="P69" s="3">
-        <v>424.39</v>
+        <v>-147.47</v>
       </c>
       <c r="Q69" s="3">
-        <v>2868.81</v>
+        <v>227.37</v>
       </c>
       <c r="R69" s="3">
-        <v>3479.68</v>
+        <v>402.62</v>
       </c>
       <c r="S69" s="3">
-        <v>30.65</v>
+        <v>29.08</v>
       </c>
       <c r="T69" t="str">
         <v/>
@@ -4688,58 +4688,58 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D70" s="1">
-        <v>16500.2</v>
+        <v>47831.05</v>
       </c>
       <c r="E70" s="2">
-        <v>-1.6</v>
+        <v>-0.94</v>
       </c>
       <c r="F70" s="2">
-        <v>-2.63</v>
+        <v>-3.58</v>
       </c>
       <c r="G70" s="2">
-        <v>-3.1</v>
+        <v>-3.52</v>
       </c>
       <c r="H70" s="2">
-        <v>-4.37</v>
+        <v>0.56</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>17228.37</v>
+        <v>49081.09</v>
       </c>
       <c r="K70" s="1">
-        <v>16857.35</v>
+        <v>49114.54</v>
       </c>
       <c r="L70" s="1">
-        <v>17717.7</v>
+        <v>50872.21</v>
       </c>
       <c r="M70" s="3">
-        <v>-279.9</v>
+        <v>-592.98</v>
       </c>
       <c r="N70" s="3">
-        <v>-278.57</v>
+        <v>-474.16</v>
       </c>
       <c r="O70" s="3">
-        <v>-55.2</v>
+        <v>80.16</v>
       </c>
       <c r="P70" s="3">
-        <v>160.54</v>
+        <v>552.91</v>
       </c>
       <c r="Q70" s="3">
-        <v>894.59</v>
+        <v>24.86</v>
       </c>
       <c r="R70" s="3">
-        <v>1047.16</v>
+        <v>-306.19</v>
       </c>
       <c r="S70" s="3">
-        <v>30.35</v>
+        <v>29.88</v>
       </c>
       <c r="T70" t="str">
         <v/>
@@ -4750,58 +4750,58 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C71" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D71" s="1">
-        <v>7371.15</v>
+        <v>15438.55</v>
       </c>
       <c r="E71" s="2">
-        <v>-1.69</v>
+        <v>-0.95</v>
       </c>
       <c r="F71" s="2">
-        <v>-2.56</v>
+        <v>-3.93</v>
       </c>
       <c r="G71" s="2">
-        <v>-4.33</v>
+        <v>-5.22</v>
       </c>
       <c r="H71" s="2">
-        <v>-14.33</v>
+        <v>-3.54</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>7691.3</v>
+        <v>16130.91</v>
       </c>
       <c r="K71" s="1">
-        <v>7503.05</v>
+        <v>15935.27</v>
       </c>
       <c r="L71" s="1">
-        <v>7781.41</v>
+        <v>16823.14</v>
       </c>
       <c r="M71" s="3">
-        <v>-92.92</v>
+        <v>-300.25</v>
       </c>
       <c r="N71" s="3">
-        <v>-87.71</v>
+        <v>-253.59</v>
       </c>
       <c r="O71" s="3">
-        <v>-66.71</v>
+        <v>9.43</v>
       </c>
       <c r="P71" s="3">
-        <v>-18.62</v>
+        <v>227.7</v>
       </c>
       <c r="Q71" s="3">
-        <v>-304.51</v>
+        <v>1531.81</v>
       </c>
       <c r="R71" s="3">
-        <v>-248.08</v>
+        <v>1744.69</v>
       </c>
       <c r="S71" s="3">
-        <v>37.1</v>
+        <v>29.25</v>
       </c>
       <c r="T71" t="str">
         <v/>
@@ -4812,58 +4812,58 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D72" s="1">
-        <v>19705.05</v>
+        <v>34837.65</v>
       </c>
       <c r="E72" s="2">
-        <v>-1.7</v>
+        <v>-0.96</v>
       </c>
       <c r="F72" s="2">
-        <v>-2.79</v>
+        <v>-3.89</v>
       </c>
       <c r="G72" s="2">
-        <v>-3.48</v>
+        <v>-4.89</v>
       </c>
       <c r="H72" s="2">
-        <v>-2.53</v>
+        <v>-5.22</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>20267.74</v>
+        <v>37113.6</v>
       </c>
       <c r="K72" s="1">
-        <v>20187.22</v>
+        <v>35897.54</v>
       </c>
       <c r="L72" s="1">
-        <v>21034.43</v>
+        <v>38399.48</v>
       </c>
       <c r="M72" s="3">
-        <v>-283.44</v>
+        <v>-806.39</v>
       </c>
       <c r="N72" s="3">
-        <v>-259.74</v>
+        <v>-752.95</v>
       </c>
       <c r="O72" s="3">
-        <v>19.81</v>
+        <v>-223.01</v>
       </c>
       <c r="P72" s="3">
-        <v>249.83</v>
+        <v>310.12</v>
       </c>
       <c r="Q72" s="3">
-        <v>1573.19</v>
+        <v>605.97</v>
       </c>
       <c r="R72" s="3">
-        <v>1822.38</v>
+        <v>933.36</v>
       </c>
       <c r="S72" s="3">
-        <v>29.74</v>
+        <v>27.4</v>
       </c>
       <c r="T72" t="str">
         <v/>
@@ -4874,58 +4874,58 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C73" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D73" s="1">
-        <v>11859.55</v>
+        <v>50373.65</v>
       </c>
       <c r="E73" s="2">
-        <v>-1.71</v>
+        <v>-0.97</v>
       </c>
       <c r="F73" s="2">
-        <v>-2.26</v>
+        <v>-3.7</v>
       </c>
       <c r="G73" s="2">
-        <v>-7.06</v>
+        <v>-4.77</v>
       </c>
       <c r="H73" s="2">
-        <v>6.2</v>
+        <v>-4.43</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>12478.21</v>
+        <v>52542.32</v>
       </c>
       <c r="K73" s="1">
-        <v>12113.93</v>
+        <v>52018.72</v>
       </c>
       <c r="L73" s="1">
-        <v>12865.76</v>
+        <v>54100.37</v>
       </c>
       <c r="M73" s="3">
-        <v>-278.11</v>
+        <v>-755.32</v>
       </c>
       <c r="N73" s="3">
-        <v>-246.99</v>
+        <v>-538.85</v>
       </c>
       <c r="O73" s="3">
-        <v>15.41</v>
+        <v>-22.78</v>
       </c>
       <c r="P73" s="3">
-        <v>208.97</v>
+        <v>433.84</v>
       </c>
       <c r="Q73" s="3">
-        <v>1137.8</v>
+        <v>-805.93</v>
       </c>
       <c r="R73" s="3">
-        <v>1130.25</v>
+        <v>-1132.88</v>
       </c>
       <c r="S73" s="3">
-        <v>33.96</v>
+        <v>29.26</v>
       </c>
       <c r="T73" t="str">
         <v/>
@@ -4936,58 +4936,58 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D74" s="1">
-        <v>15586</v>
+        <v>9214.6</v>
       </c>
       <c r="E74" s="2">
-        <v>-1.76</v>
+        <v>-0.97</v>
       </c>
       <c r="F74" s="2">
-        <v>-3.01</v>
+        <v>-3.85</v>
       </c>
       <c r="G74" s="2">
-        <v>-4.31</v>
+        <v>-4.34</v>
       </c>
       <c r="H74" s="2">
-        <v>-2.61</v>
+        <v>7.07</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
       <c r="J74" s="1">
-        <v>16132.86</v>
+        <v>8981.26</v>
       </c>
       <c r="K74" s="1">
-        <v>16045.65</v>
+        <v>9499.57</v>
       </c>
       <c r="L74" s="1">
-        <v>16859.82</v>
+        <v>9809.92</v>
       </c>
       <c r="M74" s="3">
-        <v>-268.03</v>
+        <v>-113.99</v>
       </c>
       <c r="N74" s="3">
-        <v>-241.93</v>
+        <v>-77.6</v>
       </c>
       <c r="O74" s="3">
-        <v>21.19</v>
+        <v>194.84</v>
       </c>
       <c r="P74" s="3">
-        <v>230.05</v>
+        <v>293.49</v>
       </c>
       <c r="Q74" s="3">
-        <v>1543.57</v>
+        <v>725.43</v>
       </c>
       <c r="R74" s="3">
-        <v>1747.05</v>
+        <v>716.72</v>
       </c>
       <c r="S74" s="3">
-        <v>31.3</v>
+        <v>30.93</v>
       </c>
       <c r="T74" t="str">
         <v/>
@@ -4998,58 +4998,58 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C75" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D75" s="1">
-        <v>35175.15</v>
+        <v>24393.05</v>
       </c>
       <c r="E75" s="2">
-        <v>-1.86</v>
+        <v>-1.03</v>
       </c>
       <c r="F75" s="2">
-        <v>-2.96</v>
+        <v>-5.22</v>
       </c>
       <c r="G75" s="2">
-        <v>-3.97</v>
+        <v>-7.07</v>
       </c>
       <c r="H75" s="2">
-        <v>-4.3</v>
+        <v>8.19</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>37120.37</v>
+        <v>23618.34</v>
       </c>
       <c r="K75" s="1">
-        <v>36133.07</v>
+        <v>25330.09</v>
       </c>
       <c r="L75" s="1">
-        <v>38507.54</v>
+        <v>26118.21</v>
       </c>
       <c r="M75" s="3">
-        <v>-749.75</v>
+        <v>-328.46</v>
       </c>
       <c r="N75" s="3">
-        <v>-739.59</v>
+        <v>-173.89</v>
       </c>
       <c r="O75" s="3">
-        <v>-196.08</v>
+        <v>610.99</v>
       </c>
       <c r="P75" s="3">
-        <v>315.51</v>
+        <v>857.18</v>
       </c>
       <c r="Q75" s="3">
-        <v>632.89</v>
+        <v>2290.53</v>
       </c>
       <c r="R75" s="3">
-        <v>938.74</v>
+        <v>2350.8</v>
       </c>
       <c r="S75" s="3">
-        <v>29.43</v>
+        <v>30.06</v>
       </c>
       <c r="T75" t="str">
         <v/>
@@ -5060,58 +5060,58 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D76" s="1">
-        <v>48284.2</v>
+        <v>8509.65</v>
       </c>
       <c r="E76" s="2">
-        <v>-1.89</v>
+        <v>-1.04</v>
       </c>
       <c r="F76" s="2">
-        <v>-2.67</v>
+        <v>-1.85</v>
       </c>
       <c r="G76" s="2">
-        <v>-2.6</v>
+        <v>6.02</v>
       </c>
       <c r="H76" s="2">
-        <v>1.51</v>
+        <v>-9.69</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>49077.35</v>
+        <v>8256.91</v>
       </c>
       <c r="K76" s="1">
-        <v>49399.75</v>
+        <v>8442.38</v>
       </c>
       <c r="L76" s="1">
-        <v>50957</v>
+        <v>8535.19</v>
       </c>
       <c r="M76" s="3">
-        <v>-497.9</v>
+        <v>21.33</v>
       </c>
       <c r="N76" s="3">
-        <v>-444.45</v>
+        <v>-39.36</v>
       </c>
       <c r="O76" s="3">
-        <v>116.31</v>
+        <v>65.45</v>
       </c>
       <c r="P76" s="3">
-        <v>560.14</v>
+        <v>59.13</v>
       </c>
       <c r="Q76" s="3">
-        <v>61.01</v>
+        <v>371.93</v>
       </c>
       <c r="R76" s="3">
-        <v>-298.96</v>
+        <v>513.63</v>
       </c>
       <c r="S76" s="3">
-        <v>32.6</v>
+        <v>55.1</v>
       </c>
       <c r="T76" t="str">
         <v/>
@@ -5122,58 +5122,58 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C77" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D77" s="1">
-        <v>58544.5</v>
+        <v>35101.45</v>
       </c>
       <c r="E77" s="2">
-        <v>-2.06</v>
+        <v>-1.05</v>
       </c>
       <c r="F77" s="2">
-        <v>-2.86</v>
+        <v>-3.01</v>
       </c>
       <c r="G77" s="2">
-        <v>-3.67</v>
+        <v>-4.19</v>
       </c>
       <c r="H77" s="2">
-        <v>-5.44</v>
+        <v>-0.63</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>61745.17</v>
+        <v>37726.44</v>
       </c>
       <c r="K77" s="1">
-        <v>60207.98</v>
+        <v>35919.86</v>
       </c>
       <c r="L77" s="1">
-        <v>62735.23</v>
+        <v>37412.73</v>
       </c>
       <c r="M77" s="3">
-        <v>-867.64</v>
+        <v>-542.58</v>
       </c>
       <c r="N77" s="3">
-        <v>-740.43</v>
+        <v>-489.36</v>
       </c>
       <c r="O77" s="3">
-        <v>-370.77</v>
+        <v>-546.12</v>
       </c>
       <c r="P77" s="3">
-        <v>216.3</v>
+        <v>-78.27</v>
       </c>
       <c r="Q77" s="3">
-        <v>-110.49</v>
+        <v>936.27</v>
       </c>
       <c r="R77" s="3">
-        <v>-195.03</v>
+        <v>1228.57</v>
       </c>
       <c r="S77" s="3">
-        <v>29.06</v>
+        <v>29.01</v>
       </c>
       <c r="T77" t="str">
         <v/>
@@ -5184,58 +5184,58 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>CNXMNC</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C78" t="str">
-        <v>CNXMNC</v>
+        <v>CNXIT</v>
       </c>
       <c r="D78" s="1">
-        <v>28626.65</v>
+        <v>32081.25</v>
       </c>
       <c r="E78" s="2">
-        <v>-2.1</v>
+        <v>-1.05</v>
       </c>
       <c r="F78" s="2">
-        <v>-3.01</v>
+        <v>0.49</v>
       </c>
       <c r="G78" s="2">
-        <v>-5.63</v>
+        <v>15.8</v>
       </c>
       <c r="H78" s="2">
-        <v>-6.35</v>
+        <v>-15.32</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>31410.71</v>
+        <v>30844.5</v>
       </c>
       <c r="K78" s="1">
-        <v>29553.58</v>
+        <v>30738.62</v>
       </c>
       <c r="L78" s="1">
-        <v>31651.86</v>
+        <v>29836.1</v>
       </c>
       <c r="M78" s="3">
-        <v>-696.88</v>
+        <v>680.59</v>
       </c>
       <c r="N78" s="3">
-        <v>-642.67</v>
+        <v>172.04</v>
       </c>
       <c r="O78" s="3">
-        <v>-453.52</v>
+        <v>-150</v>
       </c>
       <c r="P78" s="3">
-        <v>75.08</v>
+        <v>-518.18</v>
       </c>
       <c r="Q78" s="3">
-        <v>1989.94</v>
+        <v>-1654.18</v>
       </c>
       <c r="R78" s="3">
-        <v>2397.89</v>
+        <v>-1146.38</v>
       </c>
       <c r="S78" s="3">
-        <v>24.47</v>
+        <v>69.01</v>
       </c>
       <c r="T78" t="str">
         <v/>
@@ -5246,58 +5246,58 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C79" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D79" s="1">
-        <v>24485.75</v>
+        <v>28319.6</v>
       </c>
       <c r="E79" s="2">
-        <v>-2.24</v>
+        <v>-1.07</v>
       </c>
       <c r="F79" s="2">
-        <v>-2.85</v>
+        <v>-4.05</v>
       </c>
       <c r="G79" s="2">
-        <v>-3.58</v>
+        <v>-6.65</v>
       </c>
       <c r="H79" s="2">
-        <v>-2</v>
+        <v>-7.36</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>25474.99</v>
+        <v>31400.6</v>
       </c>
       <c r="K79" s="1">
-        <v>25152.88</v>
+        <v>29329.22</v>
       </c>
       <c r="L79" s="1">
-        <v>26223.82</v>
+        <v>31540.74</v>
       </c>
       <c r="M79" s="3">
-        <v>-354.45</v>
+        <v>-752.85</v>
       </c>
       <c r="N79" s="3">
-        <v>-316.69</v>
+        <v>-664.7</v>
       </c>
       <c r="O79" s="3">
-        <v>-46.46</v>
+        <v>-478.01</v>
       </c>
       <c r="P79" s="3">
-        <v>217.8</v>
+        <v>70.18</v>
       </c>
       <c r="Q79" s="3">
-        <v>67.16</v>
+        <v>1965.44</v>
       </c>
       <c r="R79" s="3">
-        <v>-55.02</v>
+        <v>2392.99</v>
       </c>
       <c r="S79" s="3">
-        <v>32.01</v>
+        <v>22.49</v>
       </c>
       <c r="T79" t="str">
         <v/>
@@ -5308,58 +5308,58 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D80" s="1">
-        <v>46250.45</v>
+        <v>18949.55</v>
       </c>
       <c r="E80" s="2">
-        <v>-2.26</v>
+        <v>-1.08</v>
       </c>
       <c r="F80" s="2">
-        <v>-3</v>
+        <v>-2.68</v>
       </c>
       <c r="G80" s="2">
-        <v>-3.36</v>
+        <v>0.03</v>
       </c>
       <c r="H80" s="2">
-        <v>5.15</v>
+        <v>-11.5</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>44916.55</v>
+        <v>20100.19</v>
       </c>
       <c r="K80" s="1">
-        <v>47447.54</v>
+        <v>19149.06</v>
       </c>
       <c r="L80" s="1">
-        <v>48412.97</v>
+        <v>19815.19</v>
       </c>
       <c r="M80" s="3">
-        <v>-346.62</v>
+        <v>-157.55</v>
       </c>
       <c r="N80" s="3">
-        <v>-239.01</v>
+        <v>-216.97</v>
       </c>
       <c r="O80" s="3">
-        <v>797.36</v>
+        <v>-281.72</v>
       </c>
       <c r="P80" s="3">
-        <v>1130.14</v>
+        <v>-142.1</v>
       </c>
       <c r="Q80" s="3">
-        <v>-311.48</v>
+        <v>484.31</v>
       </c>
       <c r="R80" s="3">
-        <v>-1014.14</v>
+        <v>794.91</v>
       </c>
       <c r="S80" s="3">
-        <v>34.57</v>
+        <v>40.79</v>
       </c>
       <c r="T80" t="str">
         <v/>
@@ -5376,52 +5376,52 @@
         <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D81" s="1">
-        <v>17041.95</v>
+        <v>16856.2</v>
       </c>
       <c r="E81" s="2">
-        <v>-2.26</v>
+        <v>-1.09</v>
       </c>
       <c r="F81" s="2">
-        <v>-3.38</v>
+        <v>-4.43</v>
       </c>
       <c r="G81" s="2">
-        <v>-4.25</v>
+        <v>-5.3</v>
       </c>
       <c r="H81" s="2">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>16948.75</v>
+        <v>16950.58</v>
       </c>
       <c r="K81" s="1">
-        <v>17569.8</v>
+        <v>17440.06</v>
       </c>
       <c r="L81" s="1">
-        <v>18112.58</v>
+        <v>18082.79</v>
       </c>
       <c r="M81" s="3">
-        <v>-196.63</v>
+        <v>-242.28</v>
       </c>
       <c r="N81" s="3">
-        <v>-148.54</v>
+        <v>-167.29</v>
       </c>
       <c r="O81" s="3">
-        <v>206.68</v>
+        <v>191.86</v>
       </c>
       <c r="P81" s="3">
-        <v>383.2</v>
+        <v>380.24</v>
       </c>
       <c r="Q81" s="3">
-        <v>1307.86</v>
+        <v>1293.05</v>
       </c>
       <c r="R81" s="3">
-        <v>1428.81</v>
+        <v>1425.85</v>
       </c>
       <c r="S81" s="3">
-        <v>29.72</v>
+        <v>27.09</v>
       </c>
       <c r="T81" t="str">
         <v/>
@@ -5432,58 +5432,58 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C82" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D82" s="1">
-        <v>5072.6</v>
+        <v>22202</v>
       </c>
       <c r="E82" s="2">
-        <v>-2.28</v>
+        <v>-1.1</v>
       </c>
       <c r="F82" s="2">
-        <v>-3.23</v>
+        <v>-3.33</v>
       </c>
       <c r="G82" s="2">
-        <v>-0.34</v>
+        <v>-2.48</v>
       </c>
       <c r="H82" s="2">
-        <v>8.94</v>
+        <v>-7.71</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>5103.01</v>
+        <v>23493.56</v>
       </c>
       <c r="K82" s="1">
-        <v>5200.83</v>
+        <v>22710.04</v>
       </c>
       <c r="L82" s="1">
-        <v>5307.19</v>
+        <v>23729.33</v>
       </c>
       <c r="M82" s="3">
-        <v>-31.37</v>
+        <v>-308.33</v>
       </c>
       <c r="N82" s="3">
-        <v>-30.41</v>
+        <v>-298.64</v>
       </c>
       <c r="O82" s="3">
-        <v>28.71</v>
+        <v>-218.72</v>
       </c>
       <c r="P82" s="3">
-        <v>86.76</v>
+        <v>28.36</v>
       </c>
       <c r="Q82" s="3">
-        <v>365.15</v>
+        <v>1001.39</v>
       </c>
       <c r="R82" s="3">
-        <v>325.49</v>
+        <v>1355.11</v>
       </c>
       <c r="S82" s="3">
-        <v>39.53</v>
+        <v>31.39</v>
       </c>
       <c r="T82" t="str">
         <v/>
@@ -5494,58 +5494,58 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C83" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D83" s="1">
-        <v>9304.7</v>
+        <v>15936.7</v>
       </c>
       <c r="E83" s="2">
-        <v>-2.32</v>
+        <v>-1.1</v>
       </c>
       <c r="F83" s="2">
-        <v>-2.91</v>
+        <v>-4.03</v>
       </c>
       <c r="G83" s="2">
-        <v>-3.41</v>
+        <v>0.16</v>
       </c>
       <c r="H83" s="2">
-        <v>8.12</v>
+        <v>-27.55</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>8977.76</v>
+        <v>18399.76</v>
       </c>
       <c r="K83" s="1">
-        <v>9562.89</v>
+        <v>16089.3</v>
       </c>
       <c r="L83" s="1">
-        <v>9824.13</v>
+        <v>17140.45</v>
       </c>
       <c r="M83" s="3">
-        <v>-91.43</v>
+        <v>-273.96</v>
       </c>
       <c r="N83" s="3">
-        <v>-68.5</v>
+        <v>-371.79</v>
       </c>
       <c r="O83" s="3">
-        <v>202.03</v>
+        <v>-682</v>
       </c>
       <c r="P83" s="3">
-        <v>294.93</v>
+        <v>-513.19</v>
       </c>
       <c r="Q83" s="3">
-        <v>732.62</v>
+        <v>257.41</v>
       </c>
       <c r="R83" s="3">
-        <v>718.15</v>
+        <v>925.27</v>
       </c>
       <c r="S83" s="3">
-        <v>33.4</v>
+        <v>43.02</v>
       </c>
       <c r="T83" t="str">
         <v/>
@@ -5556,58 +5556,58 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C84" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D84" s="1">
-        <v>18487.3</v>
+        <v>10447.9</v>
       </c>
       <c r="E84" s="2">
-        <v>-2.37</v>
+        <v>-1.1</v>
       </c>
       <c r="F84" s="2">
-        <v>-3.36</v>
+        <v>-4.03</v>
       </c>
       <c r="G84" s="2">
-        <v>-3.94</v>
+        <v>0.12</v>
       </c>
       <c r="H84" s="2">
-        <v>4.37</v>
+        <v>-28.93</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>18184.42</v>
+        <v>12193.53</v>
       </c>
       <c r="K84" s="1">
-        <v>19089.63</v>
+        <v>10549.81</v>
       </c>
       <c r="L84" s="1">
-        <v>19652.77</v>
+        <v>11244.44</v>
       </c>
       <c r="M84" s="3">
-        <v>-203.78</v>
+        <v>-182.23</v>
       </c>
       <c r="N84" s="3">
-        <v>-144.59</v>
+        <v>-246.39</v>
       </c>
       <c r="O84" s="3">
-        <v>303.54</v>
+        <v>-492.86</v>
       </c>
       <c r="P84" s="3">
-        <v>488.99</v>
+        <v>-386.92</v>
       </c>
       <c r="Q84" s="3">
-        <v>857</v>
+        <v>-19.18</v>
       </c>
       <c r="R84" s="3">
-        <v>855.57</v>
+        <v>423.58</v>
       </c>
       <c r="S84" s="3">
-        <v>30.69</v>
+        <v>42.9</v>
       </c>
       <c r="T84" t="str">
         <v/>
@@ -5618,58 +5618,58 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C85" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D85" s="1">
-        <v>52417.75</v>
+        <v>18275.9</v>
       </c>
       <c r="E85" s="2">
-        <v>-2.39</v>
+        <v>-1.14</v>
       </c>
       <c r="F85" s="2">
-        <v>-2.65</v>
+        <v>-4.46</v>
       </c>
       <c r="G85" s="2">
-        <v>-3.07</v>
+        <v>-5.04</v>
       </c>
       <c r="H85" s="2">
-        <v>4.19</v>
+        <v>3.17</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>52190.38</v>
+        <v>18188.2</v>
       </c>
       <c r="K85" s="1">
-        <v>54108.5</v>
+        <v>18941.68</v>
       </c>
       <c r="L85" s="1">
-        <v>55691.54</v>
+        <v>19622.01</v>
       </c>
       <c r="M85" s="3">
-        <v>-522.51</v>
+        <v>-257.2</v>
       </c>
       <c r="N85" s="3">
-        <v>-337.93</v>
+        <v>-167.11</v>
       </c>
       <c r="O85" s="3">
-        <v>687.99</v>
+        <v>286.68</v>
       </c>
       <c r="P85" s="3">
-        <v>1152.5</v>
+        <v>485.62</v>
       </c>
       <c r="Q85" s="3">
-        <v>3654.57</v>
+        <v>840.13</v>
       </c>
       <c r="R85" s="3">
-        <v>3879.75</v>
+        <v>852.2</v>
       </c>
       <c r="S85" s="3">
-        <v>33.61</v>
+        <v>28.03</v>
       </c>
       <c r="T85" t="str">
         <v/>
@@ -5680,58 +5680,58 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D86" s="1">
-        <v>50864.95</v>
+        <v>8789.7</v>
       </c>
       <c r="E86" s="2">
-        <v>-2.47</v>
+        <v>-1.21</v>
       </c>
       <c r="F86" s="2">
-        <v>-2.76</v>
+        <v>-4.57</v>
       </c>
       <c r="G86" s="2">
-        <v>-3.84</v>
+        <v>-5.25</v>
       </c>
       <c r="H86" s="2">
-        <v>-3.5</v>
+        <v>13.45</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
       <c r="J86" s="1">
-        <v>52551.71</v>
+        <v>8838.59</v>
       </c>
       <c r="K86" s="1">
-        <v>52384.29</v>
+        <v>9073.97</v>
       </c>
       <c r="L86" s="1">
-        <v>54191.73</v>
+        <v>9477.38</v>
       </c>
       <c r="M86" s="3">
-        <v>-631.31</v>
+        <v>-128.58</v>
       </c>
       <c r="N86" s="3">
-        <v>-484.74</v>
+        <v>-108.07</v>
       </c>
       <c r="O86" s="3">
-        <v>16.41</v>
+        <v>99.43</v>
       </c>
       <c r="P86" s="3">
-        <v>441.68</v>
+        <v>234.57</v>
       </c>
       <c r="Q86" s="3">
-        <v>-766.73</v>
+        <v>601.31</v>
       </c>
       <c r="R86" s="3">
-        <v>-1125.04</v>
+        <v>522.36</v>
       </c>
       <c r="S86" s="3">
-        <v>31.55</v>
+        <v>34.11</v>
       </c>
       <c r="T86" t="str">
         <v/>
@@ -5742,58 +5742,58 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D87" s="1">
-        <v>28210.45</v>
+        <v>45682.75</v>
       </c>
       <c r="E87" s="2">
-        <v>-2.47</v>
+        <v>-1.23</v>
       </c>
       <c r="F87" s="2">
-        <v>-3.03</v>
+        <v>-4.19</v>
       </c>
       <c r="G87" s="2">
-        <v>-4.43</v>
+        <v>-4.54</v>
       </c>
       <c r="H87" s="2">
-        <v>-9.43</v>
+        <v>3.86</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>30400.13</v>
+        <v>44926.78</v>
       </c>
       <c r="K87" s="1">
-        <v>29070.51</v>
+        <v>47126.67</v>
       </c>
       <c r="L87" s="1">
-        <v>30338.82</v>
+        <v>48360.46</v>
       </c>
       <c r="M87" s="3">
-        <v>-436.16</v>
+        <v>-468.02</v>
       </c>
       <c r="N87" s="3">
-        <v>-371.67</v>
+        <v>-284.81</v>
       </c>
       <c r="O87" s="3">
-        <v>-358.37</v>
+        <v>752.07</v>
       </c>
       <c r="P87" s="3">
-        <v>-90.14</v>
+        <v>1121.08</v>
       </c>
       <c r="Q87" s="3">
-        <v>1434.04</v>
+        <v>-356.76</v>
       </c>
       <c r="R87" s="3">
-        <v>1996.53</v>
+        <v>-1023.2</v>
       </c>
       <c r="S87" s="3">
-        <v>29.63</v>
+        <v>31.23</v>
       </c>
       <c r="T87" t="str">
         <v/>
@@ -5804,58 +5804,58 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D88" s="1">
-        <v>8897.2</v>
+        <v>43105.45</v>
       </c>
       <c r="E88" s="2">
-        <v>-2.49</v>
+        <v>-1.41</v>
       </c>
       <c r="F88" s="2">
-        <v>-3.4</v>
+        <v>-3.39</v>
       </c>
       <c r="G88" s="2">
-        <v>-4.09</v>
+        <v>-3.15</v>
       </c>
       <c r="H88" s="2">
-        <v>14.84</v>
+        <v>-22.3</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>8832.86</v>
+        <v>48970.83</v>
       </c>
       <c r="K88" s="1">
-        <v>9137.14</v>
+        <v>44208.15</v>
       </c>
       <c r="L88" s="1">
-        <v>9494.3</v>
+        <v>45882.54</v>
       </c>
       <c r="M88" s="3">
-        <v>-107.5</v>
+        <v>-574.55</v>
       </c>
       <c r="N88" s="3">
-        <v>-102.94</v>
+        <v>-517.63</v>
       </c>
       <c r="O88" s="3">
-        <v>108</v>
+        <v>-1668.17</v>
       </c>
       <c r="P88" s="3">
-        <v>236.29</v>
+        <v>-1354.71</v>
       </c>
       <c r="Q88" s="3">
-        <v>609.88</v>
+        <v>-2185.95</v>
       </c>
       <c r="R88" s="3">
-        <v>524.08</v>
+        <v>-970</v>
       </c>
       <c r="S88" s="3">
-        <v>36.73</v>
+        <v>35.82</v>
       </c>
       <c r="T88" t="str">
         <v/>
@@ -5866,58 +5866,58 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C89" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D89" s="1">
-        <v>24645.85</v>
+        <v>51352</v>
       </c>
       <c r="E89" s="2">
-        <v>-2.61</v>
+        <v>-2.03</v>
       </c>
       <c r="F89" s="2">
-        <v>-4.24</v>
+        <v>-4.63</v>
       </c>
       <c r="G89" s="2">
-        <v>-6.11</v>
+        <v>-5.04</v>
       </c>
       <c r="H89" s="2">
-        <v>9.31</v>
+        <v>2.07</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>23607.54</v>
+        <v>52198.32</v>
       </c>
       <c r="K89" s="1">
-        <v>25538.32</v>
+        <v>53607.32</v>
       </c>
       <c r="L89" s="1">
-        <v>26151.21</v>
+        <v>55593.73</v>
       </c>
       <c r="M89" s="3">
-        <v>-250.27</v>
+        <v>-713.53</v>
       </c>
       <c r="N89" s="3">
-        <v>-135.24</v>
+        <v>-413.05</v>
       </c>
       <c r="O89" s="3">
-        <v>631.16</v>
+        <v>602.97</v>
       </c>
       <c r="P89" s="3">
-        <v>861.21</v>
+        <v>1135.5</v>
       </c>
       <c r="Q89" s="3">
-        <v>2310.69</v>
+        <v>3569.55</v>
       </c>
       <c r="R89" s="3">
-        <v>2354.84</v>
+        <v>3862.75</v>
       </c>
       <c r="S89" s="3">
-        <v>32.27</v>
+        <v>29.27</v>
       </c>
       <c r="T89" t="str">
         <v/>
@@ -5928,58 +5928,58 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C90" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D90" s="1">
-        <v>27176.35</v>
+        <v>1584.5</v>
       </c>
       <c r="E90" s="2">
-        <v>-2.64</v>
+        <v>-2.35</v>
       </c>
       <c r="F90" s="2">
-        <v>-4.19</v>
+        <v>-3.87</v>
       </c>
       <c r="G90" s="2">
-        <v>-4.18</v>
-      </c>
-      <c r="H90" t="str">
-        <v/>
+        <v>0.08</v>
+      </c>
+      <c r="H90" s="2">
+        <v>9.68</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
-      <c r="J90" t="str">
-        <v/>
+      <c r="J90" s="1">
+        <v>1468.91</v>
       </c>
       <c r="K90" s="1">
-        <v>28093.5</v>
+        <v>1608.73</v>
       </c>
       <c r="L90" s="1">
-        <v>29400.12</v>
+        <v>1573.92</v>
       </c>
       <c r="M90" s="3">
-        <v>-420.56</v>
+        <v>17.85</v>
       </c>
       <c r="N90" s="3">
-        <v>-400.05</v>
+        <v>14.75</v>
       </c>
       <c r="O90" s="3">
-        <v>-188.9</v>
+        <v>32.67</v>
       </c>
       <c r="P90" s="3">
-        <v>171.93</v>
+        <v>31.65</v>
       </c>
       <c r="Q90" s="3">
-        <v>223.94</v>
+        <v>-73.28</v>
       </c>
       <c r="R90" s="3">
-        <v>186.07</v>
+        <v>-105.55</v>
       </c>
       <c r="S90" s="3">
-        <v>31.05</v>
+        <v>49.63</v>
       </c>
       <c r="T90" t="str">
         <v/>

--- a/Index.xlsx
+++ b/Index.xlsx
@@ -472,58 +472,58 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>India VIX</v>
       </c>
       <c r="C2" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>INDIAVIX</v>
       </c>
       <c r="D2" s="1">
-        <v>7452.2</v>
+        <v>16.76</v>
       </c>
       <c r="E2" s="2">
-        <v>1.1</v>
+        <v>6.35</v>
       </c>
       <c r="F2" s="2">
-        <v>-1.49</v>
+        <v>19.2</v>
       </c>
       <c r="G2" s="2">
-        <v>-3.27</v>
+        <v>24.24</v>
       </c>
       <c r="H2" s="2">
-        <v>-13.39</v>
+        <v>76.79</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>7685.96</v>
+        <v>14.91</v>
       </c>
       <c r="K2" s="1">
-        <v>7493.8</v>
+        <v>15.12</v>
       </c>
       <c r="L2" s="1">
-        <v>7767.83</v>
+        <v>12.6</v>
       </c>
       <c r="M2" s="3">
-        <v>-91.28</v>
+        <v>0.9</v>
       </c>
       <c r="N2" s="3">
-        <v>-88.42</v>
+        <v>0.73</v>
       </c>
       <c r="O2" s="3">
-        <v>-60.24</v>
+        <v>-0.2</v>
       </c>
       <c r="P2" s="3">
-        <v>-17.33</v>
+        <v>-0.73</v>
       </c>
       <c r="Q2" s="3">
-        <v>-298.05</v>
+        <v>0.07</v>
       </c>
       <c r="R2" s="3">
-        <v>-246.79</v>
+        <v>0.05</v>
       </c>
       <c r="S2" s="3">
-        <v>42.04</v>
+        <v>66.13</v>
       </c>
       <c r="T2" t="str">
         <v/>
@@ -534,58 +534,58 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D3" s="1">
-        <v>191.15</v>
+        <v>204.22</v>
       </c>
       <c r="E3" s="2">
-        <v>0.58</v>
+        <v>1.02</v>
       </c>
       <c r="F3" s="2">
-        <v>2.11</v>
+        <v>1.02</v>
       </c>
       <c r="G3" s="2">
-        <v>-0.13</v>
+        <v>3.78</v>
       </c>
       <c r="H3" s="2">
-        <v>16.8</v>
+        <v>-18.03</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>178.54</v>
+        <v>180.43</v>
       </c>
       <c r="K3" s="1">
-        <v>190.26</v>
+        <v>200.88</v>
       </c>
       <c r="L3" s="1">
-        <v>184.58</v>
+        <v>195.12</v>
       </c>
       <c r="M3" s="3">
-        <v>1.47</v>
+        <v>2.78</v>
       </c>
       <c r="N3" s="3">
-        <v>2.03</v>
+        <v>2.61</v>
       </c>
       <c r="O3" s="3">
-        <v>3.49</v>
+        <v>11.94</v>
       </c>
       <c r="P3" s="3">
-        <v>2.48</v>
+        <v>5.7</v>
       </c>
       <c r="Q3" s="3">
-        <v>-2.5</v>
+        <v>5.47</v>
       </c>
       <c r="R3" s="3">
-        <v>-6.03</v>
+        <v>7.68</v>
       </c>
       <c r="S3" s="3">
-        <v>56.53</v>
+        <v>100</v>
       </c>
       <c r="T3" t="str">
         <v/>
@@ -602,52 +602,52 @@
         <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D4" s="1">
-        <v>235.65</v>
+        <v>236.6</v>
       </c>
       <c r="E4" s="2">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="F4" s="2">
-        <v>2.08</v>
+        <v>2.49</v>
       </c>
       <c r="G4" s="2">
-        <v>-0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H4" s="2">
-        <v>17.83</v>
+        <v>18.3</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>219.08</v>
+        <v>219.26</v>
       </c>
       <c r="K4" s="1">
-        <v>234.58</v>
+        <v>234.95</v>
       </c>
       <c r="L4" s="1">
-        <v>227.53</v>
+        <v>227.92</v>
       </c>
       <c r="M4" s="3">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="N4" s="3">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="O4" s="3">
-        <v>4.68</v>
+        <v>4.76</v>
       </c>
       <c r="P4" s="3">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="Q4" s="3">
-        <v>-0.65</v>
+        <v>-0.58</v>
       </c>
       <c r="R4" s="3">
-        <v>-4.77</v>
+        <v>-4.76</v>
       </c>
       <c r="S4" s="3">
-        <v>56.57</v>
+        <v>58.23</v>
       </c>
       <c r="T4" t="str">
         <v/>
@@ -658,58 +658,58 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>India VIX</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="C5" t="str">
-        <v>INDIAVIX</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D5" s="1">
-        <v>15.76</v>
+        <v>191.9</v>
       </c>
       <c r="E5" s="2">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="F5" s="2">
-        <v>12.09</v>
+        <v>2.51</v>
       </c>
       <c r="G5" s="2">
-        <v>16.83</v>
+        <v>0.26</v>
       </c>
       <c r="H5" s="2">
-        <v>66.24</v>
+        <v>17.26</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>14.87</v>
+        <v>178.68</v>
       </c>
       <c r="K5" s="1">
-        <v>14.75</v>
+        <v>190.56</v>
       </c>
       <c r="L5" s="1">
-        <v>12.5</v>
+        <v>184.9</v>
       </c>
       <c r="M5" s="3">
-        <v>0.78</v>
+        <v>1.5</v>
       </c>
       <c r="N5" s="3">
-        <v>0.69</v>
+        <v>1.92</v>
       </c>
       <c r="O5" s="3">
-        <v>-0.28</v>
+        <v>3.55</v>
       </c>
       <c r="P5" s="3">
-        <v>-0.75</v>
+        <v>2.49</v>
       </c>
       <c r="Q5" s="3">
-        <v>-0.01</v>
+        <v>-2.44</v>
       </c>
       <c r="R5" s="3">
-        <v>0.04</v>
+        <v>-6.02</v>
       </c>
       <c r="S5" s="3">
-        <v>62.01</v>
+        <v>58.14</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -720,58 +720,58 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C6" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D6" s="1">
-        <v>25596.65</v>
+        <v>2597.31</v>
       </c>
       <c r="E6" s="2">
-        <v>0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="F6" s="2">
-        <v>-0.72</v>
+        <v>-0.53</v>
       </c>
       <c r="G6" s="2">
-        <v>-3.18</v>
+        <v>-1.55</v>
       </c>
       <c r="H6" s="2">
-        <v>12.64</v>
+        <v>-0.56</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>24362.22</v>
+        <v>2632.22</v>
       </c>
       <c r="K6" s="1">
-        <v>25836.58</v>
+        <v>2607.41</v>
       </c>
       <c r="L6" s="1">
-        <v>26467.62</v>
+        <v>2648.03</v>
       </c>
       <c r="M6" s="3">
-        <v>-260.98</v>
+        <v>-14.33</v>
       </c>
       <c r="N6" s="3">
-        <v>-185.97</v>
+        <v>-13.1</v>
       </c>
       <c r="O6" s="3">
-        <v>599.34</v>
+        <v>-2.09</v>
       </c>
       <c r="P6" s="3">
-        <v>796.89</v>
+        <v>7.43</v>
       </c>
       <c r="Q6" s="3">
-        <v>1774.69</v>
+        <v>89.72</v>
       </c>
       <c r="R6" s="3">
-        <v>1607.38</v>
+        <v>106.35</v>
       </c>
       <c r="S6" s="3">
-        <v>36.82</v>
+        <v>26.78</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -782,58 +782,58 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C7" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D7" s="1">
-        <v>8257.4</v>
+        <v>3276.83</v>
       </c>
       <c r="E7" s="2">
-        <v>0.07</v>
+        <v>-0.02</v>
       </c>
       <c r="F7" s="2">
-        <v>2.01</v>
+        <v>-0.14</v>
       </c>
       <c r="G7" s="2">
-        <v>3.01</v>
+        <v>-0.96</v>
       </c>
       <c r="H7" s="2">
-        <v>-3.23</v>
+        <v>1.68</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>8574.26</v>
+        <v>3280.43</v>
       </c>
       <c r="K7" s="1">
-        <v>8170.22</v>
+        <v>3284.32</v>
       </c>
       <c r="L7" s="1">
-        <v>8356.45</v>
+        <v>3319.89</v>
       </c>
       <c r="M7" s="3">
-        <v>-30.34</v>
+        <v>-12.05</v>
       </c>
       <c r="N7" s="3">
-        <v>-68.98</v>
+        <v>-11.31</v>
       </c>
       <c r="O7" s="3">
-        <v>-75.07</v>
+        <v>7.71</v>
       </c>
       <c r="P7" s="3">
-        <v>-29.67</v>
+        <v>17.99</v>
       </c>
       <c r="Q7" s="3">
-        <v>575.84</v>
+        <v>139.48</v>
       </c>
       <c r="R7" s="3">
-        <v>685.49</v>
+        <v>155.4</v>
       </c>
       <c r="S7" s="3">
-        <v>52.97</v>
+        <v>24.99</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -844,58 +844,58 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C8" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D8" s="1">
-        <v>15515.25</v>
+        <v>2966.76</v>
       </c>
       <c r="E8" s="2">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="F8" s="2">
-        <v>-1.07</v>
+        <v>-0.54</v>
       </c>
       <c r="G8" s="2">
-        <v>-3.86</v>
+        <v>-1.56</v>
       </c>
       <c r="H8" s="2">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>15441.14</v>
+        <v>3001.36</v>
       </c>
       <c r="K8" s="1">
-        <v>15715.24</v>
+        <v>2979.21</v>
       </c>
       <c r="L8" s="1">
-        <v>16350.61</v>
+        <v>3025.29</v>
       </c>
       <c r="M8" s="3">
-        <v>-253.06</v>
+        <v>-16.22</v>
       </c>
       <c r="N8" s="3">
-        <v>-208.74</v>
+        <v>-14.69</v>
       </c>
       <c r="O8" s="3">
-        <v>171.36</v>
+        <v>0.02</v>
       </c>
       <c r="P8" s="3">
-        <v>340.54</v>
+        <v>11.36</v>
       </c>
       <c r="Q8" s="3">
-        <v>979.06</v>
+        <v>114.47</v>
       </c>
       <c r="R8" s="3">
-        <v>994.28</v>
+        <v>132.77</v>
       </c>
       <c r="S8" s="3">
-        <v>31.11</v>
+        <v>24.89</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -906,58 +906,58 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C9" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D9" s="1">
-        <v>3285.67</v>
+        <v>837.73</v>
       </c>
       <c r="E9" s="2">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F9" s="2">
-        <v>-0.53</v>
+        <v>-0.69</v>
       </c>
       <c r="G9" s="2">
-        <v>-1.08</v>
+        <v>-2.04</v>
       </c>
       <c r="H9" s="2">
-        <v>1.35</v>
+        <v>-6.03</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>3295.13</v>
+        <v>873.57</v>
       </c>
       <c r="K9" s="1">
-        <v>3296.83</v>
+        <v>842.19</v>
       </c>
       <c r="L9" s="1">
-        <v>3349.65</v>
+        <v>860.69</v>
       </c>
       <c r="M9" s="3">
-        <v>-17.55</v>
+        <v>-6.52</v>
       </c>
       <c r="N9" s="3">
-        <v>-17.18</v>
+        <v>-6.09</v>
       </c>
       <c r="O9" s="3">
-        <v>7.59</v>
+        <v>-8.8</v>
       </c>
       <c r="P9" s="3">
-        <v>21.5</v>
+        <v>-5.64</v>
       </c>
       <c r="Q9" s="3">
-        <v>136.46</v>
+        <v>-17.24</v>
       </c>
       <c r="R9" s="3">
-        <v>153.9</v>
+        <v>-14.2</v>
       </c>
       <c r="S9" s="3">
-        <v>32.57</v>
+        <v>20.96</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -968,58 +968,58 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C10" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D10" s="1">
-        <v>202.16</v>
+        <v>3284.16</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="G10" s="2">
-        <v>2.73</v>
+        <v>-1.13</v>
       </c>
       <c r="H10" s="2">
-        <v>-18.86</v>
+        <v>1.3</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>180.66</v>
+        <v>3295.35</v>
       </c>
       <c r="K10" s="1">
-        <v>200.13</v>
+        <v>3294.53</v>
       </c>
       <c r="L10" s="1">
-        <v>194.79</v>
+        <v>3347.55</v>
       </c>
       <c r="M10" s="3">
-        <v>2.62</v>
+        <v>-17.47</v>
       </c>
       <c r="N10" s="3">
-        <v>2.57</v>
+        <v>-17.24</v>
       </c>
       <c r="O10" s="3">
-        <v>11.77</v>
+        <v>7.47</v>
       </c>
       <c r="P10" s="3">
-        <v>5.66</v>
+        <v>21.48</v>
       </c>
       <c r="Q10" s="3">
-        <v>5.31</v>
+        <v>136.34</v>
       </c>
       <c r="R10" s="3">
-        <v>7.65</v>
+        <v>153.87</v>
       </c>
       <c r="S10" s="3">
-        <v>100</v>
+        <v>32.06</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -1030,58 +1030,58 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D11" s="1">
-        <v>3277.38</v>
+        <v>3058.24</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="F11" s="2">
-        <v>-0.12</v>
+        <v>-0.58</v>
       </c>
       <c r="G11" s="2">
-        <v>-0.94</v>
+        <v>-1.48</v>
       </c>
       <c r="H11" s="2">
-        <v>1.7</v>
+        <v>0.19</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>3280.16</v>
+        <v>3085.97</v>
       </c>
       <c r="K11" s="1">
-        <v>3285.99</v>
+        <v>3071.26</v>
       </c>
       <c r="L11" s="1">
-        <v>3321.29</v>
+        <v>3117.28</v>
       </c>
       <c r="M11" s="3">
-        <v>-12.06</v>
+        <v>-16.04</v>
       </c>
       <c r="N11" s="3">
-        <v>-11.13</v>
+        <v>-14.54</v>
       </c>
       <c r="O11" s="3">
-        <v>7.75</v>
+        <v>2.3</v>
       </c>
       <c r="P11" s="3">
-        <v>18</v>
+        <v>13.9</v>
       </c>
       <c r="Q11" s="3">
-        <v>139.52</v>
+        <v>118.3</v>
       </c>
       <c r="R11" s="3">
-        <v>155.41</v>
+        <v>136.51</v>
       </c>
       <c r="S11" s="3">
-        <v>25.28</v>
+        <v>26.92</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -1092,58 +1092,58 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C12" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D12" s="1">
-        <v>1599.72</v>
+        <v>29934.75</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.07</v>
+        <v>-0.21</v>
       </c>
       <c r="F12" s="2">
-        <v>-0.11</v>
+        <v>-1.79</v>
       </c>
       <c r="G12" s="2">
-        <v>-0.45</v>
+        <v>3.17</v>
       </c>
       <c r="H12" s="2">
-        <v>2.1</v>
+        <v>-11.06</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>1586.66</v>
+        <v>30941.95</v>
       </c>
       <c r="K12" s="1">
-        <v>1603.06</v>
+        <v>29821.3</v>
       </c>
       <c r="L12" s="1">
-        <v>1608.95</v>
+        <v>30083.38</v>
       </c>
       <c r="M12" s="3">
-        <v>-2.27</v>
+        <v>21.38</v>
       </c>
       <c r="N12" s="3">
-        <v>-1.59</v>
+        <v>-124.43</v>
       </c>
       <c r="O12" s="3">
-        <v>6.82</v>
+        <v>-359.57</v>
       </c>
       <c r="P12" s="3">
-        <v>9.34</v>
+        <v>-317.41</v>
       </c>
       <c r="Q12" s="3">
-        <v>34.77</v>
+        <v>482.12</v>
       </c>
       <c r="R12" s="3">
-        <v>33.1</v>
+        <v>990.92</v>
       </c>
       <c r="S12" s="3">
-        <v>28.9</v>
+        <v>52.88</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -1154,58 +1154,58 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C13" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D13" s="1">
-        <v>1261.46</v>
+        <v>1596.15</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.08</v>
+        <v>-0.22</v>
       </c>
       <c r="F13" s="2">
-        <v>-0.22</v>
+        <v>-0.33</v>
       </c>
       <c r="G13" s="2">
-        <v>-0.92</v>
+        <v>-0.67</v>
       </c>
       <c r="H13" s="2">
-        <v>-0.01</v>
+        <v>1.87</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>1268.34</v>
+        <v>1586.81</v>
       </c>
       <c r="K13" s="1">
-        <v>1266.47</v>
+        <v>1601.81</v>
       </c>
       <c r="L13" s="1">
-        <v>1280.28</v>
+        <v>1608.58</v>
       </c>
       <c r="M13" s="3">
-        <v>-4.96</v>
+        <v>-2.7</v>
       </c>
       <c r="N13" s="3">
-        <v>-4.18</v>
+        <v>-1.81</v>
       </c>
       <c r="O13" s="3">
-        <v>1.13</v>
+        <v>6.53</v>
       </c>
       <c r="P13" s="3">
-        <v>4.93</v>
+        <v>9.29</v>
       </c>
       <c r="Q13" s="3">
-        <v>21.22</v>
+        <v>34.48</v>
       </c>
       <c r="R13" s="3">
-        <v>21.94</v>
+        <v>33.04</v>
       </c>
       <c r="S13" s="3">
-        <v>20.6</v>
+        <v>23.28</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1216,58 +1216,58 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C14" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D14" s="1">
-        <v>54925.7</v>
+        <v>10889.35</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.09</v>
+        <v>-0.25</v>
       </c>
       <c r="F14" s="2">
-        <v>-1.64</v>
+        <v>-1.23</v>
       </c>
       <c r="G14" s="2">
-        <v>0.54</v>
+        <v>3.32</v>
       </c>
       <c r="H14" s="2">
-        <v>-7.81</v>
+        <v>-12.77</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>56869.45</v>
+        <v>11216.63</v>
       </c>
       <c r="K14" s="1">
-        <v>55246.42</v>
+        <v>10811.35</v>
       </c>
       <c r="L14" s="1">
-        <v>56322.88</v>
+        <v>11067.8</v>
       </c>
       <c r="M14" s="3">
-        <v>-271.33</v>
+        <v>-22.75</v>
       </c>
       <c r="N14" s="3">
-        <v>-357.02</v>
+        <v>-98.95</v>
       </c>
       <c r="O14" s="3">
-        <v>-351.09</v>
+        <v>-114.58</v>
       </c>
       <c r="P14" s="3">
-        <v>-99.1</v>
+        <v>-76.04</v>
       </c>
       <c r="Q14" s="3">
-        <v>1661</v>
+        <v>31.47</v>
       </c>
       <c r="R14" s="3">
-        <v>2287.78</v>
+        <v>176.53</v>
       </c>
       <c r="S14" s="3">
-        <v>43.05</v>
+        <v>52.9</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1278,58 +1278,58 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C15" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D15" s="1">
-        <v>2597.53</v>
+        <v>10726.75</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.09</v>
+        <v>-0.25</v>
       </c>
       <c r="F15" s="2">
-        <v>-0.52</v>
+        <v>-2.97</v>
       </c>
       <c r="G15" s="2">
-        <v>-1.54</v>
+        <v>-3.12</v>
       </c>
       <c r="H15" s="2">
-        <v>-0.55</v>
+        <v>-12.72</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>2632.29</v>
+        <v>11488.94</v>
       </c>
       <c r="K15" s="1">
-        <v>2609.67</v>
+        <v>10883.66</v>
       </c>
       <c r="L15" s="1">
-        <v>2649.71</v>
+        <v>11448.4</v>
       </c>
       <c r="M15" s="3">
-        <v>-14.2</v>
+        <v>-176.46</v>
       </c>
       <c r="N15" s="3">
-        <v>-12.79</v>
+        <v>-180.36</v>
       </c>
       <c r="O15" s="3">
-        <v>-2.08</v>
+        <v>-159.66</v>
       </c>
       <c r="P15" s="3">
-        <v>7.44</v>
+        <v>-43.17</v>
       </c>
       <c r="Q15" s="3">
-        <v>89.73</v>
+        <v>208.66</v>
       </c>
       <c r="R15" s="3">
-        <v>106.36</v>
+        <v>392.4</v>
       </c>
       <c r="S15" s="3">
-        <v>26.87</v>
+        <v>34.37</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1340,58 +1340,58 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C16" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D16" s="1">
-        <v>1445.49</v>
+        <v>8281.2</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="F16" s="2">
-        <v>-0.11</v>
+        <v>-1.98</v>
       </c>
       <c r="G16" s="2">
-        <v>-0.58</v>
+        <v>2.53</v>
       </c>
       <c r="H16" s="2">
-        <v>1.46</v>
+        <v>-17.56</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>1440.78</v>
+        <v>8763.47</v>
       </c>
       <c r="K16" s="1">
-        <v>1449.04</v>
+        <v>8285.07</v>
       </c>
       <c r="L16" s="1">
-        <v>1458.33</v>
+        <v>8388.81</v>
       </c>
       <c r="M16" s="3">
-        <v>-3.35</v>
+        <v>-8.14</v>
       </c>
       <c r="N16" s="3">
-        <v>-2.75</v>
+        <v>-37.3</v>
       </c>
       <c r="O16" s="3">
-        <v>4.2</v>
+        <v>-161.61</v>
       </c>
       <c r="P16" s="3">
-        <v>7.32</v>
+        <v>-158.84</v>
       </c>
       <c r="Q16" s="3">
-        <v>29.13</v>
+        <v>-306.95</v>
       </c>
       <c r="R16" s="3">
-        <v>28.55</v>
+        <v>-192.72</v>
       </c>
       <c r="S16" s="3">
-        <v>24.73</v>
+        <v>49.51</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1402,58 +1402,58 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C17" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D17" s="1">
-        <v>3060.34</v>
+        <v>3453.01</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="F17" s="2">
-        <v>-0.51</v>
+        <v>-0.99</v>
       </c>
       <c r="G17" s="2">
-        <v>-1.42</v>
+        <v>-1.95</v>
       </c>
       <c r="H17" s="2">
-        <v>0.26</v>
+        <v>-1.14</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>3085.94</v>
+        <v>3495.25</v>
       </c>
       <c r="K17" s="1">
-        <v>3074.16</v>
+        <v>3477.14</v>
       </c>
       <c r="L17" s="1">
-        <v>3119.19</v>
+        <v>3532.06</v>
       </c>
       <c r="M17" s="3">
-        <v>-15.71</v>
+        <v>-19.58</v>
       </c>
       <c r="N17" s="3">
-        <v>-14.17</v>
+        <v>-16.39</v>
       </c>
       <c r="O17" s="3">
-        <v>2.47</v>
+        <v>1.54</v>
       </c>
       <c r="P17" s="3">
-        <v>13.94</v>
+        <v>15.18</v>
       </c>
       <c r="Q17" s="3">
-        <v>118.47</v>
+        <v>117.58</v>
       </c>
       <c r="R17" s="3">
-        <v>136.54</v>
+        <v>141.66</v>
       </c>
       <c r="S17" s="3">
-        <v>27.67</v>
+        <v>30.66</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1464,58 +1464,58 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C18" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>CNXIT</v>
       </c>
       <c r="D18" s="1">
-        <v>837.97</v>
+        <v>31995.5</v>
       </c>
       <c r="E18" s="2">
-        <v>-0.12</v>
+        <v>-0.27</v>
       </c>
       <c r="F18" s="2">
-        <v>-0.66</v>
+        <v>0.22</v>
       </c>
       <c r="G18" s="2">
-        <v>-2.02</v>
+        <v>15.49</v>
       </c>
       <c r="H18" s="2">
-        <v>-6</v>
+        <v>-15.54</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>873.84</v>
+        <v>30815.06</v>
       </c>
       <c r="K18" s="1">
-        <v>843.19</v>
+        <v>30967.15</v>
       </c>
       <c r="L18" s="1">
-        <v>861.49</v>
+        <v>29839.55</v>
       </c>
       <c r="M18" s="3">
-        <v>-6.48</v>
+        <v>749.33</v>
       </c>
       <c r="N18" s="3">
-        <v>-5.99</v>
+        <v>287.49</v>
       </c>
       <c r="O18" s="3">
-        <v>-8.78</v>
+        <v>-156.84</v>
       </c>
       <c r="P18" s="3">
-        <v>-5.64</v>
+        <v>-519.55</v>
       </c>
       <c r="Q18" s="3">
-        <v>-17.23</v>
+        <v>-1661.02</v>
       </c>
       <c r="R18" s="3">
-        <v>-14.2</v>
+        <v>-1147.75</v>
       </c>
       <c r="S18" s="3">
-        <v>21.18</v>
+        <v>68.05</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1526,58 +1526,58 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C19" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D19" s="1">
-        <v>2967.49</v>
+        <v>1440.45</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.13</v>
+        <v>-0.35</v>
       </c>
       <c r="F19" s="2">
-        <v>-0.51</v>
+        <v>-0.45</v>
       </c>
       <c r="G19" s="2">
-        <v>-1.54</v>
+        <v>-0.92</v>
       </c>
       <c r="H19" s="2">
-        <v>0.02</v>
+        <v>1.11</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>3001.36</v>
+        <v>1440.86</v>
       </c>
       <c r="K19" s="1">
-        <v>2981.99</v>
+        <v>1447.48</v>
       </c>
       <c r="L19" s="1">
-        <v>3027.17</v>
+        <v>1457.8</v>
       </c>
       <c r="M19" s="3">
-        <v>-15.97</v>
+        <v>-3.84</v>
       </c>
       <c r="N19" s="3">
-        <v>-14.3</v>
+        <v>-2.97</v>
       </c>
       <c r="O19" s="3">
-        <v>0.08</v>
+        <v>3.8</v>
       </c>
       <c r="P19" s="3">
-        <v>11.37</v>
+        <v>7.24</v>
       </c>
       <c r="Q19" s="3">
-        <v>114.53</v>
+        <v>28.73</v>
       </c>
       <c r="R19" s="3">
-        <v>132.78</v>
+        <v>28.47</v>
       </c>
       <c r="S19" s="3">
-        <v>25.15</v>
+        <v>18.6</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1588,58 +1588,58 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D20" s="1">
-        <v>26866.05</v>
+        <v>11280.35</v>
       </c>
       <c r="E20" s="2">
-        <v>-0.14</v>
+        <v>-0.36</v>
       </c>
       <c r="F20" s="2">
-        <v>-3.01</v>
+        <v>-2.18</v>
       </c>
       <c r="G20" s="2">
-        <v>0.64</v>
+        <v>1.21</v>
       </c>
       <c r="H20" s="2">
-        <v>-6.46</v>
+        <v>-15.03</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>27372.43</v>
+        <v>12171.5</v>
       </c>
       <c r="K20" s="1">
-        <v>27137.71</v>
+        <v>11317.59</v>
       </c>
       <c r="L20" s="1">
-        <v>27283.4</v>
+        <v>11538.09</v>
       </c>
       <c r="M20" s="3">
-        <v>-24.38</v>
+        <v>-43.96</v>
       </c>
       <c r="N20" s="3">
-        <v>-38.48</v>
+        <v>-81.17</v>
       </c>
       <c r="O20" s="3">
-        <v>-36.94</v>
+        <v>-267.67</v>
       </c>
       <c r="P20" s="3">
-        <v>18.1</v>
+        <v>-236.36</v>
       </c>
       <c r="Q20" s="3">
-        <v>646.68</v>
+        <v>-133.65</v>
       </c>
       <c r="R20" s="3">
-        <v>875.22</v>
+        <v>113.71</v>
       </c>
       <c r="S20" s="3">
-        <v>44.39</v>
+        <v>46.06</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1650,58 +1650,58 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY</v>
       </c>
       <c r="D21" s="1">
-        <v>24657.7</v>
+        <v>22600</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.14</v>
+        <v>-0.39</v>
       </c>
       <c r="F21" s="2">
-        <v>-2.87</v>
+        <v>-2.36</v>
       </c>
       <c r="G21" s="2">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="H21" s="2">
-        <v>-10.7</v>
+        <v>-13.51</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>26223.16</v>
+        <v>24118.84</v>
       </c>
       <c r="K21" s="1">
-        <v>24937.38</v>
+        <v>22747.25</v>
       </c>
       <c r="L21" s="1">
-        <v>25524.6</v>
+        <v>23403.72</v>
       </c>
       <c r="M21" s="3">
-        <v>-159.46</v>
+        <v>-169.46</v>
       </c>
       <c r="N21" s="3">
-        <v>-186.87</v>
+        <v>-222.63</v>
       </c>
       <c r="O21" s="3">
-        <v>-358.1</v>
+        <v>-401.05</v>
       </c>
       <c r="P21" s="3">
-        <v>-222.89</v>
+        <v>-278.18</v>
       </c>
       <c r="Q21" s="3">
-        <v>648.25</v>
+        <v>177.18</v>
       </c>
       <c r="R21" s="3">
-        <v>1081.21</v>
+        <v>596.29</v>
       </c>
       <c r="S21" s="3">
-        <v>41.17</v>
+        <v>42.39</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1718,52 +1718,52 @@
         <v>BHARATBOND-APR32</v>
       </c>
       <c r="D22" s="1">
-        <v>1305.6</v>
+        <v>1300.19</v>
       </c>
       <c r="E22" s="2">
-        <v>-0.15</v>
+        <v>-0.41</v>
       </c>
       <c r="F22" s="2">
-        <v>-0.17</v>
+        <v>-0.58</v>
       </c>
       <c r="G22" s="2">
-        <v>-0.75</v>
+        <v>-1.17</v>
       </c>
       <c r="H22" s="2">
-        <v>0.57</v>
+        <v>0.16</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>1307.99</v>
+        <v>1308</v>
       </c>
       <c r="K22" s="1">
-        <v>1310.04</v>
+        <v>1308.25</v>
       </c>
       <c r="L22" s="1">
-        <v>1321.92</v>
+        <v>1321.23</v>
       </c>
       <c r="M22" s="3">
-        <v>-4.18</v>
+        <v>-4.72</v>
       </c>
       <c r="N22" s="3">
-        <v>-3.57</v>
+        <v>-3.8</v>
       </c>
       <c r="O22" s="3">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="P22" s="3">
-        <v>5.69</v>
+        <v>5.61</v>
       </c>
       <c r="Q22" s="3">
-        <v>23.93</v>
+        <v>23.49</v>
       </c>
       <c r="R22" s="3">
-        <v>24.2</v>
+        <v>24.11</v>
       </c>
       <c r="S22" s="3">
-        <v>21.86</v>
+        <v>16.61</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1774,58 +1774,58 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D23" s="1">
-        <v>3461.91</v>
+        <v>18563.55</v>
       </c>
       <c r="E23" s="2">
-        <v>-0.18</v>
+        <v>-0.42</v>
       </c>
       <c r="F23" s="2">
-        <v>-0.74</v>
+        <v>-1.88</v>
       </c>
       <c r="G23" s="2">
-        <v>-1.7</v>
+        <v>-1.18</v>
       </c>
       <c r="H23" s="2">
-        <v>-0.89</v>
+        <v>-12.15</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>3495.45</v>
+        <v>19854.88</v>
       </c>
       <c r="K23" s="1">
-        <v>3482.5</v>
+        <v>18709.42</v>
       </c>
       <c r="L23" s="1">
-        <v>3534.62</v>
+        <v>19462.17</v>
       </c>
       <c r="M23" s="3">
-        <v>-18.31</v>
+        <v>-216.15</v>
       </c>
       <c r="N23" s="3">
-        <v>-15.59</v>
+        <v>-252.08</v>
       </c>
       <c r="O23" s="3">
-        <v>2.25</v>
+        <v>-309.66</v>
       </c>
       <c r="P23" s="3">
-        <v>15.32</v>
+        <v>-147.47</v>
       </c>
       <c r="Q23" s="3">
-        <v>118.29</v>
+        <v>746.15</v>
       </c>
       <c r="R23" s="3">
-        <v>141.8</v>
+        <v>1109.05</v>
       </c>
       <c r="S23" s="3">
-        <v>32.82</v>
+        <v>37.55</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1836,58 +1836,58 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C24" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D24" s="1">
-        <v>26507.55</v>
+        <v>8554.25</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.27</v>
+        <v>-0.44</v>
       </c>
       <c r="F24" s="2">
-        <v>-2.59</v>
+        <v>-1.96</v>
       </c>
       <c r="G24" s="2">
-        <v>-0.18</v>
+        <v>-2.06</v>
       </c>
       <c r="H24" s="2">
-        <v>-12.16</v>
+        <v>-11.04</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>28547.73</v>
+        <v>9221.18</v>
       </c>
       <c r="K24" s="1">
-        <v>26804.57</v>
+        <v>8630.32</v>
       </c>
       <c r="L24" s="1">
-        <v>27607.95</v>
+        <v>8996.44</v>
       </c>
       <c r="M24" s="3">
-        <v>-227.16</v>
+        <v>-113.42</v>
       </c>
       <c r="N24" s="3">
-        <v>-264.17</v>
+        <v>-126.4</v>
       </c>
       <c r="O24" s="3">
-        <v>-482.82</v>
+        <v>-167.26</v>
       </c>
       <c r="P24" s="3">
-        <v>-296.17</v>
+        <v>-80.58</v>
       </c>
       <c r="Q24" s="3">
-        <v>1306.83</v>
+        <v>264.02</v>
       </c>
       <c r="R24" s="3">
-        <v>1899.28</v>
+        <v>432.19</v>
       </c>
       <c r="S24" s="3">
-        <v>39.98</v>
+        <v>37.31</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1898,58 +1898,58 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D25" s="1">
-        <v>24515.7</v>
+        <v>7283.05</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.27</v>
+        <v>-0.44</v>
       </c>
       <c r="F25" s="2">
-        <v>-1.6</v>
+        <v>-2.36</v>
       </c>
       <c r="G25" s="2">
-        <v>-2.79</v>
+        <v>2.92</v>
       </c>
       <c r="H25" s="2">
-        <v>-9.46</v>
+        <v>-3.69</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>26255.24</v>
+        <v>7333.45</v>
       </c>
       <c r="K25" s="1">
-        <v>24777.22</v>
+        <v>7294.32</v>
       </c>
       <c r="L25" s="1">
-        <v>26124.11</v>
+        <v>7395.36</v>
       </c>
       <c r="M25" s="3">
-        <v>-430.74</v>
+        <v>-3.25</v>
       </c>
       <c r="N25" s="3">
-        <v>-452.35</v>
+        <v>-32.05</v>
       </c>
       <c r="O25" s="3">
-        <v>-350.04</v>
+        <v>-4.23</v>
       </c>
       <c r="P25" s="3">
-        <v>-68.07</v>
+        <v>30.63</v>
       </c>
       <c r="Q25" s="3">
-        <v>1141.66</v>
+        <v>466.66</v>
       </c>
       <c r="R25" s="3">
-        <v>1595.06</v>
+        <v>551.54</v>
       </c>
       <c r="S25" s="3">
-        <v>31.89</v>
+        <v>49.44</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1960,58 +1960,58 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>CNXREALTY</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C26" t="str">
-        <v>CNXREALTY</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D26" s="1">
-        <v>803.45</v>
+        <v>1255.18</v>
       </c>
       <c r="E26" s="2">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="F26" s="2">
-        <v>-2.72</v>
+        <v>-0.72</v>
       </c>
       <c r="G26" s="2">
-        <v>-5.18</v>
+        <v>-1.42</v>
       </c>
       <c r="H26" s="2">
-        <v>-8.49</v>
+        <v>-0.5</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>822.22</v>
+        <v>1268.31</v>
       </c>
       <c r="K26" s="1">
-        <v>817.64</v>
+        <v>1264.42</v>
       </c>
       <c r="L26" s="1">
-        <v>863.76</v>
+        <v>1279.52</v>
       </c>
       <c r="M26" s="3">
-        <v>-14.65</v>
+        <v>-5.57</v>
       </c>
       <c r="N26" s="3">
-        <v>-14.5</v>
+        <v>-4.46</v>
       </c>
       <c r="O26" s="3">
-        <v>-0.11</v>
+        <v>0.63</v>
       </c>
       <c r="P26" s="3">
-        <v>10.52</v>
+        <v>4.83</v>
       </c>
       <c r="Q26" s="3">
-        <v>1.54</v>
+        <v>20.72</v>
       </c>
       <c r="R26" s="3">
-        <v>9.88</v>
+        <v>21.84</v>
       </c>
       <c r="S26" s="3">
-        <v>37.52</v>
+        <v>15.49</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -2022,58 +2022,58 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C27" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D27" s="1">
-        <v>5056.35</v>
+        <v>3753.2</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.32</v>
+        <v>-0.55</v>
       </c>
       <c r="F27" s="2">
-        <v>-3.54</v>
+        <v>-2.91</v>
       </c>
       <c r="G27" s="2">
-        <v>-0.65</v>
+        <v>-0.77</v>
       </c>
       <c r="H27" s="2">
-        <v>8.59</v>
+        <v>-13.78</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>5105.31</v>
+        <v>4031.76</v>
       </c>
       <c r="K27" s="1">
-        <v>5174.56</v>
+        <v>3789.4</v>
       </c>
       <c r="L27" s="1">
-        <v>5302.4</v>
+        <v>3917.9</v>
       </c>
       <c r="M27" s="3">
-        <v>-40.94</v>
+        <v>-35.3</v>
       </c>
       <c r="N27" s="3">
-        <v>-32.52</v>
+        <v>-43.02</v>
       </c>
       <c r="O27" s="3">
-        <v>27.41</v>
+        <v>-69.09</v>
       </c>
       <c r="P27" s="3">
-        <v>86.51</v>
+        <v>-43.1</v>
       </c>
       <c r="Q27" s="3">
-        <v>363.85</v>
+        <v>123.09</v>
       </c>
       <c r="R27" s="3">
-        <v>325.23</v>
+        <v>206.14</v>
       </c>
       <c r="S27" s="3">
-        <v>38.74</v>
+        <v>40.11</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -2084,58 +2084,58 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D28" s="1">
-        <v>48224.25</v>
+        <v>24862.3</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.37</v>
+        <v>-0.6</v>
       </c>
       <c r="F28" s="2">
-        <v>-2.18</v>
+        <v>-3.52</v>
       </c>
       <c r="G28" s="2">
-        <v>-5.41</v>
+        <v>-5.44</v>
       </c>
       <c r="H28" s="2">
-        <v>9.94</v>
+        <v>-11.8</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>47339.06</v>
+        <v>26911.8</v>
       </c>
       <c r="K28" s="1">
-        <v>49363.48</v>
+        <v>25282.21</v>
       </c>
       <c r="L28" s="1">
-        <v>51543.84</v>
+        <v>27168.61</v>
       </c>
       <c r="M28" s="3">
-        <v>-884</v>
+        <v>-551.37</v>
       </c>
       <c r="N28" s="3">
-        <v>-650.54</v>
+        <v>-601.04</v>
       </c>
       <c r="O28" s="3">
-        <v>935.69</v>
+        <v>-308.95</v>
       </c>
       <c r="P28" s="3">
-        <v>1560.12</v>
+        <v>91.11</v>
       </c>
       <c r="Q28" s="3">
-        <v>2146.68</v>
+        <v>1449.2</v>
       </c>
       <c r="R28" s="3">
-        <v>1466.91</v>
+        <v>1805.34</v>
       </c>
       <c r="S28" s="3">
-        <v>26.75</v>
+        <v>34.23</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -2146,58 +2146,58 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C29" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D29" s="1">
-        <v>8917.6</v>
+        <v>10380.55</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.38</v>
+        <v>-0.62</v>
       </c>
       <c r="F29" s="2">
-        <v>-2</v>
+        <v>-1.67</v>
       </c>
       <c r="G29" s="2">
-        <v>-4.21</v>
+        <v>-2.2</v>
       </c>
       <c r="H29" s="2">
-        <v>-6.28</v>
+        <v>-15.13</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>9761.05</v>
+        <v>11291.49</v>
       </c>
       <c r="K29" s="1">
-        <v>9023.67</v>
+        <v>10485.64</v>
       </c>
       <c r="L29" s="1">
-        <v>9498.97</v>
+        <v>10870.59</v>
       </c>
       <c r="M29" s="3">
-        <v>-161.95</v>
+        <v>-120.55</v>
       </c>
       <c r="N29" s="3">
-        <v>-167.27</v>
+        <v>-134.21</v>
       </c>
       <c r="O29" s="3">
-        <v>-183.21</v>
+        <v>-230.43</v>
       </c>
       <c r="P29" s="3">
-        <v>-66.85</v>
+        <v>-161.29</v>
       </c>
       <c r="Q29" s="3">
-        <v>387.03</v>
+        <v>68.02</v>
       </c>
       <c r="R29" s="3">
-        <v>507.77</v>
+        <v>278.4</v>
       </c>
       <c r="S29" s="3">
-        <v>33.95</v>
+        <v>36.86</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2208,58 +2208,58 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D30" s="1">
-        <v>18642.35</v>
+        <v>30366.85</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.39</v>
+        <v>-0.64</v>
       </c>
       <c r="F30" s="2">
-        <v>-1.46</v>
+        <v>-2.67</v>
       </c>
       <c r="G30" s="2">
-        <v>-0.76</v>
+        <v>-1.74</v>
       </c>
       <c r="H30" s="2">
-        <v>-11.77</v>
+        <v>-8.89</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>19867.71</v>
+        <v>32337.72</v>
       </c>
       <c r="K30" s="1">
-        <v>18741.84</v>
+        <v>30731.31</v>
       </c>
       <c r="L30" s="1">
-        <v>19503.04</v>
+        <v>31919.58</v>
       </c>
       <c r="M30" s="3">
-        <v>-216.46</v>
+        <v>-352.25</v>
       </c>
       <c r="N30" s="3">
-        <v>-261.07</v>
+        <v>-393.41</v>
       </c>
       <c r="O30" s="3">
-        <v>-303.38</v>
+        <v>-406.6</v>
       </c>
       <c r="P30" s="3">
-        <v>-146.21</v>
+        <v>-118.39</v>
       </c>
       <c r="Q30" s="3">
-        <v>752.43</v>
+        <v>1807.56</v>
       </c>
       <c r="R30" s="3">
-        <v>1110.31</v>
+        <v>2369</v>
       </c>
       <c r="S30" s="3">
-        <v>39.34</v>
+        <v>37.19</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2270,58 +2270,58 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D31" s="1">
-        <v>13315.2</v>
+        <v>24348.8</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.39</v>
+        <v>-0.68</v>
       </c>
       <c r="F31" s="2">
-        <v>-2.93</v>
+        <v>-2.27</v>
       </c>
       <c r="G31" s="2">
-        <v>-3.03</v>
+        <v>-3.45</v>
       </c>
       <c r="H31" s="2">
-        <v>-3.35</v>
+        <v>-10.08</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>14000.56</v>
+        <v>26241.6</v>
       </c>
       <c r="K31" s="1">
-        <v>13583.71</v>
+        <v>24699.33</v>
       </c>
       <c r="L31" s="1">
-        <v>14344.89</v>
+        <v>26060.84</v>
       </c>
       <c r="M31" s="3">
-        <v>-243.09</v>
+        <v>-437.51</v>
       </c>
       <c r="N31" s="3">
-        <v>-239.67</v>
+        <v>-449.38</v>
       </c>
       <c r="O31" s="3">
-        <v>-73.08</v>
+        <v>-363.36</v>
       </c>
       <c r="P31" s="3">
-        <v>126.66</v>
+        <v>-70.73</v>
       </c>
       <c r="Q31" s="3">
-        <v>867.29</v>
+        <v>1128.35</v>
       </c>
       <c r="R31" s="3">
-        <v>1000.14</v>
+        <v>1592.4</v>
       </c>
       <c r="S31" s="3">
-        <v>30.58</v>
+        <v>29.59</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2332,58 +2332,58 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C32" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D32" s="1">
-        <v>8302.75</v>
+        <v>23465.05</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.43</v>
+        <v>-0.73</v>
       </c>
       <c r="F32" s="2">
-        <v>-1.72</v>
+        <v>-2.77</v>
       </c>
       <c r="G32" s="2">
-        <v>2.79</v>
+        <v>-1.14</v>
       </c>
       <c r="H32" s="2">
-        <v>-17.34</v>
+        <v>-12.08</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>8772.29</v>
+        <v>25023.62</v>
       </c>
       <c r="K32" s="1">
-        <v>8285.93</v>
+        <v>23729.98</v>
       </c>
       <c r="L32" s="1">
-        <v>8397.69</v>
+        <v>24513.28</v>
       </c>
       <c r="M32" s="3">
-        <v>-9.12</v>
+        <v>-219.95</v>
       </c>
       <c r="N32" s="3">
-        <v>-44.59</v>
+        <v>-255.84</v>
       </c>
       <c r="O32" s="3">
-        <v>-159.89</v>
+        <v>-362.29</v>
       </c>
       <c r="P32" s="3">
-        <v>-158.5</v>
+        <v>-199.92</v>
       </c>
       <c r="Q32" s="3">
-        <v>-305.23</v>
+        <v>310.24</v>
       </c>
       <c r="R32" s="3">
-        <v>-192.37</v>
+        <v>704.22</v>
       </c>
       <c r="S32" s="3">
-        <v>50.84</v>
+        <v>38.79</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2394,58 +2394,58 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C33" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D33" s="1">
-        <v>67354.15</v>
+        <v>15814</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.45</v>
+        <v>-0.77</v>
       </c>
       <c r="F33" s="2">
-        <v>-2.37</v>
+        <v>-4.77</v>
       </c>
       <c r="G33" s="2">
-        <v>-3.43</v>
+        <v>-0.61</v>
       </c>
       <c r="H33" s="2">
-        <v>-2.9</v>
+        <v>-28.11</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>70036.43</v>
+        <v>18368.85</v>
       </c>
       <c r="K33" s="1">
-        <v>68480.5</v>
+        <v>16039.25</v>
       </c>
       <c r="L33" s="1">
-        <v>71667.51</v>
+        <v>17081.63</v>
       </c>
       <c r="M33" s="3">
-        <v>-1029.68</v>
+        <v>-276.62</v>
       </c>
       <c r="N33" s="3">
-        <v>-995.78</v>
+        <v>-352.76</v>
       </c>
       <c r="O33" s="3">
-        <v>-222.32</v>
+        <v>-691.79</v>
       </c>
       <c r="P33" s="3">
-        <v>573.95</v>
+        <v>-515.15</v>
       </c>
       <c r="Q33" s="3">
-        <v>2639.9</v>
+        <v>247.62</v>
       </c>
       <c r="R33" s="3">
-        <v>3177.6</v>
+        <v>923.32</v>
       </c>
       <c r="S33" s="3">
-        <v>32.78</v>
+        <v>41.49</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2456,58 +2456,58 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C34" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D34" s="1">
-        <v>8592.1</v>
+        <v>26656.3</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.49</v>
+        <v>-0.78</v>
       </c>
       <c r="F34" s="2">
-        <v>-1.53</v>
+        <v>-3.77</v>
       </c>
       <c r="G34" s="2">
-        <v>-1.62</v>
+        <v>-0.15</v>
       </c>
       <c r="H34" s="2">
-        <v>-10.65</v>
+        <v>-7.19</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>9226.49</v>
+        <v>27362.11</v>
       </c>
       <c r="K34" s="1">
-        <v>8647.22</v>
+        <v>27050.18</v>
       </c>
       <c r="L34" s="1">
-        <v>9013.05</v>
+        <v>27268.91</v>
       </c>
       <c r="M34" s="3">
-        <v>-113.45</v>
+        <v>-60.86</v>
       </c>
       <c r="N34" s="3">
-        <v>-129.65</v>
+        <v>-42.96</v>
       </c>
       <c r="O34" s="3">
-        <v>-164.24</v>
+        <v>-53.67</v>
       </c>
       <c r="P34" s="3">
-        <v>-79.98</v>
+        <v>14.75</v>
       </c>
       <c r="Q34" s="3">
-        <v>267.04</v>
+        <v>629.95</v>
       </c>
       <c r="R34" s="3">
-        <v>432.8</v>
+        <v>871.88</v>
       </c>
       <c r="S34" s="3">
-        <v>38.96</v>
+        <v>41.15</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2518,58 +2518,58 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D35" s="1">
-        <v>4688.15</v>
+        <v>10365.6</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.49</v>
+        <v>-0.79</v>
       </c>
       <c r="F35" s="2">
-        <v>-2.11</v>
+        <v>-4.79</v>
       </c>
       <c r="G35" s="2">
-        <v>0.09</v>
+        <v>-0.67</v>
       </c>
       <c r="H35" s="2">
-        <v>-9.52</v>
+        <v>-29.49</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>4915.37</v>
+        <v>12171.86</v>
       </c>
       <c r="K35" s="1">
-        <v>4708.88</v>
+        <v>10516.32</v>
       </c>
       <c r="L35" s="1">
-        <v>4867.4</v>
+        <v>11205.53</v>
       </c>
       <c r="M35" s="3">
-        <v>-39.92</v>
+        <v>-184.1</v>
       </c>
       <c r="N35" s="3">
-        <v>-55.19</v>
+        <v>-233.93</v>
       </c>
       <c r="O35" s="3">
-        <v>-51.03</v>
+        <v>-499.42</v>
       </c>
       <c r="P35" s="3">
-        <v>-17.32</v>
+        <v>-388.23</v>
       </c>
       <c r="Q35" s="3">
-        <v>219.58</v>
+        <v>-25.75</v>
       </c>
       <c r="R35" s="3">
-        <v>299.35</v>
+        <v>422.27</v>
       </c>
       <c r="S35" s="3">
-        <v>43.14</v>
+        <v>41.34</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2580,58 +2580,58 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D36" s="1">
-        <v>13757.8</v>
+        <v>15387</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.5</v>
+        <v>-0.83</v>
       </c>
       <c r="F36" s="2">
-        <v>-1.4</v>
+        <v>-1.89</v>
       </c>
       <c r="G36" s="2">
-        <v>3.03</v>
+        <v>-4.65</v>
       </c>
       <c r="H36" s="2">
-        <v>-10.04</v>
+        <v>5.1</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>14394.16</v>
+        <v>15444.88</v>
       </c>
       <c r="K36" s="1">
-        <v>13691.54</v>
+        <v>15655.56</v>
       </c>
       <c r="L36" s="1">
-        <v>14035.63</v>
+        <v>16324.25</v>
       </c>
       <c r="M36" s="3">
-        <v>-53.28</v>
+        <v>-264.42</v>
       </c>
       <c r="N36" s="3">
-        <v>-134.63</v>
+        <v>-219.88</v>
       </c>
       <c r="O36" s="3">
-        <v>-215.28</v>
+        <v>161.13</v>
       </c>
       <c r="P36" s="3">
-        <v>-160.49</v>
+        <v>338.5</v>
       </c>
       <c r="Q36" s="3">
-        <v>-535.2</v>
+        <v>968.83</v>
       </c>
       <c r="R36" s="3">
-        <v>-491.58</v>
+        <v>992.24</v>
       </c>
       <c r="S36" s="3">
-        <v>50.63</v>
+        <v>28.44</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2642,58 +2642,58 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C37" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D37" s="1">
-        <v>23637.8</v>
+        <v>4647.95</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.52</v>
+        <v>-0.86</v>
       </c>
       <c r="F37" s="2">
-        <v>-2.05</v>
+        <v>-2.95</v>
       </c>
       <c r="G37" s="2">
-        <v>-0.41</v>
+        <v>-0.77</v>
       </c>
       <c r="H37" s="2">
-        <v>-11.43</v>
+        <v>-10.29</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>25039.74</v>
+        <v>4912.71</v>
       </c>
       <c r="K37" s="1">
-        <v>23788.85</v>
+        <v>4697.8</v>
       </c>
       <c r="L37" s="1">
-        <v>24556.49</v>
+        <v>4858.01</v>
       </c>
       <c r="M37" s="3">
-        <v>-208.41</v>
+        <v>-41.95</v>
       </c>
       <c r="N37" s="3">
-        <v>-264.81</v>
+        <v>-52.54</v>
       </c>
       <c r="O37" s="3">
-        <v>-348.51</v>
+        <v>-54.23</v>
       </c>
       <c r="P37" s="3">
-        <v>-197.16</v>
+        <v>-17.96</v>
       </c>
       <c r="Q37" s="3">
-        <v>324.02</v>
+        <v>216.38</v>
       </c>
       <c r="R37" s="3">
-        <v>706.97</v>
+        <v>298.7</v>
       </c>
       <c r="S37" s="3">
-        <v>41.65</v>
+        <v>39.8</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2704,58 +2704,58 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D38" s="1">
-        <v>11798.35</v>
+        <v>5878.45</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.52</v>
+        <v>-0.9</v>
       </c>
       <c r="F38" s="2">
-        <v>-2.76</v>
+        <v>-3.08</v>
       </c>
       <c r="G38" s="2">
-        <v>-7.54</v>
+        <v>-5.62</v>
       </c>
       <c r="H38" s="2">
-        <v>5.65</v>
+        <v>-7.65</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>12482.16</v>
+        <v>6742.77</v>
       </c>
       <c r="K38" s="1">
-        <v>12056.55</v>
+        <v>6010.92</v>
       </c>
       <c r="L38" s="1">
-        <v>12837.2</v>
+        <v>6291.9</v>
       </c>
       <c r="M38" s="3">
-        <v>-286.63</v>
+        <v>-105.7</v>
       </c>
       <c r="N38" s="3">
-        <v>-254.92</v>
+        <v>-95.71</v>
       </c>
       <c r="O38" s="3">
-        <v>10.53</v>
+        <v>-209.53</v>
       </c>
       <c r="P38" s="3">
-        <v>208</v>
+        <v>-148.33</v>
       </c>
       <c r="Q38" s="3">
-        <v>1132.92</v>
+        <v>223.11</v>
       </c>
       <c r="R38" s="3">
-        <v>1129.27</v>
+        <v>401.77</v>
       </c>
       <c r="S38" s="3">
-        <v>32.88</v>
+        <v>26.5</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2766,58 +2766,58 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C39" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D39" s="1">
-        <v>5580.35</v>
+        <v>42680.7</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.52</v>
+        <v>-0.99</v>
       </c>
       <c r="F39" s="2">
-        <v>-0.91</v>
+        <v>-4.34</v>
       </c>
       <c r="G39" s="2">
-        <v>1.97</v>
+        <v>-4.11</v>
       </c>
       <c r="H39" s="2">
-        <v>-12.61</v>
+        <v>-23.06</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>5953.06</v>
+        <v>48906.86</v>
       </c>
       <c r="K39" s="1">
-        <v>5550.89</v>
+        <v>43930.43</v>
       </c>
       <c r="L39" s="1">
-        <v>5688.8</v>
+        <v>45760.39</v>
       </c>
       <c r="M39" s="3">
-        <v>-24.75</v>
+        <v>-661.47</v>
       </c>
       <c r="N39" s="3">
-        <v>-55.24</v>
+        <v>-546.4</v>
       </c>
       <c r="O39" s="3">
-        <v>-116.74</v>
+        <v>-1702.06</v>
       </c>
       <c r="P39" s="3">
-        <v>-95.33</v>
+        <v>-1361.49</v>
       </c>
       <c r="Q39" s="3">
-        <v>27.36</v>
+        <v>-2219.83</v>
       </c>
       <c r="R39" s="3">
-        <v>139.95</v>
+        <v>-976.78</v>
       </c>
       <c r="S39" s="3">
-        <v>50.58</v>
+        <v>33.59</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2828,58 +2828,58 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C40" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D40" s="1">
-        <v>22687.65</v>
+        <v>8425</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.54</v>
+        <v>-0.99</v>
       </c>
       <c r="F40" s="2">
-        <v>-1.98</v>
+        <v>-2.83</v>
       </c>
       <c r="G40" s="2">
-        <v>0.3</v>
+        <v>4.96</v>
       </c>
       <c r="H40" s="2">
-        <v>-13.17</v>
+        <v>-10.59</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>24136.49</v>
+        <v>8251.92</v>
       </c>
       <c r="K40" s="1">
-        <v>22779.97</v>
+        <v>8439.22</v>
       </c>
       <c r="L40" s="1">
-        <v>23441.16</v>
+        <v>8527.3</v>
       </c>
       <c r="M40" s="3">
-        <v>-167.07</v>
+        <v>19.93</v>
       </c>
       <c r="N40" s="3">
-        <v>-235.92</v>
+        <v>-27.5</v>
       </c>
       <c r="O40" s="3">
-        <v>-394.06</v>
+        <v>58.7</v>
       </c>
       <c r="P40" s="3">
-        <v>-276.78</v>
+        <v>57.78</v>
       </c>
       <c r="Q40" s="3">
-        <v>184.18</v>
+        <v>365.18</v>
       </c>
       <c r="R40" s="3">
-        <v>597.68</v>
+        <v>512.28</v>
       </c>
       <c r="S40" s="3">
-        <v>43.98</v>
+        <v>50.99</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2890,58 +2890,58 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D41" s="1">
-        <v>16410.8</v>
+        <v>12892.4</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.54</v>
+        <v>-1.02</v>
       </c>
       <c r="F41" s="2">
-        <v>-3.16</v>
+        <v>-3.34</v>
       </c>
       <c r="G41" s="2">
-        <v>-3.63</v>
+        <v>-2.11</v>
       </c>
       <c r="H41" s="2">
-        <v>-4.89</v>
+        <v>-11.29</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>17225.13</v>
+        <v>13785.02</v>
       </c>
       <c r="K41" s="1">
-        <v>16776.16</v>
+        <v>13109.8</v>
       </c>
       <c r="L41" s="1">
-        <v>17679.94</v>
+        <v>13608.22</v>
       </c>
       <c r="M41" s="3">
-        <v>-298.05</v>
+        <v>-149.46</v>
       </c>
       <c r="N41" s="3">
-        <v>-282.47</v>
+        <v>-156.82</v>
       </c>
       <c r="O41" s="3">
-        <v>-62.33</v>
+        <v>-180.45</v>
       </c>
       <c r="P41" s="3">
-        <v>159.12</v>
+        <v>-71.22</v>
       </c>
       <c r="Q41" s="3">
-        <v>887.46</v>
+        <v>255.4</v>
       </c>
       <c r="R41" s="3">
-        <v>1045.73</v>
+        <v>461.47</v>
       </c>
       <c r="S41" s="3">
-        <v>28.89</v>
+        <v>34.9</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2952,58 +2952,58 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D42" s="1">
-        <v>29997.95</v>
+        <v>24403</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.55</v>
+        <v>-1.03</v>
       </c>
       <c r="F42" s="2">
-        <v>-1.59</v>
+        <v>-3.88</v>
       </c>
       <c r="G42" s="2">
-        <v>3.39</v>
+        <v>-1</v>
       </c>
       <c r="H42" s="2">
-        <v>-10.87</v>
+        <v>-11.63</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>30960.55</v>
+        <v>26207.11</v>
       </c>
       <c r="K42" s="1">
-        <v>29796.08</v>
+        <v>24840.22</v>
       </c>
       <c r="L42" s="1">
-        <v>30109.16</v>
+        <v>25484.01</v>
       </c>
       <c r="M42" s="3">
-        <v>7.1</v>
+        <v>-191.42</v>
       </c>
       <c r="N42" s="3">
-        <v>-160.88</v>
+        <v>-187.78</v>
       </c>
       <c r="O42" s="3">
-        <v>-354.53</v>
+        <v>-378.42</v>
       </c>
       <c r="P42" s="3">
-        <v>-316.41</v>
+        <v>-226.96</v>
       </c>
       <c r="Q42" s="3">
-        <v>487.16</v>
+        <v>627.93</v>
       </c>
       <c r="R42" s="3">
-        <v>991.93</v>
+        <v>1077.14</v>
       </c>
       <c r="S42" s="3">
-        <v>53.94</v>
+        <v>37.56</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -3014,58 +3014,58 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C43" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D43" s="1">
-        <v>13316.5</v>
+        <v>25329.45</v>
       </c>
       <c r="E43" s="2">
-        <v>-0.55</v>
+        <v>-1.04</v>
       </c>
       <c r="F43" s="2">
-        <v>-2.31</v>
+        <v>-1.75</v>
       </c>
       <c r="G43" s="2">
-        <v>-3.15</v>
+        <v>-4.19</v>
       </c>
       <c r="H43" s="2">
-        <v>-7.98</v>
+        <v>11.47</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>14149.36</v>
+        <v>24375.25</v>
       </c>
       <c r="K43" s="1">
-        <v>13516.42</v>
+        <v>25744.37</v>
       </c>
       <c r="L43" s="1">
-        <v>14139.31</v>
+        <v>26439.2</v>
       </c>
       <c r="M43" s="3">
-        <v>-205.04</v>
+        <v>-286.8</v>
       </c>
       <c r="N43" s="3">
-        <v>-205.48</v>
+        <v>-206.14</v>
       </c>
       <c r="O43" s="3">
-        <v>-171.3</v>
+        <v>578.03</v>
       </c>
       <c r="P43" s="3">
-        <v>-15.4</v>
+        <v>792.63</v>
       </c>
       <c r="Q43" s="3">
-        <v>70</v>
+        <v>1753.37</v>
       </c>
       <c r="R43" s="3">
-        <v>117.18</v>
+        <v>1603.12</v>
       </c>
       <c r="S43" s="3">
-        <v>32.28</v>
+        <v>32.77</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -3076,58 +3076,58 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D44" s="1">
-        <v>32107.2</v>
+        <v>5302.15</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.56</v>
+        <v>-1.07</v>
       </c>
       <c r="F44" s="2">
-        <v>-2.26</v>
+        <v>-3.1</v>
       </c>
       <c r="G44" s="2">
-        <v>-2.29</v>
+        <v>-0.34</v>
       </c>
       <c r="H44" s="2">
-        <v>-5.44</v>
+        <v>-9.52</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>33688.52</v>
+        <v>5545.89</v>
       </c>
       <c r="K44" s="1">
-        <v>32521.69</v>
+        <v>5364.15</v>
       </c>
       <c r="L44" s="1">
-        <v>33932.23</v>
+        <v>5511.3</v>
       </c>
       <c r="M44" s="3">
-        <v>-431.64</v>
+        <v>-31.66</v>
       </c>
       <c r="N44" s="3">
-        <v>-459.71</v>
+        <v>-45.89</v>
       </c>
       <c r="O44" s="3">
-        <v>-255.98</v>
+        <v>-50.65</v>
       </c>
       <c r="P44" s="3">
-        <v>94.89</v>
+        <v>-18.5</v>
       </c>
       <c r="Q44" s="3">
-        <v>1987.6</v>
+        <v>182.48</v>
       </c>
       <c r="R44" s="3">
-        <v>2427.44</v>
+        <v>260.16</v>
       </c>
       <c r="S44" s="3">
-        <v>34.56</v>
+        <v>41.44</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -3138,58 +3138,58 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C45" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D45" s="1">
-        <v>30563.6</v>
+        <v>13171.4</v>
       </c>
       <c r="E45" s="2">
-        <v>-0.58</v>
+        <v>-1.09</v>
       </c>
       <c r="F45" s="2">
-        <v>-2.04</v>
+        <v>-3.37</v>
       </c>
       <c r="G45" s="2">
-        <v>-1.1</v>
+        <v>-4.21</v>
       </c>
       <c r="H45" s="2">
-        <v>-8.3</v>
+        <v>-8.98</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>32352.54</v>
+        <v>14142.86</v>
       </c>
       <c r="K45" s="1">
-        <v>30812.3</v>
+        <v>13453.69</v>
       </c>
       <c r="L45" s="1">
-        <v>31983.53</v>
+        <v>14109.82</v>
       </c>
       <c r="M45" s="3">
-        <v>-339.37</v>
+        <v>-219.72</v>
       </c>
       <c r="N45" s="3">
-        <v>-403.69</v>
+        <v>-208.32</v>
       </c>
       <c r="O45" s="3">
-        <v>-390.9</v>
+        <v>-182.88</v>
       </c>
       <c r="P45" s="3">
-        <v>-115.25</v>
+        <v>-17.71</v>
       </c>
       <c r="Q45" s="3">
-        <v>1823.26</v>
+        <v>58.43</v>
       </c>
       <c r="R45" s="3">
-        <v>2372.14</v>
+        <v>114.87</v>
       </c>
       <c r="S45" s="3">
-        <v>39.56</v>
+        <v>28.96</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3200,58 +3200,58 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D46" s="1">
-        <v>13025.5</v>
+        <v>13600.85</v>
       </c>
       <c r="E46" s="2">
-        <v>-0.59</v>
+        <v>-1.14</v>
       </c>
       <c r="F46" s="2">
-        <v>-2.34</v>
+        <v>-2.53</v>
       </c>
       <c r="G46" s="2">
-        <v>-1.1</v>
+        <v>1.86</v>
       </c>
       <c r="H46" s="2">
-        <v>-10.38</v>
+        <v>-11.06</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>13793.23</v>
+        <v>14385.7</v>
       </c>
       <c r="K46" s="1">
-        <v>13158.11</v>
+        <v>13675.05</v>
       </c>
       <c r="L46" s="1">
-        <v>13634.56</v>
+        <v>14009.98</v>
       </c>
       <c r="M46" s="3">
-        <v>-137.33</v>
+        <v>-55.41</v>
       </c>
       <c r="N46" s="3">
-        <v>-158.66</v>
+        <v>-118.79</v>
       </c>
       <c r="O46" s="3">
-        <v>-169.83</v>
+        <v>-227.8</v>
       </c>
       <c r="P46" s="3">
-        <v>-69.09</v>
+        <v>-163</v>
       </c>
       <c r="Q46" s="3">
-        <v>266.02</v>
+        <v>-547.72</v>
       </c>
       <c r="R46" s="3">
-        <v>463.6</v>
+        <v>-494.09</v>
       </c>
       <c r="S46" s="3">
-        <v>38.52</v>
+        <v>46.01</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3262,58 +3262,58 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C47" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D47" s="1">
-        <v>7315.1</v>
+        <v>54287.35</v>
       </c>
       <c r="E47" s="2">
-        <v>-0.61</v>
+        <v>-1.16</v>
       </c>
       <c r="F47" s="2">
-        <v>-1.93</v>
+        <v>-2.79</v>
       </c>
       <c r="G47" s="2">
-        <v>3.38</v>
+        <v>-0.63</v>
       </c>
       <c r="H47" s="2">
-        <v>-3.27</v>
+        <v>-8.89</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>7334.84</v>
+        <v>56842.98</v>
       </c>
       <c r="K47" s="1">
-        <v>7296.83</v>
+        <v>55072.04</v>
       </c>
       <c r="L47" s="1">
-        <v>7403.27</v>
+        <v>56259.7</v>
       </c>
       <c r="M47" s="3">
-        <v>-3.14</v>
+        <v>-328.9</v>
       </c>
       <c r="N47" s="3">
-        <v>-39.25</v>
+        <v>-351.4</v>
       </c>
       <c r="O47" s="3">
-        <v>-1.67</v>
+        <v>-402.01</v>
       </c>
       <c r="P47" s="3">
-        <v>31.14</v>
+        <v>-109.29</v>
       </c>
       <c r="Q47" s="3">
-        <v>469.21</v>
+        <v>1610.08</v>
       </c>
       <c r="R47" s="3">
-        <v>552.05</v>
+        <v>2277.6</v>
       </c>
       <c r="S47" s="3">
-        <v>51.36</v>
+        <v>37.74</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3324,58 +3324,58 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D48" s="1">
-        <v>3773.9</v>
+        <v>26195.65</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.61</v>
+        <v>-1.18</v>
       </c>
       <c r="F48" s="2">
-        <v>-2.37</v>
+        <v>-3.73</v>
       </c>
       <c r="G48" s="2">
-        <v>-0.22</v>
+        <v>-1.36</v>
       </c>
       <c r="H48" s="2">
-        <v>-13.31</v>
+        <v>-13.2</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>4034.76</v>
+        <v>28527.81</v>
       </c>
       <c r="K48" s="1">
-        <v>3797.44</v>
+        <v>26693.86</v>
       </c>
       <c r="L48" s="1">
-        <v>3925.14</v>
+        <v>27555.3</v>
       </c>
       <c r="M48" s="3">
-        <v>-34.14</v>
+        <v>-260.62</v>
       </c>
       <c r="N48" s="3">
-        <v>-44.95</v>
+        <v>-263.46</v>
       </c>
       <c r="O48" s="3">
-        <v>-67.44</v>
+        <v>-507.71</v>
       </c>
       <c r="P48" s="3">
-        <v>-42.77</v>
+        <v>-301.14</v>
       </c>
       <c r="Q48" s="3">
-        <v>124.74</v>
+        <v>1281.95</v>
       </c>
       <c r="R48" s="3">
-        <v>206.47</v>
+        <v>1894.3</v>
       </c>
       <c r="S48" s="3">
-        <v>42.18</v>
+        <v>36</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3386,58 +3386,58 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D49" s="1">
-        <v>14747.95</v>
+        <v>47649.75</v>
       </c>
       <c r="E49" s="2">
-        <v>-0.63</v>
+        <v>-1.19</v>
       </c>
       <c r="F49" s="2">
-        <v>-2.81</v>
+        <v>-3.34</v>
       </c>
       <c r="G49" s="2">
-        <v>-4.57</v>
+        <v>-6.53</v>
       </c>
       <c r="H49" s="2">
-        <v>-4.31</v>
+        <v>8.63</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>15629.87</v>
+        <v>47357.97</v>
       </c>
       <c r="K49" s="1">
-        <v>15042.09</v>
+        <v>49051.9</v>
       </c>
       <c r="L49" s="1">
-        <v>15889.62</v>
+        <v>51443.8</v>
       </c>
       <c r="M49" s="3">
-        <v>-276.58</v>
+        <v>-970.56</v>
       </c>
       <c r="N49" s="3">
-        <v>-266.49</v>
+        <v>-714.55</v>
       </c>
       <c r="O49" s="3">
-        <v>-100.76</v>
+        <v>889.87</v>
       </c>
       <c r="P49" s="3">
-        <v>100.11</v>
+        <v>1550.96</v>
       </c>
       <c r="Q49" s="3">
-        <v>1239.5</v>
+        <v>2100.85</v>
       </c>
       <c r="R49" s="3">
-        <v>1442.38</v>
+        <v>1457.74</v>
       </c>
       <c r="S49" s="3">
-        <v>30.01</v>
+        <v>23.92</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3454,52 +3454,52 @@
         <v>NIFTY500</v>
       </c>
       <c r="D50" s="1">
-        <v>21696.55</v>
+        <v>21427.6</v>
       </c>
       <c r="E50" s="2">
-        <v>-0.65</v>
+        <v>-1.24</v>
       </c>
       <c r="F50" s="2">
-        <v>-2.58</v>
+        <v>-3.78</v>
       </c>
       <c r="G50" s="2">
-        <v>-1.7</v>
+        <v>-2.92</v>
       </c>
       <c r="H50" s="2">
-        <v>-9.11</v>
+        <v>-10.24</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>22844.26</v>
+        <v>22832.04</v>
       </c>
       <c r="K50" s="1">
-        <v>21982.64</v>
+        <v>21881.73</v>
       </c>
       <c r="L50" s="1">
-        <v>22790.7</v>
+        <v>22745.63</v>
       </c>
       <c r="M50" s="3">
-        <v>-243.31</v>
+        <v>-271.94</v>
       </c>
       <c r="N50" s="3">
-        <v>-261.83</v>
+        <v>-263.85</v>
       </c>
       <c r="O50" s="3">
-        <v>-220.21</v>
+        <v>-241.67</v>
       </c>
       <c r="P50" s="3">
-        <v>-41.24</v>
+        <v>-45.53</v>
       </c>
       <c r="Q50" s="3">
-        <v>506.21</v>
+        <v>484.75</v>
       </c>
       <c r="R50" s="3">
-        <v>803.19</v>
+        <v>798.9</v>
       </c>
       <c r="S50" s="3">
-        <v>36.02</v>
+        <v>31.86</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3510,58 +3510,58 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D51" s="1">
-        <v>15423.75</v>
+        <v>5510.75</v>
       </c>
       <c r="E51" s="2">
-        <v>-0.66</v>
+        <v>-1.25</v>
       </c>
       <c r="F51" s="2">
-        <v>-2.65</v>
+        <v>-2.14</v>
       </c>
       <c r="G51" s="2">
-        <v>-2.12</v>
+        <v>0.7</v>
       </c>
       <c r="H51" s="2">
-        <v>-8.49</v>
+        <v>-13.7</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>16295.33</v>
+        <v>5948.69</v>
       </c>
       <c r="K51" s="1">
-        <v>15655.11</v>
+        <v>5543.59</v>
       </c>
       <c r="L51" s="1">
-        <v>16306.59</v>
+        <v>5678.67</v>
       </c>
       <c r="M51" s="3">
-        <v>-200.8</v>
+        <v>-25.74</v>
       </c>
       <c r="N51" s="3">
-        <v>-209.43</v>
+        <v>-49.34</v>
       </c>
       <c r="O51" s="3">
-        <v>-153.74</v>
+        <v>-122.29</v>
       </c>
       <c r="P51" s="3">
-        <v>-3.46</v>
+        <v>-96.45</v>
       </c>
       <c r="Q51" s="3">
-        <v>908.97</v>
+        <v>21.8</v>
       </c>
       <c r="R51" s="3">
-        <v>1177.28</v>
+        <v>138.84</v>
       </c>
       <c r="S51" s="3">
-        <v>34.01</v>
+        <v>44.76</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3572,58 +3572,58 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>Nifty Total Market</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D52" s="1">
-        <v>12262.9</v>
+        <v>7356.85</v>
       </c>
       <c r="E52" s="2">
-        <v>-0.66</v>
+        <v>-1.28</v>
       </c>
       <c r="F52" s="2">
-        <v>-2.69</v>
+        <v>-2.75</v>
       </c>
       <c r="G52" s="2">
-        <v>-1.94</v>
+        <v>-4.51</v>
       </c>
       <c r="H52" s="2">
-        <v>-8.44</v>
+        <v>-14.5</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>12863.13</v>
+        <v>7679.73</v>
       </c>
       <c r="K52" s="1">
-        <v>12437.59</v>
+        <v>7468.9</v>
       </c>
       <c r="L52" s="1">
-        <v>12890.41</v>
+        <v>7753.04</v>
       </c>
       <c r="M52" s="3">
-        <v>-138.27</v>
+        <v>-96.56</v>
       </c>
       <c r="N52" s="3">
-        <v>-144.94</v>
+        <v>-90.05</v>
       </c>
       <c r="O52" s="3">
-        <v>-102.9</v>
+        <v>-67.85</v>
       </c>
       <c r="P52" s="3">
-        <v>-0.09</v>
+        <v>-18.85</v>
       </c>
       <c r="Q52" s="3">
-        <v>623.8</v>
+        <v>-305.65</v>
       </c>
       <c r="R52" s="3">
-        <v>824.84</v>
+        <v>-248.31</v>
       </c>
       <c r="S52" s="3">
-        <v>35.29</v>
+        <v>38.25</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3634,58 +3634,58 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C53" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D53" s="1">
-        <v>10916.2</v>
+        <v>12105.3</v>
       </c>
       <c r="E53" s="2">
-        <v>-0.66</v>
+        <v>-1.29</v>
       </c>
       <c r="F53" s="2">
-        <v>-0.99</v>
+        <v>-3.94</v>
       </c>
       <c r="G53" s="2">
-        <v>3.57</v>
+        <v>-3.2</v>
       </c>
       <c r="H53" s="2">
-        <v>-12.56</v>
+        <v>-9.62</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>11224.6</v>
+        <v>12856.69</v>
       </c>
       <c r="K53" s="1">
-        <v>10794.02</v>
+        <v>12377.17</v>
       </c>
       <c r="L53" s="1">
-        <v>11086.78</v>
+        <v>12865.16</v>
       </c>
       <c r="M53" s="3">
-        <v>-34.31</v>
+        <v>-155.97</v>
       </c>
       <c r="N53" s="3">
-        <v>-118</v>
+        <v>-147.15</v>
       </c>
       <c r="O53" s="3">
-        <v>-112.43</v>
+        <v>-115.47</v>
       </c>
       <c r="P53" s="3">
-        <v>-75.61</v>
+        <v>-2.6</v>
       </c>
       <c r="Q53" s="3">
-        <v>33.61</v>
+        <v>611.22</v>
       </c>
       <c r="R53" s="3">
-        <v>176.96</v>
+        <v>822.32</v>
       </c>
       <c r="S53" s="3">
-        <v>54.05</v>
+        <v>31.07</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3696,58 +3696,58 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C54" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D54" s="1">
-        <v>9034.35</v>
+        <v>1563.4</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.66</v>
+        <v>-1.33</v>
       </c>
       <c r="F54" s="2">
-        <v>-2.3</v>
+        <v>-5.15</v>
       </c>
       <c r="G54" s="2">
-        <v>-3.48</v>
+        <v>-1.25</v>
       </c>
       <c r="H54" s="2">
-        <v>-8.31</v>
+        <v>8.22</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>9989.14</v>
+        <v>1469.5</v>
       </c>
       <c r="K54" s="1">
-        <v>9175.85</v>
+        <v>1600.49</v>
       </c>
       <c r="L54" s="1">
-        <v>9538.32</v>
+        <v>1574.14</v>
       </c>
       <c r="M54" s="3">
-        <v>-126.37</v>
+        <v>13.19</v>
       </c>
       <c r="N54" s="3">
-        <v>-125.98</v>
+        <v>14.44</v>
       </c>
       <c r="O54" s="3">
-        <v>-232.48</v>
+        <v>30.99</v>
       </c>
       <c r="P54" s="3">
-        <v>-147.76</v>
+        <v>31.31</v>
       </c>
       <c r="Q54" s="3">
-        <v>787.92</v>
+        <v>-74.96</v>
       </c>
       <c r="R54" s="3">
-        <v>1091.01</v>
+        <v>-105.89</v>
       </c>
       <c r="S54" s="3">
-        <v>32.69</v>
+        <v>46.1</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3758,58 +3758,58 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D55" s="1">
-        <v>11320.85</v>
+        <v>15209.55</v>
       </c>
       <c r="E55" s="2">
-        <v>-0.71</v>
+        <v>-1.39</v>
       </c>
       <c r="F55" s="2">
-        <v>-1.83</v>
+        <v>-4</v>
       </c>
       <c r="G55" s="2">
-        <v>1.58</v>
+        <v>-3.48</v>
       </c>
       <c r="H55" s="2">
-        <v>-14.72</v>
+        <v>-9.76</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>12181.48</v>
+        <v>16287.1</v>
       </c>
       <c r="K55" s="1">
-        <v>11325.87</v>
+        <v>15574.1</v>
       </c>
       <c r="L55" s="1">
-        <v>11553.89</v>
+        <v>16271.59</v>
       </c>
       <c r="M55" s="3">
-        <v>-44.11</v>
+        <v>-223.57</v>
       </c>
       <c r="N55" s="3">
-        <v>-90.47</v>
+        <v>-212.26</v>
       </c>
       <c r="O55" s="3">
-        <v>-264.44</v>
+        <v>-170.83</v>
       </c>
       <c r="P55" s="3">
-        <v>-235.71</v>
+        <v>-6.87</v>
       </c>
       <c r="Q55" s="3">
-        <v>-130.42</v>
+        <v>891.89</v>
       </c>
       <c r="R55" s="3">
-        <v>114.35</v>
+        <v>1173.87</v>
       </c>
       <c r="S55" s="3">
-        <v>47.77</v>
+        <v>29.7</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3820,58 +3820,58 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C56" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D56" s="1">
-        <v>25011.5</v>
+        <v>8792.3</v>
       </c>
       <c r="E56" s="2">
-        <v>-0.73</v>
+        <v>-1.41</v>
       </c>
       <c r="F56" s="2">
-        <v>-2.94</v>
+        <v>-3.38</v>
       </c>
       <c r="G56" s="2">
-        <v>-4.88</v>
+        <v>-5.56</v>
       </c>
       <c r="H56" s="2">
-        <v>-11.27</v>
+        <v>-7.6</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>26928.44</v>
+        <v>9757.44</v>
       </c>
       <c r="K56" s="1">
-        <v>25375.52</v>
+        <v>8981.6</v>
       </c>
       <c r="L56" s="1">
-        <v>27260.53</v>
+        <v>9476.27</v>
       </c>
       <c r="M56" s="3">
-        <v>-546.04</v>
+        <v>-170.17</v>
       </c>
       <c r="N56" s="3">
-        <v>-613.46</v>
+        <v>-167.85</v>
       </c>
       <c r="O56" s="3">
-        <v>-297.05</v>
+        <v>-193.2</v>
       </c>
       <c r="P56" s="3">
-        <v>93.49</v>
+        <v>-68.85</v>
       </c>
       <c r="Q56" s="3">
-        <v>1461.1</v>
+        <v>377.04</v>
       </c>
       <c r="R56" s="3">
-        <v>1807.72</v>
+        <v>505.77</v>
       </c>
       <c r="S56" s="3">
-        <v>35.68</v>
+        <v>29.94</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3882,58 +3882,58 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C57" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D57" s="1">
-        <v>15358.1</v>
+        <v>18680</v>
       </c>
       <c r="E57" s="2">
-        <v>-0.73</v>
+        <v>-1.42</v>
       </c>
       <c r="F57" s="2">
-        <v>-2.94</v>
+        <v>-4.06</v>
       </c>
       <c r="G57" s="2">
-        <v>-2.49</v>
+        <v>-1.39</v>
       </c>
       <c r="H57" s="2">
-        <v>-6.84</v>
+        <v>-12.75</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>16020.38</v>
+        <v>20086.53</v>
       </c>
       <c r="K57" s="1">
-        <v>15628.43</v>
+        <v>19063.77</v>
       </c>
       <c r="L57" s="1">
-        <v>16221.84</v>
+        <v>19769.3</v>
       </c>
       <c r="M57" s="3">
-        <v>-188.13</v>
+        <v>-183.77</v>
       </c>
       <c r="N57" s="3">
-        <v>-184.94</v>
+        <v>-210.33</v>
       </c>
       <c r="O57" s="3">
-        <v>-83.45</v>
+        <v>-303.22</v>
       </c>
       <c r="P57" s="3">
-        <v>59.95</v>
+        <v>-146.4</v>
       </c>
       <c r="Q57" s="3">
-        <v>909.74</v>
+        <v>462.8</v>
       </c>
       <c r="R57" s="3">
-        <v>1146.63</v>
+        <v>790.61</v>
       </c>
       <c r="S57" s="3">
-        <v>32.51</v>
+        <v>36.05</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3944,58 +3944,58 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D58" s="1">
-        <v>10753.25</v>
+        <v>15081.85</v>
       </c>
       <c r="E58" s="2">
-        <v>-0.74</v>
+        <v>-1.44</v>
       </c>
       <c r="F58" s="2">
-        <v>-2.73</v>
+        <v>-4.47</v>
       </c>
       <c r="G58" s="2">
-        <v>-2.88</v>
+        <v>-5.84</v>
       </c>
       <c r="H58" s="2">
-        <v>-12.5</v>
+        <v>-5.59</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>11496.75</v>
+        <v>16004.23</v>
       </c>
       <c r="K58" s="1">
-        <v>10918.53</v>
+        <v>15527.97</v>
       </c>
       <c r="L58" s="1">
-        <v>11476.92</v>
+        <v>16383.51</v>
       </c>
       <c r="M58" s="3">
-        <v>-172.14</v>
+        <v>-288.64</v>
       </c>
       <c r="N58" s="3">
-        <v>-181.33</v>
+        <v>-254.72</v>
       </c>
       <c r="O58" s="3">
-        <v>-157.54</v>
+        <v>-70.03</v>
       </c>
       <c r="P58" s="3">
-        <v>-42.75</v>
+        <v>131.46</v>
       </c>
       <c r="Q58" s="3">
-        <v>210.77</v>
+        <v>333.27</v>
       </c>
       <c r="R58" s="3">
-        <v>392.82</v>
+        <v>323.55</v>
       </c>
       <c r="S58" s="3">
-        <v>35.09</v>
+        <v>26.71</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -4006,58 +4006,58 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D59" s="1">
-        <v>27994.55</v>
+        <v>31640.45</v>
       </c>
       <c r="E59" s="2">
-        <v>-0.77</v>
+        <v>-1.45</v>
       </c>
       <c r="F59" s="2">
-        <v>-3.77</v>
+        <v>-3.68</v>
       </c>
       <c r="G59" s="2">
-        <v>-5.16</v>
+        <v>-3.71</v>
       </c>
       <c r="H59" s="2">
-        <v>-10.12</v>
+        <v>-6.82</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>30385.86</v>
+        <v>33676.94</v>
       </c>
       <c r="K59" s="1">
-        <v>28874.88</v>
+        <v>32361.46</v>
       </c>
       <c r="L59" s="1">
-        <v>30272.63</v>
+        <v>33854.46</v>
       </c>
       <c r="M59" s="3">
-        <v>-496.07</v>
+        <v>-474.3</v>
       </c>
       <c r="N59" s="3">
-        <v>-396.55</v>
+        <v>-462.62</v>
       </c>
       <c r="O59" s="3">
-        <v>-375.6</v>
+        <v>-293.22</v>
       </c>
       <c r="P59" s="3">
-        <v>-93.58</v>
+        <v>87.44</v>
       </c>
       <c r="Q59" s="3">
-        <v>1416.82</v>
+        <v>1950.37</v>
       </c>
       <c r="R59" s="3">
-        <v>1993.08</v>
+        <v>2419.99</v>
       </c>
       <c r="S59" s="3">
-        <v>27.89</v>
+        <v>29.92</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -4068,58 +4068,58 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D60" s="1">
-        <v>24289.25</v>
+        <v>15117.8</v>
       </c>
       <c r="E60" s="2">
-        <v>-0.8</v>
+        <v>-1.56</v>
       </c>
       <c r="F60" s="2">
-        <v>-3.63</v>
+        <v>-4.46</v>
       </c>
       <c r="G60" s="2">
-        <v>-4.35</v>
+        <v>-4.02</v>
       </c>
       <c r="H60" s="2">
-        <v>-2.79</v>
+        <v>-8.29</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>25473.04</v>
+        <v>16013.54</v>
       </c>
       <c r="K60" s="1">
-        <v>24995.85</v>
+        <v>15535.59</v>
       </c>
       <c r="L60" s="1">
-        <v>26172.53</v>
+        <v>16188.45</v>
       </c>
       <c r="M60" s="3">
-        <v>-401.97</v>
+        <v>-217.14</v>
       </c>
       <c r="N60" s="3">
-        <v>-333.75</v>
+        <v>-191.38</v>
       </c>
       <c r="O60" s="3">
-        <v>-62.14</v>
+        <v>-102.62</v>
       </c>
       <c r="P60" s="3">
-        <v>214.66</v>
+        <v>56.11</v>
       </c>
       <c r="Q60" s="3">
-        <v>51.49</v>
+        <v>890.57</v>
       </c>
       <c r="R60" s="3">
-        <v>-58.15</v>
+        <v>1142.8</v>
       </c>
       <c r="S60" s="3">
-        <v>30.08</v>
+        <v>27.82</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -4130,58 +4130,58 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D61" s="1">
-        <v>21028.65</v>
+        <v>14516.75</v>
       </c>
       <c r="E61" s="2">
-        <v>-0.81</v>
+        <v>-1.57</v>
       </c>
       <c r="F61" s="2">
-        <v>-3.26</v>
+        <v>-4.33</v>
       </c>
       <c r="G61" s="2">
-        <v>-3.84</v>
+        <v>-6.07</v>
       </c>
       <c r="H61" s="2">
-        <v>-5.6</v>
+        <v>-5.81</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>22185.05</v>
+        <v>15625.39</v>
       </c>
       <c r="K61" s="1">
-        <v>21532.07</v>
+        <v>14946.58</v>
       </c>
       <c r="L61" s="1">
-        <v>22632.09</v>
+        <v>15847.78</v>
       </c>
       <c r="M61" s="3">
-        <v>-365.06</v>
+        <v>-301.4</v>
       </c>
       <c r="N61" s="3">
-        <v>-336.93</v>
+        <v>-273.48</v>
       </c>
       <c r="O61" s="3">
-        <v>-118</v>
+        <v>-119.2</v>
       </c>
       <c r="P61" s="3">
-        <v>155.21</v>
+        <v>96.42</v>
       </c>
       <c r="Q61" s="3">
-        <v>1689.03</v>
+        <v>1221.05</v>
       </c>
       <c r="R61" s="3">
-        <v>2024.42</v>
+        <v>1438.69</v>
       </c>
       <c r="S61" s="3">
-        <v>27.99</v>
+        <v>26.18</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4192,58 +4192,58 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C62" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D62" s="1">
-        <v>26950.65</v>
+        <v>8885.75</v>
       </c>
       <c r="E62" s="2">
-        <v>-0.83</v>
+        <v>-1.64</v>
       </c>
       <c r="F62" s="2">
-        <v>-4.98</v>
+        <v>-3.91</v>
       </c>
       <c r="G62" s="2">
-        <v>-4.98</v>
-      </c>
-      <c r="H62" t="str">
-        <v/>
+        <v>-5.07</v>
+      </c>
+      <c r="H62" s="2">
+        <v>-9.82</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
-      <c r="J62" t="str">
-        <v/>
+      <c r="J62" s="1">
+        <v>9984.3</v>
       </c>
       <c r="K62" s="1">
-        <v>27885.71</v>
+        <v>9123.11</v>
       </c>
       <c r="L62" s="1">
-        <v>29325.74</v>
+        <v>9519.4</v>
       </c>
       <c r="M62" s="3">
-        <v>-485.79</v>
+        <v>-141.61</v>
       </c>
       <c r="N62" s="3">
-        <v>-417.2</v>
+        <v>-129.11</v>
       </c>
       <c r="O62" s="3">
-        <v>-206.91</v>
+        <v>-244.33</v>
       </c>
       <c r="P62" s="3">
-        <v>168.33</v>
+        <v>-150.14</v>
       </c>
       <c r="Q62" s="3">
-        <v>205.94</v>
+        <v>776.06</v>
       </c>
       <c r="R62" s="3">
-        <v>182.47</v>
+        <v>1088.64</v>
       </c>
       <c r="S62" s="3">
-        <v>29.3</v>
+        <v>27.83</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4254,58 +4254,58 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C63" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D63" s="1">
-        <v>15302.2</v>
+        <v>34520.05</v>
       </c>
       <c r="E63" s="2">
-        <v>-0.84</v>
+        <v>-1.66</v>
       </c>
       <c r="F63" s="2">
-        <v>-3.07</v>
+        <v>-4.62</v>
       </c>
       <c r="G63" s="2">
-        <v>-4.46</v>
+        <v>-5.78</v>
       </c>
       <c r="H63" s="2">
-        <v>-4.21</v>
+        <v>-2.28</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>16008.69</v>
+        <v>37722.41</v>
       </c>
       <c r="K63" s="1">
-        <v>15627.1</v>
+        <v>35665.35</v>
       </c>
       <c r="L63" s="1">
-        <v>16423.41</v>
+        <v>37328.98</v>
       </c>
       <c r="M63" s="3">
-        <v>-261.16</v>
+        <v>-621.4</v>
       </c>
       <c r="N63" s="3">
-        <v>-246.24</v>
+        <v>-515.77</v>
       </c>
       <c r="O63" s="3">
-        <v>-52.45</v>
+        <v>-592.5</v>
       </c>
       <c r="P63" s="3">
-        <v>134.97</v>
+        <v>-87.54</v>
       </c>
       <c r="Q63" s="3">
-        <v>350.85</v>
+        <v>889.89</v>
       </c>
       <c r="R63" s="3">
-        <v>327.06</v>
+        <v>1219.3</v>
       </c>
       <c r="S63" s="3">
-        <v>30.31</v>
+        <v>24.93</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4316,58 +4316,58 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C64" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D64" s="1">
-        <v>10445.65</v>
+        <v>27765.7</v>
       </c>
       <c r="E64" s="2">
-        <v>-0.86</v>
+        <v>-1.96</v>
       </c>
       <c r="F64" s="2">
-        <v>-1.05</v>
+        <v>-5.93</v>
       </c>
       <c r="G64" s="2">
-        <v>-1.59</v>
+        <v>-8.47</v>
       </c>
       <c r="H64" s="2">
-        <v>-14.6</v>
+        <v>-9.17</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>11300.75</v>
+        <v>31386.59</v>
       </c>
       <c r="K64" s="1">
-        <v>10508.99</v>
+        <v>29044.94</v>
       </c>
       <c r="L64" s="1">
-        <v>10888.56</v>
+        <v>31421.13</v>
       </c>
       <c r="M64" s="3">
-        <v>-118.1</v>
+        <v>-832.31</v>
       </c>
       <c r="N64" s="3">
-        <v>-137.62</v>
+        <v>-698.23</v>
       </c>
       <c r="O64" s="3">
-        <v>-225.23</v>
+        <v>-522.2</v>
       </c>
       <c r="P64" s="3">
-        <v>-160.25</v>
+        <v>61.35</v>
       </c>
       <c r="Q64" s="3">
-        <v>73.22</v>
+        <v>1921.26</v>
       </c>
       <c r="R64" s="3">
-        <v>279.44</v>
+        <v>2384.15</v>
       </c>
       <c r="S64" s="3">
-        <v>39.39</v>
+        <v>19.44</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4378,58 +4378,58 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C65" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D65" s="1">
-        <v>57063.95</v>
+        <v>56812.1</v>
       </c>
       <c r="E65" s="2">
-        <v>-0.87</v>
+        <v>-2.05</v>
       </c>
       <c r="F65" s="2">
-        <v>-3.49</v>
+        <v>-5.73</v>
       </c>
       <c r="G65" s="2">
-        <v>-3.82</v>
+        <v>-6.52</v>
       </c>
       <c r="H65" s="2">
-        <v>-5.66</v>
+        <v>-8.24</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>60318.63</v>
+        <v>61702.99</v>
       </c>
       <c r="K65" s="1">
-        <v>58531.39</v>
+        <v>59262.32</v>
       </c>
       <c r="L65" s="1">
-        <v>61577.64</v>
+        <v>62465.58</v>
       </c>
       <c r="M65" s="3">
-        <v>-1005.14</v>
+        <v>-1173.13</v>
       </c>
       <c r="N65" s="3">
-        <v>-923.66</v>
+        <v>-867.23</v>
       </c>
       <c r="O65" s="3">
-        <v>-338.45</v>
+        <v>-508.97</v>
       </c>
       <c r="P65" s="3">
-        <v>416.39</v>
+        <v>188.66</v>
       </c>
       <c r="Q65" s="3">
-        <v>2828.77</v>
+        <v>-248.68</v>
       </c>
       <c r="R65" s="3">
-        <v>3471.67</v>
+        <v>-222.67</v>
       </c>
       <c r="S65" s="3">
-        <v>28.36</v>
+        <v>22.73</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4440,58 +4440,58 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C66" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D66" s="1">
-        <v>5359.5</v>
+        <v>20592.75</v>
       </c>
       <c r="E66" s="2">
-        <v>-0.88</v>
+        <v>-2.07</v>
       </c>
       <c r="F66" s="2">
-        <v>-2.06</v>
+        <v>-5.26</v>
       </c>
       <c r="G66" s="2">
-        <v>0.74</v>
+        <v>-5.83</v>
       </c>
       <c r="H66" s="2">
-        <v>-8.54</v>
+        <v>-7.56</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>5548.68</v>
+        <v>22176.63</v>
       </c>
       <c r="K66" s="1">
-        <v>5377.93</v>
+        <v>21361.29</v>
       </c>
       <c r="L66" s="1">
-        <v>5521.35</v>
+        <v>22574.75</v>
       </c>
       <c r="M66" s="3">
-        <v>-27.83</v>
+        <v>-417.73</v>
       </c>
       <c r="N66" s="3">
-        <v>-49.45</v>
+        <v>-353.09</v>
       </c>
       <c r="O66" s="3">
-        <v>-46.07</v>
+        <v>-152.78</v>
       </c>
       <c r="P66" s="3">
-        <v>-17.59</v>
+        <v>148.25</v>
       </c>
       <c r="Q66" s="3">
-        <v>187.05</v>
+        <v>1654.26</v>
       </c>
       <c r="R66" s="3">
-        <v>261.07</v>
+        <v>2017.46</v>
       </c>
       <c r="S66" s="3">
-        <v>45.73</v>
+        <v>23.29</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4502,58 +4502,58 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D67" s="1">
-        <v>19526.1</v>
+        <v>16066.4</v>
       </c>
       <c r="E67" s="2">
-        <v>-0.91</v>
+        <v>-2.1</v>
       </c>
       <c r="F67" s="2">
-        <v>-3.67</v>
+        <v>-5.19</v>
       </c>
       <c r="G67" s="2">
-        <v>-4.35</v>
+        <v>-5.65</v>
       </c>
       <c r="H67" s="2">
-        <v>-3.42</v>
+        <v>-6.88</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>20265.32</v>
+        <v>17219.19</v>
       </c>
       <c r="K67" s="1">
-        <v>20067.01</v>
+        <v>16647.11</v>
       </c>
       <c r="L67" s="1">
-        <v>20992.81</v>
+        <v>17635.02</v>
       </c>
       <c r="M67" s="3">
-        <v>-318.95</v>
+        <v>-336.34</v>
       </c>
       <c r="N67" s="3">
-        <v>-271.58</v>
+        <v>-293.24</v>
       </c>
       <c r="O67" s="3">
-        <v>5.54</v>
+        <v>-89.81</v>
       </c>
       <c r="P67" s="3">
-        <v>246.97</v>
+        <v>153.62</v>
       </c>
       <c r="Q67" s="3">
-        <v>1558.91</v>
+        <v>859.98</v>
       </c>
       <c r="R67" s="3">
-        <v>1819.52</v>
+        <v>1040.24</v>
       </c>
       <c r="S67" s="3">
-        <v>27.36</v>
+        <v>24.09</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4564,58 +4564,58 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D68" s="1">
-        <v>58001.55</v>
+        <v>13033.05</v>
       </c>
       <c r="E68" s="2">
-        <v>-0.93</v>
+        <v>-2.12</v>
       </c>
       <c r="F68" s="2">
-        <v>-3.76</v>
+        <v>-4.99</v>
       </c>
       <c r="G68" s="2">
-        <v>-4.56</v>
+        <v>-5.08</v>
       </c>
       <c r="H68" s="2">
-        <v>-6.32</v>
+        <v>-5.4</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>61728.51</v>
+        <v>13996.84</v>
       </c>
       <c r="K68" s="1">
-        <v>59806.81</v>
+        <v>13483.59</v>
       </c>
       <c r="L68" s="1">
-        <v>62611.84</v>
+        <v>14305.74</v>
       </c>
       <c r="M68" s="3">
-        <v>-992.06</v>
+        <v>-271.86</v>
       </c>
       <c r="N68" s="3">
-        <v>-790.76</v>
+        <v>-246.11</v>
       </c>
       <c r="O68" s="3">
-        <v>-414.08</v>
+        <v>-95.59</v>
       </c>
       <c r="P68" s="3">
-        <v>207.64</v>
+        <v>122.16</v>
       </c>
       <c r="Q68" s="3">
-        <v>-153.8</v>
+        <v>844.78</v>
       </c>
       <c r="R68" s="3">
-        <v>-203.69</v>
+        <v>995.64</v>
       </c>
       <c r="S68" s="3">
-        <v>26.84</v>
+        <v>25.6</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4626,58 +4626,58 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D69" s="1">
-        <v>5931.85</v>
+        <v>21727.8</v>
       </c>
       <c r="E69" s="2">
-        <v>-0.93</v>
+        <v>-2.14</v>
       </c>
       <c r="F69" s="2">
-        <v>-2.2</v>
+        <v>-5.39</v>
       </c>
       <c r="G69" s="2">
-        <v>-4.77</v>
+        <v>-4.56</v>
       </c>
       <c r="H69" s="2">
-        <v>-6.81</v>
+        <v>-9.69</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>6745.2</v>
+        <v>23481.91</v>
       </c>
       <c r="K69" s="1">
-        <v>6040.35</v>
+        <v>22531.45</v>
       </c>
       <c r="L69" s="1">
-        <v>6303.72</v>
+        <v>23665.6</v>
       </c>
       <c r="M69" s="3">
-        <v>-98.85</v>
+        <v>-367.53</v>
       </c>
       <c r="N69" s="3">
-        <v>-93.21</v>
+        <v>-312.41</v>
       </c>
       <c r="O69" s="3">
-        <v>-205.27</v>
+        <v>-256.55</v>
       </c>
       <c r="P69" s="3">
-        <v>-147.47</v>
+        <v>20.79</v>
       </c>
       <c r="Q69" s="3">
-        <v>227.37</v>
+        <v>963.56</v>
       </c>
       <c r="R69" s="3">
-        <v>402.62</v>
+        <v>1347.55</v>
       </c>
       <c r="S69" s="3">
-        <v>29.08</v>
+        <v>26.17</v>
       </c>
       <c r="T69" t="str">
         <v/>
@@ -4694,52 +4694,52 @@
         <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D70" s="1">
-        <v>47831.05</v>
+        <v>46788.25</v>
       </c>
       <c r="E70" s="2">
-        <v>-0.94</v>
+        <v>-2.18</v>
       </c>
       <c r="F70" s="2">
-        <v>-3.58</v>
+        <v>-5.68</v>
       </c>
       <c r="G70" s="2">
-        <v>-3.52</v>
+        <v>-5.62</v>
       </c>
       <c r="H70" s="2">
-        <v>0.56</v>
+        <v>-1.63</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>49081.09</v>
+        <v>49077.2</v>
       </c>
       <c r="K70" s="1">
-        <v>49114.54</v>
+        <v>48691.57</v>
       </c>
       <c r="L70" s="1">
-        <v>50872.21</v>
+        <v>50765.67</v>
       </c>
       <c r="M70" s="3">
-        <v>-592.98</v>
+        <v>-743.9</v>
       </c>
       <c r="N70" s="3">
-        <v>-474.16</v>
+        <v>-528.11</v>
       </c>
       <c r="O70" s="3">
-        <v>80.16</v>
+        <v>-3.03</v>
       </c>
       <c r="P70" s="3">
-        <v>552.91</v>
+        <v>536.27</v>
       </c>
       <c r="Q70" s="3">
-        <v>24.86</v>
+        <v>-58.33</v>
       </c>
       <c r="R70" s="3">
-        <v>-306.19</v>
+        <v>-322.83</v>
       </c>
       <c r="S70" s="3">
-        <v>29.88</v>
+        <v>24.75</v>
       </c>
       <c r="T70" t="str">
         <v/>
@@ -4750,58 +4750,58 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C71" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D71" s="1">
-        <v>15438.55</v>
+        <v>55800.65</v>
       </c>
       <c r="E71" s="2">
-        <v>-0.95</v>
+        <v>-2.21</v>
       </c>
       <c r="F71" s="2">
-        <v>-3.93</v>
+        <v>-5.63</v>
       </c>
       <c r="G71" s="2">
-        <v>-5.22</v>
+        <v>-5.95</v>
       </c>
       <c r="H71" s="2">
-        <v>-3.54</v>
+        <v>-7.74</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>16130.91</v>
+        <v>60295.21</v>
       </c>
       <c r="K71" s="1">
-        <v>15935.27</v>
+        <v>58034.89</v>
       </c>
       <c r="L71" s="1">
-        <v>16823.14</v>
+        <v>61416.78</v>
       </c>
       <c r="M71" s="3">
-        <v>-300.25</v>
+        <v>-1161.74</v>
       </c>
       <c r="N71" s="3">
-        <v>-253.59</v>
+        <v>-971.27</v>
       </c>
       <c r="O71" s="3">
-        <v>9.43</v>
+        <v>-439.23</v>
       </c>
       <c r="P71" s="3">
-        <v>227.7</v>
+        <v>396.23</v>
       </c>
       <c r="Q71" s="3">
-        <v>1531.81</v>
+        <v>2727.99</v>
       </c>
       <c r="R71" s="3">
-        <v>1744.69</v>
+        <v>3451.52</v>
       </c>
       <c r="S71" s="3">
-        <v>29.25</v>
+        <v>23.59</v>
       </c>
       <c r="T71" t="str">
         <v/>
@@ -4812,58 +4812,58 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D72" s="1">
-        <v>34837.65</v>
+        <v>8070.7</v>
       </c>
       <c r="E72" s="2">
-        <v>-0.96</v>
+        <v>-2.26</v>
       </c>
       <c r="F72" s="2">
-        <v>-3.89</v>
+        <v>-0.3</v>
       </c>
       <c r="G72" s="2">
-        <v>-4.89</v>
+        <v>0.68</v>
       </c>
       <c r="H72" s="2">
-        <v>-5.22</v>
+        <v>-5.42</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>37113.6</v>
+        <v>8571.95</v>
       </c>
       <c r="K72" s="1">
-        <v>35897.54</v>
+        <v>8152.13</v>
       </c>
       <c r="L72" s="1">
-        <v>38399.48</v>
+        <v>8345.06</v>
       </c>
       <c r="M72" s="3">
-        <v>-806.39</v>
+        <v>-35.55</v>
       </c>
       <c r="N72" s="3">
-        <v>-752.95</v>
+        <v>-62.29</v>
       </c>
       <c r="O72" s="3">
-        <v>-223.01</v>
+        <v>-89.97</v>
       </c>
       <c r="P72" s="3">
-        <v>310.12</v>
+        <v>-32.65</v>
       </c>
       <c r="Q72" s="3">
-        <v>605.97</v>
+        <v>560.95</v>
       </c>
       <c r="R72" s="3">
-        <v>933.36</v>
+        <v>682.51</v>
       </c>
       <c r="S72" s="3">
-        <v>27.4</v>
+        <v>44.6</v>
       </c>
       <c r="T72" t="str">
         <v/>
@@ -4874,58 +4874,58 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C73" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D73" s="1">
-        <v>50373.65</v>
+        <v>65828.6</v>
       </c>
       <c r="E73" s="2">
-        <v>-0.97</v>
+        <v>-2.27</v>
       </c>
       <c r="F73" s="2">
-        <v>-3.7</v>
+        <v>-4.58</v>
       </c>
       <c r="G73" s="2">
-        <v>-4.77</v>
+        <v>-5.62</v>
       </c>
       <c r="H73" s="2">
-        <v>-4.43</v>
+        <v>-5.1</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>52542.32</v>
+        <v>70018.75</v>
       </c>
       <c r="K73" s="1">
-        <v>52018.72</v>
+        <v>67998.34</v>
       </c>
       <c r="L73" s="1">
-        <v>54100.37</v>
+        <v>71491.06</v>
       </c>
       <c r="M73" s="3">
-        <v>-755.32</v>
+        <v>-1177.52</v>
       </c>
       <c r="N73" s="3">
-        <v>-538.85</v>
+        <v>-1032.13</v>
       </c>
       <c r="O73" s="3">
-        <v>-22.78</v>
+        <v>-344.01</v>
       </c>
       <c r="P73" s="3">
-        <v>433.84</v>
+        <v>549.61</v>
       </c>
       <c r="Q73" s="3">
-        <v>-805.93</v>
+        <v>2518.21</v>
       </c>
       <c r="R73" s="3">
-        <v>-1132.88</v>
+        <v>3153.26</v>
       </c>
       <c r="S73" s="3">
-        <v>29.26</v>
+        <v>26.85</v>
       </c>
       <c r="T73" t="str">
         <v/>
@@ -4936,58 +4936,58 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D74" s="1">
-        <v>9214.6</v>
+        <v>26325</v>
       </c>
       <c r="E74" s="2">
-        <v>-0.97</v>
+        <v>-2.32</v>
       </c>
       <c r="F74" s="2">
-        <v>-3.85</v>
+        <v>-7.19</v>
       </c>
       <c r="G74" s="2">
-        <v>-4.34</v>
-      </c>
-      <c r="H74" s="2">
-        <v>7.07</v>
+        <v>-7.19</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
-      <c r="J74" s="1">
-        <v>8981.26</v>
+      <c r="J74" t="str">
+        <v/>
       </c>
       <c r="K74" s="1">
-        <v>9499.57</v>
+        <v>27601.95</v>
       </c>
       <c r="L74" s="1">
-        <v>9809.92</v>
+        <v>29242.38</v>
       </c>
       <c r="M74" s="3">
-        <v>-113.99</v>
+        <v>-581.26</v>
       </c>
       <c r="N74" s="3">
-        <v>-77.6</v>
+        <v>-450.01</v>
       </c>
       <c r="O74" s="3">
-        <v>194.84</v>
+        <v>-256.82</v>
       </c>
       <c r="P74" s="3">
-        <v>293.49</v>
+        <v>158.35</v>
       </c>
       <c r="Q74" s="3">
-        <v>725.43</v>
+        <v>156.03</v>
       </c>
       <c r="R74" s="3">
-        <v>716.72</v>
+        <v>172.48</v>
       </c>
       <c r="S74" s="3">
-        <v>30.93</v>
+        <v>25.08</v>
       </c>
       <c r="T74" t="str">
         <v/>
@@ -5004,52 +5004,52 @@
         <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D75" s="1">
-        <v>24393.05</v>
+        <v>23827.1</v>
       </c>
       <c r="E75" s="2">
-        <v>-1.03</v>
+        <v>-2.32</v>
       </c>
       <c r="F75" s="2">
-        <v>-5.22</v>
+        <v>-7.42</v>
       </c>
       <c r="G75" s="2">
-        <v>-7.07</v>
+        <v>-9.23</v>
       </c>
       <c r="H75" s="2">
-        <v>8.19</v>
+        <v>5.68</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>23618.34</v>
+        <v>23624.75</v>
       </c>
       <c r="K75" s="1">
-        <v>25330.09</v>
+        <v>25056.82</v>
       </c>
       <c r="L75" s="1">
-        <v>26118.21</v>
+        <v>26074.8</v>
       </c>
       <c r="M75" s="3">
-        <v>-328.46</v>
+        <v>-431.12</v>
       </c>
       <c r="N75" s="3">
-        <v>-173.89</v>
+        <v>-225.33</v>
       </c>
       <c r="O75" s="3">
-        <v>610.99</v>
+        <v>565.85</v>
       </c>
       <c r="P75" s="3">
-        <v>857.18</v>
+        <v>848.15</v>
       </c>
       <c r="Q75" s="3">
-        <v>2290.53</v>
+        <v>2245.38</v>
       </c>
       <c r="R75" s="3">
-        <v>2350.8</v>
+        <v>2341.77</v>
       </c>
       <c r="S75" s="3">
-        <v>30.06</v>
+        <v>25.8</v>
       </c>
       <c r="T75" t="str">
         <v/>
@@ -5060,58 +5060,58 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D76" s="1">
-        <v>8509.65</v>
+        <v>19071.8</v>
       </c>
       <c r="E76" s="2">
-        <v>-1.04</v>
+        <v>-2.33</v>
       </c>
       <c r="F76" s="2">
-        <v>-1.85</v>
+        <v>-5.91</v>
       </c>
       <c r="G76" s="2">
-        <v>6.02</v>
+        <v>-6.58</v>
       </c>
       <c r="H76" s="2">
-        <v>-9.69</v>
+        <v>-5.67</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>8256.91</v>
+        <v>20259.6</v>
       </c>
       <c r="K76" s="1">
-        <v>8442.38</v>
+        <v>19886.07</v>
       </c>
       <c r="L76" s="1">
-        <v>8535.19</v>
+        <v>20941.94</v>
       </c>
       <c r="M76" s="3">
-        <v>21.33</v>
+        <v>-379.38</v>
       </c>
       <c r="N76" s="3">
-        <v>-39.36</v>
+        <v>-293.14</v>
       </c>
       <c r="O76" s="3">
-        <v>65.45</v>
+        <v>-30.7</v>
       </c>
       <c r="P76" s="3">
-        <v>59.13</v>
+        <v>239.72</v>
       </c>
       <c r="Q76" s="3">
-        <v>371.93</v>
+        <v>1522.67</v>
       </c>
       <c r="R76" s="3">
-        <v>513.63</v>
+        <v>1812.28</v>
       </c>
       <c r="S76" s="3">
-        <v>55.1</v>
+        <v>22.43</v>
       </c>
       <c r="T76" t="str">
         <v/>
@@ -5122,58 +5122,58 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>CNXENERGY</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C77" t="str">
-        <v>CNXENERGY</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D77" s="1">
-        <v>35101.45</v>
+        <v>784.35</v>
       </c>
       <c r="E77" s="2">
-        <v>-1.05</v>
+        <v>-2.38</v>
       </c>
       <c r="F77" s="2">
-        <v>-3.01</v>
+        <v>-5.04</v>
       </c>
       <c r="G77" s="2">
-        <v>-4.19</v>
+        <v>-7.43</v>
       </c>
       <c r="H77" s="2">
-        <v>-0.63</v>
+        <v>-10.66</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>37726.44</v>
+        <v>821.76</v>
       </c>
       <c r="K77" s="1">
-        <v>35919.86</v>
+        <v>811.59</v>
       </c>
       <c r="L77" s="1">
-        <v>37412.73</v>
+        <v>861.67</v>
       </c>
       <c r="M77" s="3">
-        <v>-542.58</v>
+        <v>-16.39</v>
       </c>
       <c r="N77" s="3">
-        <v>-489.36</v>
+        <v>-14.88</v>
       </c>
       <c r="O77" s="3">
-        <v>-546.12</v>
+        <v>-1.64</v>
       </c>
       <c r="P77" s="3">
-        <v>-78.27</v>
+        <v>10.22</v>
       </c>
       <c r="Q77" s="3">
-        <v>936.27</v>
+        <v>0.01</v>
       </c>
       <c r="R77" s="3">
-        <v>1228.57</v>
+        <v>9.58</v>
       </c>
       <c r="S77" s="3">
-        <v>29.01</v>
+        <v>32.65</v>
       </c>
       <c r="T77" t="str">
         <v/>
@@ -5184,58 +5184,58 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C78" t="str">
-        <v>CNXIT</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D78" s="1">
-        <v>32081.25</v>
+        <v>27301.75</v>
       </c>
       <c r="E78" s="2">
-        <v>-1.05</v>
+        <v>-2.47</v>
       </c>
       <c r="F78" s="2">
-        <v>0.49</v>
+        <v>-6.15</v>
       </c>
       <c r="G78" s="2">
-        <v>15.8</v>
+        <v>-7.51</v>
       </c>
       <c r="H78" s="2">
-        <v>-15.32</v>
+        <v>-12.35</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>30844.5</v>
+        <v>30366.63</v>
       </c>
       <c r="K78" s="1">
-        <v>30738.62</v>
+        <v>28588.86</v>
       </c>
       <c r="L78" s="1">
-        <v>29836.1</v>
+        <v>30194.41</v>
       </c>
       <c r="M78" s="3">
-        <v>680.59</v>
+        <v>-592.61</v>
       </c>
       <c r="N78" s="3">
-        <v>172.04</v>
+        <v>-435.76</v>
       </c>
       <c r="O78" s="3">
-        <v>-150</v>
+        <v>-430.86</v>
       </c>
       <c r="P78" s="3">
-        <v>-518.18</v>
+        <v>-104.64</v>
       </c>
       <c r="Q78" s="3">
-        <v>-1654.18</v>
+        <v>1361.55</v>
       </c>
       <c r="R78" s="3">
-        <v>-1146.38</v>
+        <v>1982.03</v>
       </c>
       <c r="S78" s="3">
-        <v>69.01</v>
+        <v>23.16</v>
       </c>
       <c r="T78" t="str">
         <v/>
@@ -5246,58 +5246,58 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C79" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D79" s="1">
-        <v>28319.6</v>
+        <v>4930.05</v>
       </c>
       <c r="E79" s="2">
-        <v>-1.07</v>
+        <v>-2.5</v>
       </c>
       <c r="F79" s="2">
-        <v>-4.05</v>
+        <v>-5.95</v>
       </c>
       <c r="G79" s="2">
-        <v>-6.65</v>
+        <v>-3.14</v>
       </c>
       <c r="H79" s="2">
-        <v>-7.36</v>
+        <v>5.88</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>31400.6</v>
+        <v>5106.68</v>
       </c>
       <c r="K79" s="1">
-        <v>29329.22</v>
+        <v>5130.1</v>
       </c>
       <c r="L79" s="1">
-        <v>31540.74</v>
+        <v>5294.25</v>
       </c>
       <c r="M79" s="3">
-        <v>-752.85</v>
+        <v>-58.04</v>
       </c>
       <c r="N79" s="3">
-        <v>-664.7</v>
+        <v>-37.62</v>
       </c>
       <c r="O79" s="3">
-        <v>-478.01</v>
+        <v>17.34</v>
       </c>
       <c r="P79" s="3">
-        <v>70.18</v>
+        <v>84.49</v>
       </c>
       <c r="Q79" s="3">
-        <v>1965.44</v>
+        <v>353.78</v>
       </c>
       <c r="R79" s="3">
-        <v>2392.99</v>
+        <v>323.22</v>
       </c>
       <c r="S79" s="3">
-        <v>22.49</v>
+        <v>33.17</v>
       </c>
       <c r="T79" t="str">
         <v/>
@@ -5308,58 +5308,58 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D80" s="1">
-        <v>18949.55</v>
+        <v>23666.85</v>
       </c>
       <c r="E80" s="2">
-        <v>-1.08</v>
+        <v>-2.56</v>
       </c>
       <c r="F80" s="2">
-        <v>-2.68</v>
+        <v>-6.1</v>
       </c>
       <c r="G80" s="2">
-        <v>0.03</v>
+        <v>-6.8</v>
       </c>
       <c r="H80" s="2">
-        <v>-11.5</v>
+        <v>-5.28</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>20100.19</v>
+        <v>25466.45</v>
       </c>
       <c r="K80" s="1">
-        <v>19149.06</v>
+        <v>24754.22</v>
       </c>
       <c r="L80" s="1">
-        <v>19815.19</v>
+        <v>26109.43</v>
       </c>
       <c r="M80" s="3">
-        <v>-157.55</v>
+        <v>-484.27</v>
       </c>
       <c r="N80" s="3">
-        <v>-216.97</v>
+        <v>-363.85</v>
       </c>
       <c r="O80" s="3">
-        <v>-281.72</v>
+        <v>-111.79</v>
       </c>
       <c r="P80" s="3">
-        <v>-142.1</v>
+        <v>204.73</v>
       </c>
       <c r="Q80" s="3">
-        <v>484.31</v>
+        <v>1.84</v>
       </c>
       <c r="R80" s="3">
-        <v>794.91</v>
+        <v>-68.08</v>
       </c>
       <c r="S80" s="3">
-        <v>40.79</v>
+        <v>24.96</v>
       </c>
       <c r="T80" t="str">
         <v/>
@@ -5370,58 +5370,58 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C81" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D81" s="1">
-        <v>16856.2</v>
+        <v>15043.45</v>
       </c>
       <c r="E81" s="2">
-        <v>-1.09</v>
+        <v>-2.56</v>
       </c>
       <c r="F81" s="2">
-        <v>-4.43</v>
+        <v>-6.39</v>
       </c>
       <c r="G81" s="2">
-        <v>-5.3</v>
+        <v>-7.65</v>
       </c>
       <c r="H81" s="2">
-        <v>1.03</v>
+        <v>-6</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>16950.58</v>
+        <v>16126.11</v>
       </c>
       <c r="K81" s="1">
-        <v>17440.06</v>
+        <v>15773.12</v>
       </c>
       <c r="L81" s="1">
-        <v>18082.79</v>
+        <v>16777.1</v>
       </c>
       <c r="M81" s="3">
-        <v>-242.28</v>
+        <v>-353.58</v>
       </c>
       <c r="N81" s="3">
-        <v>-167.29</v>
+        <v>-273.59</v>
       </c>
       <c r="O81" s="3">
-        <v>191.86</v>
+        <v>-22.09</v>
       </c>
       <c r="P81" s="3">
-        <v>380.24</v>
+        <v>221.39</v>
       </c>
       <c r="Q81" s="3">
-        <v>1293.05</v>
+        <v>1500.29</v>
       </c>
       <c r="R81" s="3">
-        <v>1425.85</v>
+        <v>1738.39</v>
       </c>
       <c r="S81" s="3">
-        <v>27.09</v>
+        <v>24.61</v>
       </c>
       <c r="T81" t="str">
         <v/>
@@ -5432,58 +5432,58 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C82" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D82" s="1">
-        <v>22202</v>
+        <v>49069.75</v>
       </c>
       <c r="E82" s="2">
-        <v>-1.1</v>
+        <v>-2.59</v>
       </c>
       <c r="F82" s="2">
-        <v>-3.33</v>
+        <v>-6.2</v>
       </c>
       <c r="G82" s="2">
-        <v>-2.48</v>
+        <v>-7.23</v>
       </c>
       <c r="H82" s="2">
-        <v>-7.71</v>
+        <v>-6.9</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>23493.56</v>
+        <v>52524.13</v>
       </c>
       <c r="K82" s="1">
-        <v>22710.04</v>
+        <v>51482.54</v>
       </c>
       <c r="L82" s="1">
-        <v>23729.33</v>
+        <v>53982.39</v>
       </c>
       <c r="M82" s="3">
-        <v>-308.33</v>
+        <v>-947.88</v>
       </c>
       <c r="N82" s="3">
-        <v>-298.64</v>
+        <v>-620.66</v>
       </c>
       <c r="O82" s="3">
-        <v>-218.72</v>
+        <v>-126.79</v>
       </c>
       <c r="P82" s="3">
-        <v>28.36</v>
+        <v>413.04</v>
       </c>
       <c r="Q82" s="3">
-        <v>1001.39</v>
+        <v>-909.94</v>
       </c>
       <c r="R82" s="3">
-        <v>1355.11</v>
+        <v>-1153.68</v>
       </c>
       <c r="S82" s="3">
-        <v>31.39</v>
+        <v>24.22</v>
       </c>
       <c r="T82" t="str">
         <v/>
@@ -5494,58 +5494,58 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C83" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D83" s="1">
-        <v>15936.7</v>
+        <v>8561.2</v>
       </c>
       <c r="E83" s="2">
-        <v>-1.1</v>
+        <v>-2.6</v>
       </c>
       <c r="F83" s="2">
-        <v>-4.03</v>
+        <v>-7.05</v>
       </c>
       <c r="G83" s="2">
-        <v>0.16</v>
+        <v>-7.71</v>
       </c>
       <c r="H83" s="2">
-        <v>-27.55</v>
+        <v>10.5</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>18399.76</v>
+        <v>8842.66</v>
       </c>
       <c r="K83" s="1">
-        <v>16089.3</v>
+        <v>8980.74</v>
       </c>
       <c r="L83" s="1">
-        <v>17140.45</v>
+        <v>9456.74</v>
       </c>
       <c r="M83" s="3">
-        <v>-273.96</v>
+        <v>-161.86</v>
       </c>
       <c r="N83" s="3">
-        <v>-371.79</v>
+        <v>-118.83</v>
       </c>
       <c r="O83" s="3">
-        <v>-682</v>
+        <v>81.2</v>
       </c>
       <c r="P83" s="3">
-        <v>-513.19</v>
+        <v>230.92</v>
       </c>
       <c r="Q83" s="3">
-        <v>257.41</v>
+        <v>583.08</v>
       </c>
       <c r="R83" s="3">
-        <v>925.27</v>
+        <v>518.72</v>
       </c>
       <c r="S83" s="3">
-        <v>43.02</v>
+        <v>29.32</v>
       </c>
       <c r="T83" t="str">
         <v/>
@@ -5556,58 +5556,58 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C84" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D84" s="1">
-        <v>10447.9</v>
+        <v>33922</v>
       </c>
       <c r="E84" s="2">
-        <v>-1.1</v>
+        <v>-2.63</v>
       </c>
       <c r="F84" s="2">
-        <v>-4.03</v>
+        <v>-6.42</v>
       </c>
       <c r="G84" s="2">
-        <v>0.12</v>
+        <v>-7.39</v>
       </c>
       <c r="H84" s="2">
-        <v>-28.93</v>
+        <v>-7.71</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>12193.53</v>
+        <v>37099.43</v>
       </c>
       <c r="K84" s="1">
-        <v>10549.81</v>
+        <v>35538.35</v>
       </c>
       <c r="L84" s="1">
-        <v>11244.44</v>
+        <v>38271.87</v>
       </c>
       <c r="M84" s="3">
-        <v>-182.23</v>
+        <v>-914.61</v>
       </c>
       <c r="N84" s="3">
-        <v>-246.39</v>
+        <v>-785.28</v>
       </c>
       <c r="O84" s="3">
-        <v>-492.86</v>
+        <v>-296.05</v>
       </c>
       <c r="P84" s="3">
-        <v>-386.92</v>
+        <v>295.51</v>
       </c>
       <c r="Q84" s="3">
-        <v>-19.18</v>
+        <v>532.92</v>
       </c>
       <c r="R84" s="3">
-        <v>423.58</v>
+        <v>918.75</v>
       </c>
       <c r="S84" s="3">
-        <v>42.9</v>
+        <v>22.79</v>
       </c>
       <c r="T84" t="str">
         <v/>
@@ -5618,58 +5618,58 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C85" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D85" s="1">
-        <v>18275.9</v>
+        <v>44470.2</v>
       </c>
       <c r="E85" s="2">
-        <v>-1.14</v>
+        <v>-2.65</v>
       </c>
       <c r="F85" s="2">
-        <v>-4.46</v>
+        <v>-6.73</v>
       </c>
       <c r="G85" s="2">
-        <v>-5.04</v>
+        <v>-7.08</v>
       </c>
       <c r="H85" s="2">
-        <v>3.17</v>
+        <v>1.1</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>18188.2</v>
+        <v>44929.21</v>
       </c>
       <c r="K85" s="1">
-        <v>18941.68</v>
+        <v>46643.68</v>
       </c>
       <c r="L85" s="1">
-        <v>19622.01</v>
+        <v>48280.02</v>
       </c>
       <c r="M85" s="3">
-        <v>-257.2</v>
+        <v>-654.52</v>
       </c>
       <c r="N85" s="3">
-        <v>-167.11</v>
+        <v>-358.76</v>
       </c>
       <c r="O85" s="3">
-        <v>286.68</v>
+        <v>655.34</v>
       </c>
       <c r="P85" s="3">
-        <v>485.62</v>
+        <v>1101.74</v>
       </c>
       <c r="Q85" s="3">
-        <v>840.13</v>
+        <v>-453.49</v>
       </c>
       <c r="R85" s="3">
-        <v>852.2</v>
+        <v>-1042.54</v>
       </c>
       <c r="S85" s="3">
-        <v>28.03</v>
+        <v>25.55</v>
       </c>
       <c r="T85" t="str">
         <v/>
@@ -5680,58 +5680,58 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D86" s="1">
-        <v>8789.7</v>
+        <v>11478.2</v>
       </c>
       <c r="E86" s="2">
-        <v>-1.21</v>
+        <v>-2.71</v>
       </c>
       <c r="F86" s="2">
-        <v>-4.57</v>
+        <v>-5.4</v>
       </c>
       <c r="G86" s="2">
-        <v>-5.25</v>
+        <v>-10.05</v>
       </c>
       <c r="H86" s="2">
-        <v>13.45</v>
+        <v>2.78</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
       <c r="J86" s="1">
-        <v>8838.59</v>
+        <v>12483.72</v>
       </c>
       <c r="K86" s="1">
-        <v>9073.97</v>
+        <v>11951.39</v>
       </c>
       <c r="L86" s="1">
-        <v>9477.38</v>
+        <v>12804.74</v>
       </c>
       <c r="M86" s="3">
-        <v>-128.58</v>
+        <v>-315.57</v>
       </c>
       <c r="N86" s="3">
-        <v>-108.07</v>
+        <v>-267.05</v>
       </c>
       <c r="O86" s="3">
-        <v>99.43</v>
+        <v>-15.01</v>
       </c>
       <c r="P86" s="3">
-        <v>234.57</v>
+        <v>202.89</v>
       </c>
       <c r="Q86" s="3">
-        <v>601.31</v>
+        <v>1107.38</v>
       </c>
       <c r="R86" s="3">
-        <v>522.36</v>
+        <v>1124.17</v>
       </c>
       <c r="S86" s="3">
-        <v>34.11</v>
+        <v>27.88</v>
       </c>
       <c r="T86" t="str">
         <v/>
@@ -5742,58 +5742,58 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D87" s="1">
-        <v>45682.75</v>
+        <v>16385.15</v>
       </c>
       <c r="E87" s="2">
-        <v>-1.23</v>
+        <v>-2.79</v>
       </c>
       <c r="F87" s="2">
-        <v>-4.19</v>
+        <v>-7.1</v>
       </c>
       <c r="G87" s="2">
-        <v>-4.54</v>
+        <v>-7.94</v>
       </c>
       <c r="H87" s="2">
-        <v>3.86</v>
+        <v>-1.8</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>44926.78</v>
+        <v>16949.08</v>
       </c>
       <c r="K87" s="1">
-        <v>47126.67</v>
+        <v>17248.25</v>
       </c>
       <c r="L87" s="1">
-        <v>48360.46</v>
+        <v>18042.86</v>
       </c>
       <c r="M87" s="3">
-        <v>-468.02</v>
+        <v>-312.85</v>
       </c>
       <c r="N87" s="3">
-        <v>-284.81</v>
+        <v>-196.4</v>
       </c>
       <c r="O87" s="3">
-        <v>752.07</v>
+        <v>154.28</v>
       </c>
       <c r="P87" s="3">
-        <v>1121.08</v>
+        <v>372.72</v>
       </c>
       <c r="Q87" s="3">
-        <v>-356.76</v>
+        <v>1255.47</v>
       </c>
       <c r="R87" s="3">
-        <v>-1023.2</v>
+        <v>1418.33</v>
       </c>
       <c r="S87" s="3">
-        <v>31.23</v>
+        <v>21.82</v>
       </c>
       <c r="T87" t="str">
         <v/>
@@ -5804,58 +5804,58 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D88" s="1">
-        <v>43105.45</v>
+        <v>49910.3</v>
       </c>
       <c r="E88" s="2">
-        <v>-1.41</v>
+        <v>-2.81</v>
       </c>
       <c r="F88" s="2">
-        <v>-3.39</v>
+        <v>-7.31</v>
       </c>
       <c r="G88" s="2">
-        <v>-3.15</v>
+        <v>-7.71</v>
       </c>
       <c r="H88" s="2">
-        <v>-22.3</v>
+        <v>-0.79</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>48970.83</v>
+        <v>52196.32</v>
       </c>
       <c r="K88" s="1">
-        <v>44208.15</v>
+        <v>52935.13</v>
       </c>
       <c r="L88" s="1">
-        <v>45882.54</v>
+        <v>55465.02</v>
       </c>
       <c r="M88" s="3">
-        <v>-574.55</v>
+        <v>-970.06</v>
       </c>
       <c r="N88" s="3">
-        <v>-517.63</v>
+        <v>-524.45</v>
       </c>
       <c r="O88" s="3">
-        <v>-1668.17</v>
+        <v>487.96</v>
       </c>
       <c r="P88" s="3">
-        <v>-1354.71</v>
+        <v>1112.5</v>
       </c>
       <c r="Q88" s="3">
-        <v>-2185.95</v>
+        <v>3454.54</v>
       </c>
       <c r="R88" s="3">
-        <v>-970</v>
+        <v>3839.75</v>
       </c>
       <c r="S88" s="3">
-        <v>35.82</v>
+        <v>24.65</v>
       </c>
       <c r="T88" t="str">
         <v/>
@@ -5866,58 +5866,58 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C89" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D89" s="1">
-        <v>51352</v>
+        <v>17739.45</v>
       </c>
       <c r="E89" s="2">
-        <v>-2.03</v>
+        <v>-2.94</v>
       </c>
       <c r="F89" s="2">
-        <v>-4.63</v>
+        <v>-7.27</v>
       </c>
       <c r="G89" s="2">
-        <v>-5.04</v>
+        <v>-7.83</v>
       </c>
       <c r="H89" s="2">
-        <v>2.07</v>
+        <v>0.14</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>52198.32</v>
+        <v>18188.33</v>
       </c>
       <c r="K89" s="1">
-        <v>53607.32</v>
+        <v>18723.09</v>
       </c>
       <c r="L89" s="1">
-        <v>55593.73</v>
+        <v>19579.65</v>
       </c>
       <c r="M89" s="3">
-        <v>-713.53</v>
+        <v>-338.91</v>
       </c>
       <c r="N89" s="3">
-        <v>-413.05</v>
+        <v>-201.47</v>
       </c>
       <c r="O89" s="3">
-        <v>602.97</v>
+        <v>243.89</v>
       </c>
       <c r="P89" s="3">
-        <v>1135.5</v>
+        <v>477.06</v>
       </c>
       <c r="Q89" s="3">
-        <v>3569.55</v>
+        <v>797.34</v>
       </c>
       <c r="R89" s="3">
-        <v>3862.75</v>
+        <v>843.64</v>
       </c>
       <c r="S89" s="3">
-        <v>29.27</v>
+        <v>22.66</v>
       </c>
       <c r="T89" t="str">
         <v/>
@@ -5928,58 +5928,58 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C90" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D90" s="1">
-        <v>1584.5</v>
+        <v>8924.75</v>
       </c>
       <c r="E90" s="2">
-        <v>-2.35</v>
+        <v>-3.15</v>
       </c>
       <c r="F90" s="2">
-        <v>-3.87</v>
+        <v>-6.87</v>
       </c>
       <c r="G90" s="2">
-        <v>0.08</v>
+        <v>-7.35</v>
       </c>
       <c r="H90" s="2">
-        <v>9.68</v>
+        <v>3.7</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
       <c r="J90" s="1">
-        <v>1468.91</v>
+        <v>8982.85</v>
       </c>
       <c r="K90" s="1">
-        <v>1608.73</v>
+        <v>9395.06</v>
       </c>
       <c r="L90" s="1">
-        <v>1573.92</v>
+        <v>9789.56</v>
       </c>
       <c r="M90" s="3">
-        <v>17.85</v>
+        <v>-153.48</v>
       </c>
       <c r="N90" s="3">
-        <v>14.75</v>
+        <v>-92.78</v>
       </c>
       <c r="O90" s="3">
-        <v>32.67</v>
+        <v>171.72</v>
       </c>
       <c r="P90" s="3">
-        <v>31.65</v>
+        <v>288.86</v>
       </c>
       <c r="Q90" s="3">
-        <v>-73.28</v>
+        <v>702.31</v>
       </c>
       <c r="R90" s="3">
-        <v>-105.55</v>
+        <v>712.09</v>
       </c>
       <c r="S90" s="3">
-        <v>49.63</v>
+        <v>24.61</v>
       </c>
       <c r="T90" t="str">
         <v/>

--- a/Index.xlsx
+++ b/Index.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T90"/>
+  <dimension ref="A1:Y90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -458,12 +458,27 @@
         <v>MONTHLY macd_line</v>
       </c>
       <c r="R1" t="str">
-        <v>MONTLY macd_signal</v>
+        <v>MONTHLY macd_signal</v>
       </c>
       <c r="S1" t="str">
         <v>rsi</v>
       </c>
       <c r="T1" t="str">
+        <v>adx_di_positive</v>
+      </c>
+      <c r="U1" t="str">
+        <v>adx_di_negative</v>
+      </c>
+      <c r="V1" t="str">
+        <v>adx</v>
+      </c>
+      <c r="W1" t="str">
+        <v>market_cap</v>
+      </c>
+      <c r="X1" t="str">
+        <v>earning_per_share</v>
+      </c>
+      <c r="Y1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -472,60 +487,75 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>India VIX</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C2" t="str">
-        <v>INDIAVIX</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D2" s="1">
-        <v>16.76</v>
+        <v>43715.85</v>
       </c>
       <c r="E2" s="2">
-        <v>6.35</v>
+        <v>1.95</v>
       </c>
       <c r="F2" s="2">
-        <v>19.2</v>
+        <v>2.43</v>
       </c>
       <c r="G2" s="2">
-        <v>24.24</v>
+        <v>-1.78</v>
       </c>
       <c r="H2" s="2">
-        <v>76.79</v>
+        <v>-21.2</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>14.91</v>
+        <v>48700.42</v>
       </c>
       <c r="K2" s="1">
-        <v>15.12</v>
+        <v>43523.55</v>
       </c>
       <c r="L2" s="1">
-        <v>12.6</v>
+        <v>45330.92</v>
       </c>
       <c r="M2" s="3">
-        <v>0.9</v>
+        <v>-672.38</v>
       </c>
       <c r="N2" s="3">
-        <v>0.73</v>
+        <v>-640.86</v>
       </c>
       <c r="O2" s="3">
-        <v>-0.2</v>
+        <v>-1724.49</v>
       </c>
       <c r="P2" s="3">
-        <v>-0.73</v>
+        <v>-1434.09</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.07</v>
+        <v>-2137.25</v>
       </c>
       <c r="R2" s="3">
-        <v>0.05</v>
+        <v>-960.27</v>
       </c>
       <c r="S2" s="3">
-        <v>66.13</v>
-      </c>
-      <c r="T2" t="str">
+        <v>44.77</v>
+      </c>
+      <c r="T2" s="3">
+        <v>18.66</v>
+      </c>
+      <c r="U2" s="3">
+        <v>28.74</v>
+      </c>
+      <c r="V2" s="3">
+        <v>38.37</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="str">
         <v/>
       </c>
     </row>
@@ -534,60 +564,75 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D3" s="1">
-        <v>204.22</v>
+        <v>6021.45</v>
       </c>
       <c r="E3" s="2">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="F3" s="2">
-        <v>1.02</v>
+        <v>2.43</v>
       </c>
       <c r="G3" s="2">
-        <v>3.78</v>
+        <v>-3.33</v>
       </c>
       <c r="H3" s="2">
-        <v>-18.03</v>
+        <v>-5.4</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>180.43</v>
+        <v>6730.92</v>
       </c>
       <c r="K3" s="1">
-        <v>200.88</v>
+        <v>5983.83</v>
       </c>
       <c r="L3" s="1">
-        <v>195.12</v>
+        <v>6250.83</v>
       </c>
       <c r="M3" s="3">
-        <v>2.78</v>
+        <v>-92.02</v>
       </c>
       <c r="N3" s="3">
-        <v>2.61</v>
+        <v>-98.05</v>
       </c>
       <c r="O3" s="3">
-        <v>11.94</v>
+        <v>-212.84</v>
       </c>
       <c r="P3" s="3">
-        <v>5.7</v>
+        <v>-161.23</v>
       </c>
       <c r="Q3" s="3">
-        <v>5.47</v>
+        <v>234.51</v>
       </c>
       <c r="R3" s="3">
-        <v>7.68</v>
+        <v>404.05</v>
       </c>
       <c r="S3" s="3">
-        <v>100</v>
-      </c>
-      <c r="T3" t="str">
+        <v>44.06</v>
+      </c>
+      <c r="T3" s="3">
+        <v>16.43</v>
+      </c>
+      <c r="U3" s="3">
+        <v>29.21</v>
+      </c>
+      <c r="V3" s="3">
+        <v>44.27</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="str">
         <v/>
       </c>
     </row>
@@ -596,60 +641,75 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C4" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D4" s="1">
-        <v>236.6</v>
+        <v>16208.1</v>
       </c>
       <c r="E4" s="2">
-        <v>0.4</v>
+        <v>1.69</v>
       </c>
       <c r="F4" s="2">
         <v>2.49</v>
       </c>
       <c r="G4" s="2">
-        <v>0.28</v>
+        <v>1.87</v>
       </c>
       <c r="H4" s="2">
-        <v>18.3</v>
+        <v>-26.32</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>219.26</v>
+        <v>18246.8</v>
       </c>
       <c r="K4" s="1">
-        <v>234.95</v>
+        <v>16050.08</v>
       </c>
       <c r="L4" s="1">
-        <v>227.92</v>
+        <v>16877.57</v>
       </c>
       <c r="M4" s="3">
-        <v>1.87</v>
+        <v>-201.92</v>
       </c>
       <c r="N4" s="3">
-        <v>2.4</v>
+        <v>-279.85</v>
       </c>
       <c r="O4" s="3">
-        <v>4.76</v>
+        <v>-692.98</v>
       </c>
       <c r="P4" s="3">
-        <v>3.47</v>
+        <v>-550.72</v>
       </c>
       <c r="Q4" s="3">
-        <v>-0.58</v>
+        <v>279.06</v>
       </c>
       <c r="R4" s="3">
-        <v>-4.76</v>
+        <v>929.6</v>
       </c>
       <c r="S4" s="3">
-        <v>58.23</v>
-      </c>
-      <c r="T4" t="str">
+        <v>48.76</v>
+      </c>
+      <c r="T4" s="3">
+        <v>14.8</v>
+      </c>
+      <c r="U4" s="3">
+        <v>25.21</v>
+      </c>
+      <c r="V4" s="3">
+        <v>36.83</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="str">
         <v/>
       </c>
     </row>
@@ -658,60 +718,75 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C5" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D5" s="1">
-        <v>191.9</v>
+        <v>10622.1</v>
       </c>
       <c r="E5" s="2">
-        <v>0.39</v>
+        <v>1.67</v>
       </c>
       <c r="F5" s="2">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="G5" s="2">
-        <v>0.26</v>
+        <v>1.79</v>
       </c>
       <c r="H5" s="2">
-        <v>17.26</v>
+        <v>-27.74</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>178.68</v>
+        <v>12086.17</v>
       </c>
       <c r="K5" s="1">
-        <v>190.56</v>
+        <v>10521.38</v>
       </c>
       <c r="L5" s="1">
-        <v>184.9</v>
+        <v>11070.47</v>
       </c>
       <c r="M5" s="3">
-        <v>1.5</v>
+        <v>-135.32</v>
       </c>
       <c r="N5" s="3">
-        <v>1.92</v>
+        <v>-186.26</v>
       </c>
       <c r="O5" s="3">
-        <v>3.55</v>
+        <v>-498.43</v>
       </c>
       <c r="P5" s="3">
-        <v>2.49</v>
+        <v>-410.27</v>
       </c>
       <c r="Q5" s="3">
-        <v>-2.44</v>
+        <v>-5.29</v>
       </c>
       <c r="R5" s="3">
-        <v>-6.02</v>
+        <v>426.36</v>
       </c>
       <c r="S5" s="3">
-        <v>58.14</v>
-      </c>
-      <c r="T5" t="str">
+        <v>48.59</v>
+      </c>
+      <c r="T5" s="3">
+        <v>14.67</v>
+      </c>
+      <c r="U5" s="3">
+        <v>25.26</v>
+      </c>
+      <c r="V5" s="3">
+        <v>37.21</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="str">
         <v/>
       </c>
     </row>
@@ -720,60 +795,75 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C6" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D6" s="1">
-        <v>2597.31</v>
+        <v>7390.85</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.01</v>
+        <v>1.41</v>
       </c>
       <c r="F6" s="2">
-        <v>-0.53</v>
+        <v>1.48</v>
       </c>
       <c r="G6" s="2">
-        <v>-1.55</v>
+        <v>4.45</v>
       </c>
       <c r="H6" s="2">
-        <v>-0.56</v>
+        <v>-2.27</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>2632.22</v>
+        <v>7328.08</v>
       </c>
       <c r="K6" s="1">
-        <v>2607.41</v>
+        <v>7323.36</v>
       </c>
       <c r="L6" s="1">
-        <v>2648.03</v>
+        <v>7367.04</v>
       </c>
       <c r="M6" s="3">
-        <v>-14.33</v>
+        <v>11.22</v>
       </c>
       <c r="N6" s="3">
-        <v>-13.1</v>
+        <v>-9.24</v>
       </c>
       <c r="O6" s="3">
-        <v>-2.09</v>
+        <v>-0.52</v>
       </c>
       <c r="P6" s="3">
-        <v>7.43</v>
+        <v>24.4</v>
       </c>
       <c r="Q6" s="3">
-        <v>89.72</v>
+        <v>475.26</v>
       </c>
       <c r="R6" s="3">
-        <v>106.35</v>
+        <v>553.26</v>
       </c>
       <c r="S6" s="3">
-        <v>26.78</v>
-      </c>
-      <c r="T6" t="str">
+        <v>55.3</v>
+      </c>
+      <c r="T6" s="3">
+        <v>21.78</v>
+      </c>
+      <c r="U6" s="3">
+        <v>23.84</v>
+      </c>
+      <c r="V6" s="3">
+        <v>23.73</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="str">
         <v/>
       </c>
     </row>
@@ -782,60 +872,75 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C7" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D7" s="1">
-        <v>3276.83</v>
+        <v>30435.6</v>
       </c>
       <c r="E7" s="2">
-        <v>-0.02</v>
+        <v>1.37</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.14</v>
+        <v>1.67</v>
       </c>
       <c r="G7" s="2">
-        <v>-0.96</v>
+        <v>4.9</v>
       </c>
       <c r="H7" s="2">
-        <v>1.68</v>
+        <v>-9.57</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>3280.43</v>
+        <v>30868.65</v>
       </c>
       <c r="K7" s="1">
-        <v>3284.32</v>
+        <v>30047.42</v>
       </c>
       <c r="L7" s="1">
-        <v>3319.89</v>
+        <v>30012.91</v>
       </c>
       <c r="M7" s="3">
-        <v>-12.05</v>
+        <v>117.91</v>
       </c>
       <c r="N7" s="3">
-        <v>-11.31</v>
+        <v>1.08</v>
       </c>
       <c r="O7" s="3">
-        <v>7.71</v>
+        <v>-305.33</v>
       </c>
       <c r="P7" s="3">
-        <v>17.99</v>
+        <v>-315</v>
       </c>
       <c r="Q7" s="3">
-        <v>139.48</v>
+        <v>522.07</v>
       </c>
       <c r="R7" s="3">
-        <v>155.4</v>
+        <v>998.91</v>
       </c>
       <c r="S7" s="3">
-        <v>24.99</v>
-      </c>
-      <c r="T7" t="str">
+        <v>59.23</v>
+      </c>
+      <c r="T7" s="3">
+        <v>21.82</v>
+      </c>
+      <c r="U7" s="3">
+        <v>21.98</v>
+      </c>
+      <c r="V7" s="3">
+        <v>22.16</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="str">
         <v/>
       </c>
     </row>
@@ -844,60 +949,75 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C8" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D8" s="1">
-        <v>2966.76</v>
+        <v>8236.4</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.02</v>
+        <v>1.26</v>
       </c>
       <c r="F8" s="2">
-        <v>-0.54</v>
+        <v>2.05</v>
       </c>
       <c r="G8" s="2">
-        <v>-1.56</v>
+        <v>2.75</v>
       </c>
       <c r="H8" s="2">
-        <v>0</v>
+        <v>-3.48</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>3001.36</v>
+        <v>8560.89</v>
       </c>
       <c r="K8" s="1">
-        <v>2979.21</v>
+        <v>8155.79</v>
       </c>
       <c r="L8" s="1">
-        <v>3025.29</v>
+        <v>8295.84</v>
       </c>
       <c r="M8" s="3">
-        <v>-16.22</v>
+        <v>-23.22</v>
       </c>
       <c r="N8" s="3">
-        <v>-14.69</v>
+        <v>-43.93</v>
       </c>
       <c r="O8" s="3">
-        <v>0.02</v>
+        <v>-85.52</v>
       </c>
       <c r="P8" s="3">
-        <v>11.36</v>
+        <v>-43.22</v>
       </c>
       <c r="Q8" s="3">
-        <v>114.47</v>
+        <v>574.16</v>
       </c>
       <c r="R8" s="3">
-        <v>132.77</v>
+        <v>685.16</v>
       </c>
       <c r="S8" s="3">
-        <v>24.89</v>
-      </c>
-      <c r="T8" t="str">
+        <v>52.97</v>
+      </c>
+      <c r="T8" s="3">
+        <v>24.03</v>
+      </c>
+      <c r="U8" s="3">
+        <v>22.65</v>
+      </c>
+      <c r="V8" s="3">
+        <v>15.31</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="str">
         <v/>
       </c>
     </row>
@@ -906,60 +1026,75 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C9" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D9" s="1">
-        <v>837.73</v>
+        <v>8395.8</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.03</v>
+        <v>1.17</v>
       </c>
       <c r="F9" s="2">
-        <v>-0.69</v>
+        <v>1.38</v>
       </c>
       <c r="G9" s="2">
-        <v>-2.04</v>
+        <v>3.94</v>
       </c>
       <c r="H9" s="2">
-        <v>-6.03</v>
+        <v>-16.41</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>873.57</v>
+        <v>8731.21</v>
       </c>
       <c r="K9" s="1">
-        <v>842.19</v>
+        <v>8319.12</v>
       </c>
       <c r="L9" s="1">
-        <v>860.69</v>
+        <v>8363.21</v>
       </c>
       <c r="M9" s="3">
-        <v>-6.52</v>
+        <v>9.57</v>
       </c>
       <c r="N9" s="3">
-        <v>-6.09</v>
+        <v>-13.07</v>
       </c>
       <c r="O9" s="3">
-        <v>-8.8</v>
+        <v>-148.54</v>
       </c>
       <c r="P9" s="3">
-        <v>-5.64</v>
+        <v>-156.78</v>
       </c>
       <c r="Q9" s="3">
-        <v>-17.24</v>
+        <v>-297.81</v>
       </c>
       <c r="R9" s="3">
-        <v>-14.2</v>
+        <v>-190.89</v>
       </c>
       <c r="S9" s="3">
-        <v>20.96</v>
-      </c>
-      <c r="T9" t="str">
+        <v>56.19</v>
+      </c>
+      <c r="T9" s="3">
+        <v>19.78</v>
+      </c>
+      <c r="U9" s="3">
+        <v>22.26</v>
+      </c>
+      <c r="V9" s="3">
+        <v>20.27</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="str">
         <v/>
       </c>
     </row>
@@ -968,60 +1103,75 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C10" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D10" s="1">
-        <v>3284.16</v>
+        <v>27000.8</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.05</v>
+        <v>1.04</v>
       </c>
       <c r="F10" s="2">
-        <v>-0.57</v>
+        <v>1.29</v>
       </c>
       <c r="G10" s="2">
-        <v>-1.13</v>
+        <v>1.14</v>
       </c>
       <c r="H10" s="2">
-        <v>1.3</v>
+        <v>-5.99</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>3295.35</v>
+        <v>27320.71</v>
       </c>
       <c r="K10" s="1">
-        <v>3294.53</v>
+        <v>26918.67</v>
       </c>
       <c r="L10" s="1">
-        <v>3347.55</v>
+        <v>27227.9</v>
       </c>
       <c r="M10" s="3">
-        <v>-17.47</v>
+        <v>-99</v>
       </c>
       <c r="N10" s="3">
-        <v>-17.24</v>
+        <v>-76.2</v>
       </c>
       <c r="O10" s="3">
-        <v>7.47</v>
+        <v>-69.18</v>
       </c>
       <c r="P10" s="3">
-        <v>21.48</v>
+        <v>-2.03</v>
       </c>
       <c r="Q10" s="3">
-        <v>136.34</v>
+        <v>657.43</v>
       </c>
       <c r="R10" s="3">
-        <v>153.87</v>
+        <v>877.37</v>
       </c>
       <c r="S10" s="3">
-        <v>32.06</v>
-      </c>
-      <c r="T10" t="str">
+        <v>49.17</v>
+      </c>
+      <c r="T10" s="3">
+        <v>17.69</v>
+      </c>
+      <c r="U10" s="3">
+        <v>23.22</v>
+      </c>
+      <c r="V10" s="3">
+        <v>16.17</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="str">
         <v/>
       </c>
     </row>
@@ -1030,60 +1180,75 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D11" s="1">
-        <v>3058.24</v>
+        <v>8777.4</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.07</v>
+        <v>1.01</v>
       </c>
       <c r="F11" s="2">
-        <v>-0.58</v>
+        <v>2.61</v>
       </c>
       <c r="G11" s="2">
-        <v>-1.48</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="2">
-        <v>0.19</v>
+        <v>-8.72</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>3085.97</v>
+        <v>9201.54</v>
       </c>
       <c r="K11" s="1">
-        <v>3071.26</v>
+        <v>8680.74</v>
       </c>
       <c r="L11" s="1">
-        <v>3117.28</v>
+        <v>8940.78</v>
       </c>
       <c r="M11" s="3">
-        <v>-16.04</v>
+        <v>-65.24</v>
       </c>
       <c r="N11" s="3">
-        <v>-14.54</v>
+        <v>-99.73</v>
       </c>
       <c r="O11" s="3">
-        <v>2.3</v>
+        <v>-166.36</v>
       </c>
       <c r="P11" s="3">
-        <v>13.9</v>
+        <v>-97.73</v>
       </c>
       <c r="Q11" s="3">
-        <v>118.3</v>
+        <v>281.83</v>
       </c>
       <c r="R11" s="3">
-        <v>136.51</v>
+        <v>435.75</v>
       </c>
       <c r="S11" s="3">
-        <v>26.92</v>
-      </c>
-      <c r="T11" t="str">
+        <v>51.46</v>
+      </c>
+      <c r="T11" s="3">
+        <v>19.42</v>
+      </c>
+      <c r="U11" s="3">
+        <v>23.39</v>
+      </c>
+      <c r="V11" s="3">
+        <v>35.68</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="str">
         <v/>
       </c>
     </row>
@@ -1092,60 +1257,75 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C12" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D12" s="1">
-        <v>29934.75</v>
+        <v>53130.9</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.21</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2">
-        <v>-1.79</v>
+        <v>6.45</v>
       </c>
       <c r="G12" s="2">
-        <v>3.17</v>
+        <v>-1.75</v>
       </c>
       <c r="H12" s="2">
-        <v>-11.06</v>
+        <v>5.61</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>30941.95</v>
+        <v>52228.88</v>
       </c>
       <c r="K12" s="1">
-        <v>29821.3</v>
+        <v>52685.46</v>
       </c>
       <c r="L12" s="1">
-        <v>30083.38</v>
+        <v>55127.99</v>
       </c>
       <c r="M12" s="3">
-        <v>21.38</v>
+        <v>-858.76</v>
       </c>
       <c r="N12" s="3">
-        <v>-124.43</v>
+        <v>-778.3</v>
       </c>
       <c r="O12" s="3">
-        <v>-359.57</v>
+        <v>368.98</v>
       </c>
       <c r="P12" s="3">
-        <v>-317.41</v>
+        <v>963.79</v>
       </c>
       <c r="Q12" s="3">
-        <v>482.12</v>
+        <v>3711.46</v>
       </c>
       <c r="R12" s="3">
-        <v>990.92</v>
+        <v>3891.13</v>
       </c>
       <c r="S12" s="3">
-        <v>52.88</v>
-      </c>
-      <c r="T12" t="str">
+        <v>46.58</v>
+      </c>
+      <c r="T12" s="3">
+        <v>18.51</v>
+      </c>
+      <c r="U12" s="3">
+        <v>37.87</v>
+      </c>
+      <c r="V12" s="3">
+        <v>36.62</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="str">
         <v/>
       </c>
     </row>
@@ -1154,60 +1334,75 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C13" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D13" s="1">
-        <v>1596.15</v>
+        <v>18855</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.22</v>
+        <v>0.99</v>
       </c>
       <c r="F13" s="2">
-        <v>-0.33</v>
+        <v>1.57</v>
       </c>
       <c r="G13" s="2">
-        <v>-0.67</v>
+        <v>0.37</v>
       </c>
       <c r="H13" s="2">
-        <v>1.87</v>
+        <v>-10.77</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>1586.81</v>
+        <v>19804.62</v>
       </c>
       <c r="K13" s="1">
-        <v>1601.81</v>
+        <v>18721.97</v>
       </c>
       <c r="L13" s="1">
-        <v>1608.58</v>
+        <v>19319.9</v>
       </c>
       <c r="M13" s="3">
-        <v>-2.7</v>
+        <v>-157.3</v>
       </c>
       <c r="N13" s="3">
-        <v>-1.81</v>
+        <v>-209.68</v>
       </c>
       <c r="O13" s="3">
-        <v>6.53</v>
+        <v>-319.23</v>
       </c>
       <c r="P13" s="3">
-        <v>9.29</v>
+        <v>-181.82</v>
       </c>
       <c r="Q13" s="3">
-        <v>34.48</v>
+        <v>769.4</v>
       </c>
       <c r="R13" s="3">
-        <v>33.04</v>
+        <v>1113.7</v>
       </c>
       <c r="S13" s="3">
-        <v>23.28</v>
-      </c>
-      <c r="T13" t="str">
+        <v>48.4</v>
+      </c>
+      <c r="T13" s="3">
+        <v>13.71</v>
+      </c>
+      <c r="U13" s="3">
+        <v>23.48</v>
+      </c>
+      <c r="V13" s="3">
+        <v>46.52</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="str">
         <v/>
       </c>
     </row>
@@ -1216,60 +1411,75 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C14" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D14" s="1">
-        <v>10889.35</v>
+        <v>35281.75</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.25</v>
+        <v>0.96</v>
       </c>
       <c r="F14" s="2">
-        <v>-1.23</v>
+        <v>2.21</v>
       </c>
       <c r="G14" s="2">
-        <v>3.32</v>
+        <v>-3.7</v>
       </c>
       <c r="H14" s="2">
-        <v>-12.77</v>
+        <v>-0.12</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>11216.63</v>
+        <v>37706.56</v>
       </c>
       <c r="K14" s="1">
-        <v>10811.35</v>
+        <v>35375.49</v>
       </c>
       <c r="L14" s="1">
-        <v>11067.8</v>
+        <v>37045.74</v>
       </c>
       <c r="M14" s="3">
-        <v>-22.75</v>
+        <v>-598.63</v>
       </c>
       <c r="N14" s="3">
-        <v>-98.95</v>
+        <v>-576.02</v>
       </c>
       <c r="O14" s="3">
-        <v>-114.58</v>
+        <v>-683.92</v>
       </c>
       <c r="P14" s="3">
-        <v>-76.04</v>
+        <v>-206.82</v>
       </c>
       <c r="Q14" s="3">
-        <v>31.47</v>
+        <v>950.65</v>
       </c>
       <c r="R14" s="3">
-        <v>176.53</v>
+        <v>1231.45</v>
       </c>
       <c r="S14" s="3">
-        <v>52.9</v>
-      </c>
-      <c r="T14" t="str">
+        <v>39.71</v>
+      </c>
+      <c r="T14" s="3">
+        <v>13.61</v>
+      </c>
+      <c r="U14" s="3">
+        <v>34.86</v>
+      </c>
+      <c r="V14" s="3">
+        <v>37.71</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="str">
         <v/>
       </c>
     </row>
@@ -1278,60 +1488,75 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C15" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D15" s="1">
-        <v>10726.75</v>
+        <v>206.19</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.25</v>
+        <v>0.96</v>
       </c>
       <c r="F15" s="2">
-        <v>-2.97</v>
+        <v>0.96</v>
       </c>
       <c r="G15" s="2">
-        <v>-3.12</v>
+        <v>4.78</v>
       </c>
       <c r="H15" s="2">
-        <v>-12.72</v>
+        <v>-17.24</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>11488.94</v>
+        <v>179.55</v>
       </c>
       <c r="K15" s="1">
-        <v>10883.66</v>
+        <v>203.08</v>
       </c>
       <c r="L15" s="1">
-        <v>11448.4</v>
+        <v>196.37</v>
       </c>
       <c r="M15" s="3">
-        <v>-176.46</v>
+        <v>3.04</v>
       </c>
       <c r="N15" s="3">
-        <v>-180.36</v>
+        <v>2.81</v>
       </c>
       <c r="O15" s="3">
-        <v>-159.66</v>
+        <v>12.48</v>
       </c>
       <c r="P15" s="3">
-        <v>-43.17</v>
+        <v>7.05</v>
       </c>
       <c r="Q15" s="3">
-        <v>208.66</v>
+        <v>5.63</v>
       </c>
       <c r="R15" s="3">
-        <v>392.4</v>
+        <v>7.71</v>
       </c>
       <c r="S15" s="3">
-        <v>34.37</v>
-      </c>
-      <c r="T15" t="str">
+        <v>100</v>
+      </c>
+      <c r="T15" s="3">
+        <v>99.72</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0.28</v>
+      </c>
+      <c r="V15" s="3">
+        <v>97.59</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="str">
         <v/>
       </c>
     </row>
@@ -1340,60 +1565,75 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D16" s="1">
-        <v>8281.2</v>
+        <v>24647.9</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.26</v>
+        <v>0.94</v>
       </c>
       <c r="F16" s="2">
-        <v>-1.98</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>2.53</v>
+        <v>-0.01</v>
       </c>
       <c r="H16" s="2">
-        <v>-17.56</v>
+        <v>-10.74</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>8763.47</v>
+        <v>26139.42</v>
       </c>
       <c r="K16" s="1">
-        <v>8285.07</v>
+        <v>24638.76</v>
       </c>
       <c r="L16" s="1">
-        <v>8388.81</v>
+        <v>25336.79</v>
       </c>
       <c r="M16" s="3">
-        <v>-8.14</v>
+        <v>-226.36</v>
       </c>
       <c r="N16" s="3">
-        <v>-37.3</v>
+        <v>-212.41</v>
       </c>
       <c r="O16" s="3">
-        <v>-161.61</v>
+        <v>-408.76</v>
       </c>
       <c r="P16" s="3">
-        <v>-158.84</v>
+        <v>-263.32</v>
       </c>
       <c r="Q16" s="3">
-        <v>-306.95</v>
+        <v>647.46</v>
       </c>
       <c r="R16" s="3">
-        <v>-192.72</v>
+        <v>1081.05</v>
       </c>
       <c r="S16" s="3">
-        <v>49.51</v>
-      </c>
-      <c r="T16" t="str">
+        <v>44.57</v>
+      </c>
+      <c r="T16" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="U16" s="3">
+        <v>25.64</v>
+      </c>
+      <c r="V16" s="3">
+        <v>28.64</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="str">
         <v/>
       </c>
     </row>
@@ -1402,60 +1642,75 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C17" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D17" s="1">
-        <v>3453.01</v>
+        <v>9077.45</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.26</v>
+        <v>0.93</v>
       </c>
       <c r="F17" s="2">
-        <v>-0.99</v>
+        <v>2.16</v>
       </c>
       <c r="G17" s="2">
-        <v>-1.95</v>
+        <v>-3.02</v>
       </c>
       <c r="H17" s="2">
-        <v>-1.14</v>
+        <v>-7.88</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>3495.25</v>
+        <v>9963.53</v>
       </c>
       <c r="K17" s="1">
-        <v>3477.14</v>
+        <v>9072.72</v>
       </c>
       <c r="L17" s="1">
-        <v>3532.06</v>
+        <v>9452.08</v>
       </c>
       <c r="M17" s="3">
-        <v>-19.58</v>
+        <v>-129.18</v>
       </c>
       <c r="N17" s="3">
-        <v>-16.39</v>
+        <v>-133.4</v>
       </c>
       <c r="O17" s="3">
-        <v>1.54</v>
+        <v>-255.43</v>
       </c>
       <c r="P17" s="3">
-        <v>15.18</v>
+        <v>-171.19</v>
       </c>
       <c r="Q17" s="3">
-        <v>117.58</v>
+        <v>791.36</v>
       </c>
       <c r="R17" s="3">
-        <v>141.66</v>
+        <v>1091.7</v>
       </c>
       <c r="S17" s="3">
-        <v>30.66</v>
-      </c>
-      <c r="T17" t="str">
+        <v>41.98</v>
+      </c>
+      <c r="T17" s="3">
+        <v>12.65</v>
+      </c>
+      <c r="U17" s="3">
+        <v>33.7</v>
+      </c>
+      <c r="V17" s="3">
+        <v>49.34</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="str">
         <v/>
       </c>
     </row>
@@ -1464,60 +1719,75 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C18" t="str">
-        <v>CNXIT</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D18" s="1">
-        <v>31995.5</v>
+        <v>35051.6</v>
       </c>
       <c r="E18" s="2">
-        <v>-0.27</v>
+        <v>0.9</v>
       </c>
       <c r="F18" s="2">
-        <v>0.22</v>
+        <v>3.33</v>
       </c>
       <c r="G18" s="2">
-        <v>15.49</v>
+        <v>-4.3</v>
       </c>
       <c r="H18" s="2">
-        <v>-15.54</v>
+        <v>-4.64</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>30815.06</v>
+        <v>37041.89</v>
       </c>
       <c r="K18" s="1">
-        <v>30967.15</v>
+        <v>35006.63</v>
       </c>
       <c r="L18" s="1">
-        <v>29839.55</v>
+        <v>37800.45</v>
       </c>
       <c r="M18" s="3">
-        <v>749.33</v>
+        <v>-915.01</v>
       </c>
       <c r="N18" s="3">
-        <v>287.49</v>
+        <v>-892.86</v>
       </c>
       <c r="O18" s="3">
-        <v>-156.84</v>
+        <v>-440.38</v>
       </c>
       <c r="P18" s="3">
-        <v>-519.55</v>
+        <v>148.33</v>
       </c>
       <c r="Q18" s="3">
-        <v>-1661.02</v>
+        <v>623.03</v>
       </c>
       <c r="R18" s="3">
-        <v>-1147.75</v>
+        <v>936.77</v>
       </c>
       <c r="S18" s="3">
-        <v>68.05</v>
-      </c>
-      <c r="T18" t="str">
+        <v>39</v>
+      </c>
+      <c r="T18" s="3">
+        <v>14.15</v>
+      </c>
+      <c r="U18" s="3">
+        <v>32.98</v>
+      </c>
+      <c r="V18" s="3">
+        <v>55.6</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="str">
         <v/>
       </c>
     </row>
@@ -1526,60 +1796,75 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C19" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D19" s="1">
-        <v>1440.45</v>
+        <v>3794.35</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.35</v>
+        <v>0.89</v>
       </c>
       <c r="F19" s="2">
-        <v>-0.45</v>
+        <v>1.1</v>
       </c>
       <c r="G19" s="2">
-        <v>-0.92</v>
+        <v>0.32</v>
       </c>
       <c r="H19" s="2">
-        <v>1.11</v>
+        <v>-12.84</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>1440.86</v>
+        <v>4019.43</v>
       </c>
       <c r="K19" s="1">
-        <v>1447.48</v>
+        <v>3783.51</v>
       </c>
       <c r="L19" s="1">
-        <v>1457.8</v>
+        <v>3892.38</v>
       </c>
       <c r="M19" s="3">
-        <v>-3.84</v>
+        <v>-28.87</v>
       </c>
       <c r="N19" s="3">
-        <v>-2.97</v>
+        <v>-36.14</v>
       </c>
       <c r="O19" s="3">
-        <v>3.8</v>
+        <v>-71.6</v>
       </c>
       <c r="P19" s="3">
-        <v>7.24</v>
+        <v>-48.8</v>
       </c>
       <c r="Q19" s="3">
-        <v>28.73</v>
+        <v>126.37</v>
       </c>
       <c r="R19" s="3">
-        <v>28.47</v>
+        <v>206.8</v>
       </c>
       <c r="S19" s="3">
-        <v>18.6</v>
-      </c>
-      <c r="T19" t="str">
+        <v>46.84</v>
+      </c>
+      <c r="T19" s="3">
+        <v>15.42</v>
+      </c>
+      <c r="U19" s="3">
+        <v>27.63</v>
+      </c>
+      <c r="V19" s="3">
+        <v>36.7</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="str">
         <v/>
       </c>
     </row>
@@ -1588,60 +1873,75 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D20" s="1">
-        <v>11280.35</v>
+        <v>9509.2</v>
       </c>
       <c r="E20" s="2">
-        <v>-0.36</v>
+        <v>0.86</v>
       </c>
       <c r="F20" s="2">
-        <v>-2.18</v>
+        <v>6.55</v>
       </c>
       <c r="G20" s="2">
-        <v>1.21</v>
+        <v>-1.28</v>
       </c>
       <c r="H20" s="2">
-        <v>-15.03</v>
+        <v>10.49</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>12171.5</v>
+        <v>8996.1</v>
       </c>
       <c r="K20" s="1">
-        <v>11317.59</v>
+        <v>9377.47</v>
       </c>
       <c r="L20" s="1">
-        <v>11538.09</v>
+        <v>9743.14</v>
       </c>
       <c r="M20" s="3">
-        <v>-43.96</v>
+        <v>-125.51</v>
       </c>
       <c r="N20" s="3">
-        <v>-81.17</v>
+        <v>-125.18</v>
       </c>
       <c r="O20" s="3">
-        <v>-267.67</v>
+        <v>154.36</v>
       </c>
       <c r="P20" s="3">
-        <v>-236.36</v>
+        <v>261.96</v>
       </c>
       <c r="Q20" s="3">
-        <v>-133.65</v>
+        <v>748.93</v>
       </c>
       <c r="R20" s="3">
-        <v>113.71</v>
+        <v>721.42</v>
       </c>
       <c r="S20" s="3">
-        <v>46.06</v>
-      </c>
-      <c r="T20" t="str">
+        <v>49.34</v>
+      </c>
+      <c r="T20" s="3">
+        <v>24.65</v>
+      </c>
+      <c r="U20" s="3">
+        <v>38.44</v>
+      </c>
+      <c r="V20" s="3">
+        <v>34.71</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="str">
         <v/>
       </c>
     </row>
@@ -1650,60 +1950,75 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTY</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTY</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D21" s="1">
-        <v>22600</v>
+        <v>4725.85</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.39</v>
+        <v>0.86</v>
       </c>
       <c r="F21" s="2">
-        <v>-2.36</v>
+        <v>1.68</v>
       </c>
       <c r="G21" s="2">
-        <v>-0.09</v>
+        <v>0.9</v>
       </c>
       <c r="H21" s="2">
-        <v>-13.51</v>
+        <v>-8.79</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>24118.84</v>
+        <v>4901.82</v>
       </c>
       <c r="K21" s="1">
-        <v>22747.25</v>
+        <v>4698.73</v>
       </c>
       <c r="L21" s="1">
-        <v>23403.72</v>
+        <v>4826.29</v>
       </c>
       <c r="M21" s="3">
-        <v>-169.46</v>
+        <v>-30.84</v>
       </c>
       <c r="N21" s="3">
-        <v>-222.63</v>
+        <v>-42.46</v>
       </c>
       <c r="O21" s="3">
-        <v>-401.05</v>
+        <v>-56.93</v>
       </c>
       <c r="P21" s="3">
-        <v>-278.18</v>
+        <v>-25.76</v>
       </c>
       <c r="Q21" s="3">
-        <v>177.18</v>
+        <v>222.59</v>
       </c>
       <c r="R21" s="3">
-        <v>596.29</v>
+        <v>299.95</v>
       </c>
       <c r="S21" s="3">
-        <v>42.39</v>
-      </c>
-      <c r="T21" t="str">
+        <v>49.12</v>
+      </c>
+      <c r="T21" s="3">
+        <v>16.57</v>
+      </c>
+      <c r="U21" s="3">
+        <v>27.35</v>
+      </c>
+      <c r="V21" s="3">
+        <v>36.27</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="str">
         <v/>
       </c>
     </row>
@@ -1712,60 +2027,75 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C22" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D22" s="1">
-        <v>1300.19</v>
+        <v>54728</v>
       </c>
       <c r="E22" s="2">
-        <v>-0.41</v>
+        <v>0.85</v>
       </c>
       <c r="F22" s="2">
-        <v>-0.58</v>
+        <v>0.81</v>
       </c>
       <c r="G22" s="2">
-        <v>-1.17</v>
+        <v>0.17</v>
       </c>
       <c r="H22" s="2">
-        <v>0.16</v>
+        <v>-8.15</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>1308</v>
+        <v>56729.54</v>
       </c>
       <c r="K22" s="1">
-        <v>1308.25</v>
+        <v>54686.01</v>
       </c>
       <c r="L22" s="1">
-        <v>1321.23</v>
+        <v>55996.24</v>
       </c>
       <c r="M22" s="3">
-        <v>-4.72</v>
+        <v>-402.88</v>
       </c>
       <c r="N22" s="3">
-        <v>-3.8</v>
+        <v>-384.63</v>
       </c>
       <c r="O22" s="3">
-        <v>1.7</v>
+        <v>-466.71</v>
       </c>
       <c r="P22" s="3">
-        <v>5.61</v>
+        <v>-180.77</v>
       </c>
       <c r="Q22" s="3">
-        <v>23.49</v>
+        <v>1645.23</v>
       </c>
       <c r="R22" s="3">
-        <v>24.11</v>
+        <v>2284.63</v>
       </c>
       <c r="S22" s="3">
-        <v>16.61</v>
-      </c>
-      <c r="T22" t="str">
+        <v>45.13</v>
+      </c>
+      <c r="T22" s="3">
+        <v>14.31</v>
+      </c>
+      <c r="U22" s="3">
+        <v>24.31</v>
+      </c>
+      <c r="V22" s="3">
+        <v>25.83</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="str">
         <v/>
       </c>
     </row>
@@ -1774,60 +2104,75 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D23" s="1">
-        <v>18563.55</v>
+        <v>32386.55</v>
       </c>
       <c r="E23" s="2">
-        <v>-0.42</v>
+        <v>0.85</v>
       </c>
       <c r="F23" s="2">
-        <v>-1.88</v>
+        <v>2.36</v>
       </c>
       <c r="G23" s="2">
-        <v>-1.18</v>
+        <v>-1.44</v>
       </c>
       <c r="H23" s="2">
-        <v>-12.15</v>
+        <v>-4.62</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>19854.88</v>
+        <v>33632.82</v>
       </c>
       <c r="K23" s="1">
-        <v>18709.42</v>
+        <v>32258.52</v>
       </c>
       <c r="L23" s="1">
-        <v>19462.17</v>
+        <v>33592.8</v>
       </c>
       <c r="M23" s="3">
-        <v>-216.15</v>
+        <v>-403.06</v>
       </c>
       <c r="N23" s="3">
-        <v>-252.08</v>
+        <v>-449.18</v>
       </c>
       <c r="O23" s="3">
-        <v>-309.66</v>
+        <v>-349.84</v>
       </c>
       <c r="P23" s="3">
-        <v>-147.47</v>
+        <v>-0.02</v>
       </c>
       <c r="Q23" s="3">
-        <v>746.15</v>
+        <v>2009.88</v>
       </c>
       <c r="R23" s="3">
-        <v>1109.05</v>
+        <v>2431.9</v>
       </c>
       <c r="S23" s="3">
-        <v>37.55</v>
-      </c>
-      <c r="T23" t="str">
+        <v>44.25</v>
+      </c>
+      <c r="T23" s="3">
+        <v>14.81</v>
+      </c>
+      <c r="U23" s="3">
+        <v>29.69</v>
+      </c>
+      <c r="V23" s="3">
+        <v>47.23</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="str">
         <v/>
       </c>
     </row>
@@ -1836,60 +2181,75 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>CNXINFRA</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C24" t="str">
-        <v>CNXINFRA</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D24" s="1">
-        <v>8554.25</v>
+        <v>18792.55</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.44</v>
+        <v>0.85</v>
       </c>
       <c r="F24" s="2">
-        <v>-1.96</v>
+        <v>5.94</v>
       </c>
       <c r="G24" s="2">
-        <v>-2.06</v>
+        <v>-2.35</v>
       </c>
       <c r="H24" s="2">
-        <v>-11.04</v>
+        <v>6.09</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>9221.18</v>
+        <v>18200.98</v>
       </c>
       <c r="K24" s="1">
-        <v>8630.32</v>
+        <v>18618.14</v>
       </c>
       <c r="L24" s="1">
-        <v>8996.44</v>
+        <v>19472.38</v>
       </c>
       <c r="M24" s="3">
-        <v>-113.42</v>
+        <v>-305.21</v>
       </c>
       <c r="N24" s="3">
-        <v>-126.4</v>
+        <v>-284.32</v>
       </c>
       <c r="O24" s="3">
-        <v>-167.26</v>
+        <v>197.9</v>
       </c>
       <c r="P24" s="3">
-        <v>-80.58</v>
+        <v>421.23</v>
       </c>
       <c r="Q24" s="3">
-        <v>264.02</v>
+        <v>881.35</v>
       </c>
       <c r="R24" s="3">
-        <v>432.19</v>
+        <v>860.44</v>
       </c>
       <c r="S24" s="3">
-        <v>37.31</v>
-      </c>
-      <c r="T24" t="str">
+        <v>46.46</v>
+      </c>
+      <c r="T24" s="3">
+        <v>23.23</v>
+      </c>
+      <c r="U24" s="3">
+        <v>40.5</v>
+      </c>
+      <c r="V24" s="3">
+        <v>36.76</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="str">
         <v/>
       </c>
     </row>
@@ -1898,60 +2258,75 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY</v>
       </c>
       <c r="D25" s="1">
-        <v>7283.05</v>
+        <v>22890</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.44</v>
+        <v>0.84</v>
       </c>
       <c r="F25" s="2">
-        <v>-2.36</v>
+        <v>1.28</v>
       </c>
       <c r="G25" s="2">
-        <v>2.92</v>
+        <v>1.19</v>
       </c>
       <c r="H25" s="2">
-        <v>-3.69</v>
+        <v>-12.4</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>7333.45</v>
+        <v>24049.78</v>
       </c>
       <c r="K25" s="1">
-        <v>7294.32</v>
+        <v>22766.9</v>
       </c>
       <c r="L25" s="1">
-        <v>7395.36</v>
+        <v>23275.85</v>
       </c>
       <c r="M25" s="3">
-        <v>-3.25</v>
+        <v>-117.91</v>
       </c>
       <c r="N25" s="3">
-        <v>-32.05</v>
+        <v>-171.91</v>
       </c>
       <c r="O25" s="3">
-        <v>-4.23</v>
+        <v>-400.89</v>
       </c>
       <c r="P25" s="3">
-        <v>30.63</v>
+        <v>-302.72</v>
       </c>
       <c r="Q25" s="3">
-        <v>466.66</v>
+        <v>200.32</v>
       </c>
       <c r="R25" s="3">
-        <v>551.54</v>
+        <v>600.91</v>
       </c>
       <c r="S25" s="3">
-        <v>49.44</v>
-      </c>
-      <c r="T25" t="str">
+        <v>49.79</v>
+      </c>
+      <c r="T25" s="3">
+        <v>15.06</v>
+      </c>
+      <c r="U25" s="3">
+        <v>24.7</v>
+      </c>
+      <c r="V25" s="3">
+        <v>34.91</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="str">
         <v/>
       </c>
     </row>
@@ -1960,60 +2335,75 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C26" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D26" s="1">
-        <v>1255.18</v>
+        <v>5189.45</v>
       </c>
       <c r="E26" s="2">
-        <v>-0.5</v>
+        <v>0.84</v>
       </c>
       <c r="F26" s="2">
-        <v>-0.72</v>
+        <v>5.26</v>
       </c>
       <c r="G26" s="2">
-        <v>-1.42</v>
+        <v>1.96</v>
       </c>
       <c r="H26" s="2">
-        <v>-0.5</v>
+        <v>11.45</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>1268.31</v>
+        <v>5115.47</v>
       </c>
       <c r="K26" s="1">
-        <v>1264.42</v>
+        <v>5130.16</v>
       </c>
       <c r="L26" s="1">
-        <v>1279.52</v>
+        <v>5277.69</v>
       </c>
       <c r="M26" s="3">
-        <v>-5.57</v>
+        <v>-44.55</v>
       </c>
       <c r="N26" s="3">
-        <v>-4.46</v>
+        <v>-47.08</v>
       </c>
       <c r="O26" s="3">
-        <v>0.63</v>
+        <v>13.45</v>
       </c>
       <c r="P26" s="3">
-        <v>4.83</v>
+        <v>70.28</v>
       </c>
       <c r="Q26" s="3">
-        <v>20.72</v>
+        <v>374.47</v>
       </c>
       <c r="R26" s="3">
-        <v>21.84</v>
+        <v>327.35</v>
       </c>
       <c r="S26" s="3">
-        <v>15.49</v>
-      </c>
-      <c r="T26" t="str">
+        <v>50.36</v>
+      </c>
+      <c r="T26" s="3">
+        <v>20.48</v>
+      </c>
+      <c r="U26" s="3">
+        <v>27.07</v>
+      </c>
+      <c r="V26" s="3">
+        <v>22.93</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="str">
         <v/>
       </c>
     </row>
@@ -2022,60 +2412,75 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C27" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D27" s="1">
-        <v>3753.2</v>
+        <v>23837.9</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.55</v>
+        <v>0.82</v>
       </c>
       <c r="F27" s="2">
-        <v>-2.91</v>
+        <v>1.59</v>
       </c>
       <c r="G27" s="2">
-        <v>-0.77</v>
+        <v>0.43</v>
       </c>
       <c r="H27" s="2">
-        <v>-13.78</v>
+        <v>-10.68</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>4031.76</v>
+        <v>24961.08</v>
       </c>
       <c r="K27" s="1">
-        <v>3789.4</v>
+        <v>23722.7</v>
       </c>
       <c r="L27" s="1">
-        <v>3917.9</v>
+        <v>24366.48</v>
       </c>
       <c r="M27" s="3">
-        <v>-35.3</v>
+        <v>-168.15</v>
       </c>
       <c r="N27" s="3">
-        <v>-43.02</v>
+        <v>-216.63</v>
       </c>
       <c r="O27" s="3">
-        <v>-69.09</v>
+        <v>-372.99</v>
       </c>
       <c r="P27" s="3">
-        <v>-43.1</v>
+        <v>-234.53</v>
       </c>
       <c r="Q27" s="3">
-        <v>123.09</v>
+        <v>339.99</v>
       </c>
       <c r="R27" s="3">
-        <v>206.14</v>
+        <v>710.17</v>
       </c>
       <c r="S27" s="3">
-        <v>40.11</v>
-      </c>
-      <c r="T27" t="str">
+        <v>48.16</v>
+      </c>
+      <c r="T27" s="3">
+        <v>14.67</v>
+      </c>
+      <c r="U27" s="3">
+        <v>27.03</v>
+      </c>
+      <c r="V27" s="3">
+        <v>41.74</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="str">
         <v/>
       </c>
     </row>
@@ -2084,60 +2489,75 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D28" s="1">
-        <v>24862.3</v>
+        <v>11034</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.6</v>
+        <v>0.82</v>
       </c>
       <c r="F28" s="2">
-        <v>-3.52</v>
+        <v>2.86</v>
       </c>
       <c r="G28" s="2">
-        <v>-5.44</v>
+        <v>-0.35</v>
       </c>
       <c r="H28" s="2">
-        <v>-11.8</v>
+        <v>-10.22</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>26911.8</v>
+        <v>11462.28</v>
       </c>
       <c r="K28" s="1">
-        <v>25282.21</v>
+        <v>10918.59</v>
       </c>
       <c r="L28" s="1">
-        <v>27168.61</v>
+        <v>11354.03</v>
       </c>
       <c r="M28" s="3">
-        <v>-551.37</v>
+        <v>-119.6</v>
       </c>
       <c r="N28" s="3">
-        <v>-601.04</v>
+        <v>-157.69</v>
       </c>
       <c r="O28" s="3">
-        <v>-308.95</v>
+        <v>-167.33</v>
       </c>
       <c r="P28" s="3">
-        <v>91.11</v>
+        <v>-68</v>
       </c>
       <c r="Q28" s="3">
-        <v>1449.2</v>
+        <v>233.17</v>
       </c>
       <c r="R28" s="3">
-        <v>1805.34</v>
+        <v>397.3</v>
       </c>
       <c r="S28" s="3">
-        <v>34.23</v>
-      </c>
-      <c r="T28" t="str">
+        <v>49.07</v>
+      </c>
+      <c r="T28" s="3">
+        <v>17.54</v>
+      </c>
+      <c r="U28" s="3">
+        <v>27.23</v>
+      </c>
+      <c r="V28" s="3">
+        <v>44.33</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="str">
         <v/>
       </c>
     </row>
@@ -2146,60 +2566,75 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C29" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D29" s="1">
-        <v>10380.55</v>
+        <v>8966.35</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.62</v>
+        <v>0.82</v>
       </c>
       <c r="F29" s="2">
-        <v>-1.67</v>
+        <v>1.98</v>
       </c>
       <c r="G29" s="2">
-        <v>-2.2</v>
+        <v>-3.69</v>
       </c>
       <c r="H29" s="2">
-        <v>-15.13</v>
+        <v>-5.77</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>11291.49</v>
+        <v>9742.51</v>
       </c>
       <c r="K29" s="1">
-        <v>10485.64</v>
+        <v>8960.49</v>
       </c>
       <c r="L29" s="1">
-        <v>10870.59</v>
+        <v>9402.41</v>
       </c>
       <c r="M29" s="3">
-        <v>-120.55</v>
+        <v>-139.15</v>
       </c>
       <c r="N29" s="3">
-        <v>-134.21</v>
+        <v>-156.76</v>
       </c>
       <c r="O29" s="3">
-        <v>-230.43</v>
+        <v>-210.82</v>
       </c>
       <c r="P29" s="3">
-        <v>-161.29</v>
+        <v>-97.24</v>
       </c>
       <c r="Q29" s="3">
-        <v>68.02</v>
+        <v>390.92</v>
       </c>
       <c r="R29" s="3">
-        <v>278.4</v>
+        <v>508.55</v>
       </c>
       <c r="S29" s="3">
-        <v>36.86</v>
-      </c>
-      <c r="T29" t="str">
+        <v>42.19</v>
+      </c>
+      <c r="T29" s="3">
+        <v>14.49</v>
+      </c>
+      <c r="U29" s="3">
+        <v>29.09</v>
+      </c>
+      <c r="V29" s="3">
+        <v>40.96</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="str">
         <v/>
       </c>
     </row>
@@ -2208,60 +2643,75 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D30" s="1">
-        <v>30366.85</v>
+        <v>8558.05</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.64</v>
+        <v>0.81</v>
       </c>
       <c r="F30" s="2">
-        <v>-2.67</v>
+        <v>1.58</v>
       </c>
       <c r="G30" s="2">
-        <v>-1.74</v>
+        <v>6.62</v>
       </c>
       <c r="H30" s="2">
-        <v>-8.89</v>
+        <v>-9.17</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>32337.72</v>
+        <v>8233.71</v>
       </c>
       <c r="K30" s="1">
-        <v>30731.31</v>
+        <v>8498.59</v>
       </c>
       <c r="L30" s="1">
-        <v>31919.58</v>
+        <v>8508.26</v>
       </c>
       <c r="M30" s="3">
-        <v>-352.25</v>
+        <v>42</v>
       </c>
       <c r="N30" s="3">
-        <v>-393.41</v>
+        <v>11.05</v>
       </c>
       <c r="O30" s="3">
-        <v>-406.6</v>
+        <v>66.63</v>
       </c>
       <c r="P30" s="3">
-        <v>-118.39</v>
+        <v>59.55</v>
       </c>
       <c r="Q30" s="3">
-        <v>1807.56</v>
+        <v>375.79</v>
       </c>
       <c r="R30" s="3">
-        <v>2369</v>
+        <v>514.4</v>
       </c>
       <c r="S30" s="3">
-        <v>37.19</v>
-      </c>
-      <c r="T30" t="str">
+        <v>55.44</v>
+      </c>
+      <c r="T30" s="3">
+        <v>20.29</v>
+      </c>
+      <c r="U30" s="3">
+        <v>22.47</v>
+      </c>
+      <c r="V30" s="3">
+        <v>17.58</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="str">
         <v/>
       </c>
     </row>
@@ -2270,60 +2720,75 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D31" s="1">
-        <v>24348.8</v>
+        <v>5555.6</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.68</v>
+        <v>0.81</v>
       </c>
       <c r="F31" s="2">
-        <v>-2.27</v>
+        <v>0.81</v>
       </c>
       <c r="G31" s="2">
-        <v>-3.45</v>
+        <v>1.52</v>
       </c>
       <c r="H31" s="2">
-        <v>-10.08</v>
+        <v>-12.99</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>26241.6</v>
+        <v>5931.63</v>
       </c>
       <c r="K31" s="1">
-        <v>24699.33</v>
+        <v>5540.3</v>
       </c>
       <c r="L31" s="1">
-        <v>26060.84</v>
+        <v>5643.85</v>
       </c>
       <c r="M31" s="3">
-        <v>-437.51</v>
+        <v>-19.55</v>
       </c>
       <c r="N31" s="3">
-        <v>-449.38</v>
+        <v>-33.04</v>
       </c>
       <c r="O31" s="3">
-        <v>-363.36</v>
+        <v>-120.55</v>
       </c>
       <c r="P31" s="3">
-        <v>-70.73</v>
+        <v>-101.27</v>
       </c>
       <c r="Q31" s="3">
-        <v>1128.35</v>
+        <v>25.38</v>
       </c>
       <c r="R31" s="3">
-        <v>1592.4</v>
+        <v>139.56</v>
       </c>
       <c r="S31" s="3">
-        <v>29.59</v>
-      </c>
-      <c r="T31" t="str">
+        <v>49.44</v>
+      </c>
+      <c r="T31" s="3">
+        <v>18.38</v>
+      </c>
+      <c r="U31" s="3">
+        <v>27.88</v>
+      </c>
+      <c r="V31" s="3">
+        <v>32.6</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="str">
         <v/>
       </c>
     </row>
@@ -2332,60 +2797,75 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C32" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D32" s="1">
-        <v>23465.05</v>
+        <v>30972.1</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.73</v>
+        <v>0.8</v>
       </c>
       <c r="F32" s="2">
-        <v>-2.77</v>
+        <v>1.99</v>
       </c>
       <c r="G32" s="2">
-        <v>-1.14</v>
+        <v>0.22</v>
       </c>
       <c r="H32" s="2">
-        <v>-12.08</v>
+        <v>-7.08</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>25023.62</v>
+        <v>32280.18</v>
       </c>
       <c r="K32" s="1">
-        <v>23729.98</v>
+        <v>30760.79</v>
       </c>
       <c r="L32" s="1">
-        <v>24513.28</v>
+        <v>31709.82</v>
       </c>
       <c r="M32" s="3">
-        <v>-219.95</v>
+        <v>-253.43</v>
       </c>
       <c r="N32" s="3">
-        <v>-255.84</v>
+        <v>-333.92</v>
       </c>
       <c r="O32" s="3">
-        <v>-362.29</v>
+        <v>-426.21</v>
       </c>
       <c r="P32" s="3">
-        <v>-199.92</v>
+        <v>-179.95</v>
       </c>
       <c r="Q32" s="3">
-        <v>310.24</v>
+        <v>1855.84</v>
       </c>
       <c r="R32" s="3">
-        <v>704.22</v>
+        <v>2378.65</v>
       </c>
       <c r="S32" s="3">
-        <v>38.79</v>
-      </c>
-      <c r="T32" t="str">
+        <v>48.59</v>
+      </c>
+      <c r="T32" s="3">
+        <v>14.74</v>
+      </c>
+      <c r="U32" s="3">
+        <v>26.48</v>
+      </c>
+      <c r="V32" s="3">
+        <v>43.06</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="str">
         <v/>
       </c>
     </row>
@@ -2394,60 +2874,75 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D33" s="1">
-        <v>15814</v>
+        <v>13591.85</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.77</v>
+        <v>0.8</v>
       </c>
       <c r="F33" s="2">
-        <v>-4.77</v>
+        <v>3.19</v>
       </c>
       <c r="G33" s="2">
-        <v>-0.61</v>
+        <v>-1.15</v>
       </c>
       <c r="H33" s="2">
-        <v>-28.11</v>
+        <v>-6.08</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>18368.85</v>
+        <v>14120.06</v>
       </c>
       <c r="K33" s="1">
-        <v>16039.25</v>
+        <v>13479.39</v>
       </c>
       <c r="L33" s="1">
-        <v>17081.63</v>
+        <v>14012.54</v>
       </c>
       <c r="M33" s="3">
-        <v>-276.62</v>
+        <v>-157.41</v>
       </c>
       <c r="N33" s="3">
-        <v>-352.76</v>
+        <v>-192.59</v>
       </c>
       <c r="O33" s="3">
-        <v>-691.79</v>
+        <v>-196.71</v>
       </c>
       <c r="P33" s="3">
-        <v>-515.15</v>
+        <v>-53.51</v>
       </c>
       <c r="Q33" s="3">
-        <v>247.62</v>
+        <v>91.97</v>
       </c>
       <c r="R33" s="3">
-        <v>923.32</v>
+        <v>121.58</v>
       </c>
       <c r="S33" s="3">
-        <v>41.49</v>
-      </c>
-      <c r="T33" t="str">
+        <v>47.39</v>
+      </c>
+      <c r="T33" s="3">
+        <v>17.35</v>
+      </c>
+      <c r="U33" s="3">
+        <v>29.39</v>
+      </c>
+      <c r="V33" s="3">
+        <v>42.16</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="str">
         <v/>
       </c>
     </row>
@@ -2456,60 +2951,75 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C34" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D34" s="1">
-        <v>26656.3</v>
+        <v>11288.05</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.78</v>
+        <v>0.78</v>
       </c>
       <c r="F34" s="2">
-        <v>-3.77</v>
+        <v>0.07</v>
       </c>
       <c r="G34" s="2">
-        <v>-0.15</v>
+        <v>1.28</v>
       </c>
       <c r="H34" s="2">
-        <v>-7.19</v>
+        <v>-14.97</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>27362.11</v>
+        <v>12131.14</v>
       </c>
       <c r="K34" s="1">
-        <v>27050.18</v>
+        <v>11293.38</v>
       </c>
       <c r="L34" s="1">
-        <v>27268.91</v>
+        <v>11481.81</v>
       </c>
       <c r="M34" s="3">
-        <v>-60.86</v>
+        <v>-41.62</v>
       </c>
       <c r="N34" s="3">
-        <v>-42.96</v>
+        <v>-57.41</v>
       </c>
       <c r="O34" s="3">
-        <v>-53.67</v>
+        <v>-266.71</v>
       </c>
       <c r="P34" s="3">
-        <v>14.75</v>
+        <v>-242.43</v>
       </c>
       <c r="Q34" s="3">
-        <v>629.95</v>
+        <v>-133.04</v>
       </c>
       <c r="R34" s="3">
-        <v>871.88</v>
+        <v>113.83</v>
       </c>
       <c r="S34" s="3">
-        <v>41.15</v>
-      </c>
-      <c r="T34" t="str">
+        <v>47.45</v>
+      </c>
+      <c r="T34" s="3">
+        <v>15.19</v>
+      </c>
+      <c r="U34" s="3">
+        <v>26.76</v>
+      </c>
+      <c r="V34" s="3">
+        <v>29.18</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="str">
         <v/>
       </c>
     </row>
@@ -2518,60 +3028,75 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D35" s="1">
-        <v>10365.6</v>
+        <v>13136.65</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.79</v>
+        <v>0.76</v>
       </c>
       <c r="F35" s="2">
-        <v>-4.79</v>
+        <v>1.89</v>
       </c>
       <c r="G35" s="2">
-        <v>-0.67</v>
+        <v>-0.25</v>
       </c>
       <c r="H35" s="2">
-        <v>-29.49</v>
+        <v>-9.61</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>12171.86</v>
+        <v>13753.64</v>
       </c>
       <c r="K35" s="1">
-        <v>10516.32</v>
+        <v>13085.22</v>
       </c>
       <c r="L35" s="1">
-        <v>11205.53</v>
+        <v>13518.65</v>
       </c>
       <c r="M35" s="3">
-        <v>-184.1</v>
+        <v>-123.17</v>
       </c>
       <c r="N35" s="3">
-        <v>-233.93</v>
+        <v>-144.3</v>
       </c>
       <c r="O35" s="3">
-        <v>-499.42</v>
+        <v>-193.06</v>
       </c>
       <c r="P35" s="3">
-        <v>-388.23</v>
+        <v>-95.59</v>
       </c>
       <c r="Q35" s="3">
-        <v>-25.75</v>
+        <v>274.89</v>
       </c>
       <c r="R35" s="3">
-        <v>422.27</v>
+        <v>465.37</v>
       </c>
       <c r="S35" s="3">
-        <v>41.34</v>
-      </c>
-      <c r="T35" t="str">
+        <v>46.1</v>
+      </c>
+      <c r="T35" s="3">
+        <v>13.75</v>
+      </c>
+      <c r="U35" s="3">
+        <v>28.98</v>
+      </c>
+      <c r="V35" s="3">
+        <v>45.95</v>
+      </c>
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="str">
         <v/>
       </c>
     </row>
@@ -2580,60 +3105,75 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D36" s="1">
-        <v>15387</v>
+        <v>26396.8</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.83</v>
+        <v>0.73</v>
       </c>
       <c r="F36" s="2">
-        <v>-1.89</v>
+        <v>0.77</v>
       </c>
       <c r="G36" s="2">
-        <v>-4.65</v>
+        <v>-0.6</v>
       </c>
       <c r="H36" s="2">
-        <v>5.1</v>
+        <v>-12.53</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>15444.88</v>
+        <v>28442.01</v>
       </c>
       <c r="K36" s="1">
-        <v>15655.56</v>
+        <v>26448.61</v>
       </c>
       <c r="L36" s="1">
-        <v>16324.25</v>
+        <v>27360.7</v>
       </c>
       <c r="M36" s="3">
-        <v>-264.42</v>
+        <v>-296.93</v>
       </c>
       <c r="N36" s="3">
-        <v>-219.88</v>
+        <v>-284.69</v>
       </c>
       <c r="O36" s="3">
-        <v>161.13</v>
+        <v>-550.45</v>
       </c>
       <c r="P36" s="3">
-        <v>338.5</v>
+        <v>-351</v>
       </c>
       <c r="Q36" s="3">
-        <v>968.83</v>
+        <v>1298</v>
       </c>
       <c r="R36" s="3">
-        <v>992.24</v>
+        <v>1897.51</v>
       </c>
       <c r="S36" s="3">
-        <v>28.44</v>
-      </c>
-      <c r="T36" t="str">
+        <v>42.02</v>
+      </c>
+      <c r="T36" s="3">
+        <v>13.02</v>
+      </c>
+      <c r="U36" s="3">
+        <v>27.21</v>
+      </c>
+      <c r="V36" s="3">
+        <v>32.04</v>
+      </c>
+      <c r="W36" s="3">
+        <v>0</v>
+      </c>
+      <c r="X36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="str">
         <v/>
       </c>
     </row>
@@ -2642,60 +3182,75 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>NIFTY100ESG</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C37" t="str">
-        <v>NIFTY100ESG</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D37" s="1">
-        <v>4647.95</v>
+        <v>67787.05</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.86</v>
+        <v>0.72</v>
       </c>
       <c r="F37" s="2">
-        <v>-2.95</v>
+        <v>2.98</v>
       </c>
       <c r="G37" s="2">
-        <v>-0.77</v>
+        <v>-2.81</v>
       </c>
       <c r="H37" s="2">
-        <v>-10.29</v>
+        <v>-2.27</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>4912.71</v>
+        <v>69957.77</v>
       </c>
       <c r="K37" s="1">
-        <v>4697.8</v>
+        <v>67625.45</v>
       </c>
       <c r="L37" s="1">
-        <v>4858.01</v>
+        <v>70900.59</v>
       </c>
       <c r="M37" s="3">
-        <v>-41.95</v>
+        <v>-1054.14</v>
       </c>
       <c r="N37" s="3">
-        <v>-52.54</v>
+        <v>-1093.47</v>
       </c>
       <c r="O37" s="3">
-        <v>-54.23</v>
+        <v>-511.47</v>
       </c>
       <c r="P37" s="3">
-        <v>-17.96</v>
+        <v>337.39</v>
       </c>
       <c r="Q37" s="3">
-        <v>216.38</v>
+        <v>2674.44</v>
       </c>
       <c r="R37" s="3">
-        <v>298.7</v>
+        <v>3184.51</v>
       </c>
       <c r="S37" s="3">
-        <v>39.8</v>
-      </c>
-      <c r="T37" t="str">
+        <v>42.63</v>
+      </c>
+      <c r="T37" s="3">
+        <v>15.79</v>
+      </c>
+      <c r="U37" s="3">
+        <v>33.85</v>
+      </c>
+      <c r="V37" s="3">
+        <v>47.52</v>
+      </c>
+      <c r="W37" s="3">
+        <v>0</v>
+      </c>
+      <c r="X37" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="str">
         <v/>
       </c>
     </row>
@@ -2704,60 +3259,75 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTY500</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTY500</v>
       </c>
       <c r="D38" s="1">
-        <v>5878.45</v>
+        <v>21880.5</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F38" s="2">
-        <v>-3.08</v>
+        <v>2.11</v>
       </c>
       <c r="G38" s="2">
-        <v>-5.62</v>
+        <v>-0.87</v>
       </c>
       <c r="H38" s="2">
-        <v>-7.65</v>
+        <v>-8.34</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>6742.77</v>
+        <v>22786.41</v>
       </c>
       <c r="K38" s="1">
-        <v>6010.92</v>
+        <v>21813.5</v>
       </c>
       <c r="L38" s="1">
-        <v>6291.9</v>
+        <v>22594.86</v>
       </c>
       <c r="M38" s="3">
-        <v>-105.7</v>
+        <v>-234.77</v>
       </c>
       <c r="N38" s="3">
-        <v>-95.71</v>
+        <v>-258.82</v>
       </c>
       <c r="O38" s="3">
-        <v>-209.53</v>
+        <v>-271</v>
       </c>
       <c r="P38" s="3">
-        <v>-148.33</v>
+        <v>-90.62</v>
       </c>
       <c r="Q38" s="3">
-        <v>223.11</v>
+        <v>520.88</v>
       </c>
       <c r="R38" s="3">
-        <v>401.77</v>
+        <v>806.12</v>
       </c>
       <c r="S38" s="3">
-        <v>26.5</v>
-      </c>
-      <c r="T38" t="str">
+        <v>44.69</v>
+      </c>
+      <c r="T38" s="3">
+        <v>14.42</v>
+      </c>
+      <c r="U38" s="3">
+        <v>30.47</v>
+      </c>
+      <c r="V38" s="3">
+        <v>46.95</v>
+      </c>
+      <c r="W38" s="3">
+        <v>0</v>
+      </c>
+      <c r="X38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="str">
         <v/>
       </c>
     </row>
@@ -2766,60 +3336,75 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>NIFTYFMCG</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C39" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D39" s="1">
-        <v>42680.7</v>
+        <v>12363.85</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.99</v>
+        <v>0.69</v>
       </c>
       <c r="F39" s="2">
-        <v>-4.34</v>
+        <v>2.14</v>
       </c>
       <c r="G39" s="2">
-        <v>-4.11</v>
+        <v>-1.13</v>
       </c>
       <c r="H39" s="2">
-        <v>-23.06</v>
+        <v>-7.69</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>48906.86</v>
+        <v>12832.78</v>
       </c>
       <c r="K39" s="1">
-        <v>43930.43</v>
+        <v>12331.46</v>
       </c>
       <c r="L39" s="1">
-        <v>45760.39</v>
+        <v>12780.61</v>
       </c>
       <c r="M39" s="3">
-        <v>-661.47</v>
+        <v>-137.54</v>
       </c>
       <c r="N39" s="3">
-        <v>-546.4</v>
+        <v>-148.07</v>
       </c>
       <c r="O39" s="3">
-        <v>-1702.06</v>
+        <v>-134.19</v>
       </c>
       <c r="P39" s="3">
-        <v>-1361.49</v>
+        <v>-28.92</v>
       </c>
       <c r="Q39" s="3">
-        <v>-2219.83</v>
+        <v>631.85</v>
       </c>
       <c r="R39" s="3">
-        <v>-976.78</v>
+        <v>826.45</v>
       </c>
       <c r="S39" s="3">
-        <v>33.59</v>
-      </c>
-      <c r="T39" t="str">
+        <v>44.15</v>
+      </c>
+      <c r="T39" s="3">
+        <v>14.59</v>
+      </c>
+      <c r="U39" s="3">
+        <v>31.24</v>
+      </c>
+      <c r="V39" s="3">
+        <v>46.54</v>
+      </c>
+      <c r="W39" s="3">
+        <v>0</v>
+      </c>
+      <c r="X39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="str">
         <v/>
       </c>
     </row>
@@ -2828,60 +3413,75 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C40" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D40" s="1">
-        <v>8425</v>
+        <v>803.3</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.99</v>
+        <v>0.68</v>
       </c>
       <c r="F40" s="2">
-        <v>-2.83</v>
+        <v>2.42</v>
       </c>
       <c r="G40" s="2">
-        <v>4.96</v>
+        <v>-5.2</v>
       </c>
       <c r="H40" s="2">
-        <v>-10.59</v>
+        <v>-8.5</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>8251.92</v>
+        <v>819.66</v>
       </c>
       <c r="K40" s="1">
-        <v>8439.22</v>
+        <v>805.06</v>
       </c>
       <c r="L40" s="1">
-        <v>8527.3</v>
+        <v>853.73</v>
       </c>
       <c r="M40" s="3">
-        <v>19.93</v>
+        <v>-15.22</v>
       </c>
       <c r="N40" s="3">
-        <v>-27.5</v>
+        <v>-15.55</v>
       </c>
       <c r="O40" s="3">
-        <v>58.7</v>
+        <v>-4.54</v>
       </c>
       <c r="P40" s="3">
-        <v>57.78</v>
+        <v>7.27</v>
       </c>
       <c r="Q40" s="3">
-        <v>365.18</v>
+        <v>1.53</v>
       </c>
       <c r="R40" s="3">
-        <v>512.28</v>
+        <v>9.88</v>
       </c>
       <c r="S40" s="3">
-        <v>50.99</v>
-      </c>
-      <c r="T40" t="str">
+        <v>42.22</v>
+      </c>
+      <c r="T40" s="3">
+        <v>16.01</v>
+      </c>
+      <c r="U40" s="3">
+        <v>29.84</v>
+      </c>
+      <c r="V40" s="3">
+        <v>28.71</v>
+      </c>
+      <c r="W40" s="3">
+        <v>0</v>
+      </c>
+      <c r="X40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="str">
         <v/>
       </c>
     </row>
@@ -2890,60 +3490,75 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D41" s="1">
-        <v>12892.4</v>
+        <v>15495.95</v>
       </c>
       <c r="E41" s="2">
-        <v>-1.02</v>
+        <v>0.65</v>
       </c>
       <c r="F41" s="2">
-        <v>-3.34</v>
+        <v>2.5</v>
       </c>
       <c r="G41" s="2">
-        <v>-2.11</v>
+        <v>-1.62</v>
       </c>
       <c r="H41" s="2">
-        <v>-11.29</v>
+        <v>-6</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>13785.02</v>
+        <v>15989.37</v>
       </c>
       <c r="K41" s="1">
-        <v>13109.8</v>
+        <v>15461.81</v>
       </c>
       <c r="L41" s="1">
-        <v>13608.22</v>
+        <v>16079.19</v>
       </c>
       <c r="M41" s="3">
-        <v>-149.46</v>
+        <v>-196.26</v>
       </c>
       <c r="N41" s="3">
-        <v>-156.82</v>
+        <v>-203.09</v>
       </c>
       <c r="O41" s="3">
-        <v>-180.45</v>
+        <v>-132.03</v>
       </c>
       <c r="P41" s="3">
-        <v>-71.22</v>
+        <v>18.48</v>
       </c>
       <c r="Q41" s="3">
-        <v>255.4</v>
+        <v>920.73</v>
       </c>
       <c r="R41" s="3">
-        <v>461.47</v>
+        <v>1148.83</v>
       </c>
       <c r="S41" s="3">
-        <v>34.9</v>
-      </c>
-      <c r="T41" t="str">
+        <v>43.09</v>
+      </c>
+      <c r="T41" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="U41" s="3">
+        <v>33.89</v>
+      </c>
+      <c r="V41" s="3">
+        <v>47.43</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="str">
         <v/>
       </c>
     </row>
@@ -2952,60 +3567,75 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D42" s="1">
-        <v>24403</v>
+        <v>24778.7</v>
       </c>
       <c r="E42" s="2">
-        <v>-1.03</v>
+        <v>0.64</v>
       </c>
       <c r="F42" s="2">
-        <v>-3.88</v>
+        <v>4.7</v>
       </c>
       <c r="G42" s="2">
-        <v>-1</v>
+        <v>-2.42</v>
       </c>
       <c r="H42" s="2">
-        <v>-11.63</v>
+        <v>-0.83</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>26207.11</v>
+        <v>25448.5</v>
       </c>
       <c r="K42" s="1">
-        <v>24840.22</v>
+        <v>24636</v>
       </c>
       <c r="L42" s="1">
-        <v>25484.01</v>
+        <v>25917.22</v>
       </c>
       <c r="M42" s="3">
-        <v>-191.42</v>
+        <v>-421.63</v>
       </c>
       <c r="N42" s="3">
-        <v>-187.78</v>
+        <v>-423.09</v>
       </c>
       <c r="O42" s="3">
-        <v>-378.42</v>
+        <v>-165.67</v>
       </c>
       <c r="P42" s="3">
-        <v>-226.96</v>
+        <v>130.65</v>
       </c>
       <c r="Q42" s="3">
-        <v>627.93</v>
+        <v>90.53</v>
       </c>
       <c r="R42" s="3">
-        <v>1077.14</v>
+        <v>-50.34</v>
       </c>
       <c r="S42" s="3">
-        <v>37.56</v>
-      </c>
-      <c r="T42" t="str">
+        <v>44.65</v>
+      </c>
+      <c r="T42" s="3">
+        <v>16.17</v>
+      </c>
+      <c r="U42" s="3">
+        <v>35.42</v>
+      </c>
+      <c r="V42" s="3">
+        <v>42.27</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="str">
         <v/>
       </c>
     </row>
@@ -3014,60 +3644,75 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C43" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D43" s="1">
-        <v>25329.45</v>
+        <v>1647.95</v>
       </c>
       <c r="E43" s="2">
-        <v>-1.04</v>
+        <v>0.64</v>
       </c>
       <c r="F43" s="2">
-        <v>-1.75</v>
+        <v>5.41</v>
       </c>
       <c r="G43" s="2">
-        <v>-4.19</v>
+        <v>4.09</v>
       </c>
       <c r="H43" s="2">
-        <v>11.47</v>
+        <v>14.07</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>24375.25</v>
+        <v>1472.6</v>
       </c>
       <c r="K43" s="1">
-        <v>25744.37</v>
+        <v>1612.16</v>
       </c>
       <c r="L43" s="1">
-        <v>26439.2</v>
+        <v>1576.71</v>
       </c>
       <c r="M43" s="3">
-        <v>-286.8</v>
+        <v>15.36</v>
       </c>
       <c r="N43" s="3">
-        <v>-206.14</v>
+        <v>13.22</v>
       </c>
       <c r="O43" s="3">
-        <v>578.03</v>
+        <v>35.35</v>
       </c>
       <c r="P43" s="3">
-        <v>792.63</v>
+        <v>32.12</v>
       </c>
       <c r="Q43" s="3">
-        <v>1753.37</v>
+        <v>-68.22</v>
       </c>
       <c r="R43" s="3">
-        <v>1603.12</v>
+        <v>-104.54</v>
       </c>
       <c r="S43" s="3">
-        <v>32.77</v>
-      </c>
-      <c r="T43" t="str">
+        <v>59.68</v>
+      </c>
+      <c r="T43" s="3">
+        <v>27.7</v>
+      </c>
+      <c r="U43" s="3">
+        <v>22.74</v>
+      </c>
+      <c r="V43" s="3">
+        <v>15.68</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="str">
         <v/>
       </c>
     </row>
@@ -3076,60 +3721,75 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D44" s="1">
-        <v>5302.15</v>
+        <v>15536.65</v>
       </c>
       <c r="E44" s="2">
-        <v>-1.07</v>
+        <v>0.63</v>
       </c>
       <c r="F44" s="2">
-        <v>-3.1</v>
+        <v>2.15</v>
       </c>
       <c r="G44" s="2">
-        <v>-0.34</v>
+        <v>-1.4</v>
       </c>
       <c r="H44" s="2">
-        <v>-9.52</v>
+        <v>-7.82</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>5545.89</v>
+        <v>16256.17</v>
       </c>
       <c r="K44" s="1">
-        <v>5364.15</v>
+        <v>15507.13</v>
       </c>
       <c r="L44" s="1">
-        <v>5511.3</v>
+        <v>16151.54</v>
       </c>
       <c r="M44" s="3">
-        <v>-31.66</v>
+        <v>-197.88</v>
       </c>
       <c r="N44" s="3">
-        <v>-45.89</v>
+        <v>-212.56</v>
       </c>
       <c r="O44" s="3">
-        <v>-50.65</v>
+        <v>-198.94</v>
       </c>
       <c r="P44" s="3">
-        <v>-18.5</v>
+        <v>-45.29</v>
       </c>
       <c r="Q44" s="3">
-        <v>182.48</v>
+        <v>917.98</v>
       </c>
       <c r="R44" s="3">
-        <v>260.16</v>
+        <v>1179.09</v>
       </c>
       <c r="S44" s="3">
-        <v>41.44</v>
-      </c>
-      <c r="T44" t="str">
+        <v>42.79</v>
+      </c>
+      <c r="T44" s="3">
+        <v>13.47</v>
+      </c>
+      <c r="U44" s="3">
+        <v>31.81</v>
+      </c>
+      <c r="V44" s="3">
+        <v>49.55</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="str">
         <v/>
       </c>
     </row>
@@ -3138,60 +3798,75 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C45" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D45" s="1">
-        <v>13171.4</v>
+        <v>59507.25</v>
       </c>
       <c r="E45" s="2">
-        <v>-1.09</v>
+        <v>0.6</v>
       </c>
       <c r="F45" s="2">
-        <v>-3.37</v>
+        <v>4.74</v>
       </c>
       <c r="G45" s="2">
-        <v>-4.21</v>
+        <v>-2.08</v>
       </c>
       <c r="H45" s="2">
-        <v>-8.98</v>
+        <v>-3.89</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>14142.86</v>
+        <v>61628.01</v>
       </c>
       <c r="K45" s="1">
-        <v>13453.69</v>
+        <v>59100.36</v>
       </c>
       <c r="L45" s="1">
-        <v>14109.82</v>
+        <v>62021.6</v>
       </c>
       <c r="M45" s="3">
-        <v>-219.72</v>
+        <v>-973.04</v>
       </c>
       <c r="N45" s="3">
-        <v>-208.32</v>
+        <v>-994.88</v>
       </c>
       <c r="O45" s="3">
-        <v>-182.88</v>
+        <v>-613.08</v>
       </c>
       <c r="P45" s="3">
-        <v>-17.71</v>
+        <v>28.31</v>
       </c>
       <c r="Q45" s="3">
-        <v>58.43</v>
+        <v>-33.68</v>
       </c>
       <c r="R45" s="3">
-        <v>114.87</v>
+        <v>-179.67</v>
       </c>
       <c r="S45" s="3">
-        <v>28.96</v>
-      </c>
-      <c r="T45" t="str">
+        <v>44.93</v>
+      </c>
+      <c r="T45" s="3">
+        <v>16.25</v>
+      </c>
+      <c r="U45" s="3">
+        <v>35.37</v>
+      </c>
+      <c r="V45" s="3">
+        <v>44.86</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="str">
         <v/>
       </c>
     </row>
@@ -3200,60 +3875,75 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D46" s="1">
-        <v>13600.85</v>
+        <v>10996.35</v>
       </c>
       <c r="E46" s="2">
-        <v>-1.14</v>
+        <v>0.6</v>
       </c>
       <c r="F46" s="2">
-        <v>-2.53</v>
+        <v>0.98</v>
       </c>
       <c r="G46" s="2">
-        <v>1.86</v>
+        <v>4.33</v>
       </c>
       <c r="H46" s="2">
-        <v>-11.06</v>
+        <v>-11.91</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>14385.7</v>
+        <v>11182.79</v>
       </c>
       <c r="K46" s="1">
-        <v>13675.05</v>
+        <v>10894.66</v>
       </c>
       <c r="L46" s="1">
-        <v>14009.98</v>
+        <v>11009.06</v>
       </c>
       <c r="M46" s="3">
-        <v>-55.41</v>
+        <v>21.11</v>
       </c>
       <c r="N46" s="3">
-        <v>-118.79</v>
+        <v>-35.25</v>
       </c>
       <c r="O46" s="3">
-        <v>-227.8</v>
+        <v>-103.22</v>
       </c>
       <c r="P46" s="3">
-        <v>-163</v>
+        <v>-81.47</v>
       </c>
       <c r="Q46" s="3">
-        <v>-547.72</v>
+        <v>40</v>
       </c>
       <c r="R46" s="3">
-        <v>-494.09</v>
+        <v>178.24</v>
       </c>
       <c r="S46" s="3">
-        <v>46.01</v>
-      </c>
-      <c r="T46" t="str">
+        <v>56.72</v>
+      </c>
+      <c r="T46" s="3">
+        <v>19.82</v>
+      </c>
+      <c r="U46" s="3">
+        <v>20.38</v>
+      </c>
+      <c r="V46" s="3">
+        <v>25.77</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="str">
         <v/>
       </c>
     </row>
@@ -3262,60 +3952,75 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C47" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D47" s="1">
-        <v>54287.35</v>
+        <v>5375.05</v>
       </c>
       <c r="E47" s="2">
-        <v>-1.16</v>
+        <v>0.59</v>
       </c>
       <c r="F47" s="2">
-        <v>-2.79</v>
+        <v>1.37</v>
       </c>
       <c r="G47" s="2">
-        <v>-0.63</v>
+        <v>1.03</v>
       </c>
       <c r="H47" s="2">
-        <v>-8.89</v>
+        <v>-8.28</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>56842.98</v>
+        <v>5535.16</v>
       </c>
       <c r="K47" s="1">
-        <v>55072.04</v>
+        <v>5360.97</v>
       </c>
       <c r="L47" s="1">
-        <v>56259.7</v>
+        <v>5478.05</v>
       </c>
       <c r="M47" s="3">
-        <v>-328.9</v>
+        <v>-24.49</v>
       </c>
       <c r="N47" s="3">
-        <v>-351.4</v>
+        <v>-35</v>
       </c>
       <c r="O47" s="3">
-        <v>-402.01</v>
+        <v>-52.85</v>
       </c>
       <c r="P47" s="3">
-        <v>-109.29</v>
+        <v>-25.37</v>
       </c>
       <c r="Q47" s="3">
-        <v>1610.08</v>
+        <v>188.29</v>
       </c>
       <c r="R47" s="3">
-        <v>2277.6</v>
+        <v>261.32</v>
       </c>
       <c r="S47" s="3">
-        <v>37.74</v>
-      </c>
-      <c r="T47" t="str">
+        <v>48.71</v>
+      </c>
+      <c r="T47" s="3">
+        <v>17.24</v>
+      </c>
+      <c r="U47" s="3">
+        <v>27.94</v>
+      </c>
+      <c r="V47" s="3">
+        <v>36.64</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="str">
         <v/>
       </c>
     </row>
@@ -3324,60 +4029,75 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D48" s="1">
-        <v>26195.65</v>
+        <v>49026.45</v>
       </c>
       <c r="E48" s="2">
-        <v>-1.18</v>
+        <v>0.56</v>
       </c>
       <c r="F48" s="2">
-        <v>-3.73</v>
+        <v>4.78</v>
       </c>
       <c r="G48" s="2">
-        <v>-1.36</v>
+        <v>-1.11</v>
       </c>
       <c r="H48" s="2">
-        <v>-13.2</v>
+        <v>3.07</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>28527.81</v>
+        <v>49088.77</v>
       </c>
       <c r="K48" s="1">
-        <v>26693.86</v>
+        <v>48621.89</v>
       </c>
       <c r="L48" s="1">
-        <v>27555.3</v>
+        <v>50468.98</v>
       </c>
       <c r="M48" s="3">
-        <v>-260.62</v>
+        <v>-601.82</v>
       </c>
       <c r="N48" s="3">
-        <v>-263.46</v>
+        <v>-623.06</v>
       </c>
       <c r="O48" s="3">
-        <v>-507.71</v>
+        <v>-72.27</v>
       </c>
       <c r="P48" s="3">
-        <v>-301.14</v>
+        <v>414.56</v>
       </c>
       <c r="Q48" s="3">
-        <v>1281.95</v>
+        <v>120.22</v>
       </c>
       <c r="R48" s="3">
-        <v>1894.3</v>
+        <v>-287.12</v>
       </c>
       <c r="S48" s="3">
-        <v>36</v>
-      </c>
-      <c r="T48" t="str">
+        <v>47.36</v>
+      </c>
+      <c r="T48" s="3">
+        <v>18.76</v>
+      </c>
+      <c r="U48" s="3">
+        <v>34.97</v>
+      </c>
+      <c r="V48" s="3">
+        <v>43.99</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="str">
         <v/>
       </c>
     </row>
@@ -3386,60 +4106,75 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D49" s="1">
-        <v>47649.75</v>
+        <v>46517.9</v>
       </c>
       <c r="E49" s="2">
-        <v>-1.19</v>
+        <v>0.52</v>
       </c>
       <c r="F49" s="2">
-        <v>-3.34</v>
+        <v>4.6</v>
       </c>
       <c r="G49" s="2">
-        <v>-6.53</v>
+        <v>-2.8</v>
       </c>
       <c r="H49" s="2">
-        <v>8.63</v>
+        <v>5.76</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>47357.97</v>
+        <v>44963.55</v>
       </c>
       <c r="K49" s="1">
-        <v>49051.9</v>
+        <v>46321.62</v>
       </c>
       <c r="L49" s="1">
-        <v>51443.8</v>
+        <v>48073.08</v>
       </c>
       <c r="M49" s="3">
-        <v>-970.56</v>
+        <v>-639.14</v>
       </c>
       <c r="N49" s="3">
-        <v>-714.55</v>
+        <v>-559.17</v>
       </c>
       <c r="O49" s="3">
-        <v>889.87</v>
+        <v>540.78</v>
       </c>
       <c r="P49" s="3">
-        <v>1550.96</v>
+        <v>989.55</v>
       </c>
       <c r="Q49" s="3">
-        <v>2100.85</v>
+        <v>-290.14</v>
       </c>
       <c r="R49" s="3">
-        <v>1457.74</v>
+        <v>-1009.87</v>
       </c>
       <c r="S49" s="3">
-        <v>23.92</v>
-      </c>
-      <c r="T49" t="str">
+        <v>45.29</v>
+      </c>
+      <c r="T49" s="3">
+        <v>21.52</v>
+      </c>
+      <c r="U49" s="3">
+        <v>38.77</v>
+      </c>
+      <c r="V49" s="3">
+        <v>34.24</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="str">
         <v/>
       </c>
     </row>
@@ -3448,60 +4183,75 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>NIFTY500</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C50" t="str">
-        <v>NIFTY500</v>
+        <v>CNXIT</v>
       </c>
       <c r="D50" s="1">
-        <v>21427.6</v>
+        <v>31718.5</v>
       </c>
       <c r="E50" s="2">
-        <v>-1.24</v>
+        <v>0.52</v>
       </c>
       <c r="F50" s="2">
-        <v>-3.78</v>
+        <v>-0.87</v>
       </c>
       <c r="G50" s="2">
-        <v>-2.92</v>
+        <v>14.49</v>
       </c>
       <c r="H50" s="2">
-        <v>-10.24</v>
+        <v>-16.27</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>22832.04</v>
+        <v>30692.53</v>
       </c>
       <c r="K50" s="1">
-        <v>21881.73</v>
+        <v>31469.78</v>
       </c>
       <c r="L50" s="1">
-        <v>22745.63</v>
+        <v>29895.2</v>
       </c>
       <c r="M50" s="3">
-        <v>-271.94</v>
+        <v>801.13</v>
       </c>
       <c r="N50" s="3">
-        <v>-263.85</v>
+        <v>602.42</v>
       </c>
       <c r="O50" s="3">
-        <v>-241.67</v>
+        <v>-8.6</v>
       </c>
       <c r="P50" s="3">
-        <v>-45.53</v>
+        <v>-417.36</v>
       </c>
       <c r="Q50" s="3">
-        <v>484.75</v>
+        <v>-1683.11</v>
       </c>
       <c r="R50" s="3">
-        <v>798.9</v>
+        <v>-1152.17</v>
       </c>
       <c r="S50" s="3">
-        <v>31.86</v>
-      </c>
-      <c r="T50" t="str">
+        <v>62.17</v>
+      </c>
+      <c r="T50" s="3">
+        <v>26.04</v>
+      </c>
+      <c r="U50" s="3">
+        <v>14.94</v>
+      </c>
+      <c r="V50" s="3">
+        <v>30.29</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="str">
         <v/>
       </c>
     </row>
@@ -3510,60 +4260,75 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D51" s="1">
-        <v>5510.75</v>
+        <v>57567.75</v>
       </c>
       <c r="E51" s="2">
-        <v>-1.25</v>
+        <v>0.51</v>
       </c>
       <c r="F51" s="2">
-        <v>-2.14</v>
+        <v>3.17</v>
       </c>
       <c r="G51" s="2">
-        <v>0.7</v>
+        <v>-2.97</v>
       </c>
       <c r="H51" s="2">
-        <v>-13.7</v>
+        <v>-4.82</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>5948.69</v>
+        <v>60214.25</v>
       </c>
       <c r="K51" s="1">
-        <v>5543.59</v>
+        <v>57558.26</v>
       </c>
       <c r="L51" s="1">
-        <v>5678.67</v>
+        <v>60868.63</v>
       </c>
       <c r="M51" s="3">
-        <v>-25.74</v>
+        <v>-1087.05</v>
       </c>
       <c r="N51" s="3">
-        <v>-49.34</v>
+        <v>-1079.42</v>
       </c>
       <c r="O51" s="3">
-        <v>-122.29</v>
+        <v>-615.44</v>
       </c>
       <c r="P51" s="3">
-        <v>-96.45</v>
+        <v>193.9</v>
       </c>
       <c r="Q51" s="3">
-        <v>21.8</v>
+        <v>2868.96</v>
       </c>
       <c r="R51" s="3">
-        <v>138.84</v>
+        <v>3479.71</v>
       </c>
       <c r="S51" s="3">
-        <v>44.76</v>
-      </c>
-      <c r="T51" t="str">
+        <v>40.12</v>
+      </c>
+      <c r="T51" s="3">
+        <v>14.28</v>
+      </c>
+      <c r="U51" s="3">
+        <v>37.13</v>
+      </c>
+      <c r="V51" s="3">
+        <v>51.34</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="str">
         <v/>
       </c>
     </row>
@@ -3572,60 +4337,75 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D52" s="1">
-        <v>7356.85</v>
+        <v>17073.75</v>
       </c>
       <c r="E52" s="2">
-        <v>-1.28</v>
+        <v>0.5</v>
       </c>
       <c r="F52" s="2">
-        <v>-2.75</v>
+        <v>4.2</v>
       </c>
       <c r="G52" s="2">
-        <v>-4.51</v>
+        <v>-4.07</v>
       </c>
       <c r="H52" s="2">
-        <v>-14.5</v>
+        <v>2.33</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>7679.73</v>
+        <v>16951.42</v>
       </c>
       <c r="K52" s="1">
-        <v>7468.9</v>
+        <v>17072.24</v>
       </c>
       <c r="L52" s="1">
-        <v>7753.04</v>
+        <v>17928.35</v>
       </c>
       <c r="M52" s="3">
-        <v>-96.56</v>
+        <v>-314.68</v>
       </c>
       <c r="N52" s="3">
-        <v>-90.05</v>
+        <v>-276.94</v>
       </c>
       <c r="O52" s="3">
-        <v>-67.85</v>
+        <v>95.02</v>
       </c>
       <c r="P52" s="3">
-        <v>-18.85</v>
+        <v>317.18</v>
       </c>
       <c r="Q52" s="3">
-        <v>-305.65</v>
+        <v>1310.4</v>
       </c>
       <c r="R52" s="3">
-        <v>-248.31</v>
+        <v>1429.32</v>
       </c>
       <c r="S52" s="3">
-        <v>38.25</v>
-      </c>
-      <c r="T52" t="str">
+        <v>41.33</v>
+      </c>
+      <c r="T52" s="3">
+        <v>18.67</v>
+      </c>
+      <c r="U52" s="3">
+        <v>41.88</v>
+      </c>
+      <c r="V52" s="3">
+        <v>40.53</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="str">
         <v/>
       </c>
     </row>
@@ -3634,60 +4414,75 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>Nifty Total Market</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C53" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D53" s="1">
-        <v>12105.3</v>
+        <v>13750.3</v>
       </c>
       <c r="E53" s="2">
-        <v>-1.29</v>
+        <v>0.49</v>
       </c>
       <c r="F53" s="2">
-        <v>-3.94</v>
+        <v>1.1</v>
       </c>
       <c r="G53" s="2">
-        <v>-3.2</v>
+        <v>2.98</v>
       </c>
       <c r="H53" s="2">
-        <v>-9.62</v>
+        <v>-10.09</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>12856.69</v>
+        <v>14350.26</v>
       </c>
       <c r="K53" s="1">
-        <v>12377.17</v>
+        <v>13687.31</v>
       </c>
       <c r="L53" s="1">
-        <v>12865.16</v>
+        <v>13928.29</v>
       </c>
       <c r="M53" s="3">
-        <v>-155.97</v>
+        <v>-32.74</v>
       </c>
       <c r="N53" s="3">
-        <v>-147.15</v>
+        <v>-73.95</v>
       </c>
       <c r="O53" s="3">
-        <v>-115.47</v>
+        <v>-221.7</v>
       </c>
       <c r="P53" s="3">
-        <v>-2.6</v>
+        <v>-174.74</v>
       </c>
       <c r="Q53" s="3">
-        <v>611.22</v>
+        <v>-535.8</v>
       </c>
       <c r="R53" s="3">
-        <v>822.32</v>
+        <v>-491.7</v>
       </c>
       <c r="S53" s="3">
-        <v>31.07</v>
-      </c>
-      <c r="T53" t="str">
+        <v>51.14</v>
+      </c>
+      <c r="T53" s="3">
+        <v>18.48</v>
+      </c>
+      <c r="U53" s="3">
+        <v>24.07</v>
+      </c>
+      <c r="V53" s="3">
+        <v>23.11</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="str">
         <v/>
       </c>
     </row>
@@ -3696,60 +4491,75 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C54" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D54" s="1">
-        <v>1563.4</v>
+        <v>16578.45</v>
       </c>
       <c r="E54" s="2">
-        <v>-1.33</v>
+        <v>0.47</v>
       </c>
       <c r="F54" s="2">
-        <v>-5.15</v>
+        <v>3.19</v>
       </c>
       <c r="G54" s="2">
-        <v>-1.25</v>
+        <v>-2.64</v>
       </c>
       <c r="H54" s="2">
-        <v>8.22</v>
+        <v>-3.92</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>1469.5</v>
+        <v>17198.97</v>
       </c>
       <c r="K54" s="1">
-        <v>1600.49</v>
+        <v>16546.44</v>
       </c>
       <c r="L54" s="1">
-        <v>1574.14</v>
+        <v>17484.35</v>
       </c>
       <c r="M54" s="3">
-        <v>13.19</v>
+        <v>-299</v>
       </c>
       <c r="N54" s="3">
-        <v>14.44</v>
+        <v>-310.31</v>
       </c>
       <c r="O54" s="3">
-        <v>30.99</v>
+        <v>-137.82</v>
       </c>
       <c r="P54" s="3">
-        <v>31.31</v>
+        <v>95.33</v>
       </c>
       <c r="Q54" s="3">
-        <v>-74.96</v>
+        <v>900.83</v>
       </c>
       <c r="R54" s="3">
-        <v>-105.89</v>
+        <v>1048.41</v>
       </c>
       <c r="S54" s="3">
-        <v>46.1</v>
-      </c>
-      <c r="T54" t="str">
+        <v>41.14</v>
+      </c>
+      <c r="T54" s="3">
+        <v>14.59</v>
+      </c>
+      <c r="U54" s="3">
+        <v>34.12</v>
+      </c>
+      <c r="V54" s="3">
+        <v>48.64</v>
+      </c>
+      <c r="W54" s="3">
+        <v>0</v>
+      </c>
+      <c r="X54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="str">
         <v/>
       </c>
     </row>
@@ -3758,60 +4568,75 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D55" s="1">
-        <v>15209.55</v>
+        <v>51827.6</v>
       </c>
       <c r="E55" s="2">
-        <v>-1.39</v>
+        <v>0.46</v>
       </c>
       <c r="F55" s="2">
-        <v>-4</v>
+        <v>5.62</v>
       </c>
       <c r="G55" s="2">
-        <v>-3.48</v>
+        <v>-2.02</v>
       </c>
       <c r="H55" s="2">
-        <v>-9.76</v>
+        <v>-1.67</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>16287.1</v>
+        <v>52483.39</v>
       </c>
       <c r="K55" s="1">
-        <v>15574.1</v>
+        <v>51426.02</v>
       </c>
       <c r="L55" s="1">
-        <v>16271.59</v>
+        <v>53670.98</v>
       </c>
       <c r="M55" s="3">
-        <v>-223.57</v>
+        <v>-759.31</v>
       </c>
       <c r="N55" s="3">
-        <v>-212.26</v>
+        <v>-762.81</v>
       </c>
       <c r="O55" s="3">
-        <v>-170.83</v>
+        <v>-202.5</v>
       </c>
       <c r="P55" s="3">
-        <v>-6.87</v>
+        <v>289.93</v>
       </c>
       <c r="Q55" s="3">
-        <v>891.89</v>
+        <v>-689.94</v>
       </c>
       <c r="R55" s="3">
-        <v>1173.87</v>
+        <v>-1109.68</v>
       </c>
       <c r="S55" s="3">
-        <v>29.7</v>
-      </c>
-      <c r="T55" t="str">
+        <v>46.54</v>
+      </c>
+      <c r="T55" s="3">
+        <v>16.71</v>
+      </c>
+      <c r="U55" s="3">
+        <v>37.63</v>
+      </c>
+      <c r="V55" s="3">
+        <v>42.62</v>
+      </c>
+      <c r="W55" s="3">
+        <v>0</v>
+      </c>
+      <c r="X55" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="str">
         <v/>
       </c>
     </row>
@@ -3820,60 +4645,75 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C56" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D56" s="1">
-        <v>8792.3</v>
+        <v>28602.95</v>
       </c>
       <c r="E56" s="2">
-        <v>-1.41</v>
+        <v>0.46</v>
       </c>
       <c r="F56" s="2">
-        <v>-3.38</v>
+        <v>4.77</v>
       </c>
       <c r="G56" s="2">
-        <v>-5.56</v>
+        <v>-3.1</v>
       </c>
       <c r="H56" s="2">
-        <v>-7.6</v>
+        <v>-8.17</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>9757.44</v>
+        <v>30300.95</v>
       </c>
       <c r="K56" s="1">
-        <v>8981.6</v>
+        <v>28472.05</v>
       </c>
       <c r="L56" s="1">
-        <v>9476.27</v>
+        <v>29961.36</v>
       </c>
       <c r="M56" s="3">
-        <v>-170.17</v>
+        <v>-506.19</v>
       </c>
       <c r="N56" s="3">
-        <v>-167.85</v>
+        <v>-506.83</v>
       </c>
       <c r="O56" s="3">
-        <v>-193.2</v>
+        <v>-481.27</v>
       </c>
       <c r="P56" s="3">
-        <v>-68.85</v>
+        <v>-179.97</v>
       </c>
       <c r="Q56" s="3">
-        <v>377.04</v>
+        <v>1465.35</v>
       </c>
       <c r="R56" s="3">
-        <v>505.77</v>
+        <v>2002.79</v>
       </c>
       <c r="S56" s="3">
-        <v>29.94</v>
-      </c>
-      <c r="T56" t="str">
+        <v>43.78</v>
+      </c>
+      <c r="T56" s="3">
+        <v>15.36</v>
+      </c>
+      <c r="U56" s="3">
+        <v>35.36</v>
+      </c>
+      <c r="V56" s="3">
+        <v>42.84</v>
+      </c>
+      <c r="W56" s="3">
+        <v>0</v>
+      </c>
+      <c r="X56" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="str">
         <v/>
       </c>
     </row>
@@ -3882,60 +4722,75 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C57" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D57" s="1">
-        <v>18680</v>
+        <v>19692.25</v>
       </c>
       <c r="E57" s="2">
-        <v>-1.42</v>
+        <v>0.46</v>
       </c>
       <c r="F57" s="2">
-        <v>-4.06</v>
+        <v>3.25</v>
       </c>
       <c r="G57" s="2">
-        <v>-1.39</v>
+        <v>-3.54</v>
       </c>
       <c r="H57" s="2">
-        <v>-12.75</v>
+        <v>-2.6</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>20086.53</v>
+        <v>20242.38</v>
       </c>
       <c r="K57" s="1">
-        <v>19063.77</v>
+        <v>19706.33</v>
       </c>
       <c r="L57" s="1">
-        <v>19769.3</v>
+        <v>20775.79</v>
       </c>
       <c r="M57" s="3">
-        <v>-183.77</v>
+        <v>-365.89</v>
       </c>
       <c r="N57" s="3">
-        <v>-210.33</v>
+        <v>-348.18</v>
       </c>
       <c r="O57" s="3">
-        <v>-303.22</v>
+        <v>-95.36</v>
       </c>
       <c r="P57" s="3">
-        <v>-146.4</v>
+        <v>172.71</v>
       </c>
       <c r="Q57" s="3">
-        <v>462.8</v>
+        <v>1572.16</v>
       </c>
       <c r="R57" s="3">
-        <v>790.61</v>
+        <v>1822.17</v>
       </c>
       <c r="S57" s="3">
-        <v>36.05</v>
-      </c>
-      <c r="T57" t="str">
+        <v>39.75</v>
+      </c>
+      <c r="T57" s="3">
+        <v>15.67</v>
+      </c>
+      <c r="U57" s="3">
+        <v>41.04</v>
+      </c>
+      <c r="V57" s="3">
+        <v>49.83</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="str">
         <v/>
       </c>
     </row>
@@ -3944,60 +4799,75 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D58" s="1">
-        <v>15081.85</v>
+        <v>21157.45</v>
       </c>
       <c r="E58" s="2">
-        <v>-1.44</v>
+        <v>0.44</v>
       </c>
       <c r="F58" s="2">
-        <v>-4.47</v>
+        <v>2.74</v>
       </c>
       <c r="G58" s="2">
-        <v>-5.84</v>
+        <v>-3.25</v>
       </c>
       <c r="H58" s="2">
-        <v>-5.59</v>
+        <v>-5.03</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>16004.23</v>
+        <v>22146.75</v>
       </c>
       <c r="K58" s="1">
-        <v>15527.97</v>
+        <v>21181.86</v>
       </c>
       <c r="L58" s="1">
-        <v>16383.51</v>
+        <v>22376.78</v>
       </c>
       <c r="M58" s="3">
-        <v>-288.64</v>
+        <v>-394.28</v>
       </c>
       <c r="N58" s="3">
-        <v>-254.72</v>
+        <v>-390.2</v>
       </c>
       <c r="O58" s="3">
-        <v>-70.03</v>
+        <v>-220.1</v>
       </c>
       <c r="P58" s="3">
-        <v>131.46</v>
+        <v>74.58</v>
       </c>
       <c r="Q58" s="3">
-        <v>333.27</v>
+        <v>1699.3</v>
       </c>
       <c r="R58" s="3">
-        <v>323.55</v>
+        <v>2026.47</v>
       </c>
       <c r="S58" s="3">
-        <v>26.71</v>
-      </c>
-      <c r="T58" t="str">
+        <v>38.83</v>
+      </c>
+      <c r="T58" s="3">
+        <v>13.81</v>
+      </c>
+      <c r="U58" s="3">
+        <v>37.68</v>
+      </c>
+      <c r="V58" s="3">
+        <v>51.17</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="str">
         <v/>
       </c>
     </row>
@@ -4006,60 +4876,75 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D59" s="1">
-        <v>31640.45</v>
+        <v>24458</v>
       </c>
       <c r="E59" s="2">
-        <v>-1.45</v>
+        <v>0.43</v>
       </c>
       <c r="F59" s="2">
-        <v>-3.68</v>
+        <v>2.65</v>
       </c>
       <c r="G59" s="2">
-        <v>-3.71</v>
+        <v>-6.83</v>
       </c>
       <c r="H59" s="2">
-        <v>-6.82</v>
+        <v>8.48</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>33676.94</v>
+        <v>23655.26</v>
       </c>
       <c r="K59" s="1">
-        <v>32361.46</v>
+        <v>24641.88</v>
       </c>
       <c r="L59" s="1">
-        <v>33854.46</v>
+        <v>25924.64</v>
       </c>
       <c r="M59" s="3">
-        <v>-474.3</v>
+        <v>-506.99</v>
       </c>
       <c r="N59" s="3">
-        <v>-462.62</v>
+        <v>-393.48</v>
       </c>
       <c r="O59" s="3">
-        <v>-293.22</v>
+        <v>439.17</v>
       </c>
       <c r="P59" s="3">
-        <v>87.44</v>
+        <v>766.35</v>
       </c>
       <c r="Q59" s="3">
-        <v>1950.37</v>
+        <v>2295.71</v>
       </c>
       <c r="R59" s="3">
-        <v>2419.99</v>
+        <v>2351.84</v>
       </c>
       <c r="S59" s="3">
-        <v>29.92</v>
-      </c>
-      <c r="T59" t="str">
+        <v>37.48</v>
+      </c>
+      <c r="T59" s="3">
+        <v>14.4</v>
+      </c>
+      <c r="U59" s="3">
+        <v>39.19</v>
+      </c>
+      <c r="V59" s="3">
+        <v>38.05</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="str">
         <v/>
       </c>
     </row>
@@ -4068,60 +4953,75 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D60" s="1">
-        <v>15117.8</v>
+        <v>24823.2</v>
       </c>
       <c r="E60" s="2">
-        <v>-1.56</v>
+        <v>0.4</v>
       </c>
       <c r="F60" s="2">
-        <v>-4.46</v>
+        <v>1.95</v>
       </c>
       <c r="G60" s="2">
-        <v>-4.02</v>
+        <v>-1.57</v>
       </c>
       <c r="H60" s="2">
-        <v>-8.29</v>
+        <v>-8.32</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>16013.54</v>
+        <v>26189.53</v>
       </c>
       <c r="K60" s="1">
-        <v>15535.59</v>
+        <v>24711.1</v>
       </c>
       <c r="L60" s="1">
-        <v>16188.45</v>
+        <v>25842.1</v>
       </c>
       <c r="M60" s="3">
-        <v>-217.14</v>
+        <v>-328.53</v>
       </c>
       <c r="N60" s="3">
-        <v>-191.38</v>
+        <v>-401.13</v>
       </c>
       <c r="O60" s="3">
-        <v>-102.62</v>
+        <v>-402.4</v>
       </c>
       <c r="P60" s="3">
-        <v>56.11</v>
+        <v>-137.06</v>
       </c>
       <c r="Q60" s="3">
-        <v>890.57</v>
+        <v>1166.19</v>
       </c>
       <c r="R60" s="3">
-        <v>1142.8</v>
+        <v>1599.97</v>
       </c>
       <c r="S60" s="3">
-        <v>27.82</v>
-      </c>
-      <c r="T60" t="str">
+        <v>43.19</v>
+      </c>
+      <c r="T60" s="3">
+        <v>13.36</v>
+      </c>
+      <c r="U60" s="3">
+        <v>26.55</v>
+      </c>
+      <c r="V60" s="3">
+        <v>49.37</v>
+      </c>
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="str">
         <v/>
       </c>
     </row>
@@ -4130,60 +5030,75 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D61" s="1">
-        <v>14516.75</v>
+        <v>18844.75</v>
       </c>
       <c r="E61" s="2">
-        <v>-1.57</v>
+        <v>0.4</v>
       </c>
       <c r="F61" s="2">
-        <v>-4.33</v>
+        <v>0.88</v>
       </c>
       <c r="G61" s="2">
-        <v>-6.07</v>
+        <v>-0.52</v>
       </c>
       <c r="H61" s="2">
-        <v>-5.81</v>
+        <v>-11.99</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>15625.39</v>
+        <v>20033.36</v>
       </c>
       <c r="K61" s="1">
-        <v>14946.58</v>
+        <v>18925.73</v>
       </c>
       <c r="L61" s="1">
-        <v>15847.78</v>
+        <v>19604.37</v>
       </c>
       <c r="M61" s="3">
-        <v>-301.4</v>
+        <v>-194.6</v>
       </c>
       <c r="N61" s="3">
-        <v>-273.48</v>
+        <v>-201.58</v>
       </c>
       <c r="O61" s="3">
-        <v>-119.2</v>
+        <v>-334.84</v>
       </c>
       <c r="P61" s="3">
-        <v>96.42</v>
+        <v>-184.09</v>
       </c>
       <c r="Q61" s="3">
-        <v>1221.05</v>
+        <v>475.95</v>
       </c>
       <c r="R61" s="3">
-        <v>1438.69</v>
+        <v>793.23</v>
       </c>
       <c r="S61" s="3">
-        <v>26.18</v>
-      </c>
-      <c r="T61" t="str">
+        <v>41.35</v>
+      </c>
+      <c r="T61" s="3">
+        <v>13.83</v>
+      </c>
+      <c r="U61" s="3">
+        <v>32.37</v>
+      </c>
+      <c r="V61" s="3">
+        <v>42.17</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="str">
         <v/>
       </c>
     </row>
@@ -4192,60 +5107,75 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C62" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D62" s="1">
-        <v>8885.75</v>
+        <v>11811.25</v>
       </c>
       <c r="E62" s="2">
-        <v>-1.64</v>
+        <v>0.36</v>
       </c>
       <c r="F62" s="2">
-        <v>-3.91</v>
+        <v>2.9</v>
       </c>
       <c r="G62" s="2">
-        <v>-5.07</v>
+        <v>-7.44</v>
       </c>
       <c r="H62" s="2">
-        <v>-9.82</v>
+        <v>5.76</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>9984.3</v>
+        <v>12490.85</v>
       </c>
       <c r="K62" s="1">
-        <v>9123.11</v>
+        <v>11859.33</v>
       </c>
       <c r="L62" s="1">
-        <v>9519.4</v>
+        <v>12702.09</v>
       </c>
       <c r="M62" s="3">
-        <v>-141.61</v>
+        <v>-281.79</v>
       </c>
       <c r="N62" s="3">
-        <v>-129.11</v>
+        <v>-284.1</v>
       </c>
       <c r="O62" s="3">
-        <v>-244.33</v>
+        <v>-68.91</v>
       </c>
       <c r="P62" s="3">
-        <v>-150.14</v>
+        <v>148.53</v>
       </c>
       <c r="Q62" s="3">
-        <v>776.06</v>
+        <v>1133.95</v>
       </c>
       <c r="R62" s="3">
-        <v>1088.64</v>
+        <v>1129.48</v>
       </c>
       <c r="S62" s="3">
-        <v>27.83</v>
-      </c>
-      <c r="T62" t="str">
+        <v>39.07</v>
+      </c>
+      <c r="T62" s="3">
+        <v>12.31</v>
+      </c>
+      <c r="U62" s="3">
+        <v>32.37</v>
+      </c>
+      <c r="V62" s="3">
+        <v>38.45</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="str">
         <v/>
       </c>
     </row>
@@ -4254,60 +5184,75 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C63" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D63" s="1">
-        <v>34520.05</v>
+        <v>10333.6</v>
       </c>
       <c r="E63" s="2">
-        <v>-1.66</v>
+        <v>0.36</v>
       </c>
       <c r="F63" s="2">
-        <v>-4.62</v>
+        <v>-0.45</v>
       </c>
       <c r="G63" s="2">
-        <v>-5.78</v>
+        <v>-2.65</v>
       </c>
       <c r="H63" s="2">
-        <v>-2.28</v>
+        <v>-15.51</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>37722.41</v>
+        <v>11255.99</v>
       </c>
       <c r="K63" s="1">
-        <v>35665.35</v>
+        <v>10439.52</v>
       </c>
       <c r="L63" s="1">
-        <v>37328.98</v>
+        <v>10805.23</v>
       </c>
       <c r="M63" s="3">
-        <v>-621.4</v>
+        <v>-111.86</v>
       </c>
       <c r="N63" s="3">
-        <v>-515.77</v>
+        <v>-118.66</v>
       </c>
       <c r="O63" s="3">
-        <v>-592.5</v>
+        <v>-248.09</v>
       </c>
       <c r="P63" s="3">
-        <v>-87.54</v>
+        <v>-178.65</v>
       </c>
       <c r="Q63" s="3">
-        <v>889.89</v>
+        <v>64.28</v>
       </c>
       <c r="R63" s="3">
-        <v>1219.3</v>
+        <v>277.65</v>
       </c>
       <c r="S63" s="3">
-        <v>24.93</v>
-      </c>
-      <c r="T63" t="str">
+        <v>38.67</v>
+      </c>
+      <c r="T63" s="3">
+        <v>14.72</v>
+      </c>
+      <c r="U63" s="3">
+        <v>30.34</v>
+      </c>
+      <c r="V63" s="3">
+        <v>31.01</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="str">
         <v/>
       </c>
     </row>
@@ -4316,60 +5261,75 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C64" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D64" s="1">
-        <v>27765.7</v>
+        <v>8811.35</v>
       </c>
       <c r="E64" s="2">
-        <v>-1.96</v>
+        <v>0.33</v>
       </c>
       <c r="F64" s="2">
-        <v>-5.93</v>
+        <v>2.92</v>
       </c>
       <c r="G64" s="2">
-        <v>-8.47</v>
+        <v>-5.02</v>
       </c>
       <c r="H64" s="2">
-        <v>-9.17</v>
+        <v>13.73</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>31386.59</v>
+        <v>8861.13</v>
       </c>
       <c r="K64" s="1">
-        <v>29044.94</v>
+        <v>8869.16</v>
       </c>
       <c r="L64" s="1">
-        <v>31421.13</v>
+        <v>9375.76</v>
       </c>
       <c r="M64" s="3">
-        <v>-832.31</v>
+        <v>-170.81</v>
       </c>
       <c r="N64" s="3">
-        <v>-698.23</v>
+        <v>-151.69</v>
       </c>
       <c r="O64" s="3">
-        <v>-522.2</v>
+        <v>41.47</v>
       </c>
       <c r="P64" s="3">
-        <v>61.35</v>
+        <v>193.03</v>
       </c>
       <c r="Q64" s="3">
-        <v>1921.26</v>
+        <v>603.03</v>
       </c>
       <c r="R64" s="3">
-        <v>2384.15</v>
+        <v>522.71</v>
       </c>
       <c r="S64" s="3">
-        <v>19.44</v>
-      </c>
-      <c r="T64" t="str">
+        <v>40.3</v>
+      </c>
+      <c r="T64" s="3">
+        <v>18.97</v>
+      </c>
+      <c r="U64" s="3">
+        <v>34.69</v>
+      </c>
+      <c r="V64" s="3">
+        <v>29.12</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="str">
         <v/>
       </c>
     </row>
@@ -4378,60 +5338,75 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C65" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D65" s="1">
-        <v>56812.1</v>
+        <v>13329.2</v>
       </c>
       <c r="E65" s="2">
-        <v>-2.05</v>
+        <v>0.32</v>
       </c>
       <c r="F65" s="2">
-        <v>-5.73</v>
+        <v>2.27</v>
       </c>
       <c r="G65" s="2">
-        <v>-6.52</v>
+        <v>-2.93</v>
       </c>
       <c r="H65" s="2">
-        <v>-8.24</v>
+        <v>-3.25</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>61702.99</v>
+        <v>13983.09</v>
       </c>
       <c r="K65" s="1">
-        <v>59262.32</v>
+        <v>13362.65</v>
       </c>
       <c r="L65" s="1">
-        <v>62465.58</v>
+        <v>14165.18</v>
       </c>
       <c r="M65" s="3">
-        <v>-1173.13</v>
+        <v>-257.6</v>
       </c>
       <c r="N65" s="3">
-        <v>-867.23</v>
+        <v>-260.28</v>
       </c>
       <c r="O65" s="3">
-        <v>-508.97</v>
+        <v>-142.59</v>
       </c>
       <c r="P65" s="3">
-        <v>188.66</v>
+        <v>69.21</v>
       </c>
       <c r="Q65" s="3">
-        <v>-248.68</v>
+        <v>868.4</v>
       </c>
       <c r="R65" s="3">
-        <v>-222.67</v>
+        <v>1000.37</v>
       </c>
       <c r="S65" s="3">
-        <v>22.73</v>
-      </c>
-      <c r="T65" t="str">
+        <v>38</v>
+      </c>
+      <c r="T65" s="3">
+        <v>12.76</v>
+      </c>
+      <c r="U65" s="3">
+        <v>33.46</v>
+      </c>
+      <c r="V65" s="3">
+        <v>46.85</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="str">
         <v/>
       </c>
     </row>
@@ -4440,60 +5415,75 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C66" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D66" s="1">
-        <v>20592.75</v>
+        <v>22293.45</v>
       </c>
       <c r="E66" s="2">
-        <v>-2.07</v>
+        <v>0.31</v>
       </c>
       <c r="F66" s="2">
-        <v>-5.26</v>
+        <v>2.6</v>
       </c>
       <c r="G66" s="2">
-        <v>-5.83</v>
+        <v>-2.08</v>
       </c>
       <c r="H66" s="2">
-        <v>-7.56</v>
+        <v>-7.33</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>22176.63</v>
+        <v>23442.37</v>
       </c>
       <c r="K66" s="1">
-        <v>21361.29</v>
+        <v>22348.7</v>
       </c>
       <c r="L66" s="1">
-        <v>22574.75</v>
+        <v>23451.03</v>
       </c>
       <c r="M66" s="3">
-        <v>-417.73</v>
+        <v>-356.65</v>
       </c>
       <c r="N66" s="3">
-        <v>-353.09</v>
+        <v>-348.32</v>
       </c>
       <c r="O66" s="3">
-        <v>-152.78</v>
+        <v>-314.91</v>
       </c>
       <c r="P66" s="3">
-        <v>148.25</v>
+        <v>-46.35</v>
       </c>
       <c r="Q66" s="3">
-        <v>1654.26</v>
+        <v>1008.68</v>
       </c>
       <c r="R66" s="3">
-        <v>2017.46</v>
+        <v>1356.57</v>
       </c>
       <c r="S66" s="3">
-        <v>23.29</v>
-      </c>
-      <c r="T66" t="str">
+        <v>39.9</v>
+      </c>
+      <c r="T66" s="3">
+        <v>15.84</v>
+      </c>
+      <c r="U66" s="3">
+        <v>36.27</v>
+      </c>
+      <c r="V66" s="3">
+        <v>42.88</v>
+      </c>
+      <c r="W66" s="3">
+        <v>0</v>
+      </c>
+      <c r="X66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="str">
         <v/>
       </c>
     </row>
@@ -4502,60 +5492,75 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D67" s="1">
-        <v>16066.4</v>
+        <v>26849.1</v>
       </c>
       <c r="E67" s="2">
-        <v>-2.1</v>
+        <v>0.29</v>
       </c>
       <c r="F67" s="2">
-        <v>-5.19</v>
+        <v>1.99</v>
       </c>
       <c r="G67" s="2">
-        <v>-5.65</v>
-      </c>
-      <c r="H67" s="2">
-        <v>-6.88</v>
+        <v>-5.34</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
-      <c r="J67" s="1">
-        <v>17219.19</v>
+      <c r="J67" t="str">
+        <v/>
       </c>
       <c r="K67" s="1">
-        <v>16647.11</v>
+        <v>27122.88</v>
       </c>
       <c r="L67" s="1">
-        <v>17635.02</v>
+        <v>28924.83</v>
       </c>
       <c r="M67" s="3">
-        <v>-336.34</v>
+        <v>-643.67</v>
       </c>
       <c r="N67" s="3">
-        <v>-293.24</v>
+        <v>-567.91</v>
       </c>
       <c r="O67" s="3">
-        <v>-89.81</v>
+        <v>-383.13</v>
       </c>
       <c r="P67" s="3">
-        <v>153.62</v>
+        <v>50.05</v>
       </c>
       <c r="Q67" s="3">
-        <v>859.98</v>
+        <v>197.84</v>
       </c>
       <c r="R67" s="3">
-        <v>1040.24</v>
+        <v>180.85</v>
       </c>
       <c r="S67" s="3">
-        <v>24.09</v>
-      </c>
-      <c r="T67" t="str">
+        <v>34.81</v>
+      </c>
+      <c r="T67" s="3">
+        <v>16.03</v>
+      </c>
+      <c r="U67" s="3">
+        <v>38.76</v>
+      </c>
+      <c r="V67" s="3">
+        <v>41.2</v>
+      </c>
+      <c r="W67" s="3">
+        <v>0</v>
+      </c>
+      <c r="X67" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="str">
         <v/>
       </c>
     </row>
@@ -4564,60 +5569,75 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D68" s="1">
-        <v>13033.05</v>
+        <v>2981.5</v>
       </c>
       <c r="E68" s="2">
-        <v>-2.12</v>
+        <v>0.26</v>
       </c>
       <c r="F68" s="2">
-        <v>-4.99</v>
+        <v>0.53</v>
       </c>
       <c r="G68" s="2">
-        <v>-5.08</v>
+        <v>-1.07</v>
       </c>
       <c r="H68" s="2">
-        <v>-5.4</v>
+        <v>0.49</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>13996.84</v>
+        <v>3001.43</v>
       </c>
       <c r="K68" s="1">
-        <v>13483.59</v>
+        <v>2975.97</v>
       </c>
       <c r="L68" s="1">
-        <v>14305.74</v>
+        <v>3017.76</v>
       </c>
       <c r="M68" s="3">
-        <v>-271.86</v>
+        <v>-13.73</v>
       </c>
       <c r="N68" s="3">
-        <v>-246.11</v>
+        <v>-14.94</v>
       </c>
       <c r="O68" s="3">
-        <v>-95.59</v>
+        <v>-2.34</v>
       </c>
       <c r="P68" s="3">
-        <v>122.16</v>
+        <v>8.61</v>
       </c>
       <c r="Q68" s="3">
-        <v>844.78</v>
+        <v>115.65</v>
       </c>
       <c r="R68" s="3">
-        <v>995.64</v>
+        <v>133.01</v>
       </c>
       <c r="S68" s="3">
-        <v>25.6</v>
-      </c>
-      <c r="T68" t="str">
+        <v>41.41</v>
+      </c>
+      <c r="T68" s="3">
+        <v>20.62</v>
+      </c>
+      <c r="U68" s="3">
+        <v>37.25</v>
+      </c>
+      <c r="V68" s="3">
+        <v>49.76</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="str">
         <v/>
       </c>
     </row>
@@ -4626,60 +5646,75 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D69" s="1">
-        <v>21727.8</v>
+        <v>15457.45</v>
       </c>
       <c r="E69" s="2">
-        <v>-2.14</v>
+        <v>0.25</v>
       </c>
       <c r="F69" s="2">
-        <v>-5.39</v>
+        <v>2.75</v>
       </c>
       <c r="G69" s="2">
-        <v>-4.56</v>
+        <v>-5.1</v>
       </c>
       <c r="H69" s="2">
-        <v>-9.69</v>
+        <v>-3.42</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>23481.91</v>
+        <v>16110.89</v>
       </c>
       <c r="K69" s="1">
-        <v>22531.45</v>
+        <v>15562.29</v>
       </c>
       <c r="L69" s="1">
-        <v>23665.6</v>
+        <v>16622.1</v>
       </c>
       <c r="M69" s="3">
-        <v>-367.53</v>
+        <v>-359.69</v>
       </c>
       <c r="N69" s="3">
-        <v>-312.41</v>
+        <v>-329.85</v>
       </c>
       <c r="O69" s="3">
-        <v>-256.55</v>
+        <v>-91.45</v>
       </c>
       <c r="P69" s="3">
-        <v>20.79</v>
+        <v>158.82</v>
       </c>
       <c r="Q69" s="3">
-        <v>963.56</v>
+        <v>1533.31</v>
       </c>
       <c r="R69" s="3">
-        <v>1347.55</v>
+        <v>1744.99</v>
       </c>
       <c r="S69" s="3">
-        <v>26.17</v>
-      </c>
-      <c r="T69" t="str">
+        <v>36.67</v>
+      </c>
+      <c r="T69" s="3">
+        <v>12.13</v>
+      </c>
+      <c r="U69" s="3">
+        <v>36.11</v>
+      </c>
+      <c r="V69" s="3">
+        <v>46.11</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="str">
         <v/>
       </c>
     </row>
@@ -4688,60 +5723,75 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D70" s="1">
-        <v>46788.25</v>
+        <v>3297.84</v>
       </c>
       <c r="E70" s="2">
-        <v>-2.18</v>
+        <v>0.23</v>
       </c>
       <c r="F70" s="2">
-        <v>-5.68</v>
+        <v>0.42</v>
       </c>
       <c r="G70" s="2">
-        <v>-5.62</v>
+        <v>-0.72</v>
       </c>
       <c r="H70" s="2">
-        <v>-1.63</v>
+        <v>1.73</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>49077.2</v>
+        <v>3296.36</v>
       </c>
       <c r="K70" s="1">
-        <v>48691.57</v>
+        <v>3291.5</v>
       </c>
       <c r="L70" s="1">
-        <v>50765.67</v>
+        <v>3338.77</v>
       </c>
       <c r="M70" s="3">
-        <v>-743.9</v>
+        <v>-14.51</v>
       </c>
       <c r="N70" s="3">
-        <v>-528.11</v>
+        <v>-16.55</v>
       </c>
       <c r="O70" s="3">
-        <v>-3.03</v>
+        <v>4.48</v>
       </c>
       <c r="P70" s="3">
-        <v>536.27</v>
+        <v>18.08</v>
       </c>
       <c r="Q70" s="3">
-        <v>-58.33</v>
+        <v>137.44</v>
       </c>
       <c r="R70" s="3">
-        <v>-322.83</v>
+        <v>154.09</v>
       </c>
       <c r="S70" s="3">
-        <v>24.75</v>
-      </c>
-      <c r="T70" t="str">
+        <v>43.53</v>
+      </c>
+      <c r="T70" s="3">
+        <v>14.87</v>
+      </c>
+      <c r="U70" s="3">
+        <v>29.49</v>
+      </c>
+      <c r="V70" s="3">
+        <v>50.33</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="str">
         <v/>
       </c>
     </row>
@@ -4750,60 +5800,75 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C71" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D71" s="1">
-        <v>55800.65</v>
+        <v>3468.55</v>
       </c>
       <c r="E71" s="2">
-        <v>-2.21</v>
+        <v>0.22</v>
       </c>
       <c r="F71" s="2">
-        <v>-5.63</v>
+        <v>0.49</v>
       </c>
       <c r="G71" s="2">
-        <v>-5.95</v>
+        <v>-1.51</v>
       </c>
       <c r="H71" s="2">
-        <v>-7.74</v>
+        <v>-0.7</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>60295.21</v>
+        <v>3494.74</v>
       </c>
       <c r="K71" s="1">
-        <v>58034.89</v>
+        <v>3467.56</v>
       </c>
       <c r="L71" s="1">
-        <v>61416.78</v>
+        <v>3520.5</v>
       </c>
       <c r="M71" s="3">
-        <v>-1161.74</v>
+        <v>-18.94</v>
       </c>
       <c r="N71" s="3">
-        <v>-971.27</v>
+        <v>-18.52</v>
       </c>
       <c r="O71" s="3">
-        <v>-439.23</v>
+        <v>-2.38</v>
       </c>
       <c r="P71" s="3">
-        <v>396.23</v>
+        <v>11.65</v>
       </c>
       <c r="Q71" s="3">
-        <v>2727.99</v>
+        <v>118.82</v>
       </c>
       <c r="R71" s="3">
-        <v>3451.52</v>
+        <v>141.9</v>
       </c>
       <c r="S71" s="3">
-        <v>23.59</v>
-      </c>
-      <c r="T71" t="str">
+        <v>40.23</v>
+      </c>
+      <c r="T71" s="3">
+        <v>20.45</v>
+      </c>
+      <c r="U71" s="3">
+        <v>34.18</v>
+      </c>
+      <c r="V71" s="3">
+        <v>33.1</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="str">
         <v/>
       </c>
     </row>
@@ -4812,60 +5877,75 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D72" s="1">
-        <v>8070.7</v>
+        <v>3072.06</v>
       </c>
       <c r="E72" s="2">
-        <v>-2.26</v>
+        <v>0.22</v>
       </c>
       <c r="F72" s="2">
-        <v>-0.3</v>
+        <v>0.48</v>
       </c>
       <c r="G72" s="2">
-        <v>0.68</v>
+        <v>-1.04</v>
       </c>
       <c r="H72" s="2">
-        <v>-5.42</v>
+        <v>0.65</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>8571.95</v>
+        <v>3086.21</v>
       </c>
       <c r="K72" s="1">
-        <v>8152.13</v>
+        <v>3067.5</v>
       </c>
       <c r="L72" s="1">
-        <v>8345.06</v>
+        <v>3109.34</v>
       </c>
       <c r="M72" s="3">
-        <v>-35.55</v>
+        <v>-13.8</v>
       </c>
       <c r="N72" s="3">
-        <v>-62.29</v>
+        <v>-14.87</v>
       </c>
       <c r="O72" s="3">
-        <v>-89.97</v>
+        <v>-0.31</v>
       </c>
       <c r="P72" s="3">
-        <v>-32.65</v>
+        <v>11.05</v>
       </c>
       <c r="Q72" s="3">
-        <v>560.95</v>
+        <v>119.4</v>
       </c>
       <c r="R72" s="3">
-        <v>682.51</v>
+        <v>136.73</v>
       </c>
       <c r="S72" s="3">
-        <v>44.6</v>
-      </c>
-      <c r="T72" t="str">
+        <v>41.08</v>
+      </c>
+      <c r="T72" s="3">
+        <v>19.03</v>
+      </c>
+      <c r="U72" s="3">
+        <v>37.28</v>
+      </c>
+      <c r="V72" s="3">
+        <v>48.52</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="str">
         <v/>
       </c>
     </row>
@@ -4874,60 +5954,75 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C73" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D73" s="1">
-        <v>65828.6</v>
+        <v>2610.37</v>
       </c>
       <c r="E73" s="2">
-        <v>-2.27</v>
+        <v>0.2</v>
       </c>
       <c r="F73" s="2">
-        <v>-4.58</v>
+        <v>0.56</v>
       </c>
       <c r="G73" s="2">
-        <v>-5.62</v>
+        <v>-1.06</v>
       </c>
       <c r="H73" s="2">
-        <v>-5.1</v>
+        <v>-0.06</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>70018.75</v>
+        <v>2632.02</v>
       </c>
       <c r="K73" s="1">
-        <v>67998.34</v>
+        <v>2605.31</v>
       </c>
       <c r="L73" s="1">
-        <v>71491.06</v>
+        <v>2641.36</v>
       </c>
       <c r="M73" s="3">
-        <v>-1177.52</v>
+        <v>-11.8</v>
       </c>
       <c r="N73" s="3">
-        <v>-1032.13</v>
+        <v>-13.12</v>
       </c>
       <c r="O73" s="3">
-        <v>-344.01</v>
+        <v>-4.05</v>
       </c>
       <c r="P73" s="3">
-        <v>549.61</v>
+        <v>5.12</v>
       </c>
       <c r="Q73" s="3">
-        <v>2518.21</v>
+        <v>90.76</v>
       </c>
       <c r="R73" s="3">
-        <v>3153.26</v>
+        <v>106.56</v>
       </c>
       <c r="S73" s="3">
-        <v>26.85</v>
-      </c>
-      <c r="T73" t="str">
+        <v>42.35</v>
+      </c>
+      <c r="T73" s="3">
+        <v>22.48</v>
+      </c>
+      <c r="U73" s="3">
+        <v>31.49</v>
+      </c>
+      <c r="V73" s="3">
+        <v>37.02</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="str">
         <v/>
       </c>
     </row>
@@ -4936,60 +6031,75 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D74" s="1">
-        <v>26325</v>
+        <v>16130.1</v>
       </c>
       <c r="E74" s="2">
-        <v>-2.32</v>
+        <v>0.19</v>
       </c>
       <c r="F74" s="2">
-        <v>-7.19</v>
+        <v>4.83</v>
       </c>
       <c r="G74" s="2">
-        <v>-7.19</v>
-      </c>
-      <c r="H74" t="str">
-        <v/>
+        <v>-0.05</v>
+      </c>
+      <c r="H74" s="2">
+        <v>10.18</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
-      <c r="J74" t="str">
-        <v/>
+      <c r="J74" s="1">
+        <v>15469.08</v>
       </c>
       <c r="K74" s="1">
-        <v>27601.95</v>
+        <v>15840.17</v>
       </c>
       <c r="L74" s="1">
-        <v>29242.38</v>
+        <v>16277.4</v>
       </c>
       <c r="M74" s="3">
-        <v>-581.26</v>
+        <v>-128.08</v>
       </c>
       <c r="N74" s="3">
-        <v>-450.01</v>
+        <v>-195.2</v>
       </c>
       <c r="O74" s="3">
-        <v>-256.82</v>
+        <v>153.79</v>
       </c>
       <c r="P74" s="3">
-        <v>158.35</v>
+        <v>301.56</v>
       </c>
       <c r="Q74" s="3">
-        <v>156.03</v>
+        <v>1028.11</v>
       </c>
       <c r="R74" s="3">
-        <v>172.48</v>
+        <v>1004.09</v>
       </c>
       <c r="S74" s="3">
-        <v>25.08</v>
-      </c>
-      <c r="T74" t="str">
+        <v>54.64</v>
+      </c>
+      <c r="T74" s="3">
+        <v>21.27</v>
+      </c>
+      <c r="U74" s="3">
+        <v>22.47</v>
+      </c>
+      <c r="V74" s="3">
+        <v>35.52</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="str">
         <v/>
       </c>
     </row>
@@ -4998,60 +6108,75 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C75" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D75" s="1">
-        <v>23827.1</v>
+        <v>841.08</v>
       </c>
       <c r="E75" s="2">
-        <v>-2.32</v>
+        <v>0.18</v>
       </c>
       <c r="F75" s="2">
-        <v>-7.42</v>
+        <v>0.46</v>
       </c>
       <c r="G75" s="2">
-        <v>-9.23</v>
+        <v>-1.65</v>
       </c>
       <c r="H75" s="2">
-        <v>5.68</v>
+        <v>-5.65</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>23624.75</v>
+        <v>872.52</v>
       </c>
       <c r="K75" s="1">
-        <v>25056.82</v>
+        <v>840.45</v>
       </c>
       <c r="L75" s="1">
-        <v>26074.8</v>
+        <v>857.48</v>
       </c>
       <c r="M75" s="3">
-        <v>-431.12</v>
+        <v>-5.69</v>
       </c>
       <c r="N75" s="3">
-        <v>-225.33</v>
+        <v>-6.12</v>
       </c>
       <c r="O75" s="3">
-        <v>565.85</v>
+        <v>-9.44</v>
       </c>
       <c r="P75" s="3">
-        <v>848.15</v>
+        <v>-6.41</v>
       </c>
       <c r="Q75" s="3">
-        <v>2245.38</v>
+        <v>-16.98</v>
       </c>
       <c r="R75" s="3">
-        <v>2341.77</v>
+        <v>-14.15</v>
       </c>
       <c r="S75" s="3">
-        <v>25.8</v>
-      </c>
-      <c r="T75" t="str">
+        <v>34.88</v>
+      </c>
+      <c r="T75" s="3">
+        <v>17.11</v>
+      </c>
+      <c r="U75" s="3">
+        <v>35.87</v>
+      </c>
+      <c r="V75" s="3">
+        <v>52.89</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="str">
         <v/>
       </c>
     </row>
@@ -5060,60 +6185,75 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D76" s="1">
-        <v>19071.8</v>
+        <v>7607.9</v>
       </c>
       <c r="E76" s="2">
-        <v>-2.33</v>
+        <v>0.16</v>
       </c>
       <c r="F76" s="2">
-        <v>-5.91</v>
+        <v>3.41</v>
       </c>
       <c r="G76" s="2">
-        <v>-6.58</v>
+        <v>-1.25</v>
       </c>
       <c r="H76" s="2">
-        <v>-5.67</v>
+        <v>-11.58</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>20259.6</v>
+        <v>7659.8</v>
       </c>
       <c r="K76" s="1">
-        <v>19886.07</v>
+        <v>7534.3</v>
       </c>
       <c r="L76" s="1">
-        <v>20941.94</v>
+        <v>7714.26</v>
       </c>
       <c r="M76" s="3">
-        <v>-379.38</v>
+        <v>-47.64</v>
       </c>
       <c r="N76" s="3">
-        <v>-293.14</v>
+        <v>-73.76</v>
       </c>
       <c r="O76" s="3">
-        <v>-30.7</v>
+        <v>-67.76</v>
       </c>
       <c r="P76" s="3">
-        <v>239.72</v>
+        <v>-28.63</v>
       </c>
       <c r="Q76" s="3">
-        <v>1522.67</v>
+        <v>-285.63</v>
       </c>
       <c r="R76" s="3">
-        <v>1812.28</v>
+        <v>-244.31</v>
       </c>
       <c r="S76" s="3">
-        <v>22.43</v>
-      </c>
-      <c r="T76" t="str">
+        <v>51.18</v>
+      </c>
+      <c r="T76" s="3">
+        <v>18.85</v>
+      </c>
+      <c r="U76" s="3">
+        <v>23.07</v>
+      </c>
+      <c r="V76" s="3">
+        <v>23.04</v>
+      </c>
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="str">
         <v/>
       </c>
     </row>
@@ -5122,60 +6262,75 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>CNXREALTY</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C77" t="str">
-        <v>CNXREALTY</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D77" s="1">
-        <v>784.35</v>
+        <v>26577.1</v>
       </c>
       <c r="E77" s="2">
-        <v>-2.38</v>
+        <v>0.13</v>
       </c>
       <c r="F77" s="2">
-        <v>-5.04</v>
+        <v>4.93</v>
       </c>
       <c r="G77" s="2">
-        <v>-7.43</v>
+        <v>0.53</v>
       </c>
       <c r="H77" s="2">
-        <v>-10.66</v>
+        <v>16.96</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>821.76</v>
+        <v>24444.58</v>
       </c>
       <c r="K77" s="1">
-        <v>811.59</v>
+        <v>26080.95</v>
       </c>
       <c r="L77" s="1">
-        <v>861.67</v>
+        <v>26417.67</v>
       </c>
       <c r="M77" s="3">
-        <v>-16.39</v>
+        <v>-84.11</v>
       </c>
       <c r="N77" s="3">
-        <v>-14.88</v>
+        <v>-178.59</v>
       </c>
       <c r="O77" s="3">
-        <v>-1.64</v>
+        <v>579.21</v>
       </c>
       <c r="P77" s="3">
-        <v>10.22</v>
+        <v>749.94</v>
       </c>
       <c r="Q77" s="3">
-        <v>0.01</v>
+        <v>1852.9</v>
       </c>
       <c r="R77" s="3">
-        <v>9.58</v>
+        <v>1623.02</v>
       </c>
       <c r="S77" s="3">
-        <v>32.65</v>
-      </c>
-      <c r="T77" t="str">
+        <v>57.8</v>
+      </c>
+      <c r="T77" s="3">
+        <v>23.11</v>
+      </c>
+      <c r="U77" s="3">
+        <v>19.36</v>
+      </c>
+      <c r="V77" s="3">
+        <v>25.64</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="str">
         <v/>
       </c>
     </row>
@@ -5184,60 +6339,75 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C78" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D78" s="1">
-        <v>27301.75</v>
+        <v>1257.69</v>
       </c>
       <c r="E78" s="2">
-        <v>-2.47</v>
+        <v>0.12</v>
       </c>
       <c r="F78" s="2">
-        <v>-6.15</v>
+        <v>0.2</v>
       </c>
       <c r="G78" s="2">
-        <v>-7.51</v>
+        <v>-1.22</v>
       </c>
       <c r="H78" s="2">
-        <v>-12.35</v>
+        <v>-0.31</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>30366.63</v>
+        <v>1268.25</v>
       </c>
       <c r="K78" s="1">
-        <v>28588.86</v>
+        <v>1259.97</v>
       </c>
       <c r="L78" s="1">
-        <v>30194.41</v>
+        <v>1276.45</v>
       </c>
       <c r="M78" s="3">
-        <v>-592.61</v>
+        <v>-6.11</v>
       </c>
       <c r="N78" s="3">
-        <v>-435.76</v>
+        <v>-5.46</v>
       </c>
       <c r="O78" s="3">
-        <v>-430.86</v>
+        <v>-0.71</v>
       </c>
       <c r="P78" s="3">
-        <v>-104.64</v>
+        <v>3.72</v>
       </c>
       <c r="Q78" s="3">
-        <v>1361.55</v>
+        <v>20.92</v>
       </c>
       <c r="R78" s="3">
-        <v>1982.03</v>
+        <v>21.88</v>
       </c>
       <c r="S78" s="3">
-        <v>23.16</v>
-      </c>
-      <c r="T78" t="str">
+        <v>25.29</v>
+      </c>
+      <c r="T78" s="3">
+        <v>25.22</v>
+      </c>
+      <c r="U78" s="3">
+        <v>72.61</v>
+      </c>
+      <c r="V78" s="3">
+        <v>46.61</v>
+      </c>
+      <c r="W78" s="3">
+        <v>0</v>
+      </c>
+      <c r="X78" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="str">
         <v/>
       </c>
     </row>
@@ -5246,60 +6416,75 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C79" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D79" s="1">
-        <v>4930.05</v>
+        <v>50944</v>
       </c>
       <c r="E79" s="2">
-        <v>-2.5</v>
+        <v>0.1</v>
       </c>
       <c r="F79" s="2">
-        <v>-5.95</v>
+        <v>6.91</v>
       </c>
       <c r="G79" s="2">
-        <v>-3.14</v>
+        <v>-0.07</v>
       </c>
       <c r="H79" s="2">
-        <v>5.88</v>
+        <v>16.14</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>5106.68</v>
+        <v>47476.83</v>
       </c>
       <c r="K79" s="1">
-        <v>5130.1</v>
+        <v>49758.75</v>
       </c>
       <c r="L79" s="1">
-        <v>5294.25</v>
+        <v>51281.38</v>
       </c>
       <c r="M79" s="3">
-        <v>-58.04</v>
+        <v>-460.47</v>
       </c>
       <c r="N79" s="3">
-        <v>-37.62</v>
+        <v>-682.8</v>
       </c>
       <c r="O79" s="3">
-        <v>17.34</v>
+        <v>863.87</v>
       </c>
       <c r="P79" s="3">
-        <v>84.49</v>
+        <v>1413.54</v>
       </c>
       <c r="Q79" s="3">
-        <v>353.78</v>
+        <v>2363.64</v>
       </c>
       <c r="R79" s="3">
-        <v>323.22</v>
+        <v>1510.3</v>
       </c>
       <c r="S79" s="3">
-        <v>33.17</v>
-      </c>
-      <c r="T79" t="str">
+        <v>55.34</v>
+      </c>
+      <c r="T79" s="3">
+        <v>26.75</v>
+      </c>
+      <c r="U79" s="3">
+        <v>26.92</v>
+      </c>
+      <c r="V79" s="3">
+        <v>34.29</v>
+      </c>
+      <c r="W79" s="3">
+        <v>0</v>
+      </c>
+      <c r="X79" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="str">
         <v/>
       </c>
     </row>
@@ -5308,60 +6493,75 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D80" s="1">
-        <v>23666.85</v>
+        <v>28490.1</v>
       </c>
       <c r="E80" s="2">
-        <v>-2.56</v>
+        <v>0.1</v>
       </c>
       <c r="F80" s="2">
-        <v>-6.1</v>
+        <v>2.61</v>
       </c>
       <c r="G80" s="2">
+        <v>-6.08</v>
+      </c>
+      <c r="H80" s="2">
         <v>-6.8</v>
       </c>
-      <c r="H80" s="2">
-        <v>-5.28</v>
-      </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>25466.45</v>
+        <v>31334.83</v>
       </c>
       <c r="K80" s="1">
-        <v>24754.22</v>
+        <v>28655.07</v>
       </c>
       <c r="L80" s="1">
-        <v>26109.43</v>
+        <v>30989.11</v>
       </c>
       <c r="M80" s="3">
-        <v>-484.27</v>
+        <v>-799.81</v>
       </c>
       <c r="N80" s="3">
-        <v>-363.85</v>
+        <v>-779.25</v>
       </c>
       <c r="O80" s="3">
-        <v>-111.79</v>
+        <v>-660.58</v>
       </c>
       <c r="P80" s="3">
-        <v>204.73</v>
+        <v>-83.04</v>
       </c>
       <c r="Q80" s="3">
-        <v>1.84</v>
+        <v>1979.04</v>
       </c>
       <c r="R80" s="3">
-        <v>-68.08</v>
+        <v>2395.71</v>
       </c>
       <c r="S80" s="3">
-        <v>24.96</v>
-      </c>
-      <c r="T80" t="str">
+        <v>33.29</v>
+      </c>
+      <c r="T80" s="3">
+        <v>14.01</v>
+      </c>
+      <c r="U80" s="3">
+        <v>41</v>
+      </c>
+      <c r="V80" s="3">
+        <v>58.88</v>
+      </c>
+      <c r="W80" s="3">
+        <v>0</v>
+      </c>
+      <c r="X80" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="str">
         <v/>
       </c>
     </row>
@@ -5370,60 +6570,75 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C81" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D81" s="1">
-        <v>15043.45</v>
+        <v>3282</v>
       </c>
       <c r="E81" s="2">
-        <v>-2.56</v>
+        <v>0.07</v>
       </c>
       <c r="F81" s="2">
-        <v>-6.39</v>
+        <v>0.16</v>
       </c>
       <c r="G81" s="2">
-        <v>-7.65</v>
+        <v>-0.8</v>
       </c>
       <c r="H81" s="2">
-        <v>-6</v>
+        <v>1.84</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>16126.11</v>
+        <v>3281.57</v>
       </c>
       <c r="K81" s="1">
-        <v>15773.12</v>
+        <v>3281.66</v>
       </c>
       <c r="L81" s="1">
-        <v>16777.1</v>
+        <v>3314.18</v>
       </c>
       <c r="M81" s="3">
-        <v>-353.58</v>
+        <v>-10.34</v>
       </c>
       <c r="N81" s="3">
-        <v>-273.59</v>
+        <v>-11.17</v>
       </c>
       <c r="O81" s="3">
-        <v>-22.09</v>
+        <v>5.24</v>
       </c>
       <c r="P81" s="3">
-        <v>221.39</v>
+        <v>15.44</v>
       </c>
       <c r="Q81" s="3">
-        <v>1500.29</v>
+        <v>139.89</v>
       </c>
       <c r="R81" s="3">
-        <v>1738.39</v>
+        <v>155.49</v>
       </c>
       <c r="S81" s="3">
-        <v>24.61</v>
-      </c>
-      <c r="T81" t="str">
+        <v>34.28</v>
+      </c>
+      <c r="T81" s="3">
+        <v>13.24</v>
+      </c>
+      <c r="U81" s="3">
+        <v>39.21</v>
+      </c>
+      <c r="V81" s="3">
+        <v>50.78</v>
+      </c>
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="str">
         <v/>
       </c>
     </row>
@@ -5432,60 +6647,75 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C82" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D82" s="1">
-        <v>49069.75</v>
+        <v>1442.33</v>
       </c>
       <c r="E82" s="2">
-        <v>-2.59</v>
+        <v>0.06</v>
       </c>
       <c r="F82" s="2">
-        <v>-6.2</v>
+        <v>0.13</v>
       </c>
       <c r="G82" s="2">
-        <v>-7.23</v>
+        <v>-0.8</v>
       </c>
       <c r="H82" s="2">
-        <v>-6.9</v>
+        <v>1.24</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>52524.13</v>
+        <v>1441.19</v>
       </c>
       <c r="K82" s="1">
-        <v>51482.54</v>
+        <v>1444.16</v>
       </c>
       <c r="L82" s="1">
-        <v>53982.39</v>
+        <v>1455.63</v>
       </c>
       <c r="M82" s="3">
-        <v>-947.88</v>
+        <v>-4.33</v>
       </c>
       <c r="N82" s="3">
-        <v>-620.66</v>
+        <v>-3.77</v>
       </c>
       <c r="O82" s="3">
-        <v>-126.79</v>
+        <v>2.66</v>
       </c>
       <c r="P82" s="3">
-        <v>413.04</v>
+        <v>6.33</v>
       </c>
       <c r="Q82" s="3">
-        <v>-909.94</v>
+        <v>28.88</v>
       </c>
       <c r="R82" s="3">
-        <v>-1153.68</v>
+        <v>28.5</v>
       </c>
       <c r="S82" s="3">
-        <v>24.22</v>
-      </c>
-      <c r="T82" t="str">
+        <v>27.44</v>
+      </c>
+      <c r="T82" s="3">
+        <v>24.99</v>
+      </c>
+      <c r="U82" s="3">
+        <v>67.65</v>
+      </c>
+      <c r="V82" s="3">
+        <v>40.17</v>
+      </c>
+      <c r="W82" s="3">
+        <v>0</v>
+      </c>
+      <c r="X82" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="str">
         <v/>
       </c>
     </row>
@@ -5494,60 +6724,75 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="C83" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="D83" s="1">
-        <v>8561.2</v>
+        <v>1301.68</v>
       </c>
       <c r="E83" s="2">
-        <v>-2.6</v>
+        <v>0.06</v>
       </c>
       <c r="F83" s="2">
-        <v>-7.05</v>
+        <v>0.11</v>
       </c>
       <c r="G83" s="2">
-        <v>-7.71</v>
+        <v>-1.05</v>
       </c>
       <c r="H83" s="2">
-        <v>10.5</v>
+        <v>0.27</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>8842.66</v>
+        <v>1308.08</v>
       </c>
       <c r="K83" s="1">
-        <v>8980.74</v>
+        <v>1304.31</v>
       </c>
       <c r="L83" s="1">
-        <v>9456.74</v>
+        <v>1318.44</v>
       </c>
       <c r="M83" s="3">
-        <v>-161.86</v>
+        <v>-5.26</v>
       </c>
       <c r="N83" s="3">
-        <v>-118.83</v>
+        <v>-4.64</v>
       </c>
       <c r="O83" s="3">
-        <v>81.2</v>
+        <v>0.43</v>
       </c>
       <c r="P83" s="3">
-        <v>230.92</v>
+        <v>4.57</v>
       </c>
       <c r="Q83" s="3">
-        <v>583.08</v>
+        <v>23.61</v>
       </c>
       <c r="R83" s="3">
-        <v>518.72</v>
+        <v>24.14</v>
       </c>
       <c r="S83" s="3">
-        <v>29.32</v>
-      </c>
-      <c r="T83" t="str">
+        <v>23.68</v>
+      </c>
+      <c r="T83" s="3">
+        <v>23.78</v>
+      </c>
+      <c r="U83" s="3">
+        <v>73.28</v>
+      </c>
+      <c r="V83" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="str">
         <v/>
       </c>
     </row>
@@ -5556,60 +6801,75 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C84" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D84" s="1">
-        <v>33922</v>
+        <v>1596.66</v>
       </c>
       <c r="E84" s="2">
-        <v>-2.63</v>
+        <v>0.02</v>
       </c>
       <c r="F84" s="2">
-        <v>-6.42</v>
+        <v>0.03</v>
       </c>
       <c r="G84" s="2">
-        <v>-7.39</v>
+        <v>-0.64</v>
       </c>
       <c r="H84" s="2">
-        <v>-7.71</v>
+        <v>1.9</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>37099.43</v>
+        <v>1587.43</v>
       </c>
       <c r="K84" s="1">
-        <v>35538.35</v>
+        <v>1598.93</v>
       </c>
       <c r="L84" s="1">
-        <v>38271.87</v>
+        <v>1607.09</v>
       </c>
       <c r="M84" s="3">
-        <v>-914.61</v>
+        <v>-3.28</v>
       </c>
       <c r="N84" s="3">
-        <v>-785.28</v>
+        <v>-2.62</v>
       </c>
       <c r="O84" s="3">
-        <v>-296.05</v>
+        <v>5.43</v>
       </c>
       <c r="P84" s="3">
-        <v>295.51</v>
+        <v>8.52</v>
       </c>
       <c r="Q84" s="3">
-        <v>532.92</v>
+        <v>34.52</v>
       </c>
       <c r="R84" s="3">
-        <v>918.75</v>
+        <v>33.05</v>
       </c>
       <c r="S84" s="3">
-        <v>22.79</v>
-      </c>
-      <c r="T84" t="str">
+        <v>27.04</v>
+      </c>
+      <c r="T84" s="3">
+        <v>18.2</v>
+      </c>
+      <c r="U84" s="3">
+        <v>66.59</v>
+      </c>
+      <c r="V84" s="3">
+        <v>35.44</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="str">
         <v/>
       </c>
     </row>
@@ -5618,60 +6878,75 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C85" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D85" s="1">
-        <v>44470.2</v>
+        <v>15591.25</v>
       </c>
       <c r="E85" s="2">
-        <v>-2.65</v>
+        <v>-0.03</v>
       </c>
       <c r="F85" s="2">
-        <v>-6.73</v>
+        <v>3.38</v>
       </c>
       <c r="G85" s="2">
-        <v>-7.08</v>
+        <v>-2.66</v>
       </c>
       <c r="H85" s="2">
-        <v>1.1</v>
+        <v>-2.4</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>44929.21</v>
+        <v>15991.22</v>
       </c>
       <c r="K85" s="1">
-        <v>46643.68</v>
+        <v>15526.91</v>
       </c>
       <c r="L85" s="1">
-        <v>48280.02</v>
+        <v>16258.73</v>
       </c>
       <c r="M85" s="3">
-        <v>-654.52</v>
+        <v>-221.94</v>
       </c>
       <c r="N85" s="3">
-        <v>-358.76</v>
+        <v>-251.87</v>
       </c>
       <c r="O85" s="3">
-        <v>655.34</v>
+        <v>-101.69</v>
       </c>
       <c r="P85" s="3">
-        <v>1101.74</v>
+        <v>84.83</v>
       </c>
       <c r="Q85" s="3">
-        <v>-453.49</v>
+        <v>373.91</v>
       </c>
       <c r="R85" s="3">
-        <v>-1042.54</v>
+        <v>331.67</v>
       </c>
       <c r="S85" s="3">
-        <v>25.55</v>
-      </c>
-      <c r="T85" t="str">
+        <v>44.17</v>
+      </c>
+      <c r="T85" s="3">
+        <v>17.13</v>
+      </c>
+      <c r="U85" s="3">
+        <v>32.57</v>
+      </c>
+      <c r="V85" s="3">
+        <v>45.96</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="str">
         <v/>
       </c>
     </row>
@@ -5680,60 +6955,75 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D86" s="1">
-        <v>11478.2</v>
+        <v>14927.4</v>
       </c>
       <c r="E86" s="2">
-        <v>-2.71</v>
+        <v>-0.03</v>
       </c>
       <c r="F86" s="2">
-        <v>-5.4</v>
+        <v>2.83</v>
       </c>
       <c r="G86" s="2">
-        <v>-10.05</v>
+        <v>-3.41</v>
       </c>
       <c r="H86" s="2">
-        <v>2.78</v>
+        <v>-3.15</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
       <c r="J86" s="1">
-        <v>12483.72</v>
+        <v>15610.26</v>
       </c>
       <c r="K86" s="1">
-        <v>11951.39</v>
+        <v>14904.59</v>
       </c>
       <c r="L86" s="1">
-        <v>12804.74</v>
+        <v>15708.24</v>
       </c>
       <c r="M86" s="3">
-        <v>-315.57</v>
+        <v>-248.13</v>
       </c>
       <c r="N86" s="3">
-        <v>-267.05</v>
+        <v>-272.6</v>
       </c>
       <c r="O86" s="3">
-        <v>-15.01</v>
+        <v>-157.83</v>
       </c>
       <c r="P86" s="3">
-        <v>202.89</v>
+        <v>45.57</v>
       </c>
       <c r="Q86" s="3">
-        <v>1107.38</v>
+        <v>1253.81</v>
       </c>
       <c r="R86" s="3">
-        <v>1124.17</v>
+        <v>1445.24</v>
       </c>
       <c r="S86" s="3">
-        <v>27.88</v>
-      </c>
-      <c r="T86" t="str">
+        <v>41.4</v>
+      </c>
+      <c r="T86" s="3">
+        <v>15.57</v>
+      </c>
+      <c r="U86" s="3">
+        <v>34.25</v>
+      </c>
+      <c r="V86" s="3">
+        <v>49.36</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="str">
         <v/>
       </c>
     </row>
@@ -5742,60 +7032,75 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D87" s="1">
-        <v>16385.15</v>
+        <v>25604.85</v>
       </c>
       <c r="E87" s="2">
-        <v>-2.79</v>
+        <v>-0.4</v>
       </c>
       <c r="F87" s="2">
-        <v>-7.1</v>
+        <v>2.99</v>
       </c>
       <c r="G87" s="2">
-        <v>-7.94</v>
+        <v>-2.62</v>
       </c>
       <c r="H87" s="2">
-        <v>-1.8</v>
+        <v>-9.17</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>16949.08</v>
+        <v>26844.42</v>
       </c>
       <c r="K87" s="1">
-        <v>17248.25</v>
+        <v>25380.23</v>
       </c>
       <c r="L87" s="1">
-        <v>18042.86</v>
+        <v>26858.26</v>
       </c>
       <c r="M87" s="3">
-        <v>-312.85</v>
+        <v>-375.95</v>
       </c>
       <c r="N87" s="3">
-        <v>-196.4</v>
+        <v>-508.62</v>
       </c>
       <c r="O87" s="3">
-        <v>154.28</v>
+        <v>-354.37</v>
       </c>
       <c r="P87" s="3">
-        <v>372.72</v>
+        <v>2.01</v>
       </c>
       <c r="Q87" s="3">
-        <v>1255.47</v>
+        <v>1508.44</v>
       </c>
       <c r="R87" s="3">
-        <v>1418.33</v>
+        <v>1817.19</v>
       </c>
       <c r="S87" s="3">
-        <v>21.82</v>
-      </c>
-      <c r="T87" t="str">
+        <v>46.98</v>
+      </c>
+      <c r="T87" s="3">
+        <v>18.76</v>
+      </c>
+      <c r="U87" s="3">
+        <v>27.9</v>
+      </c>
+      <c r="V87" s="3">
+        <v>49.2</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="str">
         <v/>
       </c>
     </row>
@@ -5804,60 +7109,75 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D88" s="1">
-        <v>49910.3</v>
+        <v>233.8</v>
       </c>
       <c r="E88" s="2">
-        <v>-2.81</v>
+        <v>-0.83</v>
       </c>
       <c r="F88" s="2">
-        <v>-7.31</v>
+        <v>-1.18</v>
       </c>
       <c r="G88" s="2">
-        <v>-7.71</v>
+        <v>-0.91</v>
       </c>
       <c r="H88" s="2">
-        <v>-0.79</v>
+        <v>16.9</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>52196.32</v>
+        <v>219.97</v>
       </c>
       <c r="K88" s="1">
-        <v>52935.13</v>
+        <v>234.91</v>
       </c>
       <c r="L88" s="1">
-        <v>55465.02</v>
+        <v>229.29</v>
       </c>
       <c r="M88" s="3">
-        <v>-970.06</v>
+        <v>1.37</v>
       </c>
       <c r="N88" s="3">
-        <v>-524.45</v>
+        <v>1.9</v>
       </c>
       <c r="O88" s="3">
-        <v>487.96</v>
+        <v>4.77</v>
       </c>
       <c r="P88" s="3">
-        <v>1112.5</v>
+        <v>3.73</v>
       </c>
       <c r="Q88" s="3">
-        <v>3454.54</v>
+        <v>-0.8</v>
       </c>
       <c r="R88" s="3">
-        <v>3839.75</v>
+        <v>-4.8</v>
       </c>
       <c r="S88" s="3">
-        <v>24.65</v>
-      </c>
-      <c r="T88" t="str">
+        <v>51.08</v>
+      </c>
+      <c r="T88" s="3">
+        <v>25.21</v>
+      </c>
+      <c r="U88" s="3">
+        <v>14.2</v>
+      </c>
+      <c r="V88" s="3">
+        <v>41</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="str">
         <v/>
       </c>
     </row>
@@ -5866,60 +7186,75 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="C89" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D89" s="1">
-        <v>17739.45</v>
+        <v>189.6</v>
       </c>
       <c r="E89" s="2">
-        <v>-2.94</v>
+        <v>-0.84</v>
       </c>
       <c r="F89" s="2">
-        <v>-7.27</v>
+        <v>-1.2</v>
       </c>
       <c r="G89" s="2">
-        <v>-7.83</v>
+        <v>-0.94</v>
       </c>
       <c r="H89" s="2">
-        <v>0.14</v>
+        <v>15.86</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>18188.33</v>
+        <v>179.23</v>
       </c>
       <c r="K89" s="1">
-        <v>18723.09</v>
+        <v>190.51</v>
       </c>
       <c r="L89" s="1">
-        <v>19579.65</v>
+        <v>186</v>
       </c>
       <c r="M89" s="3">
-        <v>-338.91</v>
+        <v>1.1</v>
       </c>
       <c r="N89" s="3">
-        <v>-201.47</v>
+        <v>1.52</v>
       </c>
       <c r="O89" s="3">
-        <v>243.89</v>
+        <v>3.57</v>
       </c>
       <c r="P89" s="3">
-        <v>477.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q89" s="3">
-        <v>797.34</v>
+        <v>-2.62</v>
       </c>
       <c r="R89" s="3">
-        <v>843.64</v>
+        <v>-6.05</v>
       </c>
       <c r="S89" s="3">
-        <v>22.66</v>
-      </c>
-      <c r="T89" t="str">
+        <v>50.97</v>
+      </c>
+      <c r="T89" s="3">
+        <v>25.16</v>
+      </c>
+      <c r="U89" s="3">
+        <v>14.17</v>
+      </c>
+      <c r="V89" s="3">
+        <v>40.56</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="str">
         <v/>
       </c>
     </row>
@@ -5928,66 +7263,81 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>India VIX</v>
       </c>
       <c r="C90" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>INDIAVIX</v>
       </c>
       <c r="D90" s="1">
-        <v>8924.75</v>
+        <v>15.31</v>
       </c>
       <c r="E90" s="2">
-        <v>-3.15</v>
+        <v>-5.78</v>
       </c>
       <c r="F90" s="2">
-        <v>-6.87</v>
+        <v>-9.19</v>
       </c>
       <c r="G90" s="2">
-        <v>-7.35</v>
+        <v>13.49</v>
       </c>
       <c r="H90" s="2">
-        <v>3.7</v>
+        <v>61.5</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
       <c r="J90" s="1">
-        <v>8982.85</v>
+        <v>15.04</v>
       </c>
       <c r="K90" s="1">
-        <v>9395.06</v>
+        <v>15.69</v>
       </c>
       <c r="L90" s="1">
-        <v>9789.56</v>
+        <v>12.98</v>
       </c>
       <c r="M90" s="3">
-        <v>-153.48</v>
+        <v>0.91</v>
       </c>
       <c r="N90" s="3">
-        <v>-92.78</v>
+        <v>0.88</v>
       </c>
       <c r="O90" s="3">
-        <v>171.72</v>
+        <v>-0.05</v>
       </c>
       <c r="P90" s="3">
-        <v>288.86</v>
+        <v>-0.59</v>
       </c>
       <c r="Q90" s="3">
-        <v>702.31</v>
+        <v>-0.05</v>
       </c>
       <c r="R90" s="3">
-        <v>712.09</v>
+        <v>0.03</v>
       </c>
       <c r="S90" s="3">
-        <v>24.61</v>
-      </c>
-      <c r="T90" t="str">
+        <v>54.43</v>
+      </c>
+      <c r="T90" s="3">
+        <v>18.42</v>
+      </c>
+      <c r="U90" s="3">
+        <v>16.97</v>
+      </c>
+      <c r="V90" s="3">
+        <v>16.7</v>
+      </c>
+      <c r="W90" s="3">
+        <v>0</v>
+      </c>
+      <c r="X90" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y90"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Index.xlsx
+++ b/Index.xlsx
@@ -487,67 +487,67 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>NIFTYFMCG</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C2" t="str">
-        <v>NIFTYFMCG</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D2" s="1">
-        <v>43715.85</v>
+        <v>819.8</v>
       </c>
       <c r="E2" s="2">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="F2" s="2">
-        <v>2.43</v>
+        <v>4.52</v>
       </c>
       <c r="G2" s="2">
-        <v>-1.78</v>
+        <v>-3.25</v>
       </c>
       <c r="H2" s="2">
-        <v>-21.2</v>
+        <v>-6.62</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>48700.42</v>
+        <v>819.74</v>
       </c>
       <c r="K2" s="1">
-        <v>43523.55</v>
+        <v>808.06</v>
       </c>
       <c r="L2" s="1">
-        <v>45330.92</v>
+        <v>854.06</v>
       </c>
       <c r="M2" s="3">
-        <v>-672.38</v>
+        <v>-13.91</v>
       </c>
       <c r="N2" s="3">
-        <v>-640.86</v>
+        <v>-15.29</v>
       </c>
       <c r="O2" s="3">
-        <v>-1724.49</v>
+        <v>-3.23</v>
       </c>
       <c r="P2" s="3">
-        <v>-1434.09</v>
+        <v>7.53</v>
       </c>
       <c r="Q2" s="3">
-        <v>-2137.25</v>
+        <v>2.84</v>
       </c>
       <c r="R2" s="3">
-        <v>-960.27</v>
+        <v>10.15</v>
       </c>
       <c r="S2" s="3">
-        <v>44.77</v>
+        <v>48.35</v>
       </c>
       <c r="T2" s="3">
-        <v>18.66</v>
+        <v>21.33</v>
       </c>
       <c r="U2" s="3">
-        <v>28.74</v>
+        <v>27.14</v>
       </c>
       <c r="V2" s="3">
-        <v>38.37</v>
+        <v>27.41</v>
       </c>
       <c r="W2" s="3">
         <v>0</v>
@@ -564,67 +564,67 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D3" s="1">
-        <v>6021.45</v>
+        <v>43882.95</v>
       </c>
       <c r="E3" s="2">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="F3" s="2">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="G3" s="2">
-        <v>-3.33</v>
+        <v>-1.41</v>
       </c>
       <c r="H3" s="2">
-        <v>-5.4</v>
+        <v>-20.9</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>6730.92</v>
+        <v>48701.26</v>
       </c>
       <c r="K3" s="1">
-        <v>5983.83</v>
+        <v>43553.93</v>
       </c>
       <c r="L3" s="1">
-        <v>6250.83</v>
+        <v>45334.26</v>
       </c>
       <c r="M3" s="3">
-        <v>-92.02</v>
+        <v>-659.05</v>
       </c>
       <c r="N3" s="3">
-        <v>-98.05</v>
+        <v>-638.2</v>
       </c>
       <c r="O3" s="3">
-        <v>-212.84</v>
+        <v>-1711.16</v>
       </c>
       <c r="P3" s="3">
-        <v>-161.23</v>
+        <v>-1431.42</v>
       </c>
       <c r="Q3" s="3">
-        <v>234.51</v>
+        <v>-2123.92</v>
       </c>
       <c r="R3" s="3">
-        <v>404.05</v>
+        <v>-957.6</v>
       </c>
       <c r="S3" s="3">
-        <v>44.06</v>
+        <v>46.15</v>
       </c>
       <c r="T3" s="3">
-        <v>16.43</v>
+        <v>20.78</v>
       </c>
       <c r="U3" s="3">
-        <v>29.21</v>
+        <v>27.99</v>
       </c>
       <c r="V3" s="3">
-        <v>44.27</v>
+        <v>37.91</v>
       </c>
       <c r="W3" s="3">
         <v>0</v>
@@ -641,67 +641,67 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C4" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D4" s="1">
-        <v>16208.1</v>
+        <v>8312.5</v>
       </c>
       <c r="E4" s="2">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="F4" s="2">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2">
-        <v>1.87</v>
+        <v>3.7</v>
       </c>
       <c r="H4" s="2">
-        <v>-26.32</v>
+        <v>-2.59</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>18246.8</v>
+        <v>8561.27</v>
       </c>
       <c r="K4" s="1">
-        <v>16050.08</v>
+        <v>8169.63</v>
       </c>
       <c r="L4" s="1">
-        <v>16877.57</v>
+        <v>8297.36</v>
       </c>
       <c r="M4" s="3">
-        <v>-201.92</v>
+        <v>-17.15</v>
       </c>
       <c r="N4" s="3">
-        <v>-279.85</v>
+        <v>-42.72</v>
       </c>
       <c r="O4" s="3">
-        <v>-692.98</v>
+        <v>-79.45</v>
       </c>
       <c r="P4" s="3">
-        <v>-550.72</v>
+        <v>-42.01</v>
       </c>
       <c r="Q4" s="3">
-        <v>279.06</v>
+        <v>580.24</v>
       </c>
       <c r="R4" s="3">
-        <v>929.6</v>
+        <v>686.37</v>
       </c>
       <c r="S4" s="3">
-        <v>48.76</v>
+        <v>56.19</v>
       </c>
       <c r="T4" s="3">
-        <v>14.8</v>
+        <v>26.53</v>
       </c>
       <c r="U4" s="3">
-        <v>25.21</v>
+        <v>21.9</v>
       </c>
       <c r="V4" s="3">
-        <v>36.83</v>
+        <v>15.78</v>
       </c>
       <c r="W4" s="3">
         <v>0</v>
@@ -718,67 +718,67 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C5" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D5" s="1">
-        <v>10622.1</v>
+        <v>16273.65</v>
       </c>
       <c r="E5" s="2">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="F5" s="2">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="G5" s="2">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="H5" s="2">
-        <v>-27.74</v>
+        <v>-26.02</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>12086.17</v>
+        <v>18247.13</v>
       </c>
       <c r="K5" s="1">
-        <v>10521.38</v>
+        <v>16062</v>
       </c>
       <c r="L5" s="1">
-        <v>11070.47</v>
+        <v>16878.88</v>
       </c>
       <c r="M5" s="3">
-        <v>-135.32</v>
+        <v>-196.69</v>
       </c>
       <c r="N5" s="3">
-        <v>-186.26</v>
+        <v>-278.81</v>
       </c>
       <c r="O5" s="3">
-        <v>-498.43</v>
+        <v>-687.75</v>
       </c>
       <c r="P5" s="3">
-        <v>-410.27</v>
+        <v>-549.67</v>
       </c>
       <c r="Q5" s="3">
-        <v>-5.29</v>
+        <v>284.29</v>
       </c>
       <c r="R5" s="3">
-        <v>426.36</v>
+        <v>930.65</v>
       </c>
       <c r="S5" s="3">
-        <v>48.59</v>
+        <v>49.84</v>
       </c>
       <c r="T5" s="3">
-        <v>14.67</v>
+        <v>15.89</v>
       </c>
       <c r="U5" s="3">
-        <v>25.26</v>
+        <v>24.89</v>
       </c>
       <c r="V5" s="3">
-        <v>37.21</v>
+        <v>36.54</v>
       </c>
       <c r="W5" s="3">
         <v>0</v>
@@ -795,67 +795,67 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C6" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D6" s="1">
-        <v>7390.85</v>
+        <v>10665.05</v>
       </c>
       <c r="E6" s="2">
-        <v>1.41</v>
+        <v>2.08</v>
       </c>
       <c r="F6" s="2">
-        <v>1.48</v>
+        <v>2.89</v>
       </c>
       <c r="G6" s="2">
-        <v>4.45</v>
+        <v>2.2</v>
       </c>
       <c r="H6" s="2">
-        <v>-2.27</v>
+        <v>-27.45</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>7328.08</v>
+        <v>12086.39</v>
       </c>
       <c r="K6" s="1">
-        <v>7323.36</v>
+        <v>10529.19</v>
       </c>
       <c r="L6" s="1">
-        <v>7367.04</v>
+        <v>11071.33</v>
       </c>
       <c r="M6" s="3">
-        <v>11.22</v>
+        <v>-131.9</v>
       </c>
       <c r="N6" s="3">
-        <v>-9.24</v>
+        <v>-185.57</v>
       </c>
       <c r="O6" s="3">
-        <v>-0.52</v>
+        <v>-495</v>
       </c>
       <c r="P6" s="3">
-        <v>24.4</v>
+        <v>-409.59</v>
       </c>
       <c r="Q6" s="3">
-        <v>475.26</v>
+        <v>-1.86</v>
       </c>
       <c r="R6" s="3">
-        <v>553.26</v>
+        <v>427.05</v>
       </c>
       <c r="S6" s="3">
-        <v>55.3</v>
+        <v>49.66</v>
       </c>
       <c r="T6" s="3">
-        <v>21.78</v>
+        <v>15.76</v>
       </c>
       <c r="U6" s="3">
-        <v>23.84</v>
+        <v>24.94</v>
       </c>
       <c r="V6" s="3">
-        <v>23.73</v>
+        <v>36.93</v>
       </c>
       <c r="W6" s="3">
         <v>0</v>
@@ -872,67 +872,67 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C7" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D7" s="1">
-        <v>30435.6</v>
+        <v>6032.3</v>
       </c>
       <c r="E7" s="2">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="F7" s="2">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="G7" s="2">
-        <v>4.9</v>
+        <v>-3.15</v>
       </c>
       <c r="H7" s="2">
-        <v>-9.57</v>
+        <v>-5.23</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>30868.65</v>
+        <v>6730.98</v>
       </c>
       <c r="K7" s="1">
-        <v>30047.42</v>
+        <v>5985.81</v>
       </c>
       <c r="L7" s="1">
-        <v>30012.91</v>
+        <v>6251.04</v>
       </c>
       <c r="M7" s="3">
-        <v>117.91</v>
+        <v>-91.15</v>
       </c>
       <c r="N7" s="3">
-        <v>1.08</v>
+        <v>-97.87</v>
       </c>
       <c r="O7" s="3">
-        <v>-305.33</v>
+        <v>-211.97</v>
       </c>
       <c r="P7" s="3">
-        <v>-315</v>
+        <v>-161.06</v>
       </c>
       <c r="Q7" s="3">
-        <v>522.07</v>
+        <v>235.38</v>
       </c>
       <c r="R7" s="3">
-        <v>998.91</v>
+        <v>404.23</v>
       </c>
       <c r="S7" s="3">
-        <v>59.23</v>
+        <v>44.97</v>
       </c>
       <c r="T7" s="3">
-        <v>21.82</v>
+        <v>18.11</v>
       </c>
       <c r="U7" s="3">
-        <v>21.98</v>
+        <v>28.63</v>
       </c>
       <c r="V7" s="3">
-        <v>22.16</v>
+        <v>43.87</v>
       </c>
       <c r="W7" s="3">
         <v>0</v>
@@ -949,67 +949,67 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C8" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D8" s="1">
-        <v>8236.4</v>
+        <v>7413.5</v>
       </c>
       <c r="E8" s="2">
-        <v>1.26</v>
+        <v>1.72</v>
       </c>
       <c r="F8" s="2">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="G8" s="2">
-        <v>2.75</v>
+        <v>4.77</v>
       </c>
       <c r="H8" s="2">
-        <v>-3.48</v>
+        <v>-1.97</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>8560.89</v>
+        <v>7328.19</v>
       </c>
       <c r="K8" s="1">
-        <v>8155.79</v>
+        <v>7327.47</v>
       </c>
       <c r="L8" s="1">
-        <v>8295.84</v>
+        <v>7367.49</v>
       </c>
       <c r="M8" s="3">
-        <v>-23.22</v>
+        <v>13.02</v>
       </c>
       <c r="N8" s="3">
-        <v>-43.93</v>
+        <v>-8.88</v>
       </c>
       <c r="O8" s="3">
-        <v>-85.52</v>
+        <v>1.29</v>
       </c>
       <c r="P8" s="3">
-        <v>-43.22</v>
+        <v>24.76</v>
       </c>
       <c r="Q8" s="3">
-        <v>574.16</v>
+        <v>477.06</v>
       </c>
       <c r="R8" s="3">
-        <v>685.16</v>
+        <v>553.62</v>
       </c>
       <c r="S8" s="3">
-        <v>52.97</v>
+        <v>56.44</v>
       </c>
       <c r="T8" s="3">
-        <v>24.03</v>
+        <v>22.52</v>
       </c>
       <c r="U8" s="3">
-        <v>22.65</v>
+        <v>23.61</v>
       </c>
       <c r="V8" s="3">
-        <v>15.31</v>
+        <v>23.58</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -1026,67 +1026,67 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C9" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D9" s="1">
-        <v>8395.8</v>
+        <v>30506.2</v>
       </c>
       <c r="E9" s="2">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="F9" s="2">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="G9" s="2">
-        <v>3.94</v>
+        <v>5.14</v>
       </c>
       <c r="H9" s="2">
-        <v>-16.41</v>
+        <v>-9.36</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>8731.21</v>
+        <v>30869.01</v>
       </c>
       <c r="K9" s="1">
-        <v>8319.12</v>
+        <v>30060.26</v>
       </c>
       <c r="L9" s="1">
-        <v>8363.21</v>
+        <v>30014.33</v>
       </c>
       <c r="M9" s="3">
-        <v>9.57</v>
+        <v>123.54</v>
       </c>
       <c r="N9" s="3">
-        <v>-13.07</v>
+        <v>2.2</v>
       </c>
       <c r="O9" s="3">
-        <v>-148.54</v>
+        <v>-299.7</v>
       </c>
       <c r="P9" s="3">
-        <v>-156.78</v>
+        <v>-313.87</v>
       </c>
       <c r="Q9" s="3">
-        <v>-297.81</v>
+        <v>527.7</v>
       </c>
       <c r="R9" s="3">
-        <v>-190.89</v>
+        <v>1000.04</v>
       </c>
       <c r="S9" s="3">
-        <v>56.19</v>
+        <v>60.1</v>
       </c>
       <c r="T9" s="3">
-        <v>19.78</v>
+        <v>22.6</v>
       </c>
       <c r="U9" s="3">
-        <v>22.26</v>
+        <v>21.76</v>
       </c>
       <c r="V9" s="3">
-        <v>20.27</v>
+        <v>22.27</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
@@ -1103,67 +1103,67 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C10" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D10" s="1">
-        <v>27000.8</v>
+        <v>8417.2</v>
       </c>
       <c r="E10" s="2">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="F10" s="2">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="G10" s="2">
-        <v>1.14</v>
+        <v>4.21</v>
       </c>
       <c r="H10" s="2">
-        <v>-5.99</v>
+        <v>-16.2</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>27320.71</v>
+        <v>8731.32</v>
       </c>
       <c r="K10" s="1">
-        <v>26918.67</v>
+        <v>8323.01</v>
       </c>
       <c r="L10" s="1">
-        <v>27227.9</v>
+        <v>8363.64</v>
       </c>
       <c r="M10" s="3">
-        <v>-99</v>
+        <v>11.28</v>
       </c>
       <c r="N10" s="3">
-        <v>-76.2</v>
+        <v>-12.73</v>
       </c>
       <c r="O10" s="3">
-        <v>-69.18</v>
+        <v>-146.83</v>
       </c>
       <c r="P10" s="3">
-        <v>-2.03</v>
+        <v>-156.44</v>
       </c>
       <c r="Q10" s="3">
-        <v>657.43</v>
+        <v>-296.1</v>
       </c>
       <c r="R10" s="3">
-        <v>877.37</v>
+        <v>-190.55</v>
       </c>
       <c r="S10" s="3">
-        <v>49.17</v>
+        <v>57.32</v>
       </c>
       <c r="T10" s="3">
-        <v>17.69</v>
+        <v>20.9</v>
       </c>
       <c r="U10" s="3">
-        <v>23.22</v>
+        <v>21.95</v>
       </c>
       <c r="V10" s="3">
-        <v>16.17</v>
+        <v>20.02</v>
       </c>
       <c r="W10" s="3">
         <v>0</v>
@@ -1180,67 +1180,67 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C11" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D11" s="1">
-        <v>8777.4</v>
+        <v>27052.6</v>
       </c>
       <c r="E11" s="2">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="F11" s="2">
-        <v>2.61</v>
+        <v>1.49</v>
       </c>
       <c r="G11" s="2">
-        <v>0.5</v>
+        <v>1.34</v>
       </c>
       <c r="H11" s="2">
-        <v>-8.72</v>
+        <v>-5.81</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>9201.54</v>
+        <v>27320.97</v>
       </c>
       <c r="K11" s="1">
-        <v>8680.74</v>
+        <v>26928.09</v>
       </c>
       <c r="L11" s="1">
-        <v>8940.78</v>
+        <v>27228.94</v>
       </c>
       <c r="M11" s="3">
-        <v>-65.24</v>
+        <v>-94.87</v>
       </c>
       <c r="N11" s="3">
-        <v>-99.73</v>
+        <v>-75.37</v>
       </c>
       <c r="O11" s="3">
-        <v>-166.36</v>
+        <v>-65.05</v>
       </c>
       <c r="P11" s="3">
-        <v>-97.73</v>
+        <v>-1.21</v>
       </c>
       <c r="Q11" s="3">
-        <v>281.83</v>
+        <v>661.56</v>
       </c>
       <c r="R11" s="3">
-        <v>435.75</v>
+        <v>878.2</v>
       </c>
       <c r="S11" s="3">
-        <v>51.46</v>
+        <v>50.1</v>
       </c>
       <c r="T11" s="3">
-        <v>19.42</v>
+        <v>18.83</v>
       </c>
       <c r="U11" s="3">
-        <v>23.39</v>
+        <v>22.89</v>
       </c>
       <c r="V11" s="3">
-        <v>35.68</v>
+        <v>15.9</v>
       </c>
       <c r="W11" s="3">
         <v>0</v>
@@ -1257,67 +1257,67 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C12" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D12" s="1">
-        <v>53130.9</v>
+        <v>68121.6</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="F12" s="2">
-        <v>6.45</v>
+        <v>3.48</v>
       </c>
       <c r="G12" s="2">
-        <v>-1.75</v>
+        <v>-2.33</v>
       </c>
       <c r="H12" s="2">
-        <v>5.61</v>
+        <v>-1.79</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>52228.88</v>
+        <v>69959.44</v>
       </c>
       <c r="K12" s="1">
-        <v>52685.46</v>
+        <v>67686.28</v>
       </c>
       <c r="L12" s="1">
-        <v>55127.99</v>
+        <v>70907.28</v>
       </c>
       <c r="M12" s="3">
-        <v>-858.76</v>
+        <v>-1027.45</v>
       </c>
       <c r="N12" s="3">
-        <v>-778.3</v>
+        <v>-1088.13</v>
       </c>
       <c r="O12" s="3">
-        <v>368.98</v>
+        <v>-484.78</v>
       </c>
       <c r="P12" s="3">
-        <v>963.79</v>
+        <v>342.73</v>
       </c>
       <c r="Q12" s="3">
-        <v>3711.46</v>
+        <v>2701.12</v>
       </c>
       <c r="R12" s="3">
-        <v>3891.13</v>
+        <v>3189.85</v>
       </c>
       <c r="S12" s="3">
-        <v>46.58</v>
+        <v>44.92</v>
       </c>
       <c r="T12" s="3">
-        <v>18.51</v>
+        <v>17.79</v>
       </c>
       <c r="U12" s="3">
-        <v>37.87</v>
+        <v>33.04</v>
       </c>
       <c r="V12" s="3">
-        <v>36.62</v>
+        <v>47.06</v>
       </c>
       <c r="W12" s="3">
         <v>0</v>
@@ -1334,67 +1334,67 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C13" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D13" s="1">
-        <v>18855</v>
+        <v>32498.35</v>
       </c>
       <c r="E13" s="2">
-        <v>0.99</v>
+        <v>1.19</v>
       </c>
       <c r="F13" s="2">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="G13" s="2">
-        <v>0.37</v>
+        <v>-1.1</v>
       </c>
       <c r="H13" s="2">
-        <v>-10.77</v>
+        <v>-4.29</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>19804.62</v>
+        <v>33633.38</v>
       </c>
       <c r="K13" s="1">
-        <v>18721.97</v>
+        <v>32278.85</v>
       </c>
       <c r="L13" s="1">
-        <v>19319.9</v>
+        <v>33595.04</v>
       </c>
       <c r="M13" s="3">
-        <v>-157.3</v>
+        <v>-394.15</v>
       </c>
       <c r="N13" s="3">
-        <v>-209.68</v>
+        <v>-447.39</v>
       </c>
       <c r="O13" s="3">
-        <v>-319.23</v>
+        <v>-340.93</v>
       </c>
       <c r="P13" s="3">
-        <v>-181.82</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" s="3">
-        <v>769.4</v>
+        <v>2018.8</v>
       </c>
       <c r="R13" s="3">
-        <v>1113.7</v>
+        <v>2433.68</v>
       </c>
       <c r="S13" s="3">
-        <v>48.4</v>
+        <v>46.09</v>
       </c>
       <c r="T13" s="3">
-        <v>13.71</v>
+        <v>16.53</v>
       </c>
       <c r="U13" s="3">
-        <v>23.48</v>
+        <v>29.09</v>
       </c>
       <c r="V13" s="3">
-        <v>46.52</v>
+        <v>46.8</v>
       </c>
       <c r="W13" s="3">
         <v>0</v>
@@ -1411,67 +1411,67 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C14" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D14" s="1">
-        <v>35281.75</v>
+        <v>18892.85</v>
       </c>
       <c r="E14" s="2">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="F14" s="2">
-        <v>2.21</v>
+        <v>1.77</v>
       </c>
       <c r="G14" s="2">
-        <v>-3.7</v>
+        <v>0.57</v>
       </c>
       <c r="H14" s="2">
-        <v>-0.12</v>
+        <v>-10.59</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>37706.56</v>
+        <v>19804.81</v>
       </c>
       <c r="K14" s="1">
-        <v>35375.49</v>
+        <v>18728.85</v>
       </c>
       <c r="L14" s="1">
-        <v>37045.74</v>
+        <v>19320.66</v>
       </c>
       <c r="M14" s="3">
-        <v>-598.63</v>
+        <v>-154.28</v>
       </c>
       <c r="N14" s="3">
-        <v>-576.02</v>
+        <v>-209.07</v>
       </c>
       <c r="O14" s="3">
-        <v>-683.92</v>
+        <v>-316.21</v>
       </c>
       <c r="P14" s="3">
-        <v>-206.82</v>
+        <v>-181.22</v>
       </c>
       <c r="Q14" s="3">
-        <v>950.65</v>
+        <v>772.42</v>
       </c>
       <c r="R14" s="3">
-        <v>1231.45</v>
+        <v>1114.3</v>
       </c>
       <c r="S14" s="3">
-        <v>39.71</v>
+        <v>49.62</v>
       </c>
       <c r="T14" s="3">
-        <v>13.61</v>
+        <v>15.17</v>
       </c>
       <c r="U14" s="3">
-        <v>34.86</v>
+        <v>23.08</v>
       </c>
       <c r="V14" s="3">
-        <v>37.71</v>
+        <v>46.12</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1488,67 +1488,67 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C15" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D15" s="1">
-        <v>206.19</v>
+        <v>54909.65</v>
       </c>
       <c r="E15" s="2">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
       <c r="F15" s="2">
-        <v>0.96</v>
+        <v>1.15</v>
       </c>
       <c r="G15" s="2">
-        <v>4.78</v>
+        <v>0.51</v>
       </c>
       <c r="H15" s="2">
-        <v>-17.24</v>
+        <v>-7.84</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>179.55</v>
+        <v>56730.45</v>
       </c>
       <c r="K15" s="1">
-        <v>203.08</v>
+        <v>54719.04</v>
       </c>
       <c r="L15" s="1">
-        <v>196.37</v>
+        <v>55999.88</v>
       </c>
       <c r="M15" s="3">
-        <v>3.04</v>
+        <v>-388.39</v>
       </c>
       <c r="N15" s="3">
-        <v>2.81</v>
+        <v>-381.74</v>
       </c>
       <c r="O15" s="3">
-        <v>12.48</v>
+        <v>-452.22</v>
       </c>
       <c r="P15" s="3">
-        <v>7.05</v>
+        <v>-177.87</v>
       </c>
       <c r="Q15" s="3">
-        <v>5.63</v>
+        <v>1659.72</v>
       </c>
       <c r="R15" s="3">
-        <v>7.71</v>
+        <v>2287.52</v>
       </c>
       <c r="S15" s="3">
-        <v>100</v>
+        <v>47.07</v>
       </c>
       <c r="T15" s="3">
-        <v>99.72</v>
+        <v>15.97</v>
       </c>
       <c r="U15" s="3">
-        <v>0.28</v>
+        <v>23.84</v>
       </c>
       <c r="V15" s="3">
-        <v>97.59</v>
+        <v>25.39</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1565,67 +1565,67 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D16" s="1">
-        <v>24647.9</v>
+        <v>35149.75</v>
       </c>
       <c r="E16" s="2">
-        <v>0.94</v>
+        <v>1.18</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>3.62</v>
       </c>
       <c r="G16" s="2">
-        <v>-0.01</v>
+        <v>-4.04</v>
       </c>
       <c r="H16" s="2">
-        <v>-10.74</v>
+        <v>-4.37</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>26139.42</v>
+        <v>37042.39</v>
       </c>
       <c r="K16" s="1">
-        <v>24638.76</v>
+        <v>35024.48</v>
       </c>
       <c r="L16" s="1">
-        <v>25336.79</v>
+        <v>37802.41</v>
       </c>
       <c r="M16" s="3">
-        <v>-226.36</v>
+        <v>-907.18</v>
       </c>
       <c r="N16" s="3">
-        <v>-212.41</v>
+        <v>-891.29</v>
       </c>
       <c r="O16" s="3">
-        <v>-408.76</v>
+        <v>-432.56</v>
       </c>
       <c r="P16" s="3">
-        <v>-263.32</v>
+        <v>149.9</v>
       </c>
       <c r="Q16" s="3">
-        <v>647.46</v>
+        <v>630.86</v>
       </c>
       <c r="R16" s="3">
-        <v>1081.05</v>
+        <v>938.34</v>
       </c>
       <c r="S16" s="3">
-        <v>44.57</v>
+        <v>40.13</v>
       </c>
       <c r="T16" s="3">
-        <v>14.5</v>
+        <v>14.83</v>
       </c>
       <c r="U16" s="3">
-        <v>25.64</v>
+        <v>32.72</v>
       </c>
       <c r="V16" s="3">
-        <v>28.64</v>
+        <v>55.44</v>
       </c>
       <c r="W16" s="3">
         <v>0</v>
@@ -1642,67 +1642,67 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C17" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D17" s="1">
-        <v>9077.45</v>
+        <v>24911.55</v>
       </c>
       <c r="E17" s="2">
-        <v>0.93</v>
+        <v>1.18</v>
       </c>
       <c r="F17" s="2">
-        <v>2.16</v>
+        <v>5.26</v>
       </c>
       <c r="G17" s="2">
-        <v>-3.02</v>
+        <v>-1.9</v>
       </c>
       <c r="H17" s="2">
-        <v>-7.88</v>
+        <v>-0.3</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>9963.53</v>
+        <v>25449.16</v>
       </c>
       <c r="K17" s="1">
-        <v>9072.72</v>
+        <v>24660.16</v>
       </c>
       <c r="L17" s="1">
-        <v>9452.08</v>
+        <v>25919.88</v>
       </c>
       <c r="M17" s="3">
-        <v>-129.18</v>
+        <v>-411.03</v>
       </c>
       <c r="N17" s="3">
-        <v>-133.4</v>
+        <v>-420.97</v>
       </c>
       <c r="O17" s="3">
-        <v>-255.43</v>
+        <v>-155.07</v>
       </c>
       <c r="P17" s="3">
-        <v>-171.19</v>
+        <v>132.77</v>
       </c>
       <c r="Q17" s="3">
-        <v>791.36</v>
+        <v>101.13</v>
       </c>
       <c r="R17" s="3">
-        <v>1091.7</v>
+        <v>-48.22</v>
       </c>
       <c r="S17" s="3">
-        <v>41.98</v>
+        <v>46.58</v>
       </c>
       <c r="T17" s="3">
-        <v>12.65</v>
+        <v>17.4</v>
       </c>
       <c r="U17" s="3">
-        <v>33.7</v>
+        <v>34.9</v>
       </c>
       <c r="V17" s="3">
-        <v>49.34</v>
+        <v>41.99</v>
       </c>
       <c r="W17" s="3">
         <v>0</v>
@@ -1719,67 +1719,67 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C18" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D18" s="1">
-        <v>35051.6</v>
+        <v>8792.5</v>
       </c>
       <c r="E18" s="2">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="F18" s="2">
-        <v>3.33</v>
+        <v>2.79</v>
       </c>
       <c r="G18" s="2">
-        <v>-4.3</v>
+        <v>0.67</v>
       </c>
       <c r="H18" s="2">
-        <v>-4.64</v>
+        <v>-8.57</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>37041.89</v>
+        <v>9201.62</v>
       </c>
       <c r="K18" s="1">
-        <v>35006.63</v>
+        <v>8683.49</v>
       </c>
       <c r="L18" s="1">
-        <v>37800.45</v>
+        <v>8941.08</v>
       </c>
       <c r="M18" s="3">
-        <v>-915.01</v>
+        <v>-64.04</v>
       </c>
       <c r="N18" s="3">
-        <v>-892.86</v>
+        <v>-99.49</v>
       </c>
       <c r="O18" s="3">
-        <v>-440.38</v>
+        <v>-165.15</v>
       </c>
       <c r="P18" s="3">
-        <v>148.33</v>
+        <v>-97.49</v>
       </c>
       <c r="Q18" s="3">
-        <v>623.03</v>
+        <v>283.03</v>
       </c>
       <c r="R18" s="3">
-        <v>936.77</v>
+        <v>435.99</v>
       </c>
       <c r="S18" s="3">
-        <v>39</v>
+        <v>52.24</v>
       </c>
       <c r="T18" s="3">
-        <v>14.15</v>
+        <v>19.95</v>
       </c>
       <c r="U18" s="3">
-        <v>32.98</v>
+        <v>23.24</v>
       </c>
       <c r="V18" s="3">
-        <v>55.6</v>
+        <v>35.56</v>
       </c>
       <c r="W18" s="3">
         <v>0</v>
@@ -1796,67 +1796,67 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C19" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D19" s="1">
-        <v>3794.35</v>
+        <v>24704.55</v>
       </c>
       <c r="E19" s="2">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="F19" s="2">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="G19" s="2">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H19" s="2">
-        <v>-12.84</v>
+        <v>-10.53</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>4019.43</v>
+        <v>26139.7</v>
       </c>
       <c r="K19" s="1">
-        <v>3783.51</v>
+        <v>24649.06</v>
       </c>
       <c r="L19" s="1">
-        <v>3892.38</v>
+        <v>25337.92</v>
       </c>
       <c r="M19" s="3">
-        <v>-28.87</v>
+        <v>-221.84</v>
       </c>
       <c r="N19" s="3">
-        <v>-36.14</v>
+        <v>-211.51</v>
       </c>
       <c r="O19" s="3">
-        <v>-71.6</v>
+        <v>-404.24</v>
       </c>
       <c r="P19" s="3">
-        <v>-48.8</v>
+        <v>-262.41</v>
       </c>
       <c r="Q19" s="3">
-        <v>126.37</v>
+        <v>651.98</v>
       </c>
       <c r="R19" s="3">
-        <v>206.8</v>
+        <v>1081.96</v>
       </c>
       <c r="S19" s="3">
-        <v>46.84</v>
+        <v>45.72</v>
       </c>
       <c r="T19" s="3">
-        <v>15.42</v>
+        <v>15.57</v>
       </c>
       <c r="U19" s="3">
-        <v>27.63</v>
+        <v>25.31</v>
       </c>
       <c r="V19" s="3">
-        <v>36.7</v>
+        <v>28.36</v>
       </c>
       <c r="W19" s="3">
         <v>0</v>
@@ -1873,67 +1873,67 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D20" s="1">
-        <v>9509.2</v>
+        <v>5575.15</v>
       </c>
       <c r="E20" s="2">
-        <v>0.86</v>
+        <v>1.16</v>
       </c>
       <c r="F20" s="2">
-        <v>6.55</v>
+        <v>1.17</v>
       </c>
       <c r="G20" s="2">
-        <v>-1.28</v>
+        <v>1.87</v>
       </c>
       <c r="H20" s="2">
-        <v>10.49</v>
+        <v>-12.69</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>8996.1</v>
+        <v>5931.72</v>
       </c>
       <c r="K20" s="1">
-        <v>9377.47</v>
+        <v>5543.85</v>
       </c>
       <c r="L20" s="1">
-        <v>9743.14</v>
+        <v>5644.24</v>
       </c>
       <c r="M20" s="3">
-        <v>-125.51</v>
+        <v>-17.99</v>
       </c>
       <c r="N20" s="3">
-        <v>-125.18</v>
+        <v>-32.73</v>
       </c>
       <c r="O20" s="3">
-        <v>154.36</v>
+        <v>-118.99</v>
       </c>
       <c r="P20" s="3">
-        <v>261.96</v>
+        <v>-100.95</v>
       </c>
       <c r="Q20" s="3">
-        <v>748.93</v>
+        <v>26.94</v>
       </c>
       <c r="R20" s="3">
-        <v>721.42</v>
+        <v>139.87</v>
       </c>
       <c r="S20" s="3">
-        <v>49.34</v>
+        <v>51.18</v>
       </c>
       <c r="T20" s="3">
-        <v>24.65</v>
+        <v>19.88</v>
       </c>
       <c r="U20" s="3">
-        <v>38.44</v>
+        <v>27.37</v>
       </c>
       <c r="V20" s="3">
-        <v>34.71</v>
+        <v>32.26</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1956,61 +1956,61 @@
         <v>NIFTY100ESG</v>
       </c>
       <c r="D21" s="1">
-        <v>4725.85</v>
+        <v>4739.85</v>
       </c>
       <c r="E21" s="2">
-        <v>0.86</v>
+        <v>1.16</v>
       </c>
       <c r="F21" s="2">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="G21" s="2">
-        <v>0.9</v>
+        <v>1.19</v>
       </c>
       <c r="H21" s="2">
-        <v>-8.79</v>
+        <v>-8.52</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>4901.82</v>
+        <v>4901.89</v>
       </c>
       <c r="K21" s="1">
-        <v>4698.73</v>
+        <v>4701.28</v>
       </c>
       <c r="L21" s="1">
-        <v>4826.29</v>
+        <v>4826.57</v>
       </c>
       <c r="M21" s="3">
-        <v>-30.84</v>
+        <v>-29.73</v>
       </c>
       <c r="N21" s="3">
-        <v>-42.46</v>
+        <v>-42.23</v>
       </c>
       <c r="O21" s="3">
-        <v>-56.93</v>
+        <v>-55.81</v>
       </c>
       <c r="P21" s="3">
-        <v>-25.76</v>
+        <v>-25.53</v>
       </c>
       <c r="Q21" s="3">
-        <v>222.59</v>
+        <v>223.71</v>
       </c>
       <c r="R21" s="3">
-        <v>299.95</v>
+        <v>300.17</v>
       </c>
       <c r="S21" s="3">
-        <v>49.12</v>
+        <v>50.58</v>
       </c>
       <c r="T21" s="3">
-        <v>16.57</v>
+        <v>17.99</v>
       </c>
       <c r="U21" s="3">
-        <v>27.35</v>
+        <v>26.88</v>
       </c>
       <c r="V21" s="3">
-        <v>36.27</v>
+        <v>35.94</v>
       </c>
       <c r="W21" s="3">
         <v>0</v>
@@ -2027,67 +2027,67 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C22" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D22" s="1">
-        <v>54728</v>
+        <v>59829.15</v>
       </c>
       <c r="E22" s="2">
-        <v>0.85</v>
+        <v>1.15</v>
       </c>
       <c r="F22" s="2">
-        <v>0.81</v>
+        <v>5.31</v>
       </c>
       <c r="G22" s="2">
-        <v>0.17</v>
+        <v>-1.55</v>
       </c>
       <c r="H22" s="2">
-        <v>-8.15</v>
+        <v>-3.37</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>56729.54</v>
+        <v>61629.62</v>
       </c>
       <c r="K22" s="1">
-        <v>54686.01</v>
+        <v>59158.88</v>
       </c>
       <c r="L22" s="1">
-        <v>55996.24</v>
+        <v>62028.04</v>
       </c>
       <c r="M22" s="3">
-        <v>-402.88</v>
+        <v>-947.36</v>
       </c>
       <c r="N22" s="3">
-        <v>-384.63</v>
+        <v>-989.74</v>
       </c>
       <c r="O22" s="3">
-        <v>-466.71</v>
+        <v>-587.4</v>
       </c>
       <c r="P22" s="3">
-        <v>-180.77</v>
+        <v>33.45</v>
       </c>
       <c r="Q22" s="3">
-        <v>1645.23</v>
+        <v>-8.01</v>
       </c>
       <c r="R22" s="3">
-        <v>2284.63</v>
+        <v>-174.53</v>
       </c>
       <c r="S22" s="3">
-        <v>45.13</v>
+        <v>47.04</v>
       </c>
       <c r="T22" s="3">
-        <v>14.31</v>
+        <v>17.68</v>
       </c>
       <c r="U22" s="3">
-        <v>24.31</v>
+        <v>34.77</v>
       </c>
       <c r="V22" s="3">
-        <v>25.83</v>
+        <v>44.54</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2104,67 +2104,67 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D23" s="1">
-        <v>32386.55</v>
+        <v>9097.1</v>
       </c>
       <c r="E23" s="2">
-        <v>0.85</v>
+        <v>1.15</v>
       </c>
       <c r="F23" s="2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G23" s="2">
-        <v>-1.44</v>
+        <v>-2.81</v>
       </c>
       <c r="H23" s="2">
-        <v>-4.62</v>
+        <v>-7.68</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>33632.82</v>
+        <v>9963.62</v>
       </c>
       <c r="K23" s="1">
-        <v>32258.52</v>
+        <v>9076.29</v>
       </c>
       <c r="L23" s="1">
-        <v>33592.8</v>
+        <v>9452.48</v>
       </c>
       <c r="M23" s="3">
-        <v>-403.06</v>
+        <v>-127.61</v>
       </c>
       <c r="N23" s="3">
-        <v>-449.18</v>
+        <v>-133.08</v>
       </c>
       <c r="O23" s="3">
-        <v>-349.84</v>
+        <v>-253.86</v>
       </c>
       <c r="P23" s="3">
-        <v>-0.02</v>
+        <v>-170.88</v>
       </c>
       <c r="Q23" s="3">
-        <v>2009.88</v>
+        <v>792.92</v>
       </c>
       <c r="R23" s="3">
-        <v>2431.9</v>
+        <v>1092.01</v>
       </c>
       <c r="S23" s="3">
-        <v>44.25</v>
+        <v>43.09</v>
       </c>
       <c r="T23" s="3">
-        <v>14.81</v>
+        <v>14.03</v>
       </c>
       <c r="U23" s="3">
-        <v>29.69</v>
+        <v>33.17</v>
       </c>
       <c r="V23" s="3">
-        <v>47.23</v>
+        <v>48.99</v>
       </c>
       <c r="W23" s="3">
         <v>0</v>
@@ -2181,67 +2181,67 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C24" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D24" s="1">
-        <v>18792.55</v>
+        <v>8882.9</v>
       </c>
       <c r="E24" s="2">
-        <v>0.85</v>
+        <v>1.14</v>
       </c>
       <c r="F24" s="2">
-        <v>5.94</v>
+        <v>3.76</v>
       </c>
       <c r="G24" s="2">
-        <v>-2.35</v>
+        <v>-4.25</v>
       </c>
       <c r="H24" s="2">
-        <v>6.09</v>
+        <v>14.66</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>18200.98</v>
+        <v>8861.48</v>
       </c>
       <c r="K24" s="1">
-        <v>18618.14</v>
+        <v>8882.17</v>
       </c>
       <c r="L24" s="1">
-        <v>19472.38</v>
+        <v>9377.19</v>
       </c>
       <c r="M24" s="3">
-        <v>-305.21</v>
+        <v>-165.1</v>
       </c>
       <c r="N24" s="3">
-        <v>-284.32</v>
+        <v>-150.55</v>
       </c>
       <c r="O24" s="3">
-        <v>197.9</v>
+        <v>47.18</v>
       </c>
       <c r="P24" s="3">
-        <v>421.23</v>
+        <v>194.18</v>
       </c>
       <c r="Q24" s="3">
-        <v>881.35</v>
+        <v>608.74</v>
       </c>
       <c r="R24" s="3">
-        <v>860.44</v>
+        <v>523.85</v>
       </c>
       <c r="S24" s="3">
-        <v>46.46</v>
+        <v>43.04</v>
       </c>
       <c r="T24" s="3">
-        <v>23.23</v>
+        <v>20.13</v>
       </c>
       <c r="U24" s="3">
-        <v>40.5</v>
+        <v>33.83</v>
       </c>
       <c r="V24" s="3">
-        <v>36.76</v>
+        <v>28.85</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2258,67 +2258,67 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D25" s="1">
-        <v>22890</v>
+        <v>53204.45</v>
       </c>
       <c r="E25" s="2">
-        <v>0.84</v>
+        <v>1.13</v>
       </c>
       <c r="F25" s="2">
-        <v>1.28</v>
+        <v>6.6</v>
       </c>
       <c r="G25" s="2">
-        <v>1.19</v>
+        <v>-1.62</v>
       </c>
       <c r="H25" s="2">
-        <v>-12.4</v>
+        <v>5.76</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>24049.78</v>
+        <v>52229.25</v>
       </c>
       <c r="K25" s="1">
-        <v>22766.9</v>
+        <v>52698.84</v>
       </c>
       <c r="L25" s="1">
-        <v>23275.85</v>
+        <v>55129.46</v>
       </c>
       <c r="M25" s="3">
-        <v>-117.91</v>
+        <v>-852.9</v>
       </c>
       <c r="N25" s="3">
-        <v>-171.91</v>
+        <v>-777.13</v>
       </c>
       <c r="O25" s="3">
-        <v>-400.89</v>
+        <v>374.85</v>
       </c>
       <c r="P25" s="3">
-        <v>-302.72</v>
+        <v>964.97</v>
       </c>
       <c r="Q25" s="3">
-        <v>200.32</v>
+        <v>3717.32</v>
       </c>
       <c r="R25" s="3">
-        <v>600.91</v>
+        <v>3892.3</v>
       </c>
       <c r="S25" s="3">
-        <v>49.79</v>
+        <v>46.99</v>
       </c>
       <c r="T25" s="3">
-        <v>15.06</v>
+        <v>18.91</v>
       </c>
       <c r="U25" s="3">
-        <v>24.7</v>
+        <v>37.69</v>
       </c>
       <c r="V25" s="3">
-        <v>34.91</v>
+        <v>36.53</v>
       </c>
       <c r="W25" s="3">
         <v>0</v>
@@ -2341,61 +2341,61 @@
         <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D26" s="1">
-        <v>5189.45</v>
+        <v>5203.75</v>
       </c>
       <c r="E26" s="2">
-        <v>0.84</v>
+        <v>1.11</v>
       </c>
       <c r="F26" s="2">
-        <v>5.26</v>
+        <v>5.55</v>
       </c>
       <c r="G26" s="2">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="H26" s="2">
-        <v>11.45</v>
+        <v>11.76</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>5115.47</v>
+        <v>5115.54</v>
       </c>
       <c r="K26" s="1">
-        <v>5130.16</v>
+        <v>5132.76</v>
       </c>
       <c r="L26" s="1">
-        <v>5277.69</v>
+        <v>5277.98</v>
       </c>
       <c r="M26" s="3">
-        <v>-44.55</v>
+        <v>-43.41</v>
       </c>
       <c r="N26" s="3">
-        <v>-47.08</v>
+        <v>-46.85</v>
       </c>
       <c r="O26" s="3">
-        <v>13.45</v>
+        <v>14.59</v>
       </c>
       <c r="P26" s="3">
-        <v>70.28</v>
+        <v>70.51</v>
       </c>
       <c r="Q26" s="3">
-        <v>374.47</v>
+        <v>375.61</v>
       </c>
       <c r="R26" s="3">
-        <v>327.35</v>
+        <v>327.58</v>
       </c>
       <c r="S26" s="3">
-        <v>50.36</v>
+        <v>51.16</v>
       </c>
       <c r="T26" s="3">
-        <v>20.48</v>
+        <v>21.42</v>
       </c>
       <c r="U26" s="3">
-        <v>27.07</v>
+        <v>26.75</v>
       </c>
       <c r="V26" s="3">
-        <v>22.93</v>
+        <v>22.73</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
@@ -2412,67 +2412,67 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C27" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D27" s="1">
-        <v>23837.9</v>
+        <v>3802.55</v>
       </c>
       <c r="E27" s="2">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="F27" s="2">
-        <v>1.59</v>
+        <v>1.31</v>
       </c>
       <c r="G27" s="2">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H27" s="2">
-        <v>-10.68</v>
+        <v>-12.65</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>24961.08</v>
+        <v>4019.47</v>
       </c>
       <c r="K27" s="1">
-        <v>23722.7</v>
+        <v>3785</v>
       </c>
       <c r="L27" s="1">
-        <v>24366.48</v>
+        <v>3892.55</v>
       </c>
       <c r="M27" s="3">
-        <v>-168.15</v>
+        <v>-28.21</v>
       </c>
       <c r="N27" s="3">
-        <v>-216.63</v>
+        <v>-36.01</v>
       </c>
       <c r="O27" s="3">
-        <v>-372.99</v>
+        <v>-70.94</v>
       </c>
       <c r="P27" s="3">
-        <v>-234.53</v>
+        <v>-48.67</v>
       </c>
       <c r="Q27" s="3">
-        <v>339.99</v>
+        <v>127.03</v>
       </c>
       <c r="R27" s="3">
-        <v>710.17</v>
+        <v>206.93</v>
       </c>
       <c r="S27" s="3">
-        <v>48.16</v>
+        <v>47.95</v>
       </c>
       <c r="T27" s="3">
-        <v>14.67</v>
+        <v>16.61</v>
       </c>
       <c r="U27" s="3">
-        <v>27.03</v>
+        <v>27.25</v>
       </c>
       <c r="V27" s="3">
-        <v>41.74</v>
+        <v>36.41</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
@@ -2489,67 +2489,67 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D28" s="1">
-        <v>11034</v>
+        <v>1655.35</v>
       </c>
       <c r="E28" s="2">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="F28" s="2">
-        <v>2.86</v>
+        <v>5.88</v>
       </c>
       <c r="G28" s="2">
-        <v>-0.35</v>
+        <v>4.56</v>
       </c>
       <c r="H28" s="2">
-        <v>-10.22</v>
+        <v>14.58</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>11462.28</v>
+        <v>1472.63</v>
       </c>
       <c r="K28" s="1">
-        <v>10918.59</v>
+        <v>1613.51</v>
       </c>
       <c r="L28" s="1">
-        <v>11354.03</v>
+        <v>1576.86</v>
       </c>
       <c r="M28" s="3">
-        <v>-119.6</v>
+        <v>15.95</v>
       </c>
       <c r="N28" s="3">
-        <v>-157.69</v>
+        <v>13.34</v>
       </c>
       <c r="O28" s="3">
-        <v>-167.33</v>
+        <v>35.94</v>
       </c>
       <c r="P28" s="3">
-        <v>-68</v>
+        <v>32.24</v>
       </c>
       <c r="Q28" s="3">
-        <v>233.17</v>
+        <v>-67.63</v>
       </c>
       <c r="R28" s="3">
-        <v>397.3</v>
+        <v>-104.42</v>
       </c>
       <c r="S28" s="3">
-        <v>49.07</v>
+        <v>60.64</v>
       </c>
       <c r="T28" s="3">
-        <v>17.54</v>
+        <v>27.7</v>
       </c>
       <c r="U28" s="3">
-        <v>27.23</v>
+        <v>22.74</v>
       </c>
       <c r="V28" s="3">
-        <v>44.33</v>
+        <v>15.68</v>
       </c>
       <c r="W28" s="3">
         <v>0</v>
@@ -2566,67 +2566,67 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C29" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D29" s="1">
-        <v>8966.35</v>
+        <v>13630.35</v>
       </c>
       <c r="E29" s="2">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="F29" s="2">
-        <v>1.98</v>
+        <v>3.48</v>
       </c>
       <c r="G29" s="2">
-        <v>-3.69</v>
+        <v>-0.87</v>
       </c>
       <c r="H29" s="2">
-        <v>-5.77</v>
+        <v>-5.81</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>9742.51</v>
+        <v>14120.26</v>
       </c>
       <c r="K29" s="1">
-        <v>8960.49</v>
+        <v>13486.39</v>
       </c>
       <c r="L29" s="1">
-        <v>9402.41</v>
+        <v>14013.31</v>
       </c>
       <c r="M29" s="3">
-        <v>-139.15</v>
+        <v>-154.34</v>
       </c>
       <c r="N29" s="3">
-        <v>-156.76</v>
+        <v>-191.97</v>
       </c>
       <c r="O29" s="3">
-        <v>-210.82</v>
+        <v>-193.64</v>
       </c>
       <c r="P29" s="3">
-        <v>-97.24</v>
+        <v>-52.9</v>
       </c>
       <c r="Q29" s="3">
-        <v>390.92</v>
+        <v>95.04</v>
       </c>
       <c r="R29" s="3">
-        <v>508.55</v>
+        <v>122.19</v>
       </c>
       <c r="S29" s="3">
-        <v>42.19</v>
+        <v>48.75</v>
       </c>
       <c r="T29" s="3">
-        <v>14.49</v>
+        <v>18.43</v>
       </c>
       <c r="U29" s="3">
-        <v>29.09</v>
+        <v>29</v>
       </c>
       <c r="V29" s="3">
-        <v>40.96</v>
+        <v>41.91</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2643,67 +2643,67 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D30" s="1">
-        <v>8558.05</v>
+        <v>23899.15</v>
       </c>
       <c r="E30" s="2">
-        <v>0.81</v>
+        <v>1.08</v>
       </c>
       <c r="F30" s="2">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="G30" s="2">
-        <v>6.62</v>
+        <v>0.69</v>
       </c>
       <c r="H30" s="2">
-        <v>-9.17</v>
+        <v>-10.45</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>8233.71</v>
+        <v>24961.39</v>
       </c>
       <c r="K30" s="1">
-        <v>8498.59</v>
+        <v>23733.84</v>
       </c>
       <c r="L30" s="1">
-        <v>8508.26</v>
+        <v>24367.71</v>
       </c>
       <c r="M30" s="3">
-        <v>42</v>
+        <v>-163.27</v>
       </c>
       <c r="N30" s="3">
-        <v>11.05</v>
+        <v>-215.66</v>
       </c>
       <c r="O30" s="3">
-        <v>66.63</v>
+        <v>-368.1</v>
       </c>
       <c r="P30" s="3">
-        <v>59.55</v>
+        <v>-233.56</v>
       </c>
       <c r="Q30" s="3">
-        <v>375.79</v>
+        <v>344.87</v>
       </c>
       <c r="R30" s="3">
-        <v>514.4</v>
+        <v>711.14</v>
       </c>
       <c r="S30" s="3">
-        <v>55.44</v>
+        <v>49.51</v>
       </c>
       <c r="T30" s="3">
-        <v>20.29</v>
+        <v>16</v>
       </c>
       <c r="U30" s="3">
-        <v>22.47</v>
+        <v>26.61</v>
       </c>
       <c r="V30" s="3">
-        <v>17.58</v>
+        <v>41.4</v>
       </c>
       <c r="W30" s="3">
         <v>0</v>
@@ -2720,67 +2720,67 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D31" s="1">
-        <v>5555.6</v>
+        <v>8579.95</v>
       </c>
       <c r="E31" s="2">
-        <v>0.81</v>
+        <v>1.07</v>
       </c>
       <c r="F31" s="2">
-        <v>0.81</v>
+        <v>1.84</v>
       </c>
       <c r="G31" s="2">
-        <v>1.52</v>
+        <v>6.89</v>
       </c>
       <c r="H31" s="2">
-        <v>-12.99</v>
+        <v>-8.94</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>5931.63</v>
+        <v>8233.82</v>
       </c>
       <c r="K31" s="1">
-        <v>5540.3</v>
+        <v>8502.57</v>
       </c>
       <c r="L31" s="1">
-        <v>5643.85</v>
+        <v>8508.7</v>
       </c>
       <c r="M31" s="3">
-        <v>-19.55</v>
+        <v>43.75</v>
       </c>
       <c r="N31" s="3">
-        <v>-33.04</v>
+        <v>11.4</v>
       </c>
       <c r="O31" s="3">
-        <v>-120.55</v>
+        <v>68.37</v>
       </c>
       <c r="P31" s="3">
-        <v>-101.27</v>
+        <v>59.9</v>
       </c>
       <c r="Q31" s="3">
-        <v>25.38</v>
+        <v>377.54</v>
       </c>
       <c r="R31" s="3">
-        <v>139.56</v>
+        <v>514.75</v>
       </c>
       <c r="S31" s="3">
-        <v>49.44</v>
+        <v>56.26</v>
       </c>
       <c r="T31" s="3">
-        <v>18.38</v>
+        <v>20.82</v>
       </c>
       <c r="U31" s="3">
-        <v>27.88</v>
+        <v>22.32</v>
       </c>
       <c r="V31" s="3">
-        <v>32.6</v>
+        <v>17.46</v>
       </c>
       <c r="W31" s="3">
         <v>0</v>
@@ -2797,67 +2797,67 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C32" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D32" s="1">
-        <v>30972.1</v>
+        <v>13176.05</v>
       </c>
       <c r="E32" s="2">
-        <v>0.8</v>
+        <v>1.06</v>
       </c>
       <c r="F32" s="2">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="G32" s="2">
-        <v>0.22</v>
+        <v>0.05</v>
       </c>
       <c r="H32" s="2">
-        <v>-7.08</v>
+        <v>-9.34</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>32280.18</v>
+        <v>13753.84</v>
       </c>
       <c r="K32" s="1">
-        <v>30760.79</v>
+        <v>13092.38</v>
       </c>
       <c r="L32" s="1">
-        <v>31709.82</v>
+        <v>13519.43</v>
       </c>
       <c r="M32" s="3">
-        <v>-253.43</v>
+        <v>-120.03</v>
       </c>
       <c r="N32" s="3">
-        <v>-333.92</v>
+        <v>-143.67</v>
       </c>
       <c r="O32" s="3">
-        <v>-426.21</v>
+        <v>-189.92</v>
       </c>
       <c r="P32" s="3">
-        <v>-179.95</v>
+        <v>-94.96</v>
       </c>
       <c r="Q32" s="3">
-        <v>1855.84</v>
+        <v>278.03</v>
       </c>
       <c r="R32" s="3">
-        <v>2378.65</v>
+        <v>466</v>
       </c>
       <c r="S32" s="3">
-        <v>48.59</v>
+        <v>47.7</v>
       </c>
       <c r="T32" s="3">
-        <v>14.74</v>
+        <v>15.11</v>
       </c>
       <c r="U32" s="3">
-        <v>26.48</v>
+        <v>28.52</v>
       </c>
       <c r="V32" s="3">
-        <v>43.06</v>
+        <v>45.6</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -2874,67 +2874,67 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY</v>
       </c>
       <c r="D33" s="1">
-        <v>13591.85</v>
+        <v>22936.75</v>
       </c>
       <c r="E33" s="2">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="F33" s="2">
-        <v>3.19</v>
+        <v>1.49</v>
       </c>
       <c r="G33" s="2">
-        <v>-1.15</v>
+        <v>1.4</v>
       </c>
       <c r="H33" s="2">
-        <v>-6.08</v>
+        <v>-12.22</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>14120.06</v>
+        <v>24050.01</v>
       </c>
       <c r="K33" s="1">
-        <v>13479.39</v>
+        <v>22775.4</v>
       </c>
       <c r="L33" s="1">
-        <v>14012.54</v>
+        <v>23276.78</v>
       </c>
       <c r="M33" s="3">
-        <v>-157.41</v>
+        <v>-114.18</v>
       </c>
       <c r="N33" s="3">
-        <v>-192.59</v>
+        <v>-171.17</v>
       </c>
       <c r="O33" s="3">
-        <v>-196.71</v>
+        <v>-397.16</v>
       </c>
       <c r="P33" s="3">
-        <v>-53.51</v>
+        <v>-301.97</v>
       </c>
       <c r="Q33" s="3">
-        <v>91.97</v>
+        <v>204.05</v>
       </c>
       <c r="R33" s="3">
-        <v>121.58</v>
+        <v>601.66</v>
       </c>
       <c r="S33" s="3">
-        <v>47.39</v>
+        <v>50.85</v>
       </c>
       <c r="T33" s="3">
-        <v>17.35</v>
+        <v>16.16</v>
       </c>
       <c r="U33" s="3">
-        <v>29.39</v>
+        <v>24.38</v>
       </c>
       <c r="V33" s="3">
-        <v>42.16</v>
+        <v>34.62</v>
       </c>
       <c r="W33" s="3">
         <v>0</v>
@@ -2951,67 +2951,67 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C34" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D34" s="1">
-        <v>11288.05</v>
+        <v>11059.15</v>
       </c>
       <c r="E34" s="2">
-        <v>0.78</v>
+        <v>1.05</v>
       </c>
       <c r="F34" s="2">
-        <v>0.07</v>
+        <v>3.1</v>
       </c>
       <c r="G34" s="2">
-        <v>1.28</v>
+        <v>-0.12</v>
       </c>
       <c r="H34" s="2">
-        <v>-14.97</v>
+        <v>-10.01</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>12131.14</v>
+        <v>11462.41</v>
       </c>
       <c r="K34" s="1">
-        <v>11293.38</v>
+        <v>10923.16</v>
       </c>
       <c r="L34" s="1">
-        <v>11481.81</v>
+        <v>11354.54</v>
       </c>
       <c r="M34" s="3">
-        <v>-41.62</v>
+        <v>-117.6</v>
       </c>
       <c r="N34" s="3">
-        <v>-57.41</v>
+        <v>-157.29</v>
       </c>
       <c r="O34" s="3">
-        <v>-266.71</v>
+        <v>-165.32</v>
       </c>
       <c r="P34" s="3">
-        <v>-242.43</v>
+        <v>-67.6</v>
       </c>
       <c r="Q34" s="3">
-        <v>-133.04</v>
+        <v>235.17</v>
       </c>
       <c r="R34" s="3">
-        <v>113.83</v>
+        <v>397.7</v>
       </c>
       <c r="S34" s="3">
-        <v>47.45</v>
+        <v>50.1</v>
       </c>
       <c r="T34" s="3">
-        <v>15.19</v>
+        <v>19.05</v>
       </c>
       <c r="U34" s="3">
-        <v>26.76</v>
+        <v>26.73</v>
       </c>
       <c r="V34" s="3">
-        <v>29.18</v>
+        <v>43.98</v>
       </c>
       <c r="W34" s="3">
         <v>0</v>
@@ -3028,67 +3028,67 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D35" s="1">
-        <v>13136.65</v>
+        <v>8986.45</v>
       </c>
       <c r="E35" s="2">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
       <c r="F35" s="2">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="G35" s="2">
-        <v>-0.25</v>
+        <v>-3.48</v>
       </c>
       <c r="H35" s="2">
-        <v>-9.61</v>
+        <v>-5.56</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>13753.64</v>
+        <v>9742.62</v>
       </c>
       <c r="K35" s="1">
-        <v>13085.22</v>
+        <v>8964.15</v>
       </c>
       <c r="L35" s="1">
-        <v>13518.65</v>
+        <v>9402.81</v>
       </c>
       <c r="M35" s="3">
-        <v>-123.17</v>
+        <v>-137.54</v>
       </c>
       <c r="N35" s="3">
-        <v>-144.3</v>
+        <v>-156.44</v>
       </c>
       <c r="O35" s="3">
-        <v>-193.06</v>
+        <v>-209.22</v>
       </c>
       <c r="P35" s="3">
-        <v>-95.59</v>
+        <v>-96.92</v>
       </c>
       <c r="Q35" s="3">
-        <v>274.89</v>
+        <v>392.52</v>
       </c>
       <c r="R35" s="3">
-        <v>465.37</v>
+        <v>508.87</v>
       </c>
       <c r="S35" s="3">
-        <v>46.1</v>
+        <v>43.23</v>
       </c>
       <c r="T35" s="3">
-        <v>13.75</v>
+        <v>15.21</v>
       </c>
       <c r="U35" s="3">
-        <v>28.98</v>
+        <v>28.84</v>
       </c>
       <c r="V35" s="3">
-        <v>45.95</v>
+        <v>40.78</v>
       </c>
       <c r="W35" s="3">
         <v>0</v>
@@ -3105,67 +3105,67 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D36" s="1">
-        <v>26396.8</v>
+        <v>31041.95</v>
       </c>
       <c r="E36" s="2">
-        <v>0.73</v>
+        <v>1.03</v>
       </c>
       <c r="F36" s="2">
-        <v>0.77</v>
+        <v>2.22</v>
       </c>
       <c r="G36" s="2">
-        <v>-0.6</v>
+        <v>0.44</v>
       </c>
       <c r="H36" s="2">
-        <v>-12.53</v>
+        <v>-6.87</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>28442.01</v>
+        <v>32280.53</v>
       </c>
       <c r="K36" s="1">
-        <v>26448.61</v>
+        <v>30773.49</v>
       </c>
       <c r="L36" s="1">
-        <v>27360.7</v>
+        <v>31711.22</v>
       </c>
       <c r="M36" s="3">
-        <v>-296.93</v>
+        <v>-247.86</v>
       </c>
       <c r="N36" s="3">
-        <v>-284.69</v>
+        <v>-332.8</v>
       </c>
       <c r="O36" s="3">
-        <v>-550.45</v>
+        <v>-420.64</v>
       </c>
       <c r="P36" s="3">
-        <v>-351</v>
+        <v>-178.84</v>
       </c>
       <c r="Q36" s="3">
-        <v>1298</v>
+        <v>1861.41</v>
       </c>
       <c r="R36" s="3">
-        <v>1897.51</v>
+        <v>2379.77</v>
       </c>
       <c r="S36" s="3">
-        <v>42.02</v>
+        <v>49.76</v>
       </c>
       <c r="T36" s="3">
-        <v>13.02</v>
+        <v>16.02</v>
       </c>
       <c r="U36" s="3">
-        <v>27.21</v>
+        <v>26.08</v>
       </c>
       <c r="V36" s="3">
-        <v>32.04</v>
+        <v>42.73</v>
       </c>
       <c r="W36" s="3">
         <v>0</v>
@@ -3182,67 +3182,67 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C37" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D37" s="1">
-        <v>67787.05</v>
+        <v>5398.45</v>
       </c>
       <c r="E37" s="2">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="F37" s="2">
-        <v>2.98</v>
+        <v>1.82</v>
       </c>
       <c r="G37" s="2">
-        <v>-2.81</v>
+        <v>1.47</v>
       </c>
       <c r="H37" s="2">
-        <v>-2.27</v>
+        <v>-7.88</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>69957.77</v>
+        <v>5535.28</v>
       </c>
       <c r="K37" s="1">
-        <v>67625.45</v>
+        <v>5365.23</v>
       </c>
       <c r="L37" s="1">
-        <v>70900.59</v>
+        <v>5478.52</v>
       </c>
       <c r="M37" s="3">
-        <v>-1054.14</v>
+        <v>-22.62</v>
       </c>
       <c r="N37" s="3">
-        <v>-1093.47</v>
+        <v>-34.62</v>
       </c>
       <c r="O37" s="3">
-        <v>-511.47</v>
+        <v>-50.99</v>
       </c>
       <c r="P37" s="3">
-        <v>337.39</v>
+        <v>-25</v>
       </c>
       <c r="Q37" s="3">
-        <v>2674.44</v>
+        <v>190.16</v>
       </c>
       <c r="R37" s="3">
-        <v>3184.51</v>
+        <v>261.7</v>
       </c>
       <c r="S37" s="3">
-        <v>42.63</v>
+        <v>50.77</v>
       </c>
       <c r="T37" s="3">
-        <v>15.79</v>
+        <v>19.03</v>
       </c>
       <c r="U37" s="3">
-        <v>33.85</v>
+        <v>27.33</v>
       </c>
       <c r="V37" s="3">
-        <v>47.52</v>
+        <v>36.22</v>
       </c>
       <c r="W37" s="3">
         <v>0</v>
@@ -3259,67 +3259,67 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTY500</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTY500</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D38" s="1">
-        <v>21880.5</v>
+        <v>35299</v>
       </c>
       <c r="E38" s="2">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="F38" s="2">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="G38" s="2">
-        <v>-0.87</v>
+        <v>-3.65</v>
       </c>
       <c r="H38" s="2">
-        <v>-8.34</v>
+        <v>-0.08</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>22786.41</v>
+        <v>37706.65</v>
       </c>
       <c r="K38" s="1">
-        <v>21813.5</v>
+        <v>35378.63</v>
       </c>
       <c r="L38" s="1">
-        <v>22594.86</v>
+        <v>37046.09</v>
       </c>
       <c r="M38" s="3">
-        <v>-234.77</v>
+        <v>-597.25</v>
       </c>
       <c r="N38" s="3">
-        <v>-258.82</v>
+        <v>-575.74</v>
       </c>
       <c r="O38" s="3">
-        <v>-271</v>
+        <v>-682.54</v>
       </c>
       <c r="P38" s="3">
-        <v>-90.62</v>
+        <v>-206.54</v>
       </c>
       <c r="Q38" s="3">
-        <v>520.88</v>
+        <v>952.02</v>
       </c>
       <c r="R38" s="3">
-        <v>806.12</v>
+        <v>1231.73</v>
       </c>
       <c r="S38" s="3">
-        <v>44.69</v>
+        <v>39.95</v>
       </c>
       <c r="T38" s="3">
-        <v>14.42</v>
+        <v>14.33</v>
       </c>
       <c r="U38" s="3">
-        <v>30.47</v>
+        <v>34.57</v>
       </c>
       <c r="V38" s="3">
-        <v>46.95</v>
+        <v>37.53</v>
       </c>
       <c r="W38" s="3">
         <v>0</v>
@@ -3336,67 +3336,67 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>Nifty Total Market</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C39" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D39" s="1">
-        <v>12363.85</v>
+        <v>57841.65</v>
       </c>
       <c r="E39" s="2">
-        <v>0.69</v>
+        <v>0.99</v>
       </c>
       <c r="F39" s="2">
-        <v>2.14</v>
+        <v>3.66</v>
       </c>
       <c r="G39" s="2">
-        <v>-1.13</v>
+        <v>-2.51</v>
       </c>
       <c r="H39" s="2">
-        <v>-7.69</v>
+        <v>-4.37</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>12832.78</v>
+        <v>60215.62</v>
       </c>
       <c r="K39" s="1">
-        <v>12331.46</v>
+        <v>57608.06</v>
       </c>
       <c r="L39" s="1">
-        <v>12780.61</v>
+        <v>60874.11</v>
       </c>
       <c r="M39" s="3">
-        <v>-137.54</v>
+        <v>-1065.2</v>
       </c>
       <c r="N39" s="3">
-        <v>-148.07</v>
+        <v>-1075.05</v>
       </c>
       <c r="O39" s="3">
-        <v>-134.19</v>
+        <v>-593.59</v>
       </c>
       <c r="P39" s="3">
-        <v>-28.92</v>
+        <v>198.27</v>
       </c>
       <c r="Q39" s="3">
-        <v>631.85</v>
+        <v>2890.81</v>
       </c>
       <c r="R39" s="3">
-        <v>826.45</v>
+        <v>3484.08</v>
       </c>
       <c r="S39" s="3">
-        <v>44.15</v>
+        <v>42.34</v>
       </c>
       <c r="T39" s="3">
-        <v>14.59</v>
+        <v>15.66</v>
       </c>
       <c r="U39" s="3">
-        <v>31.24</v>
+        <v>36.53</v>
       </c>
       <c r="V39" s="3">
-        <v>46.54</v>
+        <v>51.02</v>
       </c>
       <c r="W39" s="3">
         <v>0</v>
@@ -3413,67 +3413,67 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>CNXREALTY</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C40" t="str">
-        <v>CNXREALTY</v>
+        <v>CNXIT</v>
       </c>
       <c r="D40" s="1">
-        <v>803.3</v>
+        <v>31866.4</v>
       </c>
       <c r="E40" s="2">
-        <v>0.68</v>
+        <v>0.99</v>
       </c>
       <c r="F40" s="2">
-        <v>2.42</v>
+        <v>-0.4</v>
       </c>
       <c r="G40" s="2">
-        <v>-5.2</v>
+        <v>15.02</v>
       </c>
       <c r="H40" s="2">
-        <v>-8.5</v>
+        <v>-15.88</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>819.66</v>
+        <v>30693.27</v>
       </c>
       <c r="K40" s="1">
-        <v>805.06</v>
+        <v>31496.67</v>
       </c>
       <c r="L40" s="1">
-        <v>853.73</v>
+        <v>29898.16</v>
       </c>
       <c r="M40" s="3">
-        <v>-15.22</v>
+        <v>812.93</v>
       </c>
       <c r="N40" s="3">
-        <v>-15.55</v>
+        <v>604.78</v>
       </c>
       <c r="O40" s="3">
-        <v>-4.54</v>
+        <v>3.2</v>
       </c>
       <c r="P40" s="3">
-        <v>7.27</v>
+        <v>-415</v>
       </c>
       <c r="Q40" s="3">
-        <v>1.53</v>
+        <v>-1671.31</v>
       </c>
       <c r="R40" s="3">
-        <v>9.88</v>
+        <v>-1149.81</v>
       </c>
       <c r="S40" s="3">
-        <v>42.22</v>
+        <v>63.15</v>
       </c>
       <c r="T40" s="3">
-        <v>16.01</v>
+        <v>26.04</v>
       </c>
       <c r="U40" s="3">
-        <v>29.84</v>
+        <v>14.94</v>
       </c>
       <c r="V40" s="3">
-        <v>28.71</v>
+        <v>30.29</v>
       </c>
       <c r="W40" s="3">
         <v>0</v>
@@ -3490,67 +3490,67 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY500</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY500</v>
       </c>
       <c r="D41" s="1">
-        <v>15495.95</v>
+        <v>21941.5</v>
       </c>
       <c r="E41" s="2">
-        <v>0.65</v>
+        <v>0.99</v>
       </c>
       <c r="F41" s="2">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G41" s="2">
-        <v>-1.62</v>
+        <v>-0.59</v>
       </c>
       <c r="H41" s="2">
-        <v>-6</v>
+        <v>-8.09</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>15989.37</v>
+        <v>22786.71</v>
       </c>
       <c r="K41" s="1">
-        <v>15461.81</v>
+        <v>21824.59</v>
       </c>
       <c r="L41" s="1">
-        <v>16079.19</v>
+        <v>22596.08</v>
       </c>
       <c r="M41" s="3">
-        <v>-196.26</v>
+        <v>-229.9</v>
       </c>
       <c r="N41" s="3">
-        <v>-203.09</v>
+        <v>-257.85</v>
       </c>
       <c r="O41" s="3">
-        <v>-132.03</v>
+        <v>-266.13</v>
       </c>
       <c r="P41" s="3">
-        <v>18.48</v>
+        <v>-89.65</v>
       </c>
       <c r="Q41" s="3">
-        <v>920.73</v>
+        <v>525.75</v>
       </c>
       <c r="R41" s="3">
-        <v>1148.83</v>
+        <v>807.09</v>
       </c>
       <c r="S41" s="3">
-        <v>43.09</v>
+        <v>46.21</v>
       </c>
       <c r="T41" s="3">
-        <v>15.1</v>
+        <v>15.68</v>
       </c>
       <c r="U41" s="3">
-        <v>33.89</v>
+        <v>30.03</v>
       </c>
       <c r="V41" s="3">
-        <v>47.43</v>
+        <v>46.64</v>
       </c>
       <c r="W41" s="3">
         <v>0</v>
@@ -3567,67 +3567,67 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D42" s="1">
-        <v>24778.7</v>
+        <v>11311.05</v>
       </c>
       <c r="E42" s="2">
-        <v>0.64</v>
+        <v>0.99</v>
       </c>
       <c r="F42" s="2">
-        <v>4.7</v>
+        <v>0.27</v>
       </c>
       <c r="G42" s="2">
-        <v>-2.42</v>
+        <v>1.49</v>
       </c>
       <c r="H42" s="2">
-        <v>-0.83</v>
+        <v>-14.8</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>25448.5</v>
+        <v>12131.25</v>
       </c>
       <c r="K42" s="1">
-        <v>24636</v>
+        <v>11297.56</v>
       </c>
       <c r="L42" s="1">
-        <v>25917.22</v>
+        <v>11482.27</v>
       </c>
       <c r="M42" s="3">
-        <v>-421.63</v>
+        <v>-39.79</v>
       </c>
       <c r="N42" s="3">
-        <v>-423.09</v>
+        <v>-57.04</v>
       </c>
       <c r="O42" s="3">
-        <v>-165.67</v>
+        <v>-264.87</v>
       </c>
       <c r="P42" s="3">
-        <v>130.65</v>
+        <v>-242.06</v>
       </c>
       <c r="Q42" s="3">
-        <v>90.53</v>
+        <v>-131.2</v>
       </c>
       <c r="R42" s="3">
-        <v>-50.34</v>
+        <v>114.2</v>
       </c>
       <c r="S42" s="3">
-        <v>44.65</v>
+        <v>48.51</v>
       </c>
       <c r="T42" s="3">
-        <v>16.17</v>
+        <v>16.24</v>
       </c>
       <c r="U42" s="3">
-        <v>35.42</v>
+        <v>26.43</v>
       </c>
       <c r="V42" s="3">
-        <v>42.27</v>
+        <v>28.91</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3644,67 +3644,67 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C43" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D43" s="1">
-        <v>1647.95</v>
+        <v>15588.6</v>
       </c>
       <c r="E43" s="2">
-        <v>0.64</v>
+        <v>0.97</v>
       </c>
       <c r="F43" s="2">
-        <v>5.41</v>
+        <v>2.49</v>
       </c>
       <c r="G43" s="2">
-        <v>4.09</v>
+        <v>-1.07</v>
       </c>
       <c r="H43" s="2">
-        <v>14.07</v>
+        <v>-7.51</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>1472.6</v>
+        <v>16256.43</v>
       </c>
       <c r="K43" s="1">
-        <v>1612.16</v>
+        <v>15516.57</v>
       </c>
       <c r="L43" s="1">
-        <v>1576.71</v>
+        <v>16152.58</v>
       </c>
       <c r="M43" s="3">
-        <v>15.36</v>
+        <v>-193.73</v>
       </c>
       <c r="N43" s="3">
-        <v>13.22</v>
+        <v>-211.73</v>
       </c>
       <c r="O43" s="3">
-        <v>35.35</v>
+        <v>-194.8</v>
       </c>
       <c r="P43" s="3">
-        <v>32.12</v>
+        <v>-44.46</v>
       </c>
       <c r="Q43" s="3">
-        <v>-68.22</v>
+        <v>922.12</v>
       </c>
       <c r="R43" s="3">
-        <v>-104.54</v>
+        <v>1179.91</v>
       </c>
       <c r="S43" s="3">
-        <v>59.68</v>
+        <v>44.66</v>
       </c>
       <c r="T43" s="3">
-        <v>27.7</v>
+        <v>14.79</v>
       </c>
       <c r="U43" s="3">
-        <v>22.74</v>
+        <v>31.32</v>
       </c>
       <c r="V43" s="3">
-        <v>15.68</v>
+        <v>49.21</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3721,67 +3721,67 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D44" s="1">
-        <v>15536.65</v>
+        <v>12398</v>
       </c>
       <c r="E44" s="2">
-        <v>0.63</v>
+        <v>0.97</v>
       </c>
       <c r="F44" s="2">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="G44" s="2">
-        <v>-1.4</v>
+        <v>-0.86</v>
       </c>
       <c r="H44" s="2">
-        <v>-7.82</v>
+        <v>-7.44</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>16256.17</v>
+        <v>12832.95</v>
       </c>
       <c r="K44" s="1">
-        <v>15507.13</v>
+        <v>12337.67</v>
       </c>
       <c r="L44" s="1">
-        <v>16151.54</v>
+        <v>12781.29</v>
       </c>
       <c r="M44" s="3">
-        <v>-197.88</v>
+        <v>-134.82</v>
       </c>
       <c r="N44" s="3">
-        <v>-212.56</v>
+        <v>-147.53</v>
       </c>
       <c r="O44" s="3">
-        <v>-198.94</v>
+        <v>-131.46</v>
       </c>
       <c r="P44" s="3">
-        <v>-45.29</v>
+        <v>-28.38</v>
       </c>
       <c r="Q44" s="3">
-        <v>917.98</v>
+        <v>634.57</v>
       </c>
       <c r="R44" s="3">
-        <v>1179.09</v>
+        <v>826.99</v>
       </c>
       <c r="S44" s="3">
-        <v>42.79</v>
+        <v>45.68</v>
       </c>
       <c r="T44" s="3">
-        <v>13.47</v>
+        <v>15.82</v>
       </c>
       <c r="U44" s="3">
-        <v>31.81</v>
+        <v>30.79</v>
       </c>
       <c r="V44" s="3">
-        <v>49.55</v>
+        <v>46.24</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3798,67 +3798,67 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C45" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D45" s="1">
-        <v>59507.25</v>
+        <v>9519.15</v>
       </c>
       <c r="E45" s="2">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="F45" s="2">
-        <v>4.74</v>
+        <v>6.66</v>
       </c>
       <c r="G45" s="2">
-        <v>-2.08</v>
+        <v>-1.18</v>
       </c>
       <c r="H45" s="2">
-        <v>-3.89</v>
+        <v>10.61</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>61628.01</v>
+        <v>8996.15</v>
       </c>
       <c r="K45" s="1">
-        <v>59100.36</v>
+        <v>9379.28</v>
       </c>
       <c r="L45" s="1">
-        <v>62021.6</v>
+        <v>9743.34</v>
       </c>
       <c r="M45" s="3">
-        <v>-973.04</v>
+        <v>-124.72</v>
       </c>
       <c r="N45" s="3">
-        <v>-994.88</v>
+        <v>-125.02</v>
       </c>
       <c r="O45" s="3">
-        <v>-613.08</v>
+        <v>155.15</v>
       </c>
       <c r="P45" s="3">
-        <v>28.31</v>
+        <v>262.12</v>
       </c>
       <c r="Q45" s="3">
-        <v>-33.68</v>
+        <v>749.72</v>
       </c>
       <c r="R45" s="3">
-        <v>-179.67</v>
+        <v>721.58</v>
       </c>
       <c r="S45" s="3">
-        <v>44.93</v>
+        <v>49.66</v>
       </c>
       <c r="T45" s="3">
-        <v>16.25</v>
+        <v>25.04</v>
       </c>
       <c r="U45" s="3">
-        <v>35.37</v>
+        <v>38.24</v>
       </c>
       <c r="V45" s="3">
-        <v>44.86</v>
+        <v>34.64</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3875,67 +3875,67 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D46" s="1">
-        <v>10996.35</v>
+        <v>206.19</v>
       </c>
       <c r="E46" s="2">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="F46" s="2">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="G46" s="2">
-        <v>4.33</v>
+        <v>4.78</v>
       </c>
       <c r="H46" s="2">
-        <v>-11.91</v>
+        <v>-17.24</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>11182.79</v>
+        <v>179.55</v>
       </c>
       <c r="K46" s="1">
-        <v>10894.66</v>
+        <v>203.08</v>
       </c>
       <c r="L46" s="1">
-        <v>11009.06</v>
+        <v>196.37</v>
       </c>
       <c r="M46" s="3">
-        <v>21.11</v>
+        <v>3.04</v>
       </c>
       <c r="N46" s="3">
-        <v>-35.25</v>
+        <v>2.81</v>
       </c>
       <c r="O46" s="3">
-        <v>-103.22</v>
+        <v>12.48</v>
       </c>
       <c r="P46" s="3">
-        <v>-81.47</v>
+        <v>7.05</v>
       </c>
       <c r="Q46" s="3">
-        <v>40</v>
+        <v>5.63</v>
       </c>
       <c r="R46" s="3">
-        <v>178.24</v>
+        <v>7.71</v>
       </c>
       <c r="S46" s="3">
-        <v>56.72</v>
+        <v>100</v>
       </c>
       <c r="T46" s="3">
-        <v>19.82</v>
+        <v>99.72</v>
       </c>
       <c r="U46" s="3">
-        <v>20.38</v>
+        <v>0.28</v>
       </c>
       <c r="V46" s="3">
-        <v>25.77</v>
+        <v>97.59</v>
       </c>
       <c r="W46" s="3">
         <v>0</v>
@@ -3952,67 +3952,67 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C47" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D47" s="1">
-        <v>5375.05</v>
+        <v>26454.65</v>
       </c>
       <c r="E47" s="2">
-        <v>0.59</v>
+        <v>0.95</v>
       </c>
       <c r="F47" s="2">
-        <v>1.37</v>
+        <v>0.99</v>
       </c>
       <c r="G47" s="2">
-        <v>1.03</v>
+        <v>-0.38</v>
       </c>
       <c r="H47" s="2">
-        <v>-8.28</v>
+        <v>-12.34</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>5535.16</v>
+        <v>28442.3</v>
       </c>
       <c r="K47" s="1">
-        <v>5360.97</v>
+        <v>26459.13</v>
       </c>
       <c r="L47" s="1">
-        <v>5478.05</v>
+        <v>27361.86</v>
       </c>
       <c r="M47" s="3">
-        <v>-24.49</v>
+        <v>-292.31</v>
       </c>
       <c r="N47" s="3">
-        <v>-35</v>
+        <v>-283.77</v>
       </c>
       <c r="O47" s="3">
-        <v>-52.85</v>
+        <v>-545.83</v>
       </c>
       <c r="P47" s="3">
-        <v>-25.37</v>
+        <v>-350.08</v>
       </c>
       <c r="Q47" s="3">
-        <v>188.29</v>
+        <v>1302.61</v>
       </c>
       <c r="R47" s="3">
-        <v>261.32</v>
+        <v>1898.43</v>
       </c>
       <c r="S47" s="3">
-        <v>48.71</v>
+        <v>43.19</v>
       </c>
       <c r="T47" s="3">
-        <v>17.24</v>
+        <v>14.21</v>
       </c>
       <c r="U47" s="3">
-        <v>27.94</v>
+        <v>26.83</v>
       </c>
       <c r="V47" s="3">
-        <v>36.64</v>
+        <v>31.72</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4029,67 +4029,67 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D48" s="1">
-        <v>49026.45</v>
+        <v>18811.35</v>
       </c>
       <c r="E48" s="2">
-        <v>0.56</v>
+        <v>0.95</v>
       </c>
       <c r="F48" s="2">
-        <v>4.78</v>
+        <v>6.04</v>
       </c>
       <c r="G48" s="2">
-        <v>-1.11</v>
+        <v>-2.26</v>
       </c>
       <c r="H48" s="2">
-        <v>3.07</v>
+        <v>6.2</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>49088.77</v>
+        <v>18201.08</v>
       </c>
       <c r="K48" s="1">
-        <v>48621.89</v>
+        <v>18621.56</v>
       </c>
       <c r="L48" s="1">
-        <v>50468.98</v>
+        <v>19472.76</v>
       </c>
       <c r="M48" s="3">
-        <v>-601.82</v>
+        <v>-303.71</v>
       </c>
       <c r="N48" s="3">
-        <v>-623.06</v>
+        <v>-284.02</v>
       </c>
       <c r="O48" s="3">
-        <v>-72.27</v>
+        <v>199.4</v>
       </c>
       <c r="P48" s="3">
-        <v>414.56</v>
+        <v>421.53</v>
       </c>
       <c r="Q48" s="3">
-        <v>120.22</v>
+        <v>882.85</v>
       </c>
       <c r="R48" s="3">
-        <v>-287.12</v>
+        <v>860.74</v>
       </c>
       <c r="S48" s="3">
-        <v>47.36</v>
+        <v>46.8</v>
       </c>
       <c r="T48" s="3">
-        <v>18.76</v>
+        <v>23.65</v>
       </c>
       <c r="U48" s="3">
-        <v>34.97</v>
+        <v>40.28</v>
       </c>
       <c r="V48" s="3">
-        <v>43.99</v>
+        <v>36.68</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -4106,67 +4106,67 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D49" s="1">
-        <v>46517.9</v>
+        <v>16656.4</v>
       </c>
       <c r="E49" s="2">
-        <v>0.52</v>
+        <v>0.94</v>
       </c>
       <c r="F49" s="2">
-        <v>4.6</v>
+        <v>3.67</v>
       </c>
       <c r="G49" s="2">
-        <v>-2.8</v>
+        <v>-2.19</v>
       </c>
       <c r="H49" s="2">
-        <v>5.76</v>
+        <v>-3.46</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>44963.55</v>
+        <v>17199.36</v>
       </c>
       <c r="K49" s="1">
-        <v>46321.62</v>
+        <v>16560.61</v>
       </c>
       <c r="L49" s="1">
-        <v>48073.08</v>
+        <v>17485.91</v>
       </c>
       <c r="M49" s="3">
-        <v>-639.14</v>
+        <v>-292.78</v>
       </c>
       <c r="N49" s="3">
-        <v>-559.17</v>
+        <v>-309.06</v>
       </c>
       <c r="O49" s="3">
-        <v>540.78</v>
+        <v>-131.6</v>
       </c>
       <c r="P49" s="3">
-        <v>989.55</v>
+        <v>96.58</v>
       </c>
       <c r="Q49" s="3">
-        <v>-290.14</v>
+        <v>907.05</v>
       </c>
       <c r="R49" s="3">
-        <v>-1009.87</v>
+        <v>1049.65</v>
       </c>
       <c r="S49" s="3">
-        <v>45.29</v>
+        <v>43.36</v>
       </c>
       <c r="T49" s="3">
-        <v>21.52</v>
+        <v>15.91</v>
       </c>
       <c r="U49" s="3">
-        <v>38.77</v>
+        <v>33.59</v>
       </c>
       <c r="V49" s="3">
-        <v>34.24</v>
+        <v>48.33</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -4183,67 +4183,67 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C50" t="str">
-        <v>CNXIT</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D50" s="1">
-        <v>31718.5</v>
+        <v>49209.75</v>
       </c>
       <c r="E50" s="2">
-        <v>0.52</v>
+        <v>0.93</v>
       </c>
       <c r="F50" s="2">
-        <v>-0.87</v>
+        <v>5.18</v>
       </c>
       <c r="G50" s="2">
-        <v>14.49</v>
+        <v>-0.74</v>
       </c>
       <c r="H50" s="2">
-        <v>-16.27</v>
+        <v>3.46</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>30692.53</v>
+        <v>49089.69</v>
       </c>
       <c r="K50" s="1">
-        <v>31469.78</v>
+        <v>48655.22</v>
       </c>
       <c r="L50" s="1">
-        <v>29895.2</v>
+        <v>50472.65</v>
       </c>
       <c r="M50" s="3">
-        <v>801.13</v>
+        <v>-587.19</v>
       </c>
       <c r="N50" s="3">
-        <v>602.42</v>
+        <v>-620.13</v>
       </c>
       <c r="O50" s="3">
-        <v>-8.6</v>
+        <v>-57.65</v>
       </c>
       <c r="P50" s="3">
-        <v>-417.36</v>
+        <v>417.49</v>
       </c>
       <c r="Q50" s="3">
-        <v>-1683.11</v>
+        <v>134.84</v>
       </c>
       <c r="R50" s="3">
-        <v>-1152.17</v>
+        <v>-284.19</v>
       </c>
       <c r="S50" s="3">
-        <v>62.17</v>
+        <v>48.81</v>
       </c>
       <c r="T50" s="3">
-        <v>26.04</v>
+        <v>19.64</v>
       </c>
       <c r="U50" s="3">
-        <v>14.94</v>
+        <v>34.59</v>
       </c>
       <c r="V50" s="3">
-        <v>30.29</v>
+        <v>43.81</v>
       </c>
       <c r="W50" s="3">
         <v>0</v>
@@ -4260,67 +4260,67 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C51" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D51" s="1">
-        <v>57567.75</v>
+        <v>15538.1</v>
       </c>
       <c r="E51" s="2">
-        <v>0.51</v>
+        <v>0.92</v>
       </c>
       <c r="F51" s="2">
-        <v>3.17</v>
+        <v>2.78</v>
       </c>
       <c r="G51" s="2">
-        <v>-2.97</v>
+        <v>-1.35</v>
       </c>
       <c r="H51" s="2">
-        <v>-4.82</v>
+        <v>-5.74</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>60214.25</v>
+        <v>15989.59</v>
       </c>
       <c r="K51" s="1">
-        <v>57558.26</v>
+        <v>15469.47</v>
       </c>
       <c r="L51" s="1">
-        <v>60868.63</v>
+        <v>16080.03</v>
       </c>
       <c r="M51" s="3">
-        <v>-1087.05</v>
+        <v>-192.9</v>
       </c>
       <c r="N51" s="3">
-        <v>-1079.42</v>
+        <v>-202.42</v>
       </c>
       <c r="O51" s="3">
-        <v>-615.44</v>
+        <v>-128.67</v>
       </c>
       <c r="P51" s="3">
-        <v>193.9</v>
+        <v>19.16</v>
       </c>
       <c r="Q51" s="3">
-        <v>2868.96</v>
+        <v>924.1</v>
       </c>
       <c r="R51" s="3">
-        <v>3479.71</v>
+        <v>1149.5</v>
       </c>
       <c r="S51" s="3">
-        <v>40.12</v>
+        <v>44.57</v>
       </c>
       <c r="T51" s="3">
-        <v>14.28</v>
+        <v>16.24</v>
       </c>
       <c r="U51" s="3">
-        <v>37.13</v>
+        <v>33.43</v>
       </c>
       <c r="V51" s="3">
-        <v>51.34</v>
+        <v>47.17</v>
       </c>
       <c r="W51" s="3">
         <v>0</v>
@@ -4337,67 +4337,67 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D52" s="1">
-        <v>17073.75</v>
+        <v>28723.25</v>
       </c>
       <c r="E52" s="2">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="F52" s="2">
-        <v>4.2</v>
+        <v>5.21</v>
       </c>
       <c r="G52" s="2">
-        <v>-4.07</v>
+        <v>-2.7</v>
       </c>
       <c r="H52" s="2">
-        <v>2.33</v>
+        <v>-7.78</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>16951.42</v>
+        <v>30301.56</v>
       </c>
       <c r="K52" s="1">
-        <v>17072.24</v>
+        <v>28493.92</v>
       </c>
       <c r="L52" s="1">
-        <v>17928.35</v>
+        <v>29963.77</v>
       </c>
       <c r="M52" s="3">
-        <v>-314.68</v>
+        <v>-496.6</v>
       </c>
       <c r="N52" s="3">
-        <v>-276.94</v>
+        <v>-504.91</v>
       </c>
       <c r="O52" s="3">
-        <v>95.02</v>
+        <v>-471.68</v>
       </c>
       <c r="P52" s="3">
-        <v>317.18</v>
+        <v>-178.05</v>
       </c>
       <c r="Q52" s="3">
-        <v>1310.4</v>
+        <v>1474.95</v>
       </c>
       <c r="R52" s="3">
-        <v>1429.32</v>
+        <v>2004.71</v>
       </c>
       <c r="S52" s="3">
-        <v>41.33</v>
+        <v>45.36</v>
       </c>
       <c r="T52" s="3">
-        <v>18.67</v>
+        <v>16.37</v>
       </c>
       <c r="U52" s="3">
-        <v>41.88</v>
+        <v>34.93</v>
       </c>
       <c r="V52" s="3">
-        <v>40.53</v>
+        <v>42.61</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4420,61 +4420,61 @@
         <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D53" s="1">
-        <v>13750.3</v>
+        <v>13802.6</v>
       </c>
       <c r="E53" s="2">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="F53" s="2">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="G53" s="2">
-        <v>2.98</v>
+        <v>3.37</v>
       </c>
       <c r="H53" s="2">
-        <v>-10.09</v>
+        <v>-9.74</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>14350.26</v>
+        <v>14350.52</v>
       </c>
       <c r="K53" s="1">
-        <v>13687.31</v>
+        <v>13696.82</v>
       </c>
       <c r="L53" s="1">
-        <v>13928.29</v>
+        <v>13929.34</v>
       </c>
       <c r="M53" s="3">
-        <v>-32.74</v>
+        <v>-28.57</v>
       </c>
       <c r="N53" s="3">
-        <v>-73.95</v>
+        <v>-73.11</v>
       </c>
       <c r="O53" s="3">
-        <v>-221.7</v>
+        <v>-217.53</v>
       </c>
       <c r="P53" s="3">
-        <v>-174.74</v>
+        <v>-173.91</v>
       </c>
       <c r="Q53" s="3">
-        <v>-535.8</v>
+        <v>-531.62</v>
       </c>
       <c r="R53" s="3">
-        <v>-491.7</v>
+        <v>-490.87</v>
       </c>
       <c r="S53" s="3">
-        <v>51.14</v>
+        <v>52.79</v>
       </c>
       <c r="T53" s="3">
-        <v>18.48</v>
+        <v>19.77</v>
       </c>
       <c r="U53" s="3">
-        <v>24.07</v>
+        <v>23.7</v>
       </c>
       <c r="V53" s="3">
-        <v>23.11</v>
+        <v>22.82</v>
       </c>
       <c r="W53" s="3">
         <v>0</v>
@@ -4491,67 +4491,67 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C54" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D54" s="1">
-        <v>16578.45</v>
+        <v>11026.55</v>
       </c>
       <c r="E54" s="2">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="F54" s="2">
-        <v>3.19</v>
+        <v>1.26</v>
       </c>
       <c r="G54" s="2">
-        <v>-2.64</v>
+        <v>4.62</v>
       </c>
       <c r="H54" s="2">
-        <v>-3.92</v>
+        <v>-11.67</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>17198.97</v>
+        <v>11182.94</v>
       </c>
       <c r="K54" s="1">
-        <v>16546.44</v>
+        <v>10900.15</v>
       </c>
       <c r="L54" s="1">
-        <v>17484.35</v>
+        <v>11009.67</v>
       </c>
       <c r="M54" s="3">
-        <v>-299</v>
+        <v>23.52</v>
       </c>
       <c r="N54" s="3">
-        <v>-310.31</v>
+        <v>-34.77</v>
       </c>
       <c r="O54" s="3">
-        <v>-137.82</v>
+        <v>-100.81</v>
       </c>
       <c r="P54" s="3">
-        <v>95.33</v>
+        <v>-80.99</v>
       </c>
       <c r="Q54" s="3">
-        <v>900.83</v>
+        <v>42.41</v>
       </c>
       <c r="R54" s="3">
-        <v>1048.41</v>
+        <v>178.72</v>
       </c>
       <c r="S54" s="3">
-        <v>41.14</v>
+        <v>57.86</v>
       </c>
       <c r="T54" s="3">
-        <v>14.59</v>
+        <v>20.75</v>
       </c>
       <c r="U54" s="3">
-        <v>34.12</v>
+        <v>20.15</v>
       </c>
       <c r="V54" s="3">
-        <v>48.64</v>
+        <v>25.78</v>
       </c>
       <c r="W54" s="3">
         <v>0</v>
@@ -4568,67 +4568,67 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D55" s="1">
-        <v>51827.6</v>
+        <v>21245.3</v>
       </c>
       <c r="E55" s="2">
-        <v>0.46</v>
+        <v>0.86</v>
       </c>
       <c r="F55" s="2">
-        <v>5.62</v>
+        <v>3.17</v>
       </c>
       <c r="G55" s="2">
-        <v>-2.02</v>
+        <v>-2.85</v>
       </c>
       <c r="H55" s="2">
-        <v>-1.67</v>
+        <v>-4.63</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>52483.39</v>
+        <v>22147.19</v>
       </c>
       <c r="K55" s="1">
-        <v>51426.02</v>
+        <v>21197.83</v>
       </c>
       <c r="L55" s="1">
-        <v>53670.98</v>
+        <v>22378.54</v>
       </c>
       <c r="M55" s="3">
-        <v>-759.31</v>
+        <v>-387.27</v>
       </c>
       <c r="N55" s="3">
-        <v>-762.81</v>
+        <v>-388.8</v>
       </c>
       <c r="O55" s="3">
-        <v>-202.5</v>
+        <v>-213.09</v>
       </c>
       <c r="P55" s="3">
-        <v>289.93</v>
+        <v>75.99</v>
       </c>
       <c r="Q55" s="3">
-        <v>-689.94</v>
+        <v>1706.31</v>
       </c>
       <c r="R55" s="3">
-        <v>-1109.68</v>
+        <v>2027.88</v>
       </c>
       <c r="S55" s="3">
-        <v>46.54</v>
+        <v>40.98</v>
       </c>
       <c r="T55" s="3">
-        <v>16.71</v>
+        <v>15.05</v>
       </c>
       <c r="U55" s="3">
-        <v>37.63</v>
+        <v>37.14</v>
       </c>
       <c r="V55" s="3">
-        <v>42.62</v>
+        <v>50.88</v>
       </c>
       <c r="W55" s="3">
         <v>0</v>
@@ -4645,67 +4645,67 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C56" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D56" s="1">
-        <v>28602.95</v>
+        <v>18930.75</v>
       </c>
       <c r="E56" s="2">
-        <v>0.46</v>
+        <v>0.85</v>
       </c>
       <c r="F56" s="2">
-        <v>4.77</v>
+        <v>1.34</v>
       </c>
       <c r="G56" s="2">
-        <v>-3.1</v>
+        <v>-0.06</v>
       </c>
       <c r="H56" s="2">
-        <v>-8.17</v>
+        <v>-11.58</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>30300.95</v>
+        <v>20033.79</v>
       </c>
       <c r="K56" s="1">
-        <v>28472.05</v>
+        <v>18941.37</v>
       </c>
       <c r="L56" s="1">
-        <v>29961.36</v>
+        <v>19606.09</v>
       </c>
       <c r="M56" s="3">
-        <v>-506.19</v>
+        <v>-187.74</v>
       </c>
       <c r="N56" s="3">
-        <v>-506.83</v>
+        <v>-200.2</v>
       </c>
       <c r="O56" s="3">
-        <v>-481.27</v>
+        <v>-327.98</v>
       </c>
       <c r="P56" s="3">
-        <v>-179.97</v>
+        <v>-182.71</v>
       </c>
       <c r="Q56" s="3">
-        <v>1465.35</v>
+        <v>482.81</v>
       </c>
       <c r="R56" s="3">
-        <v>2002.79</v>
+        <v>794.61</v>
       </c>
       <c r="S56" s="3">
-        <v>43.78</v>
+        <v>43.81</v>
       </c>
       <c r="T56" s="3">
-        <v>15.36</v>
+        <v>14.74</v>
       </c>
       <c r="U56" s="3">
-        <v>35.36</v>
+        <v>32.03</v>
       </c>
       <c r="V56" s="3">
-        <v>42.84</v>
+        <v>41.94</v>
       </c>
       <c r="W56" s="3">
         <v>0</v>
@@ -4722,67 +4722,67 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C57" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D57" s="1">
-        <v>19692.25</v>
+        <v>51999.35</v>
       </c>
       <c r="E57" s="2">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="F57" s="2">
-        <v>3.25</v>
+        <v>5.97</v>
       </c>
       <c r="G57" s="2">
-        <v>-3.54</v>
+        <v>-1.69</v>
       </c>
       <c r="H57" s="2">
-        <v>-2.6</v>
+        <v>-1.34</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>20242.38</v>
+        <v>52484.25</v>
       </c>
       <c r="K57" s="1">
-        <v>19706.33</v>
+        <v>51457.25</v>
       </c>
       <c r="L57" s="1">
-        <v>20775.79</v>
+        <v>53674.42</v>
       </c>
       <c r="M57" s="3">
-        <v>-365.89</v>
+        <v>-745.61</v>
       </c>
       <c r="N57" s="3">
-        <v>-348.18</v>
+        <v>-760.07</v>
       </c>
       <c r="O57" s="3">
-        <v>-95.36</v>
+        <v>-188.8</v>
       </c>
       <c r="P57" s="3">
-        <v>172.71</v>
+        <v>292.67</v>
       </c>
       <c r="Q57" s="3">
-        <v>1572.16</v>
+        <v>-676.24</v>
       </c>
       <c r="R57" s="3">
-        <v>1822.17</v>
+        <v>-1106.94</v>
       </c>
       <c r="S57" s="3">
-        <v>39.75</v>
+        <v>47.67</v>
       </c>
       <c r="T57" s="3">
-        <v>15.67</v>
+        <v>17.65</v>
       </c>
       <c r="U57" s="3">
-        <v>41.04</v>
+        <v>37.2</v>
       </c>
       <c r="V57" s="3">
-        <v>49.83</v>
+        <v>42.42</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -4799,67 +4799,67 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D58" s="1">
-        <v>21157.45</v>
+        <v>19756.25</v>
       </c>
       <c r="E58" s="2">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="F58" s="2">
-        <v>2.74</v>
+        <v>3.59</v>
       </c>
       <c r="G58" s="2">
-        <v>-3.25</v>
+        <v>-3.23</v>
       </c>
       <c r="H58" s="2">
-        <v>-5.03</v>
+        <v>-2.28</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>22146.75</v>
+        <v>20242.7</v>
       </c>
       <c r="K58" s="1">
-        <v>21181.86</v>
+        <v>19717.97</v>
       </c>
       <c r="L58" s="1">
-        <v>22376.78</v>
+        <v>20777.07</v>
       </c>
       <c r="M58" s="3">
-        <v>-394.28</v>
+        <v>-360.79</v>
       </c>
       <c r="N58" s="3">
-        <v>-390.2</v>
+        <v>-347.16</v>
       </c>
       <c r="O58" s="3">
-        <v>-220.1</v>
+        <v>-90.26</v>
       </c>
       <c r="P58" s="3">
-        <v>74.58</v>
+        <v>173.73</v>
       </c>
       <c r="Q58" s="3">
-        <v>1699.3</v>
+        <v>1577.27</v>
       </c>
       <c r="R58" s="3">
-        <v>2026.47</v>
+        <v>1823.2</v>
       </c>
       <c r="S58" s="3">
-        <v>38.83</v>
+        <v>41.3</v>
       </c>
       <c r="T58" s="3">
-        <v>13.81</v>
+        <v>16.63</v>
       </c>
       <c r="U58" s="3">
-        <v>37.68</v>
+        <v>40.57</v>
       </c>
       <c r="V58" s="3">
-        <v>51.17</v>
+        <v>49.62</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -4876,67 +4876,67 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D59" s="1">
-        <v>24458</v>
+        <v>24908.25</v>
       </c>
       <c r="E59" s="2">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="F59" s="2">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="G59" s="2">
-        <v>-6.83</v>
+        <v>-1.23</v>
       </c>
       <c r="H59" s="2">
-        <v>8.48</v>
+        <v>-8.01</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>23655.26</v>
+        <v>26189.96</v>
       </c>
       <c r="K59" s="1">
-        <v>24641.88</v>
+        <v>24726.56</v>
       </c>
       <c r="L59" s="1">
-        <v>25924.64</v>
+        <v>25843.8</v>
       </c>
       <c r="M59" s="3">
-        <v>-506.99</v>
+        <v>-321.75</v>
       </c>
       <c r="N59" s="3">
-        <v>-393.48</v>
+        <v>-399.77</v>
       </c>
       <c r="O59" s="3">
-        <v>439.17</v>
+        <v>-395.61</v>
       </c>
       <c r="P59" s="3">
-        <v>766.35</v>
+        <v>-135.71</v>
       </c>
       <c r="Q59" s="3">
-        <v>2295.71</v>
+        <v>1172.98</v>
       </c>
       <c r="R59" s="3">
-        <v>2351.84</v>
+        <v>1601.32</v>
       </c>
       <c r="S59" s="3">
-        <v>37.48</v>
+        <v>45.37</v>
       </c>
       <c r="T59" s="3">
-        <v>14.4</v>
+        <v>14.95</v>
       </c>
       <c r="U59" s="3">
-        <v>39.19</v>
+        <v>26.06</v>
       </c>
       <c r="V59" s="3">
-        <v>38.05</v>
+        <v>48.95</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -4953,67 +4953,67 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D60" s="1">
-        <v>24823.2</v>
+        <v>13381.05</v>
       </c>
       <c r="E60" s="2">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="F60" s="2">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="G60" s="2">
-        <v>-1.57</v>
+        <v>-2.55</v>
       </c>
       <c r="H60" s="2">
-        <v>-8.32</v>
+        <v>-2.88</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>26189.53</v>
+        <v>13983.35</v>
       </c>
       <c r="K60" s="1">
-        <v>24711.1</v>
+        <v>13372.07</v>
       </c>
       <c r="L60" s="1">
-        <v>25842.1</v>
+        <v>14166.22</v>
       </c>
       <c r="M60" s="3">
-        <v>-328.53</v>
+        <v>-253.46</v>
       </c>
       <c r="N60" s="3">
-        <v>-401.13</v>
+        <v>-259.45</v>
       </c>
       <c r="O60" s="3">
-        <v>-402.4</v>
+        <v>-138.45</v>
       </c>
       <c r="P60" s="3">
-        <v>-137.06</v>
+        <v>70.04</v>
       </c>
       <c r="Q60" s="3">
-        <v>1166.19</v>
+        <v>872.54</v>
       </c>
       <c r="R60" s="3">
-        <v>1599.97</v>
+        <v>1001.19</v>
       </c>
       <c r="S60" s="3">
-        <v>43.19</v>
+        <v>40.01</v>
       </c>
       <c r="T60" s="3">
-        <v>13.36</v>
+        <v>13.01</v>
       </c>
       <c r="U60" s="3">
-        <v>26.55</v>
+        <v>33.26</v>
       </c>
       <c r="V60" s="3">
-        <v>49.37</v>
+        <v>46.77</v>
       </c>
       <c r="W60" s="3">
         <v>0</v>
@@ -5030,67 +5030,67 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D61" s="1">
-        <v>18844.75</v>
+        <v>51229.7</v>
       </c>
       <c r="E61" s="2">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="F61" s="2">
-        <v>0.88</v>
+        <v>7.51</v>
       </c>
       <c r="G61" s="2">
-        <v>-0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H61" s="2">
-        <v>-11.99</v>
+        <v>16.79</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>20033.36</v>
+        <v>47478.26</v>
       </c>
       <c r="K61" s="1">
-        <v>18925.73</v>
+        <v>49810.7</v>
       </c>
       <c r="L61" s="1">
-        <v>19604.37</v>
+        <v>51287.1</v>
       </c>
       <c r="M61" s="3">
-        <v>-194.6</v>
+        <v>-437.68</v>
       </c>
       <c r="N61" s="3">
-        <v>-201.58</v>
+        <v>-678.24</v>
       </c>
       <c r="O61" s="3">
-        <v>-334.84</v>
+        <v>886.66</v>
       </c>
       <c r="P61" s="3">
-        <v>-184.09</v>
+        <v>1418.1</v>
       </c>
       <c r="Q61" s="3">
-        <v>475.95</v>
+        <v>2386.43</v>
       </c>
       <c r="R61" s="3">
-        <v>793.23</v>
+        <v>1514.86</v>
       </c>
       <c r="S61" s="3">
-        <v>41.35</v>
+        <v>57.12</v>
       </c>
       <c r="T61" s="3">
-        <v>13.83</v>
+        <v>26.75</v>
       </c>
       <c r="U61" s="3">
-        <v>32.37</v>
+        <v>26.92</v>
       </c>
       <c r="V61" s="3">
-        <v>42.17</v>
+        <v>34.29</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -5107,67 +5107,67 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C62" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D62" s="1">
-        <v>11811.25</v>
+        <v>22372.15</v>
       </c>
       <c r="E62" s="2">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="F62" s="2">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="G62" s="2">
-        <v>-7.44</v>
+        <v>-1.73</v>
       </c>
       <c r="H62" s="2">
-        <v>5.76</v>
+        <v>-7.01</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>12490.85</v>
+        <v>23442.76</v>
       </c>
       <c r="K62" s="1">
-        <v>11859.33</v>
+        <v>22363.01</v>
       </c>
       <c r="L62" s="1">
-        <v>12702.09</v>
+        <v>23452.6</v>
       </c>
       <c r="M62" s="3">
-        <v>-281.79</v>
+        <v>-350.38</v>
       </c>
       <c r="N62" s="3">
-        <v>-284.1</v>
+        <v>-347.06</v>
       </c>
       <c r="O62" s="3">
-        <v>-68.91</v>
+        <v>-308.63</v>
       </c>
       <c r="P62" s="3">
-        <v>148.53</v>
+        <v>-45.09</v>
       </c>
       <c r="Q62" s="3">
-        <v>1133.95</v>
+        <v>1014.96</v>
       </c>
       <c r="R62" s="3">
-        <v>1129.48</v>
+        <v>1357.83</v>
       </c>
       <c r="S62" s="3">
-        <v>39.07</v>
+        <v>41.66</v>
       </c>
       <c r="T62" s="3">
-        <v>12.31</v>
+        <v>16.35</v>
       </c>
       <c r="U62" s="3">
-        <v>32.37</v>
+        <v>36.05</v>
       </c>
       <c r="V62" s="3">
-        <v>38.45</v>
+        <v>42.77</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -5184,67 +5184,67 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C63" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D63" s="1">
-        <v>10333.6</v>
+        <v>11848.45</v>
       </c>
       <c r="E63" s="2">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="F63" s="2">
-        <v>-0.45</v>
+        <v>3.23</v>
       </c>
       <c r="G63" s="2">
-        <v>-2.65</v>
+        <v>-7.15</v>
       </c>
       <c r="H63" s="2">
-        <v>-15.51</v>
+        <v>6.1</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>11255.99</v>
+        <v>12491.03</v>
       </c>
       <c r="K63" s="1">
-        <v>10439.52</v>
+        <v>11866.09</v>
       </c>
       <c r="L63" s="1">
-        <v>10805.23</v>
+        <v>12702.84</v>
       </c>
       <c r="M63" s="3">
-        <v>-111.86</v>
+        <v>-278.82</v>
       </c>
       <c r="N63" s="3">
-        <v>-118.66</v>
+        <v>-283.5</v>
       </c>
       <c r="O63" s="3">
-        <v>-248.09</v>
+        <v>-65.94</v>
       </c>
       <c r="P63" s="3">
-        <v>-178.65</v>
+        <v>149.12</v>
       </c>
       <c r="Q63" s="3">
-        <v>64.28</v>
+        <v>1136.92</v>
       </c>
       <c r="R63" s="3">
-        <v>277.65</v>
+        <v>1130.07</v>
       </c>
       <c r="S63" s="3">
-        <v>38.67</v>
+        <v>40.24</v>
       </c>
       <c r="T63" s="3">
-        <v>14.72</v>
+        <v>12.23</v>
       </c>
       <c r="U63" s="3">
-        <v>30.34</v>
+        <v>32.16</v>
       </c>
       <c r="V63" s="3">
-        <v>31.01</v>
+        <v>38.45</v>
       </c>
       <c r="W63" s="3">
         <v>0</v>
@@ -5261,67 +5261,67 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C64" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D64" s="1">
-        <v>8811.35</v>
+        <v>17101.1</v>
       </c>
       <c r="E64" s="2">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="F64" s="2">
-        <v>2.92</v>
+        <v>4.37</v>
       </c>
       <c r="G64" s="2">
-        <v>-5.02</v>
+        <v>-3.92</v>
       </c>
       <c r="H64" s="2">
-        <v>13.73</v>
+        <v>2.5</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>8861.13</v>
+        <v>16951.56</v>
       </c>
       <c r="K64" s="1">
-        <v>8869.16</v>
+        <v>17077.21</v>
       </c>
       <c r="L64" s="1">
-        <v>9375.76</v>
+        <v>17928.9</v>
       </c>
       <c r="M64" s="3">
-        <v>-170.81</v>
+        <v>-312.5</v>
       </c>
       <c r="N64" s="3">
-        <v>-151.69</v>
+        <v>-276.51</v>
       </c>
       <c r="O64" s="3">
-        <v>41.47</v>
+        <v>97.21</v>
       </c>
       <c r="P64" s="3">
-        <v>193.03</v>
+        <v>317.62</v>
       </c>
       <c r="Q64" s="3">
-        <v>603.03</v>
+        <v>1312.58</v>
       </c>
       <c r="R64" s="3">
-        <v>522.71</v>
+        <v>1429.76</v>
       </c>
       <c r="S64" s="3">
-        <v>40.3</v>
+        <v>41.99</v>
       </c>
       <c r="T64" s="3">
-        <v>18.97</v>
+        <v>19.24</v>
       </c>
       <c r="U64" s="3">
-        <v>34.69</v>
+        <v>41.59</v>
       </c>
       <c r="V64" s="3">
-        <v>29.12</v>
+        <v>40.42</v>
       </c>
       <c r="W64" s="3">
         <v>0</v>
@@ -5338,67 +5338,67 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C65" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D65" s="1">
-        <v>13329.2</v>
+        <v>24511.5</v>
       </c>
       <c r="E65" s="2">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="F65" s="2">
-        <v>2.27</v>
+        <v>2.87</v>
       </c>
       <c r="G65" s="2">
-        <v>-2.93</v>
+        <v>-6.62</v>
       </c>
       <c r="H65" s="2">
-        <v>-3.25</v>
+        <v>8.72</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>13983.09</v>
+        <v>23655.53</v>
       </c>
       <c r="K65" s="1">
-        <v>13362.65</v>
+        <v>24651.6</v>
       </c>
       <c r="L65" s="1">
-        <v>14165.18</v>
+        <v>25925.71</v>
       </c>
       <c r="M65" s="3">
-        <v>-257.6</v>
+        <v>-502.72</v>
       </c>
       <c r="N65" s="3">
-        <v>-260.28</v>
+        <v>-392.62</v>
       </c>
       <c r="O65" s="3">
-        <v>-142.59</v>
+        <v>443.43</v>
       </c>
       <c r="P65" s="3">
-        <v>69.21</v>
+        <v>767.21</v>
       </c>
       <c r="Q65" s="3">
-        <v>868.4</v>
+        <v>2299.98</v>
       </c>
       <c r="R65" s="3">
-        <v>1000.37</v>
+        <v>2352.69</v>
       </c>
       <c r="S65" s="3">
-        <v>38</v>
+        <v>38.42</v>
       </c>
       <c r="T65" s="3">
-        <v>12.76</v>
+        <v>15.17</v>
       </c>
       <c r="U65" s="3">
-        <v>33.46</v>
+        <v>38.84</v>
       </c>
       <c r="V65" s="3">
-        <v>46.85</v>
+        <v>37.88</v>
       </c>
       <c r="W65" s="3">
         <v>0</v>
@@ -5415,67 +5415,67 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C66" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D66" s="1">
-        <v>22293.45</v>
+        <v>26710.8</v>
       </c>
       <c r="E66" s="2">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="F66" s="2">
-        <v>2.6</v>
+        <v>5.45</v>
       </c>
       <c r="G66" s="2">
-        <v>-2.08</v>
+        <v>1.03</v>
       </c>
       <c r="H66" s="2">
-        <v>-7.33</v>
+        <v>17.55</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>23442.37</v>
+        <v>24445.25</v>
       </c>
       <c r="K66" s="1">
-        <v>22348.7</v>
+        <v>26105.26</v>
       </c>
       <c r="L66" s="1">
-        <v>23451.03</v>
+        <v>26420.35</v>
       </c>
       <c r="M66" s="3">
-        <v>-356.65</v>
+        <v>-73.45</v>
       </c>
       <c r="N66" s="3">
-        <v>-348.32</v>
+        <v>-176.46</v>
       </c>
       <c r="O66" s="3">
-        <v>-314.91</v>
+        <v>589.88</v>
       </c>
       <c r="P66" s="3">
-        <v>-46.35</v>
+        <v>752.08</v>
       </c>
       <c r="Q66" s="3">
-        <v>1008.68</v>
+        <v>1863.56</v>
       </c>
       <c r="R66" s="3">
-        <v>1356.57</v>
+        <v>1625.16</v>
       </c>
       <c r="S66" s="3">
-        <v>39.9</v>
+        <v>59.67</v>
       </c>
       <c r="T66" s="3">
-        <v>15.84</v>
+        <v>23.11</v>
       </c>
       <c r="U66" s="3">
-        <v>36.27</v>
+        <v>19.36</v>
       </c>
       <c r="V66" s="3">
-        <v>42.88</v>
+        <v>25.64</v>
       </c>
       <c r="W66" s="3">
         <v>0</v>
@@ -5492,67 +5492,67 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D67" s="1">
-        <v>26849.1</v>
+        <v>15510.55</v>
       </c>
       <c r="E67" s="2">
-        <v>0.29</v>
+        <v>0.6</v>
       </c>
       <c r="F67" s="2">
-        <v>1.99</v>
+        <v>3.11</v>
       </c>
       <c r="G67" s="2">
-        <v>-5.34</v>
-      </c>
-      <c r="H67" t="str">
-        <v/>
+        <v>-4.78</v>
+      </c>
+      <c r="H67" s="2">
+        <v>-3.09</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
-      <c r="J67" t="str">
-        <v/>
+      <c r="J67" s="1">
+        <v>16111.15</v>
       </c>
       <c r="K67" s="1">
-        <v>27122.88</v>
+        <v>15571.94</v>
       </c>
       <c r="L67" s="1">
-        <v>28924.83</v>
+        <v>16623.16</v>
       </c>
       <c r="M67" s="3">
-        <v>-643.67</v>
+        <v>-355.45</v>
       </c>
       <c r="N67" s="3">
-        <v>-567.91</v>
+        <v>-329.01</v>
       </c>
       <c r="O67" s="3">
-        <v>-383.13</v>
+        <v>-87.21</v>
       </c>
       <c r="P67" s="3">
-        <v>50.05</v>
+        <v>159.67</v>
       </c>
       <c r="Q67" s="3">
-        <v>197.84</v>
+        <v>1537.55</v>
       </c>
       <c r="R67" s="3">
-        <v>180.85</v>
+        <v>1745.84</v>
       </c>
       <c r="S67" s="3">
-        <v>34.81</v>
+        <v>38.16</v>
       </c>
       <c r="T67" s="3">
-        <v>16.03</v>
+        <v>12.31</v>
       </c>
       <c r="U67" s="3">
-        <v>38.76</v>
+        <v>36.04</v>
       </c>
       <c r="V67" s="3">
-        <v>41.2</v>
+        <v>46.06</v>
       </c>
       <c r="W67" s="3">
         <v>0</v>
@@ -5569,67 +5569,67 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D68" s="1">
-        <v>2981.5</v>
+        <v>46544.85</v>
       </c>
       <c r="E68" s="2">
-        <v>0.26</v>
+        <v>0.58</v>
       </c>
       <c r="F68" s="2">
-        <v>0.53</v>
+        <v>4.67</v>
       </c>
       <c r="G68" s="2">
-        <v>-1.07</v>
+        <v>-2.74</v>
       </c>
       <c r="H68" s="2">
-        <v>0.49</v>
+        <v>5.82</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>3001.43</v>
+        <v>44963.68</v>
       </c>
       <c r="K68" s="1">
-        <v>2975.97</v>
+        <v>46326.53</v>
       </c>
       <c r="L68" s="1">
-        <v>3017.76</v>
+        <v>48073.62</v>
       </c>
       <c r="M68" s="3">
-        <v>-13.73</v>
+        <v>-636.99</v>
       </c>
       <c r="N68" s="3">
-        <v>-14.94</v>
+        <v>-558.74</v>
       </c>
       <c r="O68" s="3">
-        <v>-2.34</v>
+        <v>542.93</v>
       </c>
       <c r="P68" s="3">
-        <v>8.61</v>
+        <v>989.98</v>
       </c>
       <c r="Q68" s="3">
-        <v>115.65</v>
+        <v>-287.99</v>
       </c>
       <c r="R68" s="3">
-        <v>133.01</v>
+        <v>-1009.44</v>
       </c>
       <c r="S68" s="3">
-        <v>41.41</v>
+        <v>45.5</v>
       </c>
       <c r="T68" s="3">
-        <v>20.62</v>
+        <v>21.97</v>
       </c>
       <c r="U68" s="3">
-        <v>37.25</v>
+        <v>38.55</v>
       </c>
       <c r="V68" s="3">
-        <v>49.76</v>
+        <v>34.15</v>
       </c>
       <c r="W68" s="3">
         <v>0</v>
@@ -5646,67 +5646,67 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D69" s="1">
-        <v>15457.45</v>
+        <v>16193.9</v>
       </c>
       <c r="E69" s="2">
-        <v>0.25</v>
+        <v>0.58</v>
       </c>
       <c r="F69" s="2">
-        <v>2.75</v>
+        <v>5.24</v>
       </c>
       <c r="G69" s="2">
-        <v>-5.1</v>
+        <v>0.35</v>
       </c>
       <c r="H69" s="2">
-        <v>-3.42</v>
+        <v>10.61</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>16110.89</v>
+        <v>15469.4</v>
       </c>
       <c r="K69" s="1">
-        <v>15562.29</v>
+        <v>15851.77</v>
       </c>
       <c r="L69" s="1">
-        <v>16622.1</v>
+        <v>16278.68</v>
       </c>
       <c r="M69" s="3">
-        <v>-359.69</v>
+        <v>-122.99</v>
       </c>
       <c r="N69" s="3">
-        <v>-329.85</v>
+        <v>-194.19</v>
       </c>
       <c r="O69" s="3">
-        <v>-91.45</v>
+        <v>158.88</v>
       </c>
       <c r="P69" s="3">
-        <v>158.82</v>
+        <v>302.57</v>
       </c>
       <c r="Q69" s="3">
-        <v>1533.31</v>
+        <v>1033.2</v>
       </c>
       <c r="R69" s="3">
-        <v>1744.99</v>
+        <v>1005.11</v>
       </c>
       <c r="S69" s="3">
-        <v>36.67</v>
+        <v>56.24</v>
       </c>
       <c r="T69" s="3">
-        <v>12.13</v>
+        <v>21.27</v>
       </c>
       <c r="U69" s="3">
-        <v>36.11</v>
+        <v>22.47</v>
       </c>
       <c r="V69" s="3">
-        <v>46.11</v>
+        <v>35.52</v>
       </c>
       <c r="W69" s="3">
         <v>0</v>
@@ -5723,67 +5723,67 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D70" s="1">
-        <v>3297.84</v>
+        <v>10352.4</v>
       </c>
       <c r="E70" s="2">
-        <v>0.23</v>
+        <v>0.54</v>
       </c>
       <c r="F70" s="2">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
       <c r="G70" s="2">
-        <v>-0.72</v>
+        <v>-2.47</v>
       </c>
       <c r="H70" s="2">
-        <v>1.73</v>
+        <v>-15.36</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>3296.36</v>
+        <v>11256.08</v>
       </c>
       <c r="K70" s="1">
-        <v>3291.5</v>
+        <v>10442.94</v>
       </c>
       <c r="L70" s="1">
-        <v>3338.77</v>
+        <v>10805.61</v>
       </c>
       <c r="M70" s="3">
-        <v>-14.51</v>
+        <v>-110.36</v>
       </c>
       <c r="N70" s="3">
-        <v>-16.55</v>
+        <v>-118.36</v>
       </c>
       <c r="O70" s="3">
-        <v>4.48</v>
+        <v>-246.59</v>
       </c>
       <c r="P70" s="3">
-        <v>18.08</v>
+        <v>-178.35</v>
       </c>
       <c r="Q70" s="3">
-        <v>137.44</v>
+        <v>65.78</v>
       </c>
       <c r="R70" s="3">
-        <v>154.09</v>
+        <v>277.95</v>
       </c>
       <c r="S70" s="3">
-        <v>43.53</v>
+        <v>39.67</v>
       </c>
       <c r="T70" s="3">
-        <v>14.87</v>
+        <v>14.72</v>
       </c>
       <c r="U70" s="3">
-        <v>29.49</v>
+        <v>30.34</v>
       </c>
       <c r="V70" s="3">
-        <v>50.33</v>
+        <v>31.01</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5800,67 +5800,67 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C71" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D71" s="1">
-        <v>3468.55</v>
+        <v>26900.7</v>
       </c>
       <c r="E71" s="2">
-        <v>0.22</v>
+        <v>0.48</v>
       </c>
       <c r="F71" s="2">
-        <v>0.49</v>
+        <v>2.19</v>
       </c>
       <c r="G71" s="2">
-        <v>-1.51</v>
-      </c>
-      <c r="H71" s="2">
-        <v>-0.7</v>
+        <v>-5.16</v>
+      </c>
+      <c r="H71" t="str">
+        <v/>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
-      <c r="J71" s="1">
-        <v>3494.74</v>
+      <c r="J71" t="str">
+        <v/>
       </c>
       <c r="K71" s="1">
-        <v>3467.56</v>
+        <v>27132.26</v>
       </c>
       <c r="L71" s="1">
-        <v>3520.5</v>
+        <v>28925.86</v>
       </c>
       <c r="M71" s="3">
-        <v>-18.94</v>
+        <v>-639.56</v>
       </c>
       <c r="N71" s="3">
-        <v>-18.52</v>
+        <v>-567.09</v>
       </c>
       <c r="O71" s="3">
-        <v>-2.38</v>
+        <v>-379.02</v>
       </c>
       <c r="P71" s="3">
-        <v>11.65</v>
+        <v>50.88</v>
       </c>
       <c r="Q71" s="3">
-        <v>118.82</v>
+        <v>201.96</v>
       </c>
       <c r="R71" s="3">
-        <v>141.9</v>
+        <v>181.67</v>
       </c>
       <c r="S71" s="3">
-        <v>40.23</v>
+        <v>35.69</v>
       </c>
       <c r="T71" s="3">
-        <v>20.45</v>
+        <v>15.98</v>
       </c>
       <c r="U71" s="3">
-        <v>34.18</v>
+        <v>38.65</v>
       </c>
       <c r="V71" s="3">
-        <v>33.1</v>
+        <v>41.2</v>
       </c>
       <c r="W71" s="3">
         <v>0</v>
@@ -5877,67 +5877,67 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D72" s="1">
-        <v>3072.06</v>
+        <v>3474.5</v>
       </c>
       <c r="E72" s="2">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="F72" s="2">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="G72" s="2">
-        <v>-1.04</v>
+        <v>-1.34</v>
       </c>
       <c r="H72" s="2">
-        <v>0.65</v>
+        <v>-0.53</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>3086.21</v>
+        <v>3494.77</v>
       </c>
       <c r="K72" s="1">
-        <v>3067.5</v>
+        <v>3468.64</v>
       </c>
       <c r="L72" s="1">
-        <v>3109.34</v>
+        <v>3520.61</v>
       </c>
       <c r="M72" s="3">
-        <v>-13.8</v>
+        <v>-18.47</v>
       </c>
       <c r="N72" s="3">
-        <v>-14.87</v>
+        <v>-18.42</v>
       </c>
       <c r="O72" s="3">
-        <v>-0.31</v>
+        <v>-1.91</v>
       </c>
       <c r="P72" s="3">
-        <v>11.05</v>
+        <v>11.74</v>
       </c>
       <c r="Q72" s="3">
-        <v>119.4</v>
+        <v>119.3</v>
       </c>
       <c r="R72" s="3">
-        <v>136.73</v>
+        <v>142</v>
       </c>
       <c r="S72" s="3">
-        <v>41.08</v>
+        <v>43.03</v>
       </c>
       <c r="T72" s="3">
-        <v>19.03</v>
+        <v>21.3</v>
       </c>
       <c r="U72" s="3">
-        <v>37.28</v>
+        <v>33.82</v>
       </c>
       <c r="V72" s="3">
-        <v>48.52</v>
+        <v>32.92</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -5954,67 +5954,67 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C73" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D73" s="1">
-        <v>2610.37</v>
+        <v>2984.42</v>
       </c>
       <c r="E73" s="2">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="F73" s="2">
-        <v>0.56</v>
+        <v>0.63</v>
       </c>
       <c r="G73" s="2">
-        <v>-1.06</v>
+        <v>-0.98</v>
       </c>
       <c r="H73" s="2">
-        <v>-0.06</v>
+        <v>0.59</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>2632.02</v>
+        <v>3001.44</v>
       </c>
       <c r="K73" s="1">
-        <v>2605.31</v>
+        <v>2976.5</v>
       </c>
       <c r="L73" s="1">
-        <v>2641.36</v>
+        <v>3017.81</v>
       </c>
       <c r="M73" s="3">
-        <v>-11.8</v>
+        <v>-13.5</v>
       </c>
       <c r="N73" s="3">
-        <v>-13.12</v>
+        <v>-14.9</v>
       </c>
       <c r="O73" s="3">
-        <v>-4.05</v>
+        <v>-2.11</v>
       </c>
       <c r="P73" s="3">
-        <v>5.12</v>
+        <v>8.65</v>
       </c>
       <c r="Q73" s="3">
-        <v>90.76</v>
+        <v>115.88</v>
       </c>
       <c r="R73" s="3">
-        <v>106.56</v>
+        <v>133.05</v>
       </c>
       <c r="S73" s="3">
-        <v>42.35</v>
+        <v>43.84</v>
       </c>
       <c r="T73" s="3">
-        <v>22.48</v>
+        <v>23.11</v>
       </c>
       <c r="U73" s="3">
-        <v>31.49</v>
+        <v>36.09</v>
       </c>
       <c r="V73" s="3">
-        <v>37.02</v>
+        <v>49.27</v>
       </c>
       <c r="W73" s="3">
         <v>0</v>
@@ -6031,67 +6031,67 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D74" s="1">
-        <v>16130.1</v>
+        <v>2613.83</v>
       </c>
       <c r="E74" s="2">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="F74" s="2">
-        <v>4.83</v>
+        <v>0.7</v>
       </c>
       <c r="G74" s="2">
-        <v>-0.05</v>
+        <v>-0.93</v>
       </c>
       <c r="H74" s="2">
-        <v>10.18</v>
+        <v>0.07</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
       <c r="J74" s="1">
-        <v>15469.08</v>
+        <v>2632.03</v>
       </c>
       <c r="K74" s="1">
-        <v>15840.17</v>
+        <v>2605.94</v>
       </c>
       <c r="L74" s="1">
-        <v>16277.4</v>
+        <v>2641.43</v>
       </c>
       <c r="M74" s="3">
-        <v>-128.08</v>
+        <v>-11.53</v>
       </c>
       <c r="N74" s="3">
-        <v>-195.2</v>
+        <v>-13.07</v>
       </c>
       <c r="O74" s="3">
-        <v>153.79</v>
+        <v>-3.77</v>
       </c>
       <c r="P74" s="3">
-        <v>301.56</v>
+        <v>5.17</v>
       </c>
       <c r="Q74" s="3">
-        <v>1028.11</v>
+        <v>91.03</v>
       </c>
       <c r="R74" s="3">
-        <v>1004.09</v>
+        <v>106.62</v>
       </c>
       <c r="S74" s="3">
-        <v>54.64</v>
+        <v>45.37</v>
       </c>
       <c r="T74" s="3">
-        <v>21.27</v>
+        <v>24.34</v>
       </c>
       <c r="U74" s="3">
-        <v>22.47</v>
+        <v>30.73</v>
       </c>
       <c r="V74" s="3">
-        <v>35.52</v>
+        <v>36.66</v>
       </c>
       <c r="W74" s="3">
         <v>0</v>
@@ -6108,67 +6108,67 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C75" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D75" s="1">
-        <v>841.08</v>
+        <v>3075.18</v>
       </c>
       <c r="E75" s="2">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="F75" s="2">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="G75" s="2">
-        <v>-1.65</v>
+        <v>-0.94</v>
       </c>
       <c r="H75" s="2">
-        <v>-5.65</v>
+        <v>0.75</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>872.52</v>
+        <v>3086.22</v>
       </c>
       <c r="K75" s="1">
-        <v>840.45</v>
+        <v>3068.07</v>
       </c>
       <c r="L75" s="1">
-        <v>857.48</v>
+        <v>3109.4</v>
       </c>
       <c r="M75" s="3">
-        <v>-5.69</v>
+        <v>-13.55</v>
       </c>
       <c r="N75" s="3">
-        <v>-6.12</v>
+        <v>-14.82</v>
       </c>
       <c r="O75" s="3">
-        <v>-9.44</v>
+        <v>-0.06</v>
       </c>
       <c r="P75" s="3">
-        <v>-6.41</v>
+        <v>11.1</v>
       </c>
       <c r="Q75" s="3">
-        <v>-16.98</v>
+        <v>119.65</v>
       </c>
       <c r="R75" s="3">
-        <v>-14.15</v>
+        <v>136.78</v>
       </c>
       <c r="S75" s="3">
-        <v>34.88</v>
+        <v>43.54</v>
       </c>
       <c r="T75" s="3">
-        <v>17.11</v>
+        <v>21.25</v>
       </c>
       <c r="U75" s="3">
-        <v>35.87</v>
+        <v>36.26</v>
       </c>
       <c r="V75" s="3">
-        <v>52.89</v>
+        <v>48.07</v>
       </c>
       <c r="W75" s="3">
         <v>0</v>
@@ -6185,67 +6185,67 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D76" s="1">
-        <v>7607.9</v>
+        <v>842.23</v>
       </c>
       <c r="E76" s="2">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="F76" s="2">
-        <v>3.41</v>
+        <v>0.6</v>
       </c>
       <c r="G76" s="2">
-        <v>-1.25</v>
+        <v>-1.52</v>
       </c>
       <c r="H76" s="2">
-        <v>-11.58</v>
+        <v>-5.52</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>7659.8</v>
+        <v>872.53</v>
       </c>
       <c r="K76" s="1">
-        <v>7534.3</v>
+        <v>840.66</v>
       </c>
       <c r="L76" s="1">
-        <v>7714.26</v>
+        <v>857.51</v>
       </c>
       <c r="M76" s="3">
-        <v>-47.64</v>
+        <v>-5.6</v>
       </c>
       <c r="N76" s="3">
-        <v>-73.76</v>
+        <v>-6.1</v>
       </c>
       <c r="O76" s="3">
-        <v>-67.76</v>
+        <v>-9.35</v>
       </c>
       <c r="P76" s="3">
-        <v>-28.63</v>
+        <v>-6.39</v>
       </c>
       <c r="Q76" s="3">
-        <v>-285.63</v>
+        <v>-16.89</v>
       </c>
       <c r="R76" s="3">
-        <v>-244.31</v>
+        <v>-14.13</v>
       </c>
       <c r="S76" s="3">
-        <v>51.18</v>
+        <v>38.13</v>
       </c>
       <c r="T76" s="3">
-        <v>18.85</v>
+        <v>19.08</v>
       </c>
       <c r="U76" s="3">
-        <v>23.07</v>
+        <v>35.02</v>
       </c>
       <c r="V76" s="3">
-        <v>23.04</v>
+        <v>52.47</v>
       </c>
       <c r="W76" s="3">
         <v>0</v>
@@ -6262,67 +6262,67 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C77" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D77" s="1">
-        <v>26577.1</v>
+        <v>14975.8</v>
       </c>
       <c r="E77" s="2">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="F77" s="2">
-        <v>4.93</v>
+        <v>3.16</v>
       </c>
       <c r="G77" s="2">
-        <v>0.53</v>
+        <v>-3.1</v>
       </c>
       <c r="H77" s="2">
-        <v>16.96</v>
+        <v>-2.83</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>24444.58</v>
+        <v>15610.51</v>
       </c>
       <c r="K77" s="1">
-        <v>26080.95</v>
+        <v>14913.39</v>
       </c>
       <c r="L77" s="1">
-        <v>26417.67</v>
+        <v>15709.21</v>
       </c>
       <c r="M77" s="3">
-        <v>-84.11</v>
+        <v>-244.27</v>
       </c>
       <c r="N77" s="3">
-        <v>-178.59</v>
+        <v>-271.83</v>
       </c>
       <c r="O77" s="3">
-        <v>579.21</v>
+        <v>-153.96</v>
       </c>
       <c r="P77" s="3">
-        <v>749.94</v>
+        <v>46.35</v>
       </c>
       <c r="Q77" s="3">
-        <v>1852.9</v>
+        <v>1257.67</v>
       </c>
       <c r="R77" s="3">
-        <v>1623.02</v>
+        <v>1446.02</v>
       </c>
       <c r="S77" s="3">
-        <v>57.8</v>
+        <v>42.99</v>
       </c>
       <c r="T77" s="3">
-        <v>23.11</v>
+        <v>15.46</v>
       </c>
       <c r="U77" s="3">
-        <v>19.36</v>
+        <v>34.02</v>
       </c>
       <c r="V77" s="3">
-        <v>25.64</v>
+        <v>49.36</v>
       </c>
       <c r="W77" s="3">
         <v>0</v>
@@ -6339,67 +6339,67 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C78" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D78" s="1">
-        <v>1257.69</v>
+        <v>3299.16</v>
       </c>
       <c r="E78" s="2">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="F78" s="2">
-        <v>0.2</v>
+        <v>0.46</v>
       </c>
       <c r="G78" s="2">
-        <v>-1.22</v>
+        <v>-0.68</v>
       </c>
       <c r="H78" s="2">
-        <v>-0.31</v>
+        <v>1.77</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>1268.25</v>
+        <v>3296.37</v>
       </c>
       <c r="K78" s="1">
-        <v>1259.97</v>
+        <v>3291.74</v>
       </c>
       <c r="L78" s="1">
-        <v>1276.45</v>
+        <v>3338.8</v>
       </c>
       <c r="M78" s="3">
-        <v>-6.11</v>
+        <v>-14.41</v>
       </c>
       <c r="N78" s="3">
-        <v>-5.46</v>
+        <v>-16.53</v>
       </c>
       <c r="O78" s="3">
-        <v>-0.71</v>
+        <v>4.59</v>
       </c>
       <c r="P78" s="3">
-        <v>3.72</v>
+        <v>18.1</v>
       </c>
       <c r="Q78" s="3">
-        <v>20.92</v>
+        <v>137.54</v>
       </c>
       <c r="R78" s="3">
-        <v>21.88</v>
+        <v>154.11</v>
       </c>
       <c r="S78" s="3">
-        <v>25.29</v>
+        <v>44.35</v>
       </c>
       <c r="T78" s="3">
-        <v>25.22</v>
+        <v>15.83</v>
       </c>
       <c r="U78" s="3">
-        <v>72.61</v>
+        <v>29.16</v>
       </c>
       <c r="V78" s="3">
-        <v>46.61</v>
+        <v>50.1</v>
       </c>
       <c r="W78" s="3">
         <v>0</v>
@@ -6416,67 +6416,67 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C79" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D79" s="1">
-        <v>50944</v>
+        <v>28529.45</v>
       </c>
       <c r="E79" s="2">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="F79" s="2">
-        <v>6.91</v>
+        <v>2.75</v>
       </c>
       <c r="G79" s="2">
-        <v>-0.07</v>
+        <v>-5.95</v>
       </c>
       <c r="H79" s="2">
-        <v>16.14</v>
+        <v>-6.67</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>47476.83</v>
+        <v>31335.03</v>
       </c>
       <c r="K79" s="1">
-        <v>49758.75</v>
+        <v>28662.22</v>
       </c>
       <c r="L79" s="1">
-        <v>51281.38</v>
+        <v>30989.9</v>
       </c>
       <c r="M79" s="3">
-        <v>-460.47</v>
+        <v>-796.67</v>
       </c>
       <c r="N79" s="3">
-        <v>-682.8</v>
+        <v>-778.62</v>
       </c>
       <c r="O79" s="3">
-        <v>863.87</v>
+        <v>-657.44</v>
       </c>
       <c r="P79" s="3">
-        <v>1413.54</v>
+        <v>-82.41</v>
       </c>
       <c r="Q79" s="3">
-        <v>2363.64</v>
+        <v>1982.18</v>
       </c>
       <c r="R79" s="3">
-        <v>1510.3</v>
+        <v>2396.34</v>
       </c>
       <c r="S79" s="3">
-        <v>55.34</v>
+        <v>34</v>
       </c>
       <c r="T79" s="3">
-        <v>26.75</v>
+        <v>14.82</v>
       </c>
       <c r="U79" s="3">
-        <v>26.92</v>
+        <v>40.61</v>
       </c>
       <c r="V79" s="3">
-        <v>34.29</v>
+        <v>58.7</v>
       </c>
       <c r="W79" s="3">
         <v>0</v>
@@ -6493,67 +6493,67 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C80" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D80" s="1">
-        <v>28490.1</v>
+        <v>15627</v>
       </c>
       <c r="E80" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F80" s="2">
-        <v>2.61</v>
+        <v>3.61</v>
       </c>
       <c r="G80" s="2">
-        <v>-6.08</v>
+        <v>-2.44</v>
       </c>
       <c r="H80" s="2">
-        <v>-6.8</v>
+        <v>-2.18</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>31334.83</v>
+        <v>15991.4</v>
       </c>
       <c r="K80" s="1">
-        <v>28655.07</v>
+        <v>15533.41</v>
       </c>
       <c r="L80" s="1">
-        <v>30989.11</v>
+        <v>16259.44</v>
       </c>
       <c r="M80" s="3">
-        <v>-799.81</v>
+        <v>-219.09</v>
       </c>
       <c r="N80" s="3">
-        <v>-779.25</v>
+        <v>-251.3</v>
       </c>
       <c r="O80" s="3">
-        <v>-660.58</v>
+        <v>-98.84</v>
       </c>
       <c r="P80" s="3">
-        <v>-83.04</v>
+        <v>85.4</v>
       </c>
       <c r="Q80" s="3">
-        <v>1979.04</v>
+        <v>376.76</v>
       </c>
       <c r="R80" s="3">
-        <v>2395.71</v>
+        <v>332.24</v>
       </c>
       <c r="S80" s="3">
-        <v>33.29</v>
+        <v>45.22</v>
       </c>
       <c r="T80" s="3">
-        <v>14.01</v>
+        <v>17.13</v>
       </c>
       <c r="U80" s="3">
-        <v>41</v>
+        <v>32.57</v>
       </c>
       <c r="V80" s="3">
-        <v>58.88</v>
+        <v>45.96</v>
       </c>
       <c r="W80" s="3">
         <v>0</v>
@@ -6570,67 +6570,67 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C81" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D81" s="1">
-        <v>3282</v>
+        <v>1257.69</v>
       </c>
       <c r="E81" s="2">
-        <v>0.07</v>
+        <v>0.12</v>
       </c>
       <c r="F81" s="2">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="G81" s="2">
-        <v>-0.8</v>
+        <v>-1.22</v>
       </c>
       <c r="H81" s="2">
-        <v>1.84</v>
+        <v>-0.31</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>3281.57</v>
+        <v>1268.25</v>
       </c>
       <c r="K81" s="1">
-        <v>3281.66</v>
+        <v>1259.97</v>
       </c>
       <c r="L81" s="1">
-        <v>3314.18</v>
+        <v>1276.45</v>
       </c>
       <c r="M81" s="3">
-        <v>-10.34</v>
+        <v>-6.11</v>
       </c>
       <c r="N81" s="3">
-        <v>-11.17</v>
+        <v>-5.46</v>
       </c>
       <c r="O81" s="3">
-        <v>5.24</v>
+        <v>-0.71</v>
       </c>
       <c r="P81" s="3">
-        <v>15.44</v>
+        <v>3.72</v>
       </c>
       <c r="Q81" s="3">
-        <v>139.89</v>
+        <v>20.92</v>
       </c>
       <c r="R81" s="3">
-        <v>155.49</v>
+        <v>21.88</v>
       </c>
       <c r="S81" s="3">
-        <v>34.28</v>
+        <v>25.29</v>
       </c>
       <c r="T81" s="3">
-        <v>13.24</v>
+        <v>25.22</v>
       </c>
       <c r="U81" s="3">
-        <v>39.21</v>
+        <v>72.61</v>
       </c>
       <c r="V81" s="3">
-        <v>50.78</v>
+        <v>46.61</v>
       </c>
       <c r="W81" s="3">
         <v>0</v>
@@ -6647,67 +6647,67 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C82" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D82" s="1">
-        <v>1442.33</v>
+        <v>3283.49</v>
       </c>
       <c r="E82" s="2">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="F82" s="2">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="G82" s="2">
-        <v>-0.8</v>
+        <v>-0.76</v>
       </c>
       <c r="H82" s="2">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>1441.19</v>
+        <v>3281.57</v>
       </c>
       <c r="K82" s="1">
-        <v>1444.16</v>
+        <v>3281.93</v>
       </c>
       <c r="L82" s="1">
-        <v>1455.63</v>
+        <v>3314.21</v>
       </c>
       <c r="M82" s="3">
-        <v>-4.33</v>
+        <v>-10.22</v>
       </c>
       <c r="N82" s="3">
-        <v>-3.77</v>
+        <v>-11.15</v>
       </c>
       <c r="O82" s="3">
-        <v>2.66</v>
+        <v>5.36</v>
       </c>
       <c r="P82" s="3">
-        <v>6.33</v>
+        <v>15.46</v>
       </c>
       <c r="Q82" s="3">
-        <v>28.88</v>
+        <v>140.01</v>
       </c>
       <c r="R82" s="3">
-        <v>28.5</v>
+        <v>155.51</v>
       </c>
       <c r="S82" s="3">
-        <v>27.44</v>
+        <v>36.6</v>
       </c>
       <c r="T82" s="3">
-        <v>24.99</v>
+        <v>13.78</v>
       </c>
       <c r="U82" s="3">
-        <v>67.65</v>
+        <v>38.98</v>
       </c>
       <c r="V82" s="3">
-        <v>40.17</v>
+        <v>50.66</v>
       </c>
       <c r="W82" s="3">
         <v>0</v>
@@ -6801,67 +6801,67 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C84" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D84" s="1">
-        <v>1596.66</v>
+        <v>1441.97</v>
       </c>
       <c r="E84" s="2">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F84" s="2">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="G84" s="2">
-        <v>-0.64</v>
+        <v>-0.82</v>
       </c>
       <c r="H84" s="2">
-        <v>1.9</v>
+        <v>1.21</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>1587.43</v>
+        <v>1441.19</v>
       </c>
       <c r="K84" s="1">
-        <v>1598.93</v>
+        <v>1444.09</v>
       </c>
       <c r="L84" s="1">
-        <v>1607.09</v>
+        <v>1455.62</v>
       </c>
       <c r="M84" s="3">
-        <v>-3.28</v>
+        <v>-4.36</v>
       </c>
       <c r="N84" s="3">
-        <v>-2.62</v>
+        <v>-3.77</v>
       </c>
       <c r="O84" s="3">
-        <v>5.43</v>
+        <v>2.63</v>
       </c>
       <c r="P84" s="3">
-        <v>8.52</v>
+        <v>6.32</v>
       </c>
       <c r="Q84" s="3">
-        <v>34.52</v>
+        <v>28.85</v>
       </c>
       <c r="R84" s="3">
-        <v>33.05</v>
+        <v>28.49</v>
       </c>
       <c r="S84" s="3">
-        <v>27.04</v>
+        <v>25.88</v>
       </c>
       <c r="T84" s="3">
-        <v>18.2</v>
+        <v>24.99</v>
       </c>
       <c r="U84" s="3">
-        <v>66.59</v>
+        <v>67.65</v>
       </c>
       <c r="V84" s="3">
-        <v>35.44</v>
+        <v>40.17</v>
       </c>
       <c r="W84" s="3">
         <v>0</v>
@@ -6878,67 +6878,67 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C85" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D85" s="1">
-        <v>15591.25</v>
+        <v>1596.73</v>
       </c>
       <c r="E85" s="2">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="F85" s="2">
-        <v>3.38</v>
+        <v>0.04</v>
       </c>
       <c r="G85" s="2">
-        <v>-2.66</v>
+        <v>-0.64</v>
       </c>
       <c r="H85" s="2">
-        <v>-2.4</v>
+        <v>1.9</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>15991.22</v>
+        <v>1587.43</v>
       </c>
       <c r="K85" s="1">
-        <v>15526.91</v>
+        <v>1598.94</v>
       </c>
       <c r="L85" s="1">
-        <v>16258.73</v>
+        <v>1607.09</v>
       </c>
       <c r="M85" s="3">
-        <v>-221.94</v>
+        <v>-3.28</v>
       </c>
       <c r="N85" s="3">
-        <v>-251.87</v>
+        <v>-2.62</v>
       </c>
       <c r="O85" s="3">
-        <v>-101.69</v>
+        <v>5.44</v>
       </c>
       <c r="P85" s="3">
-        <v>84.83</v>
+        <v>8.52</v>
       </c>
       <c r="Q85" s="3">
-        <v>373.91</v>
+        <v>34.53</v>
       </c>
       <c r="R85" s="3">
-        <v>331.67</v>
+        <v>33.05</v>
       </c>
       <c r="S85" s="3">
-        <v>44.17</v>
+        <v>27.38</v>
       </c>
       <c r="T85" s="3">
-        <v>17.13</v>
+        <v>18.1</v>
       </c>
       <c r="U85" s="3">
-        <v>32.57</v>
+        <v>66.22</v>
       </c>
       <c r="V85" s="3">
-        <v>45.96</v>
+        <v>35.44</v>
       </c>
       <c r="W85" s="3">
         <v>0</v>
@@ -6955,67 +6955,67 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D86" s="1">
-        <v>14927.4</v>
+        <v>7591.75</v>
       </c>
       <c r="E86" s="2">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="F86" s="2">
-        <v>2.83</v>
+        <v>3.19</v>
       </c>
       <c r="G86" s="2">
-        <v>-3.41</v>
+        <v>-1.46</v>
       </c>
       <c r="H86" s="2">
-        <v>-3.15</v>
+        <v>-11.77</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
       <c r="J86" s="1">
-        <v>15610.26</v>
+        <v>7659.72</v>
       </c>
       <c r="K86" s="1">
-        <v>14904.59</v>
+        <v>7531.36</v>
       </c>
       <c r="L86" s="1">
-        <v>15708.24</v>
+        <v>7713.93</v>
       </c>
       <c r="M86" s="3">
-        <v>-248.13</v>
+        <v>-48.93</v>
       </c>
       <c r="N86" s="3">
-        <v>-272.6</v>
+        <v>-74.02</v>
       </c>
       <c r="O86" s="3">
-        <v>-157.83</v>
+        <v>-69.05</v>
       </c>
       <c r="P86" s="3">
-        <v>45.57</v>
+        <v>-28.89</v>
       </c>
       <c r="Q86" s="3">
-        <v>1253.81</v>
+        <v>-286.92</v>
       </c>
       <c r="R86" s="3">
-        <v>1445.24</v>
+        <v>-244.56</v>
       </c>
       <c r="S86" s="3">
-        <v>41.4</v>
+        <v>50.37</v>
       </c>
       <c r="T86" s="3">
-        <v>15.57</v>
+        <v>18.84</v>
       </c>
       <c r="U86" s="3">
-        <v>34.25</v>
+        <v>23.05</v>
       </c>
       <c r="V86" s="3">
-        <v>49.36</v>
+        <v>23.04</v>
       </c>
       <c r="W86" s="3">
         <v>0</v>
@@ -7038,52 +7038,52 @@
         <v>NIFTYAUTO</v>
       </c>
       <c r="D87" s="1">
-        <v>25604.85</v>
+        <v>25645.6</v>
       </c>
       <c r="E87" s="2">
-        <v>-0.4</v>
+        <v>-0.24</v>
       </c>
       <c r="F87" s="2">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="G87" s="2">
-        <v>-2.62</v>
+        <v>-2.47</v>
       </c>
       <c r="H87" s="2">
-        <v>-9.17</v>
+        <v>-9.02</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>26844.42</v>
+        <v>26844.62</v>
       </c>
       <c r="K87" s="1">
-        <v>25380.23</v>
+        <v>25387.64</v>
       </c>
       <c r="L87" s="1">
-        <v>26858.26</v>
+        <v>26859.08</v>
       </c>
       <c r="M87" s="3">
-        <v>-375.95</v>
+        <v>-372.7</v>
       </c>
       <c r="N87" s="3">
-        <v>-508.62</v>
+        <v>-507.97</v>
       </c>
       <c r="O87" s="3">
-        <v>-354.37</v>
+        <v>-351.12</v>
       </c>
       <c r="P87" s="3">
-        <v>2.01</v>
+        <v>2.67</v>
       </c>
       <c r="Q87" s="3">
-        <v>1508.44</v>
+        <v>1511.69</v>
       </c>
       <c r="R87" s="3">
-        <v>1817.19</v>
+        <v>1817.84</v>
       </c>
       <c r="S87" s="3">
-        <v>46.98</v>
+        <v>47.52</v>
       </c>
       <c r="T87" s="3">
         <v>18.76</v>
@@ -7115,19 +7115,19 @@
         <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D88" s="1">
-        <v>233.8</v>
+        <v>233.35</v>
       </c>
       <c r="E88" s="2">
-        <v>-0.83</v>
+        <v>-1.02</v>
       </c>
       <c r="F88" s="2">
-        <v>-1.18</v>
+        <v>-1.37</v>
       </c>
       <c r="G88" s="2">
-        <v>-0.91</v>
+        <v>-1.1</v>
       </c>
       <c r="H88" s="2">
-        <v>16.9</v>
+        <v>16.68</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
@@ -7136,40 +7136,40 @@
         <v>219.97</v>
       </c>
       <c r="K88" s="1">
-        <v>234.91</v>
+        <v>234.83</v>
       </c>
       <c r="L88" s="1">
-        <v>229.29</v>
+        <v>229.28</v>
       </c>
       <c r="M88" s="3">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="N88" s="3">
         <v>1.9</v>
       </c>
       <c r="O88" s="3">
-        <v>4.77</v>
+        <v>4.73</v>
       </c>
       <c r="P88" s="3">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="Q88" s="3">
-        <v>-0.8</v>
+        <v>-0.84</v>
       </c>
       <c r="R88" s="3">
-        <v>-4.8</v>
+        <v>-4.81</v>
       </c>
       <c r="S88" s="3">
-        <v>51.08</v>
+        <v>50.07</v>
       </c>
       <c r="T88" s="3">
-        <v>25.21</v>
+        <v>24.88</v>
       </c>
       <c r="U88" s="3">
-        <v>14.2</v>
+        <v>15.32</v>
       </c>
       <c r="V88" s="3">
-        <v>41</v>
+        <v>40.7</v>
       </c>
       <c r="W88" s="3">
         <v>0</v>
@@ -7192,19 +7192,19 @@
         <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D89" s="1">
-        <v>189.6</v>
+        <v>189.2</v>
       </c>
       <c r="E89" s="2">
-        <v>-0.84</v>
+        <v>-1.05</v>
       </c>
       <c r="F89" s="2">
-        <v>-1.2</v>
+        <v>-1.41</v>
       </c>
       <c r="G89" s="2">
-        <v>-0.94</v>
+        <v>-1.15</v>
       </c>
       <c r="H89" s="2">
-        <v>15.86</v>
+        <v>15.61</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
@@ -7213,40 +7213,40 @@
         <v>179.23</v>
       </c>
       <c r="K89" s="1">
-        <v>190.51</v>
+        <v>190.44</v>
       </c>
       <c r="L89" s="1">
-        <v>186</v>
+        <v>185.99</v>
       </c>
       <c r="M89" s="3">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="N89" s="3">
         <v>1.52</v>
       </c>
       <c r="O89" s="3">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="P89" s="3">
         <v>2.7</v>
       </c>
       <c r="Q89" s="3">
-        <v>-2.62</v>
+        <v>-2.65</v>
       </c>
       <c r="R89" s="3">
-        <v>-6.05</v>
+        <v>-6.06</v>
       </c>
       <c r="S89" s="3">
-        <v>50.97</v>
+        <v>49.87</v>
       </c>
       <c r="T89" s="3">
-        <v>25.16</v>
+        <v>24.83</v>
       </c>
       <c r="U89" s="3">
-        <v>14.17</v>
+        <v>15.3</v>
       </c>
       <c r="V89" s="3">
-        <v>40.56</v>
+        <v>40.26</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -7269,19 +7269,19 @@
         <v>INDIAVIX</v>
       </c>
       <c r="D90" s="1">
-        <v>15.31</v>
+        <v>15.12</v>
       </c>
       <c r="E90" s="2">
-        <v>-5.78</v>
+        <v>-6.95</v>
       </c>
       <c r="F90" s="2">
-        <v>-9.19</v>
+        <v>-10.32</v>
       </c>
       <c r="G90" s="2">
-        <v>13.49</v>
+        <v>12.08</v>
       </c>
       <c r="H90" s="2">
-        <v>61.5</v>
+        <v>59.49</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
@@ -7290,40 +7290,40 @@
         <v>15.04</v>
       </c>
       <c r="K90" s="1">
-        <v>15.69</v>
+        <v>15.65</v>
       </c>
       <c r="L90" s="1">
         <v>12.98</v>
       </c>
       <c r="M90" s="3">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="N90" s="3">
         <v>0.88</v>
       </c>
       <c r="O90" s="3">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="P90" s="3">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
       <c r="Q90" s="3">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="R90" s="3">
         <v>0.03</v>
       </c>
       <c r="S90" s="3">
-        <v>54.43</v>
+        <v>53.29</v>
       </c>
       <c r="T90" s="3">
-        <v>18.42</v>
+        <v>18.27</v>
       </c>
       <c r="U90" s="3">
-        <v>16.97</v>
+        <v>17.65</v>
       </c>
       <c r="V90" s="3">
-        <v>16.7</v>
+        <v>16.53</v>
       </c>
       <c r="W90" s="3">
         <v>0</v>

--- a/Index.xlsx
+++ b/Index.xlsx
@@ -487,67 +487,67 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>CNXREALTY</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C2" t="str">
-        <v>CNXREALTY</v>
+        <v>CNXIT</v>
       </c>
       <c r="D2" s="1">
-        <v>819.8</v>
+        <v>32606.9</v>
       </c>
       <c r="E2" s="2">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="F2" s="2">
-        <v>4.52</v>
+        <v>1.91</v>
       </c>
       <c r="G2" s="2">
-        <v>-3.25</v>
+        <v>17.69</v>
       </c>
       <c r="H2" s="2">
-        <v>-6.62</v>
+        <v>-13.93</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>819.74</v>
+        <v>30662.86</v>
       </c>
       <c r="K2" s="1">
-        <v>808.06</v>
+        <v>31698.53</v>
       </c>
       <c r="L2" s="1">
-        <v>854.06</v>
+        <v>29946.03</v>
       </c>
       <c r="M2" s="3">
-        <v>-13.91</v>
+        <v>855.57</v>
       </c>
       <c r="N2" s="3">
-        <v>-15.29</v>
+        <v>654.94</v>
       </c>
       <c r="O2" s="3">
-        <v>-3.23</v>
+        <v>62.27</v>
       </c>
       <c r="P2" s="3">
-        <v>7.53</v>
+        <v>-403.19</v>
       </c>
       <c r="Q2" s="3">
-        <v>2.84</v>
+        <v>-1612.24</v>
       </c>
       <c r="R2" s="3">
-        <v>10.15</v>
+        <v>-1138</v>
       </c>
       <c r="S2" s="3">
-        <v>48.35</v>
+        <v>67.66</v>
       </c>
       <c r="T2" s="3">
-        <v>21.33</v>
+        <v>30.32</v>
       </c>
       <c r="U2" s="3">
-        <v>27.14</v>
+        <v>13.88</v>
       </c>
       <c r="V2" s="3">
-        <v>27.41</v>
+        <v>30.79</v>
       </c>
       <c r="W2" s="3">
         <v>0</v>
@@ -564,67 +564,67 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D3" s="1">
-        <v>43882.95</v>
+        <v>16449.55</v>
       </c>
       <c r="E3" s="2">
-        <v>2.34</v>
+        <v>1.58</v>
       </c>
       <c r="F3" s="2">
-        <v>2.82</v>
+        <v>6.91</v>
       </c>
       <c r="G3" s="2">
-        <v>-1.41</v>
+        <v>1.93</v>
       </c>
       <c r="H3" s="2">
-        <v>-20.9</v>
+        <v>12.36</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>48701.26</v>
+        <v>15476.57</v>
       </c>
       <c r="K3" s="1">
-        <v>43553.93</v>
+        <v>15960.46</v>
       </c>
       <c r="L3" s="1">
-        <v>45334.26</v>
+        <v>16278.39</v>
       </c>
       <c r="M3" s="3">
-        <v>-659.05</v>
+        <v>-66.16</v>
       </c>
       <c r="N3" s="3">
-        <v>-638.2</v>
+        <v>-168.58</v>
       </c>
       <c r="O3" s="3">
-        <v>-1711.16</v>
+        <v>179.28</v>
       </c>
       <c r="P3" s="3">
-        <v>-1431.42</v>
+        <v>306.65</v>
       </c>
       <c r="Q3" s="3">
-        <v>-2123.92</v>
+        <v>1053.59</v>
       </c>
       <c r="R3" s="3">
-        <v>-957.6</v>
+        <v>1009.19</v>
       </c>
       <c r="S3" s="3">
-        <v>46.15</v>
+        <v>62.01</v>
       </c>
       <c r="T3" s="3">
-        <v>20.78</v>
+        <v>28.5</v>
       </c>
       <c r="U3" s="3">
-        <v>27.99</v>
+        <v>20.07</v>
       </c>
       <c r="V3" s="3">
-        <v>37.91</v>
+        <v>34.22</v>
       </c>
       <c r="W3" s="3">
         <v>0</v>
@@ -641,67 +641,67 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C4" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D4" s="1">
-        <v>8312.5</v>
+        <v>27124.85</v>
       </c>
       <c r="E4" s="2">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="F4" s="2">
-        <v>3</v>
+        <v>7.09</v>
       </c>
       <c r="G4" s="2">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="H4" s="2">
-        <v>-2.59</v>
+        <v>19.37</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>8561.27</v>
+        <v>24464.44</v>
       </c>
       <c r="K4" s="1">
-        <v>8169.63</v>
+        <v>26290.64</v>
       </c>
       <c r="L4" s="1">
-        <v>8297.36</v>
+        <v>26435.61</v>
       </c>
       <c r="M4" s="3">
-        <v>-17.15</v>
+        <v>14.55</v>
       </c>
       <c r="N4" s="3">
-        <v>-42.72</v>
+        <v>-138.26</v>
       </c>
       <c r="O4" s="3">
-        <v>-79.45</v>
+        <v>622.91</v>
       </c>
       <c r="P4" s="3">
-        <v>-42.01</v>
+        <v>758.68</v>
       </c>
       <c r="Q4" s="3">
-        <v>580.24</v>
+        <v>1896.59</v>
       </c>
       <c r="R4" s="3">
-        <v>686.37</v>
+        <v>1631.76</v>
       </c>
       <c r="S4" s="3">
-        <v>56.19</v>
+        <v>64.88</v>
       </c>
       <c r="T4" s="3">
-        <v>26.53</v>
+        <v>30.89</v>
       </c>
       <c r="U4" s="3">
-        <v>21.9</v>
+        <v>17.24</v>
       </c>
       <c r="V4" s="3">
-        <v>15.78</v>
+        <v>25.83</v>
       </c>
       <c r="W4" s="3">
         <v>0</v>
@@ -718,67 +718,67 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C5" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D5" s="1">
-        <v>16273.65</v>
+        <v>51917.65</v>
       </c>
       <c r="E5" s="2">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="F5" s="2">
-        <v>2.91</v>
+        <v>8.96</v>
       </c>
       <c r="G5" s="2">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="H5" s="2">
-        <v>-26.02</v>
+        <v>18.36</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>18247.13</v>
+        <v>47512.08</v>
       </c>
       <c r="K5" s="1">
-        <v>16062</v>
+        <v>50193.78</v>
       </c>
       <c r="L5" s="1">
-        <v>16878.88</v>
+        <v>51280.8</v>
       </c>
       <c r="M5" s="3">
-        <v>-196.69</v>
+        <v>-237.44</v>
       </c>
       <c r="N5" s="3">
-        <v>-278.81</v>
+        <v>-590.08</v>
       </c>
       <c r="O5" s="3">
-        <v>-687.75</v>
+        <v>941.54</v>
       </c>
       <c r="P5" s="3">
-        <v>-549.67</v>
+        <v>1429.07</v>
       </c>
       <c r="Q5" s="3">
-        <v>284.29</v>
+        <v>2441.31</v>
       </c>
       <c r="R5" s="3">
-        <v>930.65</v>
+        <v>1525.83</v>
       </c>
       <c r="S5" s="3">
-        <v>49.84</v>
+        <v>61.14</v>
       </c>
       <c r="T5" s="3">
-        <v>15.89</v>
+        <v>30.61</v>
       </c>
       <c r="U5" s="3">
-        <v>24.89</v>
+        <v>24.76</v>
       </c>
       <c r="V5" s="3">
-        <v>36.54</v>
+        <v>32.59</v>
       </c>
       <c r="W5" s="3">
         <v>0</v>
@@ -795,67 +795,67 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>India VIX</v>
       </c>
       <c r="C6" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>INDIAVIX</v>
       </c>
       <c r="D6" s="1">
-        <v>10665.05</v>
+        <v>15.3</v>
       </c>
       <c r="E6" s="2">
-        <v>2.08</v>
+        <v>1.19</v>
       </c>
       <c r="F6" s="2">
-        <v>2.89</v>
+        <v>-9.25</v>
       </c>
       <c r="G6" s="2">
-        <v>2.2</v>
+        <v>13.42</v>
       </c>
       <c r="H6" s="2">
-        <v>-27.45</v>
+        <v>61.39</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>12086.39</v>
+        <v>15.06</v>
       </c>
       <c r="K6" s="1">
-        <v>10529.19</v>
+        <v>15.59</v>
       </c>
       <c r="L6" s="1">
-        <v>11071.33</v>
+        <v>13.06</v>
       </c>
       <c r="M6" s="3">
-        <v>-131.9</v>
+        <v>0.82</v>
       </c>
       <c r="N6" s="3">
-        <v>-185.57</v>
+        <v>0.87</v>
       </c>
       <c r="O6" s="3">
-        <v>-495</v>
+        <v>-0.05</v>
       </c>
       <c r="P6" s="3">
-        <v>-409.59</v>
+        <v>-0.59</v>
       </c>
       <c r="Q6" s="3">
-        <v>-1.86</v>
+        <v>-0.05</v>
       </c>
       <c r="R6" s="3">
-        <v>427.05</v>
+        <v>0.03</v>
       </c>
       <c r="S6" s="3">
-        <v>49.66</v>
+        <v>54.27</v>
       </c>
       <c r="T6" s="3">
-        <v>15.76</v>
+        <v>17.24</v>
       </c>
       <c r="U6" s="3">
-        <v>24.94</v>
+        <v>19.5</v>
       </c>
       <c r="V6" s="3">
-        <v>36.93</v>
+        <v>15.79</v>
       </c>
       <c r="W6" s="3">
         <v>0</v>
@@ -872,67 +872,67 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C7" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D7" s="1">
-        <v>6032.3</v>
+        <v>30861.75</v>
       </c>
       <c r="E7" s="2">
-        <v>1.9</v>
+        <v>1.17</v>
       </c>
       <c r="F7" s="2">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="G7" s="2">
-        <v>-3.15</v>
+        <v>6.37</v>
       </c>
       <c r="H7" s="2">
-        <v>-5.23</v>
+        <v>-8.3</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>6730.98</v>
+        <v>30854.01</v>
       </c>
       <c r="K7" s="1">
-        <v>5985.81</v>
+        <v>30205.99</v>
       </c>
       <c r="L7" s="1">
-        <v>6251.04</v>
+        <v>30016.37</v>
       </c>
       <c r="M7" s="3">
-        <v>-91.15</v>
+        <v>182.49</v>
       </c>
       <c r="N7" s="3">
-        <v>-97.87</v>
+        <v>38.26</v>
       </c>
       <c r="O7" s="3">
-        <v>-211.97</v>
+        <v>-271.33</v>
       </c>
       <c r="P7" s="3">
-        <v>-161.06</v>
+        <v>-308.2</v>
       </c>
       <c r="Q7" s="3">
-        <v>235.38</v>
+        <v>556.06</v>
       </c>
       <c r="R7" s="3">
-        <v>404.23</v>
+        <v>1005.71</v>
       </c>
       <c r="S7" s="3">
-        <v>44.97</v>
+        <v>64.24</v>
       </c>
       <c r="T7" s="3">
-        <v>18.11</v>
+        <v>27.68</v>
       </c>
       <c r="U7" s="3">
-        <v>28.63</v>
+        <v>20.25</v>
       </c>
       <c r="V7" s="3">
-        <v>43.87</v>
+        <v>21.78</v>
       </c>
       <c r="W7" s="3">
         <v>0</v>
@@ -949,67 +949,67 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C8" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D8" s="1">
-        <v>7413.5</v>
+        <v>16436.2</v>
       </c>
       <c r="E8" s="2">
-        <v>1.72</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>1.79</v>
+        <v>3.93</v>
       </c>
       <c r="G8" s="2">
-        <v>4.77</v>
+        <v>3.3</v>
       </c>
       <c r="H8" s="2">
-        <v>-1.97</v>
+        <v>-25.28</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>7328.19</v>
+        <v>18219.35</v>
       </c>
       <c r="K8" s="1">
-        <v>7327.47</v>
+        <v>16130.03</v>
       </c>
       <c r="L8" s="1">
-        <v>7367.49</v>
+        <v>16842.47</v>
       </c>
       <c r="M8" s="3">
-        <v>13.02</v>
+        <v>-152.67</v>
       </c>
       <c r="N8" s="3">
-        <v>-8.88</v>
+        <v>-253.58</v>
       </c>
       <c r="O8" s="3">
-        <v>1.29</v>
+        <v>-674.78</v>
       </c>
       <c r="P8" s="3">
-        <v>24.76</v>
+        <v>-547.08</v>
       </c>
       <c r="Q8" s="3">
-        <v>477.06</v>
+        <v>297.25</v>
       </c>
       <c r="R8" s="3">
-        <v>553.62</v>
+        <v>933.24</v>
       </c>
       <c r="S8" s="3">
-        <v>56.44</v>
+        <v>52.49</v>
       </c>
       <c r="T8" s="3">
-        <v>22.52</v>
+        <v>18.9</v>
       </c>
       <c r="U8" s="3">
-        <v>23.61</v>
+        <v>23.57</v>
       </c>
       <c r="V8" s="3">
-        <v>23.58</v>
+        <v>34.72</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -1026,67 +1026,67 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C9" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D9" s="1">
-        <v>30506.2</v>
+        <v>10771.6</v>
       </c>
       <c r="E9" s="2">
-        <v>1.61</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>1.91</v>
+        <v>3.92</v>
       </c>
       <c r="G9" s="2">
-        <v>5.14</v>
+        <v>3.22</v>
       </c>
       <c r="H9" s="2">
-        <v>-9.36</v>
+        <v>-26.73</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>30869.01</v>
+        <v>12066.76</v>
       </c>
       <c r="K9" s="1">
-        <v>30060.26</v>
+        <v>10573.26</v>
       </c>
       <c r="L9" s="1">
-        <v>30014.33</v>
+        <v>11047.13</v>
       </c>
       <c r="M9" s="3">
-        <v>123.54</v>
+        <v>-103.09</v>
       </c>
       <c r="N9" s="3">
-        <v>2.2</v>
+        <v>-169.08</v>
       </c>
       <c r="O9" s="3">
-        <v>-299.7</v>
+        <v>-486.5</v>
       </c>
       <c r="P9" s="3">
-        <v>-313.87</v>
+        <v>-407.89</v>
       </c>
       <c r="Q9" s="3">
-        <v>527.7</v>
+        <v>6.64</v>
       </c>
       <c r="R9" s="3">
-        <v>1000.04</v>
+        <v>428.75</v>
       </c>
       <c r="S9" s="3">
-        <v>60.1</v>
+        <v>52.33</v>
       </c>
       <c r="T9" s="3">
-        <v>22.6</v>
+        <v>18.78</v>
       </c>
       <c r="U9" s="3">
-        <v>21.76</v>
+        <v>23.62</v>
       </c>
       <c r="V9" s="3">
-        <v>22.27</v>
+        <v>35.11</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
@@ -1103,67 +1103,67 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C10" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D10" s="1">
-        <v>8417.2</v>
+        <v>11113</v>
       </c>
       <c r="E10" s="2">
-        <v>1.43</v>
+        <v>0.78</v>
       </c>
       <c r="F10" s="2">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="G10" s="2">
-        <v>4.21</v>
+        <v>5.44</v>
       </c>
       <c r="H10" s="2">
-        <v>-16.2</v>
+        <v>-10.98</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>8731.32</v>
+        <v>11174.54</v>
       </c>
       <c r="K10" s="1">
-        <v>8323.01</v>
+        <v>10938.85</v>
       </c>
       <c r="L10" s="1">
-        <v>8363.64</v>
+        <v>11001.79</v>
       </c>
       <c r="M10" s="3">
-        <v>11.28</v>
+        <v>40.35</v>
       </c>
       <c r="N10" s="3">
-        <v>-12.73</v>
+        <v>-19.75</v>
       </c>
       <c r="O10" s="3">
-        <v>-146.83</v>
+        <v>-93.91</v>
       </c>
       <c r="P10" s="3">
-        <v>-156.44</v>
+        <v>-79.61</v>
       </c>
       <c r="Q10" s="3">
-        <v>-296.1</v>
+        <v>49.31</v>
       </c>
       <c r="R10" s="3">
-        <v>-190.55</v>
+        <v>180.1</v>
       </c>
       <c r="S10" s="3">
-        <v>57.32</v>
+        <v>61.03</v>
       </c>
       <c r="T10" s="3">
-        <v>20.9</v>
+        <v>25.21</v>
       </c>
       <c r="U10" s="3">
-        <v>21.95</v>
+        <v>18.84</v>
       </c>
       <c r="V10" s="3">
-        <v>20.02</v>
+        <v>24.97</v>
       </c>
       <c r="W10" s="3">
         <v>0</v>
@@ -1180,67 +1180,67 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D11" s="1">
-        <v>27052.6</v>
+        <v>19027.05</v>
       </c>
       <c r="E11" s="2">
-        <v>1.24</v>
+        <v>0.71</v>
       </c>
       <c r="F11" s="2">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="G11" s="2">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="H11" s="2">
-        <v>-5.81</v>
+        <v>-9.95</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>27320.97</v>
+        <v>19793.08</v>
       </c>
       <c r="K11" s="1">
-        <v>26928.09</v>
+        <v>18783.07</v>
       </c>
       <c r="L11" s="1">
-        <v>27228.94</v>
+        <v>19297</v>
       </c>
       <c r="M11" s="3">
-        <v>-94.87</v>
+        <v>-119.63</v>
       </c>
       <c r="N11" s="3">
-        <v>-75.37</v>
+        <v>-191.18</v>
       </c>
       <c r="O11" s="3">
-        <v>-65.05</v>
+        <v>-305.51</v>
       </c>
       <c r="P11" s="3">
-        <v>-1.21</v>
+        <v>-179.08</v>
       </c>
       <c r="Q11" s="3">
-        <v>661.56</v>
+        <v>783.12</v>
       </c>
       <c r="R11" s="3">
-        <v>878.2</v>
+        <v>1116.44</v>
       </c>
       <c r="S11" s="3">
-        <v>50.1</v>
+        <v>53.79</v>
       </c>
       <c r="T11" s="3">
-        <v>18.83</v>
+        <v>18.87</v>
       </c>
       <c r="U11" s="3">
-        <v>22.89</v>
+        <v>21.56</v>
       </c>
       <c r="V11" s="3">
-        <v>15.9</v>
+        <v>43.3</v>
       </c>
       <c r="W11" s="3">
         <v>0</v>
@@ -1257,67 +1257,67 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C12" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D12" s="1">
-        <v>68121.6</v>
+        <v>7463.35</v>
       </c>
       <c r="E12" s="2">
-        <v>1.22</v>
+        <v>0.67</v>
       </c>
       <c r="F12" s="2">
-        <v>3.48</v>
+        <v>2.48</v>
       </c>
       <c r="G12" s="2">
-        <v>-2.33</v>
+        <v>5.47</v>
       </c>
       <c r="H12" s="2">
-        <v>-1.79</v>
+        <v>-1.31</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>69959.44</v>
+        <v>7327.97</v>
       </c>
       <c r="K12" s="1">
-        <v>67686.28</v>
+        <v>7352.18</v>
       </c>
       <c r="L12" s="1">
-        <v>70907.28</v>
+        <v>7364.04</v>
       </c>
       <c r="M12" s="3">
-        <v>-1027.45</v>
+        <v>23.55</v>
       </c>
       <c r="N12" s="3">
-        <v>-1088.13</v>
+        <v>-2.39</v>
       </c>
       <c r="O12" s="3">
-        <v>-484.78</v>
+        <v>5.26</v>
       </c>
       <c r="P12" s="3">
-        <v>342.73</v>
+        <v>25.55</v>
       </c>
       <c r="Q12" s="3">
-        <v>2701.12</v>
+        <v>481.04</v>
       </c>
       <c r="R12" s="3">
-        <v>3189.85</v>
+        <v>554.41</v>
       </c>
       <c r="S12" s="3">
-        <v>44.92</v>
+        <v>58.92</v>
       </c>
       <c r="T12" s="3">
-        <v>17.79</v>
+        <v>25.7</v>
       </c>
       <c r="U12" s="3">
-        <v>33.04</v>
+        <v>22.64</v>
       </c>
       <c r="V12" s="3">
-        <v>47.06</v>
+        <v>22.35</v>
       </c>
       <c r="W12" s="3">
         <v>0</v>
@@ -1334,67 +1334,67 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C13" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D13" s="1">
-        <v>32498.35</v>
+        <v>8466.1</v>
       </c>
       <c r="E13" s="2">
-        <v>1.19</v>
+        <v>0.58</v>
       </c>
       <c r="F13" s="2">
-        <v>2.71</v>
+        <v>2.23</v>
       </c>
       <c r="G13" s="2">
-        <v>-1.1</v>
+        <v>4.81</v>
       </c>
       <c r="H13" s="2">
-        <v>-4.29</v>
+        <v>-15.71</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>33633.38</v>
+        <v>8724.08</v>
       </c>
       <c r="K13" s="1">
-        <v>32278.85</v>
+        <v>8349.02</v>
       </c>
       <c r="L13" s="1">
-        <v>33595.04</v>
+        <v>8361.76</v>
       </c>
       <c r="M13" s="3">
-        <v>-394.15</v>
+        <v>22.54</v>
       </c>
       <c r="N13" s="3">
-        <v>-447.39</v>
+        <v>-5.68</v>
       </c>
       <c r="O13" s="3">
-        <v>-340.93</v>
+        <v>-142.93</v>
       </c>
       <c r="P13" s="3">
-        <v>1.77</v>
+        <v>-155.66</v>
       </c>
       <c r="Q13" s="3">
-        <v>2018.8</v>
+        <v>-292.2</v>
       </c>
       <c r="R13" s="3">
-        <v>2433.68</v>
+        <v>-189.77</v>
       </c>
       <c r="S13" s="3">
-        <v>46.09</v>
+        <v>59.88</v>
       </c>
       <c r="T13" s="3">
-        <v>16.53</v>
+        <v>23.07</v>
       </c>
       <c r="U13" s="3">
-        <v>29.09</v>
+        <v>20.96</v>
       </c>
       <c r="V13" s="3">
-        <v>46.8</v>
+        <v>18.94</v>
       </c>
       <c r="W13" s="3">
         <v>0</v>
@@ -1411,67 +1411,67 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C14" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D14" s="1">
-        <v>18892.85</v>
+        <v>11375.55</v>
       </c>
       <c r="E14" s="2">
-        <v>1.19</v>
+        <v>0.57</v>
       </c>
       <c r="F14" s="2">
-        <v>1.77</v>
+        <v>0.84</v>
       </c>
       <c r="G14" s="2">
-        <v>0.57</v>
+        <v>2.07</v>
       </c>
       <c r="H14" s="2">
-        <v>-10.59</v>
+        <v>-14.31</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>19804.81</v>
+        <v>12121.15</v>
       </c>
       <c r="K14" s="1">
-        <v>18728.85</v>
+        <v>11311.74</v>
       </c>
       <c r="L14" s="1">
-        <v>19320.66</v>
+        <v>11472.79</v>
       </c>
       <c r="M14" s="3">
-        <v>-154.28</v>
+        <v>-30.66</v>
       </c>
       <c r="N14" s="3">
-        <v>-209.07</v>
+        <v>-51.77</v>
       </c>
       <c r="O14" s="3">
-        <v>-316.21</v>
+        <v>-259.73</v>
       </c>
       <c r="P14" s="3">
-        <v>-181.22</v>
+        <v>-241.03</v>
       </c>
       <c r="Q14" s="3">
-        <v>772.42</v>
+        <v>-126.06</v>
       </c>
       <c r="R14" s="3">
-        <v>1114.3</v>
+        <v>115.23</v>
       </c>
       <c r="S14" s="3">
-        <v>49.62</v>
+        <v>51.47</v>
       </c>
       <c r="T14" s="3">
-        <v>15.17</v>
+        <v>18.73</v>
       </c>
       <c r="U14" s="3">
-        <v>23.08</v>
+        <v>25.04</v>
       </c>
       <c r="V14" s="3">
-        <v>46.12</v>
+        <v>27.88</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1488,67 +1488,67 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C15" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D15" s="1">
-        <v>54909.65</v>
+        <v>13876.9</v>
       </c>
       <c r="E15" s="2">
-        <v>1.18</v>
+        <v>0.54</v>
       </c>
       <c r="F15" s="2">
-        <v>1.15</v>
+        <v>2.03</v>
       </c>
       <c r="G15" s="2">
-        <v>0.51</v>
+        <v>3.92</v>
       </c>
       <c r="H15" s="2">
-        <v>-7.84</v>
+        <v>-9.26</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>56730.45</v>
+        <v>14342.04</v>
       </c>
       <c r="K15" s="1">
-        <v>54719.04</v>
+        <v>13729.56</v>
       </c>
       <c r="L15" s="1">
-        <v>55999.88</v>
+        <v>13916.46</v>
       </c>
       <c r="M15" s="3">
-        <v>-388.39</v>
+        <v>-11.39</v>
       </c>
       <c r="N15" s="3">
-        <v>-381.74</v>
+        <v>-60.77</v>
       </c>
       <c r="O15" s="3">
-        <v>-452.22</v>
+        <v>-211.6</v>
       </c>
       <c r="P15" s="3">
-        <v>-177.87</v>
+        <v>-172.72</v>
       </c>
       <c r="Q15" s="3">
-        <v>1659.72</v>
+        <v>-525.7</v>
       </c>
       <c r="R15" s="3">
-        <v>2287.52</v>
+        <v>-489.68</v>
       </c>
       <c r="S15" s="3">
-        <v>47.07</v>
+        <v>55.11</v>
       </c>
       <c r="T15" s="3">
-        <v>15.97</v>
+        <v>23.38</v>
       </c>
       <c r="U15" s="3">
-        <v>23.84</v>
+        <v>22.44</v>
       </c>
       <c r="V15" s="3">
-        <v>25.39</v>
+        <v>21.33</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1565,67 +1565,67 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTY</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTY</v>
       </c>
       <c r="D16" s="1">
-        <v>35149.75</v>
+        <v>23053.1</v>
       </c>
       <c r="E16" s="2">
-        <v>1.18</v>
+        <v>0.51</v>
       </c>
       <c r="F16" s="2">
-        <v>3.62</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2">
-        <v>-4.04</v>
+        <v>1.91</v>
       </c>
       <c r="H16" s="2">
-        <v>-4.37</v>
+        <v>-11.77</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>37042.39</v>
+        <v>24034.58</v>
       </c>
       <c r="K16" s="1">
-        <v>35024.48</v>
+        <v>22825.89</v>
       </c>
       <c r="L16" s="1">
-        <v>37802.41</v>
+        <v>23254.75</v>
       </c>
       <c r="M16" s="3">
-        <v>-907.18</v>
+        <v>-83.59</v>
       </c>
       <c r="N16" s="3">
-        <v>-891.29</v>
+        <v>-153.65</v>
       </c>
       <c r="O16" s="3">
-        <v>-432.56</v>
+        <v>-387.88</v>
       </c>
       <c r="P16" s="3">
-        <v>149.9</v>
+        <v>-300.12</v>
       </c>
       <c r="Q16" s="3">
-        <v>630.86</v>
+        <v>213.33</v>
       </c>
       <c r="R16" s="3">
-        <v>938.34</v>
+        <v>603.52</v>
       </c>
       <c r="S16" s="3">
-        <v>40.13</v>
+        <v>53.5</v>
       </c>
       <c r="T16" s="3">
-        <v>14.83</v>
+        <v>19.19</v>
       </c>
       <c r="U16" s="3">
-        <v>32.72</v>
+        <v>23.09</v>
       </c>
       <c r="V16" s="3">
-        <v>55.44</v>
+        <v>32.81</v>
       </c>
       <c r="W16" s="3">
         <v>0</v>
@@ -1642,67 +1642,67 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C17" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D17" s="1">
-        <v>24911.55</v>
+        <v>31194.45</v>
       </c>
       <c r="E17" s="2">
-        <v>1.18</v>
+        <v>0.49</v>
       </c>
       <c r="F17" s="2">
-        <v>5.26</v>
+        <v>2.73</v>
       </c>
       <c r="G17" s="2">
-        <v>-1.9</v>
+        <v>0.94</v>
       </c>
       <c r="H17" s="2">
-        <v>-0.3</v>
+        <v>-6.41</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>25449.16</v>
+        <v>32268.03</v>
       </c>
       <c r="K17" s="1">
-        <v>24660.16</v>
+        <v>30850.03</v>
       </c>
       <c r="L17" s="1">
-        <v>25919.88</v>
+        <v>31674.86</v>
       </c>
       <c r="M17" s="3">
-        <v>-411.03</v>
+        <v>-196.9</v>
       </c>
       <c r="N17" s="3">
-        <v>-420.97</v>
+        <v>-305.62</v>
       </c>
       <c r="O17" s="3">
-        <v>-155.07</v>
+        <v>-408.48</v>
       </c>
       <c r="P17" s="3">
-        <v>132.77</v>
+        <v>-176.41</v>
       </c>
       <c r="Q17" s="3">
-        <v>101.13</v>
+        <v>1873.58</v>
       </c>
       <c r="R17" s="3">
-        <v>-48.22</v>
+        <v>2382.2</v>
       </c>
       <c r="S17" s="3">
-        <v>46.58</v>
+        <v>52.33</v>
       </c>
       <c r="T17" s="3">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="U17" s="3">
-        <v>34.9</v>
+        <v>24.72</v>
       </c>
       <c r="V17" s="3">
-        <v>41.99</v>
+        <v>40.6</v>
       </c>
       <c r="W17" s="3">
         <v>0</v>
@@ -1719,67 +1719,67 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C18" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D18" s="1">
-        <v>8792.5</v>
+        <v>6058</v>
       </c>
       <c r="E18" s="2">
-        <v>1.18</v>
+        <v>0.43</v>
       </c>
       <c r="F18" s="2">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
       <c r="G18" s="2">
-        <v>0.67</v>
+        <v>-2.74</v>
       </c>
       <c r="H18" s="2">
-        <v>-8.57</v>
+        <v>-4.83</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>9201.62</v>
+        <v>6728.41</v>
       </c>
       <c r="K18" s="1">
-        <v>8683.49</v>
+        <v>5998.93</v>
       </c>
       <c r="L18" s="1">
-        <v>8941.08</v>
+        <v>6242.88</v>
       </c>
       <c r="M18" s="3">
-        <v>-64.04</v>
+        <v>-79.55</v>
       </c>
       <c r="N18" s="3">
-        <v>-99.49</v>
+        <v>-94.21</v>
       </c>
       <c r="O18" s="3">
-        <v>-165.15</v>
+        <v>-209.92</v>
       </c>
       <c r="P18" s="3">
-        <v>-97.49</v>
+        <v>-160.65</v>
       </c>
       <c r="Q18" s="3">
-        <v>283.03</v>
+        <v>237.43</v>
       </c>
       <c r="R18" s="3">
-        <v>435.99</v>
+        <v>404.64</v>
       </c>
       <c r="S18" s="3">
-        <v>52.24</v>
+        <v>47.16</v>
       </c>
       <c r="T18" s="3">
-        <v>19.95</v>
+        <v>18.45</v>
       </c>
       <c r="U18" s="3">
-        <v>23.24</v>
+        <v>26.68</v>
       </c>
       <c r="V18" s="3">
-        <v>35.56</v>
+        <v>42.04</v>
       </c>
       <c r="W18" s="3">
         <v>0</v>
@@ -1796,67 +1796,67 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C19" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D19" s="1">
-        <v>24704.55</v>
+        <v>3816.35</v>
       </c>
       <c r="E19" s="2">
-        <v>1.17</v>
+        <v>0.36</v>
       </c>
       <c r="F19" s="2">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="G19" s="2">
-        <v>0.22</v>
+        <v>0.9</v>
       </c>
       <c r="H19" s="2">
-        <v>-10.53</v>
+        <v>-12.33</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>26139.7</v>
+        <v>4016.6</v>
       </c>
       <c r="K19" s="1">
-        <v>24649.06</v>
+        <v>3790.7</v>
       </c>
       <c r="L19" s="1">
-        <v>25337.92</v>
+        <v>3887.54</v>
       </c>
       <c r="M19" s="3">
-        <v>-221.84</v>
+        <v>-23.77</v>
       </c>
       <c r="N19" s="3">
-        <v>-211.51</v>
+        <v>-33.56</v>
       </c>
       <c r="O19" s="3">
-        <v>-404.24</v>
+        <v>-69.84</v>
       </c>
       <c r="P19" s="3">
-        <v>-262.41</v>
+        <v>-48.45</v>
       </c>
       <c r="Q19" s="3">
-        <v>651.98</v>
+        <v>128.13</v>
       </c>
       <c r="R19" s="3">
-        <v>1081.96</v>
+        <v>207.15</v>
       </c>
       <c r="S19" s="3">
-        <v>45.72</v>
+        <v>49.84</v>
       </c>
       <c r="T19" s="3">
-        <v>15.57</v>
+        <v>18.56</v>
       </c>
       <c r="U19" s="3">
-        <v>25.31</v>
+        <v>25.85</v>
       </c>
       <c r="V19" s="3">
-        <v>28.36</v>
+        <v>34.98</v>
       </c>
       <c r="W19" s="3">
         <v>0</v>
@@ -1873,67 +1873,67 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D20" s="1">
-        <v>5575.15</v>
+        <v>5415.4</v>
       </c>
       <c r="E20" s="2">
-        <v>1.16</v>
+        <v>0.31</v>
       </c>
       <c r="F20" s="2">
-        <v>1.17</v>
+        <v>2.14</v>
       </c>
       <c r="G20" s="2">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="H20" s="2">
-        <v>-12.69</v>
+        <v>-7.59</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>5931.72</v>
+        <v>5532.51</v>
       </c>
       <c r="K20" s="1">
-        <v>5543.85</v>
+        <v>5374.35</v>
       </c>
       <c r="L20" s="1">
-        <v>5644.24</v>
+        <v>5472.91</v>
       </c>
       <c r="M20" s="3">
-        <v>-17.99</v>
+        <v>-16.93</v>
       </c>
       <c r="N20" s="3">
-        <v>-32.73</v>
+        <v>-31.08</v>
       </c>
       <c r="O20" s="3">
-        <v>-118.99</v>
+        <v>-49.64</v>
       </c>
       <c r="P20" s="3">
-        <v>-100.95</v>
+        <v>-24.73</v>
       </c>
       <c r="Q20" s="3">
-        <v>26.94</v>
+        <v>191.51</v>
       </c>
       <c r="R20" s="3">
-        <v>139.87</v>
+        <v>261.97</v>
       </c>
       <c r="S20" s="3">
-        <v>51.18</v>
+        <v>52.26</v>
       </c>
       <c r="T20" s="3">
-        <v>19.88</v>
+        <v>21.01</v>
       </c>
       <c r="U20" s="3">
-        <v>27.37</v>
+        <v>25.91</v>
       </c>
       <c r="V20" s="3">
-        <v>32.26</v>
+        <v>34.38</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1950,67 +1950,67 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D21" s="1">
-        <v>4739.85</v>
+        <v>23971.55</v>
       </c>
       <c r="E21" s="2">
-        <v>1.16</v>
+        <v>0.3</v>
       </c>
       <c r="F21" s="2">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="G21" s="2">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2">
-        <v>-8.52</v>
+        <v>-10.18</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>4901.89</v>
+        <v>24947.34</v>
       </c>
       <c r="K21" s="1">
-        <v>4701.28</v>
+        <v>23777.06</v>
       </c>
       <c r="L21" s="1">
-        <v>4826.57</v>
+        <v>24340.46</v>
       </c>
       <c r="M21" s="3">
-        <v>-29.73</v>
+        <v>-132.91</v>
       </c>
       <c r="N21" s="3">
-        <v>-42.23</v>
+        <v>-199.11</v>
       </c>
       <c r="O21" s="3">
-        <v>-55.81</v>
+        <v>-362.33</v>
       </c>
       <c r="P21" s="3">
-        <v>-25.53</v>
+        <v>-232.4</v>
       </c>
       <c r="Q21" s="3">
-        <v>223.71</v>
+        <v>350.65</v>
       </c>
       <c r="R21" s="3">
-        <v>300.17</v>
+        <v>712.3</v>
       </c>
       <c r="S21" s="3">
-        <v>50.58</v>
+        <v>51.14</v>
       </c>
       <c r="T21" s="3">
-        <v>17.99</v>
+        <v>17.94</v>
       </c>
       <c r="U21" s="3">
-        <v>26.88</v>
+        <v>25.26</v>
       </c>
       <c r="V21" s="3">
-        <v>35.94</v>
+        <v>39.66</v>
       </c>
       <c r="W21" s="3">
         <v>0</v>
@@ -2027,67 +2027,67 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C22" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D22" s="1">
-        <v>59829.15</v>
+        <v>11090.7</v>
       </c>
       <c r="E22" s="2">
-        <v>1.15</v>
+        <v>0.29</v>
       </c>
       <c r="F22" s="2">
-        <v>5.31</v>
+        <v>3.39</v>
       </c>
       <c r="G22" s="2">
-        <v>-1.55</v>
+        <v>0.16</v>
       </c>
       <c r="H22" s="2">
-        <v>-3.37</v>
+        <v>-9.75</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>61629.62</v>
+        <v>11456.61</v>
       </c>
       <c r="K22" s="1">
-        <v>59158.88</v>
+        <v>10953.62</v>
       </c>
       <c r="L22" s="1">
-        <v>62028.04</v>
+        <v>11336.26</v>
       </c>
       <c r="M22" s="3">
-        <v>-947.36</v>
+        <v>-96.02</v>
       </c>
       <c r="N22" s="3">
-        <v>-989.74</v>
+        <v>-145.04</v>
       </c>
       <c r="O22" s="3">
-        <v>-587.4</v>
+        <v>-162.81</v>
       </c>
       <c r="P22" s="3">
-        <v>33.45</v>
+        <v>-67.1</v>
       </c>
       <c r="Q22" s="3">
-        <v>-8.01</v>
+        <v>237.69</v>
       </c>
       <c r="R22" s="3">
-        <v>-174.53</v>
+        <v>398.2</v>
       </c>
       <c r="S22" s="3">
-        <v>47.04</v>
+        <v>51.43</v>
       </c>
       <c r="T22" s="3">
-        <v>17.68</v>
+        <v>21.13</v>
       </c>
       <c r="U22" s="3">
-        <v>34.77</v>
+        <v>25.37</v>
       </c>
       <c r="V22" s="3">
-        <v>44.54</v>
+        <v>41.49</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2104,67 +2104,67 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C23" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D23" s="1">
-        <v>9097.1</v>
+        <v>7613.45</v>
       </c>
       <c r="E23" s="2">
-        <v>1.15</v>
+        <v>0.29</v>
       </c>
       <c r="F23" s="2">
-        <v>2.38</v>
+        <v>3.49</v>
       </c>
       <c r="G23" s="2">
-        <v>-2.81</v>
+        <v>-1.18</v>
       </c>
       <c r="H23" s="2">
-        <v>-7.68</v>
+        <v>-11.51</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>9963.62</v>
+        <v>7655.77</v>
       </c>
       <c r="K23" s="1">
-        <v>9076.29</v>
+        <v>7546.28</v>
       </c>
       <c r="L23" s="1">
-        <v>9452.48</v>
+        <v>7706.08</v>
       </c>
       <c r="M23" s="3">
-        <v>-127.61</v>
+        <v>-38.79</v>
       </c>
       <c r="N23" s="3">
-        <v>-133.08</v>
+        <v>-66.97</v>
       </c>
       <c r="O23" s="3">
-        <v>-253.86</v>
+        <v>-67.32</v>
       </c>
       <c r="P23" s="3">
-        <v>-170.88</v>
+        <v>-28.54</v>
       </c>
       <c r="Q23" s="3">
-        <v>792.92</v>
+        <v>-285.19</v>
       </c>
       <c r="R23" s="3">
-        <v>1092.01</v>
+        <v>-244.22</v>
       </c>
       <c r="S23" s="3">
-        <v>43.09</v>
+        <v>51.52</v>
       </c>
       <c r="T23" s="3">
-        <v>14.03</v>
+        <v>21.03</v>
       </c>
       <c r="U23" s="3">
-        <v>33.17</v>
+        <v>21.42</v>
       </c>
       <c r="V23" s="3">
-        <v>48.99</v>
+        <v>21.46</v>
       </c>
       <c r="W23" s="3">
         <v>0</v>
@@ -2181,67 +2181,67 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C24" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D24" s="1">
-        <v>8882.9</v>
+        <v>8602.1</v>
       </c>
       <c r="E24" s="2">
-        <v>1.14</v>
+        <v>0.26</v>
       </c>
       <c r="F24" s="2">
-        <v>3.76</v>
+        <v>2.1</v>
       </c>
       <c r="G24" s="2">
-        <v>-4.25</v>
+        <v>7.17</v>
       </c>
       <c r="H24" s="2">
-        <v>14.66</v>
+        <v>-8.71</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>8861.48</v>
+        <v>8229.34</v>
       </c>
       <c r="K24" s="1">
-        <v>8882.17</v>
+        <v>8520.67</v>
       </c>
       <c r="L24" s="1">
-        <v>9377.19</v>
+        <v>8508.22</v>
       </c>
       <c r="M24" s="3">
-        <v>-165.1</v>
+        <v>49.69</v>
       </c>
       <c r="N24" s="3">
-        <v>-150.55</v>
+        <v>19.06</v>
       </c>
       <c r="O24" s="3">
-        <v>47.18</v>
+        <v>70.14</v>
       </c>
       <c r="P24" s="3">
-        <v>194.18</v>
+        <v>60.25</v>
       </c>
       <c r="Q24" s="3">
-        <v>608.74</v>
+        <v>379.31</v>
       </c>
       <c r="R24" s="3">
-        <v>523.85</v>
+        <v>515.11</v>
       </c>
       <c r="S24" s="3">
-        <v>43.04</v>
+        <v>57.13</v>
       </c>
       <c r="T24" s="3">
-        <v>20.13</v>
+        <v>23.59</v>
       </c>
       <c r="U24" s="3">
-        <v>33.83</v>
+        <v>21.43</v>
       </c>
       <c r="V24" s="3">
-        <v>28.85</v>
+        <v>16.56</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2258,67 +2258,67 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D25" s="1">
-        <v>53204.45</v>
+        <v>4751.05</v>
       </c>
       <c r="E25" s="2">
-        <v>1.13</v>
+        <v>0.24</v>
       </c>
       <c r="F25" s="2">
-        <v>6.6</v>
+        <v>2.22</v>
       </c>
       <c r="G25" s="2">
-        <v>-1.62</v>
+        <v>1.43</v>
       </c>
       <c r="H25" s="2">
-        <v>5.76</v>
+        <v>-8.3</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>52229.25</v>
+        <v>4899.34</v>
       </c>
       <c r="K25" s="1">
-        <v>52698.84</v>
+        <v>4710.33</v>
       </c>
       <c r="L25" s="1">
-        <v>55129.46</v>
+        <v>4820.7</v>
       </c>
       <c r="M25" s="3">
-        <v>-852.9</v>
+        <v>-23.61</v>
       </c>
       <c r="N25" s="3">
-        <v>-777.13</v>
+        <v>-38.51</v>
       </c>
       <c r="O25" s="3">
-        <v>374.85</v>
+        <v>-54.92</v>
       </c>
       <c r="P25" s="3">
-        <v>964.97</v>
+        <v>-25.36</v>
       </c>
       <c r="Q25" s="3">
-        <v>3717.32</v>
+        <v>224.6</v>
       </c>
       <c r="R25" s="3">
-        <v>3892.3</v>
+        <v>300.35</v>
       </c>
       <c r="S25" s="3">
-        <v>46.99</v>
+        <v>51.77</v>
       </c>
       <c r="T25" s="3">
-        <v>18.91</v>
+        <v>20.14</v>
       </c>
       <c r="U25" s="3">
-        <v>37.69</v>
+        <v>25.5</v>
       </c>
       <c r="V25" s="3">
-        <v>36.53</v>
+        <v>34.21</v>
       </c>
       <c r="W25" s="3">
         <v>0</v>
@@ -2335,67 +2335,67 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C26" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D26" s="1">
-        <v>5203.75</v>
+        <v>5587.65</v>
       </c>
       <c r="E26" s="2">
-        <v>1.11</v>
+        <v>0.22</v>
       </c>
       <c r="F26" s="2">
-        <v>5.55</v>
+        <v>1.4</v>
       </c>
       <c r="G26" s="2">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="H26" s="2">
-        <v>11.76</v>
+        <v>-12.49</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>5115.54</v>
+        <v>5927.61</v>
       </c>
       <c r="K26" s="1">
-        <v>5132.76</v>
+        <v>5551.82</v>
       </c>
       <c r="L26" s="1">
-        <v>5277.98</v>
+        <v>5638.69</v>
       </c>
       <c r="M26" s="3">
-        <v>-43.41</v>
+        <v>-13.03</v>
       </c>
       <c r="N26" s="3">
-        <v>-46.85</v>
+        <v>-28.79</v>
       </c>
       <c r="O26" s="3">
-        <v>14.59</v>
+        <v>-118</v>
       </c>
       <c r="P26" s="3">
-        <v>70.51</v>
+        <v>-100.76</v>
       </c>
       <c r="Q26" s="3">
-        <v>375.61</v>
+        <v>27.94</v>
       </c>
       <c r="R26" s="3">
-        <v>327.58</v>
+        <v>140.07</v>
       </c>
       <c r="S26" s="3">
-        <v>51.16</v>
+        <v>52.31</v>
       </c>
       <c r="T26" s="3">
-        <v>21.42</v>
+        <v>20.9</v>
       </c>
       <c r="U26" s="3">
-        <v>26.75</v>
+        <v>26.1</v>
       </c>
       <c r="V26" s="3">
-        <v>22.73</v>
+        <v>30.75</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
@@ -2412,67 +2412,67 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C27" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D27" s="1">
-        <v>3802.55</v>
+        <v>24957.7</v>
       </c>
       <c r="E27" s="2">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="F27" s="2">
-        <v>1.31</v>
+        <v>2.5</v>
       </c>
       <c r="G27" s="2">
-        <v>0.54</v>
+        <v>-1.04</v>
       </c>
       <c r="H27" s="2">
-        <v>-12.65</v>
+        <v>-7.83</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>4019.47</v>
+        <v>26177.31</v>
       </c>
       <c r="K27" s="1">
-        <v>3785</v>
+        <v>24768.59</v>
       </c>
       <c r="L27" s="1">
-        <v>3892.55</v>
+        <v>25798.54</v>
       </c>
       <c r="M27" s="3">
-        <v>-28.21</v>
+        <v>-281.5</v>
       </c>
       <c r="N27" s="3">
-        <v>-36.01</v>
+        <v>-376.11</v>
       </c>
       <c r="O27" s="3">
-        <v>-70.94</v>
+        <v>-391.67</v>
       </c>
       <c r="P27" s="3">
-        <v>-48.67</v>
+        <v>-134.92</v>
       </c>
       <c r="Q27" s="3">
-        <v>127.03</v>
+        <v>1176.92</v>
       </c>
       <c r="R27" s="3">
-        <v>206.93</v>
+        <v>1602.11</v>
       </c>
       <c r="S27" s="3">
-        <v>47.95</v>
+        <v>46.66</v>
       </c>
       <c r="T27" s="3">
-        <v>16.61</v>
+        <v>16.69</v>
       </c>
       <c r="U27" s="3">
-        <v>27.25</v>
+        <v>24.52</v>
       </c>
       <c r="V27" s="3">
-        <v>36.41</v>
+        <v>46.81</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
@@ -2489,67 +2489,67 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D28" s="1">
-        <v>1655.35</v>
+        <v>1259.69</v>
       </c>
       <c r="E28" s="2">
-        <v>1.1</v>
+        <v>0.16</v>
       </c>
       <c r="F28" s="2">
-        <v>5.88</v>
+        <v>0.36</v>
       </c>
       <c r="G28" s="2">
-        <v>4.56</v>
+        <v>-1.06</v>
       </c>
       <c r="H28" s="2">
-        <v>14.58</v>
+        <v>-0.15</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>1472.63</v>
+        <v>1268.25</v>
       </c>
       <c r="K28" s="1">
-        <v>1613.51</v>
+        <v>1259.92</v>
       </c>
       <c r="L28" s="1">
-        <v>1576.86</v>
+        <v>1275.73</v>
       </c>
       <c r="M28" s="3">
-        <v>15.95</v>
+        <v>-5.77</v>
       </c>
       <c r="N28" s="3">
-        <v>13.34</v>
+        <v>-5.52</v>
       </c>
       <c r="O28" s="3">
-        <v>35.94</v>
+        <v>-0.56</v>
       </c>
       <c r="P28" s="3">
-        <v>32.24</v>
+        <v>3.75</v>
       </c>
       <c r="Q28" s="3">
-        <v>-67.63</v>
+        <v>21.08</v>
       </c>
       <c r="R28" s="3">
-        <v>-104.42</v>
+        <v>21.91</v>
       </c>
       <c r="S28" s="3">
-        <v>60.64</v>
+        <v>32.14</v>
       </c>
       <c r="T28" s="3">
-        <v>27.7</v>
+        <v>31.87</v>
       </c>
       <c r="U28" s="3">
-        <v>22.74</v>
+        <v>66.15</v>
       </c>
       <c r="V28" s="3">
-        <v>15.68</v>
+        <v>45.78</v>
       </c>
       <c r="W28" s="3">
         <v>0</v>
@@ -2566,67 +2566,67 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="C29" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="D29" s="1">
-        <v>13630.35</v>
+        <v>1303.05</v>
       </c>
       <c r="E29" s="2">
-        <v>1.09</v>
+        <v>0.11</v>
       </c>
       <c r="F29" s="2">
-        <v>3.48</v>
+        <v>0.22</v>
       </c>
       <c r="G29" s="2">
-        <v>-0.87</v>
+        <v>-0.95</v>
       </c>
       <c r="H29" s="2">
-        <v>-5.81</v>
+        <v>0.38</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>14120.26</v>
+        <v>1308.11</v>
       </c>
       <c r="K29" s="1">
-        <v>13486.39</v>
+        <v>1304.08</v>
       </c>
       <c r="L29" s="1">
-        <v>14013.31</v>
+        <v>1317.8</v>
       </c>
       <c r="M29" s="3">
-        <v>-154.34</v>
+        <v>-5.04</v>
       </c>
       <c r="N29" s="3">
-        <v>-191.97</v>
+        <v>-4.72</v>
       </c>
       <c r="O29" s="3">
-        <v>-193.64</v>
+        <v>0.54</v>
       </c>
       <c r="P29" s="3">
-        <v>-52.9</v>
+        <v>4.59</v>
       </c>
       <c r="Q29" s="3">
-        <v>95.04</v>
+        <v>23.72</v>
       </c>
       <c r="R29" s="3">
-        <v>122.19</v>
+        <v>24.16</v>
       </c>
       <c r="S29" s="3">
-        <v>48.75</v>
+        <v>29.29</v>
       </c>
       <c r="T29" s="3">
-        <v>18.43</v>
+        <v>29.11</v>
       </c>
       <c r="U29" s="3">
-        <v>29</v>
+        <v>68.16</v>
       </c>
       <c r="V29" s="3">
-        <v>41.91</v>
+        <v>43.49</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2643,67 +2643,67 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTY100</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTY100</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D30" s="1">
-        <v>23899.15</v>
+        <v>1443.08</v>
       </c>
       <c r="E30" s="2">
-        <v>1.08</v>
+        <v>0.08</v>
       </c>
       <c r="F30" s="2">
-        <v>1.85</v>
+        <v>0.18</v>
       </c>
       <c r="G30" s="2">
-        <v>0.69</v>
+        <v>-0.74</v>
       </c>
       <c r="H30" s="2">
-        <v>-10.45</v>
+        <v>1.29</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>24961.39</v>
+        <v>1441.29</v>
       </c>
       <c r="K30" s="1">
-        <v>23733.84</v>
+        <v>1443.91</v>
       </c>
       <c r="L30" s="1">
-        <v>24367.71</v>
+        <v>1455.11</v>
       </c>
       <c r="M30" s="3">
-        <v>-163.27</v>
+        <v>-4.18</v>
       </c>
       <c r="N30" s="3">
-        <v>-215.66</v>
+        <v>-3.85</v>
       </c>
       <c r="O30" s="3">
-        <v>-368.1</v>
+        <v>2.72</v>
       </c>
       <c r="P30" s="3">
-        <v>-233.56</v>
+        <v>6.34</v>
       </c>
       <c r="Q30" s="3">
-        <v>344.87</v>
+        <v>28.94</v>
       </c>
       <c r="R30" s="3">
-        <v>711.14</v>
+        <v>28.51</v>
       </c>
       <c r="S30" s="3">
-        <v>49.51</v>
+        <v>30.83</v>
       </c>
       <c r="T30" s="3">
-        <v>16</v>
+        <v>27.64</v>
       </c>
       <c r="U30" s="3">
-        <v>26.61</v>
+        <v>63.43</v>
       </c>
       <c r="V30" s="3">
-        <v>41.4</v>
+        <v>40.11</v>
       </c>
       <c r="W30" s="3">
         <v>0</v>
@@ -2720,67 +2720,67 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D31" s="1">
-        <v>8579.95</v>
+        <v>8799</v>
       </c>
       <c r="E31" s="2">
-        <v>1.07</v>
+        <v>0.07</v>
       </c>
       <c r="F31" s="2">
-        <v>1.84</v>
+        <v>2.86</v>
       </c>
       <c r="G31" s="2">
-        <v>6.89</v>
+        <v>0.75</v>
       </c>
       <c r="H31" s="2">
-        <v>-8.94</v>
+        <v>-8.5</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>8233.82</v>
+        <v>9197.8</v>
       </c>
       <c r="K31" s="1">
-        <v>8502.57</v>
+        <v>8704.49</v>
       </c>
       <c r="L31" s="1">
-        <v>8508.7</v>
+        <v>8929.53</v>
       </c>
       <c r="M31" s="3">
-        <v>43.75</v>
+        <v>-50.05</v>
       </c>
       <c r="N31" s="3">
-        <v>11.4</v>
+        <v>-89.6</v>
       </c>
       <c r="O31" s="3">
-        <v>68.37</v>
+        <v>-164.63</v>
       </c>
       <c r="P31" s="3">
-        <v>59.9</v>
+        <v>-97.39</v>
       </c>
       <c r="Q31" s="3">
-        <v>377.54</v>
+        <v>283.55</v>
       </c>
       <c r="R31" s="3">
-        <v>514.75</v>
+        <v>436.1</v>
       </c>
       <c r="S31" s="3">
-        <v>56.26</v>
+        <v>52.59</v>
       </c>
       <c r="T31" s="3">
-        <v>20.82</v>
+        <v>19.04</v>
       </c>
       <c r="U31" s="3">
-        <v>22.32</v>
+        <v>22.18</v>
       </c>
       <c r="V31" s="3">
-        <v>17.46</v>
+        <v>33.56</v>
       </c>
       <c r="W31" s="3">
         <v>0</v>
@@ -2797,67 +2797,67 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>NIFTY200</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C32" t="str">
-        <v>NIFTY200</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D32" s="1">
-        <v>13176.05</v>
+        <v>1597.89</v>
       </c>
       <c r="E32" s="2">
-        <v>1.06</v>
+        <v>0.07</v>
       </c>
       <c r="F32" s="2">
-        <v>2.2</v>
+        <v>0.11</v>
       </c>
       <c r="G32" s="2">
-        <v>0.05</v>
+        <v>-0.56</v>
       </c>
       <c r="H32" s="2">
-        <v>-9.34</v>
+        <v>1.98</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>13753.84</v>
+        <v>1587.6</v>
       </c>
       <c r="K32" s="1">
-        <v>13092.38</v>
+        <v>1598.75</v>
       </c>
       <c r="L32" s="1">
-        <v>13519.43</v>
+        <v>1606.79</v>
       </c>
       <c r="M32" s="3">
-        <v>-120.03</v>
+        <v>-3.17</v>
       </c>
       <c r="N32" s="3">
-        <v>-143.67</v>
+        <v>-2.73</v>
       </c>
       <c r="O32" s="3">
-        <v>-189.92</v>
+        <v>5.53</v>
       </c>
       <c r="P32" s="3">
-        <v>-94.96</v>
+        <v>8.54</v>
       </c>
       <c r="Q32" s="3">
-        <v>278.03</v>
+        <v>34.62</v>
       </c>
       <c r="R32" s="3">
-        <v>466</v>
+        <v>33.07</v>
       </c>
       <c r="S32" s="3">
-        <v>47.7</v>
+        <v>32.97</v>
       </c>
       <c r="T32" s="3">
-        <v>15.11</v>
+        <v>23.73</v>
       </c>
       <c r="U32" s="3">
-        <v>28.52</v>
+        <v>61.57</v>
       </c>
       <c r="V32" s="3">
-        <v>45.6</v>
+        <v>36.08</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -2874,67 +2874,67 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTY</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTY</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D33" s="1">
-        <v>22936.75</v>
+        <v>13183.95</v>
       </c>
       <c r="E33" s="2">
-        <v>1.05</v>
+        <v>0.06</v>
       </c>
       <c r="F33" s="2">
-        <v>1.49</v>
+        <v>2.26</v>
       </c>
       <c r="G33" s="2">
-        <v>1.4</v>
+        <v>0.11</v>
       </c>
       <c r="H33" s="2">
-        <v>-12.22</v>
+        <v>-9.29</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>24050.01</v>
+        <v>13746.68</v>
       </c>
       <c r="K33" s="1">
-        <v>22775.4</v>
+        <v>13109.03</v>
       </c>
       <c r="L33" s="1">
-        <v>23276.78</v>
+        <v>13501.78</v>
       </c>
       <c r="M33" s="3">
-        <v>-114.18</v>
+        <v>-104.69</v>
       </c>
       <c r="N33" s="3">
-        <v>-171.17</v>
+        <v>-135.88</v>
       </c>
       <c r="O33" s="3">
-        <v>-397.16</v>
+        <v>-189.29</v>
       </c>
       <c r="P33" s="3">
-        <v>-301.97</v>
+        <v>-94.83</v>
       </c>
       <c r="Q33" s="3">
-        <v>204.05</v>
+        <v>278.66</v>
       </c>
       <c r="R33" s="3">
-        <v>601.66</v>
+        <v>466.12</v>
       </c>
       <c r="S33" s="3">
-        <v>50.85</v>
+        <v>48.04</v>
       </c>
       <c r="T33" s="3">
-        <v>16.16</v>
+        <v>16.07</v>
       </c>
       <c r="U33" s="3">
-        <v>24.38</v>
+        <v>27.18</v>
       </c>
       <c r="V33" s="3">
-        <v>34.62</v>
+        <v>44.18</v>
       </c>
       <c r="W33" s="3">
         <v>0</v>
@@ -2951,67 +2951,67 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C34" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D34" s="1">
-        <v>11059.15</v>
+        <v>18937.8</v>
       </c>
       <c r="E34" s="2">
-        <v>1.05</v>
+        <v>0.04</v>
       </c>
       <c r="F34" s="2">
-        <v>3.1</v>
+        <v>1.38</v>
       </c>
       <c r="G34" s="2">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="H34" s="2">
-        <v>-10.01</v>
+        <v>-11.55</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>11462.41</v>
+        <v>20020.04</v>
       </c>
       <c r="K34" s="1">
-        <v>10923.16</v>
+        <v>18940.72</v>
       </c>
       <c r="L34" s="1">
-        <v>11354.54</v>
+        <v>19573.7</v>
       </c>
       <c r="M34" s="3">
-        <v>-117.6</v>
+        <v>-175.94</v>
       </c>
       <c r="N34" s="3">
-        <v>-157.29</v>
+        <v>-195.35</v>
       </c>
       <c r="O34" s="3">
-        <v>-165.32</v>
+        <v>-327.41</v>
       </c>
       <c r="P34" s="3">
-        <v>-67.6</v>
+        <v>-182.6</v>
       </c>
       <c r="Q34" s="3">
-        <v>235.17</v>
+        <v>483.37</v>
       </c>
       <c r="R34" s="3">
-        <v>397.7</v>
+        <v>794.72</v>
       </c>
       <c r="S34" s="3">
-        <v>50.1</v>
+        <v>44.02</v>
       </c>
       <c r="T34" s="3">
-        <v>19.05</v>
+        <v>14.96</v>
       </c>
       <c r="U34" s="3">
-        <v>26.73</v>
+        <v>30.39</v>
       </c>
       <c r="V34" s="3">
-        <v>43.98</v>
+        <v>41.38</v>
       </c>
       <c r="W34" s="3">
         <v>0</v>
@@ -3028,67 +3028,67 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D35" s="1">
-        <v>8986.45</v>
+        <v>24712.2</v>
       </c>
       <c r="E35" s="2">
-        <v>1.05</v>
+        <v>0.03</v>
       </c>
       <c r="F35" s="2">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="G35" s="2">
-        <v>-3.48</v>
+        <v>0.25</v>
       </c>
       <c r="H35" s="2">
-        <v>-5.56</v>
+        <v>-10.51</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>9742.62</v>
+        <v>26124</v>
       </c>
       <c r="K35" s="1">
-        <v>8964.15</v>
+        <v>24660.54</v>
       </c>
       <c r="L35" s="1">
-        <v>9402.81</v>
+        <v>25310.01</v>
       </c>
       <c r="M35" s="3">
-        <v>-137.54</v>
+        <v>-203.1</v>
       </c>
       <c r="N35" s="3">
-        <v>-156.44</v>
+        <v>-209.82</v>
       </c>
       <c r="O35" s="3">
-        <v>-209.22</v>
+        <v>-403.63</v>
       </c>
       <c r="P35" s="3">
-        <v>-96.92</v>
+        <v>-262.29</v>
       </c>
       <c r="Q35" s="3">
-        <v>392.52</v>
+        <v>652.59</v>
       </c>
       <c r="R35" s="3">
-        <v>508.87</v>
+        <v>1082.08</v>
       </c>
       <c r="S35" s="3">
-        <v>43.23</v>
+        <v>45.89</v>
       </c>
       <c r="T35" s="3">
-        <v>15.21</v>
+        <v>16.83</v>
       </c>
       <c r="U35" s="3">
-        <v>28.84</v>
+        <v>24.12</v>
       </c>
       <c r="V35" s="3">
-        <v>40.78</v>
+        <v>27.61</v>
       </c>
       <c r="W35" s="3">
         <v>0</v>
@@ -3105,67 +3105,67 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D36" s="1">
-        <v>31041.95</v>
+        <v>3284.19</v>
       </c>
       <c r="E36" s="2">
-        <v>1.03</v>
+        <v>0.02</v>
       </c>
       <c r="F36" s="2">
-        <v>2.22</v>
+        <v>0.22</v>
       </c>
       <c r="G36" s="2">
-        <v>0.44</v>
+        <v>-0.74</v>
       </c>
       <c r="H36" s="2">
-        <v>-6.87</v>
+        <v>1.91</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>32280.53</v>
+        <v>3281.87</v>
       </c>
       <c r="K36" s="1">
-        <v>30773.49</v>
+        <v>3282.34</v>
       </c>
       <c r="L36" s="1">
-        <v>31711.22</v>
+        <v>3313.01</v>
       </c>
       <c r="M36" s="3">
-        <v>-247.86</v>
+        <v>-9.38</v>
       </c>
       <c r="N36" s="3">
-        <v>-332.8</v>
+        <v>-10.79</v>
       </c>
       <c r="O36" s="3">
-        <v>-420.64</v>
+        <v>5.42</v>
       </c>
       <c r="P36" s="3">
-        <v>-178.84</v>
+        <v>15.47</v>
       </c>
       <c r="Q36" s="3">
-        <v>1861.41</v>
+        <v>140.06</v>
       </c>
       <c r="R36" s="3">
-        <v>2379.77</v>
+        <v>155.52</v>
       </c>
       <c r="S36" s="3">
-        <v>49.76</v>
+        <v>37.7</v>
       </c>
       <c r="T36" s="3">
-        <v>16.02</v>
+        <v>16.71</v>
       </c>
       <c r="U36" s="3">
-        <v>26.08</v>
+        <v>37.46</v>
       </c>
       <c r="V36" s="3">
-        <v>42.73</v>
+        <v>49.78</v>
       </c>
       <c r="W36" s="3">
         <v>0</v>
@@ -3182,67 +3182,67 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C37" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D37" s="1">
-        <v>5398.45</v>
+        <v>27053.5</v>
       </c>
       <c r="E37" s="2">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="G37" s="2">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="H37" s="2">
-        <v>-7.88</v>
+        <v>-5.81</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>5535.28</v>
+        <v>27311.83</v>
       </c>
       <c r="K37" s="1">
-        <v>5365.23</v>
+        <v>26950.89</v>
       </c>
       <c r="L37" s="1">
-        <v>5478.52</v>
+        <v>27225.05</v>
       </c>
       <c r="M37" s="3">
-        <v>-22.62</v>
+        <v>-79.32</v>
       </c>
       <c r="N37" s="3">
-        <v>-34.62</v>
+        <v>-76.16</v>
       </c>
       <c r="O37" s="3">
-        <v>-50.99</v>
+        <v>-64.98</v>
       </c>
       <c r="P37" s="3">
-        <v>-25</v>
+        <v>-1.19</v>
       </c>
       <c r="Q37" s="3">
-        <v>190.16</v>
+        <v>661.63</v>
       </c>
       <c r="R37" s="3">
-        <v>261.7</v>
+        <v>878.21</v>
       </c>
       <c r="S37" s="3">
-        <v>50.77</v>
+        <v>50.11</v>
       </c>
       <c r="T37" s="3">
-        <v>19.03</v>
+        <v>19.77</v>
       </c>
       <c r="U37" s="3">
-        <v>27.33</v>
+        <v>21.82</v>
       </c>
       <c r="V37" s="3">
-        <v>36.22</v>
+        <v>15.11</v>
       </c>
       <c r="W37" s="3">
         <v>0</v>
@@ -3259,67 +3259,67 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C38" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D38" s="1">
-        <v>35299</v>
+        <v>206.19</v>
       </c>
       <c r="E38" s="2">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2">
-        <v>2.26</v>
+        <v>0.96</v>
       </c>
       <c r="G38" s="2">
-        <v>-3.65</v>
+        <v>4.78</v>
       </c>
       <c r="H38" s="2">
-        <v>-0.08</v>
+        <v>-17.24</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>37706.65</v>
+        <v>179.33</v>
       </c>
       <c r="K38" s="1">
-        <v>35378.63</v>
+        <v>203.65</v>
       </c>
       <c r="L38" s="1">
-        <v>37046.09</v>
+        <v>196.71</v>
       </c>
       <c r="M38" s="3">
-        <v>-597.25</v>
+        <v>3.1</v>
       </c>
       <c r="N38" s="3">
-        <v>-575.74</v>
+        <v>2.87</v>
       </c>
       <c r="O38" s="3">
-        <v>-682.54</v>
+        <v>12.48</v>
       </c>
       <c r="P38" s="3">
-        <v>-206.54</v>
+        <v>7.05</v>
       </c>
       <c r="Q38" s="3">
-        <v>952.02</v>
+        <v>5.63</v>
       </c>
       <c r="R38" s="3">
-        <v>1231.73</v>
+        <v>7.71</v>
       </c>
       <c r="S38" s="3">
-        <v>39.95</v>
+        <v>100</v>
       </c>
       <c r="T38" s="3">
-        <v>14.33</v>
+        <v>99.72</v>
       </c>
       <c r="U38" s="3">
-        <v>34.57</v>
+        <v>0.28</v>
       </c>
       <c r="V38" s="3">
-        <v>37.53</v>
+        <v>97.72</v>
       </c>
       <c r="W38" s="3">
         <v>0</v>
@@ -3336,67 +3336,67 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C39" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D39" s="1">
-        <v>57841.65</v>
+        <v>26446.9</v>
       </c>
       <c r="E39" s="2">
-        <v>0.99</v>
+        <v>-0.03</v>
       </c>
       <c r="F39" s="2">
-        <v>3.66</v>
+        <v>0.96</v>
       </c>
       <c r="G39" s="2">
-        <v>-2.51</v>
+        <v>-0.41</v>
       </c>
       <c r="H39" s="2">
-        <v>-4.37</v>
+        <v>-12.36</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>60215.62</v>
+        <v>28421.24</v>
       </c>
       <c r="K39" s="1">
-        <v>57608.06</v>
+        <v>26456.91</v>
       </c>
       <c r="L39" s="1">
-        <v>60874.11</v>
+        <v>27322.23</v>
       </c>
       <c r="M39" s="3">
-        <v>-1065.2</v>
+        <v>-275.12</v>
       </c>
       <c r="N39" s="3">
-        <v>-1075.05</v>
+        <v>-282.04</v>
       </c>
       <c r="O39" s="3">
-        <v>-593.59</v>
+        <v>-546.45</v>
       </c>
       <c r="P39" s="3">
-        <v>198.27</v>
+        <v>-350.2</v>
       </c>
       <c r="Q39" s="3">
-        <v>2890.81</v>
+        <v>1301.99</v>
       </c>
       <c r="R39" s="3">
-        <v>3484.08</v>
+        <v>1898.31</v>
       </c>
       <c r="S39" s="3">
-        <v>42.34</v>
+        <v>43.07</v>
       </c>
       <c r="T39" s="3">
-        <v>15.66</v>
+        <v>15.19</v>
       </c>
       <c r="U39" s="3">
-        <v>36.53</v>
+        <v>25.45</v>
       </c>
       <c r="V39" s="3">
-        <v>51.02</v>
+        <v>31.26</v>
       </c>
       <c r="W39" s="3">
         <v>0</v>
@@ -3413,67 +3413,67 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C40" t="str">
-        <v>CNXIT</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D40" s="1">
-        <v>31866.4</v>
+        <v>32470.45</v>
       </c>
       <c r="E40" s="2">
-        <v>0.99</v>
+        <v>-0.09</v>
       </c>
       <c r="F40" s="2">
-        <v>-0.4</v>
+        <v>2.62</v>
       </c>
       <c r="G40" s="2">
-        <v>15.02</v>
+        <v>-1.19</v>
       </c>
       <c r="H40" s="2">
-        <v>-15.88</v>
+        <v>-4.37</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>30693.27</v>
+        <v>33623.31</v>
       </c>
       <c r="K40" s="1">
-        <v>31496.67</v>
+        <v>32313.69</v>
       </c>
       <c r="L40" s="1">
-        <v>29898.16</v>
+        <v>33542.08</v>
       </c>
       <c r="M40" s="3">
-        <v>812.93</v>
+        <v>-353.05</v>
       </c>
       <c r="N40" s="3">
-        <v>604.78</v>
+        <v>-428.53</v>
       </c>
       <c r="O40" s="3">
-        <v>3.2</v>
+        <v>-343.15</v>
       </c>
       <c r="P40" s="3">
-        <v>-415</v>
+        <v>1.32</v>
       </c>
       <c r="Q40" s="3">
-        <v>-1671.31</v>
+        <v>2016.58</v>
       </c>
       <c r="R40" s="3">
-        <v>-1149.81</v>
+        <v>2433.24</v>
       </c>
       <c r="S40" s="3">
-        <v>63.15</v>
+        <v>45.68</v>
       </c>
       <c r="T40" s="3">
-        <v>26.04</v>
+        <v>16.42</v>
       </c>
       <c r="U40" s="3">
-        <v>14.94</v>
+        <v>27.76</v>
       </c>
       <c r="V40" s="3">
-        <v>30.29</v>
+        <v>45.29</v>
       </c>
       <c r="W40" s="3">
         <v>0</v>
@@ -3490,67 +3490,67 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D41" s="1">
-        <v>21941.5</v>
+        <v>2980.28</v>
       </c>
       <c r="E41" s="2">
-        <v>0.99</v>
+        <v>-0.14</v>
       </c>
       <c r="F41" s="2">
-        <v>2.4</v>
+        <v>0.49</v>
       </c>
       <c r="G41" s="2">
-        <v>-0.59</v>
+        <v>-1.12</v>
       </c>
       <c r="H41" s="2">
-        <v>-8.09</v>
+        <v>0.45</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>22786.71</v>
+        <v>3001.49</v>
       </c>
       <c r="K41" s="1">
-        <v>21824.59</v>
+        <v>2977.19</v>
       </c>
       <c r="L41" s="1">
-        <v>22596.08</v>
+        <v>3016.21</v>
       </c>
       <c r="M41" s="3">
-        <v>-229.9</v>
+        <v>-12.32</v>
       </c>
       <c r="N41" s="3">
-        <v>-257.85</v>
+        <v>-14.38</v>
       </c>
       <c r="O41" s="3">
-        <v>-266.13</v>
+        <v>-2.44</v>
       </c>
       <c r="P41" s="3">
-        <v>-89.65</v>
+        <v>8.59</v>
       </c>
       <c r="Q41" s="3">
-        <v>525.75</v>
+        <v>115.55</v>
       </c>
       <c r="R41" s="3">
-        <v>807.09</v>
+        <v>132.99</v>
       </c>
       <c r="S41" s="3">
-        <v>46.21</v>
+        <v>41.23</v>
       </c>
       <c r="T41" s="3">
-        <v>15.68</v>
+        <v>23.09</v>
       </c>
       <c r="U41" s="3">
-        <v>30.03</v>
+        <v>33.54</v>
       </c>
       <c r="V41" s="3">
-        <v>46.64</v>
+        <v>47.07</v>
       </c>
       <c r="W41" s="3">
         <v>0</v>
@@ -3567,67 +3567,67 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D42" s="1">
-        <v>11311.05</v>
+        <v>3070.19</v>
       </c>
       <c r="E42" s="2">
-        <v>0.99</v>
+        <v>-0.16</v>
       </c>
       <c r="F42" s="2">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="G42" s="2">
-        <v>1.49</v>
+        <v>-1.1</v>
       </c>
       <c r="H42" s="2">
-        <v>-14.8</v>
+        <v>0.58</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>12131.25</v>
+        <v>3086.32</v>
       </c>
       <c r="K42" s="1">
-        <v>11297.56</v>
+        <v>3068.46</v>
       </c>
       <c r="L42" s="1">
-        <v>11482.27</v>
+        <v>3107.71</v>
       </c>
       <c r="M42" s="3">
-        <v>-39.79</v>
+        <v>-12.5</v>
       </c>
       <c r="N42" s="3">
-        <v>-57.04</v>
+        <v>-14.36</v>
       </c>
       <c r="O42" s="3">
-        <v>-264.87</v>
+        <v>-0.45</v>
       </c>
       <c r="P42" s="3">
-        <v>-242.06</v>
+        <v>11.02</v>
       </c>
       <c r="Q42" s="3">
-        <v>-131.2</v>
+        <v>119.25</v>
       </c>
       <c r="R42" s="3">
-        <v>114.2</v>
+        <v>136.7</v>
       </c>
       <c r="S42" s="3">
-        <v>48.51</v>
+        <v>40.62</v>
       </c>
       <c r="T42" s="3">
-        <v>16.24</v>
+        <v>21.74</v>
       </c>
       <c r="U42" s="3">
-        <v>26.43</v>
+        <v>33.65</v>
       </c>
       <c r="V42" s="3">
-        <v>28.91</v>
+        <v>46.17</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3644,67 +3644,67 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C43" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D43" s="1">
-        <v>15588.6</v>
+        <v>3468.45</v>
       </c>
       <c r="E43" s="2">
-        <v>0.97</v>
+        <v>-0.19</v>
       </c>
       <c r="F43" s="2">
-        <v>2.49</v>
+        <v>0.49</v>
       </c>
       <c r="G43" s="2">
-        <v>-1.07</v>
+        <v>-1.52</v>
       </c>
       <c r="H43" s="2">
-        <v>-7.51</v>
+        <v>-0.7</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>16256.43</v>
+        <v>3494.74</v>
       </c>
       <c r="K43" s="1">
-        <v>15516.57</v>
+        <v>3468.66</v>
       </c>
       <c r="L43" s="1">
-        <v>16152.58</v>
+        <v>3518.16</v>
       </c>
       <c r="M43" s="3">
-        <v>-193.73</v>
+        <v>-17.31</v>
       </c>
       <c r="N43" s="3">
-        <v>-211.73</v>
+        <v>-18.2</v>
       </c>
       <c r="O43" s="3">
-        <v>-194.8</v>
+        <v>-2.39</v>
       </c>
       <c r="P43" s="3">
-        <v>-44.46</v>
+        <v>11.65</v>
       </c>
       <c r="Q43" s="3">
-        <v>922.12</v>
+        <v>118.81</v>
       </c>
       <c r="R43" s="3">
-        <v>1179.91</v>
+        <v>141.9</v>
       </c>
       <c r="S43" s="3">
-        <v>44.66</v>
+        <v>40.97</v>
       </c>
       <c r="T43" s="3">
-        <v>14.79</v>
+        <v>20.78</v>
       </c>
       <c r="U43" s="3">
-        <v>31.32</v>
+        <v>32.56</v>
       </c>
       <c r="V43" s="3">
-        <v>49.21</v>
+        <v>32.14</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3721,67 +3721,67 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>Nifty Total Market</v>
+        <v>NIFTY500</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>NIFTY500</v>
       </c>
       <c r="D44" s="1">
-        <v>12398</v>
+        <v>21895.9</v>
       </c>
       <c r="E44" s="2">
-        <v>0.97</v>
+        <v>-0.21</v>
       </c>
       <c r="F44" s="2">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="G44" s="2">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="H44" s="2">
-        <v>-7.44</v>
+        <v>-8.28</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>12832.95</v>
+        <v>22776.11</v>
       </c>
       <c r="K44" s="1">
-        <v>12337.67</v>
+        <v>21837.55</v>
       </c>
       <c r="L44" s="1">
-        <v>12781.29</v>
+        <v>22564.55</v>
       </c>
       <c r="M44" s="3">
-        <v>-134.82</v>
+        <v>-209.22</v>
       </c>
       <c r="N44" s="3">
-        <v>-147.53</v>
+        <v>-248.12</v>
       </c>
       <c r="O44" s="3">
-        <v>-131.46</v>
+        <v>-269.77</v>
       </c>
       <c r="P44" s="3">
-        <v>-28.38</v>
+        <v>-90.38</v>
       </c>
       <c r="Q44" s="3">
-        <v>634.57</v>
+        <v>522.11</v>
       </c>
       <c r="R44" s="3">
-        <v>826.99</v>
+        <v>806.37</v>
       </c>
       <c r="S44" s="3">
-        <v>45.68</v>
+        <v>45.21</v>
       </c>
       <c r="T44" s="3">
-        <v>15.82</v>
+        <v>15.34</v>
       </c>
       <c r="U44" s="3">
-        <v>30.79</v>
+        <v>28.73</v>
       </c>
       <c r="V44" s="3">
-        <v>46.24</v>
+        <v>45.48</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3798,67 +3798,67 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C45" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D45" s="1">
-        <v>9519.15</v>
+        <v>8966.45</v>
       </c>
       <c r="E45" s="2">
-        <v>0.96</v>
+        <v>-0.22</v>
       </c>
       <c r="F45" s="2">
-        <v>6.66</v>
+        <v>1.98</v>
       </c>
       <c r="G45" s="2">
-        <v>-1.18</v>
+        <v>-3.69</v>
       </c>
       <c r="H45" s="2">
-        <v>10.61</v>
+        <v>-5.77</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>8996.15</v>
+        <v>9739.1</v>
       </c>
       <c r="K45" s="1">
-        <v>9379.28</v>
+        <v>8964.57</v>
       </c>
       <c r="L45" s="1">
-        <v>9743.34</v>
+        <v>9385.84</v>
       </c>
       <c r="M45" s="3">
-        <v>-124.72</v>
+        <v>-128.35</v>
       </c>
       <c r="N45" s="3">
-        <v>-125.02</v>
+        <v>-150.82</v>
       </c>
       <c r="O45" s="3">
-        <v>155.15</v>
+        <v>-210.81</v>
       </c>
       <c r="P45" s="3">
-        <v>262.12</v>
+        <v>-97.24</v>
       </c>
       <c r="Q45" s="3">
-        <v>749.72</v>
+        <v>390.93</v>
       </c>
       <c r="R45" s="3">
-        <v>721.58</v>
+        <v>508.55</v>
       </c>
       <c r="S45" s="3">
-        <v>49.66</v>
+        <v>42.41</v>
       </c>
       <c r="T45" s="3">
-        <v>25.04</v>
+        <v>14.54</v>
       </c>
       <c r="U45" s="3">
-        <v>38.24</v>
+        <v>27.56</v>
       </c>
       <c r="V45" s="3">
-        <v>34.64</v>
+        <v>40.07</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3875,67 +3875,67 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D46" s="1">
-        <v>206.19</v>
+        <v>2607.96</v>
       </c>
       <c r="E46" s="2">
-        <v>0.96</v>
+        <v>-0.22</v>
       </c>
       <c r="F46" s="2">
-        <v>0.96</v>
+        <v>0.47</v>
       </c>
       <c r="G46" s="2">
-        <v>4.78</v>
+        <v>-1.15</v>
       </c>
       <c r="H46" s="2">
-        <v>-17.24</v>
+        <v>-0.15</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>179.55</v>
+        <v>2632</v>
       </c>
       <c r="K46" s="1">
-        <v>203.08</v>
+        <v>2606.3</v>
       </c>
       <c r="L46" s="1">
-        <v>196.37</v>
+        <v>2639.99</v>
       </c>
       <c r="M46" s="3">
-        <v>3.04</v>
+        <v>-10.62</v>
       </c>
       <c r="N46" s="3">
-        <v>2.81</v>
+        <v>-12.58</v>
       </c>
       <c r="O46" s="3">
-        <v>12.48</v>
+        <v>-4.24</v>
       </c>
       <c r="P46" s="3">
-        <v>7.05</v>
+        <v>5.08</v>
       </c>
       <c r="Q46" s="3">
-        <v>5.63</v>
+        <v>90.57</v>
       </c>
       <c r="R46" s="3">
-        <v>7.71</v>
+        <v>106.52</v>
       </c>
       <c r="S46" s="3">
-        <v>100</v>
+        <v>41.39</v>
       </c>
       <c r="T46" s="3">
-        <v>99.72</v>
+        <v>23.94</v>
       </c>
       <c r="U46" s="3">
-        <v>0.28</v>
+        <v>27.85</v>
       </c>
       <c r="V46" s="3">
-        <v>97.59</v>
+        <v>34.58</v>
       </c>
       <c r="W46" s="3">
         <v>0</v>
@@ -3952,67 +3952,67 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C47" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D47" s="1">
-        <v>26454.65</v>
+        <v>3291.31</v>
       </c>
       <c r="E47" s="2">
-        <v>0.95</v>
+        <v>-0.23</v>
       </c>
       <c r="F47" s="2">
-        <v>0.99</v>
+        <v>0.22</v>
       </c>
       <c r="G47" s="2">
-        <v>-0.38</v>
+        <v>-0.91</v>
       </c>
       <c r="H47" s="2">
-        <v>-12.34</v>
+        <v>1.52</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>28442.3</v>
+        <v>3296.66</v>
       </c>
       <c r="K47" s="1">
-        <v>26459.13</v>
+        <v>3291.62</v>
       </c>
       <c r="L47" s="1">
-        <v>27361.86</v>
+        <v>3336.83</v>
       </c>
       <c r="M47" s="3">
-        <v>-292.31</v>
+        <v>-13.52</v>
       </c>
       <c r="N47" s="3">
-        <v>-283.77</v>
+        <v>-15.93</v>
       </c>
       <c r="O47" s="3">
-        <v>-545.83</v>
+        <v>3.96</v>
       </c>
       <c r="P47" s="3">
-        <v>-350.08</v>
+        <v>17.97</v>
       </c>
       <c r="Q47" s="3">
-        <v>1302.61</v>
+        <v>136.91</v>
       </c>
       <c r="R47" s="3">
-        <v>1898.43</v>
+        <v>153.99</v>
       </c>
       <c r="S47" s="3">
-        <v>43.19</v>
+        <v>40.51</v>
       </c>
       <c r="T47" s="3">
-        <v>14.21</v>
+        <v>17.16</v>
       </c>
       <c r="U47" s="3">
-        <v>26.83</v>
+        <v>26.66</v>
       </c>
       <c r="V47" s="3">
-        <v>31.72</v>
+        <v>48.07</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4029,67 +4029,67 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C48" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D48" s="1">
-        <v>18811.35</v>
+        <v>840.27</v>
       </c>
       <c r="E48" s="2">
-        <v>0.95</v>
+        <v>-0.23</v>
       </c>
       <c r="F48" s="2">
-        <v>6.04</v>
+        <v>0.37</v>
       </c>
       <c r="G48" s="2">
-        <v>-2.26</v>
+        <v>-1.75</v>
       </c>
       <c r="H48" s="2">
-        <v>6.2</v>
+        <v>-5.74</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>18201.08</v>
+        <v>872.28</v>
       </c>
       <c r="K48" s="1">
-        <v>18621.56</v>
+        <v>840.58</v>
       </c>
       <c r="L48" s="1">
-        <v>19472.76</v>
+        <v>856.79</v>
       </c>
       <c r="M48" s="3">
-        <v>-303.71</v>
+        <v>-5.27</v>
       </c>
       <c r="N48" s="3">
-        <v>-284.02</v>
+        <v>-5.94</v>
       </c>
       <c r="O48" s="3">
-        <v>199.4</v>
+        <v>-9.5</v>
       </c>
       <c r="P48" s="3">
-        <v>421.53</v>
+        <v>-6.42</v>
       </c>
       <c r="Q48" s="3">
-        <v>882.85</v>
+        <v>-17.04</v>
       </c>
       <c r="R48" s="3">
-        <v>860.74</v>
+        <v>-14.16</v>
       </c>
       <c r="S48" s="3">
-        <v>46.8</v>
+        <v>34.89</v>
       </c>
       <c r="T48" s="3">
-        <v>23.65</v>
+        <v>19.18</v>
       </c>
       <c r="U48" s="3">
-        <v>40.28</v>
+        <v>31.78</v>
       </c>
       <c r="V48" s="3">
-        <v>36.68</v>
+        <v>50.48</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -4106,67 +4106,67 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D49" s="1">
-        <v>16656.4</v>
+        <v>9075.35</v>
       </c>
       <c r="E49" s="2">
-        <v>0.94</v>
+        <v>-0.24</v>
       </c>
       <c r="F49" s="2">
-        <v>3.67</v>
+        <v>2.13</v>
       </c>
       <c r="G49" s="2">
-        <v>-2.19</v>
+        <v>-3.05</v>
       </c>
       <c r="H49" s="2">
-        <v>-3.46</v>
+        <v>-7.9</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>17199.36</v>
+        <v>9958.59</v>
       </c>
       <c r="K49" s="1">
-        <v>16560.61</v>
+        <v>9076.12</v>
       </c>
       <c r="L49" s="1">
-        <v>17485.91</v>
+        <v>9437.21</v>
       </c>
       <c r="M49" s="3">
-        <v>-292.78</v>
+        <v>-119.59</v>
       </c>
       <c r="N49" s="3">
-        <v>-309.06</v>
+        <v>-130.38</v>
       </c>
       <c r="O49" s="3">
-        <v>-131.6</v>
+        <v>-255.59</v>
       </c>
       <c r="P49" s="3">
-        <v>96.58</v>
+        <v>-171.23</v>
       </c>
       <c r="Q49" s="3">
-        <v>907.05</v>
+        <v>791.19</v>
       </c>
       <c r="R49" s="3">
-        <v>1049.65</v>
+        <v>1091.66</v>
       </c>
       <c r="S49" s="3">
-        <v>43.36</v>
+        <v>42.13</v>
       </c>
       <c r="T49" s="3">
-        <v>15.91</v>
+        <v>13.31</v>
       </c>
       <c r="U49" s="3">
-        <v>33.59</v>
+        <v>31.46</v>
       </c>
       <c r="V49" s="3">
-        <v>48.33</v>
+        <v>48.39</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -4183,67 +4183,67 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C50" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D50" s="1">
-        <v>49209.75</v>
+        <v>15541.55</v>
       </c>
       <c r="E50" s="2">
-        <v>0.93</v>
+        <v>-0.3</v>
       </c>
       <c r="F50" s="2">
-        <v>5.18</v>
+        <v>2.18</v>
       </c>
       <c r="G50" s="2">
-        <v>-0.74</v>
+        <v>-1.37</v>
       </c>
       <c r="H50" s="2">
-        <v>3.46</v>
+        <v>-7.79</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>49089.69</v>
+        <v>16249.09</v>
       </c>
       <c r="K50" s="1">
-        <v>48655.22</v>
+        <v>15521.11</v>
       </c>
       <c r="L50" s="1">
-        <v>50472.65</v>
+        <v>16126.84</v>
       </c>
       <c r="M50" s="3">
-        <v>-587.19</v>
+        <v>-179.23</v>
       </c>
       <c r="N50" s="3">
-        <v>-620.13</v>
+        <v>-205.23</v>
       </c>
       <c r="O50" s="3">
-        <v>-57.65</v>
+        <v>-198.55</v>
       </c>
       <c r="P50" s="3">
-        <v>417.49</v>
+        <v>-45.21</v>
       </c>
       <c r="Q50" s="3">
-        <v>134.84</v>
+        <v>918.37</v>
       </c>
       <c r="R50" s="3">
-        <v>-284.19</v>
+        <v>1179.16</v>
       </c>
       <c r="S50" s="3">
-        <v>48.81</v>
+        <v>43.28</v>
       </c>
       <c r="T50" s="3">
-        <v>19.64</v>
+        <v>14.19</v>
       </c>
       <c r="U50" s="3">
-        <v>34.59</v>
+        <v>30.01</v>
       </c>
       <c r="V50" s="3">
-        <v>43.81</v>
+        <v>48.25</v>
       </c>
       <c r="W50" s="3">
         <v>0</v>
@@ -4260,67 +4260,67 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D51" s="1">
-        <v>15538.1</v>
+        <v>12360.4</v>
       </c>
       <c r="E51" s="2">
-        <v>0.92</v>
+        <v>-0.3</v>
       </c>
       <c r="F51" s="2">
-        <v>2.78</v>
+        <v>2.11</v>
       </c>
       <c r="G51" s="2">
-        <v>-1.35</v>
+        <v>-1.16</v>
       </c>
       <c r="H51" s="2">
-        <v>-5.74</v>
+        <v>-7.72</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>15989.59</v>
+        <v>12827.38</v>
       </c>
       <c r="K51" s="1">
-        <v>15469.47</v>
+        <v>12341.8</v>
       </c>
       <c r="L51" s="1">
-        <v>16080.03</v>
+        <v>12763.27</v>
       </c>
       <c r="M51" s="3">
-        <v>-192.9</v>
+        <v>-124.29</v>
       </c>
       <c r="N51" s="3">
-        <v>-202.42</v>
+        <v>-142.88</v>
       </c>
       <c r="O51" s="3">
-        <v>-128.67</v>
+        <v>-134.46</v>
       </c>
       <c r="P51" s="3">
-        <v>19.16</v>
+        <v>-28.98</v>
       </c>
       <c r="Q51" s="3">
-        <v>924.1</v>
+        <v>631.57</v>
       </c>
       <c r="R51" s="3">
-        <v>1149.5</v>
+        <v>826.39</v>
       </c>
       <c r="S51" s="3">
-        <v>44.57</v>
+        <v>44.24</v>
       </c>
       <c r="T51" s="3">
-        <v>16.24</v>
+        <v>15.15</v>
       </c>
       <c r="U51" s="3">
-        <v>33.43</v>
+        <v>29.49</v>
       </c>
       <c r="V51" s="3">
-        <v>47.17</v>
+        <v>45.23</v>
       </c>
       <c r="W51" s="3">
         <v>0</v>
@@ -4337,67 +4337,67 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D52" s="1">
-        <v>28723.25</v>
+        <v>15571.1</v>
       </c>
       <c r="E52" s="2">
-        <v>0.88</v>
+        <v>-0.36</v>
       </c>
       <c r="F52" s="2">
-        <v>5.21</v>
+        <v>3.24</v>
       </c>
       <c r="G52" s="2">
-        <v>-2.7</v>
+        <v>-2.79</v>
       </c>
       <c r="H52" s="2">
-        <v>-7.78</v>
+        <v>-2.53</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>30301.56</v>
+        <v>15988.41</v>
       </c>
       <c r="K52" s="1">
-        <v>28493.92</v>
+        <v>15540.27</v>
       </c>
       <c r="L52" s="1">
-        <v>29963.77</v>
+        <v>16230.39</v>
       </c>
       <c r="M52" s="3">
-        <v>-496.6</v>
+        <v>-201.71</v>
       </c>
       <c r="N52" s="3">
-        <v>-504.91</v>
+        <v>-241.38</v>
       </c>
       <c r="O52" s="3">
-        <v>-471.68</v>
+        <v>-103.3</v>
       </c>
       <c r="P52" s="3">
-        <v>-178.05</v>
+        <v>84.51</v>
       </c>
       <c r="Q52" s="3">
-        <v>1474.95</v>
+        <v>372.3</v>
       </c>
       <c r="R52" s="3">
-        <v>2004.71</v>
+        <v>331.35</v>
       </c>
       <c r="S52" s="3">
-        <v>45.36</v>
+        <v>43.79</v>
       </c>
       <c r="T52" s="3">
-        <v>16.37</v>
+        <v>16.46</v>
       </c>
       <c r="U52" s="3">
-        <v>34.93</v>
+        <v>31.98</v>
       </c>
       <c r="V52" s="3">
-        <v>42.61</v>
+        <v>44.96</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4414,67 +4414,67 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C53" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D53" s="1">
-        <v>13802.6</v>
+        <v>28416.15</v>
       </c>
       <c r="E53" s="2">
-        <v>0.87</v>
+        <v>-0.4</v>
       </c>
       <c r="F53" s="2">
-        <v>1.48</v>
+        <v>2.34</v>
       </c>
       <c r="G53" s="2">
-        <v>3.37</v>
+        <v>-6.33</v>
       </c>
       <c r="H53" s="2">
-        <v>-9.74</v>
+        <v>-7.04</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>14350.52</v>
+        <v>31322.03</v>
       </c>
       <c r="K53" s="1">
-        <v>13696.82</v>
+        <v>28617.48</v>
       </c>
       <c r="L53" s="1">
-        <v>13929.34</v>
+        <v>30891.43</v>
       </c>
       <c r="M53" s="3">
-        <v>-28.57</v>
+        <v>-766.9</v>
       </c>
       <c r="N53" s="3">
-        <v>-73.11</v>
+        <v>-776.28</v>
       </c>
       <c r="O53" s="3">
-        <v>-217.53</v>
+        <v>-666.48</v>
       </c>
       <c r="P53" s="3">
-        <v>-173.91</v>
+        <v>-84.22</v>
       </c>
       <c r="Q53" s="3">
-        <v>-531.62</v>
+        <v>1973.14</v>
       </c>
       <c r="R53" s="3">
-        <v>-490.87</v>
+        <v>2394.53</v>
       </c>
       <c r="S53" s="3">
-        <v>52.79</v>
+        <v>32.91</v>
       </c>
       <c r="T53" s="3">
-        <v>19.77</v>
+        <v>13.98</v>
       </c>
       <c r="U53" s="3">
-        <v>23.7</v>
+        <v>40.53</v>
       </c>
       <c r="V53" s="3">
-        <v>22.82</v>
+        <v>57.99</v>
       </c>
       <c r="W53" s="3">
         <v>0</v>
@@ -4491,67 +4491,67 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C54" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D54" s="1">
-        <v>11026.55</v>
+        <v>54686.95</v>
       </c>
       <c r="E54" s="2">
-        <v>0.87</v>
+        <v>-0.41</v>
       </c>
       <c r="F54" s="2">
-        <v>1.26</v>
+        <v>0.74</v>
       </c>
       <c r="G54" s="2">
-        <v>4.62</v>
+        <v>0.1</v>
       </c>
       <c r="H54" s="2">
-        <v>-11.67</v>
+        <v>-8.22</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>11182.94</v>
+        <v>56703.93</v>
       </c>
       <c r="K54" s="1">
-        <v>10900.15</v>
+        <v>54713.21</v>
       </c>
       <c r="L54" s="1">
-        <v>11009.67</v>
+        <v>55948.37</v>
       </c>
       <c r="M54" s="3">
-        <v>23.52</v>
+        <v>-366.71</v>
       </c>
       <c r="N54" s="3">
-        <v>-34.77</v>
+        <v>-378.73</v>
       </c>
       <c r="O54" s="3">
-        <v>-100.81</v>
+        <v>-469.98</v>
       </c>
       <c r="P54" s="3">
-        <v>-80.99</v>
+        <v>-181.43</v>
       </c>
       <c r="Q54" s="3">
-        <v>42.41</v>
+        <v>1641.95</v>
       </c>
       <c r="R54" s="3">
-        <v>178.72</v>
+        <v>2283.97</v>
       </c>
       <c r="S54" s="3">
-        <v>57.86</v>
+        <v>44.98</v>
       </c>
       <c r="T54" s="3">
-        <v>20.75</v>
+        <v>16.08</v>
       </c>
       <c r="U54" s="3">
-        <v>20.15</v>
+        <v>22.69</v>
       </c>
       <c r="V54" s="3">
-        <v>25.78</v>
+        <v>24.8</v>
       </c>
       <c r="W54" s="3">
         <v>0</v>
@@ -4568,67 +4568,67 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D55" s="1">
-        <v>21245.3</v>
+        <v>10303.25</v>
       </c>
       <c r="E55" s="2">
-        <v>0.86</v>
+        <v>-0.47</v>
       </c>
       <c r="F55" s="2">
-        <v>3.17</v>
+        <v>-0.74</v>
       </c>
       <c r="G55" s="2">
-        <v>-2.85</v>
+        <v>-2.93</v>
       </c>
       <c r="H55" s="2">
-        <v>-4.63</v>
+        <v>-15.76</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>22147.19</v>
+        <v>11248</v>
       </c>
       <c r="K55" s="1">
-        <v>21197.83</v>
+        <v>10417.54</v>
       </c>
       <c r="L55" s="1">
-        <v>22378.54</v>
+        <v>10787.05</v>
       </c>
       <c r="M55" s="3">
-        <v>-387.27</v>
+        <v>-114.4</v>
       </c>
       <c r="N55" s="3">
-        <v>-388.8</v>
+        <v>-117.56</v>
       </c>
       <c r="O55" s="3">
-        <v>-213.09</v>
+        <v>-250.51</v>
       </c>
       <c r="P55" s="3">
-        <v>75.99</v>
+        <v>-179.13</v>
       </c>
       <c r="Q55" s="3">
-        <v>1706.31</v>
+        <v>61.86</v>
       </c>
       <c r="R55" s="3">
-        <v>2027.88</v>
+        <v>277.17</v>
       </c>
       <c r="S55" s="3">
-        <v>40.98</v>
+        <v>37.93</v>
       </c>
       <c r="T55" s="3">
-        <v>15.05</v>
+        <v>13.94</v>
       </c>
       <c r="U55" s="3">
-        <v>37.14</v>
+        <v>29.31</v>
       </c>
       <c r="V55" s="3">
-        <v>50.88</v>
+        <v>31.33</v>
       </c>
       <c r="W55" s="3">
         <v>0</v>
@@ -4645,67 +4645,67 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="C56" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D56" s="1">
-        <v>18930.75</v>
+        <v>232.2</v>
       </c>
       <c r="E56" s="2">
-        <v>0.85</v>
+        <v>-0.49</v>
       </c>
       <c r="F56" s="2">
-        <v>1.34</v>
+        <v>-1.86</v>
       </c>
       <c r="G56" s="2">
-        <v>-0.06</v>
+        <v>-1.59</v>
       </c>
       <c r="H56" s="2">
-        <v>-11.58</v>
+        <v>16.1</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>20033.79</v>
+        <v>220.13</v>
       </c>
       <c r="K56" s="1">
-        <v>18941.37</v>
+        <v>234.35</v>
       </c>
       <c r="L56" s="1">
-        <v>19606.09</v>
+        <v>229.53</v>
       </c>
       <c r="M56" s="3">
-        <v>-187.74</v>
+        <v>1.03</v>
       </c>
       <c r="N56" s="3">
-        <v>-200.2</v>
+        <v>1.72</v>
       </c>
       <c r="O56" s="3">
-        <v>-327.98</v>
+        <v>4.64</v>
       </c>
       <c r="P56" s="3">
-        <v>-182.71</v>
+        <v>3.71</v>
       </c>
       <c r="Q56" s="3">
-        <v>482.81</v>
+        <v>-0.93</v>
       </c>
       <c r="R56" s="3">
-        <v>794.61</v>
+        <v>-4.83</v>
       </c>
       <c r="S56" s="3">
-        <v>43.81</v>
+        <v>47.46</v>
       </c>
       <c r="T56" s="3">
-        <v>14.74</v>
+        <v>23.56</v>
       </c>
       <c r="U56" s="3">
-        <v>32.03</v>
+        <v>18.25</v>
       </c>
       <c r="V56" s="3">
-        <v>41.94</v>
+        <v>38.7</v>
       </c>
       <c r="W56" s="3">
         <v>0</v>
@@ -4722,67 +4722,67 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C57" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D57" s="1">
-        <v>51999.35</v>
+        <v>14901.5</v>
       </c>
       <c r="E57" s="2">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="F57" s="2">
-        <v>5.97</v>
+        <v>2.65</v>
       </c>
       <c r="G57" s="2">
-        <v>-1.69</v>
+        <v>-3.58</v>
       </c>
       <c r="H57" s="2">
-        <v>-1.34</v>
+        <v>-3.32</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>52484.25</v>
+        <v>15606.69</v>
       </c>
       <c r="K57" s="1">
-        <v>51457.25</v>
+        <v>14911.23</v>
       </c>
       <c r="L57" s="1">
-        <v>53674.42</v>
+        <v>15676.17</v>
       </c>
       <c r="M57" s="3">
-        <v>-745.61</v>
+        <v>-229.36</v>
       </c>
       <c r="N57" s="3">
-        <v>-760.07</v>
+        <v>-263.34</v>
       </c>
       <c r="O57" s="3">
-        <v>-188.8</v>
+        <v>-159.89</v>
       </c>
       <c r="P57" s="3">
-        <v>292.67</v>
+        <v>45.16</v>
       </c>
       <c r="Q57" s="3">
-        <v>-676.24</v>
+        <v>1251.75</v>
       </c>
       <c r="R57" s="3">
-        <v>-1106.94</v>
+        <v>1444.83</v>
       </c>
       <c r="S57" s="3">
-        <v>47.67</v>
+        <v>41.1</v>
       </c>
       <c r="T57" s="3">
-        <v>17.65</v>
+        <v>14.78</v>
       </c>
       <c r="U57" s="3">
-        <v>37.2</v>
+        <v>33.34</v>
       </c>
       <c r="V57" s="3">
-        <v>42.42</v>
+        <v>48.59</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -4799,67 +4799,67 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D58" s="1">
-        <v>19756.25</v>
+        <v>188.25</v>
       </c>
       <c r="E58" s="2">
-        <v>0.79</v>
+        <v>-0.5</v>
       </c>
       <c r="F58" s="2">
-        <v>3.59</v>
+        <v>-1.9</v>
       </c>
       <c r="G58" s="2">
-        <v>-3.23</v>
+        <v>-1.65</v>
       </c>
       <c r="H58" s="2">
-        <v>-2.28</v>
+        <v>15.03</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>20242.7</v>
+        <v>179.35</v>
       </c>
       <c r="K58" s="1">
-        <v>19717.97</v>
+        <v>190.04</v>
       </c>
       <c r="L58" s="1">
-        <v>20777.07</v>
+        <v>186.18</v>
       </c>
       <c r="M58" s="3">
-        <v>-360.79</v>
+        <v>0.81</v>
       </c>
       <c r="N58" s="3">
-        <v>-347.16</v>
+        <v>1.38</v>
       </c>
       <c r="O58" s="3">
-        <v>-90.26</v>
+        <v>3.46</v>
       </c>
       <c r="P58" s="3">
-        <v>173.73</v>
+        <v>2.68</v>
       </c>
       <c r="Q58" s="3">
-        <v>1577.27</v>
+        <v>-2.73</v>
       </c>
       <c r="R58" s="3">
-        <v>1823.2</v>
+        <v>-6.07</v>
       </c>
       <c r="S58" s="3">
-        <v>41.3</v>
+        <v>47.26</v>
       </c>
       <c r="T58" s="3">
-        <v>16.63</v>
+        <v>23.53</v>
       </c>
       <c r="U58" s="3">
-        <v>40.57</v>
+        <v>18.23</v>
       </c>
       <c r="V58" s="3">
-        <v>49.62</v>
+        <v>38.29</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -4876,67 +4876,67 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D59" s="1">
-        <v>24908.25</v>
+        <v>11784.9</v>
       </c>
       <c r="E59" s="2">
-        <v>0.75</v>
+        <v>-0.54</v>
       </c>
       <c r="F59" s="2">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="G59" s="2">
-        <v>-1.23</v>
+        <v>-7.65</v>
       </c>
       <c r="H59" s="2">
-        <v>-8.01</v>
+        <v>5.53</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>26189.96</v>
+        <v>12492.34</v>
       </c>
       <c r="K59" s="1">
-        <v>24726.56</v>
+        <v>11851.33</v>
       </c>
       <c r="L59" s="1">
-        <v>25843.8</v>
+        <v>12678.03</v>
       </c>
       <c r="M59" s="3">
-        <v>-321.75</v>
+        <v>-267.8</v>
       </c>
       <c r="N59" s="3">
-        <v>-399.77</v>
+        <v>-280.36</v>
       </c>
       <c r="O59" s="3">
-        <v>-395.61</v>
+        <v>-71.01</v>
       </c>
       <c r="P59" s="3">
-        <v>-135.71</v>
+        <v>148.11</v>
       </c>
       <c r="Q59" s="3">
-        <v>1172.98</v>
+        <v>1131.85</v>
       </c>
       <c r="R59" s="3">
-        <v>1601.32</v>
+        <v>1129.06</v>
       </c>
       <c r="S59" s="3">
-        <v>45.37</v>
+        <v>38.87</v>
       </c>
       <c r="T59" s="3">
-        <v>14.95</v>
+        <v>11.75</v>
       </c>
       <c r="U59" s="3">
-        <v>26.06</v>
+        <v>30.91</v>
       </c>
       <c r="V59" s="3">
-        <v>48.95</v>
+        <v>38.91</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -4953,67 +4953,67 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D60" s="1">
-        <v>13381.05</v>
+        <v>28565.45</v>
       </c>
       <c r="E60" s="2">
-        <v>0.71</v>
+        <v>-0.55</v>
       </c>
       <c r="F60" s="2">
-        <v>2.67</v>
+        <v>4.63</v>
       </c>
       <c r="G60" s="2">
-        <v>-2.55</v>
+        <v>-3.23</v>
       </c>
       <c r="H60" s="2">
-        <v>-2.88</v>
+        <v>-8.29</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>13983.35</v>
+        <v>30286.4</v>
       </c>
       <c r="K60" s="1">
-        <v>13372.07</v>
+        <v>28506.92</v>
       </c>
       <c r="L60" s="1">
-        <v>14166.22</v>
+        <v>29912.69</v>
       </c>
       <c r="M60" s="3">
-        <v>-253.46</v>
+        <v>-459.76</v>
       </c>
       <c r="N60" s="3">
-        <v>-259.45</v>
+        <v>-495.88</v>
       </c>
       <c r="O60" s="3">
-        <v>-138.45</v>
+        <v>-484.27</v>
       </c>
       <c r="P60" s="3">
-        <v>70.04</v>
+        <v>-180.56</v>
       </c>
       <c r="Q60" s="3">
-        <v>872.54</v>
+        <v>1462.36</v>
       </c>
       <c r="R60" s="3">
-        <v>1001.19</v>
+        <v>2002.19</v>
       </c>
       <c r="S60" s="3">
-        <v>40.01</v>
+        <v>43.62</v>
       </c>
       <c r="T60" s="3">
-        <v>13.01</v>
+        <v>15.62</v>
       </c>
       <c r="U60" s="3">
-        <v>33.26</v>
+        <v>33.32</v>
       </c>
       <c r="V60" s="3">
-        <v>46.77</v>
+        <v>42.15</v>
       </c>
       <c r="W60" s="3">
         <v>0</v>
@@ -5030,67 +5030,67 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D61" s="1">
-        <v>51229.7</v>
+        <v>15451.55</v>
       </c>
       <c r="E61" s="2">
-        <v>0.67</v>
+        <v>-0.56</v>
       </c>
       <c r="F61" s="2">
-        <v>7.51</v>
+        <v>2.21</v>
       </c>
       <c r="G61" s="2">
-        <v>0.49</v>
+        <v>-1.9</v>
       </c>
       <c r="H61" s="2">
-        <v>16.79</v>
+        <v>-6.27</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>47478.26</v>
+        <v>15983.81</v>
       </c>
       <c r="K61" s="1">
-        <v>49810.7</v>
+        <v>15466.21</v>
       </c>
       <c r="L61" s="1">
-        <v>51287.1</v>
+        <v>16055.72</v>
       </c>
       <c r="M61" s="3">
-        <v>-437.68</v>
+        <v>-182.06</v>
       </c>
       <c r="N61" s="3">
-        <v>-678.24</v>
+        <v>-198.34</v>
       </c>
       <c r="O61" s="3">
-        <v>886.66</v>
+        <v>-135.57</v>
       </c>
       <c r="P61" s="3">
-        <v>1418.1</v>
+        <v>17.77</v>
       </c>
       <c r="Q61" s="3">
-        <v>2386.43</v>
+        <v>917.19</v>
       </c>
       <c r="R61" s="3">
-        <v>1514.86</v>
+        <v>1148.12</v>
       </c>
       <c r="S61" s="3">
-        <v>57.12</v>
+        <v>42.14</v>
       </c>
       <c r="T61" s="3">
-        <v>26.75</v>
+        <v>15.48</v>
       </c>
       <c r="U61" s="3">
-        <v>26.92</v>
+        <v>31.86</v>
       </c>
       <c r="V61" s="3">
-        <v>34.29</v>
+        <v>46.27</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -5107,67 +5107,67 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C62" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D62" s="1">
-        <v>22372.15</v>
+        <v>59469.45</v>
       </c>
       <c r="E62" s="2">
-        <v>0.67</v>
+        <v>-0.6</v>
       </c>
       <c r="F62" s="2">
-        <v>2.97</v>
+        <v>4.68</v>
       </c>
       <c r="G62" s="2">
-        <v>-1.73</v>
+        <v>-2.15</v>
       </c>
       <c r="H62" s="2">
-        <v>-7.01</v>
+        <v>-3.95</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>23442.76</v>
+        <v>61613.08</v>
       </c>
       <c r="K62" s="1">
-        <v>22363.01</v>
+        <v>59215.35</v>
       </c>
       <c r="L62" s="1">
-        <v>23452.6</v>
+        <v>61934.69</v>
       </c>
       <c r="M62" s="3">
-        <v>-350.38</v>
+        <v>-862.65</v>
       </c>
       <c r="N62" s="3">
-        <v>-347.06</v>
+        <v>-964.32</v>
       </c>
       <c r="O62" s="3">
-        <v>-308.63</v>
+        <v>-616.1</v>
       </c>
       <c r="P62" s="3">
-        <v>-45.09</v>
+        <v>27.71</v>
       </c>
       <c r="Q62" s="3">
-        <v>1014.96</v>
+        <v>-36.7</v>
       </c>
       <c r="R62" s="3">
-        <v>1357.83</v>
+        <v>-180.27</v>
       </c>
       <c r="S62" s="3">
-        <v>41.66</v>
+        <v>44.97</v>
       </c>
       <c r="T62" s="3">
-        <v>16.35</v>
+        <v>16.9</v>
       </c>
       <c r="U62" s="3">
-        <v>36.05</v>
+        <v>33.24</v>
       </c>
       <c r="V62" s="3">
-        <v>42.77</v>
+        <v>43.69</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -5184,67 +5184,67 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C63" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D63" s="1">
-        <v>11848.45</v>
+        <v>22236.95</v>
       </c>
       <c r="E63" s="2">
-        <v>0.67</v>
+        <v>-0.6</v>
       </c>
       <c r="F63" s="2">
-        <v>3.23</v>
+        <v>2.34</v>
       </c>
       <c r="G63" s="2">
-        <v>-7.15</v>
+        <v>-2.32</v>
       </c>
       <c r="H63" s="2">
-        <v>6.1</v>
+        <v>-7.57</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>12491.03</v>
+        <v>23432.59</v>
       </c>
       <c r="K63" s="1">
-        <v>11866.09</v>
+        <v>22340.09</v>
       </c>
       <c r="L63" s="1">
-        <v>12702.84</v>
+        <v>23403.55</v>
       </c>
       <c r="M63" s="3">
-        <v>-278.82</v>
+        <v>-338.58</v>
       </c>
       <c r="N63" s="3">
-        <v>-283.5</v>
+        <v>-345.36</v>
       </c>
       <c r="O63" s="3">
-        <v>-65.94</v>
+        <v>-319.42</v>
       </c>
       <c r="P63" s="3">
-        <v>149.12</v>
+        <v>-47.25</v>
       </c>
       <c r="Q63" s="3">
-        <v>1136.92</v>
+        <v>1004.18</v>
       </c>
       <c r="R63" s="3">
-        <v>1130.07</v>
+        <v>1355.67</v>
       </c>
       <c r="S63" s="3">
-        <v>40.24</v>
+        <v>39.51</v>
       </c>
       <c r="T63" s="3">
-        <v>12.23</v>
+        <v>15.58</v>
       </c>
       <c r="U63" s="3">
-        <v>32.16</v>
+        <v>35.02</v>
       </c>
       <c r="V63" s="3">
-        <v>38.45</v>
+        <v>42.46</v>
       </c>
       <c r="W63" s="3">
         <v>0</v>
@@ -5261,67 +5261,67 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C64" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D64" s="1">
-        <v>17101.1</v>
+        <v>67709.1</v>
       </c>
       <c r="E64" s="2">
-        <v>0.66</v>
+        <v>-0.61</v>
       </c>
       <c r="F64" s="2">
-        <v>4.37</v>
+        <v>2.86</v>
       </c>
       <c r="G64" s="2">
-        <v>-3.92</v>
+        <v>-2.92</v>
       </c>
       <c r="H64" s="2">
-        <v>2.5</v>
+        <v>-2.39</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>16951.56</v>
+        <v>69944.54</v>
       </c>
       <c r="K64" s="1">
-        <v>17077.21</v>
+        <v>67690.43</v>
       </c>
       <c r="L64" s="1">
-        <v>17928.9</v>
+        <v>70775.28</v>
       </c>
       <c r="M64" s="3">
-        <v>-312.5</v>
+        <v>-960.13</v>
       </c>
       <c r="N64" s="3">
-        <v>-276.51</v>
+        <v>-1062.53</v>
       </c>
       <c r="O64" s="3">
-        <v>97.21</v>
+        <v>-517.69</v>
       </c>
       <c r="P64" s="3">
-        <v>317.62</v>
+        <v>336.15</v>
       </c>
       <c r="Q64" s="3">
-        <v>1312.58</v>
+        <v>2668.22</v>
       </c>
       <c r="R64" s="3">
-        <v>1429.76</v>
+        <v>3183.27</v>
       </c>
       <c r="S64" s="3">
-        <v>41.99</v>
+        <v>42.65</v>
       </c>
       <c r="T64" s="3">
-        <v>19.24</v>
+        <v>16.98</v>
       </c>
       <c r="U64" s="3">
-        <v>41.59</v>
+        <v>31.52</v>
       </c>
       <c r="V64" s="3">
-        <v>40.42</v>
+        <v>45.84</v>
       </c>
       <c r="W64" s="3">
         <v>0</v>
@@ -5338,67 +5338,67 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C65" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D65" s="1">
-        <v>24511.5</v>
+        <v>13546.7</v>
       </c>
       <c r="E65" s="2">
-        <v>0.65</v>
+        <v>-0.61</v>
       </c>
       <c r="F65" s="2">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="G65" s="2">
-        <v>-6.62</v>
+        <v>-1.48</v>
       </c>
       <c r="H65" s="2">
-        <v>8.72</v>
+        <v>-6.39</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>23655.53</v>
+        <v>14115.67</v>
       </c>
       <c r="K65" s="1">
-        <v>24651.6</v>
+        <v>13497.35</v>
       </c>
       <c r="L65" s="1">
-        <v>25925.71</v>
+        <v>13990.21</v>
       </c>
       <c r="M65" s="3">
-        <v>-502.72</v>
+        <v>-139.08</v>
       </c>
       <c r="N65" s="3">
-        <v>-392.62</v>
+        <v>-181.39</v>
       </c>
       <c r="O65" s="3">
-        <v>443.43</v>
+        <v>-200.31</v>
       </c>
       <c r="P65" s="3">
-        <v>767.21</v>
+        <v>-54.23</v>
       </c>
       <c r="Q65" s="3">
-        <v>2299.98</v>
+        <v>88.37</v>
       </c>
       <c r="R65" s="3">
-        <v>2352.69</v>
+        <v>120.86</v>
       </c>
       <c r="S65" s="3">
-        <v>38.42</v>
+        <v>45.97</v>
       </c>
       <c r="T65" s="3">
-        <v>15.17</v>
+        <v>17.32</v>
       </c>
       <c r="U65" s="3">
-        <v>38.84</v>
+        <v>27.47</v>
       </c>
       <c r="V65" s="3">
-        <v>37.88</v>
+        <v>40.54</v>
       </c>
       <c r="W65" s="3">
         <v>0</v>
@@ -5415,67 +5415,67 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C66" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D66" s="1">
-        <v>26710.8</v>
+        <v>43609.2</v>
       </c>
       <c r="E66" s="2">
-        <v>0.64</v>
+        <v>-0.62</v>
       </c>
       <c r="F66" s="2">
-        <v>5.45</v>
+        <v>2.18</v>
       </c>
       <c r="G66" s="2">
-        <v>1.03</v>
+        <v>-2.02</v>
       </c>
       <c r="H66" s="2">
-        <v>17.55</v>
+        <v>-21.39</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>24445.25</v>
+        <v>48651.83</v>
       </c>
       <c r="K66" s="1">
-        <v>26105.26</v>
+        <v>43563.98</v>
       </c>
       <c r="L66" s="1">
-        <v>26420.35</v>
+        <v>45251.75</v>
       </c>
       <c r="M66" s="3">
-        <v>-73.45</v>
+        <v>-613.87</v>
       </c>
       <c r="N66" s="3">
-        <v>-176.46</v>
+        <v>-633.33</v>
       </c>
       <c r="O66" s="3">
-        <v>589.88</v>
+        <v>-1733</v>
       </c>
       <c r="P66" s="3">
-        <v>752.08</v>
+        <v>-1435.79</v>
       </c>
       <c r="Q66" s="3">
-        <v>1863.56</v>
+        <v>-2145.76</v>
       </c>
       <c r="R66" s="3">
-        <v>1625.16</v>
+        <v>-961.97</v>
       </c>
       <c r="S66" s="3">
-        <v>59.67</v>
+        <v>44.2</v>
       </c>
       <c r="T66" s="3">
-        <v>23.11</v>
+        <v>19.89</v>
       </c>
       <c r="U66" s="3">
-        <v>19.36</v>
+        <v>26.78</v>
       </c>
       <c r="V66" s="3">
-        <v>25.64</v>
+        <v>36.26</v>
       </c>
       <c r="W66" s="3">
         <v>0</v>
@@ -5492,67 +5492,67 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D67" s="1">
-        <v>15510.55</v>
+        <v>813.9</v>
       </c>
       <c r="E67" s="2">
-        <v>0.6</v>
+        <v>-0.72</v>
       </c>
       <c r="F67" s="2">
-        <v>3.11</v>
+        <v>3.77</v>
       </c>
       <c r="G67" s="2">
-        <v>-4.78</v>
+        <v>-3.95</v>
       </c>
       <c r="H67" s="2">
-        <v>-3.09</v>
+        <v>-7.3</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>16111.15</v>
+        <v>819.26</v>
       </c>
       <c r="K67" s="1">
-        <v>15571.94</v>
+        <v>809.12</v>
       </c>
       <c r="L67" s="1">
-        <v>16623.16</v>
+        <v>852.43</v>
       </c>
       <c r="M67" s="3">
-        <v>-355.45</v>
+        <v>-12.54</v>
       </c>
       <c r="N67" s="3">
-        <v>-329.01</v>
+        <v>-14.74</v>
       </c>
       <c r="O67" s="3">
-        <v>-87.21</v>
+        <v>-3.7</v>
       </c>
       <c r="P67" s="3">
-        <v>159.67</v>
+        <v>7.43</v>
       </c>
       <c r="Q67" s="3">
-        <v>1537.55</v>
+        <v>2.37</v>
       </c>
       <c r="R67" s="3">
-        <v>1745.84</v>
+        <v>10.05</v>
       </c>
       <c r="S67" s="3">
-        <v>38.16</v>
+        <v>46.45</v>
       </c>
       <c r="T67" s="3">
-        <v>12.31</v>
+        <v>20.85</v>
       </c>
       <c r="U67" s="3">
-        <v>36.04</v>
+        <v>25.77</v>
       </c>
       <c r="V67" s="3">
-        <v>46.06</v>
+        <v>26.21</v>
       </c>
       <c r="W67" s="3">
         <v>0</v>
@@ -5569,67 +5569,67 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D68" s="1">
-        <v>46544.85</v>
+        <v>51617</v>
       </c>
       <c r="E68" s="2">
-        <v>0.58</v>
+        <v>-0.74</v>
       </c>
       <c r="F68" s="2">
-        <v>4.67</v>
+        <v>5.19</v>
       </c>
       <c r="G68" s="2">
-        <v>-2.74</v>
+        <v>-2.41</v>
       </c>
       <c r="H68" s="2">
-        <v>5.82</v>
+        <v>-2.07</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>44963.68</v>
+        <v>52475.71</v>
       </c>
       <c r="K68" s="1">
-        <v>46326.53</v>
+        <v>51486.29</v>
       </c>
       <c r="L68" s="1">
-        <v>48073.62</v>
+        <v>53604.93</v>
       </c>
       <c r="M68" s="3">
-        <v>-636.99</v>
+        <v>-686.16</v>
       </c>
       <c r="N68" s="3">
-        <v>-558.74</v>
+        <v>-745.29</v>
       </c>
       <c r="O68" s="3">
-        <v>542.93</v>
+        <v>-219.3</v>
       </c>
       <c r="P68" s="3">
-        <v>989.98</v>
+        <v>286.57</v>
       </c>
       <c r="Q68" s="3">
-        <v>-287.99</v>
+        <v>-706.74</v>
       </c>
       <c r="R68" s="3">
-        <v>-1009.44</v>
+        <v>-1113.04</v>
       </c>
       <c r="S68" s="3">
-        <v>45.5</v>
+        <v>45.38</v>
       </c>
       <c r="T68" s="3">
-        <v>21.97</v>
+        <v>16.79</v>
       </c>
       <c r="U68" s="3">
-        <v>38.55</v>
+        <v>35.49</v>
       </c>
       <c r="V68" s="3">
-        <v>34.15</v>
+        <v>41.95</v>
       </c>
       <c r="W68" s="3">
         <v>0</v>
@@ -5646,67 +5646,67 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D69" s="1">
-        <v>16193.9</v>
+        <v>24720</v>
       </c>
       <c r="E69" s="2">
-        <v>0.58</v>
+        <v>-0.77</v>
       </c>
       <c r="F69" s="2">
-        <v>5.24</v>
+        <v>4.45</v>
       </c>
       <c r="G69" s="2">
-        <v>0.35</v>
+        <v>-2.66</v>
       </c>
       <c r="H69" s="2">
-        <v>10.61</v>
+        <v>-1.06</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>15469.4</v>
+        <v>25445.13</v>
       </c>
       <c r="K69" s="1">
-        <v>15851.77</v>
+        <v>24671.04</v>
       </c>
       <c r="L69" s="1">
-        <v>16278.68</v>
+        <v>25879.07</v>
       </c>
       <c r="M69" s="3">
-        <v>-122.99</v>
+        <v>-380.41</v>
       </c>
       <c r="N69" s="3">
-        <v>-194.19</v>
+        <v>-412.86</v>
       </c>
       <c r="O69" s="3">
-        <v>158.88</v>
+        <v>-170.35</v>
       </c>
       <c r="P69" s="3">
-        <v>302.57</v>
+        <v>129.72</v>
       </c>
       <c r="Q69" s="3">
-        <v>1033.2</v>
+        <v>85.85</v>
       </c>
       <c r="R69" s="3">
-        <v>1005.11</v>
+        <v>-51.28</v>
       </c>
       <c r="S69" s="3">
-        <v>56.24</v>
+        <v>44.19</v>
       </c>
       <c r="T69" s="3">
-        <v>21.27</v>
+        <v>16.61</v>
       </c>
       <c r="U69" s="3">
-        <v>22.47</v>
+        <v>33.3</v>
       </c>
       <c r="V69" s="3">
-        <v>35.52</v>
+        <v>41.38</v>
       </c>
       <c r="W69" s="3">
         <v>0</v>
@@ -5723,67 +5723,67 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D70" s="1">
-        <v>10352.4</v>
+        <v>48804.05</v>
       </c>
       <c r="E70" s="2">
-        <v>0.54</v>
+        <v>-0.82</v>
       </c>
       <c r="F70" s="2">
-        <v>-0.27</v>
+        <v>4.31</v>
       </c>
       <c r="G70" s="2">
-        <v>-2.47</v>
+        <v>-1.56</v>
       </c>
       <c r="H70" s="2">
-        <v>-15.36</v>
+        <v>2.6</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>11256.08</v>
+        <v>49092.06</v>
       </c>
       <c r="K70" s="1">
-        <v>10442.94</v>
+        <v>48682.28</v>
       </c>
       <c r="L70" s="1">
-        <v>10805.61</v>
+        <v>50408.09</v>
       </c>
       <c r="M70" s="3">
-        <v>-110.36</v>
+        <v>-538.03</v>
       </c>
       <c r="N70" s="3">
-        <v>-118.36</v>
+        <v>-603.71</v>
       </c>
       <c r="O70" s="3">
-        <v>-246.59</v>
+        <v>-90.01</v>
       </c>
       <c r="P70" s="3">
-        <v>-178.35</v>
+        <v>411.02</v>
       </c>
       <c r="Q70" s="3">
-        <v>65.78</v>
+        <v>102.48</v>
       </c>
       <c r="R70" s="3">
-        <v>277.95</v>
+        <v>-290.66</v>
       </c>
       <c r="S70" s="3">
-        <v>39.67</v>
+        <v>45.79</v>
       </c>
       <c r="T70" s="3">
-        <v>14.72</v>
+        <v>18.61</v>
       </c>
       <c r="U70" s="3">
-        <v>30.34</v>
+        <v>33.21</v>
       </c>
       <c r="V70" s="3">
-        <v>31.01</v>
+        <v>42.69</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5800,67 +5800,67 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C71" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D71" s="1">
-        <v>26900.7</v>
+        <v>16513.3</v>
       </c>
       <c r="E71" s="2">
-        <v>0.48</v>
+        <v>-0.86</v>
       </c>
       <c r="F71" s="2">
-        <v>2.19</v>
+        <v>2.78</v>
       </c>
       <c r="G71" s="2">
-        <v>-5.16</v>
-      </c>
-      <c r="H71" t="str">
-        <v/>
+        <v>-3.03</v>
+      </c>
+      <c r="H71" s="2">
+        <v>-4.29</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
-      <c r="J71" t="str">
-        <v/>
+      <c r="J71" s="1">
+        <v>17194.26</v>
       </c>
       <c r="K71" s="1">
-        <v>27132.26</v>
+        <v>16552.01</v>
       </c>
       <c r="L71" s="1">
-        <v>28925.86</v>
+        <v>17451.84</v>
       </c>
       <c r="M71" s="3">
-        <v>-639.56</v>
+        <v>-277.91</v>
       </c>
       <c r="N71" s="3">
-        <v>-567.09</v>
+        <v>-302.83</v>
       </c>
       <c r="O71" s="3">
-        <v>-379.02</v>
+        <v>-143.02</v>
       </c>
       <c r="P71" s="3">
-        <v>50.88</v>
+        <v>94.29</v>
       </c>
       <c r="Q71" s="3">
-        <v>201.96</v>
+        <v>895.63</v>
       </c>
       <c r="R71" s="3">
-        <v>181.67</v>
+        <v>1047.37</v>
       </c>
       <c r="S71" s="3">
-        <v>35.69</v>
+        <v>40.35</v>
       </c>
       <c r="T71" s="3">
-        <v>15.98</v>
+        <v>15.03</v>
       </c>
       <c r="U71" s="3">
-        <v>38.65</v>
+        <v>32.43</v>
       </c>
       <c r="V71" s="3">
-        <v>41.2</v>
+        <v>47.5</v>
       </c>
       <c r="W71" s="3">
         <v>0</v>
@@ -5877,67 +5877,67 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D72" s="1">
-        <v>3474.5</v>
+        <v>25422.7</v>
       </c>
       <c r="E72" s="2">
-        <v>0.39</v>
+        <v>-0.87</v>
       </c>
       <c r="F72" s="2">
-        <v>0.67</v>
+        <v>2.25</v>
       </c>
       <c r="G72" s="2">
-        <v>-1.34</v>
+        <v>-3.31</v>
       </c>
       <c r="H72" s="2">
-        <v>-0.53</v>
+        <v>-9.82</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>3494.77</v>
+        <v>26828.27</v>
       </c>
       <c r="K72" s="1">
-        <v>3468.64</v>
+        <v>25394.01</v>
       </c>
       <c r="L72" s="1">
-        <v>3520.61</v>
+        <v>26782.24</v>
       </c>
       <c r="M72" s="3">
-        <v>-18.47</v>
+        <v>-343.64</v>
       </c>
       <c r="N72" s="3">
-        <v>-18.42</v>
+        <v>-475.1</v>
       </c>
       <c r="O72" s="3">
-        <v>-1.91</v>
+        <v>-368.9</v>
       </c>
       <c r="P72" s="3">
-        <v>11.74</v>
+        <v>-0.89</v>
       </c>
       <c r="Q72" s="3">
-        <v>119.3</v>
+        <v>1493.91</v>
       </c>
       <c r="R72" s="3">
-        <v>142</v>
+        <v>1814.28</v>
       </c>
       <c r="S72" s="3">
-        <v>43.03</v>
+        <v>44.5</v>
       </c>
       <c r="T72" s="3">
-        <v>21.3</v>
+        <v>17.95</v>
       </c>
       <c r="U72" s="3">
-        <v>33.82</v>
+        <v>27.69</v>
       </c>
       <c r="V72" s="3">
-        <v>32.92</v>
+        <v>47.21</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -5954,67 +5954,67 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C73" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D73" s="1">
-        <v>2984.42</v>
+        <v>57301.25</v>
       </c>
       <c r="E73" s="2">
-        <v>0.35</v>
+        <v>-0.93</v>
       </c>
       <c r="F73" s="2">
-        <v>0.63</v>
+        <v>2.69</v>
       </c>
       <c r="G73" s="2">
-        <v>-0.98</v>
+        <v>-3.42</v>
       </c>
       <c r="H73" s="2">
-        <v>0.59</v>
+        <v>-5.26</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>3001.44</v>
+        <v>60195</v>
       </c>
       <c r="K73" s="1">
-        <v>2976.5</v>
+        <v>57552.27</v>
       </c>
       <c r="L73" s="1">
-        <v>3017.81</v>
+        <v>60749.35</v>
       </c>
       <c r="M73" s="3">
-        <v>-13.5</v>
+        <v>-1022.92</v>
       </c>
       <c r="N73" s="3">
-        <v>-14.9</v>
+        <v>-1064.62</v>
       </c>
       <c r="O73" s="3">
-        <v>-2.11</v>
+        <v>-636.7</v>
       </c>
       <c r="P73" s="3">
-        <v>8.65</v>
+        <v>189.65</v>
       </c>
       <c r="Q73" s="3">
-        <v>115.88</v>
+        <v>2847.7</v>
       </c>
       <c r="R73" s="3">
-        <v>133.05</v>
+        <v>3475.46</v>
       </c>
       <c r="S73" s="3">
-        <v>43.84</v>
+        <v>39.25</v>
       </c>
       <c r="T73" s="3">
-        <v>23.11</v>
+        <v>14.83</v>
       </c>
       <c r="U73" s="3">
-        <v>36.09</v>
+        <v>34.99</v>
       </c>
       <c r="V73" s="3">
-        <v>49.27</v>
+        <v>50.27</v>
       </c>
       <c r="W73" s="3">
         <v>0</v>
@@ -6031,67 +6031,67 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D74" s="1">
-        <v>2613.83</v>
+        <v>21047.5</v>
       </c>
       <c r="E74" s="2">
-        <v>0.33</v>
+        <v>-0.93</v>
       </c>
       <c r="F74" s="2">
-        <v>0.7</v>
+        <v>2.21</v>
       </c>
       <c r="G74" s="2">
-        <v>-0.93</v>
+        <v>-3.75</v>
       </c>
       <c r="H74" s="2">
-        <v>0.07</v>
+        <v>-5.52</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
       <c r="J74" s="1">
-        <v>2632.03</v>
+        <v>22139.39</v>
       </c>
       <c r="K74" s="1">
-        <v>2605.94</v>
+        <v>21170.5</v>
       </c>
       <c r="L74" s="1">
-        <v>2641.43</v>
+        <v>22332.19</v>
       </c>
       <c r="M74" s="3">
-        <v>-11.53</v>
+        <v>-375.03</v>
       </c>
       <c r="N74" s="3">
-        <v>-13.07</v>
+        <v>-386.05</v>
       </c>
       <c r="O74" s="3">
-        <v>-3.77</v>
+        <v>-228.87</v>
       </c>
       <c r="P74" s="3">
-        <v>5.17</v>
+        <v>72.83</v>
       </c>
       <c r="Q74" s="3">
-        <v>91.03</v>
+        <v>1690.53</v>
       </c>
       <c r="R74" s="3">
-        <v>106.62</v>
+        <v>2024.72</v>
       </c>
       <c r="S74" s="3">
-        <v>45.37</v>
+        <v>37.77</v>
       </c>
       <c r="T74" s="3">
-        <v>24.34</v>
+        <v>14.2</v>
       </c>
       <c r="U74" s="3">
-        <v>30.73</v>
+        <v>36.01</v>
       </c>
       <c r="V74" s="3">
-        <v>36.66</v>
+        <v>50.35</v>
       </c>
       <c r="W74" s="3">
         <v>0</v>
@@ -6108,67 +6108,67 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C75" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D75" s="1">
-        <v>3075.18</v>
+        <v>8234.85</v>
       </c>
       <c r="E75" s="2">
-        <v>0.32</v>
+        <v>-0.93</v>
       </c>
       <c r="F75" s="2">
-        <v>0.58</v>
+        <v>2.03</v>
       </c>
       <c r="G75" s="2">
-        <v>-0.94</v>
+        <v>2.73</v>
       </c>
       <c r="H75" s="2">
-        <v>0.75</v>
+        <v>-3.5</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>3086.22</v>
+        <v>8558.61</v>
       </c>
       <c r="K75" s="1">
-        <v>3068.07</v>
+        <v>8181.49</v>
       </c>
       <c r="L75" s="1">
-        <v>3109.4</v>
+        <v>8289.69</v>
       </c>
       <c r="M75" s="3">
-        <v>-13.55</v>
+        <v>-10.31</v>
       </c>
       <c r="N75" s="3">
-        <v>-14.82</v>
+        <v>-36.24</v>
       </c>
       <c r="O75" s="3">
-        <v>-0.06</v>
+        <v>-85.64</v>
       </c>
       <c r="P75" s="3">
-        <v>11.1</v>
+        <v>-43.24</v>
       </c>
       <c r="Q75" s="3">
-        <v>119.65</v>
+        <v>574.04</v>
       </c>
       <c r="R75" s="3">
-        <v>136.78</v>
+        <v>685.13</v>
       </c>
       <c r="S75" s="3">
-        <v>43.54</v>
+        <v>52.26</v>
       </c>
       <c r="T75" s="3">
-        <v>21.25</v>
+        <v>25.89</v>
       </c>
       <c r="U75" s="3">
-        <v>36.26</v>
+        <v>20.72</v>
       </c>
       <c r="V75" s="3">
-        <v>48.07</v>
+        <v>15.45</v>
       </c>
       <c r="W75" s="3">
         <v>0</v>
@@ -6185,67 +6185,67 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D76" s="1">
-        <v>842.23</v>
+        <v>34957.9</v>
       </c>
       <c r="E76" s="2">
-        <v>0.32</v>
+        <v>-0.97</v>
       </c>
       <c r="F76" s="2">
-        <v>0.6</v>
+        <v>1.27</v>
       </c>
       <c r="G76" s="2">
-        <v>-1.52</v>
+        <v>-4.58</v>
       </c>
       <c r="H76" s="2">
-        <v>-5.52</v>
+        <v>-1.04</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>872.53</v>
+        <v>37702.62</v>
       </c>
       <c r="K76" s="1">
-        <v>840.66</v>
+        <v>35302.13</v>
       </c>
       <c r="L76" s="1">
-        <v>857.51</v>
+        <v>36973.67</v>
       </c>
       <c r="M76" s="3">
-        <v>-5.6</v>
+        <v>-593.95</v>
       </c>
       <c r="N76" s="3">
-        <v>-6.1</v>
+        <v>-579.38</v>
       </c>
       <c r="O76" s="3">
-        <v>-9.35</v>
+        <v>-709.75</v>
       </c>
       <c r="P76" s="3">
-        <v>-6.39</v>
+        <v>-211.98</v>
       </c>
       <c r="Q76" s="3">
-        <v>-16.89</v>
+        <v>924.81</v>
       </c>
       <c r="R76" s="3">
-        <v>-14.13</v>
+        <v>1226.28</v>
       </c>
       <c r="S76" s="3">
-        <v>38.13</v>
+        <v>36.82</v>
       </c>
       <c r="T76" s="3">
-        <v>19.08</v>
+        <v>13.35</v>
       </c>
       <c r="U76" s="3">
-        <v>35.02</v>
+        <v>33.19</v>
       </c>
       <c r="V76" s="3">
-        <v>52.47</v>
+        <v>37.9</v>
       </c>
       <c r="W76" s="3">
         <v>0</v>
@@ -6262,67 +6262,67 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C77" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D77" s="1">
-        <v>14975.8</v>
+        <v>26621.25</v>
       </c>
       <c r="E77" s="2">
-        <v>0.3</v>
+        <v>-1.04</v>
       </c>
       <c r="F77" s="2">
-        <v>3.16</v>
+        <v>1.13</v>
       </c>
       <c r="G77" s="2">
-        <v>-3.1</v>
-      </c>
-      <c r="H77" s="2">
-        <v>-2.83</v>
+        <v>-6.14</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>15610.51</v>
+        <v>28678.49</v>
       </c>
       <c r="K77" s="1">
-        <v>14913.39</v>
+        <v>27039.35</v>
       </c>
       <c r="L77" s="1">
-        <v>15709.21</v>
+        <v>28843.95</v>
       </c>
       <c r="M77" s="3">
-        <v>-244.27</v>
+        <v>-641.89</v>
       </c>
       <c r="N77" s="3">
-        <v>-271.83</v>
+        <v>-582.05</v>
       </c>
       <c r="O77" s="3">
-        <v>-153.96</v>
+        <v>-401.31</v>
       </c>
       <c r="P77" s="3">
-        <v>46.35</v>
+        <v>46.42</v>
       </c>
       <c r="Q77" s="3">
-        <v>1257.67</v>
+        <v>179.66</v>
       </c>
       <c r="R77" s="3">
-        <v>1446.02</v>
+        <v>177.21</v>
       </c>
       <c r="S77" s="3">
-        <v>42.99</v>
+        <v>33.09</v>
       </c>
       <c r="T77" s="3">
-        <v>15.46</v>
+        <v>14.98</v>
       </c>
       <c r="U77" s="3">
-        <v>34.02</v>
+        <v>37.1</v>
       </c>
       <c r="V77" s="3">
-        <v>49.36</v>
+        <v>41.29</v>
       </c>
       <c r="W77" s="3">
         <v>0</v>
@@ -6339,67 +6339,67 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C78" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D78" s="1">
-        <v>3299.16</v>
+        <v>19500</v>
       </c>
       <c r="E78" s="2">
-        <v>0.27</v>
+        <v>-1.3</v>
       </c>
       <c r="F78" s="2">
-        <v>0.46</v>
+        <v>2.25</v>
       </c>
       <c r="G78" s="2">
-        <v>-0.68</v>
+        <v>-4.48</v>
       </c>
       <c r="H78" s="2">
-        <v>1.77</v>
+        <v>-3.55</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>3296.37</v>
+        <v>20237.85</v>
       </c>
       <c r="K78" s="1">
-        <v>3291.74</v>
+        <v>19678.34</v>
       </c>
       <c r="L78" s="1">
-        <v>3338.8</v>
+        <v>20736.2</v>
       </c>
       <c r="M78" s="3">
-        <v>-14.41</v>
+        <v>-355.95</v>
       </c>
       <c r="N78" s="3">
-        <v>-16.53</v>
+        <v>-348.91</v>
       </c>
       <c r="O78" s="3">
-        <v>4.59</v>
+        <v>-110.7</v>
       </c>
       <c r="P78" s="3">
-        <v>18.1</v>
+        <v>169.64</v>
       </c>
       <c r="Q78" s="3">
-        <v>137.54</v>
+        <v>1556.83</v>
       </c>
       <c r="R78" s="3">
-        <v>154.11</v>
+        <v>1819.11</v>
       </c>
       <c r="S78" s="3">
-        <v>44.35</v>
+        <v>37.16</v>
       </c>
       <c r="T78" s="3">
-        <v>15.83</v>
+        <v>15.49</v>
       </c>
       <c r="U78" s="3">
-        <v>29.16</v>
+        <v>39.86</v>
       </c>
       <c r="V78" s="3">
-        <v>50.1</v>
+        <v>49.22</v>
       </c>
       <c r="W78" s="3">
         <v>0</v>
@@ -6416,67 +6416,67 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C79" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D79" s="1">
-        <v>28529.45</v>
+        <v>52498.6</v>
       </c>
       <c r="E79" s="2">
-        <v>0.24</v>
+        <v>-1.33</v>
       </c>
       <c r="F79" s="2">
-        <v>2.75</v>
+        <v>5.19</v>
       </c>
       <c r="G79" s="2">
-        <v>-5.95</v>
+        <v>-2.92</v>
       </c>
       <c r="H79" s="2">
-        <v>-6.67</v>
+        <v>4.35</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>31335.03</v>
+        <v>52236.42</v>
       </c>
       <c r="K79" s="1">
-        <v>28662.22</v>
+        <v>52662.43</v>
       </c>
       <c r="L79" s="1">
-        <v>30989.9</v>
+        <v>55050.34</v>
       </c>
       <c r="M79" s="3">
-        <v>-796.67</v>
+        <v>-817.44</v>
       </c>
       <c r="N79" s="3">
-        <v>-778.62</v>
+        <v>-785.19</v>
       </c>
       <c r="O79" s="3">
-        <v>-657.44</v>
+        <v>318.54</v>
       </c>
       <c r="P79" s="3">
-        <v>-82.41</v>
+        <v>953.71</v>
       </c>
       <c r="Q79" s="3">
-        <v>1982.18</v>
+        <v>3661.02</v>
       </c>
       <c r="R79" s="3">
-        <v>2396.34</v>
+        <v>3881.04</v>
       </c>
       <c r="S79" s="3">
-        <v>34</v>
+        <v>43.55</v>
       </c>
       <c r="T79" s="3">
-        <v>14.82</v>
+        <v>17.84</v>
       </c>
       <c r="U79" s="3">
-        <v>40.61</v>
+        <v>35.57</v>
       </c>
       <c r="V79" s="3">
-        <v>58.7</v>
+        <v>36.29</v>
       </c>
       <c r="W79" s="3">
         <v>0</v>
@@ -6493,67 +6493,67 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D80" s="1">
-        <v>15627</v>
+        <v>5127.9</v>
       </c>
       <c r="E80" s="2">
-        <v>0.2</v>
+        <v>-1.46</v>
       </c>
       <c r="F80" s="2">
-        <v>3.61</v>
+        <v>4.01</v>
       </c>
       <c r="G80" s="2">
-        <v>-2.44</v>
+        <v>0.75</v>
       </c>
       <c r="H80" s="2">
-        <v>-2.18</v>
+        <v>10.13</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>15991.4</v>
+        <v>5117.37</v>
       </c>
       <c r="K80" s="1">
-        <v>15533.41</v>
+        <v>5131.88</v>
       </c>
       <c r="L80" s="1">
-        <v>16259.44</v>
+        <v>5274.22</v>
       </c>
       <c r="M80" s="3">
-        <v>-219.09</v>
+        <v>-41.02</v>
       </c>
       <c r="N80" s="3">
-        <v>-251.3</v>
+        <v>-45.69</v>
       </c>
       <c r="O80" s="3">
-        <v>-98.84</v>
+        <v>8.54</v>
       </c>
       <c r="P80" s="3">
-        <v>85.4</v>
+        <v>69.3</v>
       </c>
       <c r="Q80" s="3">
-        <v>376.76</v>
+        <v>369.56</v>
       </c>
       <c r="R80" s="3">
-        <v>332.24</v>
+        <v>326.37</v>
       </c>
       <c r="S80" s="3">
-        <v>45.22</v>
+        <v>46.87</v>
       </c>
       <c r="T80" s="3">
-        <v>17.13</v>
+        <v>20.08</v>
       </c>
       <c r="U80" s="3">
-        <v>32.57</v>
+        <v>27.44</v>
       </c>
       <c r="V80" s="3">
-        <v>45.96</v>
+        <v>22.21</v>
       </c>
       <c r="W80" s="3">
         <v>0</v>
@@ -6570,67 +6570,67 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C81" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D81" s="1">
-        <v>1257.69</v>
+        <v>1631.25</v>
       </c>
       <c r="E81" s="2">
-        <v>0.12</v>
+        <v>-1.46</v>
       </c>
       <c r="F81" s="2">
-        <v>0.2</v>
+        <v>4.34</v>
       </c>
       <c r="G81" s="2">
-        <v>-1.22</v>
+        <v>3.04</v>
       </c>
       <c r="H81" s="2">
-        <v>-0.31</v>
+        <v>12.91</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>1268.25</v>
+        <v>1473.5</v>
       </c>
       <c r="K81" s="1">
-        <v>1259.97</v>
+        <v>1616.73</v>
       </c>
       <c r="L81" s="1">
-        <v>1276.45</v>
+        <v>1577.44</v>
       </c>
       <c r="M81" s="3">
-        <v>-6.11</v>
+        <v>16.42</v>
       </c>
       <c r="N81" s="3">
-        <v>-5.46</v>
+        <v>13.96</v>
       </c>
       <c r="O81" s="3">
-        <v>-0.71</v>
+        <v>34.02</v>
       </c>
       <c r="P81" s="3">
-        <v>3.72</v>
+        <v>31.85</v>
       </c>
       <c r="Q81" s="3">
-        <v>20.92</v>
+        <v>-69.55</v>
       </c>
       <c r="R81" s="3">
-        <v>21.88</v>
+        <v>-104.81</v>
       </c>
       <c r="S81" s="3">
-        <v>25.29</v>
+        <v>55.98</v>
       </c>
       <c r="T81" s="3">
-        <v>25.22</v>
+        <v>26.02</v>
       </c>
       <c r="U81" s="3">
-        <v>72.61</v>
+        <v>21.9</v>
       </c>
       <c r="V81" s="3">
-        <v>46.61</v>
+        <v>15.17</v>
       </c>
       <c r="W81" s="3">
         <v>0</v>
@@ -6647,67 +6647,67 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C82" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D82" s="1">
-        <v>3283.49</v>
+        <v>13184.5</v>
       </c>
       <c r="E82" s="2">
-        <v>0.11</v>
+        <v>-1.47</v>
       </c>
       <c r="F82" s="2">
-        <v>0.2</v>
+        <v>1.16</v>
       </c>
       <c r="G82" s="2">
-        <v>-0.76</v>
+        <v>-3.98</v>
       </c>
       <c r="H82" s="2">
-        <v>1.89</v>
+        <v>-4.3</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>3281.57</v>
+        <v>13979.01</v>
       </c>
       <c r="K82" s="1">
-        <v>3281.93</v>
+        <v>13337.97</v>
       </c>
       <c r="L82" s="1">
-        <v>3314.21</v>
+        <v>14133.09</v>
       </c>
       <c r="M82" s="3">
-        <v>-10.22</v>
+        <v>-252.44</v>
       </c>
       <c r="N82" s="3">
-        <v>-11.15</v>
+        <v>-258.05</v>
       </c>
       <c r="O82" s="3">
-        <v>5.36</v>
+        <v>-154.13</v>
       </c>
       <c r="P82" s="3">
-        <v>15.46</v>
+        <v>66.9</v>
       </c>
       <c r="Q82" s="3">
-        <v>140.01</v>
+        <v>856.86</v>
       </c>
       <c r="R82" s="3">
-        <v>155.51</v>
+        <v>998.06</v>
       </c>
       <c r="S82" s="3">
-        <v>36.6</v>
+        <v>35.32</v>
       </c>
       <c r="T82" s="3">
-        <v>13.78</v>
+        <v>12.11</v>
       </c>
       <c r="U82" s="3">
-        <v>38.98</v>
+        <v>34.02</v>
       </c>
       <c r="V82" s="3">
-        <v>50.66</v>
+        <v>46.82</v>
       </c>
       <c r="W82" s="3">
         <v>0</v>
@@ -6724,67 +6724,67 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C83" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D83" s="1">
-        <v>1301.68</v>
+        <v>9363.55</v>
       </c>
       <c r="E83" s="2">
-        <v>0.06</v>
+        <v>-1.63</v>
       </c>
       <c r="F83" s="2">
-        <v>0.11</v>
+        <v>4.92</v>
       </c>
       <c r="G83" s="2">
-        <v>-1.05</v>
+        <v>-2.8</v>
       </c>
       <c r="H83" s="2">
-        <v>0.27</v>
+        <v>8.8</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>1308.08</v>
+        <v>8999.09</v>
       </c>
       <c r="K83" s="1">
-        <v>1304.31</v>
+        <v>9376.42</v>
       </c>
       <c r="L83" s="1">
-        <v>1318.44</v>
+        <v>9732.74</v>
       </c>
       <c r="M83" s="3">
-        <v>-5.26</v>
+        <v>-118.21</v>
       </c>
       <c r="N83" s="3">
-        <v>-4.64</v>
+        <v>-123.66</v>
       </c>
       <c r="O83" s="3">
-        <v>0.43</v>
+        <v>142.74</v>
       </c>
       <c r="P83" s="3">
-        <v>4.57</v>
+        <v>259.64</v>
       </c>
       <c r="Q83" s="3">
-        <v>23.61</v>
+        <v>737.31</v>
       </c>
       <c r="R83" s="3">
-        <v>24.14</v>
+        <v>719.09</v>
       </c>
       <c r="S83" s="3">
-        <v>23.68</v>
+        <v>44.89</v>
       </c>
       <c r="T83" s="3">
-        <v>23.78</v>
+        <v>23.32</v>
       </c>
       <c r="U83" s="3">
-        <v>73.28</v>
+        <v>37.87</v>
       </c>
       <c r="V83" s="3">
-        <v>43.75</v>
+        <v>33.86</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -6801,67 +6801,67 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C84" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D84" s="1">
-        <v>1441.97</v>
+        <v>34525.15</v>
       </c>
       <c r="E84" s="2">
-        <v>0.04</v>
+        <v>-1.78</v>
       </c>
       <c r="F84" s="2">
-        <v>0.11</v>
+        <v>1.78</v>
       </c>
       <c r="G84" s="2">
-        <v>-0.82</v>
+        <v>-5.74</v>
       </c>
       <c r="H84" s="2">
-        <v>1.21</v>
+        <v>-6.07</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>1441.19</v>
+        <v>37023.32</v>
       </c>
       <c r="K84" s="1">
-        <v>1444.09</v>
+        <v>34933.69</v>
       </c>
       <c r="L84" s="1">
-        <v>1455.62</v>
+        <v>37687.62</v>
       </c>
       <c r="M84" s="3">
-        <v>-4.36</v>
+        <v>-890.67</v>
       </c>
       <c r="N84" s="3">
-        <v>-3.77</v>
+        <v>-891.17</v>
       </c>
       <c r="O84" s="3">
-        <v>2.63</v>
+        <v>-482.38</v>
       </c>
       <c r="P84" s="3">
-        <v>6.32</v>
+        <v>139.93</v>
       </c>
       <c r="Q84" s="3">
-        <v>28.85</v>
+        <v>581.04</v>
       </c>
       <c r="R84" s="3">
-        <v>28.49</v>
+        <v>928.37</v>
       </c>
       <c r="S84" s="3">
-        <v>25.88</v>
+        <v>35.61</v>
       </c>
       <c r="T84" s="3">
-        <v>24.99</v>
+        <v>13.77</v>
       </c>
       <c r="U84" s="3">
-        <v>67.65</v>
+        <v>32.08</v>
       </c>
       <c r="V84" s="3">
-        <v>40.17</v>
+        <v>54.33</v>
       </c>
       <c r="W84" s="3">
         <v>0</v>
@@ -6878,67 +6878,67 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C85" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D85" s="1">
-        <v>1596.73</v>
+        <v>18463.6</v>
       </c>
       <c r="E85" s="2">
-        <v>0.03</v>
+        <v>-1.85</v>
       </c>
       <c r="F85" s="2">
-        <v>0.04</v>
+        <v>4.08</v>
       </c>
       <c r="G85" s="2">
-        <v>-0.64</v>
+        <v>-4.06</v>
       </c>
       <c r="H85" s="2">
-        <v>1.9</v>
+        <v>4.23</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>1587.43</v>
+        <v>18203.6</v>
       </c>
       <c r="K85" s="1">
-        <v>1598.94</v>
+        <v>18592.84</v>
       </c>
       <c r="L85" s="1">
-        <v>1607.09</v>
+        <v>19445.85</v>
       </c>
       <c r="M85" s="3">
-        <v>-3.28</v>
+        <v>-297.84</v>
       </c>
       <c r="N85" s="3">
-        <v>-2.62</v>
+        <v>-286.79</v>
       </c>
       <c r="O85" s="3">
-        <v>5.44</v>
+        <v>171.66</v>
       </c>
       <c r="P85" s="3">
-        <v>8.52</v>
+        <v>415.98</v>
       </c>
       <c r="Q85" s="3">
-        <v>34.53</v>
+        <v>855.11</v>
       </c>
       <c r="R85" s="3">
-        <v>33.05</v>
+        <v>855.2</v>
       </c>
       <c r="S85" s="3">
-        <v>27.38</v>
+        <v>41.64</v>
       </c>
       <c r="T85" s="3">
-        <v>18.1</v>
+        <v>21.81</v>
       </c>
       <c r="U85" s="3">
-        <v>66.22</v>
+        <v>39.96</v>
       </c>
       <c r="V85" s="3">
-        <v>35.44</v>
+        <v>36.16</v>
       </c>
       <c r="W85" s="3">
         <v>0</v>
@@ -6955,67 +6955,67 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D86" s="1">
-        <v>7591.75</v>
+        <v>16764.55</v>
       </c>
       <c r="E86" s="2">
-        <v>-0.06</v>
+        <v>-1.97</v>
       </c>
       <c r="F86" s="2">
-        <v>3.19</v>
+        <v>2.32</v>
       </c>
       <c r="G86" s="2">
-        <v>-1.46</v>
+        <v>-5.81</v>
       </c>
       <c r="H86" s="2">
-        <v>-11.77</v>
+        <v>0.48</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
       <c r="J86" s="1">
-        <v>7659.72</v>
+        <v>16951.3</v>
       </c>
       <c r="K86" s="1">
-        <v>7531.36</v>
+        <v>17020.37</v>
       </c>
       <c r="L86" s="1">
-        <v>7713.93</v>
+        <v>17897.26</v>
       </c>
       <c r="M86" s="3">
-        <v>-48.93</v>
+        <v>-318.74</v>
       </c>
       <c r="N86" s="3">
-        <v>-74.02</v>
+        <v>-284.95</v>
       </c>
       <c r="O86" s="3">
-        <v>-69.05</v>
+        <v>70.36</v>
       </c>
       <c r="P86" s="3">
-        <v>-28.89</v>
+        <v>312.25</v>
       </c>
       <c r="Q86" s="3">
-        <v>-286.92</v>
+        <v>1285.74</v>
       </c>
       <c r="R86" s="3">
-        <v>-244.56</v>
+        <v>1424.39</v>
       </c>
       <c r="S86" s="3">
-        <v>50.37</v>
+        <v>36.52</v>
       </c>
       <c r="T86" s="3">
-        <v>18.84</v>
+        <v>17.53</v>
       </c>
       <c r="U86" s="3">
-        <v>23.05</v>
+        <v>41.97</v>
       </c>
       <c r="V86" s="3">
-        <v>23.04</v>
+        <v>40.47</v>
       </c>
       <c r="W86" s="3">
         <v>0</v>
@@ -7032,67 +7032,67 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D87" s="1">
-        <v>25645.6</v>
+        <v>45614.65</v>
       </c>
       <c r="E87" s="2">
-        <v>-0.24</v>
+        <v>-2</v>
       </c>
       <c r="F87" s="2">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="G87" s="2">
-        <v>-2.47</v>
+        <v>-4.69</v>
       </c>
       <c r="H87" s="2">
-        <v>-9.02</v>
+        <v>3.7</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>26844.62</v>
+        <v>44968.77</v>
       </c>
       <c r="K87" s="1">
-        <v>25387.64</v>
+        <v>46197.09</v>
       </c>
       <c r="L87" s="1">
-        <v>26859.08</v>
+        <v>48009.07</v>
       </c>
       <c r="M87" s="3">
-        <v>-372.7</v>
+        <v>-655.83</v>
       </c>
       <c r="N87" s="3">
-        <v>-507.97</v>
+        <v>-578.16</v>
       </c>
       <c r="O87" s="3">
-        <v>-351.12</v>
+        <v>468.73</v>
       </c>
       <c r="P87" s="3">
-        <v>2.67</v>
+        <v>975.14</v>
       </c>
       <c r="Q87" s="3">
-        <v>1511.69</v>
+        <v>-362.2</v>
       </c>
       <c r="R87" s="3">
-        <v>1817.84</v>
+        <v>-1024.28</v>
       </c>
       <c r="S87" s="3">
-        <v>47.52</v>
+        <v>39.63</v>
       </c>
       <c r="T87" s="3">
-        <v>18.76</v>
+        <v>20.04</v>
       </c>
       <c r="U87" s="3">
-        <v>27.9</v>
+        <v>39.83</v>
       </c>
       <c r="V87" s="3">
-        <v>49.2</v>
+        <v>34.07</v>
       </c>
       <c r="W87" s="3">
         <v>0</v>
@@ -7109,67 +7109,67 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D88" s="1">
-        <v>233.35</v>
+        <v>8704.45</v>
       </c>
       <c r="E88" s="2">
-        <v>-1.02</v>
+        <v>-2.01</v>
       </c>
       <c r="F88" s="2">
-        <v>-1.37</v>
+        <v>1.67</v>
       </c>
       <c r="G88" s="2">
-        <v>-1.1</v>
+        <v>-6.17</v>
       </c>
       <c r="H88" s="2">
-        <v>16.68</v>
+        <v>12.35</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>219.97</v>
+        <v>8865.14</v>
       </c>
       <c r="K88" s="1">
-        <v>234.83</v>
+        <v>8849.86</v>
       </c>
       <c r="L88" s="1">
-        <v>229.28</v>
+        <v>9351.92</v>
       </c>
       <c r="M88" s="3">
-        <v>1.34</v>
+        <v>-169.28</v>
       </c>
       <c r="N88" s="3">
-        <v>1.9</v>
+        <v>-154.3</v>
       </c>
       <c r="O88" s="3">
-        <v>4.73</v>
+        <v>32.94</v>
       </c>
       <c r="P88" s="3">
-        <v>3.72</v>
+        <v>191.33</v>
       </c>
       <c r="Q88" s="3">
-        <v>-0.84</v>
+        <v>594.51</v>
       </c>
       <c r="R88" s="3">
-        <v>-4.81</v>
+        <v>521</v>
       </c>
       <c r="S88" s="3">
-        <v>50.07</v>
+        <v>38.32</v>
       </c>
       <c r="T88" s="3">
-        <v>24.88</v>
+        <v>18.41</v>
       </c>
       <c r="U88" s="3">
-        <v>15.32</v>
+        <v>33.12</v>
       </c>
       <c r="V88" s="3">
-        <v>40.7</v>
+        <v>28.82</v>
       </c>
       <c r="W88" s="3">
         <v>0</v>
@@ -7186,67 +7186,67 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C89" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D89" s="1">
-        <v>189.2</v>
+        <v>15196.65</v>
       </c>
       <c r="E89" s="2">
-        <v>-1.05</v>
+        <v>-2.02</v>
       </c>
       <c r="F89" s="2">
-        <v>-1.41</v>
+        <v>1.02</v>
       </c>
       <c r="G89" s="2">
-        <v>-1.15</v>
+        <v>-6.7</v>
       </c>
       <c r="H89" s="2">
-        <v>15.61</v>
+        <v>-5.05</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>179.23</v>
+        <v>16106</v>
       </c>
       <c r="K89" s="1">
-        <v>190.44</v>
+        <v>15503.71</v>
       </c>
       <c r="L89" s="1">
-        <v>185.99</v>
+        <v>16584.85</v>
       </c>
       <c r="M89" s="3">
-        <v>1.06</v>
+        <v>-363.76</v>
       </c>
       <c r="N89" s="3">
-        <v>1.52</v>
+        <v>-335.96</v>
       </c>
       <c r="O89" s="3">
-        <v>3.54</v>
+        <v>-112.25</v>
       </c>
       <c r="P89" s="3">
-        <v>2.7</v>
+        <v>154.66</v>
       </c>
       <c r="Q89" s="3">
-        <v>-2.65</v>
+        <v>1512.51</v>
       </c>
       <c r="R89" s="3">
-        <v>-6.06</v>
+        <v>1740.83</v>
       </c>
       <c r="S89" s="3">
-        <v>49.87</v>
+        <v>33.18</v>
       </c>
       <c r="T89" s="3">
-        <v>24.83</v>
+        <v>11.24</v>
       </c>
       <c r="U89" s="3">
-        <v>15.3</v>
+        <v>38.33</v>
       </c>
       <c r="V89" s="3">
-        <v>40.26</v>
+        <v>46.67</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -7263,67 +7263,67 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>India VIX</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C90" t="str">
-        <v>INDIAVIX</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D90" s="1">
-        <v>15.12</v>
+        <v>23900.8</v>
       </c>
       <c r="E90" s="2">
-        <v>-6.95</v>
+        <v>-2.49</v>
       </c>
       <c r="F90" s="2">
-        <v>-10.32</v>
+        <v>0.31</v>
       </c>
       <c r="G90" s="2">
-        <v>12.08</v>
+        <v>-8.95</v>
       </c>
       <c r="H90" s="2">
-        <v>59.49</v>
+        <v>6.01</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
       <c r="J90" s="1">
-        <v>15.04</v>
+        <v>23661.47</v>
       </c>
       <c r="K90" s="1">
-        <v>15.65</v>
+        <v>24515.09</v>
       </c>
       <c r="L90" s="1">
-        <v>12.98</v>
+        <v>25878</v>
       </c>
       <c r="M90" s="3">
-        <v>0.9</v>
+        <v>-533.68</v>
       </c>
       <c r="N90" s="3">
-        <v>0.88</v>
+        <v>-420.83</v>
       </c>
       <c r="O90" s="3">
-        <v>-0.06</v>
+        <v>394.72</v>
       </c>
       <c r="P90" s="3">
-        <v>-0.6</v>
+        <v>757.46</v>
       </c>
       <c r="Q90" s="3">
-        <v>-0.06</v>
+        <v>2251.26</v>
       </c>
       <c r="R90" s="3">
-        <v>0.03</v>
+        <v>2342.95</v>
       </c>
       <c r="S90" s="3">
-        <v>53.29</v>
+        <v>32.45</v>
       </c>
       <c r="T90" s="3">
-        <v>18.27</v>
+        <v>13.67</v>
       </c>
       <c r="U90" s="3">
-        <v>17.65</v>
+        <v>40.12</v>
       </c>
       <c r="V90" s="3">
-        <v>16.53</v>
+        <v>38.69</v>
       </c>
       <c r="W90" s="3">
         <v>0</v>
